--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA211E19-798A-4D98-8D83-017187B4E30F}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C262CFEA-71E2-46C9-AA3F-B019538C1027}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="361">
   <si>
     <t>Client</t>
   </si>
@@ -1072,6 +1072,57 @@
   </si>
   <si>
     <t>SYTHD260055</t>
+  </si>
+  <si>
+    <t>STANDARD CHARTERED BANK COTE D'IVOIRE SA</t>
+  </si>
+  <si>
+    <t>VALLON&gt;&gt;&gt;VITIB</t>
+  </si>
+  <si>
+    <t>SYTHD260054</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNISERV CI MACORY RESIDENTIE </t>
+  </si>
+  <si>
+    <t>SYTHD260061</t>
+  </si>
+  <si>
+    <t>PALMAFRIQUE</t>
+  </si>
+  <si>
+    <t>ATTINGUIE</t>
+  </si>
+  <si>
+    <t>SYTHD250041</t>
+  </si>
+  <si>
+    <t>Oui</t>
+  </si>
+  <si>
+    <t>RIMCO SETACI</t>
+  </si>
+  <si>
+    <t>SYTHD260064</t>
+  </si>
+  <si>
+    <t>MARCORY&gt;&gt;VITIB</t>
+  </si>
+  <si>
+    <t>SYTHD260012</t>
+  </si>
+  <si>
+    <t>DI</t>
+  </si>
+  <si>
+    <t>HK STUDIO</t>
+  </si>
+  <si>
+    <t>ARTEMIS CONSTRUCTION ET TRAVAUX</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1136,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,##0\ _€"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1176,6 +1227,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1276,7 +1334,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1326,9 +1384,6 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="2" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1370,9 +1425,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1398,14 +1450,29 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1968,10 +2035,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -2289,24 +2352,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T148"/>
+  <dimension ref="A1:T156"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.6328125" style="27" customWidth="1"/>
+    <col min="1" max="1" width="24.6328125" style="26" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.08984375" customWidth="1"/>
     <col min="15" max="15" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.90625" style="19" customWidth="1"/>
+    <col min="17" max="17" width="11.90625" style="18" customWidth="1"/>
     <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.1796875" customWidth="1"/>
     <col min="20" max="20" width="6.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -2336,10 +2399,10 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="L1" s="21" t="s">
         <v>316</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -2354,7 +2417,7 @@
       <c r="P1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="17" t="s">
         <v>14</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -2368,59 +2431,59 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="25" t="s">
         <v>44</v>
       </c>
       <c r="C2" s="9">
         <v>55472663</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="25" t="s">
         <v>155</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="25" t="s">
         <v>47</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="39">
+      <c r="H2" s="37">
         <v>46010</v>
       </c>
-      <c r="I2" s="40">
+      <c r="I2" s="38">
         <v>46015</v>
       </c>
-      <c r="J2" s="25">
+      <c r="J2" s="24">
         <f>+NETWORKDAYS(H2,I2)</f>
         <v>4</v>
       </c>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
       <c r="M2" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="N2" s="26" t="s">
+      <c r="N2" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="33">
+      <c r="O2" s="46">
         <v>0</v>
       </c>
-      <c r="P2" s="33">
+      <c r="P2" s="46">
         <v>0</v>
       </c>
-      <c r="Q2" s="33">
+      <c r="Q2" s="46">
         <f>P2+O2</f>
         <v>0</v>
       </c>
       <c r="R2" s="13">
         <v>46024</v>
       </c>
-      <c r="S2" s="25">
+      <c r="S2" s="24">
         <f>NETWORKDAYS(H2,R2)</f>
         <v>11</v>
       </c>
@@ -2456,32 +2519,32 @@
       <c r="I3" s="14">
         <v>46022</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="24">
         <f t="shared" ref="J3:J66" si="0">+NETWORKDAYS(H3,I3)</f>
         <v>17</v>
       </c>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
       <c r="M3" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N3" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="47">
         <v>1000000</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="47">
         <v>231750</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="48">
         <f>P3+O3</f>
         <v>1231750</v>
       </c>
       <c r="R3" s="13">
         <v>46024</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="24">
         <f t="shared" ref="S3:S66" si="1">NETWORKDAYS(H3,R3)</f>
         <v>19</v>
       </c>
@@ -2490,7 +2553,7 @@
       </c>
     </row>
     <row r="4" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>154</v>
       </c>
       <c r="B4" s="12" t="s">
@@ -2514,35 +2577,35 @@
       <c r="H4" s="14">
         <v>46010</v>
       </c>
-      <c r="I4" s="24">
+      <c r="I4" s="23">
         <v>46024</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="24">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
       <c r="M4" s="13" t="s">
         <v>157</v>
       </c>
       <c r="N4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="20">
+      <c r="O4" s="47">
         <v>0</v>
       </c>
-      <c r="P4" s="20">
+      <c r="P4" s="47">
         <v>0</v>
       </c>
-      <c r="Q4" s="17">
+      <c r="Q4" s="48">
         <f>P4+O4</f>
         <v>0</v>
       </c>
       <c r="R4" s="13">
         <v>46027</v>
       </c>
-      <c r="S4" s="25">
+      <c r="S4" s="24">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -2551,7 +2614,7 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="22" t="s">
         <v>154</v>
       </c>
       <c r="B5" s="12" t="s">
@@ -2578,32 +2641,32 @@
       <c r="I5" s="14">
         <v>46024</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="24">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
       <c r="M5" s="13" t="s">
         <v>157</v>
       </c>
       <c r="N5" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O5" s="20">
+      <c r="O5" s="47">
         <v>0</v>
       </c>
-      <c r="P5" s="20">
+      <c r="P5" s="47">
         <v>0</v>
       </c>
-      <c r="Q5" s="17">
+      <c r="Q5" s="48">
         <f>P5+O5</f>
         <v>0</v>
       </c>
       <c r="R5" s="13">
         <v>46027</v>
       </c>
-      <c r="S5" s="25">
+      <c r="S5" s="24">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -2639,12 +2702,12 @@
       <c r="I6" s="14">
         <v>46027</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="24">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
       <c r="M6" s="13" t="s">
         <v>24</v>
       </c>
@@ -2654,17 +2717,17 @@
       <c r="O6" s="15">
         <v>270000</v>
       </c>
-      <c r="P6" s="5">
+      <c r="P6" s="15">
         <v>71435</v>
       </c>
-      <c r="Q6" s="17">
+      <c r="Q6" s="48">
         <f t="shared" ref="Q6:Q69" si="2">P6+O6</f>
         <v>341435</v>
       </c>
       <c r="R6" s="13">
         <v>46027</v>
       </c>
-      <c r="S6" s="25">
+      <c r="S6" s="24">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
@@ -2700,12 +2763,12 @@
       <c r="I7" s="14">
         <v>46027</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="24">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
       <c r="M7" s="13" t="s">
         <v>24</v>
       </c>
@@ -2718,14 +2781,14 @@
       <c r="P7" s="15">
         <v>40000</v>
       </c>
-      <c r="Q7" s="17">
+      <c r="Q7" s="48">
         <f t="shared" si="2"/>
         <v>190000</v>
       </c>
       <c r="R7" s="13">
         <v>46027</v>
       </c>
-      <c r="S7" s="25">
+      <c r="S7" s="24">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
@@ -2758,35 +2821,35 @@
       <c r="H8" s="14">
         <v>45972</v>
       </c>
-      <c r="I8" s="35">
+      <c r="I8" s="33">
         <v>46017</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="24">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
       <c r="M8" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N8" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="O8" s="20">
+      <c r="O8" s="47">
         <v>3264000</v>
       </c>
-      <c r="P8" s="20">
+      <c r="P8" s="47">
         <v>408000</v>
       </c>
-      <c r="Q8" s="17">
+      <c r="Q8" s="48">
         <f t="shared" si="2"/>
         <v>3672000</v>
       </c>
       <c r="R8" s="13">
         <v>46028</v>
       </c>
-      <c r="S8" s="25">
+      <c r="S8" s="24">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
@@ -2801,7 +2864,7 @@
       <c r="B9" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="27">
         <v>51915231</v>
       </c>
       <c r="D9" s="12" t="s">
@@ -2819,35 +2882,35 @@
       <c r="H9" s="14">
         <v>45944</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="23">
         <v>46027</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="24">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
       <c r="M9" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N9" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O9" s="20">
+      <c r="O9" s="47">
         <v>1800000</v>
       </c>
-      <c r="P9" s="20">
+      <c r="P9" s="47">
         <v>301520</v>
       </c>
-      <c r="Q9" s="17">
+      <c r="Q9" s="48">
         <f t="shared" si="2"/>
         <v>2101520</v>
       </c>
       <c r="R9" s="13">
         <v>46029</v>
       </c>
-      <c r="S9" s="25">
+      <c r="S9" s="24">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
@@ -2880,35 +2943,35 @@
       <c r="H10" s="14">
         <v>46009</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="23">
         <v>46024</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="24">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
       <c r="M10" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N10" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="O10" s="20">
+      <c r="O10" s="47">
         <v>1977000</v>
       </c>
-      <c r="P10" s="20">
+      <c r="P10" s="47">
         <v>0</v>
       </c>
-      <c r="Q10" s="17">
+      <c r="Q10" s="48">
         <f t="shared" si="2"/>
         <v>1977000</v>
       </c>
       <c r="R10" s="13">
         <v>46029</v>
       </c>
-      <c r="S10" s="25">
+      <c r="S10" s="24">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
@@ -2944,32 +3007,32 @@
       <c r="I11" s="14">
         <v>46029</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
       <c r="M11" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N11" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="O11" s="20">
+      <c r="O11" s="47">
         <v>1977000</v>
       </c>
-      <c r="P11" s="20">
+      <c r="P11" s="47">
         <v>0</v>
       </c>
-      <c r="Q11" s="17">
+      <c r="Q11" s="48">
         <f t="shared" si="2"/>
         <v>1977000</v>
       </c>
       <c r="R11" s="13">
         <v>46029</v>
       </c>
-      <c r="S11" s="25">
+      <c r="S11" s="24">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
@@ -2978,7 +3041,7 @@
       </c>
     </row>
     <row r="12" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="22" t="s">
         <v>177</v>
       </c>
       <c r="B12" s="12" t="s">
@@ -3005,32 +3068,32 @@
       <c r="I12" s="14">
         <v>46010</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="24">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
       <c r="M12" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N12" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="O12" s="20">
+      <c r="O12" s="47">
         <v>1500000</v>
       </c>
-      <c r="P12" s="20">
+      <c r="P12" s="47">
         <v>571781</v>
       </c>
-      <c r="Q12" s="17">
+      <c r="Q12" s="48">
         <f t="shared" si="2"/>
         <v>2071781</v>
       </c>
       <c r="R12" s="13">
         <v>46030</v>
       </c>
-      <c r="S12" s="25">
+      <c r="S12" s="24">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
@@ -3039,7 +3102,7 @@
       </c>
     </row>
     <row r="13" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="22" t="s">
         <v>154</v>
       </c>
       <c r="B13" s="12" t="s">
@@ -3060,22 +3123,22 @@
       <c r="G13" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="39">
         <v>46010</v>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="39">
         <v>46030</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="42" t="s">
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="N13" s="20" t="s">
+      <c r="N13" s="19" t="s">
         <v>29</v>
       </c>
       <c r="O13" s="15">
@@ -3084,14 +3147,14 @@
       <c r="P13" s="15">
         <v>0</v>
       </c>
-      <c r="Q13" s="17">
+      <c r="Q13" s="48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R13" s="13">
         <v>46030</v>
       </c>
-      <c r="S13" s="25">
+      <c r="S13" s="24">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
@@ -3100,7 +3163,7 @@
       </c>
     </row>
     <row r="14" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="22" t="s">
         <v>154</v>
       </c>
       <c r="B14" s="12" t="s">
@@ -3121,38 +3184,38 @@
       <c r="G14" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="39">
         <v>46010</v>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="39">
         <v>46030</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="42" t="s">
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="N14" s="20" t="s">
+      <c r="N14" s="19" t="s">
         <v>29</v>
       </c>
       <c r="O14" s="15">
         <v>0</v>
       </c>
-      <c r="P14" s="5">
+      <c r="P14" s="15">
         <v>0</v>
       </c>
-      <c r="Q14" s="17">
+      <c r="Q14" s="48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14" s="13">
         <v>46030</v>
       </c>
-      <c r="S14" s="25">
+      <c r="S14" s="24">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
@@ -3185,35 +3248,35 @@
       <c r="H15" s="14">
         <v>46009</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="23">
         <v>46024</v>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="24">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="42" t="s">
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="40" t="s">
         <v>24</v>
       </c>
       <c r="N15" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="O15" s="20">
+      <c r="O15" s="47">
         <v>847200</v>
       </c>
-      <c r="P15" s="20">
+      <c r="P15" s="47">
         <v>0</v>
       </c>
-      <c r="Q15" s="17">
+      <c r="Q15" s="48">
         <f t="shared" si="2"/>
         <v>847200</v>
       </c>
       <c r="R15" s="13">
         <v>46030</v>
       </c>
-      <c r="S15" s="25">
+      <c r="S15" s="24">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
@@ -3249,32 +3312,32 @@
       <c r="I16" s="14">
         <v>46030</v>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
       <c r="M16" s="11" t="s">
         <v>157</v>
       </c>
       <c r="N16" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O16" s="20">
+      <c r="O16" s="47">
         <v>0</v>
       </c>
-      <c r="P16" s="20">
+      <c r="P16" s="47">
         <v>0</v>
       </c>
-      <c r="Q16" s="17">
+      <c r="Q16" s="48">
         <f>P16+O16</f>
         <v>0</v>
       </c>
       <c r="R16" s="13">
         <v>46030</v>
       </c>
-      <c r="S16" s="25">
+      <c r="S16" s="24">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
@@ -3310,32 +3373,32 @@
       <c r="I17" s="14">
         <v>46030</v>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
       <c r="M17" s="11" t="s">
         <v>157</v>
       </c>
       <c r="N17" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O17" s="17">
+      <c r="O17" s="48">
         <v>0</v>
       </c>
-      <c r="P17" s="17">
+      <c r="P17" s="48">
         <v>0</v>
       </c>
-      <c r="Q17" s="17">
+      <c r="Q17" s="48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R17" s="13">
         <v>46030</v>
       </c>
-      <c r="S17" s="25">
+      <c r="S17" s="24">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
@@ -3371,32 +3434,32 @@
       <c r="I18" s="14">
         <v>46030</v>
       </c>
-      <c r="J18" s="25">
+      <c r="J18" s="24">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
       <c r="M18" s="11" t="s">
         <v>188</v>
       </c>
       <c r="N18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O18" s="43">
+      <c r="O18" s="40">
         <v>0</v>
       </c>
-      <c r="P18" s="20">
+      <c r="P18" s="47">
         <v>1588888</v>
       </c>
-      <c r="Q18" s="17">
+      <c r="Q18" s="48">
         <f t="shared" si="2"/>
         <v>1588888</v>
       </c>
       <c r="R18" s="13">
         <v>46030</v>
       </c>
-      <c r="S18" s="25">
+      <c r="S18" s="24">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
@@ -3432,32 +3495,32 @@
       <c r="I19" s="14">
         <v>46030</v>
       </c>
-      <c r="J19" s="25">
+      <c r="J19" s="24">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
       <c r="M19" s="11" t="s">
         <v>157</v>
       </c>
       <c r="N19" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O19" s="43">
+      <c r="O19" s="40">
         <v>1480000</v>
       </c>
-      <c r="P19" s="20">
+      <c r="P19" s="47">
         <v>0</v>
       </c>
-      <c r="Q19" s="17">
+      <c r="Q19" s="48">
         <f t="shared" si="2"/>
         <v>1480000</v>
       </c>
       <c r="R19" s="13">
         <v>46030</v>
       </c>
-      <c r="S19" s="25">
+      <c r="S19" s="24">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -3472,7 +3535,7 @@
       <c r="B20" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="27">
         <v>55950285</v>
       </c>
       <c r="D20" s="12" t="s">
@@ -3493,32 +3556,32 @@
       <c r="I20" s="14">
         <v>46030</v>
       </c>
-      <c r="J20" s="25">
+      <c r="J20" s="24">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
       <c r="M20" s="11" t="s">
         <v>157</v>
       </c>
       <c r="N20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O20" s="17">
+      <c r="O20" s="48">
         <v>0</v>
       </c>
-      <c r="P20" s="17">
+      <c r="P20" s="48">
         <v>0</v>
       </c>
-      <c r="Q20" s="17">
+      <c r="Q20" s="48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R20" s="13">
         <v>46030</v>
       </c>
-      <c r="S20" s="25">
+      <c r="S20" s="24">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -3554,32 +3617,32 @@
       <c r="I21" s="14">
         <v>46030</v>
       </c>
-      <c r="J21" s="25">
+      <c r="J21" s="24">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
       <c r="M21" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N21" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="O21" s="20">
+      <c r="O21" s="47">
         <v>3000000</v>
       </c>
-      <c r="P21" s="20">
+      <c r="P21" s="47">
         <v>270000</v>
       </c>
-      <c r="Q21" s="17">
+      <c r="Q21" s="48">
         <f t="shared" si="2"/>
         <v>3270000</v>
       </c>
       <c r="R21" s="13">
         <v>46031</v>
       </c>
-      <c r="S21" s="25">
+      <c r="S21" s="24">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
@@ -3615,32 +3678,32 @@
       <c r="I22" s="14">
         <v>46029</v>
       </c>
-      <c r="J22" s="25">
+      <c r="J22" s="24">
         <f t="shared" si="0"/>
         <v>245</v>
       </c>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
       <c r="M22" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N22" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="O22" s="20">
+      <c r="O22" s="47">
         <v>2000000</v>
       </c>
-      <c r="P22" s="20">
+      <c r="P22" s="47">
         <v>380000</v>
       </c>
-      <c r="Q22" s="17">
+      <c r="Q22" s="48">
         <f t="shared" si="2"/>
         <v>2380000</v>
       </c>
       <c r="R22" s="13">
         <v>46035</v>
       </c>
-      <c r="S22" s="25">
+      <c r="S22" s="24">
         <f t="shared" si="1"/>
         <v>249</v>
       </c>
@@ -3676,32 +3739,32 @@
       <c r="I23" s="14">
         <v>46030</v>
       </c>
-      <c r="J23" s="25">
+      <c r="J23" s="24">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="42" t="s">
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="40" t="s">
         <v>157</v>
       </c>
       <c r="N23" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="43">
+      <c r="O23" s="40">
         <v>0</v>
       </c>
-      <c r="P23" s="20">
+      <c r="P23" s="47">
         <v>0</v>
       </c>
-      <c r="Q23" s="17">
+      <c r="Q23" s="48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R23" s="13">
         <v>46035</v>
       </c>
-      <c r="S23" s="25">
+      <c r="S23" s="24">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
@@ -3737,32 +3800,32 @@
       <c r="I24" s="14">
         <v>46030</v>
       </c>
-      <c r="J24" s="25">
+      <c r="J24" s="24">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
       <c r="M24" s="11" t="s">
         <v>157</v>
       </c>
       <c r="N24" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O24" s="20">
+      <c r="O24" s="47">
         <v>0</v>
       </c>
-      <c r="P24" s="20">
+      <c r="P24" s="47">
         <v>0</v>
       </c>
-      <c r="Q24" s="17">
+      <c r="Q24" s="48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R24" s="13">
         <v>46035</v>
       </c>
-      <c r="S24" s="25">
+      <c r="S24" s="24">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
@@ -3798,32 +3861,32 @@
       <c r="I25" s="14">
         <v>46029</v>
       </c>
-      <c r="J25" s="25">
+      <c r="J25" s="24">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
       <c r="M25" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N25" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O25" s="17">
+      <c r="O25" s="48">
         <v>144000</v>
       </c>
-      <c r="P25" s="17">
+      <c r="P25" s="48">
         <v>0</v>
       </c>
-      <c r="Q25" s="17">
+      <c r="Q25" s="48">
         <f t="shared" si="2"/>
         <v>144000</v>
       </c>
       <c r="R25" s="13">
         <v>46035</v>
       </c>
-      <c r="S25" s="25">
+      <c r="S25" s="24">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
@@ -3859,32 +3922,32 @@
       <c r="I26" s="14">
         <v>46029</v>
       </c>
-      <c r="J26" s="25">
+      <c r="J26" s="24">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
       <c r="M26" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N26" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="O26" s="17">
+      <c r="O26" s="48">
         <v>1000000</v>
       </c>
-      <c r="P26" s="17">
+      <c r="P26" s="48">
         <v>0</v>
       </c>
-      <c r="Q26" s="17">
+      <c r="Q26" s="48">
         <f t="shared" si="2"/>
         <v>1000000</v>
       </c>
       <c r="R26" s="13">
         <v>46035</v>
       </c>
-      <c r="S26" s="25">
+      <c r="S26" s="24">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
@@ -3920,32 +3983,32 @@
       <c r="I27" s="14">
         <v>46029</v>
       </c>
-      <c r="J27" s="25">
+      <c r="J27" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
       <c r="M27" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N27" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="O27" s="20">
+      <c r="O27" s="47">
         <v>847200</v>
       </c>
-      <c r="P27" s="20">
+      <c r="P27" s="47">
         <v>0</v>
       </c>
-      <c r="Q27" s="17">
+      <c r="Q27" s="48">
         <f t="shared" si="2"/>
         <v>847200</v>
       </c>
       <c r="R27" s="13">
         <v>46035</v>
       </c>
-      <c r="S27" s="25">
+      <c r="S27" s="24">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
@@ -3981,32 +4044,32 @@
       <c r="I28" s="14">
         <v>46029</v>
       </c>
-      <c r="J28" s="25">
+      <c r="J28" s="24">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
       <c r="M28" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N28" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O28" s="20">
+      <c r="O28" s="47">
         <v>2500000</v>
       </c>
-      <c r="P28" s="20">
+      <c r="P28" s="47">
         <v>280000</v>
       </c>
-      <c r="Q28" s="17">
+      <c r="Q28" s="48">
         <f t="shared" si="2"/>
         <v>2780000</v>
       </c>
       <c r="R28" s="13">
         <v>46035</v>
       </c>
-      <c r="S28" s="25">
+      <c r="S28" s="24">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
@@ -4021,7 +4084,7 @@
       <c r="B29" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="22">
         <v>32892220</v>
       </c>
       <c r="D29" s="12" t="s">
@@ -4042,32 +4105,32 @@
       <c r="I29" s="14">
         <v>45807</v>
       </c>
-      <c r="J29" s="25">
+      <c r="J29" s="24">
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
       <c r="M29" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N29" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="O29" s="20">
+      <c r="O29" s="47">
         <v>32214683</v>
       </c>
-      <c r="P29" s="20">
+      <c r="P29" s="47">
         <v>6403996</v>
       </c>
-      <c r="Q29" s="17">
+      <c r="Q29" s="48">
         <f t="shared" si="2"/>
         <v>38618679</v>
       </c>
       <c r="R29" s="13">
         <v>46036</v>
       </c>
-      <c r="S29" s="25">
+      <c r="S29" s="24">
         <f t="shared" si="1"/>
         <v>366</v>
       </c>
@@ -4103,32 +4166,32 @@
       <c r="I30" s="14">
         <v>46035</v>
       </c>
-      <c r="J30" s="25">
+      <c r="J30" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
       <c r="M30" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N30" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O30" s="17">
+      <c r="O30" s="48">
         <v>150000</v>
       </c>
-      <c r="P30" s="17">
+      <c r="P30" s="48">
         <v>40000</v>
       </c>
-      <c r="Q30" s="17">
+      <c r="Q30" s="48">
         <f t="shared" si="2"/>
         <v>190000</v>
       </c>
       <c r="R30" s="13">
         <v>46036</v>
       </c>
-      <c r="S30" s="25">
+      <c r="S30" s="24">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
@@ -4164,32 +4227,32 @@
       <c r="I31" s="14">
         <v>46035</v>
       </c>
-      <c r="J31" s="25">
+      <c r="J31" s="24">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
       <c r="M31" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N31" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="O31" s="20">
+      <c r="O31" s="47">
         <v>0</v>
       </c>
-      <c r="P31" s="20">
+      <c r="P31" s="47">
         <v>40000</v>
       </c>
-      <c r="Q31" s="17">
+      <c r="Q31" s="48">
         <f t="shared" si="2"/>
         <v>40000</v>
       </c>
       <c r="R31" s="13">
         <v>46036</v>
       </c>
-      <c r="S31" s="25">
+      <c r="S31" s="24">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -4225,32 +4288,32 @@
       <c r="I32" s="14">
         <v>45995</v>
       </c>
-      <c r="J32" s="25">
+      <c r="J32" s="24">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="K32" s="32"/>
-      <c r="L32" s="32"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
       <c r="M32" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N32" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O32" s="20">
+      <c r="O32" s="47">
         <v>1000000</v>
       </c>
-      <c r="P32" s="20">
+      <c r="P32" s="47">
         <v>705164</v>
       </c>
-      <c r="Q32" s="17">
+      <c r="Q32" s="48">
         <f t="shared" si="2"/>
         <v>1705164</v>
       </c>
       <c r="R32" s="13">
         <v>46036</v>
       </c>
-      <c r="S32" s="25">
+      <c r="S32" s="24">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
@@ -4286,32 +4349,32 @@
       <c r="I33" s="14">
         <v>46013</v>
       </c>
-      <c r="J33" s="25">
+      <c r="J33" s="24">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
       <c r="M33" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N33" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="O33" s="20">
+      <c r="O33" s="47">
         <v>0</v>
       </c>
-      <c r="P33" s="20">
+      <c r="P33" s="47">
         <v>170681</v>
       </c>
-      <c r="Q33" s="17">
+      <c r="Q33" s="48">
         <f t="shared" si="2"/>
         <v>170681</v>
       </c>
       <c r="R33" s="13">
         <v>46037</v>
       </c>
-      <c r="S33" s="25">
+      <c r="S33" s="24">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
@@ -4347,32 +4410,32 @@
       <c r="I34" s="14">
         <v>46015</v>
       </c>
-      <c r="J34" s="25">
+      <c r="J34" s="24">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
       <c r="M34" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N34" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O34" s="12">
+      <c r="O34" s="47">
         <v>0</v>
       </c>
-      <c r="P34" s="12">
+      <c r="P34" s="47">
         <v>92730</v>
       </c>
-      <c r="Q34" s="17">
+      <c r="Q34" s="48">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
       <c r="R34" s="13">
         <v>46037</v>
       </c>
-      <c r="S34" s="25">
+      <c r="S34" s="24">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
@@ -4408,32 +4471,32 @@
       <c r="I35" s="14">
         <v>46015</v>
       </c>
-      <c r="J35" s="25">
+      <c r="J35" s="24">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="K35" s="32"/>
-      <c r="L35" s="32"/>
+      <c r="K35" s="31"/>
+      <c r="L35" s="31"/>
       <c r="M35" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N35" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O35" s="12">
+      <c r="O35" s="47">
         <v>0</v>
       </c>
-      <c r="P35" s="12">
+      <c r="P35" s="47">
         <v>92730</v>
       </c>
-      <c r="Q35" s="17">
+      <c r="Q35" s="48">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
       <c r="R35" s="13">
         <v>46037</v>
       </c>
-      <c r="S35" s="25">
+      <c r="S35" s="24">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
@@ -4469,32 +4532,32 @@
       <c r="I36" s="14">
         <v>46015</v>
       </c>
-      <c r="J36" s="25">
+      <c r="J36" s="24">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="31"/>
       <c r="M36" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N36" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O36" s="12">
+      <c r="O36" s="47">
         <v>0</v>
       </c>
-      <c r="P36" s="12">
+      <c r="P36" s="47">
         <v>92730</v>
       </c>
-      <c r="Q36" s="17">
+      <c r="Q36" s="48">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
       <c r="R36" s="13">
         <v>46037</v>
       </c>
-      <c r="S36" s="25">
+      <c r="S36" s="24">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
@@ -4530,32 +4593,32 @@
       <c r="I37" s="14">
         <v>46015</v>
       </c>
-      <c r="J37" s="25">
+      <c r="J37" s="24">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="K37" s="32"/>
-      <c r="L37" s="32"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
       <c r="M37" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N37" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="O37" s="12">
+      <c r="O37" s="47">
         <v>0</v>
       </c>
-      <c r="P37" s="12">
+      <c r="P37" s="47">
         <v>92730</v>
       </c>
-      <c r="Q37" s="17">
+      <c r="Q37" s="48">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
       <c r="R37" s="13">
         <v>46037</v>
       </c>
-      <c r="S37" s="25">
+      <c r="S37" s="24">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
@@ -4570,7 +4633,7 @@
       <c r="B38" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="41">
         <v>54887240</v>
       </c>
       <c r="D38" s="12" t="s">
@@ -4591,32 +4654,32 @@
       <c r="I38" s="14">
         <v>46020</v>
       </c>
-      <c r="J38" s="25">
+      <c r="J38" s="24">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="K38" s="32"/>
-      <c r="L38" s="32"/>
+      <c r="K38" s="31"/>
+      <c r="L38" s="31"/>
       <c r="M38" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N38" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O38" s="20">
+      <c r="O38" s="47">
         <v>2000500</v>
       </c>
-      <c r="P38" s="20">
+      <c r="P38" s="47">
         <v>667054</v>
       </c>
-      <c r="Q38" s="17">
+      <c r="Q38" s="48">
         <f t="shared" si="2"/>
         <v>2667554</v>
       </c>
       <c r="R38" s="13">
         <v>46037</v>
       </c>
-      <c r="S38" s="25">
+      <c r="S38" s="24">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
@@ -4652,32 +4715,32 @@
       <c r="I39" s="14">
         <v>46027</v>
       </c>
-      <c r="J39" s="25">
+      <c r="J39" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K39" s="32"/>
-      <c r="L39" s="32"/>
+      <c r="K39" s="31"/>
+      <c r="L39" s="31"/>
       <c r="M39" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N39" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O39" s="20">
+      <c r="O39" s="47">
         <v>0</v>
       </c>
-      <c r="P39" s="20">
+      <c r="P39" s="47">
         <v>189985</v>
       </c>
-      <c r="Q39" s="17">
+      <c r="Q39" s="48">
         <f t="shared" si="2"/>
         <v>189985</v>
       </c>
       <c r="R39" s="13">
         <v>46038</v>
       </c>
-      <c r="S39" s="25">
+      <c r="S39" s="24">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
@@ -4713,32 +4776,32 @@
       <c r="I40" s="14">
         <v>46015</v>
       </c>
-      <c r="J40" s="25">
+      <c r="J40" s="24">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="K40" s="32"/>
-      <c r="L40" s="32"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
       <c r="M40" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N40" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="O40" s="12">
+      <c r="O40" s="47">
         <v>0</v>
       </c>
-      <c r="P40" s="12">
+      <c r="P40" s="47">
         <v>92730</v>
       </c>
-      <c r="Q40" s="17">
+      <c r="Q40" s="48">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
       <c r="R40" s="13">
         <v>46038</v>
       </c>
-      <c r="S40" s="25">
+      <c r="S40" s="24">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
@@ -4753,7 +4816,7 @@
       <c r="B41" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="27">
         <v>55658281</v>
       </c>
       <c r="D41" s="11" t="s">
@@ -4774,32 +4837,32 @@
       <c r="I41" s="14">
         <v>46036</v>
       </c>
-      <c r="J41" s="25">
+      <c r="J41" s="24">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="31"/>
       <c r="M41" s="11" t="s">
         <v>157</v>
       </c>
       <c r="N41" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="O41" s="17">
+      <c r="O41" s="48">
         <v>0</v>
       </c>
-      <c r="P41" s="17">
+      <c r="P41" s="48">
         <v>0</v>
       </c>
-      <c r="Q41" s="17">
+      <c r="Q41" s="48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R41" s="13">
         <v>46041</v>
       </c>
-      <c r="S41" s="25">
+      <c r="S41" s="24">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
@@ -4835,32 +4898,32 @@
       <c r="I42" s="14">
         <v>46036</v>
       </c>
-      <c r="J42" s="25">
+      <c r="J42" s="24">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="K42" s="32"/>
-      <c r="L42" s="32"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="31"/>
       <c r="M42" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N42" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="O42" s="20">
+      <c r="O42" s="47">
         <v>500000</v>
       </c>
-      <c r="P42" s="20">
+      <c r="P42" s="47">
         <v>500000</v>
       </c>
-      <c r="Q42" s="17">
+      <c r="Q42" s="48">
         <f t="shared" si="2"/>
         <v>1000000</v>
       </c>
       <c r="R42" s="13">
         <v>46041</v>
       </c>
-      <c r="S42" s="25">
+      <c r="S42" s="24">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
@@ -4890,38 +4953,38 @@
       <c r="G43" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H43" s="41">
+      <c r="H43" s="39">
         <v>45953</v>
       </c>
-      <c r="I43" s="45">
+      <c r="I43" s="42">
         <v>46038</v>
       </c>
-      <c r="J43" s="25">
+      <c r="J43" s="24">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="K43" s="32"/>
-      <c r="L43" s="32"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
       <c r="M43" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N43" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O43" s="17">
+      <c r="O43" s="48">
         <v>150000</v>
       </c>
-      <c r="P43" s="17">
+      <c r="P43" s="48">
         <v>60000</v>
       </c>
-      <c r="Q43" s="17">
+      <c r="Q43" s="48">
         <f t="shared" si="2"/>
         <v>210000</v>
       </c>
       <c r="R43" s="13">
         <v>46042</v>
       </c>
-      <c r="S43" s="25">
+      <c r="S43" s="24">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
@@ -4951,38 +5014,38 @@
       <c r="G44" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H44" s="41">
+      <c r="H44" s="39">
         <v>45999</v>
       </c>
-      <c r="I44" s="45">
+      <c r="I44" s="42">
         <v>46030</v>
       </c>
-      <c r="J44" s="25">
+      <c r="J44" s="24">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K44" s="32"/>
-      <c r="L44" s="32"/>
+      <c r="K44" s="31"/>
+      <c r="L44" s="31"/>
       <c r="M44" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N44" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O44" s="17">
+      <c r="O44" s="48">
         <v>150000</v>
       </c>
-      <c r="P44" s="17">
+      <c r="P44" s="48">
         <v>60000</v>
       </c>
-      <c r="Q44" s="17">
+      <c r="Q44" s="48">
         <f t="shared" si="2"/>
         <v>210000</v>
       </c>
       <c r="R44" s="13">
         <v>46042</v>
       </c>
-      <c r="S44" s="25">
+      <c r="S44" s="24">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
@@ -5018,32 +5081,32 @@
       <c r="I45" s="13">
         <v>46041</v>
       </c>
-      <c r="J45" s="25">
+      <c r="J45" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K45" s="32"/>
-      <c r="L45" s="32"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="31"/>
       <c r="M45" s="11" t="s">
         <v>157</v>
       </c>
       <c r="N45" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="O45" s="17">
+      <c r="O45" s="48">
         <v>955437</v>
       </c>
-      <c r="P45" s="17">
+      <c r="P45" s="48">
         <v>0</v>
       </c>
-      <c r="Q45" s="17">
+      <c r="Q45" s="48">
         <f t="shared" si="2"/>
         <v>955437</v>
       </c>
       <c r="R45" s="13">
         <v>46042</v>
       </c>
-      <c r="S45" s="25">
+      <c r="S45" s="24">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -5076,35 +5139,35 @@
       <c r="H46" s="14">
         <v>46008</v>
       </c>
-      <c r="I46" s="24">
+      <c r="I46" s="23">
         <v>46034</v>
       </c>
-      <c r="J46" s="25">
+      <c r="J46" s="24">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="K46" s="32"/>
-      <c r="L46" s="32"/>
+      <c r="K46" s="31"/>
+      <c r="L46" s="31"/>
       <c r="M46" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N46" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="O46" s="17">
+      <c r="O46" s="48">
         <v>500000</v>
       </c>
-      <c r="P46" s="17">
+      <c r="P46" s="48">
         <v>0</v>
       </c>
-      <c r="Q46" s="17">
+      <c r="Q46" s="48">
         <f t="shared" si="2"/>
         <v>500000</v>
       </c>
       <c r="R46" s="13">
         <v>46042</v>
       </c>
-      <c r="S46" s="25">
+      <c r="S46" s="24">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
@@ -5140,32 +5203,32 @@
       <c r="I47" s="14">
         <v>46027</v>
       </c>
-      <c r="J47" s="25">
+      <c r="J47" s="24">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="K47" s="32"/>
-      <c r="L47" s="32"/>
+      <c r="K47" s="31"/>
+      <c r="L47" s="31"/>
       <c r="M47" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N47" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="O47" s="20">
+      <c r="O47" s="47">
         <v>0</v>
       </c>
-      <c r="P47" s="20">
+      <c r="P47" s="47">
         <v>217691</v>
       </c>
-      <c r="Q47" s="17">
+      <c r="Q47" s="48">
         <f t="shared" si="2"/>
         <v>217691</v>
       </c>
       <c r="R47" s="13">
         <v>46043</v>
       </c>
-      <c r="S47" s="25">
+      <c r="S47" s="24">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
@@ -5201,32 +5264,32 @@
       <c r="I48" s="14">
         <v>46029</v>
       </c>
-      <c r="J48" s="25">
+      <c r="J48" s="24">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K48" s="32"/>
-      <c r="L48" s="32"/>
+      <c r="K48" s="31"/>
+      <c r="L48" s="31"/>
       <c r="M48" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N48" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="O48" s="20">
+      <c r="O48" s="47">
         <v>2362401</v>
       </c>
-      <c r="P48" s="20">
+      <c r="P48" s="47">
         <v>300000</v>
       </c>
-      <c r="Q48" s="17">
+      <c r="Q48" s="48">
         <f t="shared" si="2"/>
         <v>2662401</v>
       </c>
       <c r="R48" s="13">
         <v>46043</v>
       </c>
-      <c r="S48" s="25">
+      <c r="S48" s="24">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
@@ -5259,35 +5322,35 @@
       <c r="H49" s="14">
         <v>45996</v>
       </c>
-      <c r="I49" s="24">
+      <c r="I49" s="23">
         <v>46034</v>
       </c>
-      <c r="J49" s="25">
+      <c r="J49" s="24">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="K49" s="32"/>
-      <c r="L49" s="32"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="31"/>
       <c r="M49" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N49" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="O49" s="17">
+      <c r="O49" s="48">
         <v>0</v>
       </c>
-      <c r="P49" s="17">
+      <c r="P49" s="48">
         <v>0</v>
       </c>
-      <c r="Q49" s="17">
+      <c r="Q49" s="48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R49" s="13">
         <v>46043</v>
       </c>
-      <c r="S49" s="25">
+      <c r="S49" s="24">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
@@ -5323,32 +5386,32 @@
       <c r="I50" s="14">
         <v>46043</v>
       </c>
-      <c r="J50" s="25">
+      <c r="J50" s="24">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K50" s="32"/>
-      <c r="L50" s="32"/>
+      <c r="K50" s="31"/>
+      <c r="L50" s="31"/>
       <c r="M50" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N50" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="O50" s="20">
+      <c r="O50" s="47">
         <v>2000000</v>
       </c>
-      <c r="P50" s="20">
+      <c r="P50" s="47">
         <v>646323</v>
       </c>
-      <c r="Q50" s="17">
+      <c r="Q50" s="48">
         <f t="shared" si="2"/>
         <v>2646323</v>
       </c>
       <c r="R50" s="13">
         <v>46044</v>
       </c>
-      <c r="S50" s="25">
+      <c r="S50" s="24">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
@@ -5384,32 +5447,32 @@
       <c r="I51" s="14">
         <v>46041</v>
       </c>
-      <c r="J51" s="25">
+      <c r="J51" s="24">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K51" s="32"/>
-      <c r="L51" s="32"/>
+      <c r="K51" s="31"/>
+      <c r="L51" s="31"/>
       <c r="M51" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N51" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O51" s="20">
+      <c r="O51" s="47">
         <v>0</v>
       </c>
-      <c r="P51" s="20">
+      <c r="P51" s="47">
         <v>0</v>
       </c>
-      <c r="Q51" s="17">
+      <c r="Q51" s="48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R51" s="13">
         <v>46044</v>
       </c>
-      <c r="S51" s="25">
+      <c r="S51" s="24">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
@@ -5445,32 +5508,32 @@
       <c r="I52" s="14">
         <v>46041</v>
       </c>
-      <c r="J52" s="25">
+      <c r="J52" s="24">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K52" s="32"/>
-      <c r="L52" s="32"/>
+      <c r="K52" s="31"/>
+      <c r="L52" s="31"/>
       <c r="M52" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N52" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O52" s="20">
+      <c r="O52" s="47">
         <v>500000</v>
       </c>
-      <c r="P52" s="20">
+      <c r="P52" s="47">
         <v>325000</v>
       </c>
-      <c r="Q52" s="17">
+      <c r="Q52" s="48">
         <f t="shared" si="2"/>
         <v>825000</v>
       </c>
       <c r="R52" s="13">
         <v>46044</v>
       </c>
-      <c r="S52" s="25">
+      <c r="S52" s="24">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
@@ -5506,32 +5569,32 @@
       <c r="I53" s="14">
         <v>46041</v>
       </c>
-      <c r="J53" s="25">
+      <c r="J53" s="24">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-      <c r="K53" s="32"/>
-      <c r="L53" s="32"/>
+      <c r="K53" s="31"/>
+      <c r="L53" s="31"/>
       <c r="M53" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N53" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="O53" s="20">
+      <c r="O53" s="47">
         <v>0</v>
       </c>
-      <c r="P53" s="20">
+      <c r="P53" s="47">
         <v>433989</v>
       </c>
-      <c r="Q53" s="17">
+      <c r="Q53" s="48">
         <f t="shared" si="2"/>
         <v>433989</v>
       </c>
       <c r="R53" s="13">
         <v>46044</v>
       </c>
-      <c r="S53" s="25">
+      <c r="S53" s="24">
         <f t="shared" si="1"/>
         <v>141</v>
       </c>
@@ -5567,32 +5630,32 @@
       <c r="I54" s="13">
         <v>46043</v>
       </c>
-      <c r="J54" s="25">
+      <c r="J54" s="24">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
-      <c r="K54" s="32"/>
-      <c r="L54" s="32"/>
+      <c r="K54" s="31"/>
+      <c r="L54" s="31"/>
       <c r="M54" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N54" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O54" s="17">
+      <c r="O54" s="48">
         <v>150000</v>
       </c>
-      <c r="P54" s="17">
+      <c r="P54" s="48">
         <v>40000</v>
       </c>
-      <c r="Q54" s="17">
+      <c r="Q54" s="48">
         <f t="shared" si="2"/>
         <v>190000</v>
       </c>
       <c r="R54" s="13">
         <v>46044</v>
       </c>
-      <c r="S54" s="25">
+      <c r="S54" s="24">
         <f t="shared" si="1"/>
         <v>150</v>
       </c>
@@ -5628,32 +5691,32 @@
       <c r="I55" s="13">
         <v>46044</v>
       </c>
-      <c r="J55" s="25">
+      <c r="J55" s="24">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="K55" s="32"/>
-      <c r="L55" s="32"/>
+      <c r="K55" s="31"/>
+      <c r="L55" s="31"/>
       <c r="M55" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N55" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O55" s="17">
+      <c r="O55" s="48">
         <v>1000000</v>
       </c>
-      <c r="P55" s="17">
+      <c r="P55" s="48">
         <v>231750</v>
       </c>
-      <c r="Q55" s="17">
+      <c r="Q55" s="48">
         <f t="shared" si="2"/>
         <v>1231750</v>
       </c>
       <c r="R55" s="13">
         <v>46044</v>
       </c>
-      <c r="S55" s="25">
+      <c r="S55" s="24">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
@@ -5689,32 +5752,32 @@
       <c r="I56" s="14">
         <v>46042</v>
       </c>
-      <c r="J56" s="25">
+      <c r="J56" s="24">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="K56" s="32"/>
-      <c r="L56" s="32"/>
+      <c r="K56" s="31"/>
+      <c r="L56" s="31"/>
       <c r="M56" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N56" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="O56" s="20">
+      <c r="O56" s="47">
         <v>133779304</v>
       </c>
-      <c r="P56" s="20">
+      <c r="P56" s="47">
         <v>5620246</v>
       </c>
-      <c r="Q56" s="17">
+      <c r="Q56" s="48">
         <f t="shared" si="2"/>
         <v>139399550</v>
       </c>
       <c r="R56" s="13">
         <v>46045</v>
       </c>
-      <c r="S56" s="25">
+      <c r="S56" s="24">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -5750,32 +5813,32 @@
       <c r="I57" s="14">
         <v>46042</v>
       </c>
-      <c r="J57" s="25">
+      <c r="J57" s="24">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="K57" s="32"/>
-      <c r="L57" s="32"/>
+      <c r="K57" s="31"/>
+      <c r="L57" s="31"/>
       <c r="M57" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N57" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="O57" s="20">
+      <c r="O57" s="47">
         <v>0</v>
       </c>
-      <c r="P57" s="20">
+      <c r="P57" s="47">
         <v>500000</v>
       </c>
-      <c r="Q57" s="17">
+      <c r="Q57" s="48">
         <f t="shared" si="2"/>
         <v>500000</v>
       </c>
       <c r="R57" s="13">
         <v>46045</v>
       </c>
-      <c r="S57" s="25">
+      <c r="S57" s="24">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -5811,32 +5874,32 @@
       <c r="I58" s="14">
         <v>46042</v>
       </c>
-      <c r="J58" s="25">
+      <c r="J58" s="24">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
-      <c r="K58" s="32"/>
-      <c r="L58" s="32"/>
+      <c r="K58" s="31"/>
+      <c r="L58" s="31"/>
       <c r="M58" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N58" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="O58" s="20">
+      <c r="O58" s="47">
         <v>0</v>
       </c>
-      <c r="P58" s="20">
+      <c r="P58" s="47">
         <v>433989</v>
       </c>
-      <c r="Q58" s="17">
+      <c r="Q58" s="48">
         <f t="shared" si="2"/>
         <v>433989</v>
       </c>
       <c r="R58" s="13">
         <v>46045</v>
       </c>
-      <c r="S58" s="25">
+      <c r="S58" s="24">
         <f t="shared" si="1"/>
         <v>142</v>
       </c>
@@ -5872,32 +5935,32 @@
       <c r="I59" s="14">
         <v>46045</v>
       </c>
-      <c r="J59" s="25">
+      <c r="J59" s="24">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-      <c r="K59" s="32"/>
-      <c r="L59" s="32"/>
+      <c r="K59" s="31"/>
+      <c r="L59" s="31"/>
       <c r="M59" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N59" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O59" s="20">
+      <c r="O59" s="47">
         <v>500000</v>
       </c>
-      <c r="P59" s="20">
+      <c r="P59" s="47">
         <v>400000</v>
       </c>
-      <c r="Q59" s="17">
+      <c r="Q59" s="48">
         <f t="shared" si="2"/>
         <v>900000</v>
       </c>
       <c r="R59" s="13">
         <v>46045</v>
       </c>
-      <c r="S59" s="25">
+      <c r="S59" s="24">
         <f t="shared" si="1"/>
         <v>140</v>
       </c>
@@ -5933,32 +5996,32 @@
       <c r="I60" s="14">
         <v>46043</v>
       </c>
-      <c r="J60" s="25">
+      <c r="J60" s="24">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K60" s="32"/>
-      <c r="L60" s="32"/>
+      <c r="K60" s="31"/>
+      <c r="L60" s="31"/>
       <c r="M60" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N60" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="O60" s="20">
+      <c r="O60" s="47">
         <v>1109000</v>
       </c>
-      <c r="P60" s="20">
+      <c r="P60" s="47">
         <v>935000</v>
       </c>
-      <c r="Q60" s="17">
+      <c r="Q60" s="48">
         <f t="shared" si="2"/>
         <v>2044000</v>
       </c>
       <c r="R60" s="13">
         <v>46045</v>
       </c>
-      <c r="S60" s="25">
+      <c r="S60" s="24">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -5973,7 +6036,7 @@
       <c r="B61" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="23">
+      <c r="C61" s="22">
         <v>52894293</v>
       </c>
       <c r="D61" s="12" t="s">
@@ -5994,32 +6057,32 @@
       <c r="I61" s="14">
         <v>46043</v>
       </c>
-      <c r="J61" s="25">
+      <c r="J61" s="24">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="K61" s="32"/>
-      <c r="L61" s="32"/>
+      <c r="K61" s="31"/>
+      <c r="L61" s="31"/>
       <c r="M61" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N61" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O61" s="20">
+      <c r="O61" s="47">
         <v>1670725</v>
       </c>
-      <c r="P61" s="20">
+      <c r="P61" s="47">
         <v>512000</v>
       </c>
-      <c r="Q61" s="17">
+      <c r="Q61" s="48">
         <f t="shared" si="2"/>
         <v>2182725</v>
       </c>
       <c r="R61" s="13">
         <v>46048</v>
       </c>
-      <c r="S61" s="25">
+      <c r="S61" s="24">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
@@ -6055,32 +6118,32 @@
       <c r="I62" s="13">
         <v>46048</v>
       </c>
-      <c r="J62" s="25">
+      <c r="J62" s="24">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="K62" s="32"/>
-      <c r="L62" s="32"/>
+      <c r="K62" s="31"/>
+      <c r="L62" s="31"/>
       <c r="M62" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N62" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="O62" s="17">
+      <c r="O62" s="48">
         <v>200000</v>
       </c>
-      <c r="P62" s="17">
+      <c r="P62" s="48">
         <v>0</v>
       </c>
-      <c r="Q62" s="17">
+      <c r="Q62" s="48">
         <f t="shared" si="2"/>
         <v>200000</v>
       </c>
       <c r="R62" s="13">
         <v>46049</v>
       </c>
-      <c r="S62" s="25">
+      <c r="S62" s="24">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
@@ -6116,32 +6179,32 @@
       <c r="I63" s="13">
         <v>46048</v>
       </c>
-      <c r="J63" s="25">
+      <c r="J63" s="24">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="K63" s="32"/>
-      <c r="L63" s="32"/>
+      <c r="K63" s="31"/>
+      <c r="L63" s="31"/>
       <c r="M63" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N63" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="O63" s="17">
+      <c r="O63" s="48">
         <v>200000</v>
       </c>
-      <c r="P63" s="17">
+      <c r="P63" s="48">
         <v>0</v>
       </c>
-      <c r="Q63" s="17">
+      <c r="Q63" s="48">
         <f t="shared" si="2"/>
         <v>200000</v>
       </c>
       <c r="R63" s="13">
         <v>46049</v>
       </c>
-      <c r="S63" s="25">
+      <c r="S63" s="24">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
@@ -6174,35 +6237,35 @@
       <c r="H64" s="14">
         <v>45952</v>
       </c>
-      <c r="I64" s="24">
+      <c r="I64" s="23">
         <v>46041</v>
       </c>
-      <c r="J64" s="25">
+      <c r="J64" s="24">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="K64" s="32"/>
-      <c r="L64" s="32"/>
+      <c r="K64" s="31"/>
+      <c r="L64" s="31"/>
       <c r="M64" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N64" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="O64" s="12">
+      <c r="O64" s="47">
         <v>0</v>
       </c>
-      <c r="P64" s="12">
+      <c r="P64" s="47">
         <v>170681</v>
       </c>
-      <c r="Q64" s="17">
+      <c r="Q64" s="48">
         <f t="shared" si="2"/>
         <v>170681</v>
       </c>
       <c r="R64" s="13">
         <v>46049</v>
       </c>
-      <c r="S64" s="25">
+      <c r="S64" s="24">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
@@ -6238,32 +6301,32 @@
       <c r="I65" s="14">
         <v>46044</v>
       </c>
-      <c r="J65" s="25">
+      <c r="J65" s="24">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="K65" s="32"/>
-      <c r="L65" s="32"/>
+      <c r="K65" s="31"/>
+      <c r="L65" s="31"/>
       <c r="M65" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N65" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O65" s="20">
+      <c r="O65" s="47">
         <v>0</v>
       </c>
-      <c r="P65" s="20">
+      <c r="P65" s="47">
         <v>546923</v>
       </c>
-      <c r="Q65" s="17">
+      <c r="Q65" s="48">
         <f t="shared" si="2"/>
         <v>546923</v>
       </c>
       <c r="R65" s="13">
         <v>46049</v>
       </c>
-      <c r="S65" s="25">
+      <c r="S65" s="24">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
@@ -6278,7 +6341,7 @@
       <c r="B66" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C66" s="28">
+      <c r="C66" s="27">
         <v>52396779</v>
       </c>
       <c r="D66" s="12" t="s">
@@ -6293,38 +6356,38 @@
       <c r="G66" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H66" s="24">
+      <c r="H66" s="23">
         <v>46014</v>
       </c>
       <c r="I66" s="14">
         <v>46030</v>
       </c>
-      <c r="J66" s="25">
+      <c r="J66" s="24">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="K66" s="32"/>
-      <c r="L66" s="32"/>
+      <c r="K66" s="31"/>
+      <c r="L66" s="31"/>
       <c r="M66" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N66" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O66" s="17">
+      <c r="O66" s="48">
         <v>0</v>
       </c>
-      <c r="P66" s="20">
+      <c r="P66" s="47">
         <v>92730</v>
       </c>
-      <c r="Q66" s="17">
+      <c r="Q66" s="48">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
       <c r="R66" s="13">
         <v>46049</v>
       </c>
-      <c r="S66" s="25">
+      <c r="S66" s="24">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
@@ -6360,32 +6423,32 @@
       <c r="I67" s="14">
         <v>46049</v>
       </c>
-      <c r="J67" s="25">
+      <c r="J67" s="24">
         <f t="shared" ref="J67:J75" si="3">+NETWORKDAYS(H67,I67)</f>
         <v>46</v>
       </c>
-      <c r="K67" s="32"/>
-      <c r="L67" s="32"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="31"/>
       <c r="M67" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N67" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="O67" s="20">
+      <c r="O67" s="47">
         <v>855000</v>
       </c>
-      <c r="P67" s="20">
+      <c r="P67" s="47">
         <v>196700</v>
       </c>
-      <c r="Q67" s="17">
+      <c r="Q67" s="48">
         <f t="shared" si="2"/>
         <v>1051700</v>
       </c>
       <c r="R67" s="13">
         <v>46049</v>
       </c>
-      <c r="S67" s="25">
+      <c r="S67" s="24">
         <f t="shared" ref="S67:S75" si="4">NETWORKDAYS(H67,R67)</f>
         <v>46</v>
       </c>
@@ -6421,32 +6484,32 @@
       <c r="I68" s="13">
         <v>46048</v>
       </c>
-      <c r="J68" s="25">
+      <c r="J68" s="24">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="K68" s="32"/>
-      <c r="L68" s="32"/>
+      <c r="K68" s="31"/>
+      <c r="L68" s="31"/>
       <c r="M68" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N68" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O68" s="17">
+      <c r="O68" s="48">
         <v>150000</v>
       </c>
-      <c r="P68" s="17">
+      <c r="P68" s="48">
         <v>60000</v>
       </c>
-      <c r="Q68" s="17">
+      <c r="Q68" s="48">
         <f t="shared" si="2"/>
         <v>210000</v>
       </c>
       <c r="R68" s="13">
         <v>46049</v>
       </c>
-      <c r="S68" s="25">
+      <c r="S68" s="24">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
@@ -6482,32 +6545,32 @@
       <c r="I69" s="14">
         <v>46044</v>
       </c>
-      <c r="J69" s="25">
+      <c r="J69" s="24">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="K69" s="32"/>
-      <c r="L69" s="32"/>
+      <c r="K69" s="31"/>
+      <c r="L69" s="31"/>
       <c r="M69" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N69" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O69" s="20">
+      <c r="O69" s="47">
         <v>1200000</v>
       </c>
-      <c r="P69" s="20">
+      <c r="P69" s="47">
         <v>525090</v>
       </c>
-      <c r="Q69" s="17">
+      <c r="Q69" s="48">
         <f t="shared" si="2"/>
         <v>1725090</v>
       </c>
       <c r="R69" s="13">
         <v>46050</v>
       </c>
-      <c r="S69" s="25">
+      <c r="S69" s="24">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
@@ -6516,7 +6579,7 @@
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A70" s="23" t="s">
+      <c r="A70" s="22" t="s">
         <v>288</v>
       </c>
       <c r="B70" s="12" t="s">
@@ -6543,32 +6606,32 @@
       <c r="I70" s="14">
         <v>46048</v>
       </c>
-      <c r="J70" s="25">
+      <c r="J70" s="24">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="K70" s="32"/>
-      <c r="L70" s="32"/>
+      <c r="K70" s="31"/>
+      <c r="L70" s="31"/>
       <c r="M70" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N70" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O70" s="20">
+      <c r="O70" s="47">
         <v>3026000</v>
       </c>
-      <c r="P70" s="20">
+      <c r="P70" s="47">
         <v>250000</v>
       </c>
-      <c r="Q70" s="17">
+      <c r="Q70" s="48">
         <f t="shared" ref="Q70:Q75" si="5">P70+O70</f>
         <v>3276000</v>
       </c>
       <c r="R70" s="13">
         <v>46050</v>
       </c>
-      <c r="S70" s="25">
+      <c r="S70" s="24">
         <f t="shared" si="4"/>
         <v>38</v>
       </c>
@@ -6604,32 +6667,32 @@
       <c r="I71" s="13">
         <v>46050</v>
       </c>
-      <c r="J71" s="25">
+      <c r="J71" s="24">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="K71" s="32"/>
-      <c r="L71" s="32"/>
+      <c r="K71" s="31"/>
+      <c r="L71" s="31"/>
       <c r="M71" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N71" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="O71" s="17">
+      <c r="O71" s="48">
         <v>270000</v>
       </c>
-      <c r="P71" s="17">
+      <c r="P71" s="48">
         <v>111435</v>
       </c>
-      <c r="Q71" s="17">
+      <c r="Q71" s="48">
         <f t="shared" si="5"/>
         <v>381435</v>
       </c>
       <c r="R71" s="13">
         <v>46051</v>
       </c>
-      <c r="S71" s="25">
+      <c r="S71" s="24">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
@@ -6665,32 +6728,32 @@
       <c r="I72" s="13">
         <v>46050</v>
       </c>
-      <c r="J72" s="25">
+      <c r="J72" s="24">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="K72" s="32"/>
-      <c r="L72" s="32"/>
+      <c r="K72" s="31"/>
+      <c r="L72" s="31"/>
       <c r="M72" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N72" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O72" s="17">
+      <c r="O72" s="48">
         <v>150000</v>
       </c>
-      <c r="P72" s="17">
+      <c r="P72" s="48">
         <v>60000</v>
       </c>
-      <c r="Q72" s="17">
+      <c r="Q72" s="48">
         <f t="shared" si="5"/>
         <v>210000</v>
       </c>
       <c r="R72" s="13">
         <v>46051</v>
       </c>
-      <c r="S72" s="25">
+      <c r="S72" s="24">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
@@ -6705,7 +6768,7 @@
       <c r="B73" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C73" s="46">
+      <c r="C73" s="43">
         <v>52573790</v>
       </c>
       <c r="D73" s="12" t="s">
@@ -6726,32 +6789,32 @@
       <c r="I73" s="14">
         <v>46041</v>
       </c>
-      <c r="J73" s="25">
+      <c r="J73" s="24">
         <f t="shared" si="3"/>
         <v>64</v>
       </c>
-      <c r="K73" s="32"/>
-      <c r="L73" s="32"/>
+      <c r="K73" s="31"/>
+      <c r="L73" s="31"/>
       <c r="M73" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N73" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="O73" s="20">
+      <c r="O73" s="47">
         <v>0</v>
       </c>
-      <c r="P73" s="20">
+      <c r="P73" s="47">
         <v>217691</v>
       </c>
-      <c r="Q73" s="17">
+      <c r="Q73" s="48">
         <f t="shared" si="5"/>
         <v>217691</v>
       </c>
       <c r="R73" s="13">
         <v>46051</v>
       </c>
-      <c r="S73" s="25">
+      <c r="S73" s="24">
         <f t="shared" si="4"/>
         <v>72</v>
       </c>
@@ -6766,7 +6829,7 @@
       <c r="B74" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C74" s="23">
+      <c r="C74" s="22">
         <v>53798113</v>
       </c>
       <c r="D74" s="12" t="s">
@@ -6787,32 +6850,32 @@
       <c r="I74" s="14">
         <v>46042</v>
       </c>
-      <c r="J74" s="25">
+      <c r="J74" s="24">
         <f t="shared" si="3"/>
         <v>43</v>
       </c>
-      <c r="K74" s="32"/>
-      <c r="L74" s="32"/>
+      <c r="K74" s="31"/>
+      <c r="L74" s="31"/>
       <c r="M74" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N74" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O74" s="17">
+      <c r="O74" s="48">
         <v>1793983</v>
       </c>
-      <c r="P74" s="17">
+      <c r="P74" s="48">
         <v>200000</v>
       </c>
-      <c r="Q74" s="17">
+      <c r="Q74" s="48">
         <f t="shared" si="5"/>
         <v>1993983</v>
       </c>
       <c r="R74" s="13">
         <v>46051</v>
       </c>
-      <c r="S74" s="25">
+      <c r="S74" s="24">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
@@ -6827,7 +6890,7 @@
       <c r="B75" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C75" s="23">
+      <c r="C75" s="22">
         <v>52566880</v>
       </c>
       <c r="D75" s="12" t="s">
@@ -6848,32 +6911,32 @@
       <c r="I75" s="14">
         <v>46044</v>
       </c>
-      <c r="J75" s="25">
+      <c r="J75" s="24">
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
-      <c r="K75" s="32"/>
-      <c r="L75" s="32"/>
+      <c r="K75" s="31"/>
+      <c r="L75" s="31"/>
       <c r="M75" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N75" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O75" s="20">
+      <c r="O75" s="47">
         <v>0</v>
       </c>
-      <c r="P75" s="20">
+      <c r="P75" s="47">
         <v>540923</v>
       </c>
-      <c r="Q75" s="17">
+      <c r="Q75" s="48">
         <f t="shared" si="5"/>
         <v>540923</v>
       </c>
       <c r="R75" s="13">
         <v>46051</v>
       </c>
-      <c r="S75" s="25">
+      <c r="S75" s="24">
         <f t="shared" si="4"/>
         <v>70</v>
       </c>
@@ -6909,32 +6972,32 @@
       <c r="I76" s="14">
         <v>46045</v>
       </c>
-      <c r="J76" s="25">
+      <c r="J76" s="24">
         <f>+NETWORKDAYS(H76,I76)</f>
         <v>27</v>
       </c>
-      <c r="K76" s="32"/>
-      <c r="L76" s="32"/>
+      <c r="K76" s="31"/>
+      <c r="L76" s="31"/>
       <c r="M76" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N76" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O76" s="20">
+      <c r="O76" s="47">
         <v>500000</v>
       </c>
-      <c r="P76" s="20">
+      <c r="P76" s="47">
         <v>819491</v>
       </c>
-      <c r="Q76" s="17">
+      <c r="Q76" s="48">
         <f>P76+O76</f>
         <v>1319491</v>
       </c>
       <c r="R76" s="13">
         <v>46052</v>
       </c>
-      <c r="S76" s="25">
+      <c r="S76" s="24">
         <f>NETWORKDAYS(H76,R76)</f>
         <v>32</v>
       </c>
@@ -6970,32 +7033,32 @@
       <c r="I77" s="14">
         <v>46042</v>
       </c>
-      <c r="J77" s="25">
+      <c r="J77" s="24">
         <f t="shared" ref="J77:J140" si="6">+NETWORKDAYS(H77,I77)</f>
         <v>21</v>
       </c>
-      <c r="K77" s="32"/>
-      <c r="L77" s="32"/>
+      <c r="K77" s="31"/>
+      <c r="L77" s="31"/>
       <c r="M77" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N77" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="O77" s="20">
+      <c r="O77" s="47">
         <v>1000000</v>
       </c>
-      <c r="P77" s="20">
+      <c r="P77" s="47">
         <v>300000</v>
       </c>
-      <c r="Q77" s="33">
+      <c r="Q77" s="46">
         <f t="shared" ref="Q77:Q97" si="7">P77+O77</f>
         <v>1300000</v>
       </c>
       <c r="R77" s="13">
         <v>46055</v>
       </c>
-      <c r="S77" s="25">
+      <c r="S77" s="24">
         <f t="shared" ref="S77:S140" si="8">NETWORKDAYS(H77,R77)</f>
         <v>30</v>
       </c>
@@ -7031,32 +7094,32 @@
       <c r="I78" s="14">
         <v>46042</v>
       </c>
-      <c r="J78" s="25">
+      <c r="J78" s="24">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="K78" s="32"/>
-      <c r="L78" s="32"/>
+      <c r="K78" s="31"/>
+      <c r="L78" s="31"/>
       <c r="M78" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N78" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O78" s="20">
+      <c r="O78" s="47">
         <v>500000</v>
       </c>
-      <c r="P78" s="20">
+      <c r="P78" s="47">
         <v>892535</v>
       </c>
-      <c r="Q78" s="33">
+      <c r="Q78" s="46">
         <f t="shared" si="7"/>
         <v>1392535</v>
       </c>
       <c r="R78" s="13">
         <v>46055</v>
       </c>
-      <c r="S78" s="25">
+      <c r="S78" s="24">
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
@@ -7092,32 +7155,32 @@
       <c r="I79" s="13">
         <v>46052</v>
       </c>
-      <c r="J79" s="25">
+      <c r="J79" s="24">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="K79" s="32"/>
-      <c r="L79" s="32"/>
+      <c r="K79" s="31"/>
+      <c r="L79" s="31"/>
       <c r="M79" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N79" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="O79" s="20">
+      <c r="O79" s="47">
         <v>150000</v>
       </c>
-      <c r="P79" s="20">
+      <c r="P79" s="47">
         <v>40000</v>
       </c>
-      <c r="Q79" s="33">
+      <c r="Q79" s="46">
         <f t="shared" si="7"/>
         <v>190000</v>
       </c>
       <c r="R79" s="13">
         <v>46055</v>
       </c>
-      <c r="S79" s="25">
+      <c r="S79" s="24">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
@@ -7153,32 +7216,32 @@
       <c r="I80" s="14">
         <v>46044</v>
       </c>
-      <c r="J80" s="25">
+      <c r="J80" s="24">
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="K80" s="32"/>
-      <c r="L80" s="32"/>
+      <c r="K80" s="31"/>
+      <c r="L80" s="31"/>
       <c r="M80" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N80" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O80" s="20">
+      <c r="O80" s="47">
         <v>500000</v>
       </c>
-      <c r="P80" s="20">
+      <c r="P80" s="47">
         <v>391740</v>
       </c>
-      <c r="Q80" s="33">
+      <c r="Q80" s="46">
         <f t="shared" si="7"/>
         <v>891740</v>
       </c>
       <c r="R80" s="13">
         <v>46055</v>
       </c>
-      <c r="S80" s="25">
+      <c r="S80" s="24">
         <f t="shared" si="8"/>
         <v>32</v>
       </c>
@@ -7214,32 +7277,32 @@
       <c r="I81" s="14">
         <v>46044</v>
       </c>
-      <c r="J81" s="25">
+      <c r="J81" s="24">
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="K81" s="32"/>
-      <c r="L81" s="32"/>
+      <c r="K81" s="31"/>
+      <c r="L81" s="31"/>
       <c r="M81" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N81" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O81" s="20">
+      <c r="O81" s="47">
         <v>788712</v>
       </c>
-      <c r="P81" s="20">
+      <c r="P81" s="47">
         <v>500000</v>
       </c>
-      <c r="Q81" s="33">
+      <c r="Q81" s="46">
         <f t="shared" si="7"/>
         <v>1288712</v>
       </c>
       <c r="R81" s="13">
         <v>46055</v>
       </c>
-      <c r="S81" s="25">
+      <c r="S81" s="24">
         <f t="shared" si="8"/>
         <v>32</v>
       </c>
@@ -7275,32 +7338,32 @@
       <c r="I82" s="13">
         <v>46040</v>
       </c>
-      <c r="J82" s="25">
+      <c r="J82" s="24">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="K82" s="32"/>
-      <c r="L82" s="32"/>
+      <c r="K82" s="31"/>
+      <c r="L82" s="31"/>
       <c r="M82" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N82" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="O82" s="34">
+      <c r="O82" s="32">
         <v>570000</v>
       </c>
-      <c r="P82" s="7">
+      <c r="P82" s="32">
         <v>221635</v>
       </c>
-      <c r="Q82" s="33">
+      <c r="Q82" s="46">
         <f t="shared" si="7"/>
         <v>791635</v>
       </c>
       <c r="R82" s="13">
         <v>46057</v>
       </c>
-      <c r="S82" s="25">
+      <c r="S82" s="24">
         <f t="shared" si="8"/>
         <v>36</v>
       </c>
@@ -7336,12 +7399,12 @@
       <c r="I83" s="14">
         <v>46051</v>
       </c>
-      <c r="J83" s="25">
+      <c r="J83" s="24">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="K83" s="32"/>
-      <c r="L83" s="32"/>
+      <c r="K83" s="31"/>
+      <c r="L83" s="31"/>
       <c r="M83" s="13" t="s">
         <v>48</v>
       </c>
@@ -7354,14 +7417,14 @@
       <c r="P83" s="15">
         <v>0</v>
       </c>
-      <c r="Q83" s="17">
+      <c r="Q83" s="48">
         <f t="shared" si="7"/>
         <v>200000</v>
       </c>
       <c r="R83" s="13">
         <v>46058</v>
       </c>
-      <c r="S83" s="25">
+      <c r="S83" s="24">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
@@ -7397,12 +7460,12 @@
       <c r="I84" s="14">
         <v>46051</v>
       </c>
-      <c r="J84" s="25">
+      <c r="J84" s="24">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="K84" s="32"/>
-      <c r="L84" s="32"/>
+      <c r="K84" s="31"/>
+      <c r="L84" s="31"/>
       <c r="M84" s="13" t="s">
         <v>48</v>
       </c>
@@ -7412,17 +7475,17 @@
       <c r="O84" s="15">
         <v>200000</v>
       </c>
-      <c r="P84" s="20">
+      <c r="P84" s="47">
         <v>0</v>
       </c>
-      <c r="Q84" s="17">
+      <c r="Q84" s="48">
         <f t="shared" si="7"/>
         <v>200000</v>
       </c>
       <c r="R84" s="13">
         <v>46058</v>
       </c>
-      <c r="S84" s="25">
+      <c r="S84" s="24">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
@@ -7458,32 +7521,32 @@
       <c r="I85" s="14">
         <v>46027</v>
       </c>
-      <c r="J85" s="25">
+      <c r="J85" s="24">
         <f t="shared" si="6"/>
         <v>47</v>
       </c>
-      <c r="K85" s="32"/>
-      <c r="L85" s="32"/>
+      <c r="K85" s="31"/>
+      <c r="L85" s="31"/>
       <c r="M85" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N85" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O85" s="20">
+      <c r="O85" s="47">
         <v>0</v>
       </c>
-      <c r="P85" s="20">
+      <c r="P85" s="47">
         <v>0</v>
       </c>
-      <c r="Q85" s="17">
+      <c r="Q85" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R85" s="13">
         <v>46058</v>
       </c>
-      <c r="S85" s="25">
+      <c r="S85" s="24">
         <f t="shared" si="8"/>
         <v>70</v>
       </c>
@@ -7519,32 +7582,32 @@
       <c r="I86" s="14">
         <v>46055</v>
       </c>
-      <c r="J86" s="25">
+      <c r="J86" s="24">
         <f t="shared" si="6"/>
         <v>39</v>
       </c>
-      <c r="K86" s="32"/>
-      <c r="L86" s="32"/>
+      <c r="K86" s="31"/>
+      <c r="L86" s="31"/>
       <c r="M86" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N86" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="O86" s="20">
+      <c r="O86" s="47">
         <v>360000</v>
       </c>
-      <c r="P86" s="20">
+      <c r="P86" s="47">
         <v>152495</v>
       </c>
-      <c r="Q86" s="33">
+      <c r="Q86" s="46">
         <f t="shared" si="7"/>
         <v>512495</v>
       </c>
       <c r="R86" s="14">
         <v>46058</v>
       </c>
-      <c r="S86" s="25">
+      <c r="S86" s="24">
         <f t="shared" si="8"/>
         <v>42</v>
       </c>
@@ -7553,7 +7616,7 @@
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A87" s="23" t="s">
+      <c r="A87" s="22" t="s">
         <v>58</v>
       </c>
       <c r="B87" s="12" t="s">
@@ -7580,32 +7643,32 @@
       <c r="I87" s="14">
         <v>46056</v>
       </c>
-      <c r="J87" s="25">
+      <c r="J87" s="24">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="K87" s="32"/>
-      <c r="L87" s="32"/>
+      <c r="K87" s="31"/>
+      <c r="L87" s="31"/>
       <c r="M87" s="12" t="s">
         <v>24</v>
       </c>
       <c r="N87" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="O87" s="20">
+      <c r="O87" s="47">
         <v>0</v>
       </c>
-      <c r="P87" s="20">
+      <c r="P87" s="47">
         <v>0</v>
       </c>
-      <c r="Q87" s="17">
+      <c r="Q87" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R87" s="14">
         <v>46058</v>
       </c>
-      <c r="S87" s="25">
+      <c r="S87" s="24">
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
@@ -7638,35 +7701,35 @@
       <c r="H88" s="14">
         <v>45947</v>
       </c>
-      <c r="I88" s="24">
+      <c r="I88" s="23">
         <v>46057</v>
       </c>
-      <c r="J88" s="25">
+      <c r="J88" s="24">
         <f t="shared" si="6"/>
         <v>79</v>
       </c>
-      <c r="K88" s="32"/>
-      <c r="L88" s="32"/>
+      <c r="K88" s="31"/>
+      <c r="L88" s="31"/>
       <c r="M88" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N88" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="O88" s="20">
+      <c r="O88" s="47">
         <v>600000</v>
       </c>
-      <c r="P88" s="20">
+      <c r="P88" s="47">
         <v>400000</v>
       </c>
-      <c r="Q88" s="17">
+      <c r="Q88" s="48">
         <f t="shared" si="7"/>
         <v>1000000</v>
       </c>
       <c r="R88" s="13">
         <v>46059</v>
       </c>
-      <c r="S88" s="25">
+      <c r="S88" s="24">
         <f t="shared" si="8"/>
         <v>81</v>
       </c>
@@ -7702,32 +7765,32 @@
       <c r="I89" s="14">
         <v>46055</v>
       </c>
-      <c r="J89" s="25">
+      <c r="J89" s="24">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="K89" s="32"/>
-      <c r="L89" s="32"/>
+      <c r="K89" s="31"/>
+      <c r="L89" s="31"/>
       <c r="M89" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N89" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O89" s="12">
+      <c r="O89" s="47">
         <v>900000</v>
       </c>
-      <c r="P89" s="12">
+      <c r="P89" s="47">
         <v>461679</v>
       </c>
-      <c r="Q89" s="17">
+      <c r="Q89" s="48">
         <f t="shared" si="7"/>
         <v>1361679</v>
       </c>
       <c r="R89" s="13">
         <v>46059</v>
       </c>
-      <c r="S89" s="25">
+      <c r="S89" s="24">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
@@ -7763,32 +7826,32 @@
       <c r="I90" s="14">
         <v>46055</v>
       </c>
-      <c r="J90" s="25">
+      <c r="J90" s="24">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="K90" s="32"/>
-      <c r="L90" s="32"/>
+      <c r="K90" s="31"/>
+      <c r="L90" s="31"/>
       <c r="M90" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N90" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O90" s="20">
+      <c r="O90" s="47">
         <v>1000000</v>
       </c>
-      <c r="P90" s="20">
+      <c r="P90" s="47">
         <v>538647</v>
       </c>
-      <c r="Q90" s="17">
+      <c r="Q90" s="48">
         <f t="shared" si="7"/>
         <v>1538647</v>
       </c>
       <c r="R90" s="13">
         <v>46059</v>
       </c>
-      <c r="S90" s="25">
+      <c r="S90" s="24">
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
@@ -7824,32 +7887,32 @@
       <c r="I91" s="14">
         <v>46058</v>
       </c>
-      <c r="J91" s="25">
+      <c r="J91" s="24">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="K91" s="32"/>
-      <c r="L91" s="32"/>
+      <c r="K91" s="31"/>
+      <c r="L91" s="31"/>
       <c r="M91" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N91" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O91" s="20">
+      <c r="O91" s="47">
         <v>5494650</v>
       </c>
-      <c r="P91" s="20">
+      <c r="P91" s="47">
         <v>1211081</v>
       </c>
-      <c r="Q91" s="17">
+      <c r="Q91" s="48">
         <f t="shared" si="7"/>
         <v>6705731</v>
       </c>
       <c r="R91" s="13">
         <v>46062</v>
       </c>
-      <c r="S91" s="25">
+      <c r="S91" s="24">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
@@ -7885,32 +7948,32 @@
       <c r="I92" s="14">
         <v>46048</v>
       </c>
-      <c r="J92" s="25">
+      <c r="J92" s="24">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="K92" s="32"/>
-      <c r="L92" s="32"/>
+      <c r="K92" s="31"/>
+      <c r="L92" s="31"/>
       <c r="M92" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N92" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O92" s="20">
+      <c r="O92" s="47">
         <v>1430307</v>
       </c>
-      <c r="P92" s="20">
+      <c r="P92" s="47">
         <v>600349</v>
       </c>
-      <c r="Q92" s="17">
+      <c r="Q92" s="48">
         <f t="shared" si="7"/>
         <v>2030656</v>
       </c>
       <c r="R92" s="13">
         <v>46063</v>
       </c>
-      <c r="S92" s="25">
+      <c r="S92" s="24">
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
@@ -7919,7 +7982,7 @@
       </c>
     </row>
     <row r="93" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="31" t="s">
+      <c r="A93" s="30" t="s">
         <v>77</v>
       </c>
       <c r="B93" s="12" t="s">
@@ -7946,32 +8009,32 @@
       <c r="I93" s="14">
         <v>46048</v>
       </c>
-      <c r="J93" s="25">
+      <c r="J93" s="24">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="K93" s="32"/>
-      <c r="L93" s="32"/>
+      <c r="K93" s="31"/>
+      <c r="L93" s="31"/>
       <c r="M93" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N93" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="O93" s="20">
+      <c r="O93" s="47">
         <v>500000</v>
       </c>
-      <c r="P93" s="20">
+      <c r="P93" s="47">
         <v>590836</v>
       </c>
-      <c r="Q93" s="17">
+      <c r="Q93" s="48">
         <f t="shared" si="7"/>
         <v>1090836</v>
       </c>
       <c r="R93" s="13">
         <v>46063</v>
       </c>
-      <c r="S93" s="25">
+      <c r="S93" s="24">
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
@@ -8007,32 +8070,32 @@
       <c r="I94" s="14">
         <v>46058</v>
       </c>
-      <c r="J94" s="25">
+      <c r="J94" s="24">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="K94" s="32"/>
-      <c r="L94" s="32"/>
+      <c r="K94" s="31"/>
+      <c r="L94" s="31"/>
       <c r="M94" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N94" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O94" s="20">
+      <c r="O94" s="47">
         <v>200000</v>
       </c>
-      <c r="P94" s="20">
+      <c r="P94" s="47">
         <v>0</v>
       </c>
-      <c r="Q94" s="17">
+      <c r="Q94" s="48">
         <f t="shared" si="7"/>
         <v>200000</v>
       </c>
       <c r="R94" s="13">
         <v>46063</v>
       </c>
-      <c r="S94" s="25">
+      <c r="S94" s="24">
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
@@ -8068,32 +8131,32 @@
       <c r="I95" s="14">
         <v>46059</v>
       </c>
-      <c r="J95" s="25">
+      <c r="J95" s="24">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="K95" s="32"/>
-      <c r="L95" s="32"/>
+      <c r="K95" s="31"/>
+      <c r="L95" s="31"/>
       <c r="M95" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N95" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="O95" s="20">
+      <c r="O95" s="47">
         <v>0</v>
       </c>
-      <c r="P95" s="20">
+      <c r="P95" s="47">
         <v>0</v>
       </c>
-      <c r="Q95" s="17">
+      <c r="Q95" s="48">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R95" s="13">
         <v>46063</v>
       </c>
-      <c r="S95" s="25">
+      <c r="S95" s="24">
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
@@ -8126,35 +8189,35 @@
       <c r="H96" s="13">
         <v>46030</v>
       </c>
-      <c r="I96" s="35">
+      <c r="I96" s="33">
         <v>46045</v>
       </c>
-      <c r="J96" s="25">
+      <c r="J96" s="24">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="K96" s="32"/>
-      <c r="L96" s="32"/>
+      <c r="K96" s="31"/>
+      <c r="L96" s="31"/>
       <c r="M96" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N96" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="O96" s="11">
+      <c r="O96" s="48">
         <v>360000</v>
       </c>
-      <c r="P96" s="11">
+      <c r="P96" s="48">
         <v>92495</v>
       </c>
-      <c r="Q96" s="17">
+      <c r="Q96" s="48">
         <f t="shared" si="7"/>
         <v>452495</v>
       </c>
       <c r="R96" s="13">
         <v>46063</v>
       </c>
-      <c r="S96" s="25">
+      <c r="S96" s="24">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
@@ -8184,38 +8247,38 @@
       <c r="G97" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H97" s="35">
+      <c r="H97" s="33">
         <v>46055</v>
       </c>
       <c r="I97" s="13">
         <v>46055</v>
       </c>
-      <c r="J97" s="25">
+      <c r="J97" s="24">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="K97" s="32"/>
-      <c r="L97" s="32"/>
+      <c r="K97" s="31"/>
+      <c r="L97" s="31"/>
       <c r="M97" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N97" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O97" s="20">
+      <c r="O97" s="47">
         <v>1000000</v>
       </c>
-      <c r="P97" s="20">
+      <c r="P97" s="47">
         <v>495000</v>
       </c>
-      <c r="Q97" s="17">
+      <c r="Q97" s="48">
         <f t="shared" si="7"/>
         <v>1495000</v>
       </c>
       <c r="R97" s="13">
         <v>46063</v>
       </c>
-      <c r="S97" s="25">
+      <c r="S97" s="24">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
@@ -8251,32 +8314,32 @@
       <c r="I98" s="14">
         <v>46038</v>
       </c>
-      <c r="J98" s="25">
+      <c r="J98" s="24">
         <f t="shared" si="6"/>
         <v>144</v>
       </c>
-      <c r="K98" s="32"/>
-      <c r="L98" s="32"/>
+      <c r="K98" s="31"/>
+      <c r="L98" s="31"/>
       <c r="M98" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N98" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O98" s="20">
+      <c r="O98" s="47">
         <v>2245845</v>
       </c>
-      <c r="P98" s="20">
+      <c r="P98" s="47">
         <v>474962</v>
       </c>
-      <c r="Q98" s="17">
+      <c r="Q98" s="48">
         <f>P98+O98</f>
         <v>2720807</v>
       </c>
       <c r="R98" s="13">
         <v>46063</v>
       </c>
-      <c r="S98" s="25">
+      <c r="S98" s="24">
         <f t="shared" si="8"/>
         <v>161</v>
       </c>
@@ -8312,32 +8375,32 @@
       <c r="I99" s="14">
         <v>46059</v>
       </c>
-      <c r="J99" s="25">
+      <c r="J99" s="24">
         <f t="shared" si="6"/>
         <v>76</v>
       </c>
-      <c r="K99" s="32"/>
-      <c r="L99" s="32"/>
+      <c r="K99" s="31"/>
+      <c r="L99" s="31"/>
       <c r="M99" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N99" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="O99" s="11">
+      <c r="O99" s="48">
         <v>0</v>
       </c>
-      <c r="P99" s="11">
+      <c r="P99" s="48">
         <v>725636</v>
       </c>
-      <c r="Q99" s="17">
+      <c r="Q99" s="48">
         <f>P99+O99</f>
         <v>725636</v>
       </c>
       <c r="R99" s="13">
         <v>46063</v>
       </c>
-      <c r="S99" s="25">
+      <c r="S99" s="24">
         <f t="shared" si="8"/>
         <v>78</v>
       </c>
@@ -8346,7 +8409,7 @@
       </c>
     </row>
     <row r="100" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="31" t="s">
+      <c r="A100" s="30" t="s">
         <v>95</v>
       </c>
       <c r="B100" s="12" t="s">
@@ -8370,35 +8433,35 @@
       <c r="H100" s="14">
         <v>46036</v>
       </c>
-      <c r="I100" s="24">
+      <c r="I100" s="23">
         <v>46061</v>
       </c>
-      <c r="J100" s="25">
+      <c r="J100" s="24">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="K100" s="32"/>
-      <c r="L100" s="32"/>
+      <c r="K100" s="31"/>
+      <c r="L100" s="31"/>
       <c r="M100" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N100" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O100" s="20">
+      <c r="O100" s="47">
         <v>1200000</v>
       </c>
-      <c r="P100" s="17">
+      <c r="P100" s="48">
         <v>515054</v>
       </c>
-      <c r="Q100" s="17">
+      <c r="Q100" s="48">
         <f>P100+O100</f>
         <v>1715054</v>
       </c>
       <c r="R100" s="13">
         <v>46063</v>
       </c>
-      <c r="S100" s="25">
+      <c r="S100" s="24">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
@@ -8434,32 +8497,32 @@
       <c r="I101" s="14">
         <v>46034</v>
       </c>
-      <c r="J101" s="25">
+      <c r="J101" s="24">
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="K101" s="32"/>
-      <c r="L101" s="32"/>
+      <c r="K101" s="31"/>
+      <c r="L101" s="31"/>
       <c r="M101" s="12" t="s">
         <v>24</v>
       </c>
       <c r="N101" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O101" s="20">
+      <c r="O101" s="47">
         <v>0</v>
       </c>
-      <c r="P101" s="20">
+      <c r="P101" s="47">
         <v>0</v>
       </c>
-      <c r="Q101" s="17">
+      <c r="Q101" s="48">
         <f>P101+O101</f>
         <v>0</v>
       </c>
       <c r="R101" s="13">
         <v>46063</v>
       </c>
-      <c r="S101" s="25">
+      <c r="S101" s="24">
         <f t="shared" si="8"/>
         <v>56</v>
       </c>
@@ -8468,7 +8531,7 @@
       </c>
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A102" s="23" t="s">
+      <c r="A102" s="22" t="s">
         <v>58</v>
       </c>
       <c r="B102" s="12" t="s">
@@ -8495,32 +8558,32 @@
       <c r="I102" s="14">
         <v>46008</v>
       </c>
-      <c r="J102" s="25">
+      <c r="J102" s="24">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="K102" s="32"/>
-      <c r="L102" s="32"/>
+      <c r="K102" s="31"/>
+      <c r="L102" s="31"/>
       <c r="M102" s="12" t="s">
         <v>24</v>
       </c>
       <c r="N102" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="O102" s="20">
+      <c r="O102" s="47">
         <v>0</v>
       </c>
-      <c r="P102" s="20">
+      <c r="P102" s="47">
         <v>0</v>
       </c>
-      <c r="Q102" s="17">
+      <c r="Q102" s="48">
         <f>P102+O102</f>
         <v>0</v>
       </c>
       <c r="R102" s="13">
         <v>46063</v>
       </c>
-      <c r="S102" s="25">
+      <c r="S102" s="24">
         <f t="shared" si="8"/>
         <v>56</v>
       </c>
@@ -8535,7 +8598,7 @@
       <c r="B103" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C103" s="23">
+      <c r="C103" s="22">
         <v>54959817</v>
       </c>
       <c r="D103" s="11" t="s">
@@ -8556,32 +8619,32 @@
       <c r="I103" s="14">
         <v>46064</v>
       </c>
-      <c r="J103" s="25">
+      <c r="J103" s="24">
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K103" s="32"/>
-      <c r="L103" s="32"/>
+      <c r="K103" s="31"/>
+      <c r="L103" s="31"/>
       <c r="M103" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N103" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O103" s="20">
+      <c r="O103" s="47">
         <v>200000</v>
       </c>
-      <c r="P103" s="20">
+      <c r="P103" s="47">
         <v>0</v>
       </c>
-      <c r="Q103" s="17">
+      <c r="Q103" s="48">
         <f t="shared" ref="Q103:Q109" si="9">P103+O103</f>
         <v>200000</v>
       </c>
       <c r="R103" s="13">
         <v>46064</v>
       </c>
-      <c r="S103" s="25">
+      <c r="S103" s="24">
         <f t="shared" si="8"/>
         <v>43</v>
       </c>
@@ -8617,32 +8680,32 @@
       <c r="I104" s="14">
         <v>46065</v>
       </c>
-      <c r="J104" s="25">
+      <c r="J104" s="24">
         <f t="shared" si="6"/>
         <v>123</v>
       </c>
-      <c r="K104" s="32"/>
-      <c r="L104" s="32"/>
+      <c r="K104" s="31"/>
+      <c r="L104" s="31"/>
       <c r="M104" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N104" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O104" s="20">
+      <c r="O104" s="47">
         <v>2148649</v>
       </c>
-      <c r="P104" s="20">
+      <c r="P104" s="47">
         <v>0</v>
       </c>
-      <c r="Q104" s="17">
+      <c r="Q104" s="48">
         <f t="shared" si="9"/>
         <v>2148649</v>
       </c>
       <c r="R104" s="13">
         <v>46064</v>
       </c>
-      <c r="S104" s="25">
+      <c r="S104" s="24">
         <f t="shared" si="8"/>
         <v>122</v>
       </c>
@@ -8678,32 +8741,32 @@
       <c r="I105" s="13">
         <v>46058</v>
       </c>
-      <c r="J105" s="25">
+      <c r="J105" s="24">
         <f t="shared" si="6"/>
         <v>46</v>
       </c>
-      <c r="K105" s="32"/>
-      <c r="L105" s="32"/>
+      <c r="K105" s="31"/>
+      <c r="L105" s="31"/>
       <c r="M105" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N105" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O105" s="5">
+      <c r="O105" s="15">
         <v>60000</v>
       </c>
-      <c r="P105" s="5">
+      <c r="P105" s="15">
         <v>0</v>
       </c>
-      <c r="Q105" s="17">
+      <c r="Q105" s="48">
         <f t="shared" si="9"/>
         <v>60000</v>
       </c>
       <c r="R105" s="13">
         <v>46065</v>
       </c>
-      <c r="S105" s="25">
+      <c r="S105" s="24">
         <f t="shared" si="8"/>
         <v>51</v>
       </c>
@@ -8739,32 +8802,32 @@
       <c r="I106" s="13">
         <v>46063</v>
       </c>
-      <c r="J106" s="25">
+      <c r="J106" s="24">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="K106" s="32"/>
-      <c r="L106" s="32"/>
+      <c r="K106" s="31"/>
+      <c r="L106" s="31"/>
       <c r="M106" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N106" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O106" s="5">
+      <c r="O106" s="15">
         <v>60000</v>
       </c>
-      <c r="P106" s="5">
+      <c r="P106" s="15">
         <v>0</v>
       </c>
-      <c r="Q106" s="17">
+      <c r="Q106" s="48">
         <f t="shared" si="9"/>
         <v>60000</v>
       </c>
       <c r="R106" s="13">
         <v>46065</v>
       </c>
-      <c r="S106" s="25">
+      <c r="S106" s="24">
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
@@ -8800,12 +8863,12 @@
       <c r="I107" s="14">
         <v>46064</v>
       </c>
-      <c r="J107" s="25">
+      <c r="J107" s="24">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="K107" s="32"/>
-      <c r="L107" s="32"/>
+      <c r="K107" s="31"/>
+      <c r="L107" s="31"/>
       <c r="M107" s="5" t="s">
         <v>24</v>
       </c>
@@ -8818,14 +8881,14 @@
       <c r="P107" s="15">
         <v>40000</v>
       </c>
-      <c r="Q107" s="17">
+      <c r="Q107" s="48">
         <f t="shared" si="9"/>
         <v>190000</v>
       </c>
       <c r="R107" s="13">
         <v>46065</v>
       </c>
-      <c r="S107" s="25">
+      <c r="S107" s="24">
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
@@ -8861,12 +8924,12 @@
       <c r="I108" s="14">
         <v>46064</v>
       </c>
-      <c r="J108" s="25">
+      <c r="J108" s="24">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="K108" s="32"/>
-      <c r="L108" s="32"/>
+      <c r="K108" s="31"/>
+      <c r="L108" s="31"/>
       <c r="M108" s="5" t="s">
         <v>24</v>
       </c>
@@ -8876,17 +8939,17 @@
       <c r="O108" s="15">
         <v>1000000</v>
       </c>
-      <c r="P108" s="5">
+      <c r="P108" s="15">
         <v>231750</v>
       </c>
-      <c r="Q108" s="17">
+      <c r="Q108" s="48">
         <f t="shared" si="9"/>
         <v>1231750</v>
       </c>
       <c r="R108" s="13">
         <v>46065</v>
       </c>
-      <c r="S108" s="25">
+      <c r="S108" s="24">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
@@ -8922,12 +8985,12 @@
       <c r="I109" s="14">
         <v>46064</v>
       </c>
-      <c r="J109" s="25">
+      <c r="J109" s="24">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="K109" s="32"/>
-      <c r="L109" s="32"/>
+      <c r="K109" s="31"/>
+      <c r="L109" s="31"/>
       <c r="M109" s="5" t="s">
         <v>24</v>
       </c>
@@ -8940,14 +9003,14 @@
       <c r="P109" s="15">
         <v>60000</v>
       </c>
-      <c r="Q109" s="17">
+      <c r="Q109" s="48">
         <f t="shared" si="9"/>
         <v>210000</v>
       </c>
       <c r="R109" s="13">
         <v>46065</v>
       </c>
-      <c r="S109" s="25">
+      <c r="S109" s="24">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
@@ -8983,32 +9046,32 @@
       <c r="I110" s="14">
         <v>46055</v>
       </c>
-      <c r="J110" s="25">
+      <c r="J110" s="24">
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
-      <c r="K110" s="32"/>
-      <c r="L110" s="32"/>
+      <c r="K110" s="31"/>
+      <c r="L110" s="31"/>
       <c r="M110" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N110" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O110" s="20">
+      <c r="O110" s="47">
         <v>835588</v>
       </c>
-      <c r="P110" s="20">
+      <c r="P110" s="47">
         <v>200000</v>
       </c>
-      <c r="Q110" s="17">
+      <c r="Q110" s="48">
         <f>P110+O110</f>
         <v>1035588</v>
       </c>
       <c r="R110" s="13">
         <v>46065</v>
       </c>
-      <c r="S110" s="25">
+      <c r="S110" s="24">
         <f t="shared" si="8"/>
         <v>35</v>
       </c>
@@ -9044,32 +9107,32 @@
       <c r="I111" s="14">
         <v>46064</v>
       </c>
-      <c r="J111" s="25">
+      <c r="J111" s="24">
         <f t="shared" si="6"/>
         <v>45</v>
       </c>
-      <c r="K111" s="36"/>
-      <c r="L111" s="36"/>
-      <c r="M111" s="37" t="s">
+      <c r="K111" s="34"/>
+      <c r="L111" s="34"/>
+      <c r="M111" s="35" t="s">
         <v>24</v>
       </c>
       <c r="N111" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O111" s="20">
+      <c r="O111" s="47">
         <v>1500000</v>
       </c>
-      <c r="P111" s="20">
+      <c r="P111" s="47">
         <v>333527</v>
       </c>
-      <c r="Q111" s="17">
+      <c r="Q111" s="48">
         <f t="shared" ref="Q111:Q118" si="10">P111+O111</f>
         <v>1833527</v>
       </c>
-      <c r="R111" s="38">
+      <c r="R111" s="36">
         <v>46066</v>
       </c>
-      <c r="S111" s="25">
+      <c r="S111" s="24">
         <f t="shared" si="8"/>
         <v>47</v>
       </c>
@@ -9084,7 +9147,7 @@
       <c r="B112" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C112" s="23">
+      <c r="C112" s="22">
         <v>57313786</v>
       </c>
       <c r="D112" s="11" t="s">
@@ -9105,32 +9168,32 @@
       <c r="I112" s="13">
         <v>46065</v>
       </c>
-      <c r="J112" s="25">
+      <c r="J112" s="24">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="K112" s="32"/>
-      <c r="L112" s="32"/>
+      <c r="K112" s="31"/>
+      <c r="L112" s="31"/>
       <c r="M112" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N112" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="O112" s="17">
+      <c r="O112" s="48">
         <v>420853</v>
       </c>
-      <c r="P112" s="17">
+      <c r="P112" s="48">
         <v>467395</v>
       </c>
-      <c r="Q112" s="17">
+      <c r="Q112" s="48">
         <f t="shared" si="10"/>
         <v>888248</v>
       </c>
-      <c r="R112" s="38">
+      <c r="R112" s="36">
         <v>46066</v>
       </c>
-      <c r="S112" s="25">
+      <c r="S112" s="24">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
@@ -9166,32 +9229,32 @@
       <c r="I113" s="14">
         <v>46067</v>
       </c>
-      <c r="J113" s="25">
+      <c r="J113" s="24">
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
-      <c r="K113" s="32"/>
-      <c r="L113" s="32"/>
+      <c r="K113" s="31"/>
+      <c r="L113" s="31"/>
       <c r="M113" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N113" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O113" s="20">
+      <c r="O113" s="47">
         <v>500000</v>
       </c>
-      <c r="P113" s="20">
+      <c r="P113" s="47">
         <v>998817</v>
       </c>
-      <c r="Q113" s="17">
+      <c r="Q113" s="48">
         <f t="shared" si="10"/>
         <v>1498817</v>
       </c>
       <c r="R113" s="13">
         <v>46069</v>
       </c>
-      <c r="S113" s="25">
+      <c r="S113" s="24">
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
@@ -9227,32 +9290,32 @@
       <c r="I114" s="14">
         <v>46048</v>
       </c>
-      <c r="J114" s="25">
+      <c r="J114" s="24">
         <f t="shared" si="6"/>
         <v>45</v>
       </c>
-      <c r="K114" s="32"/>
-      <c r="L114" s="32"/>
+      <c r="K114" s="31"/>
+      <c r="L114" s="31"/>
       <c r="M114" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N114" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O114" s="20">
+      <c r="O114" s="47">
         <v>700000</v>
       </c>
-      <c r="P114" s="20">
+      <c r="P114" s="47">
         <v>497454</v>
       </c>
-      <c r="Q114" s="17">
+      <c r="Q114" s="48">
         <f t="shared" si="10"/>
         <v>1197454</v>
       </c>
       <c r="R114" s="13">
         <v>46069</v>
       </c>
-      <c r="S114" s="25">
+      <c r="S114" s="24">
         <f t="shared" si="8"/>
         <v>60</v>
       </c>
@@ -9288,32 +9351,32 @@
       <c r="I115" s="14">
         <v>46049</v>
       </c>
-      <c r="J115" s="25">
+      <c r="J115" s="24">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="K115" s="32"/>
-      <c r="L115" s="32"/>
+      <c r="K115" s="31"/>
+      <c r="L115" s="31"/>
       <c r="M115" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N115" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O115" s="20">
+      <c r="O115" s="47">
         <v>638483</v>
       </c>
-      <c r="P115" s="20">
+      <c r="P115" s="47">
         <v>200000</v>
       </c>
-      <c r="Q115" s="17">
+      <c r="Q115" s="48">
         <f t="shared" si="10"/>
         <v>838483</v>
       </c>
       <c r="R115" s="13">
         <v>46069</v>
       </c>
-      <c r="S115" s="25">
+      <c r="S115" s="24">
         <f t="shared" si="8"/>
         <v>37</v>
       </c>
@@ -9349,32 +9412,32 @@
       <c r="I116" s="14">
         <v>46070</v>
       </c>
-      <c r="J116" s="25">
+      <c r="J116" s="24">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="K116" s="32"/>
-      <c r="L116" s="32"/>
+      <c r="K116" s="31"/>
+      <c r="L116" s="31"/>
       <c r="M116" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N116" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="O116" s="20">
+      <c r="O116" s="47">
         <v>2000500</v>
       </c>
-      <c r="P116" s="20">
+      <c r="P116" s="47">
         <v>557454</v>
       </c>
-      <c r="Q116" s="17">
+      <c r="Q116" s="48">
         <f t="shared" si="10"/>
         <v>2557954</v>
       </c>
       <c r="R116" s="13">
         <v>46070</v>
       </c>
-      <c r="S116" s="25">
+      <c r="S116" s="24">
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
@@ -9410,32 +9473,32 @@
       <c r="I117" s="13">
         <v>46066</v>
       </c>
-      <c r="J117" s="25">
+      <c r="J117" s="24">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="K117" s="32"/>
-      <c r="L117" s="32"/>
+      <c r="K117" s="31"/>
+      <c r="L117" s="31"/>
       <c r="M117" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N117" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O117" s="17">
+      <c r="O117" s="48">
         <v>150000</v>
       </c>
-      <c r="P117" s="17">
+      <c r="P117" s="48">
         <v>60000</v>
       </c>
-      <c r="Q117" s="17">
+      <c r="Q117" s="48">
         <f t="shared" si="10"/>
         <v>210000</v>
       </c>
       <c r="R117" s="13">
         <v>46070</v>
       </c>
-      <c r="S117" s="25">
+      <c r="S117" s="24">
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
@@ -9471,32 +9534,32 @@
       <c r="I118" s="13">
         <v>46069</v>
       </c>
-      <c r="J118" s="25">
+      <c r="J118" s="24">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="K118" s="32"/>
-      <c r="L118" s="32"/>
+      <c r="K118" s="31"/>
+      <c r="L118" s="31"/>
       <c r="M118" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N118" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O118" s="17">
+      <c r="O118" s="48">
         <v>1000000</v>
       </c>
-      <c r="P118" s="17">
+      <c r="P118" s="48">
         <v>231750</v>
       </c>
-      <c r="Q118" s="17">
+      <c r="Q118" s="48">
         <f t="shared" si="10"/>
         <v>1231750</v>
       </c>
       <c r="R118" s="13">
         <v>46070</v>
       </c>
-      <c r="S118" s="25">
+      <c r="S118" s="24">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
@@ -9529,35 +9592,35 @@
       <c r="H119" s="14">
         <v>46044</v>
       </c>
-      <c r="I119" s="24">
+      <c r="I119" s="23">
         <v>46063</v>
       </c>
-      <c r="J119" s="25">
+      <c r="J119" s="24">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="K119" s="32"/>
-      <c r="L119" s="32"/>
+      <c r="K119" s="31"/>
+      <c r="L119" s="31"/>
       <c r="M119" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N119" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O119" s="17">
+      <c r="O119" s="48">
         <v>1474962</v>
       </c>
-      <c r="P119" s="20">
+      <c r="P119" s="47">
         <v>0</v>
       </c>
-      <c r="Q119" s="17">
+      <c r="Q119" s="48">
         <f>P119+O119</f>
         <v>1474962</v>
       </c>
       <c r="R119" s="13">
         <v>46070</v>
       </c>
-      <c r="S119" s="25">
+      <c r="S119" s="24">
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
@@ -9578,7 +9641,7 @@
       <c r="D120" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="E120" s="23" t="s">
+      <c r="E120" s="22" t="s">
         <v>136</v>
       </c>
       <c r="F120" s="11" t="s">
@@ -9593,32 +9656,32 @@
       <c r="I120" s="14">
         <v>46069</v>
       </c>
-      <c r="J120" s="25">
+      <c r="J120" s="24">
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="K120" s="32"/>
-      <c r="L120" s="32"/>
+      <c r="K120" s="31"/>
+      <c r="L120" s="31"/>
       <c r="M120" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N120" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="O120" s="17">
+      <c r="O120" s="48">
         <v>2000000</v>
       </c>
-      <c r="P120" s="17">
+      <c r="P120" s="48">
         <v>0</v>
       </c>
-      <c r="Q120" s="17">
+      <c r="Q120" s="48">
         <f>P120+O120</f>
         <v>2000000</v>
       </c>
       <c r="R120" s="13">
         <v>46071</v>
       </c>
-      <c r="S120" s="25">
+      <c r="S120" s="24">
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
@@ -9654,32 +9717,32 @@
       <c r="I121" s="14">
         <v>46069</v>
       </c>
-      <c r="J121" s="25">
+      <c r="J121" s="24">
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="K121" s="32"/>
-      <c r="L121" s="32"/>
+      <c r="K121" s="31"/>
+      <c r="L121" s="31"/>
       <c r="M121" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N121" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="O121" s="17">
+      <c r="O121" s="48">
         <v>2000000</v>
       </c>
-      <c r="P121" s="17">
+      <c r="P121" s="48">
         <v>0</v>
       </c>
-      <c r="Q121" s="17">
+      <c r="Q121" s="48">
         <f>P121+O121</f>
         <v>2000000</v>
       </c>
       <c r="R121" s="13">
         <v>46071</v>
       </c>
-      <c r="S121" s="25">
+      <c r="S121" s="24">
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
@@ -9715,32 +9778,32 @@
       <c r="I122" s="14">
         <v>46064</v>
       </c>
-      <c r="J122" s="25">
+      <c r="J122" s="24">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="K122" s="32"/>
-      <c r="L122" s="32"/>
+      <c r="K122" s="31"/>
+      <c r="L122" s="31"/>
       <c r="M122" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N122" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="O122" s="17">
+      <c r="O122" s="48">
         <v>2000000</v>
       </c>
-      <c r="P122" s="20">
+      <c r="P122" s="47">
         <v>300000</v>
       </c>
-      <c r="Q122" s="17">
+      <c r="Q122" s="48">
         <f>P122+O122</f>
         <v>2300000</v>
       </c>
       <c r="R122" s="13">
         <v>46071</v>
       </c>
-      <c r="S122" s="25">
+      <c r="S122" s="24">
         <f t="shared" si="8"/>
         <v>28</v>
       </c>
@@ -9776,32 +9839,32 @@
       <c r="I123" s="14">
         <v>46070</v>
       </c>
-      <c r="J123" s="25">
+      <c r="J123" s="24">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="K123" s="32"/>
-      <c r="L123" s="32"/>
+      <c r="K123" s="31"/>
+      <c r="L123" s="31"/>
       <c r="M123" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N123" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O123" s="20">
+      <c r="O123" s="47">
         <v>1000000</v>
       </c>
-      <c r="P123" s="20">
+      <c r="P123" s="47">
         <v>693500</v>
       </c>
-      <c r="Q123" s="17">
+      <c r="Q123" s="48">
         <f t="shared" ref="Q123:Q148" si="11">P123+O123</f>
         <v>1693500</v>
       </c>
       <c r="R123" s="13">
         <v>46072</v>
       </c>
-      <c r="S123" s="25">
+      <c r="S123" s="24">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
@@ -9837,32 +9900,32 @@
       <c r="I124" s="14">
         <v>46071</v>
       </c>
-      <c r="J124" s="25">
+      <c r="J124" s="24">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="K124" s="32"/>
-      <c r="L124" s="32"/>
+      <c r="K124" s="31"/>
+      <c r="L124" s="31"/>
       <c r="M124" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N124" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O124" s="17">
+      <c r="O124" s="48">
         <v>0</v>
       </c>
-      <c r="P124" s="17">
+      <c r="P124" s="48">
         <v>0</v>
       </c>
-      <c r="Q124" s="17">
+      <c r="Q124" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R124" s="13">
         <v>46072</v>
       </c>
-      <c r="S124" s="25">
+      <c r="S124" s="24">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
@@ -9898,32 +9961,32 @@
       <c r="I125" s="14">
         <v>46070</v>
       </c>
-      <c r="J125" s="25">
+      <c r="J125" s="24">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="K125" s="32"/>
-      <c r="L125" s="32"/>
+      <c r="K125" s="31"/>
+      <c r="L125" s="31"/>
       <c r="M125" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N125" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="O125" s="20">
+      <c r="O125" s="47">
         <v>150000</v>
       </c>
-      <c r="P125" s="20">
+      <c r="P125" s="47">
         <v>443127</v>
       </c>
-      <c r="Q125" s="17">
+      <c r="Q125" s="48">
         <f t="shared" si="11"/>
         <v>593127</v>
       </c>
       <c r="R125" s="13">
         <v>46072</v>
       </c>
-      <c r="S125" s="25">
+      <c r="S125" s="24">
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
@@ -9959,32 +10022,32 @@
       <c r="I126" s="14">
         <v>46070</v>
       </c>
-      <c r="J126" s="25">
+      <c r="J126" s="24">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="K126" s="32"/>
-      <c r="L126" s="32"/>
+      <c r="K126" s="31"/>
+      <c r="L126" s="31"/>
       <c r="M126" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N126" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O126" s="20">
+      <c r="O126" s="47">
         <v>1987902</v>
       </c>
-      <c r="P126" s="20">
+      <c r="P126" s="47">
         <v>270000</v>
       </c>
-      <c r="Q126" s="17">
+      <c r="Q126" s="48">
         <f t="shared" si="11"/>
         <v>2257902</v>
       </c>
       <c r="R126" s="13">
         <v>46072</v>
       </c>
-      <c r="S126" s="25">
+      <c r="S126" s="24">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
@@ -10020,11 +10083,11 @@
       <c r="I127" s="14">
         <v>46063</v>
       </c>
-      <c r="J127" s="25">
+      <c r="J127" s="24">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="K127" s="26" t="s">
+      <c r="K127" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L127" s="11" t="s">
@@ -10036,20 +10099,20 @@
       <c r="N127" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O127" s="17">
+      <c r="O127" s="48">
         <v>1100000</v>
       </c>
-      <c r="P127" s="20">
+      <c r="P127" s="47">
         <v>474962</v>
       </c>
-      <c r="Q127" s="17">
+      <c r="Q127" s="48">
         <f t="shared" si="11"/>
         <v>1574962</v>
       </c>
       <c r="R127" s="13">
         <v>46076</v>
       </c>
-      <c r="S127" s="25">
+      <c r="S127" s="24">
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
@@ -10085,11 +10148,11 @@
       <c r="I128" s="14">
         <v>46057</v>
       </c>
-      <c r="J128" s="25">
+      <c r="J128" s="24">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="K128" s="26" t="s">
+      <c r="K128" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L128" s="11" t="s">
@@ -10101,20 +10164,20 @@
       <c r="N128" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O128" s="20">
+      <c r="O128" s="47">
         <v>1100000</v>
       </c>
-      <c r="P128" s="20">
+      <c r="P128" s="47">
         <v>474962</v>
       </c>
-      <c r="Q128" s="17">
+      <c r="Q128" s="48">
         <f t="shared" si="11"/>
         <v>1574962</v>
       </c>
       <c r="R128" s="13">
         <v>46076</v>
       </c>
-      <c r="S128" s="25">
+      <c r="S128" s="24">
         <f t="shared" si="8"/>
         <v>34</v>
       </c>
@@ -10150,11 +10213,11 @@
       <c r="I129" s="14">
         <v>46076</v>
       </c>
-      <c r="J129" s="25">
+      <c r="J129" s="24">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="K129" s="26" t="s">
+      <c r="K129" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L129" s="11" t="s">
@@ -10166,20 +10229,20 @@
       <c r="N129" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O129" s="20">
+      <c r="O129" s="47">
         <v>0</v>
       </c>
-      <c r="P129" s="20">
+      <c r="P129" s="47">
         <v>0</v>
       </c>
-      <c r="Q129" s="17">
+      <c r="Q129" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R129" s="13">
         <v>46077</v>
       </c>
-      <c r="S129" s="25">
+      <c r="S129" s="24">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
@@ -10215,11 +10278,11 @@
       <c r="I130" s="14">
         <v>46077</v>
       </c>
-      <c r="J130" s="25">
+      <c r="J130" s="24">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="K130" s="26" t="s">
+      <c r="K130" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L130" s="11" t="s">
@@ -10231,20 +10294,20 @@
       <c r="N130" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="O130" s="20">
+      <c r="O130" s="47">
         <v>270000</v>
       </c>
-      <c r="P130" s="20">
+      <c r="P130" s="47">
         <v>71435</v>
       </c>
-      <c r="Q130" s="17">
+      <c r="Q130" s="48">
         <f t="shared" si="11"/>
         <v>341435</v>
       </c>
       <c r="R130" s="13">
         <v>46077</v>
       </c>
-      <c r="S130" s="25">
+      <c r="S130" s="24">
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
@@ -10280,11 +10343,11 @@
       <c r="I131" s="14">
         <v>46066</v>
       </c>
-      <c r="J131" s="25">
+      <c r="J131" s="24">
         <f t="shared" si="6"/>
         <v>69</v>
       </c>
-      <c r="K131" s="26" t="s">
+      <c r="K131" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L131" s="11" t="s">
@@ -10296,20 +10359,20 @@
       <c r="N131" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="O131" s="20">
+      <c r="O131" s="47">
         <v>360000</v>
       </c>
-      <c r="P131" s="20">
+      <c r="P131" s="47">
         <v>92495</v>
       </c>
-      <c r="Q131" s="17">
+      <c r="Q131" s="48">
         <f t="shared" si="11"/>
         <v>452495</v>
       </c>
       <c r="R131" s="13">
         <v>46077</v>
       </c>
-      <c r="S131" s="25">
+      <c r="S131" s="24">
         <f t="shared" si="8"/>
         <v>76</v>
       </c>
@@ -10317,8 +10380,8 @@
         <v>314</v>
       </c>
     </row>
-    <row r="132" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="23" t="s">
+    <row r="132" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="22" t="s">
         <v>311</v>
       </c>
       <c r="B132" s="12" t="s">
@@ -10342,14 +10405,14 @@
       <c r="H132" s="14">
         <v>46029</v>
       </c>
-      <c r="I132" s="24">
+      <c r="I132" s="23">
         <v>46073</v>
       </c>
-      <c r="J132" s="25">
+      <c r="J132" s="24">
         <f t="shared" si="6"/>
         <v>33</v>
       </c>
-      <c r="K132" s="26" t="s">
+      <c r="K132" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L132" s="11" t="s">
@@ -10361,20 +10424,20 @@
       <c r="N132" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O132" s="20">
+      <c r="O132" s="47">
         <v>500000</v>
       </c>
-      <c r="P132" s="20">
+      <c r="P132" s="47">
         <v>1963000</v>
       </c>
-      <c r="Q132" s="17">
+      <c r="Q132" s="48">
         <f t="shared" si="11"/>
         <v>2463000</v>
       </c>
       <c r="R132" s="13">
         <v>46078</v>
       </c>
-      <c r="S132" s="25">
+      <c r="S132" s="24">
         <f t="shared" si="8"/>
         <v>36</v>
       </c>
@@ -10382,14 +10445,14 @@
         <v>314</v>
       </c>
     </row>
-    <row r="133" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A133" s="12" t="s">
         <v>311</v>
       </c>
       <c r="B133" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C133" s="28">
+      <c r="C133" s="27">
         <v>54079438</v>
       </c>
       <c r="D133" s="12" t="s">
@@ -10407,14 +10470,14 @@
       <c r="H133" s="14">
         <v>45986</v>
       </c>
-      <c r="I133" s="24">
+      <c r="I133" s="23">
         <v>46073</v>
       </c>
-      <c r="J133" s="25">
+      <c r="J133" s="24">
         <f t="shared" si="6"/>
         <v>64</v>
       </c>
-      <c r="K133" s="26" t="s">
+      <c r="K133" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L133" s="11" t="s">
@@ -10426,20 +10489,20 @@
       <c r="N133" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O133" s="20">
+      <c r="O133" s="47">
         <v>500000</v>
       </c>
-      <c r="P133" s="20">
+      <c r="P133" s="47">
         <v>350000</v>
       </c>
-      <c r="Q133" s="17">
+      <c r="Q133" s="48">
         <f t="shared" si="11"/>
         <v>850000</v>
       </c>
       <c r="R133" s="13">
         <v>46078</v>
       </c>
-      <c r="S133" s="25">
+      <c r="S133" s="24">
         <f t="shared" si="8"/>
         <v>67</v>
       </c>
@@ -10475,11 +10538,11 @@
       <c r="I134" s="14">
         <v>46071</v>
       </c>
-      <c r="J134" s="25">
+      <c r="J134" s="24">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="K134" s="26" t="s">
+      <c r="K134" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L134" s="11" t="s">
@@ -10491,20 +10554,20 @@
       <c r="N134" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O134" s="20">
+      <c r="O134" s="47">
         <v>2000000</v>
       </c>
-      <c r="P134" s="20">
+      <c r="P134" s="47">
         <v>3000000</v>
       </c>
-      <c r="Q134" s="17">
+      <c r="Q134" s="48">
         <f t="shared" si="11"/>
         <v>5000000</v>
       </c>
       <c r="R134" s="13">
         <v>46078</v>
       </c>
-      <c r="S134" s="25">
+      <c r="S134" s="24">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
@@ -10540,11 +10603,11 @@
       <c r="I135" s="13">
         <v>46078</v>
       </c>
-      <c r="J135" s="25">
+      <c r="J135" s="24">
         <f t="shared" si="6"/>
         <v>28</v>
       </c>
-      <c r="K135" s="26" t="s">
+      <c r="K135" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L135" s="11" t="s">
@@ -10556,20 +10619,20 @@
       <c r="N135" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O135" s="17">
+      <c r="O135" s="48">
         <v>400000</v>
       </c>
-      <c r="P135" s="17">
+      <c r="P135" s="48">
         <v>0</v>
       </c>
-      <c r="Q135" s="17">
+      <c r="Q135" s="48">
         <f t="shared" si="11"/>
         <v>400000</v>
       </c>
       <c r="R135" s="13">
         <v>46079</v>
       </c>
-      <c r="S135" s="25">
+      <c r="S135" s="24">
         <f t="shared" si="8"/>
         <v>29</v>
       </c>
@@ -10605,11 +10668,11 @@
       <c r="I136" s="13">
         <v>46078</v>
       </c>
-      <c r="J136" s="25">
+      <c r="J136" s="24">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="K136" s="26" t="s">
+      <c r="K136" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L136" s="11" t="s">
@@ -10621,20 +10684,20 @@
       <c r="N136" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O136" s="17">
+      <c r="O136" s="48">
         <v>150000</v>
       </c>
-      <c r="P136" s="17">
+      <c r="P136" s="48">
         <v>0</v>
       </c>
-      <c r="Q136" s="17">
+      <c r="Q136" s="48">
         <f t="shared" si="11"/>
         <v>150000</v>
       </c>
       <c r="R136" s="13">
         <v>46079</v>
       </c>
-      <c r="S136" s="25">
+      <c r="S136" s="24">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
@@ -10670,11 +10733,11 @@
       <c r="I137" s="13">
         <v>46078</v>
       </c>
-      <c r="J137" s="25">
+      <c r="J137" s="24">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="K137" s="26" t="s">
+      <c r="K137" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L137" s="11" t="s">
@@ -10686,20 +10749,20 @@
       <c r="N137" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O137" s="17">
+      <c r="O137" s="48">
         <v>1000000</v>
       </c>
-      <c r="P137" s="17">
+      <c r="P137" s="48">
         <v>0</v>
       </c>
-      <c r="Q137" s="17">
+      <c r="Q137" s="48">
         <f t="shared" si="11"/>
         <v>1000000</v>
       </c>
       <c r="R137" s="13">
         <v>46079</v>
       </c>
-      <c r="S137" s="25">
+      <c r="S137" s="24">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
@@ -10735,11 +10798,11 @@
       <c r="I138" s="13">
         <v>46078</v>
       </c>
-      <c r="J138" s="25">
+      <c r="J138" s="24">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="K138" s="26" t="s">
+      <c r="K138" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L138" s="11" t="s">
@@ -10751,20 +10814,20 @@
       <c r="N138" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O138" s="17">
+      <c r="O138" s="48">
         <v>1000000</v>
       </c>
-      <c r="P138" s="17">
+      <c r="P138" s="48">
         <v>0</v>
       </c>
-      <c r="Q138" s="17">
+      <c r="Q138" s="48">
         <f t="shared" si="11"/>
         <v>1000000</v>
       </c>
       <c r="R138" s="13">
         <v>46079</v>
       </c>
-      <c r="S138" s="25">
+      <c r="S138" s="24">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
@@ -10800,11 +10863,11 @@
       <c r="I139" s="13">
         <v>46078</v>
       </c>
-      <c r="J139" s="25">
+      <c r="J139" s="24">
         <f t="shared" si="6"/>
         <v>75</v>
       </c>
-      <c r="K139" s="26" t="s">
+      <c r="K139" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L139" s="11" t="s">
@@ -10816,20 +10879,20 @@
       <c r="N139" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O139" s="17">
+      <c r="O139" s="48">
         <v>108000</v>
       </c>
-      <c r="P139" s="17">
+      <c r="P139" s="48">
         <v>0</v>
       </c>
-      <c r="Q139" s="17">
+      <c r="Q139" s="48">
         <f t="shared" si="11"/>
         <v>108000</v>
       </c>
       <c r="R139" s="13">
         <v>46079</v>
       </c>
-      <c r="S139" s="25">
+      <c r="S139" s="24">
         <f t="shared" si="8"/>
         <v>76</v>
       </c>
@@ -10865,11 +10928,11 @@
       <c r="I140" s="13">
         <v>46079</v>
       </c>
-      <c r="J140" s="25">
+      <c r="J140" s="24">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="K140" s="26" t="s">
+      <c r="K140" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L140" s="11" t="s">
@@ -10881,20 +10944,20 @@
       <c r="N140" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="O140" s="17">
+      <c r="O140" s="48">
         <v>270000</v>
       </c>
-      <c r="P140" s="17">
+      <c r="P140" s="48">
         <v>71435</v>
       </c>
-      <c r="Q140" s="17">
+      <c r="Q140" s="48">
         <f t="shared" si="11"/>
         <v>341435</v>
       </c>
       <c r="R140" s="13">
         <v>46079</v>
       </c>
-      <c r="S140" s="25">
+      <c r="S140" s="24">
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
@@ -10930,11 +10993,11 @@
       <c r="I141" s="13">
         <v>46079</v>
       </c>
-      <c r="J141" s="25">
-        <f t="shared" ref="J141:J148" si="12">+NETWORKDAYS(H141,I141)</f>
+      <c r="J141" s="24">
+        <f t="shared" ref="J141:J156" si="12">+NETWORKDAYS(H141,I141)</f>
         <v>261</v>
       </c>
-      <c r="K141" s="26" t="s">
+      <c r="K141" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L141" s="11" t="s">
@@ -10946,21 +11009,21 @@
       <c r="N141" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O141" s="17">
+      <c r="O141" s="48">
         <v>3000000</v>
       </c>
-      <c r="P141" s="17">
+      <c r="P141" s="48">
         <v>139050</v>
       </c>
-      <c r="Q141" s="17">
+      <c r="Q141" s="48">
         <f t="shared" si="11"/>
         <v>3139050</v>
       </c>
       <c r="R141" s="13">
         <v>46079</v>
       </c>
-      <c r="S141" s="25">
-        <f t="shared" ref="S141:S148" si="13">NETWORKDAYS(H141,R141)</f>
+      <c r="S141" s="24">
+        <f t="shared" ref="S141:S156" si="13">NETWORKDAYS(H141,R141)</f>
         <v>261</v>
       </c>
       <c r="T141" s="11" t="s">
@@ -10995,11 +11058,11 @@
       <c r="I142" s="14">
         <v>46073</v>
       </c>
-      <c r="J142" s="25">
+      <c r="J142" s="24">
         <f t="shared" si="12"/>
         <v>23</v>
       </c>
-      <c r="K142" s="26" t="s">
+      <c r="K142" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L142" s="11" t="s">
@@ -11011,20 +11074,20 @@
       <c r="N142" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O142" s="20">
+      <c r="O142" s="47">
         <v>350000</v>
       </c>
-      <c r="P142" s="20">
+      <c r="P142" s="47">
         <v>197989</v>
       </c>
-      <c r="Q142" s="17">
+      <c r="Q142" s="48">
         <f t="shared" si="11"/>
         <v>547989</v>
       </c>
       <c r="R142" s="13">
         <v>46079</v>
       </c>
-      <c r="S142" s="25">
+      <c r="S142" s="24">
         <f t="shared" si="13"/>
         <v>27</v>
       </c>
@@ -11060,11 +11123,11 @@
       <c r="I143" s="14">
         <v>46079</v>
       </c>
-      <c r="J143" s="25">
+      <c r="J143" s="24">
         <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="K143" s="26" t="s">
+      <c r="K143" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L143" s="11" t="s">
@@ -11076,20 +11139,20 @@
       <c r="N143" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="O143" s="17">
+      <c r="O143" s="48">
         <v>842820</v>
       </c>
-      <c r="P143" s="17">
+      <c r="P143" s="48">
         <v>0</v>
       </c>
-      <c r="Q143" s="17">
+      <c r="Q143" s="48">
         <f t="shared" si="11"/>
         <v>842820</v>
       </c>
       <c r="R143" s="13">
         <v>46080</v>
       </c>
-      <c r="S143" s="25">
+      <c r="S143" s="24">
         <f t="shared" si="13"/>
         <v>15</v>
       </c>
@@ -11125,11 +11188,11 @@
       <c r="I144" s="14">
         <v>46077</v>
       </c>
-      <c r="J144" s="25">
+      <c r="J144" s="24">
         <f t="shared" si="12"/>
         <v>9</v>
       </c>
-      <c r="K144" s="26" t="s">
+      <c r="K144" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L144" s="11" t="s">
@@ -11141,20 +11204,20 @@
       <c r="N144" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="O144" s="20">
+      <c r="O144" s="47">
         <v>3986938</v>
       </c>
-      <c r="P144" s="20">
+      <c r="P144" s="47">
         <v>400908</v>
       </c>
-      <c r="Q144" s="17">
+      <c r="Q144" s="48">
         <f t="shared" si="11"/>
         <v>4387846</v>
       </c>
       <c r="R144" s="13">
         <v>46080</v>
       </c>
-      <c r="S144" s="25">
+      <c r="S144" s="24">
         <f t="shared" si="13"/>
         <v>12</v>
       </c>
@@ -11190,11 +11253,11 @@
       <c r="I145" s="14">
         <v>45999</v>
       </c>
-      <c r="J145" s="25">
+      <c r="J145" s="24">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="K145" s="26" t="s">
+      <c r="K145" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L145" s="11" t="s">
@@ -11206,20 +11269,20 @@
       <c r="N145" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="O145" s="20">
+      <c r="O145" s="47">
         <v>250000</v>
       </c>
-      <c r="P145" s="20">
+      <c r="P145" s="47">
         <v>370000</v>
       </c>
-      <c r="Q145" s="17">
+      <c r="Q145" s="48">
         <f t="shared" si="11"/>
         <v>620000</v>
       </c>
       <c r="R145" s="13">
         <v>46080</v>
       </c>
-      <c r="S145" s="25">
+      <c r="S145" s="24">
         <f t="shared" si="13"/>
         <v>79</v>
       </c>
@@ -11255,7 +11318,7 @@
       <c r="I146" s="14">
         <v>46051</v>
       </c>
-      <c r="J146" s="25">
+      <c r="J146" s="24">
         <f t="shared" si="12"/>
         <v>13</v>
       </c>
@@ -11271,20 +11334,20 @@
       <c r="N146" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O146" s="20">
+      <c r="O146" s="47">
         <v>1000000</v>
       </c>
-      <c r="P146" s="20">
+      <c r="P146" s="47">
         <v>965500</v>
       </c>
-      <c r="Q146" s="17">
+      <c r="Q146" s="48">
         <f t="shared" si="11"/>
         <v>1965500</v>
       </c>
       <c r="R146" s="13">
         <v>46080</v>
       </c>
-      <c r="S146" s="25">
+      <c r="S146" s="24">
         <f t="shared" si="13"/>
         <v>34</v>
       </c>
@@ -11320,7 +11383,7 @@
       <c r="I147" s="14">
         <v>46052</v>
       </c>
-      <c r="J147" s="25">
+      <c r="J147" s="24">
         <f t="shared" si="12"/>
         <v>14</v>
       </c>
@@ -11336,20 +11399,20 @@
       <c r="N147" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="O147" s="20">
+      <c r="O147" s="47">
         <v>2000000</v>
       </c>
-      <c r="P147" s="20">
+      <c r="P147" s="47">
         <v>300000</v>
       </c>
-      <c r="Q147" s="17">
+      <c r="Q147" s="48">
         <f t="shared" si="11"/>
         <v>2300000</v>
       </c>
       <c r="R147" s="13">
         <v>46080</v>
       </c>
-      <c r="S147" s="25">
+      <c r="S147" s="24">
         <f t="shared" si="13"/>
         <v>34</v>
       </c>
@@ -11358,7 +11421,7 @@
       </c>
     </row>
     <row r="148" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A148" s="23" t="s">
+      <c r="A148" s="22" t="s">
         <v>58</v>
       </c>
       <c r="B148" s="12" t="s">
@@ -11385,11 +11448,11 @@
       <c r="I148" s="14">
         <v>46076</v>
       </c>
-      <c r="J148" s="25">
+      <c r="J148" s="24">
         <f t="shared" si="12"/>
         <v>65</v>
       </c>
-      <c r="K148" s="26" t="s">
+      <c r="K148" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L148" s="11" t="s">
@@ -11401,40 +11464,560 @@
       <c r="N148" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O148" s="12">
+      <c r="O148" s="47">
         <v>0</v>
       </c>
-      <c r="P148" s="12">
+      <c r="P148" s="47">
         <v>0</v>
       </c>
-      <c r="Q148" s="17">
+      <c r="Q148" s="48">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R148" s="13">
         <v>46081</v>
       </c>
-      <c r="S148" s="25">
+      <c r="S148" s="24">
         <f t="shared" si="13"/>
         <v>69</v>
       </c>
       <c r="T148" s="11" t="s">
         <v>314</v>
+      </c>
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A149" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="B149" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C149" s="44">
+        <v>57664431</v>
+      </c>
+      <c r="D149" s="44" t="s">
+        <v>345</v>
+      </c>
+      <c r="E149" s="44" t="s">
+        <v>346</v>
+      </c>
+      <c r="F149" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="G149" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H149" s="45">
+        <v>46055</v>
+      </c>
+      <c r="I149" s="45">
+        <v>46083</v>
+      </c>
+      <c r="J149" s="24">
+        <f t="shared" si="12"/>
+        <v>21</v>
+      </c>
+      <c r="K149" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L149" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="M149" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="N149" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="O149" s="49">
+        <v>2500000</v>
+      </c>
+      <c r="P149" s="49">
+        <v>2325347</v>
+      </c>
+      <c r="Q149" s="47">
+        <f>P149+O149</f>
+        <v>4825347</v>
+      </c>
+      <c r="R149" s="45">
+        <v>46084</v>
+      </c>
+      <c r="S149" s="24">
+        <f t="shared" si="13"/>
+        <v>22</v>
+      </c>
+      <c r="T149" s="44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A150" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B150" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C150" s="44">
+        <v>57417024</v>
+      </c>
+      <c r="D150" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="E150" s="44">
+        <v>2721710775</v>
+      </c>
+      <c r="F150" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="G150" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H150" s="45">
+        <v>46050</v>
+      </c>
+      <c r="I150" s="45">
+        <v>46083</v>
+      </c>
+      <c r="J150" s="24">
+        <f t="shared" si="12"/>
+        <v>24</v>
+      </c>
+      <c r="K150" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L150" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="M150" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="N150" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="O150" s="49">
+        <v>150000</v>
+      </c>
+      <c r="P150" s="49">
+        <v>40000</v>
+      </c>
+      <c r="Q150" s="47">
+        <f t="shared" ref="Q150:Q156" si="14">P150+O150</f>
+        <v>190000</v>
+      </c>
+      <c r="R150" s="45">
+        <v>46084</v>
+      </c>
+      <c r="S150" s="24">
+        <f t="shared" si="13"/>
+        <v>25</v>
+      </c>
+      <c r="T150" s="44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="151" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A151" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="B151" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C151" s="44">
+        <v>57847231</v>
+      </c>
+      <c r="D151" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="E151" s="44" t="s">
+        <v>349</v>
+      </c>
+      <c r="F151" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="G151" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H151" s="45">
+        <v>46058</v>
+      </c>
+      <c r="I151" s="45">
+        <v>46078</v>
+      </c>
+      <c r="J151" s="24">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="K151" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L151" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="M151" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="N151" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="O151" s="49">
+        <v>485500</v>
+      </c>
+      <c r="P151" s="49">
+        <v>251105</v>
+      </c>
+      <c r="Q151" s="47">
+        <f t="shared" si="14"/>
+        <v>736605</v>
+      </c>
+      <c r="R151" s="45">
+        <v>46085</v>
+      </c>
+      <c r="S151" s="24">
+        <f t="shared" si="13"/>
+        <v>20</v>
+      </c>
+      <c r="T151" s="44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="152" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A152" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B152" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C152" s="44">
+        <v>24190516</v>
+      </c>
+      <c r="D152" s="44" t="s">
+        <v>351</v>
+      </c>
+      <c r="E152" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="F152" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="G152" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H152" s="45">
+        <v>45261</v>
+      </c>
+      <c r="I152" s="45">
+        <v>46079</v>
+      </c>
+      <c r="J152" s="24">
+        <f t="shared" si="12"/>
+        <v>585</v>
+      </c>
+      <c r="K152" s="44" t="s">
+        <v>353</v>
+      </c>
+      <c r="L152" s="44" t="s">
+        <v>327</v>
+      </c>
+      <c r="M152" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="N152" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="O152" s="49">
+        <v>8018371</v>
+      </c>
+      <c r="P152" s="49">
+        <v>800000</v>
+      </c>
+      <c r="Q152" s="47">
+        <f t="shared" si="14"/>
+        <v>8818371</v>
+      </c>
+      <c r="R152" s="45">
+        <v>46085</v>
+      </c>
+      <c r="S152" s="24">
+        <f t="shared" si="13"/>
+        <v>589</v>
+      </c>
+      <c r="T152" s="44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="153" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A153" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B153" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C153" s="44">
+        <v>58227435</v>
+      </c>
+      <c r="D153" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E153" s="44" t="s">
+        <v>355</v>
+      </c>
+      <c r="F153" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G153" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H153" s="45">
+        <v>46069</v>
+      </c>
+      <c r="I153" s="45">
+        <v>46083</v>
+      </c>
+      <c r="J153" s="24">
+        <f t="shared" si="12"/>
+        <v>11</v>
+      </c>
+      <c r="K153" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L153" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="M153" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="N153" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="O153" s="49">
+        <v>0</v>
+      </c>
+      <c r="P153" s="49">
+        <v>430500</v>
+      </c>
+      <c r="Q153" s="47">
+        <f t="shared" si="14"/>
+        <v>430500</v>
+      </c>
+      <c r="R153" s="45">
+        <v>46085</v>
+      </c>
+      <c r="S153" s="24">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="T153" s="44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A154" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B154" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C154" s="44">
+        <v>54990268</v>
+      </c>
+      <c r="D154" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="E154" s="44" t="s">
+        <v>357</v>
+      </c>
+      <c r="F154" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="G154" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H154" s="45">
+        <v>46002</v>
+      </c>
+      <c r="I154" s="45">
+        <v>46084</v>
+      </c>
+      <c r="J154" s="24">
+        <f t="shared" si="12"/>
+        <v>59</v>
+      </c>
+      <c r="K154" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L154" s="44" t="s">
+        <v>327</v>
+      </c>
+      <c r="M154" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="N154" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="O154" s="49">
+        <v>0</v>
+      </c>
+      <c r="P154" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q154" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R154" s="45">
+        <v>46085</v>
+      </c>
+      <c r="S154" s="24">
+        <f t="shared" si="13"/>
+        <v>60</v>
+      </c>
+      <c r="T154" s="44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="155" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A155" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="B155" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C155" s="44">
+        <v>57782724</v>
+      </c>
+      <c r="D155" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E155" s="44">
+        <v>2722229745</v>
+      </c>
+      <c r="F155" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="G155" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H155" s="45">
+        <v>46057</v>
+      </c>
+      <c r="I155" s="45">
+        <v>46073</v>
+      </c>
+      <c r="J155" s="24">
+        <f t="shared" si="12"/>
+        <v>13</v>
+      </c>
+      <c r="K155" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L155" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="M155" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="N155" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="O155" s="49">
+        <v>150000</v>
+      </c>
+      <c r="P155" s="49">
+        <v>60000</v>
+      </c>
+      <c r="Q155" s="47">
+        <f t="shared" si="14"/>
+        <v>210000</v>
+      </c>
+      <c r="R155" s="45">
+        <v>46085</v>
+      </c>
+      <c r="S155" s="24">
+        <f t="shared" si="13"/>
+        <v>21</v>
+      </c>
+      <c r="T155" s="44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A156" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="B156" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C156" s="44">
+        <v>58585753</v>
+      </c>
+      <c r="D156" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E156" s="44">
+        <v>2722229950</v>
+      </c>
+      <c r="F156" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="G156" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H156" s="45">
+        <v>46072</v>
+      </c>
+      <c r="I156" s="45">
+        <v>46084</v>
+      </c>
+      <c r="J156" s="24">
+        <f t="shared" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="K156" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L156" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="M156" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="N156" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="O156" s="49">
+        <v>150000</v>
+      </c>
+      <c r="P156" s="49">
+        <v>60000</v>
+      </c>
+      <c r="Q156" s="47">
+        <f t="shared" si="14"/>
+        <v>210000</v>
+      </c>
+      <c r="R156" s="45">
+        <v>46085</v>
+      </c>
+      <c r="S156" s="24">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="T156" s="44" t="s">
+        <v>347</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T148" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="53" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="49"/>
     <cfRule type="duplicateValues" dxfId="51" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
     <cfRule type="duplicateValues" dxfId="49" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="47" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
     <cfRule type="duplicateValues" dxfId="45" priority="7"/>
@@ -11502,8 +12085,8 @@
     <cfRule type="duplicateValues" dxfId="23" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="22" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
     <cfRule type="duplicateValues" dxfId="20" priority="41"/>
@@ -11531,8 +12114,8 @@
     <cfRule type="duplicateValues" dxfId="12" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
     <cfRule type="duplicateValues" dxfId="9" priority="48"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C262CFEA-71E2-46C9-AA3F-B019538C1027}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EF6B794-B08C-48BA-B7C0-F56CA25684D7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$T$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$T$163</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="374">
   <si>
     <t>Client</t>
   </si>
@@ -1123,6 +1123,45 @@
   </si>
   <si>
     <t>ARTEMIS CONSTRUCTION ET TRAVAUX</t>
+  </si>
+  <si>
+    <t>BUVPN260035</t>
+  </si>
+  <si>
+    <t>FRANCHISE DE WILLIAMSVILLE</t>
+  </si>
+  <si>
+    <t>WILLIAMCIVILLE</t>
+  </si>
+  <si>
+    <t>BUVPN260046</t>
+  </si>
+  <si>
+    <t>BONDOUKOU</t>
+  </si>
+  <si>
+    <t>VPNLL100068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEVOLUTION </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COCODY 2 PLTX </t>
+  </si>
+  <si>
+    <t>GEK CAPITAL</t>
+  </si>
+  <si>
+    <t>SYTHD260067</t>
+  </si>
+  <si>
+    <t>UNITE SECTORIELLE D'EXECUTION DES PROJETS</t>
+  </si>
+  <si>
+    <t>SYTHD260063</t>
+  </si>
+  <si>
+    <t>BUVPN260043</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1175,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,##0\ _€"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1231,6 +1270,12 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1334,7 +1379,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1475,13 +1520,40 @@
     <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="54">
+  <dxfs count="55">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2035,6 +2107,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -2352,7 +2428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T156"/>
+  <dimension ref="A1:T163"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.6328125" style="26" customWidth="1"/>
@@ -10994,7 +11070,7 @@
         <v>46079</v>
       </c>
       <c r="J141" s="24">
-        <f t="shared" ref="J141:J156" si="12">+NETWORKDAYS(H141,I141)</f>
+        <f t="shared" ref="J141:J163" si="12">+NETWORKDAYS(H141,I141)</f>
         <v>261</v>
       </c>
       <c r="K141" s="25" t="s">
@@ -11023,7 +11099,7 @@
         <v>46079</v>
       </c>
       <c r="S141" s="24">
-        <f t="shared" ref="S141:S156" si="13">NETWORKDAYS(H141,R141)</f>
+        <f t="shared" ref="S141:S163" si="13">NETWORKDAYS(H141,R141)</f>
         <v>261</v>
       </c>
       <c r="T141" s="11" t="s">
@@ -11601,7 +11677,7 @@
         <v>40000</v>
       </c>
       <c r="Q150" s="47">
-        <f t="shared" ref="Q150:Q156" si="14">P150+O150</f>
+        <f t="shared" ref="Q150:Q163" si="14">P150+O150</f>
         <v>190000</v>
       </c>
       <c r="R150" s="45">
@@ -12005,145 +12081,603 @@
         <v>347</v>
       </c>
     </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A157" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B157" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C157" s="44">
+        <v>55490966</v>
+      </c>
+      <c r="D157" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="E157" s="44" t="s">
+        <v>361</v>
+      </c>
+      <c r="F157" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G157" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="H157" s="45">
+        <v>46010</v>
+      </c>
+      <c r="I157" s="45">
+        <v>46084</v>
+      </c>
+      <c r="J157" s="24">
+        <f t="shared" si="12"/>
+        <v>53</v>
+      </c>
+      <c r="K157" s="50" t="s">
+        <v>303</v>
+      </c>
+      <c r="L157" s="51" t="s">
+        <v>327</v>
+      </c>
+      <c r="M157" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="N157" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="O157" s="52">
+        <v>0</v>
+      </c>
+      <c r="P157" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q157" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R157" s="53">
+        <v>46086</v>
+      </c>
+      <c r="S157" s="24">
+        <f t="shared" si="13"/>
+        <v>55</v>
+      </c>
+      <c r="T157" s="44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A158" s="44" t="s">
+        <v>362</v>
+      </c>
+      <c r="B158" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C158" s="44">
+        <v>58853643</v>
+      </c>
+      <c r="D158" s="44" t="s">
+        <v>363</v>
+      </c>
+      <c r="E158" s="44" t="s">
+        <v>364</v>
+      </c>
+      <c r="F158" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G158" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="H158" s="54">
+        <v>46079</v>
+      </c>
+      <c r="I158" s="54">
+        <v>46085</v>
+      </c>
+      <c r="J158" s="24">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="K158" s="50" t="s">
+        <v>303</v>
+      </c>
+      <c r="L158" s="51" t="s">
+        <v>304</v>
+      </c>
+      <c r="M158" s="51" t="s">
+        <v>358</v>
+      </c>
+      <c r="N158" s="44" t="s">
+        <v>148</v>
+      </c>
+      <c r="O158" s="52">
+        <v>0</v>
+      </c>
+      <c r="P158" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q158" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R158" s="53">
+        <v>46086</v>
+      </c>
+      <c r="S158" s="24">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="T158" s="44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A159" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C159" s="55">
+        <v>54479742</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="E159" s="55" t="s">
+        <v>366</v>
+      </c>
+      <c r="F159" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G159" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H159" s="56">
+        <v>45993</v>
+      </c>
+      <c r="I159" s="56">
+        <v>46084</v>
+      </c>
+      <c r="J159" s="24">
+        <f t="shared" si="12"/>
+        <v>66</v>
+      </c>
+      <c r="K159" s="50" t="s">
+        <v>303</v>
+      </c>
+      <c r="L159" s="51" t="s">
+        <v>304</v>
+      </c>
+      <c r="M159" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="N159" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="O159" s="5">
+        <v>6064001</v>
+      </c>
+      <c r="P159" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q159" s="47">
+        <f t="shared" si="14"/>
+        <v>6064001</v>
+      </c>
+      <c r="R159" s="53">
+        <v>46086</v>
+      </c>
+      <c r="S159" s="24">
+        <f t="shared" si="13"/>
+        <v>68</v>
+      </c>
+      <c r="T159" s="44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A160" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="B160" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="C160" s="5">
+        <v>58932414</v>
+      </c>
+      <c r="D160" s="44" t="s">
+        <v>368</v>
+      </c>
+      <c r="E160" s="5">
+        <v>2722229955</v>
+      </c>
+      <c r="F160" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="G160" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H160" s="45">
+        <v>46078</v>
+      </c>
+      <c r="I160" s="45">
+        <v>46086</v>
+      </c>
+      <c r="J160" s="24">
+        <f t="shared" si="12"/>
+        <v>7</v>
+      </c>
+      <c r="K160" s="50" t="s">
+        <v>303</v>
+      </c>
+      <c r="L160" s="51" t="s">
+        <v>304</v>
+      </c>
+      <c r="M160" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="N160" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="O160" s="52">
+        <v>1000000</v>
+      </c>
+      <c r="P160" s="52">
+        <v>495000</v>
+      </c>
+      <c r="Q160" s="47">
+        <f t="shared" si="14"/>
+        <v>1495000</v>
+      </c>
+      <c r="R160" s="53">
+        <v>46086</v>
+      </c>
+      <c r="S160" s="24">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="T160" s="44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A161" s="44" t="s">
+        <v>369</v>
+      </c>
+      <c r="B161" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C161" s="44">
+        <v>57932962</v>
+      </c>
+      <c r="D161" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E161" s="44" t="s">
+        <v>370</v>
+      </c>
+      <c r="F161" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G161" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="H161" s="45">
+        <v>46059</v>
+      </c>
+      <c r="I161" s="45">
+        <v>46085</v>
+      </c>
+      <c r="J161" s="24">
+        <f t="shared" si="12"/>
+        <v>19</v>
+      </c>
+      <c r="K161" s="50" t="s">
+        <v>303</v>
+      </c>
+      <c r="L161" s="51" t="s">
+        <v>304</v>
+      </c>
+      <c r="M161" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N161" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="O161" s="52">
+        <v>500000</v>
+      </c>
+      <c r="P161" s="52">
+        <v>187644</v>
+      </c>
+      <c r="Q161" s="47">
+        <f t="shared" si="14"/>
+        <v>687644</v>
+      </c>
+      <c r="R161" s="53">
+        <v>46086</v>
+      </c>
+      <c r="S161" s="24">
+        <f t="shared" si="13"/>
+        <v>20</v>
+      </c>
+      <c r="T161" s="44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A162" s="44" t="s">
+        <v>371</v>
+      </c>
+      <c r="B162" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C162" s="44">
+        <v>58272102</v>
+      </c>
+      <c r="D162" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E162" s="44" t="s">
+        <v>372</v>
+      </c>
+      <c r="F162" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G162" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H162" s="45">
+        <v>46066</v>
+      </c>
+      <c r="I162" s="45">
+        <v>46083</v>
+      </c>
+      <c r="J162" s="24">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="K162" s="50" t="s">
+        <v>303</v>
+      </c>
+      <c r="L162" s="51" t="s">
+        <v>304</v>
+      </c>
+      <c r="M162" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="N162" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="O162" s="52">
+        <v>2621414</v>
+      </c>
+      <c r="P162" s="52">
+        <v>667054</v>
+      </c>
+      <c r="Q162" s="47">
+        <f t="shared" si="14"/>
+        <v>3288468</v>
+      </c>
+      <c r="R162" s="53">
+        <v>46086</v>
+      </c>
+      <c r="S162" s="24">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
+      <c r="T162" s="44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A163" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B163" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C163" s="44">
+        <v>58150208</v>
+      </c>
+      <c r="D163" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="E163" s="44" t="s">
+        <v>373</v>
+      </c>
+      <c r="F163" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G163" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H163" s="45">
+        <v>46064</v>
+      </c>
+      <c r="I163" s="45">
+        <v>46086</v>
+      </c>
+      <c r="J163" s="24">
+        <f t="shared" si="12"/>
+        <v>17</v>
+      </c>
+      <c r="K163" s="50" t="s">
+        <v>303</v>
+      </c>
+      <c r="L163" s="51" t="s">
+        <v>304</v>
+      </c>
+      <c r="M163" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="N163" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="O163" s="52">
+        <v>2000000</v>
+      </c>
+      <c r="P163" s="52">
+        <v>380000</v>
+      </c>
+      <c r="Q163" s="47">
+        <f t="shared" si="14"/>
+        <v>2380000</v>
+      </c>
+      <c r="R163" s="53">
+        <v>46087</v>
+      </c>
+      <c r="S163" s="24">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
+      <c r="T163" s="44" t="s">
+        <v>347</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T148" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T163" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="53" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="47" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="45" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="43" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="42" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
+    <cfRule type="duplicateValues" dxfId="41" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10">
     <cfRule type="duplicateValues" dxfId="40" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10">
+  <conditionalFormatting sqref="C12">
     <cfRule type="duplicateValues" dxfId="39" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C12">
+  <conditionalFormatting sqref="C15">
     <cfRule type="duplicateValues" dxfId="38" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="37" priority="21"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="36" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="35" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
+    <cfRule type="duplicateValues" dxfId="35" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C33:C37">
     <cfRule type="duplicateValues" dxfId="34" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="33" priority="17"/>
+  <conditionalFormatting sqref="C39">
+    <cfRule type="duplicateValues" dxfId="33" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C39">
+  <conditionalFormatting sqref="C40">
     <cfRule type="duplicateValues" dxfId="32" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="31" priority="14"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="30" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="29" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
+    <cfRule type="duplicateValues" dxfId="29" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C75">
     <cfRule type="duplicateValues" dxfId="28" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="27" priority="3"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="26" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="25" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
+    <cfRule type="duplicateValues" dxfId="25" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C80:C81">
     <cfRule type="duplicateValues" dxfId="24" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="23" priority="44"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="22" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
+    <cfRule type="duplicateValues" dxfId="21" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C93">
     <cfRule type="duplicateValues" dxfId="20" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="19" priority="40"/>
+  <conditionalFormatting sqref="C98">
+    <cfRule type="duplicateValues" dxfId="19" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C98">
+  <conditionalFormatting sqref="C101">
     <cfRule type="duplicateValues" dxfId="18" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="17" priority="37"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="16" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="14" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C114">
+    <cfRule type="duplicateValues" dxfId="14" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C115">
     <cfRule type="duplicateValues" dxfId="13" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="12" priority="31"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="9" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="7" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="5" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="4" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
+    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E53">
     <cfRule type="duplicateValues" dxfId="3" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C157:C163">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EF6B794-B08C-48BA-B7C0-F56CA25684D7}"/>
+  <xr:revisionPtr revIDLastSave="198" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C32127D-9884-48E9-9720-117B3309F02A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="430">
   <si>
     <t>Client</t>
   </si>
@@ -1162,6 +1162,174 @@
   </si>
   <si>
     <t>BUVPN260043</t>
+  </si>
+  <si>
+    <t>HUAWEI PROJET MINISTERE DE LA DEFENSE</t>
+  </si>
+  <si>
+    <t>ABJ&gt;&gt;&gt;YAKRO</t>
+  </si>
+  <si>
+    <t>SYTHD250396</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>ABJ &gt;&gt;&gt;DALOA</t>
+  </si>
+  <si>
+    <t>SYTHD250397</t>
+  </si>
+  <si>
+    <t>ABJ&gt;&gt;&gt;SAN PEDRO</t>
+  </si>
+  <si>
+    <t>SYTHD250399</t>
+  </si>
+  <si>
+    <t>ABJ&gt;&gt;&gt;FERKE</t>
+  </si>
+  <si>
+    <t>SYTHD250416</t>
+  </si>
+  <si>
+    <t>ABJ&gt;&gt;&gt;TENGRELA</t>
+  </si>
+  <si>
+    <t>SYTHD250405</t>
+  </si>
+  <si>
+    <t>ABD&gt;&gt;&gt;BONDOUKOU</t>
+  </si>
+  <si>
+    <t>SYTHD250402</t>
+  </si>
+  <si>
+    <t>ABJ &gt;&gt;&gt;&gt;BOUNA</t>
+  </si>
+  <si>
+    <t>SYTHD250403</t>
+  </si>
+  <si>
+    <t>ABJ&gt;&gt;&gt;&gt;ODIENNE</t>
+  </si>
+  <si>
+    <t>SYTHD250404</t>
+  </si>
+  <si>
+    <t>ABJ &gt;&gt;&gt;TOUBA</t>
+  </si>
+  <si>
+    <t>SYTHD250411</t>
+  </si>
+  <si>
+    <t>ABJ &gt;&gt;&gt;&gt; ADIAKE</t>
+  </si>
+  <si>
+    <t>SYTHD250409</t>
+  </si>
+  <si>
+    <t>ABJ &gt;&gt;&gt;ABENG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYTHD250414 </t>
+  </si>
+  <si>
+    <t>ABJ&gt;&gt;&gt;&gt;BOUNDIALI</t>
+  </si>
+  <si>
+    <t>SYTHD250415</t>
+  </si>
+  <si>
+    <t>ABJ&gt;&gt;&gt;&gt;MAN</t>
+  </si>
+  <si>
+    <t>SYTHD250407</t>
+  </si>
+  <si>
+    <t>ABJ&gt;&gt;&gt;&gt;KORHOGO</t>
+  </si>
+  <si>
+    <t>SYTHD250401</t>
+  </si>
+  <si>
+    <t>KOUTO</t>
+  </si>
+  <si>
+    <t>SYTHD250410</t>
+  </si>
+  <si>
+    <t>ABJ&gt;&gt;&gt;&gt;ABOISSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYTHD250412 </t>
+  </si>
+  <si>
+    <t>Huawei Technologies Cote d'Ivoire SAU</t>
+  </si>
+  <si>
+    <t>PLATEAU&gt;&gt;&gt;MARCORY</t>
+  </si>
+  <si>
+    <t>SYTHD260059</t>
+  </si>
+  <si>
+    <t>AFRIX TELECOM</t>
+  </si>
+  <si>
+    <t>ACCRA&gt;&gt;&gt;KM4</t>
+  </si>
+  <si>
+    <t>OT-FN-2026 001</t>
+  </si>
+  <si>
+    <t>TOP TELECOM SERVICES</t>
+  </si>
+  <si>
+    <t>SYTHD260074</t>
+  </si>
+  <si>
+    <t>LCF GROUP SARL</t>
+  </si>
+  <si>
+    <t>SYTHD260043</t>
+  </si>
+  <si>
+    <t>SYTHD260041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIMORIS </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> YOPOUGON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIGICOM  </t>
+  </si>
+  <si>
+    <t>CMC NETWORKS</t>
+  </si>
+  <si>
+    <t>PLATEAU&gt;&gt;&gt;</t>
+  </si>
+  <si>
+    <t>SYTHD250211</t>
+  </si>
+  <si>
+    <t>DM/WHOLSALE</t>
+  </si>
+  <si>
+    <t>PLATEAU&gt;&gt;AFRIQUE SUD</t>
+  </si>
+  <si>
+    <t>SYTHD250246</t>
+  </si>
+  <si>
+    <t>KWADO INTERNATIONAL FZ-LLC</t>
+  </si>
+  <si>
+    <t>SYTHD260019</t>
   </si>
 </sst>
 </file>
@@ -1379,7 +1547,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1537,13 +1705,205 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="55">
+  <dxfs count="73">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2428,17 +2788,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T163"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:T192"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.6328125" style="26" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7265625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.08984375" customWidth="1"/>
     <col min="12" max="12" width="12.08984375" customWidth="1"/>
+    <col min="13" max="13" width="7.90625" customWidth="1"/>
+    <col min="14" max="14" width="7.54296875" customWidth="1"/>
     <col min="15" max="15" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.90625" style="18" customWidth="1"/>
+    <col min="16" max="16" width="9.08984375" customWidth="1"/>
+    <col min="17" max="17" width="9.90625" style="18" customWidth="1"/>
     <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.1796875" customWidth="1"/>
     <col min="20" max="20" width="6.54296875" customWidth="1"/>
@@ -2506,7 +2870,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29" t="s">
         <v>154</v>
       </c>
@@ -2628,7 +2992,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>154</v>
       </c>
@@ -2689,7 +3053,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
         <v>154</v>
       </c>
@@ -2872,7 +3236,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>166</v>
       </c>
@@ -2933,7 +3297,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>169</v>
       </c>
@@ -2994,7 +3358,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>172</v>
       </c>
@@ -3055,7 +3419,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>172</v>
       </c>
@@ -3116,7 +3480,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
         <v>177</v>
       </c>
@@ -3177,7 +3541,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
         <v>154</v>
       </c>
@@ -3238,7 +3602,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
         <v>154</v>
       </c>
@@ -3299,7 +3663,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>172</v>
       </c>
@@ -3360,7 +3724,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>154</v>
       </c>
@@ -3421,7 +3785,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>154</v>
       </c>
@@ -3482,7 +3846,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
         <v>186</v>
       </c>
@@ -3543,7 +3907,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>189</v>
       </c>
@@ -3604,7 +3968,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
         <v>189</v>
       </c>
@@ -3665,7 +4029,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>193</v>
       </c>
@@ -3726,7 +4090,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>43</v>
       </c>
@@ -3787,7 +4151,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
         <v>201</v>
       </c>
@@ -3848,7 +4212,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>204</v>
       </c>
@@ -4031,7 +4395,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
         <v>172</v>
       </c>
@@ -4092,7 +4456,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
         <v>210</v>
       </c>
@@ -4153,7 +4517,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
         <v>213</v>
       </c>
@@ -4336,7 +4700,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
         <v>81</v>
       </c>
@@ -4397,7 +4761,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
         <v>91</v>
       </c>
@@ -4458,7 +4822,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
         <v>91</v>
       </c>
@@ -4519,7 +4883,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
         <v>91</v>
       </c>
@@ -4580,7 +4944,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12" t="s">
         <v>91</v>
       </c>
@@ -4641,7 +5005,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12" t="s">
         <v>91</v>
       </c>
@@ -4702,7 +5066,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
         <v>226</v>
       </c>
@@ -4763,7 +5127,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
         <v>228</v>
       </c>
@@ -4824,7 +5188,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
         <v>91</v>
       </c>
@@ -4885,7 +5249,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
         <v>231</v>
       </c>
@@ -4946,7 +5310,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
         <v>234</v>
       </c>
@@ -5129,7 +5493,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
         <v>238</v>
       </c>
@@ -5190,7 +5554,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="12" t="s">
         <v>240</v>
       </c>
@@ -5251,7 +5615,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="12" t="s">
         <v>91</v>
       </c>
@@ -5312,7 +5676,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="12" t="s">
         <v>243</v>
       </c>
@@ -5373,7 +5737,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="12" t="s">
         <v>246</v>
       </c>
@@ -5434,7 +5798,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12" t="s">
         <v>248</v>
       </c>
@@ -5495,7 +5859,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="12" t="s">
         <v>250</v>
       </c>
@@ -5556,7 +5920,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="12" t="s">
         <v>250</v>
       </c>
@@ -5617,7 +5981,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="12" t="s">
         <v>253</v>
       </c>
@@ -5800,7 +6164,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="12" t="s">
         <v>259</v>
       </c>
@@ -5861,7 +6225,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="12" t="s">
         <v>259</v>
       </c>
@@ -5922,7 +6286,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="12" t="s">
         <v>253</v>
       </c>
@@ -5983,7 +6347,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="12" t="s">
         <v>265</v>
       </c>
@@ -6044,7 +6408,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="12" t="s">
         <v>267</v>
       </c>
@@ -6105,7 +6469,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="12" t="s">
         <v>271</v>
       </c>
@@ -6166,7 +6530,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="12" t="s">
         <v>43</v>
       </c>
@@ -6227,7 +6591,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="11" t="s">
         <v>58</v>
       </c>
@@ -6288,7 +6652,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="12" t="s">
         <v>91</v>
       </c>
@@ -6349,7 +6713,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="12" t="s">
         <v>91</v>
       </c>
@@ -6410,7 +6774,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12" t="s">
         <v>91</v>
       </c>
@@ -6471,7 +6835,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="12" t="s">
         <v>282</v>
       </c>
@@ -6593,7 +6957,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="12" t="s">
         <v>286</v>
       </c>
@@ -6654,7 +7018,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="22" t="s">
         <v>288</v>
       </c>
@@ -6837,7 +7201,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="12" t="s">
         <v>91</v>
       </c>
@@ -6898,7 +7262,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="12" t="s">
         <v>294</v>
       </c>
@@ -6959,7 +7323,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="12" t="s">
         <v>91</v>
       </c>
@@ -7020,7 +7384,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="12" t="s">
         <v>299</v>
       </c>
@@ -7081,7 +7445,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="12" t="s">
         <v>18</v>
       </c>
@@ -7142,7 +7506,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="12" t="s">
         <v>27</v>
       </c>
@@ -7264,7 +7628,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="12" t="s">
         <v>35</v>
       </c>
@@ -7325,7 +7689,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="12" t="s">
         <v>35</v>
       </c>
@@ -7447,7 +7811,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="12" t="s">
         <v>43</v>
       </c>
@@ -7508,7 +7872,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="12" t="s">
         <v>43</v>
       </c>
@@ -7569,7 +7933,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="12" t="s">
         <v>52</v>
       </c>
@@ -7691,7 +8055,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="22" t="s">
         <v>58</v>
       </c>
@@ -7752,7 +8116,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="12" t="s">
         <v>62</v>
       </c>
@@ -7813,7 +8177,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="12" t="s">
         <v>65</v>
       </c>
@@ -7874,7 +8238,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="12" t="s">
         <v>67</v>
       </c>
@@ -7935,7 +8299,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="12" t="s">
         <v>70</v>
       </c>
@@ -7996,7 +8360,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="12" t="s">
         <v>75</v>
       </c>
@@ -8057,7 +8421,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:20" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="30" t="s">
         <v>77</v>
       </c>
@@ -8118,7 +8482,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="12" t="s">
         <v>43</v>
       </c>
@@ -8179,7 +8543,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="12" t="s">
         <v>81</v>
       </c>
@@ -8362,7 +8726,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="12" t="s">
         <v>88</v>
       </c>
@@ -8423,7 +8787,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="12" t="s">
         <v>91</v>
       </c>
@@ -8484,7 +8848,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:20" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="30" t="s">
         <v>95</v>
       </c>
@@ -8545,7 +8909,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="12" t="s">
         <v>58</v>
       </c>
@@ -8606,7 +8970,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="22" t="s">
         <v>58</v>
       </c>
@@ -8667,7 +9031,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="12" t="s">
         <v>43</v>
       </c>
@@ -8728,7 +9092,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="12" t="s">
         <v>103</v>
       </c>
@@ -9094,7 +9458,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="12" t="s">
         <v>110</v>
       </c>
@@ -9155,7 +9519,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="12" t="s">
         <v>113</v>
       </c>
@@ -9216,7 +9580,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="11" t="s">
         <v>116</v>
       </c>
@@ -9277,7 +9641,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="12" t="s">
         <v>120</v>
       </c>
@@ -9338,7 +9702,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="12" t="s">
         <v>123</v>
       </c>
@@ -9399,7 +9763,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="12" t="s">
         <v>110</v>
       </c>
@@ -9460,7 +9824,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="12" t="s">
         <v>127</v>
       </c>
@@ -9643,7 +10007,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="12" t="s">
         <v>132</v>
       </c>
@@ -9704,7 +10068,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="12" t="s">
         <v>134</v>
       </c>
@@ -9765,7 +10129,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="12" t="s">
         <v>134</v>
       </c>
@@ -9826,7 +10190,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="12" t="s">
         <v>140</v>
       </c>
@@ -9887,7 +10251,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="12" t="s">
         <v>143</v>
       </c>
@@ -9948,7 +10312,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="12" t="s">
         <v>145</v>
       </c>
@@ -10009,7 +10373,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="12" t="s">
         <v>149</v>
       </c>
@@ -10070,7 +10434,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="12" t="s">
         <v>143</v>
       </c>
@@ -10131,7 +10495,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="12" t="s">
         <v>301</v>
       </c>
@@ -10196,7 +10560,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="12" t="s">
         <v>305</v>
       </c>
@@ -10261,7 +10625,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="12" t="s">
         <v>145</v>
       </c>
@@ -10456,7 +10820,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="132" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:20" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="22" t="s">
         <v>311</v>
       </c>
@@ -10521,7 +10885,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="133" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:20" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="12" t="s">
         <v>311</v>
       </c>
@@ -10586,7 +10950,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="12" t="s">
         <v>317</v>
       </c>
@@ -11070,7 +11434,7 @@
         <v>46079</v>
       </c>
       <c r="J141" s="24">
-        <f t="shared" ref="J141:J163" si="12">+NETWORKDAYS(H141,I141)</f>
+        <f t="shared" ref="J141:J192" si="12">+NETWORKDAYS(H141,I141)</f>
         <v>261</v>
       </c>
       <c r="K141" s="25" t="s">
@@ -11099,14 +11463,14 @@
         <v>46079</v>
       </c>
       <c r="S141" s="24">
-        <f t="shared" ref="S141:S163" si="13">NETWORKDAYS(H141,R141)</f>
+        <f t="shared" ref="S141:S192" si="13">NETWORKDAYS(H141,R141)</f>
         <v>261</v>
       </c>
       <c r="T141" s="11" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="12" t="s">
         <v>328</v>
       </c>
@@ -11171,7 +11535,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="12" t="s">
         <v>331</v>
       </c>
@@ -11236,7 +11600,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="12" t="s">
         <v>333</v>
       </c>
@@ -11301,7 +11665,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="12" t="s">
         <v>335</v>
       </c>
@@ -11366,7 +11730,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="12" t="s">
         <v>140</v>
       </c>
@@ -11431,7 +11795,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="12" t="s">
         <v>140</v>
       </c>
@@ -11496,7 +11860,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="22" t="s">
         <v>58</v>
       </c>
@@ -11561,7 +11925,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="12" t="s">
         <v>344</v>
       </c>
@@ -11677,7 +12041,7 @@
         <v>40000</v>
       </c>
       <c r="Q150" s="47">
-        <f t="shared" ref="Q150:Q163" si="14">P150+O150</f>
+        <f t="shared" ref="Q150:Q192" si="14">P150+O150</f>
         <v>190000</v>
       </c>
       <c r="R150" s="45">
@@ -11691,7 +12055,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="12" t="s">
         <v>324</v>
       </c>
@@ -11756,7 +12120,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="12" t="s">
         <v>350</v>
       </c>
@@ -11821,7 +12185,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="12" t="s">
         <v>354</v>
       </c>
@@ -11886,7 +12250,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="12" t="s">
         <v>145</v>
       </c>
@@ -12081,7 +12445,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="44" t="s">
         <v>43</v>
       </c>
@@ -12146,7 +12510,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="44" t="s">
         <v>362</v>
       </c>
@@ -12211,7 +12575,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
         <v>43</v>
       </c>
@@ -12341,7 +12705,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="44" t="s">
         <v>369</v>
       </c>
@@ -12406,7 +12770,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="44" t="s">
         <v>371</v>
       </c>
@@ -12471,7 +12835,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="44" t="s">
         <v>43</v>
       </c>
@@ -12536,148 +12900,2086 @@
         <v>347</v>
       </c>
     </row>
+    <row r="164" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A164" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B164" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C164" s="12">
+        <v>57932962</v>
+      </c>
+      <c r="D164" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E164" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="F164" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G164" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H164" s="14">
+        <v>46059</v>
+      </c>
+      <c r="I164" s="14">
+        <v>46085</v>
+      </c>
+      <c r="J164" s="24">
+        <f t="shared" si="12"/>
+        <v>19</v>
+      </c>
+      <c r="K164" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L164" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M164" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N164" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="O164" s="19">
+        <v>500000</v>
+      </c>
+      <c r="P164" s="19">
+        <v>187644</v>
+      </c>
+      <c r="Q164" s="47">
+        <f t="shared" si="14"/>
+        <v>687644</v>
+      </c>
+      <c r="R164" s="13">
+        <v>46086</v>
+      </c>
+      <c r="S164" s="24">
+        <f t="shared" si="13"/>
+        <v>20</v>
+      </c>
+      <c r="T164" s="11" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="165" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A165" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B165" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C165" s="12">
+        <v>58272102</v>
+      </c>
+      <c r="D165" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E165" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="F165" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G165" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H165" s="14">
+        <v>46066</v>
+      </c>
+      <c r="I165" s="14">
+        <v>46083</v>
+      </c>
+      <c r="J165" s="24">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="K165" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L165" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M165" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N165" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O165" s="19">
+        <v>2621414</v>
+      </c>
+      <c r="P165" s="19">
+        <v>667054</v>
+      </c>
+      <c r="Q165" s="47">
+        <f t="shared" si="14"/>
+        <v>3288468</v>
+      </c>
+      <c r="R165" s="13">
+        <v>46086</v>
+      </c>
+      <c r="S165" s="24">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
+      <c r="T165" s="11" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A166" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B166" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C166" s="12">
+        <v>58150208</v>
+      </c>
+      <c r="D166" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E166" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="F166" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G166" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H166" s="14">
+        <v>46064</v>
+      </c>
+      <c r="I166" s="14">
+        <v>46086</v>
+      </c>
+      <c r="J166" s="24">
+        <f t="shared" si="12"/>
+        <v>17</v>
+      </c>
+      <c r="K166" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L166" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M166" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N166" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O166" s="19">
+        <v>2000000</v>
+      </c>
+      <c r="P166" s="19">
+        <v>380000</v>
+      </c>
+      <c r="Q166" s="47">
+        <f t="shared" si="14"/>
+        <v>2380000</v>
+      </c>
+      <c r="R166" s="13">
+        <v>46087</v>
+      </c>
+      <c r="S166" s="24">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
+      <c r="T166" s="11" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A167" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B167" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C167" s="12">
+        <v>54968651</v>
+      </c>
+      <c r="D167" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="E167" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="F167" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G167" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H167" s="14">
+        <v>46002</v>
+      </c>
+      <c r="I167" s="14">
+        <v>46076</v>
+      </c>
+      <c r="J167" s="24">
+        <f t="shared" si="12"/>
+        <v>53</v>
+      </c>
+      <c r="K167" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="L167" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="M167" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N167" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="O167" s="19">
+        <v>1000000</v>
+      </c>
+      <c r="P167" s="19">
+        <v>1700000</v>
+      </c>
+      <c r="Q167" s="47">
+        <f t="shared" si="14"/>
+        <v>2700000</v>
+      </c>
+      <c r="R167" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S167" s="24">
+        <f t="shared" si="13"/>
+        <v>63</v>
+      </c>
+      <c r="T167" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="168" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A168" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B168" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C168" s="12">
+        <v>54971775</v>
+      </c>
+      <c r="D168" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="E168" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="F168" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G168" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H168" s="14">
+        <v>46002</v>
+      </c>
+      <c r="I168" s="14">
+        <v>46057</v>
+      </c>
+      <c r="J168" s="24">
+        <f t="shared" si="12"/>
+        <v>40</v>
+      </c>
+      <c r="K168" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="L168" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="M168" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N168" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="O168" s="19">
+        <v>1000000</v>
+      </c>
+      <c r="P168" s="19">
+        <v>1700000</v>
+      </c>
+      <c r="Q168" s="47">
+        <f t="shared" si="14"/>
+        <v>2700000</v>
+      </c>
+      <c r="R168" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S168" s="24">
+        <f t="shared" si="13"/>
+        <v>63</v>
+      </c>
+      <c r="T168" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="169" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A169" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C169" s="12">
+        <v>54973833</v>
+      </c>
+      <c r="D169" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="E169" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="F169" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G169" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H169" s="14">
+        <v>46002</v>
+      </c>
+      <c r="I169" s="14">
+        <v>46021</v>
+      </c>
+      <c r="J169" s="24">
+        <f t="shared" si="12"/>
+        <v>14</v>
+      </c>
+      <c r="K169" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L169" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M169" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N169" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="O169" s="19">
+        <v>250000</v>
+      </c>
+      <c r="P169" s="19">
+        <v>1700000</v>
+      </c>
+      <c r="Q169" s="47">
+        <f t="shared" si="14"/>
+        <v>1950000</v>
+      </c>
+      <c r="R169" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S169" s="24">
+        <f t="shared" si="13"/>
+        <v>63</v>
+      </c>
+      <c r="T169" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="170" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A170" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B170" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C170" s="12">
+        <v>54980338</v>
+      </c>
+      <c r="D170" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="E170" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="F170" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G170" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H170" s="14">
+        <v>46002</v>
+      </c>
+      <c r="I170" s="23">
+        <v>46024</v>
+      </c>
+      <c r="J170" s="24">
+        <f t="shared" si="12"/>
+        <v>17</v>
+      </c>
+      <c r="K170" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L170" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M170" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N170" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O170" s="19">
+        <v>500000</v>
+      </c>
+      <c r="P170" s="19">
+        <v>1300000</v>
+      </c>
+      <c r="Q170" s="47">
+        <f t="shared" si="14"/>
+        <v>1800000</v>
+      </c>
+      <c r="R170" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S170" s="24">
+        <f t="shared" si="13"/>
+        <v>63</v>
+      </c>
+      <c r="T170" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="171" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A171" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B171" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C171" s="12">
+        <v>55103426</v>
+      </c>
+      <c r="D171" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="E171" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="F171" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G171" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H171" s="14">
+        <v>46004</v>
+      </c>
+      <c r="I171" s="14">
+        <v>46042</v>
+      </c>
+      <c r="J171" s="24">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="K171" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L171" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M171" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N171" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O171" s="19">
+        <v>500000</v>
+      </c>
+      <c r="P171" s="19">
+        <v>1300000</v>
+      </c>
+      <c r="Q171" s="47">
+        <f t="shared" si="14"/>
+        <v>1800000</v>
+      </c>
+      <c r="R171" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S171" s="24">
+        <f t="shared" si="13"/>
+        <v>61</v>
+      </c>
+      <c r="T171" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="172" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A172" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B172" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C172" s="12">
+        <v>54979384</v>
+      </c>
+      <c r="D172" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="E172" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="F172" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G172" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H172" s="14">
+        <v>46002</v>
+      </c>
+      <c r="I172" s="14">
+        <v>46065</v>
+      </c>
+      <c r="J172" s="24">
+        <f t="shared" si="12"/>
+        <v>46</v>
+      </c>
+      <c r="K172" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="L172" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="M172" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N172" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O172" s="19">
+        <v>250000</v>
+      </c>
+      <c r="P172" s="19">
+        <v>1300000</v>
+      </c>
+      <c r="Q172" s="47">
+        <f t="shared" si="14"/>
+        <v>1550000</v>
+      </c>
+      <c r="R172" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S172" s="24">
+        <f t="shared" si="13"/>
+        <v>63</v>
+      </c>
+      <c r="T172" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="173" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A173" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B173" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C173" s="12">
+        <v>54979901</v>
+      </c>
+      <c r="D173" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="E173" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="F173" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G173" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H173" s="14">
+        <v>46002</v>
+      </c>
+      <c r="I173" s="14">
+        <v>46036</v>
+      </c>
+      <c r="J173" s="24">
+        <f t="shared" si="12"/>
+        <v>25</v>
+      </c>
+      <c r="K173" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L173" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M173" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N173" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O173" s="19">
+        <v>500000</v>
+      </c>
+      <c r="P173" s="12">
+        <v>1300000</v>
+      </c>
+      <c r="Q173" s="47">
+        <f t="shared" si="14"/>
+        <v>1800000</v>
+      </c>
+      <c r="R173" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S173" s="24">
+        <f t="shared" si="13"/>
+        <v>63</v>
+      </c>
+      <c r="T173" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="174" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A174" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B174" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C174" s="12">
+        <v>54981048</v>
+      </c>
+      <c r="D174" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="E174" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="F174" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G174" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H174" s="14">
+        <v>46002</v>
+      </c>
+      <c r="I174" s="14">
+        <v>46048</v>
+      </c>
+      <c r="J174" s="24">
+        <f t="shared" si="12"/>
+        <v>33</v>
+      </c>
+      <c r="K174" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="L174" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="M174" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N174" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O174" s="19">
+        <v>500000</v>
+      </c>
+      <c r="P174" s="19">
+        <v>1300000</v>
+      </c>
+      <c r="Q174" s="47">
+        <f t="shared" si="14"/>
+        <v>1800000</v>
+      </c>
+      <c r="R174" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S174" s="24">
+        <f t="shared" si="13"/>
+        <v>63</v>
+      </c>
+      <c r="T174" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="175" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A175" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C175" s="57">
+        <v>55105863</v>
+      </c>
+      <c r="D175" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="E175" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="F175" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G175" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H175" s="39">
+        <v>46004</v>
+      </c>
+      <c r="I175" s="14">
+        <v>46065</v>
+      </c>
+      <c r="J175" s="24">
+        <f t="shared" si="12"/>
+        <v>44</v>
+      </c>
+      <c r="K175" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="L175" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="M175" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N175" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O175" s="19">
+        <v>1250000</v>
+      </c>
+      <c r="P175" s="19">
+        <v>1300000</v>
+      </c>
+      <c r="Q175" s="47">
+        <f t="shared" si="14"/>
+        <v>2550000</v>
+      </c>
+      <c r="R175" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S175" s="24">
+        <f t="shared" si="13"/>
+        <v>61</v>
+      </c>
+      <c r="T175" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="176" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A176" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C176" s="12">
+        <v>55104619</v>
+      </c>
+      <c r="D176" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="E176" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="F176" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G176" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H176" s="14">
+        <v>46004</v>
+      </c>
+      <c r="I176" s="14">
+        <v>46081</v>
+      </c>
+      <c r="J176" s="24">
+        <f t="shared" si="12"/>
+        <v>55</v>
+      </c>
+      <c r="K176" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L176" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="M176" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N176" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="O176" s="19">
+        <v>1000000</v>
+      </c>
+      <c r="P176" s="19">
+        <v>1700000</v>
+      </c>
+      <c r="Q176" s="47">
+        <f t="shared" si="14"/>
+        <v>2700000</v>
+      </c>
+      <c r="R176" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S176" s="24">
+        <f t="shared" si="13"/>
+        <v>61</v>
+      </c>
+      <c r="T176" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="177" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A177" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C177" s="12">
+        <v>54978747</v>
+      </c>
+      <c r="D177" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="E177" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="F177" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G177" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H177" s="14">
+        <v>46002</v>
+      </c>
+      <c r="I177" s="14">
+        <v>46034</v>
+      </c>
+      <c r="J177" s="24">
+        <f t="shared" si="12"/>
+        <v>23</v>
+      </c>
+      <c r="K177" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L177" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M177" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N177" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O177" s="19">
+        <v>250000</v>
+      </c>
+      <c r="P177" s="19">
+        <v>1300000</v>
+      </c>
+      <c r="Q177" s="47">
+        <f t="shared" si="14"/>
+        <v>1550000</v>
+      </c>
+      <c r="R177" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S177" s="24">
+        <f t="shared" si="13"/>
+        <v>63</v>
+      </c>
+      <c r="T177" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A178" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B178" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C178" s="12">
+        <v>54978242</v>
+      </c>
+      <c r="D178" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="E178" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="F178" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G178" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H178" s="14">
+        <v>46002</v>
+      </c>
+      <c r="I178" s="14">
+        <v>46041</v>
+      </c>
+      <c r="J178" s="24">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="K178" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="L178" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="M178" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N178" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="O178" s="19">
+        <v>500000</v>
+      </c>
+      <c r="P178" s="19">
+        <v>1700000</v>
+      </c>
+      <c r="Q178" s="47">
+        <f t="shared" si="14"/>
+        <v>2200000</v>
+      </c>
+      <c r="R178" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S178" s="24">
+        <f t="shared" si="13"/>
+        <v>63</v>
+      </c>
+      <c r="T178" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A179" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B179" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C179" s="12">
+        <v>55105778</v>
+      </c>
+      <c r="D179" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="E179" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="F179" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G179" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H179" s="14">
+        <v>46004</v>
+      </c>
+      <c r="I179" s="14">
+        <v>46079</v>
+      </c>
+      <c r="J179" s="24">
+        <f t="shared" si="12"/>
+        <v>54</v>
+      </c>
+      <c r="K179" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="L179" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="M179" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N179" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O179" s="19">
+        <v>1000000</v>
+      </c>
+      <c r="P179" s="19">
+        <v>1300000</v>
+      </c>
+      <c r="Q179" s="47">
+        <f t="shared" si="14"/>
+        <v>2300000</v>
+      </c>
+      <c r="R179" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S179" s="24">
+        <f t="shared" si="13"/>
+        <v>61</v>
+      </c>
+      <c r="T179" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A180" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B180" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C180" s="12">
+        <v>54973195</v>
+      </c>
+      <c r="D180" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="E180" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="F180" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G180" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H180" s="14">
+        <v>46002</v>
+      </c>
+      <c r="I180" s="14">
+        <v>46027</v>
+      </c>
+      <c r="J180" s="24">
+        <f t="shared" si="12"/>
+        <v>18</v>
+      </c>
+      <c r="K180" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="L180" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M180" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N180" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="O180" s="19">
+        <v>500000</v>
+      </c>
+      <c r="P180" s="19">
+        <v>1700000</v>
+      </c>
+      <c r="Q180" s="47">
+        <f t="shared" si="14"/>
+        <v>2200000</v>
+      </c>
+      <c r="R180" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S180" s="24">
+        <f t="shared" si="13"/>
+        <v>63</v>
+      </c>
+      <c r="T180" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A181" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B181" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C181" s="12">
+        <v>55105296</v>
+      </c>
+      <c r="D181" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="E181" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="F181" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G181" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H181" s="14">
+        <v>46004</v>
+      </c>
+      <c r="I181" s="14">
+        <v>46035</v>
+      </c>
+      <c r="J181" s="24">
+        <f t="shared" si="12"/>
+        <v>22</v>
+      </c>
+      <c r="K181" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="L181" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M181" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N181" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O181" s="19">
+        <v>1500000</v>
+      </c>
+      <c r="P181" s="19">
+        <v>1300000</v>
+      </c>
+      <c r="Q181" s="47">
+        <f t="shared" si="14"/>
+        <v>2800000</v>
+      </c>
+      <c r="R181" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S181" s="24">
+        <f t="shared" si="13"/>
+        <v>61</v>
+      </c>
+      <c r="T181" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A182" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B182" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C182" s="5">
+        <v>54976425</v>
+      </c>
+      <c r="D182" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="E182" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="F182" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G182" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H182" s="14">
+        <v>46002</v>
+      </c>
+      <c r="I182" s="23">
+        <v>46024</v>
+      </c>
+      <c r="J182" s="24">
+        <f t="shared" si="12"/>
+        <v>17</v>
+      </c>
+      <c r="K182" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="L182" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M182" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N182" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O182" s="19">
+        <v>1250000</v>
+      </c>
+      <c r="P182" s="19">
+        <v>1300000</v>
+      </c>
+      <c r="Q182" s="47">
+        <f t="shared" si="14"/>
+        <v>2550000</v>
+      </c>
+      <c r="R182" s="13">
+        <v>46090</v>
+      </c>
+      <c r="S182" s="24">
+        <f t="shared" si="13"/>
+        <v>63</v>
+      </c>
+      <c r="T182" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="183" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A183" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C183" s="12">
+        <v>57900967</v>
+      </c>
+      <c r="D183" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="E183" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="F183" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G183" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H183" s="14">
+        <v>46059</v>
+      </c>
+      <c r="I183" s="14">
+        <v>46079</v>
+      </c>
+      <c r="J183" s="24">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="K183" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="L183" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M183" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N183" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O183" s="19">
+        <v>1388682</v>
+      </c>
+      <c r="P183" s="19">
+        <v>2207940</v>
+      </c>
+      <c r="Q183" s="47">
+        <f t="shared" si="14"/>
+        <v>3596622</v>
+      </c>
+      <c r="R183" s="13">
+        <v>46091</v>
+      </c>
+      <c r="S183" s="24">
+        <f t="shared" si="13"/>
+        <v>23</v>
+      </c>
+      <c r="T183" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A184" s="22" t="s">
+        <v>411</v>
+      </c>
+      <c r="B184" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C184" s="12">
+        <v>58136263</v>
+      </c>
+      <c r="D184" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="E184" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="F184" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G184" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H184" s="14">
+        <v>46071</v>
+      </c>
+      <c r="I184" s="14">
+        <v>46085</v>
+      </c>
+      <c r="J184" s="24">
+        <f t="shared" si="12"/>
+        <v>11</v>
+      </c>
+      <c r="K184" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L184" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M184" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="N184" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="O184" s="19">
+        <v>0</v>
+      </c>
+      <c r="P184" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q184" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R184" s="13">
+        <v>46091</v>
+      </c>
+      <c r="S184" s="24">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
+      <c r="T184" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="185" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A185" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="B185" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C185" s="12">
+        <v>59207750</v>
+      </c>
+      <c r="D185" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E185" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="F185" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G185" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H185" s="14">
+        <v>46083</v>
+      </c>
+      <c r="I185" s="14">
+        <v>46091</v>
+      </c>
+      <c r="J185" s="24">
+        <f t="shared" si="12"/>
+        <v>7</v>
+      </c>
+      <c r="K185" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="L185" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M185" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N185" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="O185" s="19">
+        <v>1000000</v>
+      </c>
+      <c r="P185" s="19">
+        <v>590836</v>
+      </c>
+      <c r="Q185" s="47">
+        <f t="shared" si="14"/>
+        <v>1590836</v>
+      </c>
+      <c r="R185" s="13">
+        <v>46091</v>
+      </c>
+      <c r="S185" s="24">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="T185" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A186" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="B186" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C186" s="11">
+        <v>57111758</v>
+      </c>
+      <c r="D186" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="E186" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="F186" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G186" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H186" s="14">
+        <v>46044</v>
+      </c>
+      <c r="I186" s="14">
+        <v>46059</v>
+      </c>
+      <c r="J186" s="24">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="K186" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L186" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M186" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N186" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="O186" s="19">
+        <v>0</v>
+      </c>
+      <c r="P186" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q186" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R186" s="13">
+        <v>46091</v>
+      </c>
+      <c r="S186" s="24">
+        <f t="shared" si="13"/>
+        <v>34</v>
+      </c>
+      <c r="T186" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A187" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="B187" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C187" s="12">
+        <v>57111764</v>
+      </c>
+      <c r="D187" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="E187" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="F187" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G187" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H187" s="13">
+        <v>46044</v>
+      </c>
+      <c r="I187" s="14">
+        <v>46059</v>
+      </c>
+      <c r="J187" s="24">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="K187" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L187" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M187" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N187" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="O187" s="19">
+        <v>0</v>
+      </c>
+      <c r="P187" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q187" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R187" s="13">
+        <v>46091</v>
+      </c>
+      <c r="S187" s="24">
+        <f t="shared" si="13"/>
+        <v>34</v>
+      </c>
+      <c r="T187" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="188" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A188" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="B188" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C188" s="5">
+        <v>59019541</v>
+      </c>
+      <c r="D188" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="E188" s="5">
+        <v>2723489400</v>
+      </c>
+      <c r="F188" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G188" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H188" s="13">
+        <v>46079</v>
+      </c>
+      <c r="I188" s="13">
+        <v>46091</v>
+      </c>
+      <c r="J188" s="24">
+        <f t="shared" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="K188" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="L188" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M188" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N188" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O188" s="59">
+        <v>150000</v>
+      </c>
+      <c r="P188" s="59">
+        <v>60000</v>
+      </c>
+      <c r="Q188" s="47">
+        <f t="shared" si="14"/>
+        <v>210000</v>
+      </c>
+      <c r="R188" s="13">
+        <v>46091</v>
+      </c>
+      <c r="S188" s="24">
+        <f t="shared" si="13"/>
+        <v>9</v>
+      </c>
+      <c r="T188" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A189" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="B189" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C189" s="9">
+        <v>54955589</v>
+      </c>
+      <c r="D189" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E189" s="9">
+        <v>2722229185</v>
+      </c>
+      <c r="F189" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G189" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H189" s="13">
+        <v>46002</v>
+      </c>
+      <c r="I189" s="13">
+        <v>46021</v>
+      </c>
+      <c r="J189" s="24">
+        <f t="shared" si="12"/>
+        <v>14</v>
+      </c>
+      <c r="K189" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="L189" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M189" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N189" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O189" s="59">
+        <v>150000</v>
+      </c>
+      <c r="P189" s="59">
+        <v>60000</v>
+      </c>
+      <c r="Q189" s="47">
+        <f t="shared" si="14"/>
+        <v>210000</v>
+      </c>
+      <c r="R189" s="13">
+        <v>46091</v>
+      </c>
+      <c r="S189" s="24">
+        <f t="shared" si="13"/>
+        <v>64</v>
+      </c>
+      <c r="T189" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A190" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="B190" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C190" s="12">
+        <v>47899159</v>
+      </c>
+      <c r="D190" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="E190" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="F190" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G190" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H190" s="14">
+        <v>45862</v>
+      </c>
+      <c r="I190" s="14">
+        <v>46055</v>
+      </c>
+      <c r="J190" s="24">
+        <f t="shared" si="12"/>
+        <v>138</v>
+      </c>
+      <c r="K190" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L190" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M190" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="N190" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="O190" s="19">
+        <v>0</v>
+      </c>
+      <c r="P190" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q190" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R190" s="13">
+        <v>46091</v>
+      </c>
+      <c r="S190" s="24">
+        <f t="shared" si="13"/>
+        <v>164</v>
+      </c>
+      <c r="T190" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A191" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C191" s="22">
+        <v>48425163</v>
+      </c>
+      <c r="D191" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="E191" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="F191" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G191" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H191" s="14">
+        <v>45880</v>
+      </c>
+      <c r="I191" s="23">
+        <v>46061</v>
+      </c>
+      <c r="J191" s="24">
+        <f t="shared" si="12"/>
+        <v>130</v>
+      </c>
+      <c r="K191" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L191" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M191" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="N191" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="O191" s="19">
+        <v>0</v>
+      </c>
+      <c r="P191" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q191" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R191" s="13">
+        <v>46091</v>
+      </c>
+      <c r="S191" s="24">
+        <f t="shared" si="13"/>
+        <v>152</v>
+      </c>
+      <c r="T191" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A192" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="B192" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C192" s="12">
+        <v>53934458</v>
+      </c>
+      <c r="D192" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E192" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="F192" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G192" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H192" s="14">
+        <v>45995</v>
+      </c>
+      <c r="I192" s="14">
+        <v>46063</v>
+      </c>
+      <c r="J192" s="24">
+        <f t="shared" si="12"/>
+        <v>49</v>
+      </c>
+      <c r="K192" s="58" t="s">
+        <v>303</v>
+      </c>
+      <c r="L192" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="M192" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="N192" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="O192" s="60">
+        <v>0</v>
+      </c>
+      <c r="P192" s="60">
+        <v>0</v>
+      </c>
+      <c r="Q192" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R192" s="13">
+        <v>46091</v>
+      </c>
+      <c r="S192" s="24">
+        <f t="shared" si="13"/>
+        <v>69</v>
+      </c>
+      <c r="T192" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T163" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T163" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="T0"/>
+        <filter val="T2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="54" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="48" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="46" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="44" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="43" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="41" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="40" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="39" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="38" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="37" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="36" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="35" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="34" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="33" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="32" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="31" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="30" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="29" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="28" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="27" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="26" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
-    <cfRule type="duplicateValues" dxfId="25" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="24" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="23" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="21" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="20" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="19" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="18" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="17" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="15" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C114">
-    <cfRule type="duplicateValues" dxfId="14" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="13" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="10" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="8" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="2" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="1" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C164:C166">
+    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C169">
+    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C170">
+    <cfRule type="duplicateValues" dxfId="15" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C171">
+    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C173">
+    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C174">
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C176">
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C177">
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C178">
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C180">
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C180:C181">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C182">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E175">
+    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E178">
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C157:C163">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="198" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C32127D-9884-48E9-9720-117B3309F02A}"/>
+  <xr:revisionPtr revIDLastSave="199" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C00E798F-55C6-4EBE-82F9-361CBFBE099A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$T$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$T$192</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2931,7 +2931,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>159</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>164</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>165</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>206</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>207</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>217</v>
       </c>
@@ -4639,7 +4639,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>218</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>236</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
         <v>237</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
         <v>256</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>258</v>
       </c>
@@ -6896,7 +6896,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>285</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>291</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>292</v>
       </c>
@@ -7567,7 +7567,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
         <v>30</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="12" t="s">
         <v>35</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="6" t="s">
         <v>55</v>
       </c>
@@ -8604,7 +8604,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="8" t="s">
         <v>85</v>
       </c>
@@ -8665,7 +8665,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:20" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
         <v>86</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>106</v>
       </c>
@@ -9214,7 +9214,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>81</v>
       </c>
@@ -9275,7 +9275,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>107</v>
       </c>
@@ -9336,7 +9336,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>108</v>
       </c>
@@ -9397,7 +9397,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
         <v>109</v>
       </c>
@@ -9885,7 +9885,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
         <v>130</v>
       </c>
@@ -9946,7 +9946,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
         <v>131</v>
       </c>
@@ -10690,7 +10690,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
         <v>308</v>
       </c>
@@ -10755,7 +10755,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="9" t="s">
         <v>309</v>
       </c>
@@ -11015,7 +11015,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="9" t="s">
         <v>320</v>
       </c>
@@ -11080,7 +11080,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="9" t="s">
         <v>321</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="9" t="s">
         <v>321</v>
       </c>
@@ -11210,7 +11210,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="9" t="s">
         <v>322</v>
       </c>
@@ -11275,7 +11275,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="9" t="s">
         <v>323</v>
       </c>
@@ -11340,7 +11340,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
         <v>324</v>
       </c>
@@ -11405,7 +11405,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
         <v>326</v>
       </c>
@@ -14786,21 +14786,26 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T163" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:T192" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
         <filter val="T0"/>
         <filter val="T2"/>
       </filters>
     </filterColumn>
+    <filterColumn colId="17">
+      <filters>
+        <dateGroupItem year="2026" month="3" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="72" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
     <cfRule type="duplicateValues" dxfId="66" priority="46"/>
@@ -14814,8 +14819,8 @@
     <cfRule type="duplicateValues" dxfId="62" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="61" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
     <cfRule type="duplicateValues" dxfId="59" priority="43"/>
@@ -14904,82 +14909,82 @@
     <cfRule type="duplicateValues" dxfId="30" priority="20"/>
     <cfRule type="duplicateValues" dxfId="29" priority="21"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C157:C163">
+    <cfRule type="duplicateValues" dxfId="28" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C164:C166">
+    <cfRule type="duplicateValues" dxfId="27" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C169">
+    <cfRule type="duplicateValues" dxfId="26" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C170">
+    <cfRule type="duplicateValues" dxfId="24" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C171">
+    <cfRule type="duplicateValues" dxfId="22" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C173">
+    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C174">
+    <cfRule type="duplicateValues" dxfId="20" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C176">
+    <cfRule type="duplicateValues" dxfId="19" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C177">
+    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C178">
+    <cfRule type="duplicateValues" dxfId="16" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C180">
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C180:C181">
+    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C182">
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="28" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="26" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="25" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="24" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="23" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="22" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="20" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="19" priority="76"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C164:C166">
-    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C169">
-    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="15" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C171">
-    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C173">
-    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C176">
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C178">
-    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C180">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C180:C181">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C182">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175">
-    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E178">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C157:C163">
-    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="199" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C00E798F-55C6-4EBE-82F9-361CBFBE099A}"/>
+  <xr:revisionPtr revIDLastSave="207" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E028221-A1C7-4A57-B997-0DC67898E7E5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$T$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$T$189</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="430">
   <si>
     <t>Client</t>
   </si>
@@ -1723,7 +1723,747 @@
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="73">
+  <dxfs count="147">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2789,10 +3529,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:T192"/>
+  <dimension ref="A1:T189"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.7265625" style="26" customWidth="1"/>
+    <col min="1" max="1" width="29.453125" style="26" customWidth="1"/>
     <col min="3" max="3" width="8.90625" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="11" bestFit="1" customWidth="1"/>
@@ -11434,7 +12174,7 @@
         <v>46079</v>
       </c>
       <c r="J141" s="24">
-        <f t="shared" ref="J141:J192" si="12">+NETWORKDAYS(H141,I141)</f>
+        <f t="shared" ref="J141:J189" si="12">+NETWORKDAYS(H141,I141)</f>
         <v>261</v>
       </c>
       <c r="K141" s="25" t="s">
@@ -11463,7 +12203,7 @@
         <v>46079</v>
       </c>
       <c r="S141" s="24">
-        <f t="shared" ref="S141:S192" si="13">NETWORKDAYS(H141,R141)</f>
+        <f t="shared" ref="S141:S189" si="13">NETWORKDAYS(H141,R141)</f>
         <v>261</v>
       </c>
       <c r="T141" s="11" t="s">
@@ -11925,7 +12665,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="149" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A149" s="12" t="s">
         <v>344</v>
       </c>
@@ -12041,7 +12781,7 @@
         <v>40000</v>
       </c>
       <c r="Q150" s="47">
-        <f t="shared" ref="Q150:Q192" si="14">P150+O150</f>
+        <f t="shared" ref="Q150:Q189" si="14">P150+O150</f>
         <v>190000</v>
       </c>
       <c r="R150" s="45">
@@ -12055,7 +12795,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="151" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A151" s="12" t="s">
         <v>324</v>
       </c>
@@ -12120,7 +12860,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="152" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A152" s="12" t="s">
         <v>350</v>
       </c>
@@ -12185,7 +12925,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="153" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A153" s="12" t="s">
         <v>354</v>
       </c>
@@ -12250,7 +12990,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="154" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A154" s="12" t="s">
         <v>145</v>
       </c>
@@ -12445,7 +13185,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="157" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A157" s="44" t="s">
         <v>43</v>
       </c>
@@ -12510,7 +13250,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="158" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A158" s="44" t="s">
         <v>362</v>
       </c>
@@ -12575,7 +13315,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="159" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
         <v>43</v>
       </c>
@@ -12705,362 +13445,362 @@
         <v>347</v>
       </c>
     </row>
-    <row r="161" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="44" t="s">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A161" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="B161" s="44" t="s">
+      <c r="B161" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C161" s="44">
+      <c r="C161" s="12">
         <v>57932962</v>
       </c>
-      <c r="D161" s="44" t="s">
+      <c r="D161" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E161" s="44" t="s">
+      <c r="E161" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="F161" s="44" t="s">
+      <c r="F161" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G161" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="H161" s="45">
+      <c r="G161" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H161" s="14">
         <v>46059</v>
       </c>
-      <c r="I161" s="45">
+      <c r="I161" s="14">
         <v>46085</v>
       </c>
       <c r="J161" s="24">
         <f t="shared" si="12"/>
         <v>19</v>
       </c>
-      <c r="K161" s="50" t="s">
+      <c r="K161" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L161" s="51" t="s">
+      <c r="L161" s="11" t="s">
         <v>304</v>
       </c>
       <c r="M161" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="N161" s="44" t="s">
+      <c r="N161" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O161" s="52">
+      <c r="O161" s="19">
         <v>500000</v>
       </c>
-      <c r="P161" s="52">
+      <c r="P161" s="19">
         <v>187644</v>
       </c>
       <c r="Q161" s="47">
         <f t="shared" si="14"/>
         <v>687644</v>
       </c>
-      <c r="R161" s="53">
+      <c r="R161" s="13">
         <v>46086</v>
       </c>
       <c r="S161" s="24">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
-      <c r="T161" s="44" t="s">
+      <c r="T161" s="11" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="162" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="44" t="s">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A162" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="B162" s="44" t="s">
+      <c r="B162" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C162" s="44">
+      <c r="C162" s="12">
         <v>58272102</v>
       </c>
-      <c r="D162" s="44" t="s">
+      <c r="D162" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E162" s="44" t="s">
+      <c r="E162" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="F162" s="44" t="s">
+      <c r="F162" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G162" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="H162" s="45">
+      <c r="G162" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H162" s="14">
         <v>46066</v>
       </c>
-      <c r="I162" s="45">
+      <c r="I162" s="14">
         <v>46083</v>
       </c>
       <c r="J162" s="24">
         <f t="shared" si="12"/>
         <v>12</v>
       </c>
-      <c r="K162" s="50" t="s">
+      <c r="K162" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L162" s="51" t="s">
+      <c r="L162" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="M162" s="51" t="s">
+      <c r="M162" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N162" s="44" t="s">
+      <c r="N162" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O162" s="52">
+      <c r="O162" s="19">
         <v>2621414</v>
       </c>
-      <c r="P162" s="52">
+      <c r="P162" s="19">
         <v>667054</v>
       </c>
       <c r="Q162" s="47">
         <f t="shared" si="14"/>
         <v>3288468</v>
       </c>
-      <c r="R162" s="53">
+      <c r="R162" s="13">
         <v>46086</v>
       </c>
       <c r="S162" s="24">
         <f t="shared" si="13"/>
         <v>15</v>
       </c>
-      <c r="T162" s="44" t="s">
+      <c r="T162" s="11" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="163" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="44" t="s">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A163" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B163" s="44" t="s">
+      <c r="B163" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C163" s="44">
+      <c r="C163" s="12">
         <v>58150208</v>
       </c>
-      <c r="D163" s="44" t="s">
+      <c r="D163" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E163" s="44" t="s">
+      <c r="E163" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="F163" s="44" t="s">
+      <c r="F163" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G163" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="H163" s="45">
+      <c r="G163" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H163" s="14">
         <v>46064</v>
       </c>
-      <c r="I163" s="45">
+      <c r="I163" s="14">
         <v>46086</v>
       </c>
       <c r="J163" s="24">
         <f t="shared" si="12"/>
         <v>17</v>
       </c>
-      <c r="K163" s="50" t="s">
+      <c r="K163" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L163" s="51" t="s">
+      <c r="L163" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="M163" s="51" t="s">
+      <c r="M163" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N163" s="44" t="s">
+      <c r="N163" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O163" s="52">
+      <c r="O163" s="19">
         <v>2000000</v>
       </c>
-      <c r="P163" s="52">
+      <c r="P163" s="19">
         <v>380000</v>
       </c>
       <c r="Q163" s="47">
         <f t="shared" si="14"/>
         <v>2380000</v>
       </c>
-      <c r="R163" s="53">
+      <c r="R163" s="13">
         <v>46087</v>
       </c>
       <c r="S163" s="24">
         <f t="shared" si="13"/>
         <v>18</v>
       </c>
-      <c r="T163" s="44" t="s">
+      <c r="T163" s="11" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="164" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A164" s="12" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C164" s="12">
-        <v>57932962</v>
+        <v>54968651</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>20</v>
+        <v>375</v>
       </c>
       <c r="E164" s="12" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F164" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G164" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G164" s="12" t="s">
         <v>23</v>
       </c>
       <c r="H164" s="14">
-        <v>46059</v>
+        <v>46002</v>
       </c>
       <c r="I164" s="14">
-        <v>46085</v>
+        <v>46076</v>
       </c>
       <c r="J164" s="24">
         <f t="shared" si="12"/>
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K164" s="25" t="s">
-        <v>303</v>
+        <v>353</v>
       </c>
       <c r="L164" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="M164" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="M164" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N164" s="12" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="O164" s="19">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="P164" s="19">
-        <v>187644</v>
+        <v>1700000</v>
       </c>
       <c r="Q164" s="47">
         <f t="shared" si="14"/>
-        <v>687644</v>
+        <v>2700000</v>
       </c>
       <c r="R164" s="13">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="S164" s="24">
         <f t="shared" si="13"/>
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="T164" s="11" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
     </row>
     <row r="165" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A165" s="12" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C165" s="12">
-        <v>58272102</v>
+        <v>54971775</v>
       </c>
       <c r="D165" s="12" t="s">
-        <v>36</v>
+        <v>378</v>
       </c>
       <c r="E165" s="12" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="F165" s="12" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>23</v>
       </c>
       <c r="H165" s="14">
-        <v>46066</v>
+        <v>46002</v>
       </c>
       <c r="I165" s="14">
-        <v>46083</v>
+        <v>46057</v>
       </c>
       <c r="J165" s="24">
         <f t="shared" si="12"/>
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="K165" s="25" t="s">
-        <v>303</v>
+        <v>353</v>
       </c>
       <c r="L165" s="11" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="M165" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N165" s="12" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="O165" s="19">
-        <v>2621414</v>
+        <v>1000000</v>
       </c>
       <c r="P165" s="19">
-        <v>667054</v>
+        <v>1700000</v>
       </c>
       <c r="Q165" s="47">
         <f t="shared" si="14"/>
-        <v>3288468</v>
+        <v>2700000</v>
       </c>
       <c r="R165" s="13">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="S165" s="24">
         <f t="shared" si="13"/>
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="T165" s="11" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
     </row>
     <row r="166" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A166" s="12" t="s">
-        <v>43</v>
+        <v>374</v>
       </c>
       <c r="B166" s="12" t="s">
         <v>44</v>
       </c>
       <c r="C166" s="12">
-        <v>58150208</v>
+        <v>54973833</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>68</v>
+        <v>380</v>
       </c>
       <c r="E166" s="12" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F166" s="12" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G166" s="12" t="s">
         <v>23</v>
       </c>
       <c r="H166" s="14">
-        <v>46064</v>
+        <v>46002</v>
       </c>
       <c r="I166" s="14">
-        <v>46086</v>
+        <v>46021</v>
       </c>
       <c r="J166" s="24">
         <f t="shared" si="12"/>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K166" s="25" t="s">
         <v>303</v>
@@ -13072,27 +13812,27 @@
         <v>24</v>
       </c>
       <c r="N166" s="12" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="O166" s="19">
-        <v>2000000</v>
+        <v>250000</v>
       </c>
       <c r="P166" s="19">
-        <v>380000</v>
+        <v>1700000</v>
       </c>
       <c r="Q166" s="47">
         <f t="shared" si="14"/>
-        <v>2380000</v>
+        <v>1950000</v>
       </c>
       <c r="R166" s="13">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="S166" s="24">
         <f t="shared" si="13"/>
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="T166" s="11" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
     </row>
     <row r="167" spans="1:20" x14ac:dyDescent="0.35">
@@ -13103,13 +13843,13 @@
         <v>44</v>
       </c>
       <c r="C167" s="12">
-        <v>54968651</v>
+        <v>54980338</v>
       </c>
       <c r="D167" s="12" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="E167" s="12" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F167" s="12" t="s">
         <v>47</v>
@@ -13120,34 +13860,34 @@
       <c r="H167" s="14">
         <v>46002</v>
       </c>
-      <c r="I167" s="14">
-        <v>46076</v>
+      <c r="I167" s="23">
+        <v>46024</v>
       </c>
       <c r="J167" s="24">
         <f t="shared" si="12"/>
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="K167" s="25" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="L167" s="11" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="M167" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N167" s="12" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="O167" s="19">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="P167" s="19">
-        <v>1700000</v>
+        <v>1300000</v>
       </c>
       <c r="Q167" s="47">
         <f t="shared" si="14"/>
-        <v>2700000</v>
+        <v>1800000</v>
       </c>
       <c r="R167" s="13">
         <v>46090</v>
@@ -13168,13 +13908,13 @@
         <v>44</v>
       </c>
       <c r="C168" s="12">
-        <v>54971775</v>
+        <v>55103426</v>
       </c>
       <c r="D168" s="12" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="E168" s="12" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="F168" s="12" t="s">
         <v>47</v>
@@ -13183,43 +13923,43 @@
         <v>23</v>
       </c>
       <c r="H168" s="14">
-        <v>46002</v>
+        <v>46004</v>
       </c>
       <c r="I168" s="14">
-        <v>46057</v>
+        <v>46042</v>
       </c>
       <c r="J168" s="24">
         <f t="shared" si="12"/>
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="K168" s="25" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="L168" s="11" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="M168" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N168" s="12" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="O168" s="19">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="P168" s="19">
-        <v>1700000</v>
+        <v>1300000</v>
       </c>
       <c r="Q168" s="47">
         <f t="shared" si="14"/>
-        <v>2700000</v>
+        <v>1800000</v>
       </c>
       <c r="R168" s="13">
         <v>46090</v>
       </c>
       <c r="S168" s="24">
         <f t="shared" si="13"/>
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T168" s="11" t="s">
         <v>377</v>
@@ -13233,13 +13973,13 @@
         <v>44</v>
       </c>
       <c r="C169" s="12">
-        <v>54973833</v>
+        <v>54979384</v>
       </c>
       <c r="D169" s="12" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E169" s="12" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F169" s="12" t="s">
         <v>47</v>
@@ -13251,33 +13991,33 @@
         <v>46002</v>
       </c>
       <c r="I169" s="14">
-        <v>46021</v>
+        <v>46065</v>
       </c>
       <c r="J169" s="24">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="K169" s="25" t="s">
-        <v>303</v>
+        <v>353</v>
       </c>
       <c r="L169" s="11" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="M169" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N169" s="12" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="O169" s="19">
         <v>250000</v>
       </c>
       <c r="P169" s="19">
-        <v>1700000</v>
+        <v>1300000</v>
       </c>
       <c r="Q169" s="47">
         <f t="shared" si="14"/>
-        <v>1950000</v>
+        <v>1550000</v>
       </c>
       <c r="R169" s="13">
         <v>46090</v>
@@ -13298,13 +14038,13 @@
         <v>44</v>
       </c>
       <c r="C170" s="12">
-        <v>54980338</v>
+        <v>54979901</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="E170" s="12" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F170" s="12" t="s">
         <v>47</v>
@@ -13315,12 +14055,12 @@
       <c r="H170" s="14">
         <v>46002</v>
       </c>
-      <c r="I170" s="23">
-        <v>46024</v>
+      <c r="I170" s="14">
+        <v>46036</v>
       </c>
       <c r="J170" s="24">
         <f t="shared" si="12"/>
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K170" s="25" t="s">
         <v>303</v>
@@ -13337,7 +14077,7 @@
       <c r="O170" s="19">
         <v>500000</v>
       </c>
-      <c r="P170" s="19">
+      <c r="P170" s="12">
         <v>1300000</v>
       </c>
       <c r="Q170" s="47">
@@ -13363,13 +14103,13 @@
         <v>44</v>
       </c>
       <c r="C171" s="12">
-        <v>55103426</v>
+        <v>54981048</v>
       </c>
       <c r="D171" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="E171" s="12" t="s">
-        <v>385</v>
+        <v>390</v>
+      </c>
+      <c r="E171" s="11" t="s">
+        <v>391</v>
       </c>
       <c r="F171" s="12" t="s">
         <v>47</v>
@@ -13378,20 +14118,20 @@
         <v>23</v>
       </c>
       <c r="H171" s="14">
-        <v>46004</v>
+        <v>46002</v>
       </c>
       <c r="I171" s="14">
-        <v>46042</v>
+        <v>46048</v>
       </c>
       <c r="J171" s="24">
         <f t="shared" si="12"/>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K171" s="25" t="s">
-        <v>303</v>
+        <v>353</v>
       </c>
       <c r="L171" s="11" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="M171" s="11" t="s">
         <v>24</v>
@@ -13414,7 +14154,7 @@
       </c>
       <c r="S171" s="24">
         <f t="shared" si="13"/>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T171" s="11" t="s">
         <v>377</v>
@@ -13427,14 +14167,14 @@
       <c r="B172" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C172" s="12">
-        <v>54979384</v>
+      <c r="C172" s="57">
+        <v>55105863</v>
       </c>
       <c r="D172" s="12" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="E172" s="12" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F172" s="12" t="s">
         <v>47</v>
@@ -13442,15 +14182,15 @@
       <c r="G172" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H172" s="14">
-        <v>46002</v>
+      <c r="H172" s="39">
+        <v>46004</v>
       </c>
       <c r="I172" s="14">
         <v>46065</v>
       </c>
       <c r="J172" s="24">
         <f t="shared" si="12"/>
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K172" s="25" t="s">
         <v>353</v>
@@ -13465,21 +14205,21 @@
         <v>29</v>
       </c>
       <c r="O172" s="19">
-        <v>250000</v>
+        <v>1250000</v>
       </c>
       <c r="P172" s="19">
         <v>1300000</v>
       </c>
       <c r="Q172" s="47">
         <f t="shared" si="14"/>
-        <v>1550000</v>
+        <v>2550000</v>
       </c>
       <c r="R172" s="13">
         <v>46090</v>
       </c>
       <c r="S172" s="24">
         <f t="shared" si="13"/>
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T172" s="11" t="s">
         <v>377</v>
@@ -13493,13 +14233,13 @@
         <v>44</v>
       </c>
       <c r="C173" s="12">
-        <v>54979901</v>
+        <v>55104619</v>
       </c>
       <c r="D173" s="12" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="E173" s="12" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="F173" s="12" t="s">
         <v>47</v>
@@ -13508,43 +14248,43 @@
         <v>23</v>
       </c>
       <c r="H173" s="14">
-        <v>46002</v>
+        <v>46004</v>
       </c>
       <c r="I173" s="14">
-        <v>46036</v>
+        <v>46081</v>
       </c>
       <c r="J173" s="24">
         <f t="shared" si="12"/>
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="K173" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L173" s="11" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="M173" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N173" s="12" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="O173" s="19">
-        <v>500000</v>
-      </c>
-      <c r="P173" s="12">
-        <v>1300000</v>
+        <v>1000000</v>
+      </c>
+      <c r="P173" s="19">
+        <v>1700000</v>
       </c>
       <c r="Q173" s="47">
         <f t="shared" si="14"/>
-        <v>1800000</v>
+        <v>2700000</v>
       </c>
       <c r="R173" s="13">
         <v>46090</v>
       </c>
       <c r="S173" s="24">
         <f t="shared" si="13"/>
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T173" s="11" t="s">
         <v>377</v>
@@ -13558,13 +14298,13 @@
         <v>44</v>
       </c>
       <c r="C174" s="12">
-        <v>54981048</v>
+        <v>54978747</v>
       </c>
       <c r="D174" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="E174" s="11" t="s">
-        <v>391</v>
+        <v>396</v>
+      </c>
+      <c r="E174" s="12" t="s">
+        <v>397</v>
       </c>
       <c r="F174" s="12" t="s">
         <v>47</v>
@@ -13576,17 +14316,17 @@
         <v>46002</v>
       </c>
       <c r="I174" s="14">
-        <v>46048</v>
+        <v>46034</v>
       </c>
       <c r="J174" s="24">
         <f t="shared" si="12"/>
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="K174" s="25" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="L174" s="11" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="M174" s="11" t="s">
         <v>24</v>
@@ -13595,14 +14335,14 @@
         <v>29</v>
       </c>
       <c r="O174" s="19">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="P174" s="19">
         <v>1300000</v>
       </c>
       <c r="Q174" s="47">
         <f t="shared" si="14"/>
-        <v>1800000</v>
+        <v>1550000</v>
       </c>
       <c r="R174" s="13">
         <v>46090</v>
@@ -13622,14 +14362,14 @@
       <c r="B175" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C175" s="57">
-        <v>55105863</v>
+      <c r="C175" s="12">
+        <v>54978242</v>
       </c>
       <c r="D175" s="12" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="E175" s="12" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="F175" s="12" t="s">
         <v>47</v>
@@ -13637,17 +14377,17 @@
       <c r="G175" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H175" s="39">
-        <v>46004</v>
+      <c r="H175" s="14">
+        <v>46002</v>
       </c>
       <c r="I175" s="14">
-        <v>46065</v>
+        <v>46041</v>
       </c>
       <c r="J175" s="24">
         <f t="shared" si="12"/>
-        <v>44</v>
-      </c>
-      <c r="K175" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="K175" s="11" t="s">
         <v>353</v>
       </c>
       <c r="L175" s="11" t="s">
@@ -13657,24 +14397,24 @@
         <v>24</v>
       </c>
       <c r="N175" s="12" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="O175" s="19">
-        <v>1250000</v>
+        <v>500000</v>
       </c>
       <c r="P175" s="19">
-        <v>1300000</v>
+        <v>1700000</v>
       </c>
       <c r="Q175" s="47">
         <f t="shared" si="14"/>
-        <v>2550000</v>
+        <v>2200000</v>
       </c>
       <c r="R175" s="13">
         <v>46090</v>
       </c>
       <c r="S175" s="24">
         <f t="shared" si="13"/>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T175" s="11" t="s">
         <v>377</v>
@@ -13688,13 +14428,13 @@
         <v>44</v>
       </c>
       <c r="C176" s="12">
-        <v>55104619</v>
+        <v>55105778</v>
       </c>
       <c r="D176" s="12" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E176" s="12" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="F176" s="12" t="s">
         <v>47</v>
@@ -13706,14 +14446,14 @@
         <v>46004</v>
       </c>
       <c r="I176" s="14">
-        <v>46081</v>
+        <v>46079</v>
       </c>
       <c r="J176" s="24">
         <f t="shared" si="12"/>
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K176" s="25" t="s">
-        <v>303</v>
+        <v>353</v>
       </c>
       <c r="L176" s="11" t="s">
         <v>327</v>
@@ -13722,17 +14462,17 @@
         <v>24</v>
       </c>
       <c r="N176" s="12" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="O176" s="19">
         <v>1000000</v>
       </c>
       <c r="P176" s="19">
-        <v>1700000</v>
+        <v>1300000</v>
       </c>
       <c r="Q176" s="47">
         <f t="shared" si="14"/>
-        <v>2700000</v>
+        <v>2300000</v>
       </c>
       <c r="R176" s="13">
         <v>46090</v>
@@ -13753,13 +14493,13 @@
         <v>44</v>
       </c>
       <c r="C177" s="12">
-        <v>54978747</v>
+        <v>54973195</v>
       </c>
       <c r="D177" s="12" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E177" s="12" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="F177" s="12" t="s">
         <v>47</v>
@@ -13771,13 +14511,13 @@
         <v>46002</v>
       </c>
       <c r="I177" s="14">
-        <v>46034</v>
+        <v>46027</v>
       </c>
       <c r="J177" s="24">
         <f t="shared" si="12"/>
-        <v>23</v>
-      </c>
-      <c r="K177" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="K177" s="11" t="s">
         <v>303</v>
       </c>
       <c r="L177" s="11" t="s">
@@ -13787,17 +14527,17 @@
         <v>24</v>
       </c>
       <c r="N177" s="12" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="O177" s="19">
-        <v>250000</v>
+        <v>500000</v>
       </c>
       <c r="P177" s="19">
-        <v>1300000</v>
+        <v>1700000</v>
       </c>
       <c r="Q177" s="47">
         <f t="shared" si="14"/>
-        <v>1550000</v>
+        <v>2200000</v>
       </c>
       <c r="R177" s="13">
         <v>46090</v>
@@ -13818,13 +14558,13 @@
         <v>44</v>
       </c>
       <c r="C178" s="12">
-        <v>54978242</v>
+        <v>55105296</v>
       </c>
       <c r="D178" s="12" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="E178" s="12" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="F178" s="12" t="s">
         <v>47</v>
@@ -13833,43 +14573,43 @@
         <v>23</v>
       </c>
       <c r="H178" s="14">
-        <v>46002</v>
+        <v>46004</v>
       </c>
       <c r="I178" s="14">
-        <v>46041</v>
+        <v>46035</v>
       </c>
       <c r="J178" s="24">
         <f t="shared" si="12"/>
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K178" s="11" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="L178" s="11" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="M178" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N178" s="12" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="O178" s="19">
-        <v>500000</v>
+        <v>1500000</v>
       </c>
       <c r="P178" s="19">
-        <v>1700000</v>
+        <v>1300000</v>
       </c>
       <c r="Q178" s="47">
         <f t="shared" si="14"/>
-        <v>2200000</v>
+        <v>2800000</v>
       </c>
       <c r="R178" s="13">
         <v>46090</v>
       </c>
       <c r="S178" s="24">
         <f t="shared" si="13"/>
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T178" s="11" t="s">
         <v>377</v>
@@ -13882,14 +14622,14 @@
       <c r="B179" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C179" s="12">
-        <v>55105778</v>
+      <c r="C179" s="5">
+        <v>54976425</v>
       </c>
       <c r="D179" s="12" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="E179" s="12" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="F179" s="12" t="s">
         <v>47</v>
@@ -13898,20 +14638,20 @@
         <v>23</v>
       </c>
       <c r="H179" s="14">
-        <v>46004</v>
-      </c>
-      <c r="I179" s="14">
-        <v>46079</v>
+        <v>46002</v>
+      </c>
+      <c r="I179" s="23">
+        <v>46024</v>
       </c>
       <c r="J179" s="24">
         <f t="shared" si="12"/>
-        <v>54</v>
-      </c>
-      <c r="K179" s="25" t="s">
-        <v>353</v>
+        <v>17</v>
+      </c>
+      <c r="K179" s="11" t="s">
+        <v>303</v>
       </c>
       <c r="L179" s="11" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="M179" s="11" t="s">
         <v>24</v>
@@ -13920,21 +14660,21 @@
         <v>29</v>
       </c>
       <c r="O179" s="19">
-        <v>1000000</v>
+        <v>1250000</v>
       </c>
       <c r="P179" s="19">
         <v>1300000</v>
       </c>
       <c r="Q179" s="47">
         <f t="shared" si="14"/>
-        <v>2300000</v>
+        <v>2550000</v>
       </c>
       <c r="R179" s="13">
         <v>46090</v>
       </c>
       <c r="S179" s="24">
         <f t="shared" si="13"/>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T179" s="11" t="s">
         <v>377</v>
@@ -13942,19 +14682,19 @@
     </row>
     <row r="180" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A180" s="12" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="B180" s="12" t="s">
         <v>44</v>
       </c>
       <c r="C180" s="12">
-        <v>54973195</v>
+        <v>57900967</v>
       </c>
       <c r="D180" s="12" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="E180" s="12" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="F180" s="12" t="s">
         <v>47</v>
@@ -13963,14 +14703,14 @@
         <v>23</v>
       </c>
       <c r="H180" s="14">
-        <v>46002</v>
+        <v>46059</v>
       </c>
       <c r="I180" s="14">
-        <v>46027</v>
+        <v>46079</v>
       </c>
       <c r="J180" s="24">
         <f t="shared" si="12"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K180" s="11" t="s">
         <v>303</v>
@@ -13982,44 +14722,44 @@
         <v>24</v>
       </c>
       <c r="N180" s="12" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="O180" s="19">
-        <v>500000</v>
+        <v>1388682</v>
       </c>
       <c r="P180" s="19">
-        <v>1700000</v>
+        <v>2207940</v>
       </c>
       <c r="Q180" s="47">
         <f t="shared" si="14"/>
-        <v>2200000</v>
+        <v>3596622</v>
       </c>
       <c r="R180" s="13">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="S180" s="24">
         <f t="shared" si="13"/>
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="T180" s="11" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A181" s="12" t="s">
-        <v>374</v>
+      <c r="A181" s="22" t="s">
+        <v>411</v>
       </c>
       <c r="B181" s="12" t="s">
         <v>44</v>
       </c>
       <c r="C181" s="12">
-        <v>55105296</v>
+        <v>58136263</v>
       </c>
       <c r="D181" s="12" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="E181" s="12" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="F181" s="12" t="s">
         <v>47</v>
@@ -14028,43 +14768,43 @@
         <v>23</v>
       </c>
       <c r="H181" s="14">
-        <v>46004</v>
+        <v>46071</v>
       </c>
       <c r="I181" s="14">
-        <v>46035</v>
+        <v>46085</v>
       </c>
       <c r="J181" s="24">
         <f t="shared" si="12"/>
-        <v>22</v>
-      </c>
-      <c r="K181" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K181" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L181" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="M181" s="11" t="s">
+      <c r="M181" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N181" s="12" t="s">
-        <v>29</v>
+        <v>148</v>
       </c>
       <c r="O181" s="19">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="P181" s="19">
-        <v>1300000</v>
+        <v>0</v>
       </c>
       <c r="Q181" s="47">
         <f t="shared" si="14"/>
-        <v>2800000</v>
+        <v>0</v>
       </c>
       <c r="R181" s="13">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="S181" s="24">
         <f t="shared" si="13"/>
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="T181" s="11" t="s">
         <v>377</v>
@@ -14072,35 +14812,35 @@
     </row>
     <row r="182" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A182" s="12" t="s">
-        <v>374</v>
+        <v>414</v>
       </c>
       <c r="B182" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C182" s="5">
-        <v>54976425</v>
+        <v>19</v>
+      </c>
+      <c r="C182" s="12">
+        <v>59207750</v>
       </c>
       <c r="D182" s="12" t="s">
-        <v>406</v>
+        <v>283</v>
       </c>
       <c r="E182" s="12" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="F182" s="12" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G182" s="12" t="s">
         <v>23</v>
       </c>
       <c r="H182" s="14">
-        <v>46002</v>
-      </c>
-      <c r="I182" s="23">
-        <v>46024</v>
+        <v>46083</v>
+      </c>
+      <c r="I182" s="14">
+        <v>46091</v>
       </c>
       <c r="J182" s="24">
         <f t="shared" si="12"/>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K182" s="11" t="s">
         <v>303</v>
@@ -14112,24 +14852,24 @@
         <v>24</v>
       </c>
       <c r="N182" s="12" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="O182" s="19">
-        <v>1250000</v>
+        <v>1000000</v>
       </c>
       <c r="P182" s="19">
-        <v>1300000</v>
+        <v>590836</v>
       </c>
       <c r="Q182" s="47">
         <f t="shared" si="14"/>
-        <v>2550000</v>
+        <v>1590836</v>
       </c>
       <c r="R182" s="13">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="S182" s="24">
         <f t="shared" si="13"/>
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="T182" s="11" t="s">
         <v>377</v>
@@ -14137,37 +14877,37 @@
     </row>
     <row r="183" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A183" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="B183" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C183" s="12">
-        <v>57900967</v>
-      </c>
-      <c r="D183" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
+      </c>
+      <c r="B183" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C183" s="11">
+        <v>57111758</v>
+      </c>
+      <c r="D183" s="11" t="s">
+        <v>175</v>
       </c>
       <c r="E183" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="F183" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="F183" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G183" s="12" t="s">
-        <v>23</v>
+      <c r="G183" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="H183" s="14">
+        <v>46044</v>
+      </c>
+      <c r="I183" s="14">
         <v>46059</v>
-      </c>
-      <c r="I183" s="14">
-        <v>46079</v>
       </c>
       <c r="J183" s="24">
         <f t="shared" si="12"/>
-        <v>15</v>
-      </c>
-      <c r="K183" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="K183" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L183" s="11" t="s">
@@ -14176,61 +14916,61 @@
       <c r="M183" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N183" s="12" t="s">
-        <v>29</v>
+      <c r="N183" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="O183" s="19">
-        <v>1388682</v>
+        <v>0</v>
       </c>
       <c r="P183" s="19">
-        <v>2207940</v>
+        <v>0</v>
       </c>
       <c r="Q183" s="47">
         <f t="shared" si="14"/>
-        <v>3596622</v>
+        <v>0</v>
       </c>
       <c r="R183" s="13">
         <v>46091</v>
       </c>
       <c r="S183" s="24">
         <f t="shared" si="13"/>
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="T183" s="11" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="184" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A184" s="22" t="s">
-        <v>411</v>
-      </c>
-      <c r="B184" s="12" t="s">
-        <v>44</v>
+      <c r="A184" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="B184" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="C184" s="12">
-        <v>58136263</v>
-      </c>
-      <c r="D184" s="12" t="s">
-        <v>412</v>
+        <v>57111764</v>
+      </c>
+      <c r="D184" s="11" t="s">
+        <v>175</v>
       </c>
       <c r="E184" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="F184" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="F184" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G184" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H184" s="14">
-        <v>46071</v>
+      <c r="G184" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H184" s="13">
+        <v>46044</v>
       </c>
       <c r="I184" s="14">
-        <v>46085</v>
+        <v>46059</v>
       </c>
       <c r="J184" s="24">
         <f t="shared" si="12"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K184" s="25" t="s">
         <v>303</v>
@@ -14238,11 +14978,11 @@
       <c r="L184" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="M184" s="13" t="s">
+      <c r="M184" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N184" s="12" t="s">
-        <v>148</v>
+      <c r="N184" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="O184" s="19">
         <v>0</v>
@@ -14259,43 +14999,43 @@
       </c>
       <c r="S184" s="24">
         <f t="shared" si="13"/>
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="T184" s="11" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="185" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A185" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="B185" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C185" s="12">
-        <v>59207750</v>
-      </c>
-      <c r="D185" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="E185" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="F185" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G185" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H185" s="14">
-        <v>46083</v>
-      </c>
-      <c r="I185" s="14">
+      <c r="A185" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="B185" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C185" s="5">
+        <v>59019541</v>
+      </c>
+      <c r="D185" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="E185" s="5">
+        <v>2723489400</v>
+      </c>
+      <c r="F185" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G185" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H185" s="13">
+        <v>46079</v>
+      </c>
+      <c r="I185" s="13">
         <v>46091</v>
       </c>
       <c r="J185" s="24">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K185" s="11" t="s">
         <v>303</v>
@@ -14306,63 +15046,63 @@
       <c r="M185" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N185" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="O185" s="19">
-        <v>1000000</v>
-      </c>
-      <c r="P185" s="19">
-        <v>590836</v>
+      <c r="N185" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O185" s="59">
+        <v>150000</v>
+      </c>
+      <c r="P185" s="59">
+        <v>60000</v>
       </c>
       <c r="Q185" s="47">
         <f t="shared" si="14"/>
-        <v>1590836</v>
+        <v>210000</v>
       </c>
       <c r="R185" s="13">
         <v>46091</v>
       </c>
       <c r="S185" s="24">
         <f t="shared" si="13"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T185" s="11" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="186" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A186" s="12" t="s">
-        <v>416</v>
+      <c r="A186" s="9" t="s">
+        <v>421</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C186" s="11">
-        <v>57111758</v>
+        <v>31</v>
+      </c>
+      <c r="C186" s="9">
+        <v>54955589</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="E186" s="12" t="s">
-        <v>417</v>
+        <v>50</v>
+      </c>
+      <c r="E186" s="9">
+        <v>2722229185</v>
       </c>
       <c r="F186" s="11" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G186" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="H186" s="14">
-        <v>46044</v>
-      </c>
-      <c r="I186" s="14">
-        <v>46059</v>
+        <v>23</v>
+      </c>
+      <c r="H186" s="13">
+        <v>46002</v>
+      </c>
+      <c r="I186" s="13">
+        <v>46021</v>
       </c>
       <c r="J186" s="24">
         <f t="shared" si="12"/>
-        <v>12</v>
-      </c>
-      <c r="K186" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="K186" s="11" t="s">
         <v>303</v>
       </c>
       <c r="L186" s="11" t="s">
@@ -14372,24 +15112,24 @@
         <v>24</v>
       </c>
       <c r="N186" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="O186" s="19">
-        <v>0</v>
-      </c>
-      <c r="P186" s="19">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="O186" s="59">
+        <v>150000</v>
+      </c>
+      <c r="P186" s="59">
+        <v>60000</v>
       </c>
       <c r="Q186" s="47">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="R186" s="13">
         <v>46091</v>
       </c>
       <c r="S186" s="24">
         <f t="shared" si="13"/>
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="T186" s="11" t="s">
         <v>377</v>
@@ -14397,35 +15137,35 @@
     </row>
     <row r="187" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A187" s="12" t="s">
-        <v>416</v>
-      </c>
-      <c r="B187" s="11" t="s">
-        <v>19</v>
+        <v>422</v>
+      </c>
+      <c r="B187" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="C187" s="12">
-        <v>57111764</v>
-      </c>
-      <c r="D187" s="11" t="s">
-        <v>175</v>
+        <v>47899159</v>
+      </c>
+      <c r="D187" s="12" t="s">
+        <v>423</v>
       </c>
       <c r="E187" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="F187" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G187" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="H187" s="13">
-        <v>46044</v>
+        <v>424</v>
+      </c>
+      <c r="F187" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G187" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H187" s="14">
+        <v>45862</v>
       </c>
       <c r="I187" s="14">
-        <v>46059</v>
+        <v>46055</v>
       </c>
       <c r="J187" s="24">
         <f t="shared" si="12"/>
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="K187" s="25" t="s">
         <v>303</v>
@@ -14433,11 +15173,11 @@
       <c r="L187" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="M187" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="N187" s="11" t="s">
-        <v>64</v>
+      <c r="M187" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="N187" s="12" t="s">
+        <v>197</v>
       </c>
       <c r="O187" s="19">
         <v>0</v>
@@ -14454,345 +15194,144 @@
       </c>
       <c r="S187" s="24">
         <f t="shared" si="13"/>
-        <v>34</v>
+        <v>164</v>
       </c>
       <c r="T187" s="11" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="188" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A188" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="B188" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C188" s="5">
-        <v>59019541</v>
+      <c r="A188" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="B188" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C188" s="22">
+        <v>48425163</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>420</v>
-      </c>
-      <c r="E188" s="5">
-        <v>2723489400</v>
-      </c>
-      <c r="F188" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G188" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="H188" s="13">
-        <v>46079</v>
-      </c>
-      <c r="I188" s="13">
-        <v>46091</v>
+        <v>426</v>
+      </c>
+      <c r="E188" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="F188" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G188" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H188" s="14">
+        <v>45880</v>
+      </c>
+      <c r="I188" s="23">
+        <v>46061</v>
       </c>
       <c r="J188" s="24">
         <f t="shared" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="K188" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="K188" s="25" t="s">
         <v>303</v>
       </c>
       <c r="L188" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="M188" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="N188" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="O188" s="59">
-        <v>150000</v>
-      </c>
-      <c r="P188" s="59">
-        <v>60000</v>
+      <c r="M188" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="N188" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="O188" s="19">
+        <v>0</v>
+      </c>
+      <c r="P188" s="19">
+        <v>0</v>
       </c>
       <c r="Q188" s="47">
         <f t="shared" si="14"/>
-        <v>210000</v>
+        <v>0</v>
       </c>
       <c r="R188" s="13">
         <v>46091</v>
       </c>
       <c r="S188" s="24">
         <f t="shared" si="13"/>
-        <v>9</v>
+        <v>152</v>
       </c>
       <c r="T188" s="11" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="189" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A189" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="B189" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C189" s="9">
-        <v>54955589</v>
-      </c>
-      <c r="D189" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E189" s="9">
-        <v>2722229185</v>
-      </c>
-      <c r="F189" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G189" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="H189" s="13">
-        <v>46002</v>
-      </c>
-      <c r="I189" s="13">
-        <v>46021</v>
+      <c r="A189" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="B189" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C189" s="12">
+        <v>53934458</v>
+      </c>
+      <c r="D189" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E189" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="F189" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G189" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H189" s="14">
+        <v>45995</v>
+      </c>
+      <c r="I189" s="14">
+        <v>46063</v>
       </c>
       <c r="J189" s="24">
         <f t="shared" si="12"/>
-        <v>14</v>
-      </c>
-      <c r="K189" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="K189" s="58" t="s">
         <v>303</v>
       </c>
-      <c r="L189" s="11" t="s">
+      <c r="L189" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="M189" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="N189" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="O189" s="59">
-        <v>150000</v>
-      </c>
-      <c r="P189" s="59">
-        <v>60000</v>
+      <c r="M189" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="N189" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="O189" s="60">
+        <v>0</v>
+      </c>
+      <c r="P189" s="60">
+        <v>0</v>
       </c>
       <c r="Q189" s="47">
         <f t="shared" si="14"/>
-        <v>210000</v>
+        <v>0</v>
       </c>
       <c r="R189" s="13">
         <v>46091</v>
       </c>
       <c r="S189" s="24">
         <f t="shared" si="13"/>
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="T189" s="11" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A190" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="B190" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C190" s="12">
-        <v>47899159</v>
-      </c>
-      <c r="D190" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="E190" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="F190" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G190" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H190" s="14">
-        <v>45862</v>
-      </c>
-      <c r="I190" s="14">
-        <v>46055</v>
-      </c>
-      <c r="J190" s="24">
-        <f t="shared" si="12"/>
-        <v>138</v>
-      </c>
-      <c r="K190" s="25" t="s">
-        <v>303</v>
-      </c>
-      <c r="L190" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="M190" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="N190" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="O190" s="19">
-        <v>0</v>
-      </c>
-      <c r="P190" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q190" s="47">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="R190" s="13">
-        <v>46091</v>
-      </c>
-      <c r="S190" s="24">
-        <f t="shared" si="13"/>
-        <v>164</v>
-      </c>
-      <c r="T190" s="11" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A191" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="B191" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C191" s="22">
-        <v>48425163</v>
-      </c>
-      <c r="D191" s="11" t="s">
-        <v>426</v>
-      </c>
-      <c r="E191" s="12" t="s">
-        <v>427</v>
-      </c>
-      <c r="F191" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G191" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H191" s="14">
-        <v>45880</v>
-      </c>
-      <c r="I191" s="23">
-        <v>46061</v>
-      </c>
-      <c r="J191" s="24">
-        <f t="shared" si="12"/>
-        <v>130</v>
-      </c>
-      <c r="K191" s="25" t="s">
-        <v>303</v>
-      </c>
-      <c r="L191" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="M191" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="N191" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="O191" s="19">
-        <v>0</v>
-      </c>
-      <c r="P191" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q191" s="47">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="R191" s="13">
-        <v>46091</v>
-      </c>
-      <c r="S191" s="24">
-        <f t="shared" si="13"/>
-        <v>152</v>
-      </c>
-      <c r="T191" s="11" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A192" s="12" t="s">
-        <v>428</v>
-      </c>
-      <c r="B192" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C192" s="12">
-        <v>53934458</v>
-      </c>
-      <c r="D192" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="E192" s="12" t="s">
-        <v>429</v>
-      </c>
-      <c r="F192" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G192" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H192" s="14">
-        <v>45995</v>
-      </c>
-      <c r="I192" s="14">
-        <v>46063</v>
-      </c>
-      <c r="J192" s="24">
-        <f t="shared" si="12"/>
-        <v>49</v>
-      </c>
-      <c r="K192" s="58" t="s">
-        <v>303</v>
-      </c>
-      <c r="L192" s="35" t="s">
-        <v>304</v>
-      </c>
-      <c r="M192" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="N192" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="O192" s="60">
-        <v>0</v>
-      </c>
-      <c r="P192" s="60">
-        <v>0</v>
-      </c>
-      <c r="Q192" s="47">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="R192" s="13">
-        <v>46091</v>
-      </c>
-      <c r="S192" s="24">
-        <f t="shared" si="13"/>
-        <v>69</v>
-      </c>
-      <c r="T192" s="11" t="s">
-        <v>377</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T192" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="T0"/>
-        <filter val="T2"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="A1:T189" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="17">
       <filters>
         <dateGroupItem year="2026" month="3" dateTimeGrouping="month"/>
@@ -14800,191 +15339,194 @@
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="72" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="66" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="64" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="62" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="61" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
     <cfRule type="duplicateValues" dxfId="60" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
+  <conditionalFormatting sqref="C10">
     <cfRule type="duplicateValues" dxfId="59" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10">
+  <conditionalFormatting sqref="C12">
     <cfRule type="duplicateValues" dxfId="58" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C12">
+  <conditionalFormatting sqref="C15">
     <cfRule type="duplicateValues" dxfId="57" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="56" priority="40"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="55" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="54" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
+    <cfRule type="duplicateValues" dxfId="54" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C33:C37">
     <cfRule type="duplicateValues" dxfId="53" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="52" priority="36"/>
+  <conditionalFormatting sqref="C39">
+    <cfRule type="duplicateValues" dxfId="52" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C39">
+  <conditionalFormatting sqref="C40">
     <cfRule type="duplicateValues" dxfId="51" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="50" priority="33"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="49" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="48" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
+    <cfRule type="duplicateValues" dxfId="48" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C75">
     <cfRule type="duplicateValues" dxfId="47" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="46" priority="22"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="45" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="44" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
+    <cfRule type="duplicateValues" dxfId="44" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C80:C81">
     <cfRule type="duplicateValues" dxfId="43" priority="64"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="42" priority="63"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="41" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
+    <cfRule type="duplicateValues" dxfId="40" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C93">
     <cfRule type="duplicateValues" dxfId="39" priority="60"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="38" priority="59"/>
+  <conditionalFormatting sqref="C98">
+    <cfRule type="duplicateValues" dxfId="38" priority="58"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C98">
+  <conditionalFormatting sqref="C101">
     <cfRule type="duplicateValues" dxfId="37" priority="57"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="36" priority="56"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="35" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="33" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C114">
+    <cfRule type="duplicateValues" dxfId="33" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C115">
     <cfRule type="duplicateValues" dxfId="32" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="31" priority="50"/>
+  <conditionalFormatting sqref="C145">
+    <cfRule type="duplicateValues" dxfId="31" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="30" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="21"/>
+  <conditionalFormatting sqref="C161:C163">
+    <cfRule type="duplicateValues" dxfId="29" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C157:C163">
-    <cfRule type="duplicateValues" dxfId="28" priority="77"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C164:C166">
+  <conditionalFormatting sqref="C166">
+    <cfRule type="duplicateValues" dxfId="28" priority="17"/>
     <cfRule type="duplicateValues" dxfId="27" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C169">
-    <cfRule type="duplicateValues" dxfId="26" priority="17"/>
+  <conditionalFormatting sqref="C167">
+    <cfRule type="duplicateValues" dxfId="26" priority="15"/>
     <cfRule type="duplicateValues" dxfId="25" priority="16"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C168">
+    <cfRule type="duplicateValues" dxfId="24" priority="14"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="24" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171">
-    <cfRule type="duplicateValues" dxfId="22" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173">
-    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="20" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C176">
-    <cfRule type="duplicateValues" dxfId="19" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="9"/>
+  <conditionalFormatting sqref="C175">
+    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C178">
-    <cfRule type="duplicateValues" dxfId="16" priority="6"/>
+  <conditionalFormatting sqref="C177:C178">
+    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C180">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C180:C181">
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C182">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+  <conditionalFormatting sqref="C179">
+    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="11" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="9" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="8" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="7" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="6" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="5" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="4" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="3" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="2" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E172">
+    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175">
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E178">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C157:C160">
+    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="207" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E028221-A1C7-4A57-B997-0DC67898E7E5}"/>
+  <xr:revisionPtr revIDLastSave="227" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2500FE49-8CE3-4EFB-84B8-31AC1EAE3369}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="442">
   <si>
     <t>Client</t>
   </si>
@@ -1330,6 +1330,42 @@
   </si>
   <si>
     <t>SYTHD260019</t>
+  </si>
+  <si>
+    <t>OCI/TOP SERVICES</t>
+  </si>
+  <si>
+    <t>BUVPN260016</t>
+  </si>
+  <si>
+    <t>BERNABE CI</t>
+  </si>
+  <si>
+    <t>RIVIERA PALMERAIE</t>
+  </si>
+  <si>
+    <t>SYTHD260071</t>
+  </si>
+  <si>
+    <t>GRAND BASSAM</t>
+  </si>
+  <si>
+    <t>SYTHD260070</t>
+  </si>
+  <si>
+    <t>CLINIQUE MEDICALE SPECIALISEE</t>
+  </si>
+  <si>
+    <t>STE TEDIS PHARMA</t>
+  </si>
+  <si>
+    <t>FRANCHISE OCI</t>
+  </si>
+  <si>
+    <t>WILLIAMSVILLE</t>
+  </si>
+  <si>
+    <t>BUVPN260047</t>
   </si>
 </sst>
 </file>
@@ -1723,737 +1759,7 @@
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="147">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="74">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3529,7 +2835,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:T189"/>
+  <dimension ref="A1:T195"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29.453125" style="26" customWidth="1"/>
@@ -12174,7 +11480,7 @@
         <v>46079</v>
       </c>
       <c r="J141" s="24">
-        <f t="shared" ref="J141:J189" si="12">+NETWORKDAYS(H141,I141)</f>
+        <f t="shared" ref="J141:J195" si="12">+NETWORKDAYS(H141,I141)</f>
         <v>261</v>
       </c>
       <c r="K141" s="25" t="s">
@@ -12203,7 +11509,7 @@
         <v>46079</v>
       </c>
       <c r="S141" s="24">
-        <f t="shared" ref="S141:S189" si="13">NETWORKDAYS(H141,R141)</f>
+        <f t="shared" ref="S141:S195" si="13">NETWORKDAYS(H141,R141)</f>
         <v>261</v>
       </c>
       <c r="T141" s="11" t="s">
@@ -15327,6 +14633,390 @@
         <v>69</v>
       </c>
       <c r="T189" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A190" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="B190" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C190" s="44">
+        <v>50732535</v>
+      </c>
+      <c r="D190" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E190" s="44" t="s">
+        <v>431</v>
+      </c>
+      <c r="F190" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G190" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="H190" s="45">
+        <v>45919</v>
+      </c>
+      <c r="I190" s="45">
+        <v>46056</v>
+      </c>
+      <c r="J190" s="24">
+        <f t="shared" si="12"/>
+        <v>98</v>
+      </c>
+      <c r="K190" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L190" s="44" t="s">
+        <v>327</v>
+      </c>
+      <c r="M190" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="N190" s="44" t="s">
+        <v>148</v>
+      </c>
+      <c r="O190" s="44">
+        <v>0</v>
+      </c>
+      <c r="P190" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q190" s="52">
+        <v>0</v>
+      </c>
+      <c r="R190" s="14">
+        <v>46092</v>
+      </c>
+      <c r="S190" s="24">
+        <f t="shared" si="13"/>
+        <v>124</v>
+      </c>
+      <c r="T190" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A191" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="B191" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C191" s="44">
+        <v>58205267</v>
+      </c>
+      <c r="D191" s="44" t="s">
+        <v>433</v>
+      </c>
+      <c r="E191" s="44" t="s">
+        <v>434</v>
+      </c>
+      <c r="F191" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G191" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H191" s="45">
+        <v>46067</v>
+      </c>
+      <c r="I191" s="45">
+        <v>46087</v>
+      </c>
+      <c r="J191" s="24">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="K191" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L191" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="M191" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="N191" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="O191" s="44">
+        <v>0</v>
+      </c>
+      <c r="P191" s="44">
+        <v>430500</v>
+      </c>
+      <c r="Q191" s="52">
+        <v>430500</v>
+      </c>
+      <c r="R191" s="14">
+        <v>46092</v>
+      </c>
+      <c r="S191" s="24">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
+      <c r="T191" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A192" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="B192" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C192" s="44">
+        <v>58173859</v>
+      </c>
+      <c r="D192" s="44" t="s">
+        <v>435</v>
+      </c>
+      <c r="E192" s="44" t="s">
+        <v>436</v>
+      </c>
+      <c r="F192" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G192" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H192" s="45">
+        <v>46066</v>
+      </c>
+      <c r="I192" s="45">
+        <v>46087</v>
+      </c>
+      <c r="J192" s="24">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="K192" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L192" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="M192" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="N192" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="O192" s="44">
+        <v>0</v>
+      </c>
+      <c r="P192" s="44">
+        <v>430500</v>
+      </c>
+      <c r="Q192" s="52">
+        <v>430500</v>
+      </c>
+      <c r="R192" s="14">
+        <v>46092</v>
+      </c>
+      <c r="S192" s="24">
+        <f t="shared" si="13"/>
+        <v>19</v>
+      </c>
+      <c r="T192" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A193" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="B193" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C193" s="44">
+        <v>58650763</v>
+      </c>
+      <c r="D193" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E193" s="44">
+        <v>2722417296</v>
+      </c>
+      <c r="F193" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="G193" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H193" s="45">
+        <v>46073</v>
+      </c>
+      <c r="I193" s="45">
+        <v>46092</v>
+      </c>
+      <c r="J193" s="24">
+        <f t="shared" si="12"/>
+        <v>14</v>
+      </c>
+      <c r="K193" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L193" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="M193" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="N193" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="O193" s="44">
+        <v>150000</v>
+      </c>
+      <c r="P193" s="44">
+        <v>40000</v>
+      </c>
+      <c r="Q193" s="52">
+        <v>190000</v>
+      </c>
+      <c r="R193" s="14">
+        <v>46092</v>
+      </c>
+      <c r="S193" s="24">
+        <f t="shared" si="13"/>
+        <v>14</v>
+      </c>
+      <c r="T193" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A194" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="B194" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C194" s="44">
+        <v>58276534</v>
+      </c>
+      <c r="D194" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E194" s="44">
+        <v>2723489370</v>
+      </c>
+      <c r="F194" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="G194" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H194" s="45">
+        <v>46066</v>
+      </c>
+      <c r="I194" s="45">
+        <v>46092</v>
+      </c>
+      <c r="J194" s="24">
+        <f t="shared" si="12"/>
+        <v>19</v>
+      </c>
+      <c r="K194" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L194" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="M194" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="N194" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="O194" s="44">
+        <v>150000</v>
+      </c>
+      <c r="P194" s="44">
+        <v>40000</v>
+      </c>
+      <c r="Q194" s="52">
+        <v>190000</v>
+      </c>
+      <c r="R194" s="14">
+        <v>46092</v>
+      </c>
+      <c r="S194" s="24">
+        <f t="shared" si="13"/>
+        <v>19</v>
+      </c>
+      <c r="T194" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A195" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="B195" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C195" s="44">
+        <v>58853633</v>
+      </c>
+      <c r="D195" s="44" t="s">
+        <v>440</v>
+      </c>
+      <c r="E195" s="44" t="s">
+        <v>441</v>
+      </c>
+      <c r="F195" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="G195" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="H195" s="45">
+        <v>46079</v>
+      </c>
+      <c r="I195" s="45">
+        <v>46092</v>
+      </c>
+      <c r="J195" s="24">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="K195" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L195" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="M195" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="N195" s="44" t="s">
+        <v>148</v>
+      </c>
+      <c r="O195" s="44">
+        <v>0</v>
+      </c>
+      <c r="P195" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q195" s="52">
+        <v>0</v>
+      </c>
+      <c r="R195" s="14">
+        <v>46092</v>
+      </c>
+      <c r="S195" s="24">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="T195" s="11" t="s">
         <v>377</v>
       </c>
     </row>
@@ -15346,187 +15036,187 @@
     <cfRule type="duplicateValues" dxfId="69" priority="72"/>
     <cfRule type="duplicateValues" dxfId="68" priority="73"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="67" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="67" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="65" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="63" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="62" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="60" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="59" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="58" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="57" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="56" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="55" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="54" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="53" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="52" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="51" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="50" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="49" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="48" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="47" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="46" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="45" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
-    <cfRule type="duplicateValues" dxfId="44" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="43" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="42" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="40" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="39" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="38" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="37" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="36" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="34" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C114">
-    <cfRule type="duplicateValues" dxfId="33" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="32" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="31" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C157:C160">
+    <cfRule type="duplicateValues" dxfId="28" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C161:C163">
-    <cfRule type="duplicateValues" dxfId="29" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="28" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="26" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C168">
-    <cfRule type="duplicateValues" dxfId="24" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="23" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171">
-    <cfRule type="duplicateValues" dxfId="22" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173">
-    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="19" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C175">
-    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C178">
-    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179">
-    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="13" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="11" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="10" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="9" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="8" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="7" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="6" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="5" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="4" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172">
-    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C157:C160">
-    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="227" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2500FE49-8CE3-4EFB-84B8-31AC1EAE3369}"/>
+  <xr:revisionPtr revIDLastSave="270" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C336A09-76B4-440B-A3BC-BF0FF3777075}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$T$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$205</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="462">
   <si>
     <t>Client</t>
   </si>
@@ -1366,6 +1366,66 @@
   </si>
   <si>
     <t>BUVPN260047</t>
+  </si>
+  <si>
+    <t>Type demande</t>
+  </si>
+  <si>
+    <t>Hors Projet</t>
+  </si>
+  <si>
+    <t>Projet</t>
+  </si>
+  <si>
+    <t>REX HOTEL</t>
+  </si>
+  <si>
+    <t>YAMOUSSOUKRO</t>
+  </si>
+  <si>
+    <t>SYTHD260065</t>
+  </si>
+  <si>
+    <t>SYTHD260069</t>
+  </si>
+  <si>
+    <t>BOUNA</t>
+  </si>
+  <si>
+    <t>BUVPN260052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AERIA </t>
+  </si>
+  <si>
+    <t>BUVPN250197</t>
+  </si>
+  <si>
+    <t>BUVPN250196</t>
+  </si>
+  <si>
+    <t>SOUBRE</t>
+  </si>
+  <si>
+    <t>BUVPN150291</t>
+  </si>
+  <si>
+    <t>AERIA</t>
+  </si>
+  <si>
+    <t>BUVPN260007</t>
+  </si>
+  <si>
+    <t>VPNLL140112</t>
+  </si>
+  <si>
+    <t>AFRICA SOURCING COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>TRV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC MARKET COCODY BONOUMIN </t>
   </si>
 </sst>
 </file>
@@ -1583,7 +1643,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1665,9 +1725,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1687,12 +1744,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1753,13 +1804,787 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="74">
+  <dxfs count="149">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2834,11 +3659,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:T195"/>
+  <dimension ref="A1:U205"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.453125" style="26" customWidth="1"/>
+    <col min="1" max="1" width="27.90625" style="26" customWidth="1"/>
     <col min="3" max="3" width="8.90625" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="11" bestFit="1" customWidth="1"/>
@@ -2852,9 +3676,10 @@
     <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.1796875" customWidth="1"/>
     <col min="20" max="20" width="6.54296875" customWidth="1"/>
+    <col min="21" max="21" width="13.7265625" style="67" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
@@ -2915,69 +3740,73 @@
       <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="s">
+      <c r="U1" s="65" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="58" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="59">
         <v>55472663</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="37">
+      <c r="H2" s="61">
         <v>46010</v>
       </c>
-      <c r="I2" s="38">
+      <c r="I2" s="62">
         <v>46015</v>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="63">
         <f>+NETWORKDAYS(H2,I2)</f>
         <v>4</v>
       </c>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="13" t="s">
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="N2" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="46">
+      <c r="O2" s="64">
         <v>0</v>
       </c>
-      <c r="P2" s="46">
+      <c r="P2" s="64">
         <v>0</v>
       </c>
-      <c r="Q2" s="46">
+      <c r="Q2" s="64">
         <f>P2+O2</f>
         <v>0</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="35">
         <v>46024</v>
       </c>
-      <c r="S2" s="24">
+      <c r="S2" s="63">
         <f>NETWORKDAYS(H2,R2)</f>
         <v>11</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="T2" s="34" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U2" s="65"/>
+    </row>
+    <row r="3" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>159</v>
       </c>
@@ -3017,13 +3846,13 @@
       <c r="N3" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="O3" s="47">
+      <c r="O3" s="44">
         <v>1000000</v>
       </c>
-      <c r="P3" s="47">
+      <c r="P3" s="44">
         <v>231750</v>
       </c>
-      <c r="Q3" s="48">
+      <c r="Q3" s="45">
         <f>P3+O3</f>
         <v>1231750</v>
       </c>
@@ -3037,8 +3866,9 @@
       <c r="T3" s="11" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U3" s="65"/>
+    </row>
+    <row r="4" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>154</v>
       </c>
@@ -3078,13 +3908,13 @@
       <c r="N4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="47">
+      <c r="O4" s="44">
         <v>0</v>
       </c>
-      <c r="P4" s="47">
+      <c r="P4" s="44">
         <v>0</v>
       </c>
-      <c r="Q4" s="48">
+      <c r="Q4" s="45">
         <f>P4+O4</f>
         <v>0</v>
       </c>
@@ -3098,8 +3928,9 @@
       <c r="T4" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U4" s="65"/>
+    </row>
+    <row r="5" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
         <v>154</v>
       </c>
@@ -3139,13 +3970,13 @@
       <c r="N5" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="44">
         <v>0</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="44">
         <v>0</v>
       </c>
-      <c r="Q5" s="48">
+      <c r="Q5" s="45">
         <f>P5+O5</f>
         <v>0</v>
       </c>
@@ -3159,8 +3990,9 @@
       <c r="T5" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U5" s="65"/>
+    </row>
+    <row r="6" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>164</v>
       </c>
@@ -3206,7 +4038,7 @@
       <c r="P6" s="15">
         <v>71435</v>
       </c>
-      <c r="Q6" s="48">
+      <c r="Q6" s="45">
         <f t="shared" ref="Q6:Q69" si="2">P6+O6</f>
         <v>341435</v>
       </c>
@@ -3220,8 +4052,9 @@
       <c r="T6" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U6" s="65"/>
+    </row>
+    <row r="7" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>165</v>
       </c>
@@ -3267,7 +4100,7 @@
       <c r="P7" s="15">
         <v>40000</v>
       </c>
-      <c r="Q7" s="48">
+      <c r="Q7" s="45">
         <f t="shared" si="2"/>
         <v>190000</v>
       </c>
@@ -3281,8 +4114,9 @@
       <c r="T7" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U7" s="65"/>
+    </row>
+    <row r="8" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>166</v>
       </c>
@@ -3307,7 +4141,7 @@
       <c r="H8" s="14">
         <v>45972</v>
       </c>
-      <c r="I8" s="33">
+      <c r="I8" s="32">
         <v>46017</v>
       </c>
       <c r="J8" s="24">
@@ -3322,13 +4156,13 @@
       <c r="N8" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="O8" s="47">
+      <c r="O8" s="44">
         <v>3264000</v>
       </c>
-      <c r="P8" s="47">
+      <c r="P8" s="44">
         <v>408000</v>
       </c>
-      <c r="Q8" s="48">
+      <c r="Q8" s="45">
         <f t="shared" si="2"/>
         <v>3672000</v>
       </c>
@@ -3342,8 +4176,9 @@
       <c r="T8" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U8" s="65"/>
+    </row>
+    <row r="9" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>169</v>
       </c>
@@ -3375,21 +4210,21 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
       <c r="M9" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N9" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O9" s="47">
+      <c r="O9" s="44">
         <v>1800000</v>
       </c>
-      <c r="P9" s="47">
+      <c r="P9" s="44">
         <v>301520</v>
       </c>
-      <c r="Q9" s="48">
+      <c r="Q9" s="45">
         <f t="shared" si="2"/>
         <v>2101520</v>
       </c>
@@ -3403,8 +4238,9 @@
       <c r="T9" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U9" s="65"/>
+    </row>
+    <row r="10" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>172</v>
       </c>
@@ -3436,21 +4272,21 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
       <c r="M10" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N10" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="O10" s="47">
+      <c r="O10" s="44">
         <v>1977000</v>
       </c>
-      <c r="P10" s="47">
+      <c r="P10" s="44">
         <v>0</v>
       </c>
-      <c r="Q10" s="48">
+      <c r="Q10" s="45">
         <f t="shared" si="2"/>
         <v>1977000</v>
       </c>
@@ -3464,8 +4300,9 @@
       <c r="T10" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U10" s="65"/>
+    </row>
+    <row r="11" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>172</v>
       </c>
@@ -3497,21 +4334,21 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
       <c r="M11" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N11" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="O11" s="47">
+      <c r="O11" s="44">
         <v>1977000</v>
       </c>
-      <c r="P11" s="47">
+      <c r="P11" s="44">
         <v>0</v>
       </c>
-      <c r="Q11" s="48">
+      <c r="Q11" s="45">
         <f t="shared" si="2"/>
         <v>1977000</v>
       </c>
@@ -3525,8 +4362,9 @@
       <c r="T11" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U11" s="65"/>
+    </row>
+    <row r="12" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
         <v>177</v>
       </c>
@@ -3558,21 +4396,21 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
       <c r="M12" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N12" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="O12" s="47">
+      <c r="O12" s="44">
         <v>1500000</v>
       </c>
-      <c r="P12" s="47">
+      <c r="P12" s="44">
         <v>571781</v>
       </c>
-      <c r="Q12" s="48">
+      <c r="Q12" s="45">
         <f t="shared" si="2"/>
         <v>2071781</v>
       </c>
@@ -3586,8 +4424,9 @@
       <c r="T12" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U12" s="65"/>
+    </row>
+    <row r="13" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
         <v>154</v>
       </c>
@@ -3609,19 +4448,19 @@
       <c r="G13" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="39">
+      <c r="H13" s="36">
         <v>46010</v>
       </c>
-      <c r="I13" s="39">
+      <c r="I13" s="36">
         <v>46030</v>
       </c>
       <c r="J13" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="40" t="s">
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="37" t="s">
         <v>157</v>
       </c>
       <c r="N13" s="19" t="s">
@@ -3633,7 +4472,7 @@
       <c r="P13" s="15">
         <v>0</v>
       </c>
-      <c r="Q13" s="48">
+      <c r="Q13" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3647,8 +4486,9 @@
       <c r="T13" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U13" s="65"/>
+    </row>
+    <row r="14" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
         <v>154</v>
       </c>
@@ -3670,19 +4510,19 @@
       <c r="G14" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="39">
+      <c r="H14" s="36">
         <v>46010</v>
       </c>
-      <c r="I14" s="39">
+      <c r="I14" s="36">
         <v>46030</v>
       </c>
       <c r="J14" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="40" t="s">
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="37" t="s">
         <v>157</v>
       </c>
       <c r="N14" s="19" t="s">
@@ -3694,7 +4534,7 @@
       <c r="P14" s="15">
         <v>0</v>
       </c>
-      <c r="Q14" s="48">
+      <c r="Q14" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3708,8 +4548,9 @@
       <c r="T14" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U14" s="65"/>
+    </row>
+    <row r="15" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>172</v>
       </c>
@@ -3741,21 +4582,21 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="40" t="s">
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="37" t="s">
         <v>24</v>
       </c>
       <c r="N15" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="O15" s="47">
+      <c r="O15" s="44">
         <v>847200</v>
       </c>
-      <c r="P15" s="47">
+      <c r="P15" s="44">
         <v>0</v>
       </c>
-      <c r="Q15" s="48">
+      <c r="Q15" s="45">
         <f t="shared" si="2"/>
         <v>847200</v>
       </c>
@@ -3769,8 +4610,9 @@
       <c r="T15" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U15" s="65"/>
+    </row>
+    <row r="16" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>154</v>
       </c>
@@ -3802,21 +4644,21 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
       <c r="M16" s="11" t="s">
         <v>157</v>
       </c>
       <c r="N16" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O16" s="47">
+      <c r="O16" s="44">
         <v>0</v>
       </c>
-      <c r="P16" s="47">
+      <c r="P16" s="44">
         <v>0</v>
       </c>
-      <c r="Q16" s="48">
+      <c r="Q16" s="45">
         <f>P16+O16</f>
         <v>0</v>
       </c>
@@ -3830,8 +4672,9 @@
       <c r="T16" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U16" s="65"/>
+    </row>
+    <row r="17" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>154</v>
       </c>
@@ -3863,21 +4706,21 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
       <c r="M17" s="11" t="s">
         <v>157</v>
       </c>
       <c r="N17" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O17" s="48">
+      <c r="O17" s="45">
         <v>0</v>
       </c>
-      <c r="P17" s="48">
+      <c r="P17" s="45">
         <v>0</v>
       </c>
-      <c r="Q17" s="48">
+      <c r="Q17" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3891,8 +4734,9 @@
       <c r="T17" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U17" s="65"/>
+    </row>
+    <row r="18" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
         <v>186</v>
       </c>
@@ -3924,21 +4768,21 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="K18" s="31"/>
-      <c r="L18" s="31"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
       <c r="M18" s="11" t="s">
         <v>188</v>
       </c>
       <c r="N18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O18" s="40">
+      <c r="O18" s="37">
         <v>0</v>
       </c>
-      <c r="P18" s="47">
+      <c r="P18" s="44">
         <v>1588888</v>
       </c>
-      <c r="Q18" s="48">
+      <c r="Q18" s="45">
         <f t="shared" si="2"/>
         <v>1588888</v>
       </c>
@@ -3952,8 +4796,9 @@
       <c r="T18" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U18" s="65"/>
+    </row>
+    <row r="19" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>189</v>
       </c>
@@ -3985,21 +4830,21 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
       <c r="M19" s="11" t="s">
         <v>157</v>
       </c>
       <c r="N19" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O19" s="40">
+      <c r="O19" s="37">
         <v>1480000</v>
       </c>
-      <c r="P19" s="47">
+      <c r="P19" s="44">
         <v>0</v>
       </c>
-      <c r="Q19" s="48">
+      <c r="Q19" s="45">
         <f t="shared" si="2"/>
         <v>1480000</v>
       </c>
@@ -4013,8 +4858,9 @@
       <c r="T19" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U19" s="65"/>
+    </row>
+    <row r="20" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
         <v>189</v>
       </c>
@@ -4046,21 +4892,21 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
       <c r="M20" s="11" t="s">
         <v>157</v>
       </c>
       <c r="N20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O20" s="48">
+      <c r="O20" s="45">
         <v>0</v>
       </c>
-      <c r="P20" s="48">
+      <c r="P20" s="45">
         <v>0</v>
       </c>
-      <c r="Q20" s="48">
+      <c r="Q20" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4074,8 +4920,9 @@
       <c r="T20" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U20" s="65"/>
+    </row>
+    <row r="21" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>193</v>
       </c>
@@ -4107,21 +4954,21 @@
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
       <c r="M21" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N21" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="O21" s="47">
+      <c r="O21" s="44">
         <v>3000000</v>
       </c>
-      <c r="P21" s="47">
+      <c r="P21" s="44">
         <v>270000</v>
       </c>
-      <c r="Q21" s="48">
+      <c r="Q21" s="45">
         <f t="shared" si="2"/>
         <v>3270000</v>
       </c>
@@ -4135,8 +4982,9 @@
       <c r="T21" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U21" s="65"/>
+    </row>
+    <row r="22" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>43</v>
       </c>
@@ -4168,21 +5016,21 @@
         <f t="shared" si="0"/>
         <v>245</v>
       </c>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
       <c r="M22" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N22" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="O22" s="47">
+      <c r="O22" s="44">
         <v>2000000</v>
       </c>
-      <c r="P22" s="47">
+      <c r="P22" s="44">
         <v>380000</v>
       </c>
-      <c r="Q22" s="48">
+      <c r="Q22" s="45">
         <f t="shared" si="2"/>
         <v>2380000</v>
       </c>
@@ -4196,8 +5044,9 @@
       <c r="T22" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U22" s="65"/>
+    </row>
+    <row r="23" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
         <v>201</v>
       </c>
@@ -4229,21 +5078,21 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="40" t="s">
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="37" t="s">
         <v>157</v>
       </c>
       <c r="N23" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="40">
+      <c r="O23" s="37">
         <v>0</v>
       </c>
-      <c r="P23" s="47">
+      <c r="P23" s="44">
         <v>0</v>
       </c>
-      <c r="Q23" s="48">
+      <c r="Q23" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4257,8 +5106,9 @@
       <c r="T23" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U23" s="65"/>
+    </row>
+    <row r="24" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>204</v>
       </c>
@@ -4290,21 +5140,21 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
       <c r="M24" s="11" t="s">
         <v>157</v>
       </c>
       <c r="N24" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O24" s="47">
+      <c r="O24" s="44">
         <v>0</v>
       </c>
-      <c r="P24" s="47">
+      <c r="P24" s="44">
         <v>0</v>
       </c>
-      <c r="Q24" s="48">
+      <c r="Q24" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4318,8 +5168,9 @@
       <c r="T24" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U24" s="65"/>
+    </row>
+    <row r="25" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>206</v>
       </c>
@@ -4351,21 +5202,21 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
       <c r="M25" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N25" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O25" s="48">
+      <c r="O25" s="45">
         <v>144000</v>
       </c>
-      <c r="P25" s="48">
+      <c r="P25" s="45">
         <v>0</v>
       </c>
-      <c r="Q25" s="48">
+      <c r="Q25" s="45">
         <f t="shared" si="2"/>
         <v>144000</v>
       </c>
@@ -4379,8 +5230,9 @@
       <c r="T25" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U25" s="65"/>
+    </row>
+    <row r="26" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>207</v>
       </c>
@@ -4412,21 +5264,21 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
       <c r="M26" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N26" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="O26" s="48">
+      <c r="O26" s="45">
         <v>1000000</v>
       </c>
-      <c r="P26" s="48">
+      <c r="P26" s="45">
         <v>0</v>
       </c>
-      <c r="Q26" s="48">
+      <c r="Q26" s="45">
         <f t="shared" si="2"/>
         <v>1000000</v>
       </c>
@@ -4440,8 +5292,9 @@
       <c r="T26" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U26" s="65"/>
+    </row>
+    <row r="27" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
         <v>172</v>
       </c>
@@ -4473,21 +5326,21 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
       <c r="M27" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N27" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="O27" s="47">
+      <c r="O27" s="44">
         <v>847200</v>
       </c>
-      <c r="P27" s="47">
+      <c r="P27" s="44">
         <v>0</v>
       </c>
-      <c r="Q27" s="48">
+      <c r="Q27" s="45">
         <f t="shared" si="2"/>
         <v>847200</v>
       </c>
@@ -4501,8 +5354,9 @@
       <c r="T27" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U27" s="65"/>
+    </row>
+    <row r="28" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
         <v>210</v>
       </c>
@@ -4534,21 +5388,21 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
       <c r="M28" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N28" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O28" s="47">
+      <c r="O28" s="44">
         <v>2500000</v>
       </c>
-      <c r="P28" s="47">
+      <c r="P28" s="44">
         <v>280000</v>
       </c>
-      <c r="Q28" s="48">
+      <c r="Q28" s="45">
         <f t="shared" si="2"/>
         <v>2780000</v>
       </c>
@@ -4562,8 +5416,9 @@
       <c r="T28" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U28" s="65"/>
+    </row>
+    <row r="29" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
         <v>213</v>
       </c>
@@ -4595,21 +5450,21 @@
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
       <c r="M29" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N29" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="O29" s="47">
+      <c r="O29" s="44">
         <v>32214683</v>
       </c>
-      <c r="P29" s="47">
+      <c r="P29" s="44">
         <v>6403996</v>
       </c>
-      <c r="Q29" s="48">
+      <c r="Q29" s="45">
         <f t="shared" si="2"/>
         <v>38618679</v>
       </c>
@@ -4623,8 +5478,9 @@
       <c r="T29" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U29" s="65"/>
+    </row>
+    <row r="30" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>217</v>
       </c>
@@ -4656,21 +5512,21 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
       <c r="M30" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N30" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O30" s="48">
+      <c r="O30" s="45">
         <v>150000</v>
       </c>
-      <c r="P30" s="48">
+      <c r="P30" s="45">
         <v>40000</v>
       </c>
-      <c r="Q30" s="48">
+      <c r="Q30" s="45">
         <f t="shared" si="2"/>
         <v>190000</v>
       </c>
@@ -4684,8 +5540,9 @@
       <c r="T30" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U30" s="65"/>
+    </row>
+    <row r="31" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>218</v>
       </c>
@@ -4717,21 +5574,21 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
       <c r="M31" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N31" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="O31" s="47">
+      <c r="O31" s="44">
         <v>0</v>
       </c>
-      <c r="P31" s="47">
+      <c r="P31" s="44">
         <v>40000</v>
       </c>
-      <c r="Q31" s="48">
+      <c r="Q31" s="45">
         <f t="shared" si="2"/>
         <v>40000</v>
       </c>
@@ -4745,8 +5602,9 @@
       <c r="T31" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U31" s="65"/>
+    </row>
+    <row r="32" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
         <v>81</v>
       </c>
@@ -4778,21 +5636,21 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
       <c r="M32" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N32" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O32" s="47">
+      <c r="O32" s="44">
         <v>1000000</v>
       </c>
-      <c r="P32" s="47">
+      <c r="P32" s="44">
         <v>705164</v>
       </c>
-      <c r="Q32" s="48">
+      <c r="Q32" s="45">
         <f t="shared" si="2"/>
         <v>1705164</v>
       </c>
@@ -4806,8 +5664,9 @@
       <c r="T32" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U32" s="65"/>
+    </row>
+    <row r="33" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
         <v>91</v>
       </c>
@@ -4839,21 +5698,21 @@
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
       <c r="M33" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N33" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="O33" s="47">
+      <c r="O33" s="44">
         <v>0</v>
       </c>
-      <c r="P33" s="47">
+      <c r="P33" s="44">
         <v>170681</v>
       </c>
-      <c r="Q33" s="48">
+      <c r="Q33" s="45">
         <f t="shared" si="2"/>
         <v>170681</v>
       </c>
@@ -4867,8 +5726,9 @@
       <c r="T33" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U33" s="65"/>
+    </row>
+    <row r="34" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
         <v>91</v>
       </c>
@@ -4900,21 +5760,21 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
       <c r="M34" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N34" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O34" s="47">
+      <c r="O34" s="44">
         <v>0</v>
       </c>
-      <c r="P34" s="47">
+      <c r="P34" s="44">
         <v>92730</v>
       </c>
-      <c r="Q34" s="48">
+      <c r="Q34" s="45">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
@@ -4928,8 +5788,9 @@
       <c r="T34" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U34" s="65"/>
+    </row>
+    <row r="35" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
         <v>91</v>
       </c>
@@ -4961,21 +5822,21 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
       <c r="M35" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N35" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O35" s="47">
+      <c r="O35" s="44">
         <v>0</v>
       </c>
-      <c r="P35" s="47">
+      <c r="P35" s="44">
         <v>92730</v>
       </c>
-      <c r="Q35" s="48">
+      <c r="Q35" s="45">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
@@ -4989,8 +5850,9 @@
       <c r="T35" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U35" s="65"/>
+    </row>
+    <row r="36" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12" t="s">
         <v>91</v>
       </c>
@@ -5022,21 +5884,21 @@
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="K36" s="31"/>
-      <c r="L36" s="31"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
       <c r="M36" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N36" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O36" s="47">
+      <c r="O36" s="44">
         <v>0</v>
       </c>
-      <c r="P36" s="47">
+      <c r="P36" s="44">
         <v>92730</v>
       </c>
-      <c r="Q36" s="48">
+      <c r="Q36" s="45">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
@@ -5050,8 +5912,9 @@
       <c r="T36" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U36" s="65"/>
+    </row>
+    <row r="37" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12" t="s">
         <v>91</v>
       </c>
@@ -5083,21 +5946,21 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
       <c r="M37" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N37" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="O37" s="47">
+      <c r="O37" s="44">
         <v>0</v>
       </c>
-      <c r="P37" s="47">
+      <c r="P37" s="44">
         <v>92730</v>
       </c>
-      <c r="Q37" s="48">
+      <c r="Q37" s="45">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
@@ -5111,15 +5974,16 @@
       <c r="T37" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U37" s="65"/>
+    </row>
+    <row r="38" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
         <v>226</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C38" s="41">
+      <c r="C38" s="38">
         <v>54887240</v>
       </c>
       <c r="D38" s="12" t="s">
@@ -5144,21 +6008,21 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="K38" s="31"/>
-      <c r="L38" s="31"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
       <c r="M38" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N38" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O38" s="47">
+      <c r="O38" s="44">
         <v>2000500</v>
       </c>
-      <c r="P38" s="47">
+      <c r="P38" s="44">
         <v>667054</v>
       </c>
-      <c r="Q38" s="48">
+      <c r="Q38" s="45">
         <f t="shared" si="2"/>
         <v>2667554</v>
       </c>
@@ -5172,8 +6036,9 @@
       <c r="T38" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U38" s="65"/>
+    </row>
+    <row r="39" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
         <v>228</v>
       </c>
@@ -5205,21 +6070,21 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
       <c r="M39" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N39" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O39" s="47">
+      <c r="O39" s="44">
         <v>0</v>
       </c>
-      <c r="P39" s="47">
+      <c r="P39" s="44">
         <v>189985</v>
       </c>
-      <c r="Q39" s="48">
+      <c r="Q39" s="45">
         <f t="shared" si="2"/>
         <v>189985</v>
       </c>
@@ -5233,8 +6098,9 @@
       <c r="T39" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U39" s="65"/>
+    </row>
+    <row r="40" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
         <v>91</v>
       </c>
@@ -5266,21 +6132,21 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="K40" s="31"/>
-      <c r="L40" s="31"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
       <c r="M40" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N40" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="O40" s="47">
+      <c r="O40" s="44">
         <v>0</v>
       </c>
-      <c r="P40" s="47">
+      <c r="P40" s="44">
         <v>92730</v>
       </c>
-      <c r="Q40" s="48">
+      <c r="Q40" s="45">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
@@ -5294,8 +6160,9 @@
       <c r="T40" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="41" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U40" s="65"/>
+    </row>
+    <row r="41" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
         <v>231</v>
       </c>
@@ -5327,21 +6194,21 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="K41" s="31"/>
-      <c r="L41" s="31"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
       <c r="M41" s="11" t="s">
         <v>157</v>
       </c>
       <c r="N41" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="O41" s="48">
+      <c r="O41" s="45">
         <v>0</v>
       </c>
-      <c r="P41" s="48">
+      <c r="P41" s="45">
         <v>0</v>
       </c>
-      <c r="Q41" s="48">
+      <c r="Q41" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5355,8 +6222,9 @@
       <c r="T41" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U41" s="65"/>
+    </row>
+    <row r="42" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
         <v>234</v>
       </c>
@@ -5388,21 +6256,21 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
       <c r="M42" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N42" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="O42" s="47">
+      <c r="O42" s="44">
         <v>500000</v>
       </c>
-      <c r="P42" s="47">
+      <c r="P42" s="44">
         <v>500000</v>
       </c>
-      <c r="Q42" s="48">
+      <c r="Q42" s="45">
         <f t="shared" si="2"/>
         <v>1000000</v>
       </c>
@@ -5416,8 +6284,9 @@
       <c r="T42" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="43" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U42" s="65"/>
+    </row>
+    <row r="43" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>236</v>
       </c>
@@ -5439,31 +6308,31 @@
       <c r="G43" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H43" s="39">
+      <c r="H43" s="36">
         <v>45953</v>
       </c>
-      <c r="I43" s="42">
+      <c r="I43" s="39">
         <v>46038</v>
       </c>
       <c r="J43" s="24">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="K43" s="31"/>
-      <c r="L43" s="31"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
       <c r="M43" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N43" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O43" s="48">
+      <c r="O43" s="45">
         <v>150000</v>
       </c>
-      <c r="P43" s="48">
+      <c r="P43" s="45">
         <v>60000</v>
       </c>
-      <c r="Q43" s="48">
+      <c r="Q43" s="45">
         <f t="shared" si="2"/>
         <v>210000</v>
       </c>
@@ -5477,8 +6346,9 @@
       <c r="T43" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U43" s="65"/>
+    </row>
+    <row r="44" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
         <v>237</v>
       </c>
@@ -5500,31 +6370,31 @@
       <c r="G44" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H44" s="39">
+      <c r="H44" s="36">
         <v>45999</v>
       </c>
-      <c r="I44" s="42">
+      <c r="I44" s="39">
         <v>46030</v>
       </c>
       <c r="J44" s="24">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K44" s="31"/>
-      <c r="L44" s="31"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
       <c r="M44" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N44" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O44" s="48">
+      <c r="O44" s="45">
         <v>150000</v>
       </c>
-      <c r="P44" s="48">
+      <c r="P44" s="45">
         <v>60000</v>
       </c>
-      <c r="Q44" s="48">
+      <c r="Q44" s="45">
         <f t="shared" si="2"/>
         <v>210000</v>
       </c>
@@ -5538,8 +6408,9 @@
       <c r="T44" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="45" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U44" s="65"/>
+    </row>
+    <row r="45" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
         <v>238</v>
       </c>
@@ -5571,21 +6442,21 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K45" s="31"/>
-      <c r="L45" s="31"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
       <c r="M45" s="11" t="s">
         <v>157</v>
       </c>
       <c r="N45" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="O45" s="48">
+      <c r="O45" s="45">
         <v>955437</v>
       </c>
-      <c r="P45" s="48">
+      <c r="P45" s="45">
         <v>0</v>
       </c>
-      <c r="Q45" s="48">
+      <c r="Q45" s="45">
         <f t="shared" si="2"/>
         <v>955437</v>
       </c>
@@ -5599,8 +6470,9 @@
       <c r="T45" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U45" s="65"/>
+    </row>
+    <row r="46" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="12" t="s">
         <v>240</v>
       </c>
@@ -5632,21 +6504,21 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="K46" s="31"/>
-      <c r="L46" s="31"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
       <c r="M46" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N46" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="O46" s="48">
+      <c r="O46" s="45">
         <v>500000</v>
       </c>
-      <c r="P46" s="48">
+      <c r="P46" s="45">
         <v>0</v>
       </c>
-      <c r="Q46" s="48">
+      <c r="Q46" s="45">
         <f t="shared" si="2"/>
         <v>500000</v>
       </c>
@@ -5660,8 +6532,9 @@
       <c r="T46" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="47" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U46" s="65"/>
+    </row>
+    <row r="47" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="12" t="s">
         <v>91</v>
       </c>
@@ -5693,21 +6566,21 @@
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="K47" s="31"/>
-      <c r="L47" s="31"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
       <c r="M47" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N47" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="O47" s="47">
+      <c r="O47" s="44">
         <v>0</v>
       </c>
-      <c r="P47" s="47">
+      <c r="P47" s="44">
         <v>217691</v>
       </c>
-      <c r="Q47" s="48">
+      <c r="Q47" s="45">
         <f t="shared" si="2"/>
         <v>217691</v>
       </c>
@@ -5721,8 +6594,9 @@
       <c r="T47" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="48" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U47" s="65"/>
+    </row>
+    <row r="48" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="12" t="s">
         <v>243</v>
       </c>
@@ -5754,21 +6628,21 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K48" s="31"/>
-      <c r="L48" s="31"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
       <c r="M48" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N48" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="O48" s="47">
+      <c r="O48" s="44">
         <v>2362401</v>
       </c>
-      <c r="P48" s="47">
+      <c r="P48" s="44">
         <v>300000</v>
       </c>
-      <c r="Q48" s="48">
+      <c r="Q48" s="45">
         <f t="shared" si="2"/>
         <v>2662401</v>
       </c>
@@ -5782,8 +6656,9 @@
       <c r="T48" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="49" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U48" s="65"/>
+    </row>
+    <row r="49" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="12" t="s">
         <v>246</v>
       </c>
@@ -5815,21 +6690,21 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="K49" s="31"/>
-      <c r="L49" s="31"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
       <c r="M49" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N49" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="O49" s="48">
+      <c r="O49" s="45">
         <v>0</v>
       </c>
-      <c r="P49" s="48">
+      <c r="P49" s="45">
         <v>0</v>
       </c>
-      <c r="Q49" s="48">
+      <c r="Q49" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5843,8 +6718,9 @@
       <c r="T49" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="50" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U49" s="65"/>
+    </row>
+    <row r="50" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12" t="s">
         <v>248</v>
       </c>
@@ -5876,21 +6752,21 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K50" s="31"/>
-      <c r="L50" s="31"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
       <c r="M50" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N50" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="O50" s="47">
+      <c r="O50" s="44">
         <v>2000000</v>
       </c>
-      <c r="P50" s="47">
+      <c r="P50" s="44">
         <v>646323</v>
       </c>
-      <c r="Q50" s="48">
+      <c r="Q50" s="45">
         <f t="shared" si="2"/>
         <v>2646323</v>
       </c>
@@ -5904,8 +6780,9 @@
       <c r="T50" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="51" spans="1:20" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U50" s="65"/>
+    </row>
+    <row r="51" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="12" t="s">
         <v>250</v>
       </c>
@@ -5937,21 +6814,21 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K51" s="31"/>
-      <c r="L51" s="31"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
       <c r="M51" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N51" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O51" s="47">
+      <c r="O51" s="44">
         <v>0</v>
       </c>
-      <c r="P51" s="47">
+      <c r="P51" s="44">
         <v>0</v>
       </c>
-      <c r="Q51" s="48">
+      <c r="Q51" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5965,8 +6842,9 @@
       <c r="T51" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U51" s="65"/>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" s="12" t="s">
         <v>250</v>
       </c>
@@ -5998,21 +6876,21 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K52" s="31"/>
-      <c r="L52" s="31"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
       <c r="M52" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N52" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O52" s="47">
+      <c r="O52" s="44">
         <v>500000</v>
       </c>
-      <c r="P52" s="47">
+      <c r="P52" s="44">
         <v>325000</v>
       </c>
-      <c r="Q52" s="48">
+      <c r="Q52" s="45">
         <f t="shared" si="2"/>
         <v>825000</v>
       </c>
@@ -6026,8 +6904,9 @@
       <c r="T52" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U52" s="65"/>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" s="12" t="s">
         <v>253</v>
       </c>
@@ -6059,21 +6938,21 @@
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
       <c r="M53" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N53" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="O53" s="47">
+      <c r="O53" s="44">
         <v>0</v>
       </c>
-      <c r="P53" s="47">
+      <c r="P53" s="44">
         <v>433989</v>
       </c>
-      <c r="Q53" s="48">
+      <c r="Q53" s="45">
         <f t="shared" si="2"/>
         <v>433989</v>
       </c>
@@ -6087,8 +6966,9 @@
       <c r="T53" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U53" s="65"/>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
         <v>256</v>
       </c>
@@ -6120,21 +7000,21 @@
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
-      <c r="K54" s="31"/>
-      <c r="L54" s="31"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
       <c r="M54" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N54" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O54" s="48">
+      <c r="O54" s="45">
         <v>150000</v>
       </c>
-      <c r="P54" s="48">
+      <c r="P54" s="45">
         <v>40000</v>
       </c>
-      <c r="Q54" s="48">
+      <c r="Q54" s="45">
         <f t="shared" si="2"/>
         <v>190000</v>
       </c>
@@ -6148,8 +7028,9 @@
       <c r="T54" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U54" s="65"/>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>258</v>
       </c>
@@ -6181,21 +7062,21 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="K55" s="31"/>
-      <c r="L55" s="31"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
       <c r="M55" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N55" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O55" s="48">
+      <c r="O55" s="45">
         <v>1000000</v>
       </c>
-      <c r="P55" s="48">
+      <c r="P55" s="45">
         <v>231750</v>
       </c>
-      <c r="Q55" s="48">
+      <c r="Q55" s="45">
         <f t="shared" si="2"/>
         <v>1231750</v>
       </c>
@@ -6209,8 +7090,9 @@
       <c r="T55" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U55" s="65"/>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" s="12" t="s">
         <v>259</v>
       </c>
@@ -6242,21 +7124,21 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="K56" s="31"/>
-      <c r="L56" s="31"/>
+      <c r="K56" s="30"/>
+      <c r="L56" s="30"/>
       <c r="M56" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N56" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="O56" s="47">
+      <c r="O56" s="44">
         <v>133779304</v>
       </c>
-      <c r="P56" s="47">
+      <c r="P56" s="44">
         <v>5620246</v>
       </c>
-      <c r="Q56" s="48">
+      <c r="Q56" s="45">
         <f t="shared" si="2"/>
         <v>139399550</v>
       </c>
@@ -6270,8 +7152,9 @@
       <c r="T56" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U56" s="65"/>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A57" s="12" t="s">
         <v>259</v>
       </c>
@@ -6303,21 +7186,21 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="K57" s="31"/>
-      <c r="L57" s="31"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
       <c r="M57" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N57" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="O57" s="47">
+      <c r="O57" s="44">
         <v>0</v>
       </c>
-      <c r="P57" s="47">
+      <c r="P57" s="44">
         <v>500000</v>
       </c>
-      <c r="Q57" s="48">
+      <c r="Q57" s="45">
         <f t="shared" si="2"/>
         <v>500000</v>
       </c>
@@ -6331,8 +7214,9 @@
       <c r="T57" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U57" s="65"/>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A58" s="12" t="s">
         <v>253</v>
       </c>
@@ -6364,21 +7248,21 @@
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
-      <c r="K58" s="31"/>
-      <c r="L58" s="31"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
       <c r="M58" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N58" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="O58" s="47">
+      <c r="O58" s="44">
         <v>0</v>
       </c>
-      <c r="P58" s="47">
+      <c r="P58" s="44">
         <v>433989</v>
       </c>
-      <c r="Q58" s="48">
+      <c r="Q58" s="45">
         <f t="shared" si="2"/>
         <v>433989</v>
       </c>
@@ -6392,8 +7276,9 @@
       <c r="T58" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U58" s="65"/>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A59" s="12" t="s">
         <v>265</v>
       </c>
@@ -6425,21 +7310,21 @@
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-      <c r="K59" s="31"/>
-      <c r="L59" s="31"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="30"/>
       <c r="M59" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N59" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O59" s="47">
+      <c r="O59" s="44">
         <v>500000</v>
       </c>
-      <c r="P59" s="47">
+      <c r="P59" s="44">
         <v>400000</v>
       </c>
-      <c r="Q59" s="48">
+      <c r="Q59" s="45">
         <f t="shared" si="2"/>
         <v>900000</v>
       </c>
@@ -6453,8 +7338,9 @@
       <c r="T59" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U59" s="65"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A60" s="12" t="s">
         <v>267</v>
       </c>
@@ -6486,21 +7372,21 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K60" s="31"/>
-      <c r="L60" s="31"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="30"/>
       <c r="M60" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N60" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="O60" s="47">
+      <c r="O60" s="44">
         <v>1109000</v>
       </c>
-      <c r="P60" s="47">
+      <c r="P60" s="44">
         <v>935000</v>
       </c>
-      <c r="Q60" s="48">
+      <c r="Q60" s="45">
         <f t="shared" si="2"/>
         <v>2044000</v>
       </c>
@@ -6514,8 +7400,9 @@
       <c r="T60" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U60" s="65"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A61" s="12" t="s">
         <v>271</v>
       </c>
@@ -6547,21 +7434,21 @@
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="K61" s="31"/>
-      <c r="L61" s="31"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
       <c r="M61" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N61" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O61" s="47">
+      <c r="O61" s="44">
         <v>1670725</v>
       </c>
-      <c r="P61" s="47">
+      <c r="P61" s="44">
         <v>512000</v>
       </c>
-      <c r="Q61" s="48">
+      <c r="Q61" s="45">
         <f t="shared" si="2"/>
         <v>2182725</v>
       </c>
@@ -6575,8 +7462,9 @@
       <c r="T61" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U61" s="65"/>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A62" s="12" t="s">
         <v>43</v>
       </c>
@@ -6608,21 +7496,21 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="K62" s="31"/>
-      <c r="L62" s="31"/>
+      <c r="K62" s="30"/>
+      <c r="L62" s="30"/>
       <c r="M62" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N62" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="O62" s="48">
+      <c r="O62" s="45">
         <v>200000</v>
       </c>
-      <c r="P62" s="48">
+      <c r="P62" s="45">
         <v>0</v>
       </c>
-      <c r="Q62" s="48">
+      <c r="Q62" s="45">
         <f t="shared" si="2"/>
         <v>200000</v>
       </c>
@@ -6636,8 +7524,9 @@
       <c r="T62" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U62" s="65"/>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A63" s="11" t="s">
         <v>58</v>
       </c>
@@ -6669,21 +7558,21 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="K63" s="31"/>
-      <c r="L63" s="31"/>
+      <c r="K63" s="30"/>
+      <c r="L63" s="30"/>
       <c r="M63" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N63" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="O63" s="48">
+      <c r="O63" s="45">
         <v>200000</v>
       </c>
-      <c r="P63" s="48">
+      <c r="P63" s="45">
         <v>0</v>
       </c>
-      <c r="Q63" s="48">
+      <c r="Q63" s="45">
         <f t="shared" si="2"/>
         <v>200000</v>
       </c>
@@ -6697,8 +7586,9 @@
       <c r="T63" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U63" s="65"/>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A64" s="12" t="s">
         <v>91</v>
       </c>
@@ -6730,21 +7620,21 @@
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="K64" s="31"/>
-      <c r="L64" s="31"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
       <c r="M64" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N64" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="O64" s="47">
+      <c r="O64" s="44">
         <v>0</v>
       </c>
-      <c r="P64" s="47">
+      <c r="P64" s="44">
         <v>170681</v>
       </c>
-      <c r="Q64" s="48">
+      <c r="Q64" s="45">
         <f t="shared" si="2"/>
         <v>170681</v>
       </c>
@@ -6758,8 +7648,9 @@
       <c r="T64" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="65" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U64" s="65"/>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A65" s="12" t="s">
         <v>91</v>
       </c>
@@ -6791,21 +7682,21 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="K65" s="31"/>
-      <c r="L65" s="31"/>
+      <c r="K65" s="30"/>
+      <c r="L65" s="30"/>
       <c r="M65" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N65" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O65" s="47">
+      <c r="O65" s="44">
         <v>0</v>
       </c>
-      <c r="P65" s="47">
+      <c r="P65" s="44">
         <v>546923</v>
       </c>
-      <c r="Q65" s="48">
+      <c r="Q65" s="45">
         <f t="shared" si="2"/>
         <v>546923</v>
       </c>
@@ -6819,8 +7710,9 @@
       <c r="T65" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="66" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U65" s="65"/>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A66" s="12" t="s">
         <v>91</v>
       </c>
@@ -6852,21 +7744,21 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="K66" s="31"/>
-      <c r="L66" s="31"/>
+      <c r="K66" s="30"/>
+      <c r="L66" s="30"/>
       <c r="M66" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N66" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O66" s="48">
+      <c r="O66" s="45">
         <v>0</v>
       </c>
-      <c r="P66" s="47">
+      <c r="P66" s="44">
         <v>92730</v>
       </c>
-      <c r="Q66" s="48">
+      <c r="Q66" s="45">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
@@ -6880,8 +7772,9 @@
       <c r="T66" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="67" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U66" s="65"/>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A67" s="12" t="s">
         <v>282</v>
       </c>
@@ -6913,21 +7806,21 @@
         <f t="shared" ref="J67:J75" si="3">+NETWORKDAYS(H67,I67)</f>
         <v>46</v>
       </c>
-      <c r="K67" s="31"/>
-      <c r="L67" s="31"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
       <c r="M67" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N67" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="O67" s="47">
+      <c r="O67" s="44">
         <v>855000</v>
       </c>
-      <c r="P67" s="47">
+      <c r="P67" s="44">
         <v>196700</v>
       </c>
-      <c r="Q67" s="48">
+      <c r="Q67" s="45">
         <f t="shared" si="2"/>
         <v>1051700</v>
       </c>
@@ -6941,8 +7834,9 @@
       <c r="T67" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="68" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U67" s="65"/>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>285</v>
       </c>
@@ -6974,21 +7868,21 @@
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="K68" s="31"/>
-      <c r="L68" s="31"/>
+      <c r="K68" s="30"/>
+      <c r="L68" s="30"/>
       <c r="M68" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N68" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O68" s="48">
+      <c r="O68" s="45">
         <v>150000</v>
       </c>
-      <c r="P68" s="48">
+      <c r="P68" s="45">
         <v>60000</v>
       </c>
-      <c r="Q68" s="48">
+      <c r="Q68" s="45">
         <f t="shared" si="2"/>
         <v>210000</v>
       </c>
@@ -7002,8 +7896,9 @@
       <c r="T68" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="69" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U68" s="65"/>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A69" s="12" t="s">
         <v>286</v>
       </c>
@@ -7035,21 +7930,21 @@
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="K69" s="31"/>
-      <c r="L69" s="31"/>
+      <c r="K69" s="30"/>
+      <c r="L69" s="30"/>
       <c r="M69" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N69" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O69" s="47">
+      <c r="O69" s="44">
         <v>1200000</v>
       </c>
-      <c r="P69" s="47">
+      <c r="P69" s="44">
         <v>525090</v>
       </c>
-      <c r="Q69" s="48">
+      <c r="Q69" s="45">
         <f t="shared" si="2"/>
         <v>1725090</v>
       </c>
@@ -7063,8 +7958,9 @@
       <c r="T69" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="70" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U69" s="65"/>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A70" s="22" t="s">
         <v>288</v>
       </c>
@@ -7096,21 +7992,21 @@
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="K70" s="31"/>
-      <c r="L70" s="31"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
       <c r="M70" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N70" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O70" s="47">
+      <c r="O70" s="44">
         <v>3026000</v>
       </c>
-      <c r="P70" s="47">
+      <c r="P70" s="44">
         <v>250000</v>
       </c>
-      <c r="Q70" s="48">
+      <c r="Q70" s="45">
         <f t="shared" ref="Q70:Q75" si="5">P70+O70</f>
         <v>3276000</v>
       </c>
@@ -7124,8 +8020,9 @@
       <c r="T70" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="71" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U70" s="65"/>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>291</v>
       </c>
@@ -7157,21 +8054,21 @@
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="K71" s="31"/>
-      <c r="L71" s="31"/>
+      <c r="K71" s="30"/>
+      <c r="L71" s="30"/>
       <c r="M71" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N71" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="O71" s="48">
+      <c r="O71" s="45">
         <v>270000</v>
       </c>
-      <c r="P71" s="48">
+      <c r="P71" s="45">
         <v>111435</v>
       </c>
-      <c r="Q71" s="48">
+      <c r="Q71" s="45">
         <f t="shared" si="5"/>
         <v>381435</v>
       </c>
@@ -7185,8 +8082,9 @@
       <c r="T71" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="72" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U71" s="65"/>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>292</v>
       </c>
@@ -7218,21 +8116,21 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="K72" s="31"/>
-      <c r="L72" s="31"/>
+      <c r="K72" s="30"/>
+      <c r="L72" s="30"/>
       <c r="M72" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N72" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O72" s="48">
+      <c r="O72" s="45">
         <v>150000</v>
       </c>
-      <c r="P72" s="48">
+      <c r="P72" s="45">
         <v>60000</v>
       </c>
-      <c r="Q72" s="48">
+      <c r="Q72" s="45">
         <f t="shared" si="5"/>
         <v>210000</v>
       </c>
@@ -7246,15 +8144,16 @@
       <c r="T72" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="73" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U72" s="65"/>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A73" s="12" t="s">
         <v>91</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C73" s="43">
+      <c r="C73" s="40">
         <v>52573790</v>
       </c>
       <c r="D73" s="12" t="s">
@@ -7279,21 +8178,21 @@
         <f t="shared" si="3"/>
         <v>64</v>
       </c>
-      <c r="K73" s="31"/>
-      <c r="L73" s="31"/>
+      <c r="K73" s="30"/>
+      <c r="L73" s="30"/>
       <c r="M73" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N73" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="O73" s="47">
+      <c r="O73" s="44">
         <v>0</v>
       </c>
-      <c r="P73" s="47">
+      <c r="P73" s="44">
         <v>217691</v>
       </c>
-      <c r="Q73" s="48">
+      <c r="Q73" s="45">
         <f t="shared" si="5"/>
         <v>217691</v>
       </c>
@@ -7307,8 +8206,9 @@
       <c r="T73" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="74" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U73" s="65"/>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A74" s="12" t="s">
         <v>294</v>
       </c>
@@ -7340,21 +8240,21 @@
         <f t="shared" si="3"/>
         <v>43</v>
       </c>
-      <c r="K74" s="31"/>
-      <c r="L74" s="31"/>
+      <c r="K74" s="30"/>
+      <c r="L74" s="30"/>
       <c r="M74" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N74" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O74" s="48">
+      <c r="O74" s="45">
         <v>1793983</v>
       </c>
-      <c r="P74" s="48">
+      <c r="P74" s="45">
         <v>200000</v>
       </c>
-      <c r="Q74" s="48">
+      <c r="Q74" s="45">
         <f t="shared" si="5"/>
         <v>1993983</v>
       </c>
@@ -7368,8 +8268,9 @@
       <c r="T74" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="75" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U74" s="65"/>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A75" s="12" t="s">
         <v>91</v>
       </c>
@@ -7401,21 +8302,21 @@
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
-      <c r="K75" s="31"/>
-      <c r="L75" s="31"/>
+      <c r="K75" s="30"/>
+      <c r="L75" s="30"/>
       <c r="M75" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N75" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O75" s="47">
+      <c r="O75" s="44">
         <v>0</v>
       </c>
-      <c r="P75" s="47">
+      <c r="P75" s="44">
         <v>540923</v>
       </c>
-      <c r="Q75" s="48">
+      <c r="Q75" s="45">
         <f t="shared" si="5"/>
         <v>540923</v>
       </c>
@@ -7429,8 +8330,9 @@
       <c r="T75" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="76" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U75" s="65"/>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A76" s="12" t="s">
         <v>299</v>
       </c>
@@ -7462,21 +8364,21 @@
         <f>+NETWORKDAYS(H76,I76)</f>
         <v>27</v>
       </c>
-      <c r="K76" s="31"/>
-      <c r="L76" s="31"/>
+      <c r="K76" s="30"/>
+      <c r="L76" s="30"/>
       <c r="M76" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N76" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O76" s="47">
+      <c r="O76" s="44">
         <v>500000</v>
       </c>
-      <c r="P76" s="47">
+      <c r="P76" s="44">
         <v>819491</v>
       </c>
-      <c r="Q76" s="48">
+      <c r="Q76" s="45">
         <f>P76+O76</f>
         <v>1319491</v>
       </c>
@@ -7490,8 +8392,9 @@
       <c r="T76" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="77" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U76" s="65"/>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A77" s="12" t="s">
         <v>18</v>
       </c>
@@ -7523,21 +8426,21 @@
         <f t="shared" ref="J77:J140" si="6">+NETWORKDAYS(H77,I77)</f>
         <v>21</v>
       </c>
-      <c r="K77" s="31"/>
-      <c r="L77" s="31"/>
+      <c r="K77" s="30"/>
+      <c r="L77" s="30"/>
       <c r="M77" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N77" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="O77" s="47">
+      <c r="O77" s="44">
         <v>1000000</v>
       </c>
-      <c r="P77" s="47">
+      <c r="P77" s="44">
         <v>300000</v>
       </c>
-      <c r="Q77" s="46">
+      <c r="Q77" s="43">
         <f t="shared" ref="Q77:Q97" si="7">P77+O77</f>
         <v>1300000</v>
       </c>
@@ -7551,8 +8454,9 @@
       <c r="T77" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="78" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U77" s="65"/>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A78" s="12" t="s">
         <v>27</v>
       </c>
@@ -7584,21 +8488,21 @@
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="K78" s="31"/>
-      <c r="L78" s="31"/>
+      <c r="K78" s="30"/>
+      <c r="L78" s="30"/>
       <c r="M78" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N78" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O78" s="47">
+      <c r="O78" s="44">
         <v>500000</v>
       </c>
-      <c r="P78" s="47">
+      <c r="P78" s="44">
         <v>892535</v>
       </c>
-      <c r="Q78" s="46">
+      <c r="Q78" s="43">
         <f t="shared" si="7"/>
         <v>1392535</v>
       </c>
@@ -7612,8 +8516,9 @@
       <c r="T78" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="79" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U78" s="65"/>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
         <v>30</v>
       </c>
@@ -7645,21 +8550,21 @@
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="K79" s="31"/>
-      <c r="L79" s="31"/>
+      <c r="K79" s="30"/>
+      <c r="L79" s="30"/>
       <c r="M79" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N79" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="O79" s="47">
+      <c r="O79" s="44">
         <v>150000</v>
       </c>
-      <c r="P79" s="47">
+      <c r="P79" s="44">
         <v>40000</v>
       </c>
-      <c r="Q79" s="46">
+      <c r="Q79" s="43">
         <f t="shared" si="7"/>
         <v>190000</v>
       </c>
@@ -7673,8 +8578,9 @@
       <c r="T79" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="80" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U79" s="65"/>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A80" s="12" t="s">
         <v>35</v>
       </c>
@@ -7706,21 +8612,21 @@
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="K80" s="31"/>
-      <c r="L80" s="31"/>
+      <c r="K80" s="30"/>
+      <c r="L80" s="30"/>
       <c r="M80" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N80" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O80" s="47">
+      <c r="O80" s="44">
         <v>500000</v>
       </c>
-      <c r="P80" s="47">
+      <c r="P80" s="44">
         <v>391740</v>
       </c>
-      <c r="Q80" s="46">
+      <c r="Q80" s="43">
         <f t="shared" si="7"/>
         <v>891740</v>
       </c>
@@ -7734,8 +8640,9 @@
       <c r="T80" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U80" s="65"/>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A81" s="12" t="s">
         <v>35</v>
       </c>
@@ -7767,21 +8674,21 @@
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="K81" s="31"/>
-      <c r="L81" s="31"/>
+      <c r="K81" s="30"/>
+      <c r="L81" s="30"/>
       <c r="M81" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N81" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O81" s="47">
+      <c r="O81" s="44">
         <v>788712</v>
       </c>
-      <c r="P81" s="47">
+      <c r="P81" s="44">
         <v>500000</v>
       </c>
-      <c r="Q81" s="46">
+      <c r="Q81" s="43">
         <f t="shared" si="7"/>
         <v>1288712</v>
       </c>
@@ -7795,8 +8702,9 @@
       <c r="T81" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="82" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U81" s="65"/>
+    </row>
+    <row r="82" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="12" t="s">
         <v>35</v>
       </c>
@@ -7828,21 +8736,21 @@
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="K82" s="31"/>
-      <c r="L82" s="31"/>
+      <c r="K82" s="30"/>
+      <c r="L82" s="30"/>
       <c r="M82" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N82" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="O82" s="32">
+      <c r="O82" s="31">
         <v>570000</v>
       </c>
-      <c r="P82" s="32">
+      <c r="P82" s="31">
         <v>221635</v>
       </c>
-      <c r="Q82" s="46">
+      <c r="Q82" s="43">
         <f t="shared" si="7"/>
         <v>791635</v>
       </c>
@@ -7856,8 +8764,9 @@
       <c r="T82" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U82" s="65"/>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A83" s="12" t="s">
         <v>43</v>
       </c>
@@ -7889,8 +8798,8 @@
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="K83" s="31"/>
-      <c r="L83" s="31"/>
+      <c r="K83" s="30"/>
+      <c r="L83" s="30"/>
       <c r="M83" s="13" t="s">
         <v>48</v>
       </c>
@@ -7903,7 +8812,7 @@
       <c r="P83" s="15">
         <v>0</v>
       </c>
-      <c r="Q83" s="48">
+      <c r="Q83" s="45">
         <f t="shared" si="7"/>
         <v>200000</v>
       </c>
@@ -7917,8 +8826,9 @@
       <c r="T83" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U83" s="65"/>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A84" s="12" t="s">
         <v>43</v>
       </c>
@@ -7950,8 +8860,8 @@
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="K84" s="31"/>
-      <c r="L84" s="31"/>
+      <c r="K84" s="30"/>
+      <c r="L84" s="30"/>
       <c r="M84" s="13" t="s">
         <v>48</v>
       </c>
@@ -7961,10 +8871,10 @@
       <c r="O84" s="15">
         <v>200000</v>
       </c>
-      <c r="P84" s="47">
+      <c r="P84" s="44">
         <v>0</v>
       </c>
-      <c r="Q84" s="48">
+      <c r="Q84" s="45">
         <f t="shared" si="7"/>
         <v>200000</v>
       </c>
@@ -7978,8 +8888,9 @@
       <c r="T84" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U84" s="65"/>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A85" s="12" t="s">
         <v>52</v>
       </c>
@@ -8011,21 +8922,21 @@
         <f t="shared" si="6"/>
         <v>47</v>
       </c>
-      <c r="K85" s="31"/>
-      <c r="L85" s="31"/>
+      <c r="K85" s="30"/>
+      <c r="L85" s="30"/>
       <c r="M85" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N85" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O85" s="47">
+      <c r="O85" s="44">
         <v>0</v>
       </c>
-      <c r="P85" s="47">
+      <c r="P85" s="44">
         <v>0</v>
       </c>
-      <c r="Q85" s="48">
+      <c r="Q85" s="45">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -8039,8 +8950,9 @@
       <c r="T85" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="86" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U85" s="65"/>
+    </row>
+    <row r="86" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="6" t="s">
         <v>55</v>
       </c>
@@ -8072,21 +8984,21 @@
         <f t="shared" si="6"/>
         <v>39</v>
       </c>
-      <c r="K86" s="31"/>
-      <c r="L86" s="31"/>
+      <c r="K86" s="30"/>
+      <c r="L86" s="30"/>
       <c r="M86" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N86" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="O86" s="47">
+      <c r="O86" s="44">
         <v>360000</v>
       </c>
-      <c r="P86" s="47">
+      <c r="P86" s="44">
         <v>152495</v>
       </c>
-      <c r="Q86" s="46">
+      <c r="Q86" s="43">
         <f t="shared" si="7"/>
         <v>512495</v>
       </c>
@@ -8100,8 +9012,9 @@
       <c r="T86" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U86" s="65"/>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A87" s="22" t="s">
         <v>58</v>
       </c>
@@ -8133,21 +9046,21 @@
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="K87" s="31"/>
-      <c r="L87" s="31"/>
+      <c r="K87" s="30"/>
+      <c r="L87" s="30"/>
       <c r="M87" s="12" t="s">
         <v>24</v>
       </c>
       <c r="N87" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="O87" s="47">
+      <c r="O87" s="44">
         <v>0</v>
       </c>
-      <c r="P87" s="47">
+      <c r="P87" s="44">
         <v>0</v>
       </c>
-      <c r="Q87" s="48">
+      <c r="Q87" s="45">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -8161,8 +9074,9 @@
       <c r="T87" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U87" s="65"/>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A88" s="12" t="s">
         <v>62</v>
       </c>
@@ -8194,21 +9108,21 @@
         <f t="shared" si="6"/>
         <v>79</v>
       </c>
-      <c r="K88" s="31"/>
-      <c r="L88" s="31"/>
+      <c r="K88" s="30"/>
+      <c r="L88" s="30"/>
       <c r="M88" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N88" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="O88" s="47">
+      <c r="O88" s="44">
         <v>600000</v>
       </c>
-      <c r="P88" s="47">
+      <c r="P88" s="44">
         <v>400000</v>
       </c>
-      <c r="Q88" s="48">
+      <c r="Q88" s="45">
         <f t="shared" si="7"/>
         <v>1000000</v>
       </c>
@@ -8222,8 +9136,9 @@
       <c r="T88" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U88" s="65"/>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A89" s="12" t="s">
         <v>65</v>
       </c>
@@ -8255,21 +9170,21 @@
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="K89" s="31"/>
-      <c r="L89" s="31"/>
+      <c r="K89" s="30"/>
+      <c r="L89" s="30"/>
       <c r="M89" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N89" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O89" s="47">
+      <c r="O89" s="44">
         <v>900000</v>
       </c>
-      <c r="P89" s="47">
+      <c r="P89" s="44">
         <v>461679</v>
       </c>
-      <c r="Q89" s="48">
+      <c r="Q89" s="45">
         <f t="shared" si="7"/>
         <v>1361679</v>
       </c>
@@ -8283,8 +9198,9 @@
       <c r="T89" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U89" s="65"/>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A90" s="12" t="s">
         <v>67</v>
       </c>
@@ -8316,21 +9232,21 @@
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="K90" s="31"/>
-      <c r="L90" s="31"/>
+      <c r="K90" s="30"/>
+      <c r="L90" s="30"/>
       <c r="M90" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N90" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O90" s="47">
+      <c r="O90" s="44">
         <v>1000000</v>
       </c>
-      <c r="P90" s="47">
+      <c r="P90" s="44">
         <v>538647</v>
       </c>
-      <c r="Q90" s="48">
+      <c r="Q90" s="45">
         <f t="shared" si="7"/>
         <v>1538647</v>
       </c>
@@ -8344,8 +9260,9 @@
       <c r="T90" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U90" s="65"/>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A91" s="12" t="s">
         <v>70</v>
       </c>
@@ -8377,21 +9294,21 @@
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="K91" s="31"/>
-      <c r="L91" s="31"/>
+      <c r="K91" s="30"/>
+      <c r="L91" s="30"/>
       <c r="M91" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N91" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O91" s="47">
+      <c r="O91" s="44">
         <v>5494650</v>
       </c>
-      <c r="P91" s="47">
+      <c r="P91" s="44">
         <v>1211081</v>
       </c>
-      <c r="Q91" s="48">
+      <c r="Q91" s="45">
         <f t="shared" si="7"/>
         <v>6705731</v>
       </c>
@@ -8405,8 +9322,9 @@
       <c r="T91" s="12" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="92" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U91" s="65"/>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A92" s="12" t="s">
         <v>75</v>
       </c>
@@ -8438,21 +9356,21 @@
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="K92" s="31"/>
-      <c r="L92" s="31"/>
+      <c r="K92" s="30"/>
+      <c r="L92" s="30"/>
       <c r="M92" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N92" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O92" s="47">
+      <c r="O92" s="44">
         <v>1430307</v>
       </c>
-      <c r="P92" s="47">
+      <c r="P92" s="44">
         <v>600349</v>
       </c>
-      <c r="Q92" s="48">
+      <c r="Q92" s="45">
         <f t="shared" si="7"/>
         <v>2030656</v>
       </c>
@@ -8466,9 +9384,10 @@
       <c r="T92" s="12" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="93" spans="1:20" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="30" t="s">
+      <c r="U92" s="65"/>
+    </row>
+    <row r="93" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="29" t="s">
         <v>77</v>
       </c>
       <c r="B93" s="12" t="s">
@@ -8499,21 +9418,21 @@
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="K93" s="31"/>
-      <c r="L93" s="31"/>
+      <c r="K93" s="30"/>
+      <c r="L93" s="30"/>
       <c r="M93" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N93" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="O93" s="47">
+      <c r="O93" s="44">
         <v>500000</v>
       </c>
-      <c r="P93" s="47">
+      <c r="P93" s="44">
         <v>590836</v>
       </c>
-      <c r="Q93" s="48">
+      <c r="Q93" s="45">
         <f t="shared" si="7"/>
         <v>1090836</v>
       </c>
@@ -8527,8 +9446,9 @@
       <c r="T93" s="12" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U93" s="65"/>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A94" s="12" t="s">
         <v>43</v>
       </c>
@@ -8560,21 +9480,21 @@
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="K94" s="31"/>
-      <c r="L94" s="31"/>
+      <c r="K94" s="30"/>
+      <c r="L94" s="30"/>
       <c r="M94" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N94" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O94" s="47">
+      <c r="O94" s="44">
         <v>200000</v>
       </c>
-      <c r="P94" s="47">
+      <c r="P94" s="44">
         <v>0</v>
       </c>
-      <c r="Q94" s="48">
+      <c r="Q94" s="45">
         <f t="shared" si="7"/>
         <v>200000</v>
       </c>
@@ -8588,8 +9508,9 @@
       <c r="T94" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U94" s="65"/>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A95" s="12" t="s">
         <v>81</v>
       </c>
@@ -8621,21 +9542,21 @@
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="K95" s="31"/>
-      <c r="L95" s="31"/>
+      <c r="K95" s="30"/>
+      <c r="L95" s="30"/>
       <c r="M95" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N95" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="O95" s="47">
+      <c r="O95" s="44">
         <v>0</v>
       </c>
-      <c r="P95" s="47">
+      <c r="P95" s="44">
         <v>0</v>
       </c>
-      <c r="Q95" s="48">
+      <c r="Q95" s="45">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -8649,8 +9570,9 @@
       <c r="T95" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="96" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U95" s="65"/>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A96" s="8" t="s">
         <v>85</v>
       </c>
@@ -8675,28 +9597,28 @@
       <c r="H96" s="13">
         <v>46030</v>
       </c>
-      <c r="I96" s="33">
+      <c r="I96" s="32">
         <v>46045</v>
       </c>
       <c r="J96" s="24">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="K96" s="31"/>
-      <c r="L96" s="31"/>
+      <c r="K96" s="30"/>
+      <c r="L96" s="30"/>
       <c r="M96" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N96" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="O96" s="48">
+      <c r="O96" s="45">
         <v>360000</v>
       </c>
-      <c r="P96" s="48">
+      <c r="P96" s="45">
         <v>92495</v>
       </c>
-      <c r="Q96" s="48">
+      <c r="Q96" s="45">
         <f t="shared" si="7"/>
         <v>452495</v>
       </c>
@@ -8710,8 +9632,9 @@
       <c r="T96" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="97" spans="1:20" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U96" s="65"/>
+    </row>
+    <row r="97" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
         <v>86</v>
       </c>
@@ -8733,7 +9656,7 @@
       <c r="G97" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H97" s="33">
+      <c r="H97" s="32">
         <v>46055</v>
       </c>
       <c r="I97" s="13">
@@ -8743,21 +9666,21 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="K97" s="31"/>
-      <c r="L97" s="31"/>
+      <c r="K97" s="30"/>
+      <c r="L97" s="30"/>
       <c r="M97" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N97" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O97" s="47">
+      <c r="O97" s="44">
         <v>1000000</v>
       </c>
-      <c r="P97" s="47">
+      <c r="P97" s="44">
         <v>495000</v>
       </c>
-      <c r="Q97" s="48">
+      <c r="Q97" s="45">
         <f t="shared" si="7"/>
         <v>1495000</v>
       </c>
@@ -8771,8 +9694,9 @@
       <c r="T97" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="98" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U97" s="65"/>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98" s="12" t="s">
         <v>88</v>
       </c>
@@ -8804,21 +9728,21 @@
         <f t="shared" si="6"/>
         <v>144</v>
       </c>
-      <c r="K98" s="31"/>
-      <c r="L98" s="31"/>
+      <c r="K98" s="30"/>
+      <c r="L98" s="30"/>
       <c r="M98" s="13" t="s">
         <v>24</v>
       </c>
       <c r="N98" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O98" s="47">
+      <c r="O98" s="44">
         <v>2245845</v>
       </c>
-      <c r="P98" s="47">
+      <c r="P98" s="44">
         <v>474962</v>
       </c>
-      <c r="Q98" s="48">
+      <c r="Q98" s="45">
         <f>P98+O98</f>
         <v>2720807</v>
       </c>
@@ -8832,8 +9756,9 @@
       <c r="T98" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="99" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U98" s="65"/>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99" s="12" t="s">
         <v>91</v>
       </c>
@@ -8865,21 +9790,21 @@
         <f t="shared" si="6"/>
         <v>76</v>
       </c>
-      <c r="K99" s="31"/>
-      <c r="L99" s="31"/>
+      <c r="K99" s="30"/>
+      <c r="L99" s="30"/>
       <c r="M99" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N99" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="O99" s="48">
+      <c r="O99" s="45">
         <v>0</v>
       </c>
-      <c r="P99" s="48">
+      <c r="P99" s="45">
         <v>725636</v>
       </c>
-      <c r="Q99" s="48">
+      <c r="Q99" s="45">
         <f>P99+O99</f>
         <v>725636</v>
       </c>
@@ -8893,9 +9818,10 @@
       <c r="T99" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="100" spans="1:20" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="30" t="s">
+      <c r="U99" s="65"/>
+    </row>
+    <row r="100" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="29" t="s">
         <v>95</v>
       </c>
       <c r="B100" s="12" t="s">
@@ -8926,21 +9852,21 @@
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="K100" s="31"/>
-      <c r="L100" s="31"/>
+      <c r="K100" s="30"/>
+      <c r="L100" s="30"/>
       <c r="M100" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N100" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O100" s="47">
+      <c r="O100" s="44">
         <v>1200000</v>
       </c>
-      <c r="P100" s="48">
+      <c r="P100" s="45">
         <v>515054</v>
       </c>
-      <c r="Q100" s="48">
+      <c r="Q100" s="45">
         <f>P100+O100</f>
         <v>1715054</v>
       </c>
@@ -8954,8 +9880,9 @@
       <c r="T100" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="101" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U100" s="65"/>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101" s="12" t="s">
         <v>58</v>
       </c>
@@ -8987,21 +9914,21 @@
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="K101" s="31"/>
-      <c r="L101" s="31"/>
+      <c r="K101" s="30"/>
+      <c r="L101" s="30"/>
       <c r="M101" s="12" t="s">
         <v>24</v>
       </c>
       <c r="N101" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O101" s="47">
+      <c r="O101" s="44">
         <v>0</v>
       </c>
-      <c r="P101" s="47">
+      <c r="P101" s="44">
         <v>0</v>
       </c>
-      <c r="Q101" s="48">
+      <c r="Q101" s="45">
         <f>P101+O101</f>
         <v>0</v>
       </c>
@@ -9015,8 +9942,9 @@
       <c r="T101" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="102" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U101" s="65"/>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102" s="22" t="s">
         <v>58</v>
       </c>
@@ -9048,21 +9976,21 @@
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="K102" s="31"/>
-      <c r="L102" s="31"/>
+      <c r="K102" s="30"/>
+      <c r="L102" s="30"/>
       <c r="M102" s="12" t="s">
         <v>24</v>
       </c>
       <c r="N102" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="O102" s="47">
+      <c r="O102" s="44">
         <v>0</v>
       </c>
-      <c r="P102" s="47">
+      <c r="P102" s="44">
         <v>0</v>
       </c>
-      <c r="Q102" s="48">
+      <c r="Q102" s="45">
         <f>P102+O102</f>
         <v>0</v>
       </c>
@@ -9076,8 +10004,9 @@
       <c r="T102" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U102" s="65"/>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A103" s="12" t="s">
         <v>43</v>
       </c>
@@ -9109,21 +10038,21 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K103" s="31"/>
-      <c r="L103" s="31"/>
+      <c r="K103" s="30"/>
+      <c r="L103" s="30"/>
       <c r="M103" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N103" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O103" s="47">
+      <c r="O103" s="44">
         <v>200000</v>
       </c>
-      <c r="P103" s="47">
+      <c r="P103" s="44">
         <v>0</v>
       </c>
-      <c r="Q103" s="48">
+      <c r="Q103" s="45">
         <f t="shared" ref="Q103:Q109" si="9">P103+O103</f>
         <v>200000</v>
       </c>
@@ -9137,8 +10066,9 @@
       <c r="T103" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="104" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U103" s="65"/>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104" s="12" t="s">
         <v>103</v>
       </c>
@@ -9170,21 +10100,21 @@
         <f t="shared" si="6"/>
         <v>123</v>
       </c>
-      <c r="K104" s="31"/>
-      <c r="L104" s="31"/>
+      <c r="K104" s="30"/>
+      <c r="L104" s="30"/>
       <c r="M104" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N104" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O104" s="47">
+      <c r="O104" s="44">
         <v>2148649</v>
       </c>
-      <c r="P104" s="47">
+      <c r="P104" s="44">
         <v>0</v>
       </c>
-      <c r="Q104" s="48">
+      <c r="Q104" s="45">
         <f t="shared" si="9"/>
         <v>2148649</v>
       </c>
@@ -9198,8 +10128,9 @@
       <c r="T104" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U104" s="65"/>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>106</v>
       </c>
@@ -9231,8 +10162,8 @@
         <f t="shared" si="6"/>
         <v>46</v>
       </c>
-      <c r="K105" s="31"/>
-      <c r="L105" s="31"/>
+      <c r="K105" s="30"/>
+      <c r="L105" s="30"/>
       <c r="M105" s="11" t="s">
         <v>48</v>
       </c>
@@ -9245,7 +10176,7 @@
       <c r="P105" s="15">
         <v>0</v>
       </c>
-      <c r="Q105" s="48">
+      <c r="Q105" s="45">
         <f t="shared" si="9"/>
         <v>60000</v>
       </c>
@@ -9259,8 +10190,9 @@
       <c r="T105" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U105" s="65"/>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>81</v>
       </c>
@@ -9292,8 +10224,8 @@
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="K106" s="31"/>
-      <c r="L106" s="31"/>
+      <c r="K106" s="30"/>
+      <c r="L106" s="30"/>
       <c r="M106" s="11" t="s">
         <v>48</v>
       </c>
@@ -9306,7 +10238,7 @@
       <c r="P106" s="15">
         <v>0</v>
       </c>
-      <c r="Q106" s="48">
+      <c r="Q106" s="45">
         <f t="shared" si="9"/>
         <v>60000</v>
       </c>
@@ -9320,8 +10252,9 @@
       <c r="T106" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U106" s="65"/>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>107</v>
       </c>
@@ -9353,8 +10286,8 @@
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="K107" s="31"/>
-      <c r="L107" s="31"/>
+      <c r="K107" s="30"/>
+      <c r="L107" s="30"/>
       <c r="M107" s="5" t="s">
         <v>24</v>
       </c>
@@ -9367,7 +10300,7 @@
       <c r="P107" s="15">
         <v>40000</v>
       </c>
-      <c r="Q107" s="48">
+      <c r="Q107" s="45">
         <f t="shared" si="9"/>
         <v>190000</v>
       </c>
@@ -9381,8 +10314,9 @@
       <c r="T107" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U107" s="65"/>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>108</v>
       </c>
@@ -9414,8 +10348,8 @@
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="K108" s="31"/>
-      <c r="L108" s="31"/>
+      <c r="K108" s="30"/>
+      <c r="L108" s="30"/>
       <c r="M108" s="5" t="s">
         <v>24</v>
       </c>
@@ -9428,7 +10362,7 @@
       <c r="P108" s="15">
         <v>231750</v>
       </c>
-      <c r="Q108" s="48">
+      <c r="Q108" s="45">
         <f t="shared" si="9"/>
         <v>1231750</v>
       </c>
@@ -9442,8 +10376,9 @@
       <c r="T108" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U108" s="65"/>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
         <v>109</v>
       </c>
@@ -9475,8 +10410,8 @@
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="K109" s="31"/>
-      <c r="L109" s="31"/>
+      <c r="K109" s="30"/>
+      <c r="L109" s="30"/>
       <c r="M109" s="5" t="s">
         <v>24</v>
       </c>
@@ -9489,7 +10424,7 @@
       <c r="P109" s="15">
         <v>60000</v>
       </c>
-      <c r="Q109" s="48">
+      <c r="Q109" s="45">
         <f t="shared" si="9"/>
         <v>210000</v>
       </c>
@@ -9503,8 +10438,9 @@
       <c r="T109" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="110" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U109" s="65"/>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A110" s="12" t="s">
         <v>110</v>
       </c>
@@ -9536,21 +10472,21 @@
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
-      <c r="K110" s="31"/>
-      <c r="L110" s="31"/>
+      <c r="K110" s="30"/>
+      <c r="L110" s="30"/>
       <c r="M110" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N110" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O110" s="47">
+      <c r="O110" s="44">
         <v>835588</v>
       </c>
-      <c r="P110" s="47">
+      <c r="P110" s="44">
         <v>200000</v>
       </c>
-      <c r="Q110" s="48">
+      <c r="Q110" s="45">
         <f>P110+O110</f>
         <v>1035588</v>
       </c>
@@ -9564,8 +10500,9 @@
       <c r="T110" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="111" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U110" s="65"/>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A111" s="12" t="s">
         <v>113</v>
       </c>
@@ -9597,25 +10534,25 @@
         <f t="shared" si="6"/>
         <v>45</v>
       </c>
-      <c r="K111" s="34"/>
-      <c r="L111" s="34"/>
-      <c r="M111" s="35" t="s">
+      <c r="K111" s="33"/>
+      <c r="L111" s="33"/>
+      <c r="M111" s="34" t="s">
         <v>24</v>
       </c>
       <c r="N111" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O111" s="47">
+      <c r="O111" s="44">
         <v>1500000</v>
       </c>
-      <c r="P111" s="47">
+      <c r="P111" s="44">
         <v>333527</v>
       </c>
-      <c r="Q111" s="48">
+      <c r="Q111" s="45">
         <f t="shared" ref="Q111:Q118" si="10">P111+O111</f>
         <v>1833527</v>
       </c>
-      <c r="R111" s="36">
+      <c r="R111" s="35">
         <v>46066</v>
       </c>
       <c r="S111" s="24">
@@ -9625,8 +10562,9 @@
       <c r="T111" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="112" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U111" s="65"/>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A112" s="11" t="s">
         <v>116</v>
       </c>
@@ -9658,25 +10596,25 @@
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="K112" s="31"/>
-      <c r="L112" s="31"/>
+      <c r="K112" s="30"/>
+      <c r="L112" s="30"/>
       <c r="M112" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N112" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="O112" s="48">
+      <c r="O112" s="45">
         <v>420853</v>
       </c>
-      <c r="P112" s="48">
+      <c r="P112" s="45">
         <v>467395</v>
       </c>
-      <c r="Q112" s="48">
+      <c r="Q112" s="45">
         <f t="shared" si="10"/>
         <v>888248</v>
       </c>
-      <c r="R112" s="36">
+      <c r="R112" s="35">
         <v>46066</v>
       </c>
       <c r="S112" s="24">
@@ -9686,8 +10624,9 @@
       <c r="T112" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="113" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U112" s="65"/>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A113" s="12" t="s">
         <v>120</v>
       </c>
@@ -9719,21 +10658,21 @@
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
-      <c r="K113" s="31"/>
-      <c r="L113" s="31"/>
+      <c r="K113" s="30"/>
+      <c r="L113" s="30"/>
       <c r="M113" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N113" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O113" s="47">
+      <c r="O113" s="44">
         <v>500000</v>
       </c>
-      <c r="P113" s="47">
+      <c r="P113" s="44">
         <v>998817</v>
       </c>
-      <c r="Q113" s="48">
+      <c r="Q113" s="45">
         <f t="shared" si="10"/>
         <v>1498817</v>
       </c>
@@ -9747,8 +10686,9 @@
       <c r="T113" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="114" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U113" s="65"/>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A114" s="12" t="s">
         <v>123</v>
       </c>
@@ -9780,21 +10720,21 @@
         <f t="shared" si="6"/>
         <v>45</v>
       </c>
-      <c r="K114" s="31"/>
-      <c r="L114" s="31"/>
+      <c r="K114" s="30"/>
+      <c r="L114" s="30"/>
       <c r="M114" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N114" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O114" s="47">
+      <c r="O114" s="44">
         <v>700000</v>
       </c>
-      <c r="P114" s="47">
+      <c r="P114" s="44">
         <v>497454</v>
       </c>
-      <c r="Q114" s="48">
+      <c r="Q114" s="45">
         <f t="shared" si="10"/>
         <v>1197454</v>
       </c>
@@ -9808,8 +10748,9 @@
       <c r="T114" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="115" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U114" s="65"/>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A115" s="12" t="s">
         <v>110</v>
       </c>
@@ -9841,21 +10782,21 @@
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="K115" s="31"/>
-      <c r="L115" s="31"/>
+      <c r="K115" s="30"/>
+      <c r="L115" s="30"/>
       <c r="M115" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N115" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O115" s="47">
+      <c r="O115" s="44">
         <v>638483</v>
       </c>
-      <c r="P115" s="47">
+      <c r="P115" s="44">
         <v>200000</v>
       </c>
-      <c r="Q115" s="48">
+      <c r="Q115" s="45">
         <f t="shared" si="10"/>
         <v>838483</v>
       </c>
@@ -9869,8 +10810,9 @@
       <c r="T115" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="116" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U115" s="65"/>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A116" s="12" t="s">
         <v>127</v>
       </c>
@@ -9902,21 +10844,21 @@
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="K116" s="31"/>
-      <c r="L116" s="31"/>
+      <c r="K116" s="30"/>
+      <c r="L116" s="30"/>
       <c r="M116" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N116" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="O116" s="47">
+      <c r="O116" s="44">
         <v>2000500</v>
       </c>
-      <c r="P116" s="47">
+      <c r="P116" s="44">
         <v>557454</v>
       </c>
-      <c r="Q116" s="48">
+      <c r="Q116" s="45">
         <f t="shared" si="10"/>
         <v>2557954</v>
       </c>
@@ -9930,8 +10872,9 @@
       <c r="T116" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U116" s="65"/>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
         <v>130</v>
       </c>
@@ -9963,21 +10906,21 @@
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="K117" s="31"/>
-      <c r="L117" s="31"/>
+      <c r="K117" s="30"/>
+      <c r="L117" s="30"/>
       <c r="M117" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N117" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O117" s="48">
+      <c r="O117" s="45">
         <v>150000</v>
       </c>
-      <c r="P117" s="48">
+      <c r="P117" s="45">
         <v>60000</v>
       </c>
-      <c r="Q117" s="48">
+      <c r="Q117" s="45">
         <f t="shared" si="10"/>
         <v>210000</v>
       </c>
@@ -9991,8 +10934,9 @@
       <c r="T117" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U117" s="65"/>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
         <v>131</v>
       </c>
@@ -10024,21 +10968,21 @@
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="K118" s="31"/>
-      <c r="L118" s="31"/>
+      <c r="K118" s="30"/>
+      <c r="L118" s="30"/>
       <c r="M118" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N118" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O118" s="48">
+      <c r="O118" s="45">
         <v>1000000</v>
       </c>
-      <c r="P118" s="48">
+      <c r="P118" s="45">
         <v>231750</v>
       </c>
-      <c r="Q118" s="48">
+      <c r="Q118" s="45">
         <f t="shared" si="10"/>
         <v>1231750</v>
       </c>
@@ -10052,8 +10996,9 @@
       <c r="T118" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="119" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U118" s="65"/>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A119" s="12" t="s">
         <v>132</v>
       </c>
@@ -10085,21 +11030,21 @@
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="K119" s="31"/>
-      <c r="L119" s="31"/>
+      <c r="K119" s="30"/>
+      <c r="L119" s="30"/>
       <c r="M119" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N119" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O119" s="48">
+      <c r="O119" s="45">
         <v>1474962</v>
       </c>
-      <c r="P119" s="47">
+      <c r="P119" s="44">
         <v>0</v>
       </c>
-      <c r="Q119" s="48">
+      <c r="Q119" s="45">
         <f>P119+O119</f>
         <v>1474962</v>
       </c>
@@ -10113,8 +11058,9 @@
       <c r="T119" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="120" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U119" s="65"/>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A120" s="12" t="s">
         <v>134</v>
       </c>
@@ -10146,21 +11092,21 @@
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="K120" s="31"/>
-      <c r="L120" s="31"/>
+      <c r="K120" s="30"/>
+      <c r="L120" s="30"/>
       <c r="M120" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N120" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="O120" s="48">
+      <c r="O120" s="45">
         <v>2000000</v>
       </c>
-      <c r="P120" s="48">
+      <c r="P120" s="45">
         <v>0</v>
       </c>
-      <c r="Q120" s="48">
+      <c r="Q120" s="45">
         <f>P120+O120</f>
         <v>2000000</v>
       </c>
@@ -10174,8 +11120,9 @@
       <c r="T120" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="121" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U120" s="65"/>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A121" s="12" t="s">
         <v>134</v>
       </c>
@@ -10207,21 +11154,21 @@
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="K121" s="31"/>
-      <c r="L121" s="31"/>
+      <c r="K121" s="30"/>
+      <c r="L121" s="30"/>
       <c r="M121" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N121" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="O121" s="48">
+      <c r="O121" s="45">
         <v>2000000</v>
       </c>
-      <c r="P121" s="48">
+      <c r="P121" s="45">
         <v>0</v>
       </c>
-      <c r="Q121" s="48">
+      <c r="Q121" s="45">
         <f>P121+O121</f>
         <v>2000000</v>
       </c>
@@ -10235,8 +11182,9 @@
       <c r="T121" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U121" s="65"/>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A122" s="12" t="s">
         <v>140</v>
       </c>
@@ -10268,21 +11216,21 @@
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="K122" s="31"/>
-      <c r="L122" s="31"/>
+      <c r="K122" s="30"/>
+      <c r="L122" s="30"/>
       <c r="M122" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N122" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="O122" s="48">
+      <c r="O122" s="45">
         <v>2000000</v>
       </c>
-      <c r="P122" s="47">
+      <c r="P122" s="44">
         <v>300000</v>
       </c>
-      <c r="Q122" s="48">
+      <c r="Q122" s="45">
         <f>P122+O122</f>
         <v>2300000</v>
       </c>
@@ -10296,8 +11244,9 @@
       <c r="T122" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="123" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U122" s="65"/>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A123" s="12" t="s">
         <v>143</v>
       </c>
@@ -10329,21 +11278,21 @@
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="K123" s="31"/>
-      <c r="L123" s="31"/>
+      <c r="K123" s="30"/>
+      <c r="L123" s="30"/>
       <c r="M123" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N123" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O123" s="47">
+      <c r="O123" s="44">
         <v>1000000</v>
       </c>
-      <c r="P123" s="47">
+      <c r="P123" s="44">
         <v>693500</v>
       </c>
-      <c r="Q123" s="48">
+      <c r="Q123" s="45">
         <f t="shared" ref="Q123:Q148" si="11">P123+O123</f>
         <v>1693500</v>
       </c>
@@ -10357,8 +11306,9 @@
       <c r="T123" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="124" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U123" s="65"/>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A124" s="12" t="s">
         <v>145</v>
       </c>
@@ -10390,21 +11340,21 @@
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="K124" s="31"/>
-      <c r="L124" s="31"/>
+      <c r="K124" s="30"/>
+      <c r="L124" s="30"/>
       <c r="M124" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N124" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O124" s="48">
+      <c r="O124" s="45">
         <v>0</v>
       </c>
-      <c r="P124" s="48">
+      <c r="P124" s="45">
         <v>0</v>
       </c>
-      <c r="Q124" s="48">
+      <c r="Q124" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -10418,8 +11368,9 @@
       <c r="T124" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="125" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U124" s="65"/>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A125" s="12" t="s">
         <v>149</v>
       </c>
@@ -10451,21 +11402,21 @@
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="K125" s="31"/>
-      <c r="L125" s="31"/>
+      <c r="K125" s="30"/>
+      <c r="L125" s="30"/>
       <c r="M125" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N125" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="O125" s="47">
+      <c r="O125" s="44">
         <v>150000</v>
       </c>
-      <c r="P125" s="47">
+      <c r="P125" s="44">
         <v>443127</v>
       </c>
-      <c r="Q125" s="48">
+      <c r="Q125" s="45">
         <f t="shared" si="11"/>
         <v>593127</v>
       </c>
@@ -10479,8 +11430,9 @@
       <c r="T125" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="126" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U125" s="65"/>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A126" s="12" t="s">
         <v>143</v>
       </c>
@@ -10512,21 +11464,21 @@
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="K126" s="31"/>
-      <c r="L126" s="31"/>
+      <c r="K126" s="30"/>
+      <c r="L126" s="30"/>
       <c r="M126" s="11" t="s">
         <v>24</v>
       </c>
       <c r="N126" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O126" s="47">
+      <c r="O126" s="44">
         <v>1987902</v>
       </c>
-      <c r="P126" s="47">
+      <c r="P126" s="44">
         <v>270000</v>
       </c>
-      <c r="Q126" s="48">
+      <c r="Q126" s="45">
         <f t="shared" si="11"/>
         <v>2257902</v>
       </c>
@@ -10540,8 +11492,9 @@
       <c r="T126" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="127" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U126" s="65"/>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A127" s="12" t="s">
         <v>301</v>
       </c>
@@ -10585,13 +11538,13 @@
       <c r="N127" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O127" s="48">
+      <c r="O127" s="45">
         <v>1100000</v>
       </c>
-      <c r="P127" s="47">
+      <c r="P127" s="44">
         <v>474962</v>
       </c>
-      <c r="Q127" s="48">
+      <c r="Q127" s="45">
         <f t="shared" si="11"/>
         <v>1574962</v>
       </c>
@@ -10605,8 +11558,9 @@
       <c r="T127" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="128" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U127" s="65"/>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A128" s="12" t="s">
         <v>305</v>
       </c>
@@ -10650,13 +11604,13 @@
       <c r="N128" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O128" s="47">
+      <c r="O128" s="44">
         <v>1100000</v>
       </c>
-      <c r="P128" s="47">
+      <c r="P128" s="44">
         <v>474962</v>
       </c>
-      <c r="Q128" s="48">
+      <c r="Q128" s="45">
         <f t="shared" si="11"/>
         <v>1574962</v>
       </c>
@@ -10670,8 +11624,9 @@
       <c r="T128" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="129" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U128" s="65"/>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A129" s="12" t="s">
         <v>145</v>
       </c>
@@ -10715,13 +11670,13 @@
       <c r="N129" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O129" s="47">
+      <c r="O129" s="44">
         <v>0</v>
       </c>
-      <c r="P129" s="47">
+      <c r="P129" s="44">
         <v>0</v>
       </c>
-      <c r="Q129" s="48">
+      <c r="Q129" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -10735,8 +11690,9 @@
       <c r="T129" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="130" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U129" s="65"/>
+    </row>
+    <row r="130" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
         <v>308</v>
       </c>
@@ -10780,13 +11736,13 @@
       <c r="N130" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="O130" s="47">
+      <c r="O130" s="44">
         <v>270000</v>
       </c>
-      <c r="P130" s="47">
+      <c r="P130" s="44">
         <v>71435</v>
       </c>
-      <c r="Q130" s="48">
+      <c r="Q130" s="45">
         <f t="shared" si="11"/>
         <v>341435</v>
       </c>
@@ -10800,8 +11756,9 @@
       <c r="T130" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="131" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U130" s="65"/>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A131" s="9" t="s">
         <v>309</v>
       </c>
@@ -10845,13 +11802,13 @@
       <c r="N131" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="O131" s="47">
+      <c r="O131" s="44">
         <v>360000</v>
       </c>
-      <c r="P131" s="47">
+      <c r="P131" s="44">
         <v>92495</v>
       </c>
-      <c r="Q131" s="48">
+      <c r="Q131" s="45">
         <f t="shared" si="11"/>
         <v>452495</v>
       </c>
@@ -10865,8 +11822,9 @@
       <c r="T131" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="132" spans="1:20" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U131" s="65"/>
+    </row>
+    <row r="132" spans="1:21" s="26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A132" s="22" t="s">
         <v>311</v>
       </c>
@@ -10910,13 +11868,13 @@
       <c r="N132" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O132" s="47">
+      <c r="O132" s="44">
         <v>500000</v>
       </c>
-      <c r="P132" s="47">
+      <c r="P132" s="44">
         <v>1963000</v>
       </c>
-      <c r="Q132" s="48">
+      <c r="Q132" s="45">
         <f t="shared" si="11"/>
         <v>2463000</v>
       </c>
@@ -10930,8 +11888,9 @@
       <c r="T132" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="133" spans="1:20" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U132" s="66"/>
+    </row>
+    <row r="133" spans="1:21" s="26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A133" s="12" t="s">
         <v>311</v>
       </c>
@@ -10975,13 +11934,13 @@
       <c r="N133" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O133" s="47">
+      <c r="O133" s="44">
         <v>500000</v>
       </c>
-      <c r="P133" s="47">
+      <c r="P133" s="44">
         <v>350000</v>
       </c>
-      <c r="Q133" s="48">
+      <c r="Q133" s="45">
         <f t="shared" si="11"/>
         <v>850000</v>
       </c>
@@ -10995,8 +11954,9 @@
       <c r="T133" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="134" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U133" s="66"/>
+    </row>
+    <row r="134" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A134" s="12" t="s">
         <v>317</v>
       </c>
@@ -11040,13 +12000,13 @@
       <c r="N134" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O134" s="47">
+      <c r="O134" s="44">
         <v>2000000</v>
       </c>
-      <c r="P134" s="47">
+      <c r="P134" s="44">
         <v>3000000</v>
       </c>
-      <c r="Q134" s="48">
+      <c r="Q134" s="45">
         <f t="shared" si="11"/>
         <v>5000000</v>
       </c>
@@ -11060,8 +12020,9 @@
       <c r="T134" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="135" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U134" s="65"/>
+    </row>
+    <row r="135" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A135" s="9" t="s">
         <v>320</v>
       </c>
@@ -11105,13 +12066,13 @@
       <c r="N135" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O135" s="48">
+      <c r="O135" s="45">
         <v>400000</v>
       </c>
-      <c r="P135" s="48">
+      <c r="P135" s="45">
         <v>0</v>
       </c>
-      <c r="Q135" s="48">
+      <c r="Q135" s="45">
         <f t="shared" si="11"/>
         <v>400000</v>
       </c>
@@ -11125,8 +12086,9 @@
       <c r="T135" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="136" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U135" s="65"/>
+    </row>
+    <row r="136" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A136" s="9" t="s">
         <v>321</v>
       </c>
@@ -11170,13 +12132,13 @@
       <c r="N136" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O136" s="48">
+      <c r="O136" s="45">
         <v>150000</v>
       </c>
-      <c r="P136" s="48">
+      <c r="P136" s="45">
         <v>0</v>
       </c>
-      <c r="Q136" s="48">
+      <c r="Q136" s="45">
         <f t="shared" si="11"/>
         <v>150000</v>
       </c>
@@ -11190,8 +12152,9 @@
       <c r="T136" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="137" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U136" s="65"/>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A137" s="9" t="s">
         <v>321</v>
       </c>
@@ -11235,13 +12198,13 @@
       <c r="N137" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O137" s="48">
+      <c r="O137" s="45">
         <v>1000000</v>
       </c>
-      <c r="P137" s="48">
+      <c r="P137" s="45">
         <v>0</v>
       </c>
-      <c r="Q137" s="48">
+      <c r="Q137" s="45">
         <f t="shared" si="11"/>
         <v>1000000</v>
       </c>
@@ -11255,8 +12218,9 @@
       <c r="T137" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="138" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U137" s="65"/>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A138" s="9" t="s">
         <v>322</v>
       </c>
@@ -11300,13 +12264,13 @@
       <c r="N138" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O138" s="48">
+      <c r="O138" s="45">
         <v>1000000</v>
       </c>
-      <c r="P138" s="48">
+      <c r="P138" s="45">
         <v>0</v>
       </c>
-      <c r="Q138" s="48">
+      <c r="Q138" s="45">
         <f t="shared" si="11"/>
         <v>1000000</v>
       </c>
@@ -11320,8 +12284,9 @@
       <c r="T138" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="139" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U138" s="65"/>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A139" s="9" t="s">
         <v>323</v>
       </c>
@@ -11365,13 +12330,13 @@
       <c r="N139" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O139" s="48">
+      <c r="O139" s="45">
         <v>108000</v>
       </c>
-      <c r="P139" s="48">
+      <c r="P139" s="45">
         <v>0</v>
       </c>
-      <c r="Q139" s="48">
+      <c r="Q139" s="45">
         <f t="shared" si="11"/>
         <v>108000</v>
       </c>
@@ -11385,8 +12350,9 @@
       <c r="T139" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="140" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U139" s="65"/>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
         <v>324</v>
       </c>
@@ -11430,13 +12396,13 @@
       <c r="N140" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="O140" s="48">
+      <c r="O140" s="45">
         <v>270000</v>
       </c>
-      <c r="P140" s="48">
+      <c r="P140" s="45">
         <v>71435</v>
       </c>
-      <c r="Q140" s="48">
+      <c r="Q140" s="45">
         <f t="shared" si="11"/>
         <v>341435</v>
       </c>
@@ -11450,8 +12416,9 @@
       <c r="T140" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="141" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U140" s="65"/>
+    </row>
+    <row r="141" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
         <v>326</v>
       </c>
@@ -11480,7 +12447,7 @@
         <v>46079</v>
       </c>
       <c r="J141" s="24">
-        <f t="shared" ref="J141:J195" si="12">+NETWORKDAYS(H141,I141)</f>
+        <f t="shared" ref="J141:J204" si="12">+NETWORKDAYS(H141,I141)</f>
         <v>261</v>
       </c>
       <c r="K141" s="25" t="s">
@@ -11495,13 +12462,13 @@
       <c r="N141" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O141" s="48">
+      <c r="O141" s="45">
         <v>3000000</v>
       </c>
-      <c r="P141" s="48">
+      <c r="P141" s="45">
         <v>139050</v>
       </c>
-      <c r="Q141" s="48">
+      <c r="Q141" s="45">
         <f t="shared" si="11"/>
         <v>3139050</v>
       </c>
@@ -11509,14 +12476,15 @@
         <v>46079</v>
       </c>
       <c r="S141" s="24">
-        <f t="shared" ref="S141:S195" si="13">NETWORKDAYS(H141,R141)</f>
+        <f t="shared" ref="S141:S204" si="13">NETWORKDAYS(H141,R141)</f>
         <v>261</v>
       </c>
       <c r="T141" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="142" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U141" s="65"/>
+    </row>
+    <row r="142" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A142" s="12" t="s">
         <v>328</v>
       </c>
@@ -11560,13 +12528,13 @@
       <c r="N142" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O142" s="47">
+      <c r="O142" s="44">
         <v>350000</v>
       </c>
-      <c r="P142" s="47">
+      <c r="P142" s="44">
         <v>197989</v>
       </c>
-      <c r="Q142" s="48">
+      <c r="Q142" s="45">
         <f t="shared" si="11"/>
         <v>547989</v>
       </c>
@@ -11580,8 +12548,9 @@
       <c r="T142" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="143" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U142" s="65"/>
+    </row>
+    <row r="143" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A143" s="12" t="s">
         <v>331</v>
       </c>
@@ -11625,13 +12594,13 @@
       <c r="N143" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="O143" s="48">
+      <c r="O143" s="45">
         <v>842820</v>
       </c>
-      <c r="P143" s="48">
+      <c r="P143" s="45">
         <v>0</v>
       </c>
-      <c r="Q143" s="48">
+      <c r="Q143" s="45">
         <f t="shared" si="11"/>
         <v>842820</v>
       </c>
@@ -11645,8 +12614,9 @@
       <c r="T143" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="144" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U143" s="65"/>
+    </row>
+    <row r="144" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A144" s="12" t="s">
         <v>333</v>
       </c>
@@ -11690,13 +12660,13 @@
       <c r="N144" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="O144" s="47">
+      <c r="O144" s="44">
         <v>3986938</v>
       </c>
-      <c r="P144" s="47">
+      <c r="P144" s="44">
         <v>400908</v>
       </c>
-      <c r="Q144" s="48">
+      <c r="Q144" s="45">
         <f t="shared" si="11"/>
         <v>4387846</v>
       </c>
@@ -11710,8 +12680,9 @@
       <c r="T144" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="145" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U144" s="65"/>
+    </row>
+    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A145" s="12" t="s">
         <v>335</v>
       </c>
@@ -11755,13 +12726,13 @@
       <c r="N145" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="O145" s="47">
+      <c r="O145" s="44">
         <v>250000</v>
       </c>
-      <c r="P145" s="47">
+      <c r="P145" s="44">
         <v>370000</v>
       </c>
-      <c r="Q145" s="48">
+      <c r="Q145" s="45">
         <f t="shared" si="11"/>
         <v>620000</v>
       </c>
@@ -11775,8 +12746,9 @@
       <c r="T145" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="146" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U145" s="65"/>
+    </row>
+    <row r="146" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A146" s="12" t="s">
         <v>140</v>
       </c>
@@ -11820,13 +12792,13 @@
       <c r="N146" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O146" s="47">
+      <c r="O146" s="44">
         <v>1000000</v>
       </c>
-      <c r="P146" s="47">
+      <c r="P146" s="44">
         <v>965500</v>
       </c>
-      <c r="Q146" s="48">
+      <c r="Q146" s="45">
         <f t="shared" si="11"/>
         <v>1965500</v>
       </c>
@@ -11840,8 +12812,9 @@
       <c r="T146" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="147" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U146" s="65"/>
+    </row>
+    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A147" s="12" t="s">
         <v>140</v>
       </c>
@@ -11885,13 +12858,13 @@
       <c r="N147" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="O147" s="47">
+      <c r="O147" s="44">
         <v>2000000</v>
       </c>
-      <c r="P147" s="47">
+      <c r="P147" s="44">
         <v>300000</v>
       </c>
-      <c r="Q147" s="48">
+      <c r="Q147" s="45">
         <f t="shared" si="11"/>
         <v>2300000</v>
       </c>
@@ -11905,8 +12878,9 @@
       <c r="T147" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="148" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+      <c r="U147" s="65"/>
+    </row>
+    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A148" s="22" t="s">
         <v>58</v>
       </c>
@@ -11950,13 +12924,13 @@
       <c r="N148" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O148" s="47">
+      <c r="O148" s="44">
         <v>0</v>
       </c>
-      <c r="P148" s="47">
+      <c r="P148" s="44">
         <v>0</v>
       </c>
-      <c r="Q148" s="48">
+      <c r="Q148" s="45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -11970,671 +12944,702 @@
       <c r="T148" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U148" s="65"/>
+    </row>
+    <row r="149" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A149" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="B149" s="44" t="s">
+      <c r="B149" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="C149" s="44">
+      <c r="C149" s="41">
         <v>57664431</v>
       </c>
-      <c r="D149" s="44" t="s">
+      <c r="D149" s="41" t="s">
         <v>345</v>
       </c>
-      <c r="E149" s="44" t="s">
+      <c r="E149" s="41" t="s">
         <v>346</v>
       </c>
-      <c r="F149" s="44" t="s">
+      <c r="F149" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="G149" s="44" t="s">
+      <c r="G149" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H149" s="45">
+      <c r="H149" s="42">
         <v>46055</v>
       </c>
-      <c r="I149" s="45">
+      <c r="I149" s="42">
         <v>46083</v>
       </c>
       <c r="J149" s="24">
         <f t="shared" si="12"/>
         <v>21</v>
       </c>
-      <c r="K149" s="44" t="s">
+      <c r="K149" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="L149" s="44" t="s">
+      <c r="L149" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="M149" s="44" t="s">
+      <c r="M149" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="N149" s="44" t="s">
+      <c r="N149" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="O149" s="49">
+      <c r="O149" s="46">
         <v>2500000</v>
       </c>
-      <c r="P149" s="49">
+      <c r="P149" s="46">
         <v>2325347</v>
       </c>
-      <c r="Q149" s="47">
+      <c r="Q149" s="44">
         <f>P149+O149</f>
         <v>4825347</v>
       </c>
-      <c r="R149" s="45">
+      <c r="R149" s="42">
         <v>46084</v>
       </c>
       <c r="S149" s="24">
         <f t="shared" si="13"/>
         <v>22</v>
       </c>
-      <c r="T149" s="44" t="s">
+      <c r="T149" s="41" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U149" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A150" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="B150" s="44" t="s">
+      <c r="B150" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C150" s="44">
+      <c r="C150" s="41">
         <v>57417024</v>
       </c>
-      <c r="D150" s="44" t="s">
+      <c r="D150" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="E150" s="44">
+      <c r="E150" s="41">
         <v>2721710775</v>
       </c>
-      <c r="F150" s="44" t="s">
+      <c r="F150" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="G150" s="44" t="s">
+      <c r="G150" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H150" s="45">
+      <c r="H150" s="42">
         <v>46050</v>
       </c>
-      <c r="I150" s="45">
+      <c r="I150" s="42">
         <v>46083</v>
       </c>
       <c r="J150" s="24">
         <f t="shared" si="12"/>
         <v>24</v>
       </c>
-      <c r="K150" s="44" t="s">
+      <c r="K150" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="L150" s="44" t="s">
+      <c r="L150" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="M150" s="44" t="s">
+      <c r="M150" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="N150" s="44" t="s">
+      <c r="N150" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="O150" s="49">
+      <c r="O150" s="46">
         <v>150000</v>
       </c>
-      <c r="P150" s="49">
+      <c r="P150" s="46">
         <v>40000</v>
       </c>
-      <c r="Q150" s="47">
+      <c r="Q150" s="44">
         <f t="shared" ref="Q150:Q189" si="14">P150+O150</f>
         <v>190000</v>
       </c>
-      <c r="R150" s="45">
+      <c r="R150" s="42">
         <v>46084</v>
       </c>
       <c r="S150" s="24">
         <f t="shared" si="13"/>
         <v>25</v>
       </c>
-      <c r="T150" s="44" t="s">
+      <c r="T150" s="41" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U150" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A151" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="B151" s="44" t="s">
+      <c r="B151" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C151" s="44">
+      <c r="C151" s="41">
         <v>57847231</v>
       </c>
-      <c r="D151" s="44" t="s">
+      <c r="D151" s="41" t="s">
         <v>325</v>
       </c>
-      <c r="E151" s="44" t="s">
+      <c r="E151" s="41" t="s">
         <v>349</v>
       </c>
-      <c r="F151" s="44" t="s">
+      <c r="F151" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="G151" s="44" t="s">
+      <c r="G151" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H151" s="45">
+      <c r="H151" s="42">
         <v>46058</v>
       </c>
-      <c r="I151" s="45">
+      <c r="I151" s="42">
         <v>46078</v>
       </c>
       <c r="J151" s="24">
         <f t="shared" si="12"/>
         <v>15</v>
       </c>
-      <c r="K151" s="44" t="s">
+      <c r="K151" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="L151" s="44" t="s">
+      <c r="L151" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="M151" s="44" t="s">
+      <c r="M151" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="N151" s="44" t="s">
+      <c r="N151" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="O151" s="49">
+      <c r="O151" s="46">
         <v>485500</v>
       </c>
-      <c r="P151" s="49">
+      <c r="P151" s="46">
         <v>251105</v>
       </c>
-      <c r="Q151" s="47">
+      <c r="Q151" s="44">
         <f t="shared" si="14"/>
         <v>736605</v>
       </c>
-      <c r="R151" s="45">
+      <c r="R151" s="42">
         <v>46085</v>
       </c>
       <c r="S151" s="24">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
-      <c r="T151" s="44" t="s">
+      <c r="T151" s="41" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U151" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A152" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="B152" s="44" t="s">
+      <c r="B152" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C152" s="44">
+      <c r="C152" s="41">
         <v>24190516</v>
       </c>
-      <c r="D152" s="44" t="s">
+      <c r="D152" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="E152" s="44" t="s">
+      <c r="E152" s="41" t="s">
         <v>352</v>
       </c>
-      <c r="F152" s="44" t="s">
+      <c r="F152" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="G152" s="44" t="s">
+      <c r="G152" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H152" s="45">
+      <c r="H152" s="42">
         <v>45261</v>
       </c>
-      <c r="I152" s="45">
+      <c r="I152" s="42">
         <v>46079</v>
       </c>
       <c r="J152" s="24">
         <f t="shared" si="12"/>
         <v>585</v>
       </c>
-      <c r="K152" s="44" t="s">
+      <c r="K152" s="41" t="s">
         <v>353</v>
       </c>
-      <c r="L152" s="44" t="s">
+      <c r="L152" s="41" t="s">
         <v>327</v>
       </c>
-      <c r="M152" s="44" t="s">
+      <c r="M152" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="N152" s="44" t="s">
+      <c r="N152" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="O152" s="49">
+      <c r="O152" s="46">
         <v>8018371</v>
       </c>
-      <c r="P152" s="49">
+      <c r="P152" s="46">
         <v>800000</v>
       </c>
-      <c r="Q152" s="47">
+      <c r="Q152" s="44">
         <f t="shared" si="14"/>
         <v>8818371</v>
       </c>
-      <c r="R152" s="45">
+      <c r="R152" s="42">
         <v>46085</v>
       </c>
       <c r="S152" s="24">
         <f t="shared" si="13"/>
         <v>589</v>
       </c>
-      <c r="T152" s="44" t="s">
+      <c r="T152" s="41" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U152" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A153" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="B153" s="44" t="s">
+      <c r="B153" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="44">
+      <c r="C153" s="41">
         <v>58227435</v>
       </c>
-      <c r="D153" s="44" t="s">
+      <c r="D153" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="E153" s="44" t="s">
+      <c r="E153" s="41" t="s">
         <v>355</v>
       </c>
-      <c r="F153" s="44" t="s">
+      <c r="F153" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="G153" s="44" t="s">
+      <c r="G153" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H153" s="45">
+      <c r="H153" s="42">
         <v>46069</v>
       </c>
-      <c r="I153" s="45">
+      <c r="I153" s="42">
         <v>46083</v>
       </c>
       <c r="J153" s="24">
         <f t="shared" si="12"/>
         <v>11</v>
       </c>
-      <c r="K153" s="44" t="s">
+      <c r="K153" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="L153" s="44" t="s">
+      <c r="L153" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="M153" s="44" t="s">
+      <c r="M153" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="N153" s="44" t="s">
+      <c r="N153" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="O153" s="49">
+      <c r="O153" s="46">
         <v>0</v>
       </c>
-      <c r="P153" s="49">
+      <c r="P153" s="46">
         <v>430500</v>
       </c>
-      <c r="Q153" s="47">
+      <c r="Q153" s="44">
         <f t="shared" si="14"/>
         <v>430500</v>
       </c>
-      <c r="R153" s="45">
+      <c r="R153" s="42">
         <v>46085</v>
       </c>
       <c r="S153" s="24">
         <f t="shared" si="13"/>
         <v>13</v>
       </c>
-      <c r="T153" s="44" t="s">
+      <c r="T153" s="41" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U153" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="154" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A154" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B154" s="44" t="s">
+      <c r="B154" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="C154" s="44">
+      <c r="C154" s="41">
         <v>54990268</v>
       </c>
-      <c r="D154" s="44" t="s">
+      <c r="D154" s="41" t="s">
         <v>356</v>
       </c>
-      <c r="E154" s="44" t="s">
+      <c r="E154" s="41" t="s">
         <v>357</v>
       </c>
-      <c r="F154" s="44" t="s">
+      <c r="F154" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="G154" s="44" t="s">
+      <c r="G154" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H154" s="45">
+      <c r="H154" s="42">
         <v>46002</v>
       </c>
-      <c r="I154" s="45">
+      <c r="I154" s="42">
         <v>46084</v>
       </c>
       <c r="J154" s="24">
         <f t="shared" si="12"/>
         <v>59</v>
       </c>
-      <c r="K154" s="44" t="s">
+      <c r="K154" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="L154" s="44" t="s">
+      <c r="L154" s="41" t="s">
         <v>327</v>
       </c>
-      <c r="M154" s="44" t="s">
+      <c r="M154" s="41" t="s">
         <v>358</v>
       </c>
-      <c r="N154" s="44" t="s">
+      <c r="N154" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="O154" s="49">
+      <c r="O154" s="46">
         <v>0</v>
       </c>
-      <c r="P154" s="49">
+      <c r="P154" s="46">
         <v>0</v>
       </c>
-      <c r="Q154" s="47">
+      <c r="Q154" s="44">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="R154" s="45">
+      <c r="R154" s="42">
         <v>46085</v>
       </c>
       <c r="S154" s="24">
         <f t="shared" si="13"/>
         <v>60</v>
       </c>
-      <c r="T154" s="44" t="s">
+      <c r="T154" s="41" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U154" s="48" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="155" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A155" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="B155" s="44" t="s">
+      <c r="B155" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C155" s="44">
+      <c r="C155" s="41">
         <v>57782724</v>
       </c>
-      <c r="D155" s="44" t="s">
+      <c r="D155" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="E155" s="44">
+      <c r="E155" s="41">
         <v>2722229745</v>
       </c>
-      <c r="F155" s="44" t="s">
+      <c r="F155" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="G155" s="44" t="s">
+      <c r="G155" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H155" s="45">
+      <c r="H155" s="42">
         <v>46057</v>
       </c>
-      <c r="I155" s="45">
+      <c r="I155" s="42">
         <v>46073</v>
       </c>
       <c r="J155" s="24">
         <f t="shared" si="12"/>
         <v>13</v>
       </c>
-      <c r="K155" s="44" t="s">
+      <c r="K155" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="L155" s="44" t="s">
+      <c r="L155" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="M155" s="44" t="s">
+      <c r="M155" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="N155" s="44" t="s">
+      <c r="N155" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="O155" s="49">
+      <c r="O155" s="46">
         <v>150000</v>
       </c>
-      <c r="P155" s="49">
+      <c r="P155" s="46">
         <v>60000</v>
       </c>
-      <c r="Q155" s="47">
+      <c r="Q155" s="44">
         <f t="shared" si="14"/>
         <v>210000</v>
       </c>
-      <c r="R155" s="45">
+      <c r="R155" s="42">
         <v>46085</v>
       </c>
       <c r="S155" s="24">
         <f t="shared" si="13"/>
         <v>21</v>
       </c>
-      <c r="T155" s="44" t="s">
+      <c r="T155" s="41" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U155" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A156" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="B156" s="44" t="s">
+      <c r="B156" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C156" s="44">
+      <c r="C156" s="41">
         <v>58585753</v>
       </c>
-      <c r="D156" s="44" t="s">
+      <c r="D156" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="E156" s="44">
+      <c r="E156" s="41">
         <v>2722229950</v>
       </c>
-      <c r="F156" s="44" t="s">
+      <c r="F156" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="G156" s="44" t="s">
+      <c r="G156" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H156" s="45">
+      <c r="H156" s="42">
         <v>46072</v>
       </c>
-      <c r="I156" s="45">
+      <c r="I156" s="42">
         <v>46084</v>
       </c>
       <c r="J156" s="24">
         <f t="shared" si="12"/>
         <v>9</v>
       </c>
-      <c r="K156" s="44" t="s">
+      <c r="K156" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="L156" s="44" t="s">
+      <c r="L156" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="M156" s="44" t="s">
+      <c r="M156" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="N156" s="44" t="s">
+      <c r="N156" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="O156" s="49">
+      <c r="O156" s="46">
         <v>150000</v>
       </c>
-      <c r="P156" s="49">
+      <c r="P156" s="46">
         <v>60000</v>
       </c>
-      <c r="Q156" s="47">
+      <c r="Q156" s="44">
         <f t="shared" si="14"/>
         <v>210000</v>
       </c>
-      <c r="R156" s="45">
+      <c r="R156" s="42">
         <v>46085</v>
       </c>
       <c r="S156" s="24">
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
-      <c r="T156" s="44" t="s">
+      <c r="T156" s="41" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A157" s="44" t="s">
+      <c r="U156" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="157" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A157" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="B157" s="44" t="s">
+      <c r="B157" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="C157" s="44">
+      <c r="C157" s="41">
         <v>55490966</v>
       </c>
-      <c r="D157" s="44" t="s">
+      <c r="D157" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="E157" s="44" t="s">
+      <c r="E157" s="41" t="s">
         <v>361</v>
       </c>
-      <c r="F157" s="44" t="s">
+      <c r="F157" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="G157" s="44" t="s">
+      <c r="G157" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="H157" s="45">
+      <c r="H157" s="42">
         <v>46010</v>
       </c>
-      <c r="I157" s="45">
+      <c r="I157" s="42">
         <v>46084</v>
       </c>
       <c r="J157" s="24">
         <f t="shared" si="12"/>
         <v>53</v>
       </c>
-      <c r="K157" s="50" t="s">
+      <c r="K157" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="L157" s="51" t="s">
+      <c r="L157" s="48" t="s">
         <v>327</v>
       </c>
-      <c r="M157" s="51" t="s">
+      <c r="M157" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="N157" s="44" t="s">
+      <c r="N157" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="O157" s="52">
+      <c r="O157" s="49">
         <v>0</v>
       </c>
-      <c r="P157" s="52">
+      <c r="P157" s="49">
         <v>0</v>
       </c>
-      <c r="Q157" s="47">
+      <c r="Q157" s="44">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="R157" s="53">
+      <c r="R157" s="50">
         <v>46086</v>
       </c>
       <c r="S157" s="24">
         <f t="shared" si="13"/>
         <v>55</v>
       </c>
-      <c r="T157" s="44" t="s">
+      <c r="T157" s="41" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A158" s="44" t="s">
+      <c r="U157" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="158" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A158" s="41" t="s">
         <v>362</v>
       </c>
-      <c r="B158" s="44" t="s">
+      <c r="B158" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="C158" s="44">
+      <c r="C158" s="41">
         <v>58853643</v>
       </c>
-      <c r="D158" s="44" t="s">
+      <c r="D158" s="41" t="s">
         <v>363</v>
       </c>
-      <c r="E158" s="44" t="s">
+      <c r="E158" s="41" t="s">
         <v>364</v>
       </c>
-      <c r="F158" s="44" t="s">
+      <c r="F158" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="G158" s="44" t="s">
+      <c r="G158" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="H158" s="54">
+      <c r="H158" s="51">
         <v>46079</v>
       </c>
-      <c r="I158" s="54">
+      <c r="I158" s="51">
         <v>46085</v>
       </c>
       <c r="J158" s="24">
         <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="K158" s="50" t="s">
+      <c r="K158" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="L158" s="51" t="s">
+      <c r="L158" s="48" t="s">
         <v>304</v>
       </c>
-      <c r="M158" s="51" t="s">
+      <c r="M158" s="48" t="s">
         <v>358</v>
       </c>
-      <c r="N158" s="44" t="s">
+      <c r="N158" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="O158" s="52">
+      <c r="O158" s="49">
         <v>0</v>
       </c>
-      <c r="P158" s="52">
+      <c r="P158" s="49">
         <v>0</v>
       </c>
-      <c r="Q158" s="47">
+      <c r="Q158" s="44">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="R158" s="53">
+      <c r="R158" s="50">
         <v>46086</v>
       </c>
       <c r="S158" s="24">
         <f t="shared" si="13"/>
         <v>6</v>
       </c>
-      <c r="T158" s="44" t="s">
+      <c r="T158" s="41" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U158" s="48" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="159" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C159" s="55">
+      <c r="C159" s="52">
         <v>54479742</v>
       </c>
       <c r="D159" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="E159" s="55" t="s">
+      <c r="E159" s="52" t="s">
         <v>366</v>
       </c>
       <c r="F159" s="11" t="s">
@@ -12643,23 +13648,23 @@
       <c r="G159" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H159" s="56">
+      <c r="H159" s="53">
         <v>45993</v>
       </c>
-      <c r="I159" s="56">
+      <c r="I159" s="53">
         <v>46084</v>
       </c>
       <c r="J159" s="24">
         <f t="shared" si="12"/>
         <v>66</v>
       </c>
-      <c r="K159" s="50" t="s">
+      <c r="K159" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="L159" s="51" t="s">
+      <c r="L159" s="48" t="s">
         <v>304</v>
       </c>
-      <c r="M159" s="51" t="s">
+      <c r="M159" s="48" t="s">
         <v>48</v>
       </c>
       <c r="N159" s="11" t="s">
@@ -12671,87 +13676,93 @@
       <c r="P159" s="5">
         <v>0</v>
       </c>
-      <c r="Q159" s="47">
+      <c r="Q159" s="44">
         <f t="shared" si="14"/>
         <v>6064001</v>
       </c>
-      <c r="R159" s="53">
+      <c r="R159" s="50">
         <v>46086</v>
       </c>
       <c r="S159" s="24">
         <f t="shared" si="13"/>
         <v>68</v>
       </c>
-      <c r="T159" s="44" t="s">
+      <c r="T159" s="41" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U159" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="160" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A160" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="B160" s="44" t="s">
+      <c r="B160" s="41" t="s">
         <v>87</v>
       </c>
       <c r="C160" s="5">
         <v>58932414</v>
       </c>
-      <c r="D160" s="44" t="s">
+      <c r="D160" s="41" t="s">
         <v>368</v>
       </c>
       <c r="E160" s="5">
         <v>2722229955</v>
       </c>
-      <c r="F160" s="44" t="s">
+      <c r="F160" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="G160" s="44" t="s">
+      <c r="G160" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H160" s="45">
+      <c r="H160" s="42">
         <v>46078</v>
       </c>
-      <c r="I160" s="45">
+      <c r="I160" s="42">
         <v>46086</v>
       </c>
       <c r="J160" s="24">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="K160" s="50" t="s">
+      <c r="K160" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="L160" s="51" t="s">
+      <c r="L160" s="48" t="s">
         <v>304</v>
       </c>
-      <c r="M160" s="51" t="s">
+      <c r="M160" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="N160" s="44" t="s">
+      <c r="N160" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="O160" s="52">
+      <c r="O160" s="49">
         <v>1000000</v>
       </c>
-      <c r="P160" s="52">
+      <c r="P160" s="49">
         <v>495000</v>
       </c>
-      <c r="Q160" s="47">
+      <c r="Q160" s="44">
         <f t="shared" si="14"/>
         <v>1495000</v>
       </c>
-      <c r="R160" s="53">
+      <c r="R160" s="50">
         <v>46086</v>
       </c>
       <c r="S160" s="24">
         <f t="shared" si="13"/>
         <v>7</v>
       </c>
-      <c r="T160" s="44" t="s">
+      <c r="T160" s="41" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U160" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="161" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A161" s="12" t="s">
         <v>369</v>
       </c>
@@ -12801,7 +13812,7 @@
       <c r="P161" s="19">
         <v>187644</v>
       </c>
-      <c r="Q161" s="47">
+      <c r="Q161" s="44">
         <f t="shared" si="14"/>
         <v>687644</v>
       </c>
@@ -12815,8 +13826,11 @@
       <c r="T161" s="11" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U161" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="162" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A162" s="12" t="s">
         <v>371</v>
       </c>
@@ -12866,7 +13880,7 @@
       <c r="P162" s="19">
         <v>667054</v>
       </c>
-      <c r="Q162" s="47">
+      <c r="Q162" s="44">
         <f t="shared" si="14"/>
         <v>3288468</v>
       </c>
@@ -12880,8 +13894,11 @@
       <c r="T162" s="11" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U162" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="163" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A163" s="12" t="s">
         <v>43</v>
       </c>
@@ -12931,7 +13948,7 @@
       <c r="P163" s="19">
         <v>380000</v>
       </c>
-      <c r="Q163" s="47">
+      <c r="Q163" s="44">
         <f t="shared" si="14"/>
         <v>2380000</v>
       </c>
@@ -12945,8 +13962,11 @@
       <c r="T163" s="11" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U163" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="164" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A164" s="12" t="s">
         <v>374</v>
       </c>
@@ -12996,7 +14016,7 @@
       <c r="P164" s="19">
         <v>1700000</v>
       </c>
-      <c r="Q164" s="47">
+      <c r="Q164" s="44">
         <f t="shared" si="14"/>
         <v>2700000</v>
       </c>
@@ -13010,8 +14030,11 @@
       <c r="T164" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U164" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="165" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A165" s="12" t="s">
         <v>374</v>
       </c>
@@ -13061,7 +14084,7 @@
       <c r="P165" s="19">
         <v>1700000</v>
       </c>
-      <c r="Q165" s="47">
+      <c r="Q165" s="44">
         <f t="shared" si="14"/>
         <v>2700000</v>
       </c>
@@ -13075,8 +14098,11 @@
       <c r="T165" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U165" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="166" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A166" s="12" t="s">
         <v>374</v>
       </c>
@@ -13126,7 +14152,7 @@
       <c r="P166" s="19">
         <v>1700000</v>
       </c>
-      <c r="Q166" s="47">
+      <c r="Q166" s="44">
         <f t="shared" si="14"/>
         <v>1950000</v>
       </c>
@@ -13140,8 +14166,11 @@
       <c r="T166" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U166" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="167" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A167" s="12" t="s">
         <v>374</v>
       </c>
@@ -13191,7 +14220,7 @@
       <c r="P167" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q167" s="47">
+      <c r="Q167" s="44">
         <f t="shared" si="14"/>
         <v>1800000</v>
       </c>
@@ -13205,8 +14234,11 @@
       <c r="T167" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U167" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="168" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A168" s="12" t="s">
         <v>374</v>
       </c>
@@ -13256,7 +14288,7 @@
       <c r="P168" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q168" s="47">
+      <c r="Q168" s="44">
         <f t="shared" si="14"/>
         <v>1800000</v>
       </c>
@@ -13270,8 +14302,11 @@
       <c r="T168" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U168" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="169" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A169" s="12" t="s">
         <v>374</v>
       </c>
@@ -13321,7 +14356,7 @@
       <c r="P169" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q169" s="47">
+      <c r="Q169" s="44">
         <f t="shared" si="14"/>
         <v>1550000</v>
       </c>
@@ -13335,8 +14370,11 @@
       <c r="T169" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U169" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="170" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A170" s="12" t="s">
         <v>374</v>
       </c>
@@ -13386,7 +14424,7 @@
       <c r="P170" s="12">
         <v>1300000</v>
       </c>
-      <c r="Q170" s="47">
+      <c r="Q170" s="44">
         <f t="shared" si="14"/>
         <v>1800000</v>
       </c>
@@ -13400,8 +14438,11 @@
       <c r="T170" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U170" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="171" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A171" s="12" t="s">
         <v>374</v>
       </c>
@@ -13451,7 +14492,7 @@
       <c r="P171" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q171" s="47">
+      <c r="Q171" s="44">
         <f t="shared" si="14"/>
         <v>1800000</v>
       </c>
@@ -13465,15 +14506,18 @@
       <c r="T171" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U171" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="172" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A172" s="12" t="s">
         <v>374</v>
       </c>
       <c r="B172" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C172" s="57">
+      <c r="C172" s="54">
         <v>55105863</v>
       </c>
       <c r="D172" s="12" t="s">
@@ -13488,7 +14532,7 @@
       <c r="G172" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H172" s="39">
+      <c r="H172" s="36">
         <v>46004</v>
       </c>
       <c r="I172" s="14">
@@ -13516,7 +14560,7 @@
       <c r="P172" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q172" s="47">
+      <c r="Q172" s="44">
         <f t="shared" si="14"/>
         <v>2550000</v>
       </c>
@@ -13530,8 +14574,11 @@
       <c r="T172" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U172" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="173" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A173" s="12" t="s">
         <v>374</v>
       </c>
@@ -13581,7 +14628,7 @@
       <c r="P173" s="19">
         <v>1700000</v>
       </c>
-      <c r="Q173" s="47">
+      <c r="Q173" s="44">
         <f t="shared" si="14"/>
         <v>2700000</v>
       </c>
@@ -13595,8 +14642,11 @@
       <c r="T173" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U173" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="174" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A174" s="12" t="s">
         <v>374</v>
       </c>
@@ -13646,7 +14696,7 @@
       <c r="P174" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q174" s="47">
+      <c r="Q174" s="44">
         <f t="shared" si="14"/>
         <v>1550000</v>
       </c>
@@ -13660,8 +14710,11 @@
       <c r="T174" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U174" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="175" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A175" s="12" t="s">
         <v>374</v>
       </c>
@@ -13711,7 +14764,7 @@
       <c r="P175" s="19">
         <v>1700000</v>
       </c>
-      <c r="Q175" s="47">
+      <c r="Q175" s="44">
         <f t="shared" si="14"/>
         <v>2200000</v>
       </c>
@@ -13725,8 +14778,11 @@
       <c r="T175" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U175" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="176" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A176" s="12" t="s">
         <v>374</v>
       </c>
@@ -13776,7 +14832,7 @@
       <c r="P176" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q176" s="47">
+      <c r="Q176" s="44">
         <f t="shared" si="14"/>
         <v>2300000</v>
       </c>
@@ -13790,8 +14846,11 @@
       <c r="T176" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U176" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="177" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A177" s="12" t="s">
         <v>374</v>
       </c>
@@ -13841,7 +14900,7 @@
       <c r="P177" s="19">
         <v>1700000</v>
       </c>
-      <c r="Q177" s="47">
+      <c r="Q177" s="44">
         <f t="shared" si="14"/>
         <v>2200000</v>
       </c>
@@ -13855,8 +14914,11 @@
       <c r="T177" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U177" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="178" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A178" s="12" t="s">
         <v>374</v>
       </c>
@@ -13906,7 +14968,7 @@
       <c r="P178" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q178" s="47">
+      <c r="Q178" s="44">
         <f t="shared" si="14"/>
         <v>2800000</v>
       </c>
@@ -13920,8 +14982,11 @@
       <c r="T178" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U178" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="179" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A179" s="12" t="s">
         <v>374</v>
       </c>
@@ -13971,7 +15036,7 @@
       <c r="P179" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q179" s="47">
+      <c r="Q179" s="44">
         <f t="shared" si="14"/>
         <v>2550000</v>
       </c>
@@ -13985,8 +15050,11 @@
       <c r="T179" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U179" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="180" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A180" s="12" t="s">
         <v>408</v>
       </c>
@@ -14036,7 +15104,7 @@
       <c r="P180" s="19">
         <v>2207940</v>
       </c>
-      <c r="Q180" s="47">
+      <c r="Q180" s="44">
         <f t="shared" si="14"/>
         <v>3596622</v>
       </c>
@@ -14050,8 +15118,11 @@
       <c r="T180" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U180" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="181" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A181" s="22" t="s">
         <v>411</v>
       </c>
@@ -14101,7 +15172,7 @@
       <c r="P181" s="19">
         <v>0</v>
       </c>
-      <c r="Q181" s="47">
+      <c r="Q181" s="44">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -14115,8 +15186,11 @@
       <c r="T181" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U181" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="182" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A182" s="12" t="s">
         <v>414</v>
       </c>
@@ -14166,7 +15240,7 @@
       <c r="P182" s="19">
         <v>590836</v>
       </c>
-      <c r="Q182" s="47">
+      <c r="Q182" s="44">
         <f t="shared" si="14"/>
         <v>1590836</v>
       </c>
@@ -14180,8 +15254,11 @@
       <c r="T182" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U182" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="183" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A183" s="12" t="s">
         <v>416</v>
       </c>
@@ -14231,7 +15308,7 @@
       <c r="P183" s="19">
         <v>0</v>
       </c>
-      <c r="Q183" s="47">
+      <c r="Q183" s="44">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -14245,8 +15322,11 @@
       <c r="T183" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U183" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="184" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A184" s="12" t="s">
         <v>416</v>
       </c>
@@ -14296,7 +15376,7 @@
       <c r="P184" s="19">
         <v>0</v>
       </c>
-      <c r="Q184" s="47">
+      <c r="Q184" s="44">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -14310,8 +15390,11 @@
       <c r="T184" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U184" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="185" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A185" s="5" t="s">
         <v>419</v>
       </c>
@@ -14355,13 +15438,13 @@
       <c r="N185" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O185" s="59">
+      <c r="O185" s="56">
         <v>150000</v>
       </c>
-      <c r="P185" s="59">
+      <c r="P185" s="56">
         <v>60000</v>
       </c>
-      <c r="Q185" s="47">
+      <c r="Q185" s="44">
         <f t="shared" si="14"/>
         <v>210000</v>
       </c>
@@ -14375,8 +15458,11 @@
       <c r="T185" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U185" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="186" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A186" s="9" t="s">
         <v>421</v>
       </c>
@@ -14420,13 +15506,13 @@
       <c r="N186" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O186" s="59">
+      <c r="O186" s="56">
         <v>150000</v>
       </c>
-      <c r="P186" s="59">
+      <c r="P186" s="56">
         <v>60000</v>
       </c>
-      <c r="Q186" s="47">
+      <c r="Q186" s="44">
         <f t="shared" si="14"/>
         <v>210000</v>
       </c>
@@ -14440,8 +15526,11 @@
       <c r="T186" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U186" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="187" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A187" s="12" t="s">
         <v>422</v>
       </c>
@@ -14491,7 +15580,7 @@
       <c r="P187" s="19">
         <v>0</v>
       </c>
-      <c r="Q187" s="47">
+      <c r="Q187" s="44">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -14505,8 +15594,11 @@
       <c r="T187" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U187" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="188" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A188" s="12" t="s">
         <v>422</v>
       </c>
@@ -14556,7 +15648,7 @@
       <c r="P188" s="19">
         <v>0</v>
       </c>
-      <c r="Q188" s="47">
+      <c r="Q188" s="44">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -14570,8 +15662,11 @@
       <c r="T188" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U188" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="189" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A189" s="12" t="s">
         <v>428</v>
       </c>
@@ -14603,10 +15698,10 @@
         <f t="shared" si="12"/>
         <v>49</v>
       </c>
-      <c r="K189" s="58" t="s">
+      <c r="K189" s="55" t="s">
         <v>303</v>
       </c>
-      <c r="L189" s="35" t="s">
+      <c r="L189" s="34" t="s">
         <v>304</v>
       </c>
       <c r="M189" s="12" t="s">
@@ -14615,13 +15710,13 @@
       <c r="N189" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="O189" s="60">
+      <c r="O189" s="57">
         <v>0</v>
       </c>
-      <c r="P189" s="60">
+      <c r="P189" s="57">
         <v>0</v>
       </c>
-      <c r="Q189" s="47">
+      <c r="Q189" s="44">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -14635,58 +15730,61 @@
       <c r="T189" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U189" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="190" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A190" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="B190" s="44" t="s">
+      <c r="B190" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="C190" s="44">
+      <c r="C190" s="41">
         <v>50732535</v>
       </c>
-      <c r="D190" s="44" t="s">
+      <c r="D190" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="E190" s="44" t="s">
+      <c r="E190" s="41" t="s">
         <v>431</v>
       </c>
-      <c r="F190" s="44" t="s">
+      <c r="F190" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="G190" s="44" t="s">
+      <c r="G190" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="H190" s="45">
+      <c r="H190" s="42">
         <v>45919</v>
       </c>
-      <c r="I190" s="45">
+      <c r="I190" s="42">
         <v>46056</v>
       </c>
       <c r="J190" s="24">
         <f t="shared" si="12"/>
         <v>98</v>
       </c>
-      <c r="K190" s="44" t="s">
+      <c r="K190" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="L190" s="44" t="s">
+      <c r="L190" s="41" t="s">
         <v>327</v>
       </c>
-      <c r="M190" s="44" t="s">
+      <c r="M190" s="41" t="s">
         <v>358</v>
       </c>
-      <c r="N190" s="44" t="s">
+      <c r="N190" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="O190" s="44">
+      <c r="O190" s="41">
         <v>0</v>
       </c>
-      <c r="P190" s="44">
+      <c r="P190" s="41">
         <v>0</v>
       </c>
-      <c r="Q190" s="52">
+      <c r="Q190" s="49">
         <v>0</v>
       </c>
       <c r="R190" s="14">
@@ -14699,58 +15797,61 @@
       <c r="T190" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U190" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="191" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A191" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="B191" s="44" t="s">
+      <c r="B191" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C191" s="44">
+      <c r="C191" s="41">
         <v>58205267</v>
       </c>
-      <c r="D191" s="44" t="s">
+      <c r="D191" s="41" t="s">
         <v>433</v>
       </c>
-      <c r="E191" s="44" t="s">
+      <c r="E191" s="41" t="s">
         <v>434</v>
       </c>
-      <c r="F191" s="44" t="s">
+      <c r="F191" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="G191" s="44" t="s">
+      <c r="G191" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H191" s="45">
+      <c r="H191" s="42">
         <v>46067</v>
       </c>
-      <c r="I191" s="45">
+      <c r="I191" s="42">
         <v>46087</v>
       </c>
       <c r="J191" s="24">
         <f t="shared" si="12"/>
         <v>15</v>
       </c>
-      <c r="K191" s="44" t="s">
+      <c r="K191" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="L191" s="44" t="s">
+      <c r="L191" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="M191" s="44" t="s">
+      <c r="M191" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="N191" s="44" t="s">
+      <c r="N191" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="O191" s="44">
+      <c r="O191" s="41">
         <v>0</v>
       </c>
-      <c r="P191" s="44">
+      <c r="P191" s="41">
         <v>430500</v>
       </c>
-      <c r="Q191" s="52">
+      <c r="Q191" s="49">
         <v>430500</v>
       </c>
       <c r="R191" s="14">
@@ -14763,58 +15864,61 @@
       <c r="T191" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U191" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="192" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A192" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="B192" s="44" t="s">
+      <c r="B192" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C192" s="44">
+      <c r="C192" s="41">
         <v>58173859</v>
       </c>
-      <c r="D192" s="44" t="s">
+      <c r="D192" s="41" t="s">
         <v>435</v>
       </c>
-      <c r="E192" s="44" t="s">
+      <c r="E192" s="41" t="s">
         <v>436</v>
       </c>
-      <c r="F192" s="44" t="s">
+      <c r="F192" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="G192" s="44" t="s">
+      <c r="G192" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H192" s="45">
+      <c r="H192" s="42">
         <v>46066</v>
       </c>
-      <c r="I192" s="45">
+      <c r="I192" s="42">
         <v>46087</v>
       </c>
       <c r="J192" s="24">
         <f t="shared" si="12"/>
         <v>16</v>
       </c>
-      <c r="K192" s="44" t="s">
+      <c r="K192" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="L192" s="44" t="s">
+      <c r="L192" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="M192" s="44" t="s">
+      <c r="M192" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="N192" s="44" t="s">
+      <c r="N192" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="O192" s="44">
+      <c r="O192" s="41">
         <v>0</v>
       </c>
-      <c r="P192" s="44">
+      <c r="P192" s="41">
         <v>430500</v>
       </c>
-      <c r="Q192" s="52">
+      <c r="Q192" s="49">
         <v>430500</v>
       </c>
       <c r="R192" s="14">
@@ -14827,58 +15931,61 @@
       <c r="T192" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U192" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="193" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A193" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="B193" s="44" t="s">
+      <c r="B193" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C193" s="44">
+      <c r="C193" s="41">
         <v>58650763</v>
       </c>
-      <c r="D193" s="44" t="s">
+      <c r="D193" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="E193" s="44">
+      <c r="E193" s="41">
         <v>2722417296</v>
       </c>
-      <c r="F193" s="44" t="s">
+      <c r="F193" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="G193" s="44" t="s">
+      <c r="G193" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H193" s="45">
+      <c r="H193" s="42">
         <v>46073</v>
       </c>
-      <c r="I193" s="45">
+      <c r="I193" s="42">
         <v>46092</v>
       </c>
       <c r="J193" s="24">
         <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="K193" s="44" t="s">
+      <c r="K193" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="L193" s="44" t="s">
+      <c r="L193" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="M193" s="44" t="s">
+      <c r="M193" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="N193" s="44" t="s">
+      <c r="N193" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="O193" s="44">
+      <c r="O193" s="41">
         <v>150000</v>
       </c>
-      <c r="P193" s="44">
+      <c r="P193" s="41">
         <v>40000</v>
       </c>
-      <c r="Q193" s="52">
+      <c r="Q193" s="49">
         <v>190000</v>
       </c>
       <c r="R193" s="14">
@@ -14891,58 +15998,61 @@
       <c r="T193" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U193" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="194" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A194" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="B194" s="44" t="s">
+      <c r="B194" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C194" s="44">
+      <c r="C194" s="41">
         <v>58276534</v>
       </c>
-      <c r="D194" s="44" t="s">
+      <c r="D194" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="E194" s="44">
+      <c r="E194" s="41">
         <v>2723489370</v>
       </c>
-      <c r="F194" s="44" t="s">
+      <c r="F194" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="G194" s="44" t="s">
+      <c r="G194" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H194" s="45">
+      <c r="H194" s="42">
         <v>46066</v>
       </c>
-      <c r="I194" s="45">
+      <c r="I194" s="42">
         <v>46092</v>
       </c>
       <c r="J194" s="24">
         <f t="shared" si="12"/>
         <v>19</v>
       </c>
-      <c r="K194" s="44" t="s">
+      <c r="K194" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="L194" s="44" t="s">
+      <c r="L194" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="M194" s="44" t="s">
+      <c r="M194" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="N194" s="44" t="s">
+      <c r="N194" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="O194" s="44">
+      <c r="O194" s="41">
         <v>150000</v>
       </c>
-      <c r="P194" s="44">
+      <c r="P194" s="41">
         <v>40000</v>
       </c>
-      <c r="Q194" s="52">
+      <c r="Q194" s="49">
         <v>190000</v>
       </c>
       <c r="R194" s="14">
@@ -14955,58 +16065,61 @@
       <c r="T194" s="11" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U194" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="195" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A195" s="12" t="s">
         <v>439</v>
       </c>
-      <c r="B195" s="44" t="s">
+      <c r="B195" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="C195" s="44">
+      <c r="C195" s="41">
         <v>58853633</v>
       </c>
-      <c r="D195" s="44" t="s">
+      <c r="D195" s="41" t="s">
         <v>440</v>
       </c>
-      <c r="E195" s="44" t="s">
+      <c r="E195" s="41" t="s">
         <v>441</v>
       </c>
-      <c r="F195" s="44" t="s">
+      <c r="F195" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="G195" s="44" t="s">
+      <c r="G195" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="H195" s="45">
+      <c r="H195" s="42">
         <v>46079</v>
       </c>
-      <c r="I195" s="45">
+      <c r="I195" s="42">
         <v>46092</v>
       </c>
       <c r="J195" s="24">
         <f t="shared" si="12"/>
         <v>10</v>
       </c>
-      <c r="K195" s="44" t="s">
+      <c r="K195" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="L195" s="44" t="s">
+      <c r="L195" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="M195" s="44" t="s">
+      <c r="M195" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="N195" s="44" t="s">
+      <c r="N195" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="O195" s="44">
+      <c r="O195" s="41">
         <v>0</v>
       </c>
-      <c r="P195" s="44">
+      <c r="P195" s="41">
         <v>0</v>
       </c>
-      <c r="Q195" s="52">
+      <c r="Q195" s="49">
         <v>0</v>
       </c>
       <c r="R195" s="14">
@@ -15019,204 +16132,872 @@
       <c r="T195" s="11" t="s">
         <v>377</v>
       </c>
+      <c r="U195" s="41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="196" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A196" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="B196" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C196" s="12">
+        <v>54466861</v>
+      </c>
+      <c r="D196" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="E196" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="F196" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G196" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H196" s="14">
+        <v>45993</v>
+      </c>
+      <c r="I196" s="14">
+        <v>46079</v>
+      </c>
+      <c r="J196" s="24">
+        <f t="shared" si="12"/>
+        <v>63</v>
+      </c>
+      <c r="K196" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="L196" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="M196" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="N196" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="O196" s="41">
+        <v>2932569</v>
+      </c>
+      <c r="P196" s="41">
+        <v>709840</v>
+      </c>
+      <c r="Q196" s="49">
+        <v>3642409</v>
+      </c>
+      <c r="R196" s="42">
+        <v>46093</v>
+      </c>
+      <c r="S196" s="24">
+        <f t="shared" si="13"/>
+        <v>73</v>
+      </c>
+      <c r="T196" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="U196" s="48" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="197" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A197" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="B197" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C197" s="12">
+        <v>58163711</v>
+      </c>
+      <c r="D197" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E197" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="F197" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G197" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H197" s="14">
+        <v>46066</v>
+      </c>
+      <c r="I197" s="14">
+        <v>46092</v>
+      </c>
+      <c r="J197" s="24">
+        <f t="shared" si="12"/>
+        <v>19</v>
+      </c>
+      <c r="K197" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="L197" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="M197" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="N197" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="O197" s="41">
+        <v>0</v>
+      </c>
+      <c r="P197" s="41">
+        <v>430500</v>
+      </c>
+      <c r="Q197" s="49">
+        <v>430500</v>
+      </c>
+      <c r="R197" s="42">
+        <v>46093</v>
+      </c>
+      <c r="S197" s="24">
+        <f t="shared" si="13"/>
+        <v>20</v>
+      </c>
+      <c r="T197" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="U197" s="48" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="198" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A198" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B198" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C198" s="12">
+        <v>56603158</v>
+      </c>
+      <c r="D198" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="E198" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="F198" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G198" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H198" s="14">
+        <v>46035</v>
+      </c>
+      <c r="I198" s="14">
+        <v>46092</v>
+      </c>
+      <c r="J198" s="24">
+        <f t="shared" si="12"/>
+        <v>42</v>
+      </c>
+      <c r="K198" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="L198" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="M198" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="N198" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="O198" s="41">
+        <v>2000000</v>
+      </c>
+      <c r="P198" s="41">
+        <v>300000</v>
+      </c>
+      <c r="Q198" s="49">
+        <v>2300000</v>
+      </c>
+      <c r="R198" s="42">
+        <v>46093</v>
+      </c>
+      <c r="S198" s="24">
+        <f t="shared" si="13"/>
+        <v>43</v>
+      </c>
+      <c r="T198" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="U198" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="199" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A199" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="B199" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C199" s="12">
+        <v>52799560</v>
+      </c>
+      <c r="D199" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E199" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="F199" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G199" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H199" s="14">
+        <v>45960</v>
+      </c>
+      <c r="I199" s="14">
+        <v>45979</v>
+      </c>
+      <c r="J199" s="24">
+        <f t="shared" si="12"/>
+        <v>14</v>
+      </c>
+      <c r="K199" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="L199" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="M199" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="N199" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="O199" s="41">
+        <v>0</v>
+      </c>
+      <c r="P199" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q199" s="49">
+        <v>0</v>
+      </c>
+      <c r="R199" s="42">
+        <v>46093</v>
+      </c>
+      <c r="S199" s="24">
+        <f t="shared" si="13"/>
+        <v>96</v>
+      </c>
+      <c r="T199" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="U199" s="48" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="200" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A200" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="B200" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C200" s="12">
+        <v>52799573</v>
+      </c>
+      <c r="D200" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E200" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="F200" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G200" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H200" s="14">
+        <v>45960</v>
+      </c>
+      <c r="I200" s="14">
+        <v>45979</v>
+      </c>
+      <c r="J200" s="24">
+        <f t="shared" si="12"/>
+        <v>14</v>
+      </c>
+      <c r="K200" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="L200" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="M200" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="N200" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="O200" s="41">
+        <v>0</v>
+      </c>
+      <c r="P200" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q200" s="49">
+        <v>0</v>
+      </c>
+      <c r="R200" s="42">
+        <v>46093</v>
+      </c>
+      <c r="S200" s="24">
+        <f t="shared" si="13"/>
+        <v>96</v>
+      </c>
+      <c r="T200" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="U200" s="48" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="201" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A201" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B201" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C201" s="12">
+        <v>56620712</v>
+      </c>
+      <c r="D201" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E201" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="F201" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G201" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H201" s="14">
+        <v>46035</v>
+      </c>
+      <c r="I201" s="14">
+        <v>46090</v>
+      </c>
+      <c r="J201" s="24">
+        <f t="shared" si="12"/>
+        <v>40</v>
+      </c>
+      <c r="K201" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="L201" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="M201" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="N201" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="O201" s="41">
+        <v>2000000</v>
+      </c>
+      <c r="P201" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q201" s="49">
+        <v>2000000</v>
+      </c>
+      <c r="R201" s="42">
+        <v>46092</v>
+      </c>
+      <c r="S201" s="24">
+        <f t="shared" si="13"/>
+        <v>42</v>
+      </c>
+      <c r="T201" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="U201" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="202" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A202" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="B202" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C202" s="12">
+        <v>52808194</v>
+      </c>
+      <c r="D202" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="E202" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="F202" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G202" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H202" s="14">
+        <v>45960</v>
+      </c>
+      <c r="I202" s="14">
+        <v>46036</v>
+      </c>
+      <c r="J202" s="24">
+        <f t="shared" si="12"/>
+        <v>55</v>
+      </c>
+      <c r="K202" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="L202" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="M202" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="N202" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="O202" s="41">
+        <v>0</v>
+      </c>
+      <c r="P202" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q202" s="49">
+        <v>0</v>
+      </c>
+      <c r="R202" s="42">
+        <v>46093</v>
+      </c>
+      <c r="S202" s="24">
+        <f t="shared" si="13"/>
+        <v>96</v>
+      </c>
+      <c r="T202" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="U202" s="48" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="203" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A203" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B203" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C203" s="12">
+        <v>58164578</v>
+      </c>
+      <c r="D203" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E203" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="F203" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G203" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H203" s="14">
+        <v>46064</v>
+      </c>
+      <c r="I203" s="14">
+        <v>46093</v>
+      </c>
+      <c r="J203" s="24">
+        <f t="shared" si="12"/>
+        <v>22</v>
+      </c>
+      <c r="K203" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="L203" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="M203" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="N203" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="O203" s="41">
+        <v>200000</v>
+      </c>
+      <c r="P203" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q203" s="49">
+        <v>200000</v>
+      </c>
+      <c r="R203" s="42">
+        <v>46094</v>
+      </c>
+      <c r="S203" s="24">
+        <f t="shared" si="13"/>
+        <v>23</v>
+      </c>
+      <c r="T203" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="U203" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="204" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A204" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="B204" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C204" s="12">
+        <v>58030822</v>
+      </c>
+      <c r="D204" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="E204" s="12">
+        <v>2721358023</v>
+      </c>
+      <c r="F204" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G204" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H204" s="14">
+        <v>46062</v>
+      </c>
+      <c r="I204" s="14">
+        <v>46094</v>
+      </c>
+      <c r="J204" s="24">
+        <f t="shared" si="12"/>
+        <v>25</v>
+      </c>
+      <c r="K204" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="L204" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="M204" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="N204" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="O204" s="41">
+        <v>144000</v>
+      </c>
+      <c r="P204" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q204" s="49">
+        <v>144000</v>
+      </c>
+      <c r="R204" s="42">
+        <v>46094</v>
+      </c>
+      <c r="S204" s="24">
+        <f t="shared" si="13"/>
+        <v>25</v>
+      </c>
+      <c r="T204" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="U204" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="205" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A205" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="B205" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C205" s="12">
+        <v>58514013</v>
+      </c>
+      <c r="D205" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E205" s="12">
+        <v>2722520110</v>
+      </c>
+      <c r="F205" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G205" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H205" s="14">
+        <v>46071</v>
+      </c>
+      <c r="I205" s="14">
+        <v>46094</v>
+      </c>
+      <c r="J205" s="24">
+        <f t="shared" ref="J205" si="15">+NETWORKDAYS(H205,I205)</f>
+        <v>18</v>
+      </c>
+      <c r="K205" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="L205" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="M205" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="N205" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="O205" s="41">
+        <v>360000</v>
+      </c>
+      <c r="P205" s="41">
+        <v>92495</v>
+      </c>
+      <c r="Q205" s="49">
+        <v>452495</v>
+      </c>
+      <c r="R205" s="42">
+        <v>46094</v>
+      </c>
+      <c r="S205" s="24">
+        <f t="shared" ref="S205" si="16">NETWORKDAYS(H205,R205)</f>
+        <v>18</v>
+      </c>
+      <c r="T205" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="U205" s="48" t="s">
+        <v>443</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T189" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="17">
-      <filters>
-        <dateGroupItem year="2026" month="3" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:U205" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="73" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="67" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="66" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="64" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="62" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="61" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="59" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="58" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="57" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="56" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="55" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="54" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="53" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="52" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="51" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="50" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="49" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="48" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="47" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="46" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="45" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="44" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
-    <cfRule type="duplicateValues" dxfId="43" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="42" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="41" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="39" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="38" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="37" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="36" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="35" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="33" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C114">
-    <cfRule type="duplicateValues" dxfId="32" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="31" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="30" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C157:C160">
-    <cfRule type="duplicateValues" dxfId="28" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C161:C163">
-    <cfRule type="duplicateValues" dxfId="27" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="26" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="24" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C168">
-    <cfRule type="duplicateValues" dxfId="22" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="21" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171">
-    <cfRule type="duplicateValues" dxfId="20" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173">
-    <cfRule type="duplicateValues" dxfId="19" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C175">
-    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C178">
-    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="11" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="9" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="8" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="7" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="6" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="5" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="4" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="3" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="2" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172">
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="270" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C336A09-76B4-440B-A3BC-BF0FF3777075}"/>
+  <xr:revisionPtr revIDLastSave="288" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95CFDE26-0A9D-4EF2-9463-4A0EA5668C04}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="475">
   <si>
     <t>Client</t>
   </si>
@@ -1426,6 +1426,45 @@
   </si>
   <si>
     <t xml:space="preserve">PC MARKET COCODY BONOUMIN </t>
+  </si>
+  <si>
+    <t>CFAO MOBILTY COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>SYTHD260040</t>
+  </si>
+  <si>
+    <t>SYTHD250340</t>
+  </si>
+  <si>
+    <t>SYTHD250339</t>
+  </si>
+  <si>
+    <t>BAD</t>
+  </si>
+  <si>
+    <t>SYTHD260078</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>DIRECTION GENERALE DES DOUANES</t>
+  </si>
+  <si>
+    <t>BUVPN260050</t>
+  </si>
+  <si>
+    <t>BANQUE DE L'UNION</t>
+  </si>
+  <si>
+    <t>BUVPN260051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SICTA  </t>
+  </si>
+  <si>
+    <t>MARCORY  ZONE  4</t>
   </si>
 </sst>
 </file>
@@ -1834,7 +1873,127 @@
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="149">
+  <dxfs count="161">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3659,7 +3818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U205"/>
+  <dimension ref="A1:U220"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="26" customWidth="1"/>
@@ -16768,7 +16927,7 @@
         <v>46094</v>
       </c>
       <c r="J205" s="24">
-        <f t="shared" ref="J205" si="15">+NETWORKDAYS(H205,I205)</f>
+        <f t="shared" ref="J205:J212" si="15">+NETWORKDAYS(H205,I205)</f>
         <v>18</v>
       </c>
       <c r="K205" s="41" t="s">
@@ -16796,7 +16955,7 @@
         <v>46094</v>
       </c>
       <c r="S205" s="24">
-        <f t="shared" ref="S205" si="16">NETWORKDAYS(H205,R205)</f>
+        <f t="shared" ref="S205:S212" si="16">NETWORKDAYS(H205,R205)</f>
         <v>18</v>
       </c>
       <c r="T205" s="41" t="s">
@@ -16805,199 +16964,731 @@
       <c r="U205" s="48" t="s">
         <v>443</v>
       </c>
+    </row>
+    <row r="206" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A206" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="B206" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C206" s="12">
+        <v>57157406</v>
+      </c>
+      <c r="D206" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E206" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="F206" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G206" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H206" s="16">
+        <v>46045</v>
+      </c>
+      <c r="I206" s="14">
+        <v>46055</v>
+      </c>
+      <c r="J206" s="24">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="K206" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L206" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M206" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N206" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="O206" s="56">
+        <v>0</v>
+      </c>
+      <c r="P206" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q206" s="56">
+        <f t="shared" ref="Q206:Q212" si="17">P206+O206</f>
+        <v>0</v>
+      </c>
+      <c r="R206" s="13">
+        <v>46094</v>
+      </c>
+      <c r="S206" s="24">
+        <f t="shared" si="16"/>
+        <v>36</v>
+      </c>
+      <c r="T206" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="U206" s="11" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="207" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A207" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="B207" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C207" s="12">
+        <v>52797879</v>
+      </c>
+      <c r="D207" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E207" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="F207" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G207" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H207" s="14">
+        <v>45960</v>
+      </c>
+      <c r="I207" s="14">
+        <v>45979</v>
+      </c>
+      <c r="J207" s="24">
+        <f t="shared" si="15"/>
+        <v>14</v>
+      </c>
+      <c r="K207" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L207" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M207" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N207" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="O207" s="56">
+        <v>0</v>
+      </c>
+      <c r="P207" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q207" s="56">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R207" s="13">
+        <v>46097</v>
+      </c>
+      <c r="S207" s="24">
+        <f t="shared" si="16"/>
+        <v>98</v>
+      </c>
+      <c r="T207" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="U207" s="11" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="208" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A208" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="B208" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C208" s="12">
+        <v>52797893</v>
+      </c>
+      <c r="D208" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E208" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="F208" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G208" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H208" s="14">
+        <v>45960</v>
+      </c>
+      <c r="I208" s="14">
+        <v>45979</v>
+      </c>
+      <c r="J208" s="24">
+        <f t="shared" si="15"/>
+        <v>14</v>
+      </c>
+      <c r="K208" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L208" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M208" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N208" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="O208" s="56">
+        <v>0</v>
+      </c>
+      <c r="P208" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q208" s="56">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R208" s="13">
+        <v>46097</v>
+      </c>
+      <c r="S208" s="24">
+        <f t="shared" si="16"/>
+        <v>98</v>
+      </c>
+      <c r="T208" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="U208" s="11" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="209" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A209" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="B209" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C209" s="12">
+        <v>57917222</v>
+      </c>
+      <c r="D209" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E209" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="F209" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G209" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H209" s="14">
+        <v>46059</v>
+      </c>
+      <c r="I209" s="14">
+        <v>46098</v>
+      </c>
+      <c r="J209" s="24">
+        <f t="shared" si="15"/>
+        <v>28</v>
+      </c>
+      <c r="K209" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L209" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M209" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="N209" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O209" s="56">
+        <v>577056</v>
+      </c>
+      <c r="P209" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q209" s="56">
+        <f t="shared" si="17"/>
+        <v>577056</v>
+      </c>
+      <c r="R209" s="13">
+        <v>46098</v>
+      </c>
+      <c r="S209" s="24">
+        <f t="shared" si="16"/>
+        <v>28</v>
+      </c>
+      <c r="T209" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="U209" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="210" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A210" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="B210" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C210" s="12">
+        <v>58809676</v>
+      </c>
+      <c r="D210" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E210" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="F210" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G210" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H210" s="14">
+        <v>46076</v>
+      </c>
+      <c r="I210" s="14">
+        <v>46098</v>
+      </c>
+      <c r="J210" s="24">
+        <f t="shared" si="15"/>
+        <v>17</v>
+      </c>
+      <c r="K210" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L210" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M210" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N210" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O210" s="19">
+        <v>2000000</v>
+      </c>
+      <c r="P210" s="19">
+        <v>380000</v>
+      </c>
+      <c r="Q210" s="56">
+        <f t="shared" si="17"/>
+        <v>2380000</v>
+      </c>
+      <c r="R210" s="13">
+        <v>46098</v>
+      </c>
+      <c r="S210" s="24">
+        <f t="shared" si="16"/>
+        <v>17</v>
+      </c>
+      <c r="T210" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="U210" s="11" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="211" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A211" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="B211" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C211" s="12">
+        <v>58167492</v>
+      </c>
+      <c r="D211" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="E211" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="F211" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G211" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H211" s="14">
+        <v>46066</v>
+      </c>
+      <c r="I211" s="14">
+        <v>46092</v>
+      </c>
+      <c r="J211" s="24">
+        <f t="shared" si="15"/>
+        <v>19</v>
+      </c>
+      <c r="K211" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L211" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M211" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N211" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O211" s="19">
+        <v>650000</v>
+      </c>
+      <c r="P211" s="19">
+        <v>350000</v>
+      </c>
+      <c r="Q211" s="56">
+        <f t="shared" si="17"/>
+        <v>1000000</v>
+      </c>
+      <c r="R211" s="13">
+        <v>46098</v>
+      </c>
+      <c r="S211" s="24">
+        <f t="shared" si="16"/>
+        <v>23</v>
+      </c>
+      <c r="T211" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="U211" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="212" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A212" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="B212" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C212" s="5">
+        <v>58476260</v>
+      </c>
+      <c r="D212" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="E212" s="5">
+        <v>2721711965</v>
+      </c>
+      <c r="F212" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G212" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H212" s="13">
+        <v>46070</v>
+      </c>
+      <c r="I212" s="13">
+        <v>46098</v>
+      </c>
+      <c r="J212" s="24">
+        <f t="shared" si="15"/>
+        <v>21</v>
+      </c>
+      <c r="K212" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="L212" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="M212" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N212" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O212" s="56">
+        <v>150000</v>
+      </c>
+      <c r="P212" s="56">
+        <v>60000</v>
+      </c>
+      <c r="Q212" s="56">
+        <f t="shared" si="17"/>
+        <v>210000</v>
+      </c>
+      <c r="R212" s="13">
+        <v>46098</v>
+      </c>
+      <c r="S212" s="24">
+        <f t="shared" si="16"/>
+        <v>21</v>
+      </c>
+      <c r="T212" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="U212" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="214" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="P214" s="18"/>
+      <c r="Q214"/>
+      <c r="T214" s="67"/>
+      <c r="U214"/>
+    </row>
+    <row r="215" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="P215" s="18"/>
+      <c r="Q215"/>
+      <c r="T215" s="67"/>
+      <c r="U215"/>
+    </row>
+    <row r="216" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="P216" s="18"/>
+      <c r="Q216"/>
+      <c r="T216" s="67"/>
+      <c r="U216"/>
+    </row>
+    <row r="217" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="P217" s="18"/>
+      <c r="Q217"/>
+      <c r="T217" s="67"/>
+      <c r="U217"/>
+    </row>
+    <row r="218" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="P218" s="18"/>
+      <c r="Q218"/>
+      <c r="T218" s="67"/>
+      <c r="U218"/>
+    </row>
+    <row r="219" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="P219" s="18"/>
+      <c r="Q219"/>
+      <c r="T219" s="67"/>
+      <c r="U219"/>
+    </row>
+    <row r="220" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="P220" s="18"/>
+      <c r="Q220"/>
+      <c r="T220" s="67"/>
+      <c r="U220"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:U205" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="148" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C205 C213 C221:C1048576">
+    <cfRule type="duplicateValues" dxfId="154" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C15 C17:C31">
+    <cfRule type="duplicateValues" dxfId="152" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C58">
+    <cfRule type="duplicateValues" dxfId="150" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C70">
+    <cfRule type="duplicateValues" dxfId="148" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="duplicateValues" dxfId="147" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="duplicateValues" dxfId="145" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="duplicateValues" dxfId="144" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12">
+    <cfRule type="duplicateValues" dxfId="143" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15">
+    <cfRule type="duplicateValues" dxfId="142" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16">
+    <cfRule type="duplicateValues" dxfId="141" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:C31">
+    <cfRule type="duplicateValues" dxfId="140" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32">
+    <cfRule type="duplicateValues" dxfId="139" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C33:C37">
+    <cfRule type="duplicateValues" dxfId="138" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C39">
+    <cfRule type="duplicateValues" dxfId="137" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40">
+    <cfRule type="duplicateValues" dxfId="136" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C47">
+    <cfRule type="duplicateValues" dxfId="135" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C59:C66">
+    <cfRule type="duplicateValues" dxfId="134" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C73">
+    <cfRule type="duplicateValues" dxfId="133" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C75">
+    <cfRule type="duplicateValues" dxfId="132" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C77">
+    <cfRule type="duplicateValues" dxfId="131" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C77:C109 C1">
+    <cfRule type="duplicateValues" dxfId="130" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C78">
+    <cfRule type="duplicateValues" dxfId="129" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C80:C81">
+    <cfRule type="duplicateValues" dxfId="128" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C85">
+    <cfRule type="duplicateValues" dxfId="127" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C92">
+    <cfRule type="duplicateValues" dxfId="125" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C93">
+    <cfRule type="duplicateValues" dxfId="124" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C98">
+    <cfRule type="duplicateValues" dxfId="123" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C101">
+    <cfRule type="duplicateValues" dxfId="122" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C102">
+    <cfRule type="duplicateValues" dxfId="121" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C103:C109">
+    <cfRule type="duplicateValues" dxfId="119" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C114">
+    <cfRule type="duplicateValues" dxfId="118" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C115">
+    <cfRule type="duplicateValues" dxfId="117" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C145">
+    <cfRule type="duplicateValues" dxfId="116" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C157:C160">
+    <cfRule type="duplicateValues" dxfId="114" priority="88"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C161:C163">
+    <cfRule type="duplicateValues" dxfId="113" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C166">
+    <cfRule type="duplicateValues" dxfId="112" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C167">
+    <cfRule type="duplicateValues" dxfId="110" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C168">
+    <cfRule type="duplicateValues" dxfId="108" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C170">
+    <cfRule type="duplicateValues" dxfId="107" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C171">
+    <cfRule type="duplicateValues" dxfId="106" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C173">
+    <cfRule type="duplicateValues" dxfId="105" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C174">
+    <cfRule type="duplicateValues" dxfId="103" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C175">
+    <cfRule type="duplicateValues" dxfId="102" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C177">
+    <cfRule type="duplicateValues" dxfId="101" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C177:C178">
+    <cfRule type="duplicateValues" dxfId="100" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C179">
+    <cfRule type="duplicateValues" dxfId="99" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1">
+    <cfRule type="duplicateValues" dxfId="97" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E15 E17:E31">
+    <cfRule type="duplicateValues" dxfId="95" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="duplicateValues" dxfId="94" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20:E31">
+    <cfRule type="duplicateValues" dxfId="93" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E33">
+    <cfRule type="duplicateValues" dxfId="92" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E47">
+    <cfRule type="duplicateValues" dxfId="91" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E53">
+    <cfRule type="duplicateValues" dxfId="90" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E58">
+    <cfRule type="duplicateValues" dxfId="89" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E77:E97 E1">
+    <cfRule type="duplicateValues" dxfId="88" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E172">
+    <cfRule type="duplicateValues" dxfId="87" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E175">
+    <cfRule type="duplicateValues" dxfId="86" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C207">
+    <cfRule type="duplicateValues" dxfId="85" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C208">
+    <cfRule type="duplicateValues" dxfId="83" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C206:C212">
+    <cfRule type="duplicateValues" dxfId="81" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="142" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="140" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="138" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="137" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="135" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="134" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="133" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="132" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="131" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="130" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="129" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="128" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="127" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="126" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="125" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="124" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="123" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="122" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="121" priority="67"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="120" priority="76"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C78">
-    <cfRule type="duplicateValues" dxfId="119" priority="66"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="118" priority="65"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="117" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="64"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="115" priority="62"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="114" priority="61"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="113" priority="59"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="112" priority="58"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="111" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="57"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="109" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C114">
-    <cfRule type="duplicateValues" dxfId="108" priority="53"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="107" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="106" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C157:C160">
-    <cfRule type="duplicateValues" dxfId="104" priority="82"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C161:C163">
-    <cfRule type="duplicateValues" dxfId="103" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="102" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="100" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C168">
-    <cfRule type="duplicateValues" dxfId="98" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="97" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C171">
-    <cfRule type="duplicateValues" dxfId="96" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C173">
-    <cfRule type="duplicateValues" dxfId="95" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="93" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C175">
-    <cfRule type="duplicateValues" dxfId="92" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="91" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C177:C178">
-    <cfRule type="duplicateValues" dxfId="90" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C179">
-    <cfRule type="duplicateValues" dxfId="89" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="87" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="75"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="85" priority="51"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="84" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="83" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="82" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="81" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="80" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="79" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="78" priority="78"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E172">
-    <cfRule type="duplicateValues" dxfId="77" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E175">
-    <cfRule type="duplicateValues" dxfId="76" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="288" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95CFDE26-0A9D-4EF2-9463-4A0EA5668C04}"/>
+  <xr:revisionPtr revIDLastSave="317" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A68C04BF-F8F4-4D3B-AA41-19C29088046B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$217</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2170" uniqueCount="483">
   <si>
     <t>Client</t>
   </si>
@@ -1465,6 +1465,30 @@
   </si>
   <si>
     <t>MARCORY  ZONE  4</t>
+  </si>
+  <si>
+    <t>BUVPN260017</t>
+  </si>
+  <si>
+    <t>BASE AERIENN D’ABIDJAN</t>
+  </si>
+  <si>
+    <t>SYTHD260077</t>
+  </si>
+  <si>
+    <t>BUVPN260048</t>
+  </si>
+  <si>
+    <t>GBELEBAN</t>
+  </si>
+  <si>
+    <t>BUVPN260049</t>
+  </si>
+  <si>
+    <t>PRIMORIS</t>
+  </si>
+  <si>
+    <t>SYTHD260073</t>
   </si>
 </sst>
 </file>
@@ -1873,807 +1897,7 @@
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="161">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="81">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3818,7 +3042,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U220"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:U217"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="26" customWidth="1"/>
@@ -3903,7 +3128,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="58" t="s">
         <v>154</v>
       </c>
@@ -3965,7 +3190,7 @@
       </c>
       <c r="U2" s="65"/>
     </row>
-    <row r="3" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>159</v>
       </c>
@@ -4027,7 +3252,7 @@
       </c>
       <c r="U3" s="65"/>
     </row>
-    <row r="4" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>154</v>
       </c>
@@ -4089,7 +3314,7 @@
       </c>
       <c r="U4" s="65"/>
     </row>
-    <row r="5" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
         <v>154</v>
       </c>
@@ -4151,7 +3376,7 @@
       </c>
       <c r="U5" s="65"/>
     </row>
-    <row r="6" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>164</v>
       </c>
@@ -4213,7 +3438,7 @@
       </c>
       <c r="U6" s="65"/>
     </row>
-    <row r="7" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>165</v>
       </c>
@@ -4275,7 +3500,7 @@
       </c>
       <c r="U7" s="65"/>
     </row>
-    <row r="8" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>166</v>
       </c>
@@ -4337,7 +3562,7 @@
       </c>
       <c r="U8" s="65"/>
     </row>
-    <row r="9" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>169</v>
       </c>
@@ -4399,7 +3624,7 @@
       </c>
       <c r="U9" s="65"/>
     </row>
-    <row r="10" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>172</v>
       </c>
@@ -4461,7 +3686,7 @@
       </c>
       <c r="U10" s="65"/>
     </row>
-    <row r="11" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>172</v>
       </c>
@@ -4523,7 +3748,7 @@
       </c>
       <c r="U11" s="65"/>
     </row>
-    <row r="12" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
         <v>177</v>
       </c>
@@ -4585,7 +3810,7 @@
       </c>
       <c r="U12" s="65"/>
     </row>
-    <row r="13" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
         <v>154</v>
       </c>
@@ -4647,7 +3872,7 @@
       </c>
       <c r="U13" s="65"/>
     </row>
-    <row r="14" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
         <v>154</v>
       </c>
@@ -4709,7 +3934,7 @@
       </c>
       <c r="U14" s="65"/>
     </row>
-    <row r="15" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>172</v>
       </c>
@@ -4771,7 +3996,7 @@
       </c>
       <c r="U15" s="65"/>
     </row>
-    <row r="16" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>154</v>
       </c>
@@ -4833,7 +4058,7 @@
       </c>
       <c r="U16" s="65"/>
     </row>
-    <row r="17" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>154</v>
       </c>
@@ -4895,7 +4120,7 @@
       </c>
       <c r="U17" s="65"/>
     </row>
-    <row r="18" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
         <v>186</v>
       </c>
@@ -4957,7 +4182,7 @@
       </c>
       <c r="U18" s="65"/>
     </row>
-    <row r="19" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>189</v>
       </c>
@@ -5019,7 +4244,7 @@
       </c>
       <c r="U19" s="65"/>
     </row>
-    <row r="20" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
         <v>189</v>
       </c>
@@ -5081,7 +4306,7 @@
       </c>
       <c r="U20" s="65"/>
     </row>
-    <row r="21" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>193</v>
       </c>
@@ -5143,7 +4368,7 @@
       </c>
       <c r="U21" s="65"/>
     </row>
-    <row r="22" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>43</v>
       </c>
@@ -5205,7 +4430,7 @@
       </c>
       <c r="U22" s="65"/>
     </row>
-    <row r="23" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
         <v>201</v>
       </c>
@@ -5267,7 +4492,7 @@
       </c>
       <c r="U23" s="65"/>
     </row>
-    <row r="24" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>204</v>
       </c>
@@ -5329,7 +4554,7 @@
       </c>
       <c r="U24" s="65"/>
     </row>
-    <row r="25" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>206</v>
       </c>
@@ -5391,7 +4616,7 @@
       </c>
       <c r="U25" s="65"/>
     </row>
-    <row r="26" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>207</v>
       </c>
@@ -5453,7 +4678,7 @@
       </c>
       <c r="U26" s="65"/>
     </row>
-    <row r="27" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
         <v>172</v>
       </c>
@@ -5515,7 +4740,7 @@
       </c>
       <c r="U27" s="65"/>
     </row>
-    <row r="28" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
         <v>210</v>
       </c>
@@ -5577,7 +4802,7 @@
       </c>
       <c r="U28" s="65"/>
     </row>
-    <row r="29" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
         <v>213</v>
       </c>
@@ -5639,7 +4864,7 @@
       </c>
       <c r="U29" s="65"/>
     </row>
-    <row r="30" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>217</v>
       </c>
@@ -5701,7 +4926,7 @@
       </c>
       <c r="U30" s="65"/>
     </row>
-    <row r="31" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>218</v>
       </c>
@@ -5763,7 +4988,7 @@
       </c>
       <c r="U31" s="65"/>
     </row>
-    <row r="32" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
         <v>81</v>
       </c>
@@ -5825,7 +5050,7 @@
       </c>
       <c r="U32" s="65"/>
     </row>
-    <row r="33" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
         <v>91</v>
       </c>
@@ -5887,7 +5112,7 @@
       </c>
       <c r="U33" s="65"/>
     </row>
-    <row r="34" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
         <v>91</v>
       </c>
@@ -5949,7 +5174,7 @@
       </c>
       <c r="U34" s="65"/>
     </row>
-    <row r="35" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
         <v>91</v>
       </c>
@@ -6011,7 +5236,7 @@
       </c>
       <c r="U35" s="65"/>
     </row>
-    <row r="36" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12" t="s">
         <v>91</v>
       </c>
@@ -6073,7 +5298,7 @@
       </c>
       <c r="U36" s="65"/>
     </row>
-    <row r="37" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12" t="s">
         <v>91</v>
       </c>
@@ -6135,7 +5360,7 @@
       </c>
       <c r="U37" s="65"/>
     </row>
-    <row r="38" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
         <v>226</v>
       </c>
@@ -6197,7 +5422,7 @@
       </c>
       <c r="U38" s="65"/>
     </row>
-    <row r="39" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
         <v>228</v>
       </c>
@@ -6259,7 +5484,7 @@
       </c>
       <c r="U39" s="65"/>
     </row>
-    <row r="40" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
         <v>91</v>
       </c>
@@ -6321,7 +5546,7 @@
       </c>
       <c r="U40" s="65"/>
     </row>
-    <row r="41" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
         <v>231</v>
       </c>
@@ -6383,7 +5608,7 @@
       </c>
       <c r="U41" s="65"/>
     </row>
-    <row r="42" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
         <v>234</v>
       </c>
@@ -6445,7 +5670,7 @@
       </c>
       <c r="U42" s="65"/>
     </row>
-    <row r="43" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>236</v>
       </c>
@@ -6507,7 +5732,7 @@
       </c>
       <c r="U43" s="65"/>
     </row>
-    <row r="44" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
         <v>237</v>
       </c>
@@ -6569,7 +5794,7 @@
       </c>
       <c r="U44" s="65"/>
     </row>
-    <row r="45" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
         <v>238</v>
       </c>
@@ -6631,7 +5856,7 @@
       </c>
       <c r="U45" s="65"/>
     </row>
-    <row r="46" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="12" t="s">
         <v>240</v>
       </c>
@@ -6693,7 +5918,7 @@
       </c>
       <c r="U46" s="65"/>
     </row>
-    <row r="47" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="12" t="s">
         <v>91</v>
       </c>
@@ -6755,7 +5980,7 @@
       </c>
       <c r="U47" s="65"/>
     </row>
-    <row r="48" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="12" t="s">
         <v>243</v>
       </c>
@@ -6817,7 +6042,7 @@
       </c>
       <c r="U48" s="65"/>
     </row>
-    <row r="49" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="12" t="s">
         <v>246</v>
       </c>
@@ -6879,7 +6104,7 @@
       </c>
       <c r="U49" s="65"/>
     </row>
-    <row r="50" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12" t="s">
         <v>248</v>
       </c>
@@ -6941,7 +6166,7 @@
       </c>
       <c r="U50" s="65"/>
     </row>
-    <row r="51" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="12" t="s">
         <v>250</v>
       </c>
@@ -7003,7 +6228,7 @@
       </c>
       <c r="U51" s="65"/>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="12" t="s">
         <v>250</v>
       </c>
@@ -7065,7 +6290,7 @@
       </c>
       <c r="U52" s="65"/>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="12" t="s">
         <v>253</v>
       </c>
@@ -7127,7 +6352,7 @@
       </c>
       <c r="U53" s="65"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
         <v>256</v>
       </c>
@@ -7189,7 +6414,7 @@
       </c>
       <c r="U54" s="65"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>258</v>
       </c>
@@ -7251,7 +6476,7 @@
       </c>
       <c r="U55" s="65"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="12" t="s">
         <v>259</v>
       </c>
@@ -7313,7 +6538,7 @@
       </c>
       <c r="U56" s="65"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="12" t="s">
         <v>259</v>
       </c>
@@ -7375,7 +6600,7 @@
       </c>
       <c r="U57" s="65"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="12" t="s">
         <v>253</v>
       </c>
@@ -7437,7 +6662,7 @@
       </c>
       <c r="U58" s="65"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="12" t="s">
         <v>265</v>
       </c>
@@ -7499,7 +6724,7 @@
       </c>
       <c r="U59" s="65"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="12" t="s">
         <v>267</v>
       </c>
@@ -7561,7 +6786,7 @@
       </c>
       <c r="U60" s="65"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="12" t="s">
         <v>271</v>
       </c>
@@ -7623,7 +6848,7 @@
       </c>
       <c r="U61" s="65"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="12" t="s">
         <v>43</v>
       </c>
@@ -7685,7 +6910,7 @@
       </c>
       <c r="U62" s="65"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="11" t="s">
         <v>58</v>
       </c>
@@ -7747,7 +6972,7 @@
       </c>
       <c r="U63" s="65"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="12" t="s">
         <v>91</v>
       </c>
@@ -7809,7 +7034,7 @@
       </c>
       <c r="U64" s="65"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="12" t="s">
         <v>91</v>
       </c>
@@ -7871,7 +7096,7 @@
       </c>
       <c r="U65" s="65"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12" t="s">
         <v>91</v>
       </c>
@@ -7933,7 +7158,7 @@
       </c>
       <c r="U66" s="65"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="12" t="s">
         <v>282</v>
       </c>
@@ -7995,7 +7220,7 @@
       </c>
       <c r="U67" s="65"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>285</v>
       </c>
@@ -8057,7 +7282,7 @@
       </c>
       <c r="U68" s="65"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="12" t="s">
         <v>286</v>
       </c>
@@ -8119,7 +7344,7 @@
       </c>
       <c r="U69" s="65"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="22" t="s">
         <v>288</v>
       </c>
@@ -8181,7 +7406,7 @@
       </c>
       <c r="U70" s="65"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>291</v>
       </c>
@@ -8243,7 +7468,7 @@
       </c>
       <c r="U71" s="65"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>292</v>
       </c>
@@ -8305,7 +7530,7 @@
       </c>
       <c r="U72" s="65"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="12" t="s">
         <v>91</v>
       </c>
@@ -8367,7 +7592,7 @@
       </c>
       <c r="U73" s="65"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="12" t="s">
         <v>294</v>
       </c>
@@ -8429,7 +7654,7 @@
       </c>
       <c r="U74" s="65"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="12" t="s">
         <v>91</v>
       </c>
@@ -8491,7 +7716,7 @@
       </c>
       <c r="U75" s="65"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="12" t="s">
         <v>299</v>
       </c>
@@ -8553,7 +7778,7 @@
       </c>
       <c r="U76" s="65"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="12" t="s">
         <v>18</v>
       </c>
@@ -8615,7 +7840,7 @@
       </c>
       <c r="U77" s="65"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="12" t="s">
         <v>27</v>
       </c>
@@ -8677,7 +7902,7 @@
       </c>
       <c r="U78" s="65"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
         <v>30</v>
       </c>
@@ -8739,7 +7964,7 @@
       </c>
       <c r="U79" s="65"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="12" t="s">
         <v>35</v>
       </c>
@@ -8801,7 +8026,7 @@
       </c>
       <c r="U80" s="65"/>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="12" t="s">
         <v>35</v>
       </c>
@@ -8863,7 +8088,7 @@
       </c>
       <c r="U81" s="65"/>
     </row>
-    <row r="82" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:21" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="12" t="s">
         <v>35</v>
       </c>
@@ -8925,7 +8150,7 @@
       </c>
       <c r="U82" s="65"/>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="12" t="s">
         <v>43</v>
       </c>
@@ -8987,7 +8212,7 @@
       </c>
       <c r="U83" s="65"/>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="12" t="s">
         <v>43</v>
       </c>
@@ -9049,7 +8274,7 @@
       </c>
       <c r="U84" s="65"/>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="12" t="s">
         <v>52</v>
       </c>
@@ -9111,7 +8336,7 @@
       </c>
       <c r="U85" s="65"/>
     </row>
-    <row r="86" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:21" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="6" t="s">
         <v>55</v>
       </c>
@@ -9173,7 +8398,7 @@
       </c>
       <c r="U86" s="65"/>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="22" t="s">
         <v>58</v>
       </c>
@@ -9235,7 +8460,7 @@
       </c>
       <c r="U87" s="65"/>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="12" t="s">
         <v>62</v>
       </c>
@@ -9297,7 +8522,7 @@
       </c>
       <c r="U88" s="65"/>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="12" t="s">
         <v>65</v>
       </c>
@@ -9359,7 +8584,7 @@
       </c>
       <c r="U89" s="65"/>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="12" t="s">
         <v>67</v>
       </c>
@@ -9421,7 +8646,7 @@
       </c>
       <c r="U90" s="65"/>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="12" t="s">
         <v>70</v>
       </c>
@@ -9483,7 +8708,7 @@
       </c>
       <c r="U91" s="65"/>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="12" t="s">
         <v>75</v>
       </c>
@@ -9545,7 +8770,7 @@
       </c>
       <c r="U92" s="65"/>
     </row>
-    <row r="93" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:21" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="29" t="s">
         <v>77</v>
       </c>
@@ -9607,7 +8832,7 @@
       </c>
       <c r="U93" s="65"/>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="12" t="s">
         <v>43</v>
       </c>
@@ -9669,7 +8894,7 @@
       </c>
       <c r="U94" s="65"/>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="12" t="s">
         <v>81</v>
       </c>
@@ -9731,7 +8956,7 @@
       </c>
       <c r="U95" s="65"/>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="8" t="s">
         <v>85</v>
       </c>
@@ -9793,7 +9018,7 @@
       </c>
       <c r="U96" s="65"/>
     </row>
-    <row r="97" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:21" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
         <v>86</v>
       </c>
@@ -9855,7 +9080,7 @@
       </c>
       <c r="U97" s="65"/>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="12" t="s">
         <v>88</v>
       </c>
@@ -9917,7 +9142,7 @@
       </c>
       <c r="U98" s="65"/>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="12" t="s">
         <v>91</v>
       </c>
@@ -9979,7 +9204,7 @@
       </c>
       <c r="U99" s="65"/>
     </row>
-    <row r="100" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:21" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="29" t="s">
         <v>95</v>
       </c>
@@ -10041,7 +9266,7 @@
       </c>
       <c r="U100" s="65"/>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="12" t="s">
         <v>58</v>
       </c>
@@ -10103,7 +9328,7 @@
       </c>
       <c r="U101" s="65"/>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="22" t="s">
         <v>58</v>
       </c>
@@ -10165,7 +9390,7 @@
       </c>
       <c r="U102" s="65"/>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="12" t="s">
         <v>43</v>
       </c>
@@ -10227,7 +9452,7 @@
       </c>
       <c r="U103" s="65"/>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="12" t="s">
         <v>103</v>
       </c>
@@ -10289,7 +9514,7 @@
       </c>
       <c r="U104" s="65"/>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>106</v>
       </c>
@@ -10351,7 +9576,7 @@
       </c>
       <c r="U105" s="65"/>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>81</v>
       </c>
@@ -10413,7 +9638,7 @@
       </c>
       <c r="U106" s="65"/>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>107</v>
       </c>
@@ -10475,7 +9700,7 @@
       </c>
       <c r="U107" s="65"/>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>108</v>
       </c>
@@ -10537,7 +9762,7 @@
       </c>
       <c r="U108" s="65"/>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
         <v>109</v>
       </c>
@@ -10599,7 +9824,7 @@
       </c>
       <c r="U109" s="65"/>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="12" t="s">
         <v>110</v>
       </c>
@@ -10661,7 +9886,7 @@
       </c>
       <c r="U110" s="65"/>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="12" t="s">
         <v>113</v>
       </c>
@@ -10723,7 +9948,7 @@
       </c>
       <c r="U111" s="65"/>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="11" t="s">
         <v>116</v>
       </c>
@@ -10785,7 +10010,7 @@
       </c>
       <c r="U112" s="65"/>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="12" t="s">
         <v>120</v>
       </c>
@@ -10847,7 +10072,7 @@
       </c>
       <c r="U113" s="65"/>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="12" t="s">
         <v>123</v>
       </c>
@@ -10909,7 +10134,7 @@
       </c>
       <c r="U114" s="65"/>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="12" t="s">
         <v>110</v>
       </c>
@@ -10971,7 +10196,7 @@
       </c>
       <c r="U115" s="65"/>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="12" t="s">
         <v>127</v>
       </c>
@@ -11033,7 +10258,7 @@
       </c>
       <c r="U116" s="65"/>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
         <v>130</v>
       </c>
@@ -11095,7 +10320,7 @@
       </c>
       <c r="U117" s="65"/>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
         <v>131</v>
       </c>
@@ -11157,7 +10382,7 @@
       </c>
       <c r="U118" s="65"/>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="12" t="s">
         <v>132</v>
       </c>
@@ -11219,7 +10444,7 @@
       </c>
       <c r="U119" s="65"/>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="12" t="s">
         <v>134</v>
       </c>
@@ -11281,7 +10506,7 @@
       </c>
       <c r="U120" s="65"/>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="12" t="s">
         <v>134</v>
       </c>
@@ -11343,7 +10568,7 @@
       </c>
       <c r="U121" s="65"/>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="12" t="s">
         <v>140</v>
       </c>
@@ -11405,7 +10630,7 @@
       </c>
       <c r="U122" s="65"/>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="12" t="s">
         <v>143</v>
       </c>
@@ -11467,7 +10692,7 @@
       </c>
       <c r="U123" s="65"/>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="12" t="s">
         <v>145</v>
       </c>
@@ -11529,7 +10754,7 @@
       </c>
       <c r="U124" s="65"/>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="12" t="s">
         <v>149</v>
       </c>
@@ -11591,7 +10816,7 @@
       </c>
       <c r="U125" s="65"/>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="12" t="s">
         <v>143</v>
       </c>
@@ -11653,7 +10878,7 @@
       </c>
       <c r="U126" s="65"/>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="12" t="s">
         <v>301</v>
       </c>
@@ -11719,7 +10944,7 @@
       </c>
       <c r="U127" s="65"/>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="12" t="s">
         <v>305</v>
       </c>
@@ -11785,7 +11010,7 @@
       </c>
       <c r="U128" s="65"/>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="12" t="s">
         <v>145</v>
       </c>
@@ -11851,7 +11076,7 @@
       </c>
       <c r="U129" s="65"/>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
         <v>308</v>
       </c>
@@ -11917,7 +11142,7 @@
       </c>
       <c r="U130" s="65"/>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="9" t="s">
         <v>309</v>
       </c>
@@ -11983,7 +11208,7 @@
       </c>
       <c r="U131" s="65"/>
     </row>
-    <row r="132" spans="1:21" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:21" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="22" t="s">
         <v>311</v>
       </c>
@@ -12049,7 +11274,7 @@
       </c>
       <c r="U132" s="66"/>
     </row>
-    <row r="133" spans="1:21" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:21" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="12" t="s">
         <v>311</v>
       </c>
@@ -12115,7 +11340,7 @@
       </c>
       <c r="U133" s="66"/>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="12" t="s">
         <v>317</v>
       </c>
@@ -12181,7 +11406,7 @@
       </c>
       <c r="U134" s="65"/>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="9" t="s">
         <v>320</v>
       </c>
@@ -12247,7 +11472,7 @@
       </c>
       <c r="U135" s="65"/>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="9" t="s">
         <v>321</v>
       </c>
@@ -12313,7 +11538,7 @@
       </c>
       <c r="U136" s="65"/>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="9" t="s">
         <v>321</v>
       </c>
@@ -12379,7 +11604,7 @@
       </c>
       <c r="U137" s="65"/>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="9" t="s">
         <v>322</v>
       </c>
@@ -12445,7 +11670,7 @@
       </c>
       <c r="U138" s="65"/>
     </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="9" t="s">
         <v>323</v>
       </c>
@@ -12511,7 +11736,7 @@
       </c>
       <c r="U139" s="65"/>
     </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
         <v>324</v>
       </c>
@@ -12577,7 +11802,7 @@
       </c>
       <c r="U140" s="65"/>
     </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
         <v>326</v>
       </c>
@@ -12643,7 +11868,7 @@
       </c>
       <c r="U141" s="65"/>
     </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="12" t="s">
         <v>328</v>
       </c>
@@ -12709,7 +11934,7 @@
       </c>
       <c r="U142" s="65"/>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="12" t="s">
         <v>331</v>
       </c>
@@ -12775,7 +12000,7 @@
       </c>
       <c r="U143" s="65"/>
     </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="12" t="s">
         <v>333</v>
       </c>
@@ -12841,7 +12066,7 @@
       </c>
       <c r="U144" s="65"/>
     </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="12" t="s">
         <v>335</v>
       </c>
@@ -12907,7 +12132,7 @@
       </c>
       <c r="U145" s="65"/>
     </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="12" t="s">
         <v>140</v>
       </c>
@@ -12973,7 +12198,7 @@
       </c>
       <c r="U146" s="65"/>
     </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="12" t="s">
         <v>140</v>
       </c>
@@ -13039,7 +12264,7 @@
       </c>
       <c r="U147" s="65"/>
     </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="22" t="s">
         <v>58</v>
       </c>
@@ -16927,7 +16152,7 @@
         <v>46094</v>
       </c>
       <c r="J205" s="24">
-        <f t="shared" ref="J205:J212" si="15">+NETWORKDAYS(H205,I205)</f>
+        <f t="shared" ref="J205:J217" si="15">+NETWORKDAYS(H205,I205)</f>
         <v>18</v>
       </c>
       <c r="K205" s="41" t="s">
@@ -16955,7 +16180,7 @@
         <v>46094</v>
       </c>
       <c r="S205" s="24">
-        <f t="shared" ref="S205:S212" si="16">NETWORKDAYS(H205,R205)</f>
+        <f t="shared" ref="S205:S217" si="16">NETWORKDAYS(H205,R205)</f>
         <v>18</v>
       </c>
       <c r="T205" s="41" t="s">
@@ -17285,11 +16510,11 @@
         <v>2000000</v>
       </c>
       <c r="P210" s="19">
-        <v>380000</v>
+        <v>462000</v>
       </c>
       <c r="Q210" s="56">
         <f t="shared" si="17"/>
-        <v>2380000</v>
+        <v>2462000</v>
       </c>
       <c r="R210" s="13">
         <v>46098</v>
@@ -17441,254 +16666,558 @@
         <v>443</v>
       </c>
     </row>
+    <row r="213" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A213" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B213" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C213" s="12">
+        <v>56460494</v>
+      </c>
+      <c r="D213" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E213" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="F213" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G213" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H213" s="16">
+        <v>46031</v>
+      </c>
+      <c r="I213" s="14">
+        <v>46071</v>
+      </c>
+      <c r="J213" s="24">
+        <f t="shared" si="15"/>
+        <v>29</v>
+      </c>
+      <c r="K213" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L213" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="M213" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N213" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="O213" s="19">
+        <v>500000</v>
+      </c>
+      <c r="P213" s="19">
+        <v>593997</v>
+      </c>
+      <c r="Q213" s="56">
+        <f>P213+O213</f>
+        <v>1093997</v>
+      </c>
+      <c r="R213" s="13">
+        <v>46099</v>
+      </c>
+      <c r="S213" s="24">
+        <f t="shared" si="16"/>
+        <v>49</v>
+      </c>
+      <c r="T213" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="U213" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="P214" s="18"/>
-      <c r="Q214"/>
-      <c r="T214" s="67"/>
-      <c r="U214"/>
+      <c r="A214" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="B214" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C214" s="5">
+        <v>57771694</v>
+      </c>
+      <c r="D214" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="E214" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="F214" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G214" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H214" s="14">
+        <v>46057</v>
+      </c>
+      <c r="I214" s="14">
+        <v>46099</v>
+      </c>
+      <c r="J214" s="24">
+        <f t="shared" si="15"/>
+        <v>31</v>
+      </c>
+      <c r="K214" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L214" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="M214" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N214" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="O214" s="19">
+        <v>400000</v>
+      </c>
+      <c r="P214" s="19">
+        <v>1034117</v>
+      </c>
+      <c r="Q214" s="56">
+        <f>P214+O214</f>
+        <v>1434117</v>
+      </c>
+      <c r="R214" s="13">
+        <v>46099</v>
+      </c>
+      <c r="S214" s="24">
+        <f t="shared" si="16"/>
+        <v>31</v>
+      </c>
+      <c r="T214" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="U214" s="11" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="P215" s="18"/>
-      <c r="Q215"/>
-      <c r="T215" s="67"/>
-      <c r="U215"/>
+      <c r="A215" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="B215" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C215" s="12">
+        <v>58809268</v>
+      </c>
+      <c r="D215" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E215" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="F215" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G215" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H215" s="14">
+        <v>46076</v>
+      </c>
+      <c r="I215" s="14">
+        <v>46099</v>
+      </c>
+      <c r="J215" s="24">
+        <f t="shared" si="15"/>
+        <v>18</v>
+      </c>
+      <c r="K215" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L215" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M215" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N215" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O215" s="19">
+        <v>2000000</v>
+      </c>
+      <c r="P215" s="19">
+        <v>462000</v>
+      </c>
+      <c r="Q215" s="56">
+        <f>P215+O215</f>
+        <v>2462000</v>
+      </c>
+      <c r="R215" s="13">
+        <v>46100</v>
+      </c>
+      <c r="S215" s="24">
+        <f t="shared" si="16"/>
+        <v>19</v>
+      </c>
+      <c r="T215" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="U215" s="11" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="P216" s="18"/>
-      <c r="Q216"/>
-      <c r="T216" s="67"/>
-      <c r="U216"/>
+      <c r="A216" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B216" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C216" s="12">
+        <v>56601140</v>
+      </c>
+      <c r="D216" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="E216" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="F216" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G216" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H216" s="14">
+        <v>46035</v>
+      </c>
+      <c r="I216" s="14">
+        <v>46098</v>
+      </c>
+      <c r="J216" s="24">
+        <f t="shared" si="15"/>
+        <v>46</v>
+      </c>
+      <c r="K216" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L216" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="M216" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N216" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O216" s="19">
+        <v>8033717</v>
+      </c>
+      <c r="P216" s="19">
+        <v>400000</v>
+      </c>
+      <c r="Q216" s="56">
+        <f>P216+O216</f>
+        <v>8433717</v>
+      </c>
+      <c r="R216" s="13">
+        <v>46100</v>
+      </c>
+      <c r="S216" s="24">
+        <f t="shared" si="16"/>
+        <v>48</v>
+      </c>
+      <c r="T216" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="U216" s="11" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="P217" s="18"/>
-      <c r="Q217"/>
-      <c r="T217" s="67"/>
-      <c r="U217"/>
-    </row>
-    <row r="218" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="P218" s="18"/>
-      <c r="Q218"/>
-      <c r="T218" s="67"/>
-      <c r="U218"/>
-    </row>
-    <row r="219" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="P219" s="18"/>
-      <c r="Q219"/>
-      <c r="T219" s="67"/>
-      <c r="U219"/>
-    </row>
-    <row r="220" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="P220" s="18"/>
-      <c r="Q220"/>
-      <c r="T220" s="67"/>
-      <c r="U220"/>
+      <c r="A217" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="B217" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C217" s="12">
+        <v>59027644</v>
+      </c>
+      <c r="D217" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E217" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="F217" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G217" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H217" s="14">
+        <v>46079</v>
+      </c>
+      <c r="I217" s="14">
+        <v>46091</v>
+      </c>
+      <c r="J217" s="24">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="K217" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L217" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M217" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N217" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O217" s="19">
+        <v>1500000</v>
+      </c>
+      <c r="P217" s="19">
+        <v>700000</v>
+      </c>
+      <c r="Q217" s="56">
+        <f>P217+O217</f>
+        <v>2200000</v>
+      </c>
+      <c r="R217" s="13">
+        <v>46100</v>
+      </c>
+      <c r="S217" s="24">
+        <f t="shared" si="16"/>
+        <v>16</v>
+      </c>
+      <c r="T217" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="U217" s="11" t="s">
+        <v>443</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U205" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U217" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="17">
+      <filters>
+        <dateGroupItem year="2026" month="3" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="160" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="80"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C205 C213 C221:C1048576">
-    <cfRule type="duplicateValues" dxfId="154" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="152" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="150" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="148" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="147" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="145" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="144" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="143" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="142" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="141" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="140" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="139" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="138" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="137" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="136" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="135" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="134" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="133" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="132" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="131" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="130" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
-    <cfRule type="duplicateValues" dxfId="129" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="128" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="127" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="125" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="124" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="123" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="122" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="121" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="119" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C114">
-    <cfRule type="duplicateValues" dxfId="118" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="117" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="116" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C157:C160">
-    <cfRule type="duplicateValues" dxfId="114" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C161:C163">
-    <cfRule type="duplicateValues" dxfId="113" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="112" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="110" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C168">
-    <cfRule type="duplicateValues" dxfId="108" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="107" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171">
-    <cfRule type="duplicateValues" dxfId="106" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173">
-    <cfRule type="duplicateValues" dxfId="105" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="103" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C175">
-    <cfRule type="duplicateValues" dxfId="102" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="101" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C178">
-    <cfRule type="duplicateValues" dxfId="100" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179">
-    <cfRule type="duplicateValues" dxfId="99" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C206:C212">
+    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C207">
+    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C208">
+    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="97" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="95" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="94" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="93" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="92" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="91" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="90" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="89" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="88" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172">
-    <cfRule type="duplicateValues" dxfId="87" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175">
-    <cfRule type="duplicateValues" dxfId="86" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C207">
-    <cfRule type="duplicateValues" dxfId="85" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="4"/>
+  <conditionalFormatting sqref="C1:C212 C218:C1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="91"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C208">
-    <cfRule type="duplicateValues" dxfId="83" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C206:C212">
-    <cfRule type="duplicateValues" dxfId="81" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="C1:C205 C218:C1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="96"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="317" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A68C04BF-F8F4-4D3B-AA41-19C29088046B}"/>
+  <xr:revisionPtr revIDLastSave="332" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18B2862D-1BF9-4AE9-8C7C-3FA7A0E682C6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2170" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="495">
   <si>
     <t>Client</t>
   </si>
@@ -1489,6 +1489,42 @@
   </si>
   <si>
     <t>SYTHD260073</t>
+  </si>
+  <si>
+    <t>CLIENT ARTCI SUR LE SITE DE MARCORY</t>
+  </si>
+  <si>
+    <t>DEMANDE INTERNE OCI/ POC CALL CENTER CLIENT AGL</t>
+  </si>
+  <si>
+    <t>STANDARD CHARTERED BANK</t>
+  </si>
+  <si>
+    <t>BUVPN260044</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>BUVPN260037</t>
+  </si>
+  <si>
+    <t>FOUAD GROUPE</t>
+  </si>
+  <si>
+    <t>MARCORY ZONE 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYTHD260076 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEMANDE INTERNE PERMANENT : SITE ODA </t>
+  </si>
+  <si>
+    <t>RIVIERA GOLF 4</t>
+  </si>
+  <si>
+    <t>BUVPN260058</t>
   </si>
 </sst>
 </file>
@@ -1706,7 +1742,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1891,13 +1927,24 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="81">
+  <dxfs count="82">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3043,7 +3090,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:U217"/>
+  <dimension ref="A1:U224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="26" customWidth="1"/>
@@ -16152,7 +16199,7 @@
         <v>46094</v>
       </c>
       <c r="J205" s="24">
-        <f t="shared" ref="J205:J217" si="15">+NETWORKDAYS(H205,I205)</f>
+        <f t="shared" ref="J205:J224" si="15">+NETWORKDAYS(H205,I205)</f>
         <v>18</v>
       </c>
       <c r="K205" s="41" t="s">
@@ -16180,7 +16227,7 @@
         <v>46094</v>
       </c>
       <c r="S205" s="24">
-        <f t="shared" ref="S205:S217" si="16">NETWORKDAYS(H205,R205)</f>
+        <f t="shared" ref="S205:S224" si="16">NETWORKDAYS(H205,R205)</f>
         <v>18</v>
       </c>
       <c r="T205" s="41" t="s">
@@ -17004,6 +17051,482 @@
       </c>
       <c r="U217" s="11" t="s">
         <v>443</v>
+      </c>
+    </row>
+    <row r="218" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A218" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="B218" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C218" s="5">
+        <v>59312351</v>
+      </c>
+      <c r="D218" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E218" s="5">
+        <v>2721252525</v>
+      </c>
+      <c r="F218" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G218" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H218" s="13">
+        <v>46084</v>
+      </c>
+      <c r="I218" s="13">
+        <v>46099</v>
+      </c>
+      <c r="J218" s="24">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="K218" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L218" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M218" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N218" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O218" s="56">
+        <v>150000</v>
+      </c>
+      <c r="P218" s="56">
+        <v>40000</v>
+      </c>
+      <c r="Q218" s="56">
+        <f t="shared" ref="Q218:Q224" si="18">P218+O218</f>
+        <v>190000</v>
+      </c>
+      <c r="R218" s="13">
+        <v>46100</v>
+      </c>
+      <c r="S218" s="24">
+        <f t="shared" si="16"/>
+        <v>13</v>
+      </c>
+      <c r="T218" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="U218" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="219" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A219" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="B219" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C219" s="5">
+        <v>60063122</v>
+      </c>
+      <c r="D219" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="E219" s="5">
+        <v>2721711970</v>
+      </c>
+      <c r="F219" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G219" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H219" s="14">
+        <v>46098</v>
+      </c>
+      <c r="I219" s="13">
+        <v>46100</v>
+      </c>
+      <c r="J219" s="24">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="K219" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L219" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M219" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N219" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O219" s="56">
+        <v>150000</v>
+      </c>
+      <c r="P219" s="56">
+        <v>40000</v>
+      </c>
+      <c r="Q219" s="56">
+        <f t="shared" si="18"/>
+        <v>190000</v>
+      </c>
+      <c r="R219" s="13">
+        <v>46100</v>
+      </c>
+      <c r="S219" s="24">
+        <f t="shared" si="16"/>
+        <v>3</v>
+      </c>
+      <c r="T219" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="U219" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="220" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A220" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B220" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C220" s="5">
+        <v>52805083</v>
+      </c>
+      <c r="D220" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E220" s="5">
+        <v>2722229570</v>
+      </c>
+      <c r="F220" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G220" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H220" s="14">
+        <v>45960</v>
+      </c>
+      <c r="I220" s="32">
+        <v>46037</v>
+      </c>
+      <c r="J220" s="24">
+        <f t="shared" si="15"/>
+        <v>56</v>
+      </c>
+      <c r="K220" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L220" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="M220" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N220" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O220" s="56">
+        <v>150000</v>
+      </c>
+      <c r="P220" s="56">
+        <v>40000</v>
+      </c>
+      <c r="Q220" s="56">
+        <f t="shared" si="18"/>
+        <v>190000</v>
+      </c>
+      <c r="R220" s="13">
+        <v>46100</v>
+      </c>
+      <c r="S220" s="24">
+        <f t="shared" si="16"/>
+        <v>101</v>
+      </c>
+      <c r="T220" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="U220" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="221" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A221" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="B221" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C221" s="12">
+        <v>58897521</v>
+      </c>
+      <c r="D221" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E221" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="F221" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G221" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H221" s="14">
+        <v>46079</v>
+      </c>
+      <c r="I221" s="14">
+        <v>46099</v>
+      </c>
+      <c r="J221" s="24">
+        <f t="shared" si="15"/>
+        <v>15</v>
+      </c>
+      <c r="K221" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L221" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M221" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N221" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="O221" s="19">
+        <v>2400000</v>
+      </c>
+      <c r="P221" s="19">
+        <v>275790</v>
+      </c>
+      <c r="Q221" s="56">
+        <f t="shared" si="18"/>
+        <v>2675790</v>
+      </c>
+      <c r="R221" s="13">
+        <v>46105</v>
+      </c>
+      <c r="S221" s="24">
+        <f t="shared" si="16"/>
+        <v>19</v>
+      </c>
+      <c r="T221" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="U221" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="222" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A222" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="B222" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C222" s="12">
+        <v>58824101</v>
+      </c>
+      <c r="D222" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="E222" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="F222" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G222" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H222" s="14">
+        <v>46076</v>
+      </c>
+      <c r="I222" s="14">
+        <v>46098</v>
+      </c>
+      <c r="J222" s="24">
+        <f t="shared" si="15"/>
+        <v>17</v>
+      </c>
+      <c r="K222" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L222" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M222" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N222" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="O222" s="19">
+        <v>543324</v>
+      </c>
+      <c r="P222" s="19">
+        <v>115000</v>
+      </c>
+      <c r="Q222" s="56">
+        <f t="shared" si="18"/>
+        <v>658324</v>
+      </c>
+      <c r="R222" s="13">
+        <v>46105</v>
+      </c>
+      <c r="S222" s="24">
+        <f t="shared" si="16"/>
+        <v>22</v>
+      </c>
+      <c r="T222" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="U222" s="11" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="223" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A223" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="B223" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C223" s="12">
+        <v>59248227</v>
+      </c>
+      <c r="D223" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="E223" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F223" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G223" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H223" s="14">
+        <v>46083</v>
+      </c>
+      <c r="I223" s="14">
+        <v>46104</v>
+      </c>
+      <c r="J223" s="24">
+        <f t="shared" si="15"/>
+        <v>16</v>
+      </c>
+      <c r="K223" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L223" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M223" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N223" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="O223" s="19">
+        <v>800000</v>
+      </c>
+      <c r="P223" s="19">
+        <v>569818</v>
+      </c>
+      <c r="Q223" s="56">
+        <f t="shared" si="18"/>
+        <v>1369818</v>
+      </c>
+      <c r="R223" s="13">
+        <v>46105</v>
+      </c>
+      <c r="S223" s="24">
+        <f t="shared" si="16"/>
+        <v>17</v>
+      </c>
+      <c r="T223" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="U223" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="224" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A224" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="B224" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C224" s="12">
+        <v>56800015</v>
+      </c>
+      <c r="D224" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="E224" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="F224" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G224" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H224" s="14">
+        <v>46038</v>
+      </c>
+      <c r="I224" s="13">
+        <v>46099</v>
+      </c>
+      <c r="J224" s="24">
+        <f t="shared" si="15"/>
+        <v>44</v>
+      </c>
+      <c r="K224" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L224" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="M224" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N224" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O224" s="56">
+        <v>0</v>
+      </c>
+      <c r="P224" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q224" s="56">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R224" s="13">
+        <v>46106</v>
+      </c>
+      <c r="S224" s="24">
+        <f t="shared" si="16"/>
+        <v>49</v>
+      </c>
+      <c r="T224" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="U224" s="11" t="s">
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -17015,209 +17538,212 @@
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="80" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C205 C225:C1048576">
+    <cfRule type="duplicateValues" dxfId="75" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="97"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C212 C225:C1048576">
+    <cfRule type="duplicateValues" dxfId="73" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="74" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="72" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="70" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="69" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="67" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="66" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="65" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="64" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="63" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="62" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="61" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="60" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="59" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="58" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="57" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="56" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="55" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="54" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="53" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="52" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
-    <cfRule type="duplicateValues" dxfId="51" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="50" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="49" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="47" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="46" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="45" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="44" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="43" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="41" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C114">
-    <cfRule type="duplicateValues" dxfId="40" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="39" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="38" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C157:C160">
-    <cfRule type="duplicateValues" dxfId="36" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C161:C163">
-    <cfRule type="duplicateValues" dxfId="35" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="34" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="32" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C168">
-    <cfRule type="duplicateValues" dxfId="30" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="29" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171">
-    <cfRule type="duplicateValues" dxfId="28" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173">
-    <cfRule type="duplicateValues" dxfId="27" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C175">
-    <cfRule type="duplicateValues" dxfId="24" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="23" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C178">
-    <cfRule type="duplicateValues" dxfId="22" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179">
-    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C206:C212">
-    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
-    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C208">
-    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="14" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="12" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="11" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="10" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="9" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="8" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="7" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="6" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="5" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172">
-    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175">
-    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C212 C218:C1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="91"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C205 C218:C1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="96"/>
+  <conditionalFormatting sqref="C218:C223">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="332" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18B2862D-1BF9-4AE9-8C7C-3FA7A0E682C6}"/>
+  <xr:revisionPtr revIDLastSave="352" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C9C997C-89E1-411E-9C01-855BC6DE31BF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$232</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="509">
   <si>
     <t>Client</t>
   </si>
@@ -1525,6 +1525,48 @@
   </si>
   <si>
     <t>BUVPN260058</t>
+  </si>
+  <si>
+    <t>AMOAMAN &amp; ASSOCIES </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AKOUEDO</t>
+  </si>
+  <si>
+    <t>SYTHD260079</t>
+  </si>
+  <si>
+    <t>80M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOGENA CI  </t>
+  </si>
+  <si>
+    <t>MARCORY  ZONE 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUVPN260059 </t>
+  </si>
+  <si>
+    <t>SYNELIA GROUP AFRIQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINISTERE DE LA DEFENSE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLATEAU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NANO </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DGTCP </t>
+  </si>
+  <si>
+    <t>SOCIETE GEZA EXPERTISE</t>
+  </si>
+  <si>
+    <t>SINOAFRICK AUTO SARL</t>
   </si>
 </sst>
 </file>
@@ -1742,7 +1784,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1928,13 +1970,869 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="82">
+  <dxfs count="167">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3089,8 +3987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:U224"/>
+  <dimension ref="A1:U232"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="26" customWidth="1"/>
@@ -3175,7 +4072,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="58" t="s">
         <v>154</v>
       </c>
@@ -3237,7 +4134,7 @@
       </c>
       <c r="U2" s="65"/>
     </row>
-    <row r="3" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>159</v>
       </c>
@@ -3299,7 +4196,7 @@
       </c>
       <c r="U3" s="65"/>
     </row>
-    <row r="4" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>154</v>
       </c>
@@ -3361,7 +4258,7 @@
       </c>
       <c r="U4" s="65"/>
     </row>
-    <row r="5" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
         <v>154</v>
       </c>
@@ -3423,7 +4320,7 @@
       </c>
       <c r="U5" s="65"/>
     </row>
-    <row r="6" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>164</v>
       </c>
@@ -3485,7 +4382,7 @@
       </c>
       <c r="U6" s="65"/>
     </row>
-    <row r="7" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>165</v>
       </c>
@@ -3547,7 +4444,7 @@
       </c>
       <c r="U7" s="65"/>
     </row>
-    <row r="8" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>166</v>
       </c>
@@ -3609,7 +4506,7 @@
       </c>
       <c r="U8" s="65"/>
     </row>
-    <row r="9" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>169</v>
       </c>
@@ -3671,7 +4568,7 @@
       </c>
       <c r="U9" s="65"/>
     </row>
-    <row r="10" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>172</v>
       </c>
@@ -3733,7 +4630,7 @@
       </c>
       <c r="U10" s="65"/>
     </row>
-    <row r="11" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>172</v>
       </c>
@@ -3795,7 +4692,7 @@
       </c>
       <c r="U11" s="65"/>
     </row>
-    <row r="12" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
         <v>177</v>
       </c>
@@ -3857,7 +4754,7 @@
       </c>
       <c r="U12" s="65"/>
     </row>
-    <row r="13" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
         <v>154</v>
       </c>
@@ -3919,7 +4816,7 @@
       </c>
       <c r="U13" s="65"/>
     </row>
-    <row r="14" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
         <v>154</v>
       </c>
@@ -3981,7 +4878,7 @@
       </c>
       <c r="U14" s="65"/>
     </row>
-    <row r="15" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>172</v>
       </c>
@@ -4043,7 +4940,7 @@
       </c>
       <c r="U15" s="65"/>
     </row>
-    <row r="16" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>154</v>
       </c>
@@ -4105,7 +5002,7 @@
       </c>
       <c r="U16" s="65"/>
     </row>
-    <row r="17" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>154</v>
       </c>
@@ -4167,7 +5064,7 @@
       </c>
       <c r="U17" s="65"/>
     </row>
-    <row r="18" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
         <v>186</v>
       </c>
@@ -4229,7 +5126,7 @@
       </c>
       <c r="U18" s="65"/>
     </row>
-    <row r="19" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>189</v>
       </c>
@@ -4291,7 +5188,7 @@
       </c>
       <c r="U19" s="65"/>
     </row>
-    <row r="20" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
         <v>189</v>
       </c>
@@ -4353,7 +5250,7 @@
       </c>
       <c r="U20" s="65"/>
     </row>
-    <row r="21" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>193</v>
       </c>
@@ -4415,7 +5312,7 @@
       </c>
       <c r="U21" s="65"/>
     </row>
-    <row r="22" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>43</v>
       </c>
@@ -4477,7 +5374,7 @@
       </c>
       <c r="U22" s="65"/>
     </row>
-    <row r="23" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
         <v>201</v>
       </c>
@@ -4539,7 +5436,7 @@
       </c>
       <c r="U23" s="65"/>
     </row>
-    <row r="24" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>204</v>
       </c>
@@ -4601,7 +5498,7 @@
       </c>
       <c r="U24" s="65"/>
     </row>
-    <row r="25" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>206</v>
       </c>
@@ -4663,7 +5560,7 @@
       </c>
       <c r="U25" s="65"/>
     </row>
-    <row r="26" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>207</v>
       </c>
@@ -4725,7 +5622,7 @@
       </c>
       <c r="U26" s="65"/>
     </row>
-    <row r="27" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
         <v>172</v>
       </c>
@@ -4787,7 +5684,7 @@
       </c>
       <c r="U27" s="65"/>
     </row>
-    <row r="28" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
         <v>210</v>
       </c>
@@ -4849,7 +5746,7 @@
       </c>
       <c r="U28" s="65"/>
     </row>
-    <row r="29" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
         <v>213</v>
       </c>
@@ -4911,7 +5808,7 @@
       </c>
       <c r="U29" s="65"/>
     </row>
-    <row r="30" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>217</v>
       </c>
@@ -4973,7 +5870,7 @@
       </c>
       <c r="U30" s="65"/>
     </row>
-    <row r="31" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>218</v>
       </c>
@@ -5035,7 +5932,7 @@
       </c>
       <c r="U31" s="65"/>
     </row>
-    <row r="32" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
         <v>81</v>
       </c>
@@ -5097,7 +5994,7 @@
       </c>
       <c r="U32" s="65"/>
     </row>
-    <row r="33" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
         <v>91</v>
       </c>
@@ -5159,7 +6056,7 @@
       </c>
       <c r="U33" s="65"/>
     </row>
-    <row r="34" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
         <v>91</v>
       </c>
@@ -5221,7 +6118,7 @@
       </c>
       <c r="U34" s="65"/>
     </row>
-    <row r="35" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
         <v>91</v>
       </c>
@@ -5283,7 +6180,7 @@
       </c>
       <c r="U35" s="65"/>
     </row>
-    <row r="36" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12" t="s">
         <v>91</v>
       </c>
@@ -5345,7 +6242,7 @@
       </c>
       <c r="U36" s="65"/>
     </row>
-    <row r="37" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12" t="s">
         <v>91</v>
       </c>
@@ -5407,7 +6304,7 @@
       </c>
       <c r="U37" s="65"/>
     </row>
-    <row r="38" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
         <v>226</v>
       </c>
@@ -5469,7 +6366,7 @@
       </c>
       <c r="U38" s="65"/>
     </row>
-    <row r="39" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
         <v>228</v>
       </c>
@@ -5531,7 +6428,7 @@
       </c>
       <c r="U39" s="65"/>
     </row>
-    <row r="40" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
         <v>91</v>
       </c>
@@ -5593,7 +6490,7 @@
       </c>
       <c r="U40" s="65"/>
     </row>
-    <row r="41" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
         <v>231</v>
       </c>
@@ -5655,7 +6552,7 @@
       </c>
       <c r="U41" s="65"/>
     </row>
-    <row r="42" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
         <v>234</v>
       </c>
@@ -5717,7 +6614,7 @@
       </c>
       <c r="U42" s="65"/>
     </row>
-    <row r="43" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>236</v>
       </c>
@@ -5779,7 +6676,7 @@
       </c>
       <c r="U43" s="65"/>
     </row>
-    <row r="44" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
         <v>237</v>
       </c>
@@ -5841,7 +6738,7 @@
       </c>
       <c r="U44" s="65"/>
     </row>
-    <row r="45" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
         <v>238</v>
       </c>
@@ -5903,7 +6800,7 @@
       </c>
       <c r="U45" s="65"/>
     </row>
-    <row r="46" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="12" t="s">
         <v>240</v>
       </c>
@@ -5965,7 +6862,7 @@
       </c>
       <c r="U46" s="65"/>
     </row>
-    <row r="47" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="12" t="s">
         <v>91</v>
       </c>
@@ -6027,7 +6924,7 @@
       </c>
       <c r="U47" s="65"/>
     </row>
-    <row r="48" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="12" t="s">
         <v>243</v>
       </c>
@@ -6089,7 +6986,7 @@
       </c>
       <c r="U48" s="65"/>
     </row>
-    <row r="49" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="12" t="s">
         <v>246</v>
       </c>
@@ -6151,7 +7048,7 @@
       </c>
       <c r="U49" s="65"/>
     </row>
-    <row r="50" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12" t="s">
         <v>248</v>
       </c>
@@ -6213,7 +7110,7 @@
       </c>
       <c r="U50" s="65"/>
     </row>
-    <row r="51" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="12" t="s">
         <v>250</v>
       </c>
@@ -6275,7 +7172,7 @@
       </c>
       <c r="U51" s="65"/>
     </row>
-    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" s="12" t="s">
         <v>250</v>
       </c>
@@ -6337,7 +7234,7 @@
       </c>
       <c r="U52" s="65"/>
     </row>
-    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" s="12" t="s">
         <v>253</v>
       </c>
@@ -6399,7 +7296,7 @@
       </c>
       <c r="U53" s="65"/>
     </row>
-    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
         <v>256</v>
       </c>
@@ -6461,7 +7358,7 @@
       </c>
       <c r="U54" s="65"/>
     </row>
-    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>258</v>
       </c>
@@ -6523,7 +7420,7 @@
       </c>
       <c r="U55" s="65"/>
     </row>
-    <row r="56" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" s="12" t="s">
         <v>259</v>
       </c>
@@ -6585,7 +7482,7 @@
       </c>
       <c r="U56" s="65"/>
     </row>
-    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A57" s="12" t="s">
         <v>259</v>
       </c>
@@ -6647,7 +7544,7 @@
       </c>
       <c r="U57" s="65"/>
     </row>
-    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A58" s="12" t="s">
         <v>253</v>
       </c>
@@ -6709,7 +7606,7 @@
       </c>
       <c r="U58" s="65"/>
     </row>
-    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A59" s="12" t="s">
         <v>265</v>
       </c>
@@ -6771,7 +7668,7 @@
       </c>
       <c r="U59" s="65"/>
     </row>
-    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A60" s="12" t="s">
         <v>267</v>
       </c>
@@ -6833,7 +7730,7 @@
       </c>
       <c r="U60" s="65"/>
     </row>
-    <row r="61" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A61" s="12" t="s">
         <v>271</v>
       </c>
@@ -6895,7 +7792,7 @@
       </c>
       <c r="U61" s="65"/>
     </row>
-    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A62" s="12" t="s">
         <v>43</v>
       </c>
@@ -6957,7 +7854,7 @@
       </c>
       <c r="U62" s="65"/>
     </row>
-    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A63" s="11" t="s">
         <v>58</v>
       </c>
@@ -7019,7 +7916,7 @@
       </c>
       <c r="U63" s="65"/>
     </row>
-    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A64" s="12" t="s">
         <v>91</v>
       </c>
@@ -7081,7 +7978,7 @@
       </c>
       <c r="U64" s="65"/>
     </row>
-    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A65" s="12" t="s">
         <v>91</v>
       </c>
@@ -7143,7 +8040,7 @@
       </c>
       <c r="U65" s="65"/>
     </row>
-    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A66" s="12" t="s">
         <v>91</v>
       </c>
@@ -7205,7 +8102,7 @@
       </c>
       <c r="U66" s="65"/>
     </row>
-    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A67" s="12" t="s">
         <v>282</v>
       </c>
@@ -7267,7 +8164,7 @@
       </c>
       <c r="U67" s="65"/>
     </row>
-    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>285</v>
       </c>
@@ -7329,7 +8226,7 @@
       </c>
       <c r="U68" s="65"/>
     </row>
-    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A69" s="12" t="s">
         <v>286</v>
       </c>
@@ -7391,7 +8288,7 @@
       </c>
       <c r="U69" s="65"/>
     </row>
-    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A70" s="22" t="s">
         <v>288</v>
       </c>
@@ -7453,7 +8350,7 @@
       </c>
       <c r="U70" s="65"/>
     </row>
-    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>291</v>
       </c>
@@ -7515,7 +8412,7 @@
       </c>
       <c r="U71" s="65"/>
     </row>
-    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>292</v>
       </c>
@@ -7577,7 +8474,7 @@
       </c>
       <c r="U72" s="65"/>
     </row>
-    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A73" s="12" t="s">
         <v>91</v>
       </c>
@@ -7639,7 +8536,7 @@
       </c>
       <c r="U73" s="65"/>
     </row>
-    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A74" s="12" t="s">
         <v>294</v>
       </c>
@@ -7701,7 +8598,7 @@
       </c>
       <c r="U74" s="65"/>
     </row>
-    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A75" s="12" t="s">
         <v>91</v>
       </c>
@@ -7763,7 +8660,7 @@
       </c>
       <c r="U75" s="65"/>
     </row>
-    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A76" s="12" t="s">
         <v>299</v>
       </c>
@@ -7825,7 +8722,7 @@
       </c>
       <c r="U76" s="65"/>
     </row>
-    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A77" s="12" t="s">
         <v>18</v>
       </c>
@@ -7887,7 +8784,7 @@
       </c>
       <c r="U77" s="65"/>
     </row>
-    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A78" s="12" t="s">
         <v>27</v>
       </c>
@@ -7949,7 +8846,7 @@
       </c>
       <c r="U78" s="65"/>
     </row>
-    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
         <v>30</v>
       </c>
@@ -8011,7 +8908,7 @@
       </c>
       <c r="U79" s="65"/>
     </row>
-    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A80" s="12" t="s">
         <v>35</v>
       </c>
@@ -8073,7 +8970,7 @@
       </c>
       <c r="U80" s="65"/>
     </row>
-    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A81" s="12" t="s">
         <v>35</v>
       </c>
@@ -8135,7 +9032,7 @@
       </c>
       <c r="U81" s="65"/>
     </row>
-    <row r="82" spans="1:21" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="12" t="s">
         <v>35</v>
       </c>
@@ -8197,7 +9094,7 @@
       </c>
       <c r="U82" s="65"/>
     </row>
-    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A83" s="12" t="s">
         <v>43</v>
       </c>
@@ -8259,7 +9156,7 @@
       </c>
       <c r="U83" s="65"/>
     </row>
-    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A84" s="12" t="s">
         <v>43</v>
       </c>
@@ -8321,7 +9218,7 @@
       </c>
       <c r="U84" s="65"/>
     </row>
-    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A85" s="12" t="s">
         <v>52</v>
       </c>
@@ -8383,7 +9280,7 @@
       </c>
       <c r="U85" s="65"/>
     </row>
-    <row r="86" spans="1:21" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="6" t="s">
         <v>55</v>
       </c>
@@ -8445,7 +9342,7 @@
       </c>
       <c r="U86" s="65"/>
     </row>
-    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A87" s="22" t="s">
         <v>58</v>
       </c>
@@ -8507,7 +9404,7 @@
       </c>
       <c r="U87" s="65"/>
     </row>
-    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A88" s="12" t="s">
         <v>62</v>
       </c>
@@ -8569,7 +9466,7 @@
       </c>
       <c r="U88" s="65"/>
     </row>
-    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A89" s="12" t="s">
         <v>65</v>
       </c>
@@ -8631,7 +9528,7 @@
       </c>
       <c r="U89" s="65"/>
     </row>
-    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A90" s="12" t="s">
         <v>67</v>
       </c>
@@ -8693,7 +9590,7 @@
       </c>
       <c r="U90" s="65"/>
     </row>
-    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A91" s="12" t="s">
         <v>70</v>
       </c>
@@ -8755,7 +9652,7 @@
       </c>
       <c r="U91" s="65"/>
     </row>
-    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A92" s="12" t="s">
         <v>75</v>
       </c>
@@ -8817,7 +9714,7 @@
       </c>
       <c r="U92" s="65"/>
     </row>
-    <row r="93" spans="1:21" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="29" t="s">
         <v>77</v>
       </c>
@@ -8879,7 +9776,7 @@
       </c>
       <c r="U93" s="65"/>
     </row>
-    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A94" s="12" t="s">
         <v>43</v>
       </c>
@@ -8941,7 +9838,7 @@
       </c>
       <c r="U94" s="65"/>
     </row>
-    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A95" s="12" t="s">
         <v>81</v>
       </c>
@@ -9003,7 +9900,7 @@
       </c>
       <c r="U95" s="65"/>
     </row>
-    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A96" s="8" t="s">
         <v>85</v>
       </c>
@@ -9065,7 +9962,7 @@
       </c>
       <c r="U96" s="65"/>
     </row>
-    <row r="97" spans="1:21" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
         <v>86</v>
       </c>
@@ -9127,7 +10024,7 @@
       </c>
       <c r="U97" s="65"/>
     </row>
-    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98" s="12" t="s">
         <v>88</v>
       </c>
@@ -9189,7 +10086,7 @@
       </c>
       <c r="U98" s="65"/>
     </row>
-    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99" s="12" t="s">
         <v>91</v>
       </c>
@@ -9251,7 +10148,7 @@
       </c>
       <c r="U99" s="65"/>
     </row>
-    <row r="100" spans="1:21" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="29" t="s">
         <v>95</v>
       </c>
@@ -9313,7 +10210,7 @@
       </c>
       <c r="U100" s="65"/>
     </row>
-    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101" s="12" t="s">
         <v>58</v>
       </c>
@@ -9375,7 +10272,7 @@
       </c>
       <c r="U101" s="65"/>
     </row>
-    <row r="102" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102" s="22" t="s">
         <v>58</v>
       </c>
@@ -9437,7 +10334,7 @@
       </c>
       <c r="U102" s="65"/>
     </row>
-    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A103" s="12" t="s">
         <v>43</v>
       </c>
@@ -9499,7 +10396,7 @@
       </c>
       <c r="U103" s="65"/>
     </row>
-    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104" s="12" t="s">
         <v>103</v>
       </c>
@@ -9561,7 +10458,7 @@
       </c>
       <c r="U104" s="65"/>
     </row>
-    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>106</v>
       </c>
@@ -9623,7 +10520,7 @@
       </c>
       <c r="U105" s="65"/>
     </row>
-    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>81</v>
       </c>
@@ -9685,7 +10582,7 @@
       </c>
       <c r="U106" s="65"/>
     </row>
-    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>107</v>
       </c>
@@ -9747,7 +10644,7 @@
       </c>
       <c r="U107" s="65"/>
     </row>
-    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>108</v>
       </c>
@@ -9809,7 +10706,7 @@
       </c>
       <c r="U108" s="65"/>
     </row>
-    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
         <v>109</v>
       </c>
@@ -9871,7 +10768,7 @@
       </c>
       <c r="U109" s="65"/>
     </row>
-    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A110" s="12" t="s">
         <v>110</v>
       </c>
@@ -9933,7 +10830,7 @@
       </c>
       <c r="U110" s="65"/>
     </row>
-    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A111" s="12" t="s">
         <v>113</v>
       </c>
@@ -9995,7 +10892,7 @@
       </c>
       <c r="U111" s="65"/>
     </row>
-    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A112" s="11" t="s">
         <v>116</v>
       </c>
@@ -10057,7 +10954,7 @@
       </c>
       <c r="U112" s="65"/>
     </row>
-    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A113" s="12" t="s">
         <v>120</v>
       </c>
@@ -10119,7 +11016,7 @@
       </c>
       <c r="U113" s="65"/>
     </row>
-    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A114" s="12" t="s">
         <v>123</v>
       </c>
@@ -10181,7 +11078,7 @@
       </c>
       <c r="U114" s="65"/>
     </row>
-    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A115" s="12" t="s">
         <v>110</v>
       </c>
@@ -10243,7 +11140,7 @@
       </c>
       <c r="U115" s="65"/>
     </row>
-    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A116" s="12" t="s">
         <v>127</v>
       </c>
@@ -10305,7 +11202,7 @@
       </c>
       <c r="U116" s="65"/>
     </row>
-    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
         <v>130</v>
       </c>
@@ -10367,7 +11264,7 @@
       </c>
       <c r="U117" s="65"/>
     </row>
-    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
         <v>131</v>
       </c>
@@ -10429,7 +11326,7 @@
       </c>
       <c r="U118" s="65"/>
     </row>
-    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A119" s="12" t="s">
         <v>132</v>
       </c>
@@ -10491,7 +11388,7 @@
       </c>
       <c r="U119" s="65"/>
     </row>
-    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A120" s="12" t="s">
         <v>134</v>
       </c>
@@ -10553,7 +11450,7 @@
       </c>
       <c r="U120" s="65"/>
     </row>
-    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A121" s="12" t="s">
         <v>134</v>
       </c>
@@ -10615,7 +11512,7 @@
       </c>
       <c r="U121" s="65"/>
     </row>
-    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A122" s="12" t="s">
         <v>140</v>
       </c>
@@ -10677,7 +11574,7 @@
       </c>
       <c r="U122" s="65"/>
     </row>
-    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A123" s="12" t="s">
         <v>143</v>
       </c>
@@ -10739,7 +11636,7 @@
       </c>
       <c r="U123" s="65"/>
     </row>
-    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A124" s="12" t="s">
         <v>145</v>
       </c>
@@ -10801,7 +11698,7 @@
       </c>
       <c r="U124" s="65"/>
     </row>
-    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A125" s="12" t="s">
         <v>149</v>
       </c>
@@ -10863,7 +11760,7 @@
       </c>
       <c r="U125" s="65"/>
     </row>
-    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A126" s="12" t="s">
         <v>143</v>
       </c>
@@ -10925,7 +11822,7 @@
       </c>
       <c r="U126" s="65"/>
     </row>
-    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A127" s="12" t="s">
         <v>301</v>
       </c>
@@ -10991,7 +11888,7 @@
       </c>
       <c r="U127" s="65"/>
     </row>
-    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A128" s="12" t="s">
         <v>305</v>
       </c>
@@ -11057,7 +11954,7 @@
       </c>
       <c r="U128" s="65"/>
     </row>
-    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A129" s="12" t="s">
         <v>145</v>
       </c>
@@ -11123,7 +12020,7 @@
       </c>
       <c r="U129" s="65"/>
     </row>
-    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
         <v>308</v>
       </c>
@@ -11189,7 +12086,7 @@
       </c>
       <c r="U130" s="65"/>
     </row>
-    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A131" s="9" t="s">
         <v>309</v>
       </c>
@@ -11255,7 +12152,7 @@
       </c>
       <c r="U131" s="65"/>
     </row>
-    <row r="132" spans="1:21" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:21" s="26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A132" s="22" t="s">
         <v>311</v>
       </c>
@@ -11321,7 +12218,7 @@
       </c>
       <c r="U132" s="66"/>
     </row>
-    <row r="133" spans="1:21" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:21" s="26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A133" s="12" t="s">
         <v>311</v>
       </c>
@@ -11387,7 +12284,7 @@
       </c>
       <c r="U133" s="66"/>
     </row>
-    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A134" s="12" t="s">
         <v>317</v>
       </c>
@@ -11453,7 +12350,7 @@
       </c>
       <c r="U134" s="65"/>
     </row>
-    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A135" s="9" t="s">
         <v>320</v>
       </c>
@@ -11519,7 +12416,7 @@
       </c>
       <c r="U135" s="65"/>
     </row>
-    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A136" s="9" t="s">
         <v>321</v>
       </c>
@@ -11585,7 +12482,7 @@
       </c>
       <c r="U136" s="65"/>
     </row>
-    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A137" s="9" t="s">
         <v>321</v>
       </c>
@@ -11651,7 +12548,7 @@
       </c>
       <c r="U137" s="65"/>
     </row>
-    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A138" s="9" t="s">
         <v>322</v>
       </c>
@@ -11717,7 +12614,7 @@
       </c>
       <c r="U138" s="65"/>
     </row>
-    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A139" s="9" t="s">
         <v>323</v>
       </c>
@@ -11783,7 +12680,7 @@
       </c>
       <c r="U139" s="65"/>
     </row>
-    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
         <v>324</v>
       </c>
@@ -11849,7 +12746,7 @@
       </c>
       <c r="U140" s="65"/>
     </row>
-    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
         <v>326</v>
       </c>
@@ -11915,7 +12812,7 @@
       </c>
       <c r="U141" s="65"/>
     </row>
-    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A142" s="12" t="s">
         <v>328</v>
       </c>
@@ -11981,7 +12878,7 @@
       </c>
       <c r="U142" s="65"/>
     </row>
-    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A143" s="12" t="s">
         <v>331</v>
       </c>
@@ -12047,7 +12944,7 @@
       </c>
       <c r="U143" s="65"/>
     </row>
-    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A144" s="12" t="s">
         <v>333</v>
       </c>
@@ -12113,7 +13010,7 @@
       </c>
       <c r="U144" s="65"/>
     </row>
-    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A145" s="12" t="s">
         <v>335</v>
       </c>
@@ -12179,7 +13076,7 @@
       </c>
       <c r="U145" s="65"/>
     </row>
-    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A146" s="12" t="s">
         <v>140</v>
       </c>
@@ -12245,7 +13142,7 @@
       </c>
       <c r="U146" s="65"/>
     </row>
-    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A147" s="12" t="s">
         <v>140</v>
       </c>
@@ -12311,7 +13208,7 @@
       </c>
       <c r="U147" s="65"/>
     </row>
-    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A148" s="22" t="s">
         <v>58</v>
       </c>
@@ -16199,7 +17096,7 @@
         <v>46094</v>
       </c>
       <c r="J205" s="24">
-        <f t="shared" ref="J205:J224" si="15">+NETWORKDAYS(H205,I205)</f>
+        <f t="shared" ref="J205:J232" si="15">+NETWORKDAYS(H205,I205)</f>
         <v>18</v>
       </c>
       <c r="K205" s="41" t="s">
@@ -16227,7 +17124,7 @@
         <v>46094</v>
       </c>
       <c r="S205" s="24">
-        <f t="shared" ref="S205:S224" si="16">NETWORKDAYS(H205,R205)</f>
+        <f t="shared" ref="S205:S232" si="16">NETWORKDAYS(H205,R205)</f>
         <v>18</v>
       </c>
       <c r="T205" s="41" t="s">
@@ -17529,220 +18426,764 @@
         <v>444</v>
       </c>
     </row>
+    <row r="225" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A225" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="B225" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C225" s="5">
+        <v>59889656</v>
+      </c>
+      <c r="D225" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="E225" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="F225" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G225" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H225" s="13">
+        <v>46094</v>
+      </c>
+      <c r="I225" s="13">
+        <v>46107</v>
+      </c>
+      <c r="J225" s="24">
+        <f t="shared" si="15"/>
+        <v>10</v>
+      </c>
+      <c r="K225" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L225" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M225" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N225" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="O225" s="56">
+        <v>600000</v>
+      </c>
+      <c r="P225" s="56">
+        <v>60000</v>
+      </c>
+      <c r="Q225" s="56">
+        <f t="shared" ref="Q225:Q232" si="19">P225+O225</f>
+        <v>660000</v>
+      </c>
+      <c r="R225" s="13">
+        <v>46108</v>
+      </c>
+      <c r="S225" s="24">
+        <f t="shared" si="16"/>
+        <v>11</v>
+      </c>
+      <c r="T225" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="U225" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="226" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A226" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C226" s="5">
+        <v>60025705</v>
+      </c>
+      <c r="D226" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="E226" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="F226" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G226" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H226" s="13">
+        <v>46098</v>
+      </c>
+      <c r="I226" s="13">
+        <v>46107</v>
+      </c>
+      <c r="J226" s="24">
+        <f t="shared" si="15"/>
+        <v>8</v>
+      </c>
+      <c r="K226" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L226" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M226" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N226" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="O226" s="56">
+        <v>0</v>
+      </c>
+      <c r="P226" s="56">
+        <v>0</v>
+      </c>
+      <c r="Q226" s="56">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R226" s="13">
+        <v>46108</v>
+      </c>
+      <c r="S226" s="24">
+        <f t="shared" si="16"/>
+        <v>9</v>
+      </c>
+      <c r="T226" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="U226" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="227" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A227" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C227" s="5">
+        <v>59834036</v>
+      </c>
+      <c r="D227" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E227" s="5">
+        <v>2722516010</v>
+      </c>
+      <c r="F227" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G227" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H227" s="13">
+        <v>46093</v>
+      </c>
+      <c r="I227" s="13">
+        <v>46106</v>
+      </c>
+      <c r="J227" s="24">
+        <f t="shared" si="15"/>
+        <v>10</v>
+      </c>
+      <c r="K227" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L227" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M227" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N227" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O227" s="69">
+        <v>570000</v>
+      </c>
+      <c r="P227" s="69">
+        <v>141635</v>
+      </c>
+      <c r="Q227" s="56">
+        <f t="shared" si="19"/>
+        <v>711635</v>
+      </c>
+      <c r="R227" s="13">
+        <v>46108</v>
+      </c>
+      <c r="S227" s="24">
+        <f t="shared" si="16"/>
+        <v>12</v>
+      </c>
+      <c r="T227" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="U227" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="228" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A228" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C228" s="5">
+        <v>58407509</v>
+      </c>
+      <c r="D228" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="E228" s="5">
+        <v>2720238050</v>
+      </c>
+      <c r="F228" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G228" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H228" s="13">
+        <v>46069</v>
+      </c>
+      <c r="I228" s="13">
+        <v>46107</v>
+      </c>
+      <c r="J228" s="24">
+        <f t="shared" si="15"/>
+        <v>29</v>
+      </c>
+      <c r="K228" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L228" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M228" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N228" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="O228" s="69">
+        <v>1000000</v>
+      </c>
+      <c r="P228" s="69">
+        <v>231750</v>
+      </c>
+      <c r="Q228" s="56">
+        <f t="shared" si="19"/>
+        <v>1231750</v>
+      </c>
+      <c r="R228" s="13">
+        <v>46108</v>
+      </c>
+      <c r="S228" s="24">
+        <f t="shared" si="16"/>
+        <v>30</v>
+      </c>
+      <c r="T228" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="U228" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="229" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A229" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C229" s="9">
+        <v>54992969</v>
+      </c>
+      <c r="D229" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E229" s="9">
+        <v>2723489320</v>
+      </c>
+      <c r="F229" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G229" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H229" s="13">
+        <v>46002</v>
+      </c>
+      <c r="I229" s="13">
+        <v>46035</v>
+      </c>
+      <c r="J229" s="24">
+        <f t="shared" si="15"/>
+        <v>24</v>
+      </c>
+      <c r="K229" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L229" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="M229" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N229" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="O229" s="70">
+        <v>1000000</v>
+      </c>
+      <c r="P229" s="70">
+        <v>231750</v>
+      </c>
+      <c r="Q229" s="56">
+        <f t="shared" si="19"/>
+        <v>1231750</v>
+      </c>
+      <c r="R229" s="13">
+        <v>46108</v>
+      </c>
+      <c r="S229" s="24">
+        <f t="shared" si="16"/>
+        <v>77</v>
+      </c>
+      <c r="T229" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="U229" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="230" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A230" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="B230" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C230" s="9">
+        <v>59888143</v>
+      </c>
+      <c r="D230" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E230" s="9">
+        <v>2720219745</v>
+      </c>
+      <c r="F230" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G230" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H230" s="13">
+        <v>46094</v>
+      </c>
+      <c r="I230" s="13">
+        <v>46108</v>
+      </c>
+      <c r="J230" s="24">
+        <f t="shared" si="15"/>
+        <v>11</v>
+      </c>
+      <c r="K230" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L230" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M230" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N230" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O230" s="70">
+        <v>150000</v>
+      </c>
+      <c r="P230" s="70">
+        <v>40000</v>
+      </c>
+      <c r="Q230" s="56">
+        <f t="shared" si="19"/>
+        <v>190000</v>
+      </c>
+      <c r="R230" s="13">
+        <v>46108</v>
+      </c>
+      <c r="S230" s="24">
+        <f t="shared" si="16"/>
+        <v>11</v>
+      </c>
+      <c r="T230" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="U230" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="231" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A231" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="B231" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C231" s="9">
+        <v>60084243</v>
+      </c>
+      <c r="D231" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E231" s="9">
+        <v>2722487090</v>
+      </c>
+      <c r="F231" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G231" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H231" s="13">
+        <v>46098</v>
+      </c>
+      <c r="I231" s="13">
+        <v>46108</v>
+      </c>
+      <c r="J231" s="24">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="K231" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L231" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M231" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N231" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O231" s="70">
+        <v>570000</v>
+      </c>
+      <c r="P231" s="70">
+        <v>221635</v>
+      </c>
+      <c r="Q231" s="56">
+        <f t="shared" si="19"/>
+        <v>791635</v>
+      </c>
+      <c r="R231" s="13">
+        <v>46108</v>
+      </c>
+      <c r="S231" s="24">
+        <f t="shared" si="16"/>
+        <v>9</v>
+      </c>
+      <c r="T231" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="U231" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="232" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A232" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="B232" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C232" s="9">
+        <v>58650374</v>
+      </c>
+      <c r="D232" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E232" s="9">
+        <v>2722229765</v>
+      </c>
+      <c r="F232" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G232" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H232" s="13">
+        <v>46073</v>
+      </c>
+      <c r="I232" s="13">
+        <v>46108</v>
+      </c>
+      <c r="J232" s="24">
+        <f t="shared" si="15"/>
+        <v>26</v>
+      </c>
+      <c r="K232" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L232" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M232" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N232" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O232" s="70">
+        <v>150000</v>
+      </c>
+      <c r="P232" s="70">
+        <v>60000</v>
+      </c>
+      <c r="Q232" s="56">
+        <f t="shared" si="19"/>
+        <v>210000</v>
+      </c>
+      <c r="R232" s="13">
+        <v>46108</v>
+      </c>
+      <c r="S232" s="24">
+        <f t="shared" si="16"/>
+        <v>26</v>
+      </c>
+      <c r="T232" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="U232" s="11" t="s">
+        <v>443</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U217" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="17">
-      <filters>
-        <dateGroupItem year="2026" month="3" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:U232" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="81" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="83"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C205 C225:C1048576">
-    <cfRule type="duplicateValues" dxfId="75" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="97"/>
+  <conditionalFormatting sqref="C1:C205 C233:C1048576">
+    <cfRule type="duplicateValues" dxfId="160" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="99"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C212 C225:C1048576">
-    <cfRule type="duplicateValues" dxfId="73" priority="92"/>
+  <conditionalFormatting sqref="C1:C212 C233:C1048576">
+    <cfRule type="duplicateValues" dxfId="158" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="72" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="70" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="68" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="67" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="65" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="64" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="63" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="62" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="61" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="60" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="59" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="58" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="57" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="56" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="55" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="54" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="53" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="52" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="51" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="50" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
-    <cfRule type="duplicateValues" dxfId="49" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="48" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="47" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="45" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="44" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="43" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="42" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="41" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="39" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C114">
-    <cfRule type="duplicateValues" dxfId="38" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="37" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="36" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C157:C160">
-    <cfRule type="duplicateValues" dxfId="34" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C161:C163">
-    <cfRule type="duplicateValues" dxfId="33" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="32" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="30" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C168">
-    <cfRule type="duplicateValues" dxfId="28" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="27" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171">
-    <cfRule type="duplicateValues" dxfId="26" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173">
-    <cfRule type="duplicateValues" dxfId="25" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="23" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C175">
-    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C178">
-    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179">
-    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C206:C212">
-    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
-    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C208">
-    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C218:C223">
+    <cfRule type="duplicateValues" dxfId="97" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="12" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="10" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="9" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="8" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="7" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="6" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="5" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="4" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="3" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172">
-    <cfRule type="duplicateValues" dxfId="2" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175">
-    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C218:C223">
+  <conditionalFormatting sqref="C225:C232">
+    <cfRule type="duplicateValues" dxfId="84" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="352" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C9C997C-89E1-411E-9C01-855BC6DE31BF}"/>
+  <xr:revisionPtr revIDLastSave="368" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D3CE027-A40C-4B48-B0E9-C9AFCEA2FBA0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$243</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="533">
   <si>
     <t>Client</t>
   </si>
@@ -1567,6 +1567,78 @@
   </si>
   <si>
     <t>SINOAFRICK AUTO SARL</t>
+  </si>
+  <si>
+    <t>SOGENA</t>
+  </si>
+  <si>
+    <t>60025705 </t>
+  </si>
+  <si>
+    <t>BUVPN260059</t>
+  </si>
+  <si>
+    <t>LTE</t>
+  </si>
+  <si>
+    <t>BACK UP</t>
+  </si>
+  <si>
+    <t>BASE AERIENN KORHOGO</t>
+  </si>
+  <si>
+    <t>SYTHD260075</t>
+  </si>
+  <si>
+    <t>FESTIVAL YAKRO YÔFÊ 9</t>
+  </si>
+  <si>
+    <t>BUVPN260065</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>SYTHD260084</t>
+  </si>
+  <si>
+    <t>CTCI</t>
+  </si>
+  <si>
+    <t>BUVPN260063</t>
+  </si>
+  <si>
+    <t>DIRECTION GENERALE DES DOUANES GREENWAYS</t>
+  </si>
+  <si>
+    <t>BUVPN260057</t>
+  </si>
+  <si>
+    <t>IFM</t>
+  </si>
+  <si>
+    <t>SYTHD260082</t>
+  </si>
+  <si>
+    <t>MAXAM CI</t>
+  </si>
+  <si>
+    <t>SYTHD260080</t>
+  </si>
+  <si>
+    <t>BGFI SERVICE SIMAO</t>
+  </si>
+  <si>
+    <t>COCODY VALLON</t>
+  </si>
+  <si>
+    <t>BUVPN260055</t>
+  </si>
+  <si>
+    <t>BUVPN260056</t>
+  </si>
+  <si>
+    <t>BUVPN260062</t>
   </si>
 </sst>
 </file>
@@ -1580,7 +1652,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,##0\ _€"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1685,6 +1757,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1784,7 +1863,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1976,823 +2055,43 @@
     <xf numFmtId="167" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="167">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="86">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3987,7 +3286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U232"/>
+  <dimension ref="A1:U243"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="26" customWidth="1"/>
@@ -4004,7 +3303,7 @@
     <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.1796875" customWidth="1"/>
     <col min="20" max="20" width="6.54296875" customWidth="1"/>
-    <col min="21" max="21" width="13.7265625" style="67" customWidth="1"/>
+    <col min="21" max="21" width="9.6328125" style="67" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
@@ -17096,7 +16395,7 @@
         <v>46094</v>
       </c>
       <c r="J205" s="24">
-        <f t="shared" ref="J205:J232" si="15">+NETWORKDAYS(H205,I205)</f>
+        <f t="shared" ref="J205:J243" si="15">+NETWORKDAYS(H205,I205)</f>
         <v>18</v>
       </c>
       <c r="K205" s="41" t="s">
@@ -17124,7 +16423,7 @@
         <v>46094</v>
       </c>
       <c r="S205" s="24">
-        <f t="shared" ref="S205:S232" si="16">NETWORKDAYS(H205,R205)</f>
+        <f t="shared" ref="S205:S243" si="16">NETWORKDAYS(H205,R205)</f>
         <v>18</v>
       </c>
       <c r="T205" s="41" t="s">
@@ -18970,221 +18269,973 @@
         <v>443</v>
       </c>
     </row>
+    <row r="233" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A233" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="D233" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E233" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="F233" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="G233" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="H233" s="71">
+        <v>46098</v>
+      </c>
+      <c r="I233" s="71">
+        <v>46107</v>
+      </c>
+      <c r="J233" s="24">
+        <f t="shared" si="15"/>
+        <v>8</v>
+      </c>
+      <c r="K233" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="L233" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M233" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N233" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="O233" s="5">
+        <v>0</v>
+      </c>
+      <c r="P233" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q233" s="5">
+        <v>0</v>
+      </c>
+      <c r="R233" s="50">
+        <v>46108</v>
+      </c>
+      <c r="S233" s="24">
+        <f t="shared" si="16"/>
+        <v>9</v>
+      </c>
+      <c r="T233" s="48" t="s">
+        <v>487</v>
+      </c>
+      <c r="U233" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="234" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A234" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C234" s="5">
+        <v>57773018</v>
+      </c>
+      <c r="D234" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="E234" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="F234" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G234" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H234" s="71">
+        <v>46057</v>
+      </c>
+      <c r="I234" s="71">
+        <v>46107</v>
+      </c>
+      <c r="J234" s="24">
+        <f t="shared" si="15"/>
+        <v>37</v>
+      </c>
+      <c r="K234" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="L234" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M234" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N234" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="O234" s="15">
+        <v>2600000</v>
+      </c>
+      <c r="P234" s="15">
+        <v>1034117</v>
+      </c>
+      <c r="Q234" s="15">
+        <v>3634117</v>
+      </c>
+      <c r="R234" s="50">
+        <v>46108</v>
+      </c>
+      <c r="S234" s="24">
+        <f t="shared" si="16"/>
+        <v>38</v>
+      </c>
+      <c r="T234" s="48" t="s">
+        <v>487</v>
+      </c>
+      <c r="U234" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="235" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A235" s="72" t="s">
+        <v>516</v>
+      </c>
+      <c r="B235" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="C235" s="72">
+        <v>60423011</v>
+      </c>
+      <c r="D235" s="73" t="s">
+        <v>146</v>
+      </c>
+      <c r="E235" s="72" t="s">
+        <v>517</v>
+      </c>
+      <c r="F235" s="73" t="s">
+        <v>47</v>
+      </c>
+      <c r="G235" s="73" t="s">
+        <v>23</v>
+      </c>
+      <c r="H235" s="74">
+        <v>46105</v>
+      </c>
+      <c r="I235" s="74">
+        <v>46111</v>
+      </c>
+      <c r="J235" s="24">
+        <f t="shared" si="15"/>
+        <v>5</v>
+      </c>
+      <c r="K235" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L235" s="73" t="s">
+        <v>304</v>
+      </c>
+      <c r="M235" s="73" t="s">
+        <v>358</v>
+      </c>
+      <c r="N235" s="73" t="s">
+        <v>29</v>
+      </c>
+      <c r="O235" s="76">
+        <v>0</v>
+      </c>
+      <c r="P235" s="76">
+        <v>0</v>
+      </c>
+      <c r="Q235" s="76">
+        <f t="shared" ref="Q235:Q243" si="20">P235+O235</f>
+        <v>0</v>
+      </c>
+      <c r="R235" s="77">
+        <v>46111</v>
+      </c>
+      <c r="S235" s="24">
+        <f t="shared" si="16"/>
+        <v>5</v>
+      </c>
+      <c r="T235" s="73" t="s">
+        <v>518</v>
+      </c>
+      <c r="U235" s="73" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="236" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A236" s="41" t="s">
+        <v>516</v>
+      </c>
+      <c r="B236" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C236" s="41">
+        <v>60422373</v>
+      </c>
+      <c r="D236" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="E236" s="41" t="s">
+        <v>519</v>
+      </c>
+      <c r="F236" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="G236" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="H236" s="42">
+        <v>46105</v>
+      </c>
+      <c r="I236" s="42">
+        <v>46111</v>
+      </c>
+      <c r="J236" s="24">
+        <f t="shared" si="15"/>
+        <v>5</v>
+      </c>
+      <c r="K236" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="L236" s="48" t="s">
+        <v>304</v>
+      </c>
+      <c r="M236" s="48" t="s">
+        <v>358</v>
+      </c>
+      <c r="N236" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="O236" s="78">
+        <v>0</v>
+      </c>
+      <c r="P236" s="78">
+        <v>0</v>
+      </c>
+      <c r="Q236" s="78">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R236" s="50">
+        <v>46111</v>
+      </c>
+      <c r="S236" s="24">
+        <f t="shared" si="16"/>
+        <v>5</v>
+      </c>
+      <c r="T236" s="73" t="s">
+        <v>518</v>
+      </c>
+      <c r="U236" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="237" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A237" s="41" t="s">
+        <v>520</v>
+      </c>
+      <c r="B237" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C237" s="41">
+        <v>58144220</v>
+      </c>
+      <c r="D237" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E237" s="41" t="s">
+        <v>521</v>
+      </c>
+      <c r="F237" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G237" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="H237" s="79">
+        <v>46064</v>
+      </c>
+      <c r="I237" s="42">
+        <v>46111</v>
+      </c>
+      <c r="J237" s="24">
+        <f t="shared" si="15"/>
+        <v>34</v>
+      </c>
+      <c r="K237" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="L237" s="48" t="s">
+        <v>304</v>
+      </c>
+      <c r="M237" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="N237" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="O237" s="78">
+        <v>0</v>
+      </c>
+      <c r="P237" s="78">
+        <v>0</v>
+      </c>
+      <c r="Q237" s="78">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R237" s="50">
+        <v>46111</v>
+      </c>
+      <c r="S237" s="24">
+        <f t="shared" si="16"/>
+        <v>34</v>
+      </c>
+      <c r="T237" s="73" t="s">
+        <v>518</v>
+      </c>
+      <c r="U237" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="238" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A238" s="41" t="s">
+        <v>522</v>
+      </c>
+      <c r="B238" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C238" s="41">
+        <v>58808846</v>
+      </c>
+      <c r="D238" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="E238" s="41" t="s">
+        <v>523</v>
+      </c>
+      <c r="F238" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G238" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H238" s="42">
+        <v>46076</v>
+      </c>
+      <c r="I238" s="42">
+        <v>46108</v>
+      </c>
+      <c r="J238" s="24">
+        <f t="shared" si="15"/>
+        <v>25</v>
+      </c>
+      <c r="K238" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="L238" s="48" t="s">
+        <v>304</v>
+      </c>
+      <c r="M238" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="N238" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="O238" s="49">
+        <v>2000000</v>
+      </c>
+      <c r="P238" s="49">
+        <v>462000</v>
+      </c>
+      <c r="Q238" s="78">
+        <f t="shared" si="20"/>
+        <v>2462000</v>
+      </c>
+      <c r="R238" s="50">
+        <v>46111</v>
+      </c>
+      <c r="S238" s="24">
+        <f t="shared" si="16"/>
+        <v>26</v>
+      </c>
+      <c r="T238" s="73" t="s">
+        <v>518</v>
+      </c>
+      <c r="U238" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="239" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A239" s="41" t="s">
+        <v>524</v>
+      </c>
+      <c r="B239" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C239" s="41">
+        <v>59821965</v>
+      </c>
+      <c r="D239" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="E239" s="41" t="s">
+        <v>525</v>
+      </c>
+      <c r="F239" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G239" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="H239" s="42">
+        <v>46093</v>
+      </c>
+      <c r="I239" s="42">
+        <v>46111</v>
+      </c>
+      <c r="J239" s="24">
+        <f t="shared" si="15"/>
+        <v>13</v>
+      </c>
+      <c r="K239" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="L239" s="48" t="s">
+        <v>304</v>
+      </c>
+      <c r="M239" s="48" t="s">
+        <v>157</v>
+      </c>
+      <c r="N239" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="O239" s="78">
+        <v>3000000</v>
+      </c>
+      <c r="P239" s="78">
+        <v>0</v>
+      </c>
+      <c r="Q239" s="78">
+        <f>P239+O239</f>
+        <v>3000000</v>
+      </c>
+      <c r="R239" s="50">
+        <v>46111</v>
+      </c>
+      <c r="S239" s="24">
+        <f t="shared" si="16"/>
+        <v>13</v>
+      </c>
+      <c r="T239" s="73" t="s">
+        <v>518</v>
+      </c>
+      <c r="U239" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="240" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A240" s="41" t="s">
+        <v>526</v>
+      </c>
+      <c r="B240" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C240" s="41">
+        <v>59894758</v>
+      </c>
+      <c r="D240" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E240" s="41" t="s">
+        <v>527</v>
+      </c>
+      <c r="F240" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G240" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="H240" s="42">
+        <v>46094</v>
+      </c>
+      <c r="I240" s="42">
+        <v>46111</v>
+      </c>
+      <c r="J240" s="24">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="K240" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="L240" s="48" t="s">
+        <v>304</v>
+      </c>
+      <c r="M240" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N240" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="O240" s="49">
+        <v>1000000</v>
+      </c>
+      <c r="P240" s="49">
+        <v>678945</v>
+      </c>
+      <c r="Q240" s="78">
+        <f t="shared" si="20"/>
+        <v>1678945</v>
+      </c>
+      <c r="R240" s="50">
+        <v>46111</v>
+      </c>
+      <c r="S240" s="24">
+        <f t="shared" si="16"/>
+        <v>12</v>
+      </c>
+      <c r="T240" s="73" t="s">
+        <v>518</v>
+      </c>
+      <c r="U240" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="241" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A241" s="41" t="s">
+        <v>528</v>
+      </c>
+      <c r="B241" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C241" s="41">
+        <v>59278285</v>
+      </c>
+      <c r="D241" s="41" t="s">
+        <v>529</v>
+      </c>
+      <c r="E241" s="41" t="s">
+        <v>530</v>
+      </c>
+      <c r="F241" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="G241" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H241" s="42">
+        <v>46084</v>
+      </c>
+      <c r="I241" s="42">
+        <v>46105</v>
+      </c>
+      <c r="J241" s="24">
+        <f t="shared" si="15"/>
+        <v>16</v>
+      </c>
+      <c r="K241" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="L241" s="48" t="s">
+        <v>304</v>
+      </c>
+      <c r="M241" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N241" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="O241" s="49">
+        <v>1050000</v>
+      </c>
+      <c r="P241" s="49">
+        <v>500000</v>
+      </c>
+      <c r="Q241" s="78">
+        <f t="shared" si="20"/>
+        <v>1550000</v>
+      </c>
+      <c r="R241" s="50">
+        <v>46112</v>
+      </c>
+      <c r="S241" s="24">
+        <f t="shared" si="16"/>
+        <v>21</v>
+      </c>
+      <c r="T241" s="73" t="s">
+        <v>518</v>
+      </c>
+      <c r="U241" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="242" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A242" s="41" t="s">
+        <v>528</v>
+      </c>
+      <c r="B242" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C242" s="41">
+        <v>59278925</v>
+      </c>
+      <c r="D242" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="E242" s="41" t="s">
+        <v>531</v>
+      </c>
+      <c r="F242" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G242" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H242" s="42">
+        <v>46084</v>
+      </c>
+      <c r="I242" s="42">
+        <v>46105</v>
+      </c>
+      <c r="J242" s="24">
+        <f t="shared" si="15"/>
+        <v>16</v>
+      </c>
+      <c r="K242" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="L242" s="48" t="s">
+        <v>304</v>
+      </c>
+      <c r="M242" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N242" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="O242" s="49">
+        <v>1050000</v>
+      </c>
+      <c r="P242" s="49">
+        <v>500000</v>
+      </c>
+      <c r="Q242" s="78">
+        <f t="shared" si="20"/>
+        <v>1550000</v>
+      </c>
+      <c r="R242" s="50">
+        <v>46112</v>
+      </c>
+      <c r="S242" s="24">
+        <f t="shared" si="16"/>
+        <v>21</v>
+      </c>
+      <c r="T242" s="73" t="s">
+        <v>518</v>
+      </c>
+      <c r="U242" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="243" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A243" s="41" t="s">
+        <v>469</v>
+      </c>
+      <c r="B243" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C243" s="80">
+        <v>59300338</v>
+      </c>
+      <c r="D243" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="E243" s="41" t="s">
+        <v>532</v>
+      </c>
+      <c r="F243" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G243" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H243" s="42">
+        <v>46084</v>
+      </c>
+      <c r="I243" s="42">
+        <v>46112</v>
+      </c>
+      <c r="J243" s="24">
+        <f t="shared" si="15"/>
+        <v>21</v>
+      </c>
+      <c r="K243" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="L243" s="48" t="s">
+        <v>304</v>
+      </c>
+      <c r="M243" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N243" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="O243" s="49">
+        <v>2000000</v>
+      </c>
+      <c r="P243" s="49">
+        <v>462000</v>
+      </c>
+      <c r="Q243" s="78">
+        <f t="shared" si="20"/>
+        <v>2462000</v>
+      </c>
+      <c r="R243" s="50">
+        <v>46112</v>
+      </c>
+      <c r="S243" s="24">
+        <f t="shared" si="16"/>
+        <v>21</v>
+      </c>
+      <c r="T243" s="73" t="s">
+        <v>518</v>
+      </c>
+      <c r="U243" s="48" t="s">
+        <v>443</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U232" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U243" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="166" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="165" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="161" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C205 C233:C1048576">
-    <cfRule type="duplicateValues" dxfId="160" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="99"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C212 C233:C1048576">
-    <cfRule type="duplicateValues" dxfId="158" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="157" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="155" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="153" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="152" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="150" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="149" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="148" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="147" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="146" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="145" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="144" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="143" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="142" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="141" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="140" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="139" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="138" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="137" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="136" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="135" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
-    <cfRule type="duplicateValues" dxfId="134" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="133" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="132" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="130" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="129" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="128" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="127" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="126" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="124" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C114">
-    <cfRule type="duplicateValues" dxfId="123" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="122" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="121" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C157:C160">
-    <cfRule type="duplicateValues" dxfId="119" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C161:C163">
-    <cfRule type="duplicateValues" dxfId="118" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="117" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="115" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C168">
-    <cfRule type="duplicateValues" dxfId="113" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="112" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171">
-    <cfRule type="duplicateValues" dxfId="111" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173">
-    <cfRule type="duplicateValues" dxfId="110" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="108" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C175">
-    <cfRule type="duplicateValues" dxfId="107" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="106" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C178">
-    <cfRule type="duplicateValues" dxfId="105" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179">
-    <cfRule type="duplicateValues" dxfId="104" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C206:C212">
-    <cfRule type="duplicateValues" dxfId="102" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
-    <cfRule type="duplicateValues" dxfId="101" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C208">
-    <cfRule type="duplicateValues" dxfId="99" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218:C223">
-    <cfRule type="duplicateValues" dxfId="97" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C225:C232">
+    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="96" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="94" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="93" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="92" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="91" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="90" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="89" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="88" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="87" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172">
-    <cfRule type="duplicateValues" dxfId="86" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175">
-    <cfRule type="duplicateValues" dxfId="85" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C225:C232">
-    <cfRule type="duplicateValues" dxfId="84" priority="2"/>
+  <conditionalFormatting sqref="E243">
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="C233:C243">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C205 C244:C1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="103"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C212 C244:C1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="110"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C232 C244:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="368" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D3CE027-A40C-4B48-B0E9-C9AFCEA2FBA0}"/>
+  <xr:revisionPtr revIDLastSave="394" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{777F1244-B65D-4C91-BFFB-37E2249E79FA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$259</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2658" uniqueCount="553">
   <si>
     <t>Client</t>
   </si>
@@ -1639,6 +1639,66 @@
   </si>
   <si>
     <t>BUVPN260062</t>
+  </si>
+  <si>
+    <t>DIRECTION GENERALE DES IMPOTS</t>
+  </si>
+  <si>
+    <t>VPNLL120232</t>
+  </si>
+  <si>
+    <t>CAISSE NATIONALE DE PREVOYANCE SOCIALE</t>
+  </si>
+  <si>
+    <t>BUVPN150600</t>
+  </si>
+  <si>
+    <t>BUVPN150689</t>
+  </si>
+  <si>
+    <t>EGLISE METHODISTE UNIE DE COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>DIRECTION GENERALE DU TRESOR ET DE LA COMPTABILITE PUBLIQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGTCP </t>
+  </si>
+  <si>
+    <t>CNPS</t>
+  </si>
+  <si>
+    <t>SYTHD240176</t>
+  </si>
+  <si>
+    <t>VPNLL130015</t>
+  </si>
+  <si>
+    <t>BUVPN260066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TREICHVILLE HANNYYAH </t>
+  </si>
+  <si>
+    <t>BUVPN260061</t>
+  </si>
+  <si>
+    <t>EUROFIND PARTICIPATION PLATEAU</t>
+  </si>
+  <si>
+    <t>SOCIETE DE MECANIQUE GENERALE TRECHVILLE</t>
+  </si>
+  <si>
+    <t>LONACI</t>
+  </si>
+  <si>
+    <t>BUVPN200153</t>
+  </si>
+  <si>
+    <t>Hors projet</t>
+  </si>
+  <si>
+    <t>S15</t>
   </si>
 </sst>
 </file>
@@ -1652,7 +1712,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,##0\ _€"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1751,19 +1811,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1797,7 +1844,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1857,13 +1904,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1977,12 +2037,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1992,26 +2046,6 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2058,32 +2092,19 @@
     <xf numFmtId="14" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3286,13 +3307,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U243"/>
+  <dimension ref="A1:U259"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="26" customWidth="1"/>
     <col min="3" max="3" width="8.90625" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11" style="63" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.08984375" customWidth="1"/>
     <col min="12" max="12" width="12.08984375" customWidth="1"/>
     <col min="13" max="13" width="7.90625" customWidth="1"/>
@@ -3300,10 +3321,10 @@
     <col min="15" max="15" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.08984375" customWidth="1"/>
     <col min="17" max="17" width="9.90625" style="18" customWidth="1"/>
-    <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11" style="63" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.1796875" customWidth="1"/>
     <col min="20" max="20" width="6.54296875" customWidth="1"/>
-    <col min="21" max="21" width="9.6328125" style="67" customWidth="1"/>
+    <col min="21" max="21" width="9.6328125" style="57" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
@@ -3328,10 +3349,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="62" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -3358,7 +3379,7 @@
       <c r="Q1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="62" t="s">
         <v>15</v>
       </c>
       <c r="S1" s="4" t="s">
@@ -3367,71 +3388,71 @@
       <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="65" t="s">
+      <c r="U1" s="55" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="59">
+      <c r="C2" s="49">
         <v>55472663</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="49" t="s">
         <v>156</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="60" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="61">
+      <c r="G2" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="51">
         <v>46010</v>
       </c>
-      <c r="I2" s="62">
+      <c r="I2" s="52">
         <v>46015</v>
       </c>
-      <c r="J2" s="63">
+      <c r="J2" s="53">
         <f>+NETWORKDAYS(H2,I2)</f>
         <v>4</v>
       </c>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
       <c r="M2" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="N2" s="55" t="s">
+      <c r="N2" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="64">
+      <c r="O2" s="54">
         <v>0</v>
       </c>
-      <c r="P2" s="64">
+      <c r="P2" s="54">
         <v>0</v>
       </c>
-      <c r="Q2" s="64">
+      <c r="Q2" s="54">
         <f>P2+O2</f>
         <v>0</v>
       </c>
       <c r="R2" s="35">
         <v>46024</v>
       </c>
-      <c r="S2" s="63">
+      <c r="S2" s="53">
         <f>NETWORKDAYS(H2,R2)</f>
         <v>11</v>
       </c>
       <c r="T2" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="U2" s="65"/>
+      <c r="U2" s="56"/>
     </row>
     <row r="3" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
@@ -3473,13 +3494,13 @@
       <c r="N3" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="O3" s="44">
+      <c r="O3" s="42">
         <v>1000000</v>
       </c>
-      <c r="P3" s="44">
+      <c r="P3" s="42">
         <v>231750</v>
       </c>
-      <c r="Q3" s="45">
+      <c r="Q3" s="43">
         <f>P3+O3</f>
         <v>1231750</v>
       </c>
@@ -3493,7 +3514,7 @@
       <c r="T3" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="U3" s="65"/>
+      <c r="U3" s="56"/>
     </row>
     <row r="4" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
@@ -3535,13 +3556,13 @@
       <c r="N4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="44">
+      <c r="O4" s="42">
         <v>0</v>
       </c>
-      <c r="P4" s="44">
+      <c r="P4" s="42">
         <v>0</v>
       </c>
-      <c r="Q4" s="45">
+      <c r="Q4" s="43">
         <f>P4+O4</f>
         <v>0</v>
       </c>
@@ -3555,7 +3576,7 @@
       <c r="T4" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U4" s="65"/>
+      <c r="U4" s="56"/>
     </row>
     <row r="5" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
@@ -3597,13 +3618,13 @@
       <c r="N5" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="42">
         <v>0</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="42">
         <v>0</v>
       </c>
-      <c r="Q5" s="45">
+      <c r="Q5" s="43">
         <f>P5+O5</f>
         <v>0</v>
       </c>
@@ -3617,7 +3638,7 @@
       <c r="T5" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U5" s="65"/>
+      <c r="U5" s="56"/>
     </row>
     <row r="6" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
@@ -3665,7 +3686,7 @@
       <c r="P6" s="15">
         <v>71435</v>
       </c>
-      <c r="Q6" s="45">
+      <c r="Q6" s="43">
         <f t="shared" ref="Q6:Q69" si="2">P6+O6</f>
         <v>341435</v>
       </c>
@@ -3679,7 +3700,7 @@
       <c r="T6" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U6" s="65"/>
+      <c r="U6" s="56"/>
     </row>
     <row r="7" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -3727,7 +3748,7 @@
       <c r="P7" s="15">
         <v>40000</v>
       </c>
-      <c r="Q7" s="45">
+      <c r="Q7" s="43">
         <f t="shared" si="2"/>
         <v>190000</v>
       </c>
@@ -3741,7 +3762,7 @@
       <c r="T7" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U7" s="65"/>
+      <c r="U7" s="56"/>
     </row>
     <row r="8" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
@@ -3783,13 +3804,13 @@
       <c r="N8" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="O8" s="44">
+      <c r="O8" s="42">
         <v>3264000</v>
       </c>
-      <c r="P8" s="44">
+      <c r="P8" s="42">
         <v>408000</v>
       </c>
-      <c r="Q8" s="45">
+      <c r="Q8" s="43">
         <f t="shared" si="2"/>
         <v>3672000</v>
       </c>
@@ -3803,7 +3824,7 @@
       <c r="T8" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U8" s="65"/>
+      <c r="U8" s="56"/>
     </row>
     <row r="9" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
@@ -3845,13 +3866,13 @@
       <c r="N9" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O9" s="44">
+      <c r="O9" s="42">
         <v>1800000</v>
       </c>
-      <c r="P9" s="44">
+      <c r="P9" s="42">
         <v>301520</v>
       </c>
-      <c r="Q9" s="45">
+      <c r="Q9" s="43">
         <f t="shared" si="2"/>
         <v>2101520</v>
       </c>
@@ -3865,7 +3886,7 @@
       <c r="T9" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U9" s="65"/>
+      <c r="U9" s="56"/>
     </row>
     <row r="10" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
@@ -3907,13 +3928,13 @@
       <c r="N10" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="O10" s="44">
+      <c r="O10" s="42">
         <v>1977000</v>
       </c>
-      <c r="P10" s="44">
+      <c r="P10" s="42">
         <v>0</v>
       </c>
-      <c r="Q10" s="45">
+      <c r="Q10" s="43">
         <f t="shared" si="2"/>
         <v>1977000</v>
       </c>
@@ -3927,7 +3948,7 @@
       <c r="T10" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U10" s="65"/>
+      <c r="U10" s="56"/>
     </row>
     <row r="11" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
@@ -3969,13 +3990,13 @@
       <c r="N11" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="O11" s="44">
+      <c r="O11" s="42">
         <v>1977000</v>
       </c>
-      <c r="P11" s="44">
+      <c r="P11" s="42">
         <v>0</v>
       </c>
-      <c r="Q11" s="45">
+      <c r="Q11" s="43">
         <f t="shared" si="2"/>
         <v>1977000</v>
       </c>
@@ -3989,7 +4010,7 @@
       <c r="T11" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U11" s="65"/>
+      <c r="U11" s="56"/>
     </row>
     <row r="12" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
@@ -4031,13 +4052,13 @@
       <c r="N12" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="O12" s="44">
+      <c r="O12" s="42">
         <v>1500000</v>
       </c>
-      <c r="P12" s="44">
+      <c r="P12" s="42">
         <v>571781</v>
       </c>
-      <c r="Q12" s="45">
+      <c r="Q12" s="43">
         <f t="shared" si="2"/>
         <v>2071781</v>
       </c>
@@ -4051,7 +4072,7 @@
       <c r="T12" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U12" s="65"/>
+      <c r="U12" s="56"/>
     </row>
     <row r="13" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
@@ -4099,7 +4120,7 @@
       <c r="P13" s="15">
         <v>0</v>
       </c>
-      <c r="Q13" s="45">
+      <c r="Q13" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4113,7 +4134,7 @@
       <c r="T13" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U13" s="65"/>
+      <c r="U13" s="56"/>
     </row>
     <row r="14" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
@@ -4161,7 +4182,7 @@
       <c r="P14" s="15">
         <v>0</v>
       </c>
-      <c r="Q14" s="45">
+      <c r="Q14" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4175,7 +4196,7 @@
       <c r="T14" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U14" s="65"/>
+      <c r="U14" s="56"/>
     </row>
     <row r="15" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
@@ -4217,13 +4238,13 @@
       <c r="N15" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="O15" s="44">
+      <c r="O15" s="42">
         <v>847200</v>
       </c>
-      <c r="P15" s="44">
+      <c r="P15" s="42">
         <v>0</v>
       </c>
-      <c r="Q15" s="45">
+      <c r="Q15" s="43">
         <f t="shared" si="2"/>
         <v>847200</v>
       </c>
@@ -4237,7 +4258,7 @@
       <c r="T15" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U15" s="65"/>
+      <c r="U15" s="56"/>
     </row>
     <row r="16" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
@@ -4279,13 +4300,13 @@
       <c r="N16" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O16" s="44">
+      <c r="O16" s="42">
         <v>0</v>
       </c>
-      <c r="P16" s="44">
+      <c r="P16" s="42">
         <v>0</v>
       </c>
-      <c r="Q16" s="45">
+      <c r="Q16" s="43">
         <f>P16+O16</f>
         <v>0</v>
       </c>
@@ -4299,7 +4320,7 @@
       <c r="T16" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U16" s="65"/>
+      <c r="U16" s="56"/>
     </row>
     <row r="17" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
@@ -4341,13 +4362,13 @@
       <c r="N17" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O17" s="45">
+      <c r="O17" s="43">
         <v>0</v>
       </c>
-      <c r="P17" s="45">
+      <c r="P17" s="43">
         <v>0</v>
       </c>
-      <c r="Q17" s="45">
+      <c r="Q17" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4361,7 +4382,7 @@
       <c r="T17" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U17" s="65"/>
+      <c r="U17" s="56"/>
     </row>
     <row r="18" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
@@ -4406,10 +4427,10 @@
       <c r="O18" s="37">
         <v>0</v>
       </c>
-      <c r="P18" s="44">
+      <c r="P18" s="42">
         <v>1588888</v>
       </c>
-      <c r="Q18" s="45">
+      <c r="Q18" s="43">
         <f t="shared" si="2"/>
         <v>1588888</v>
       </c>
@@ -4423,7 +4444,7 @@
       <c r="T18" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U18" s="65"/>
+      <c r="U18" s="56"/>
     </row>
     <row r="19" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
@@ -4468,10 +4489,10 @@
       <c r="O19" s="37">
         <v>1480000</v>
       </c>
-      <c r="P19" s="44">
+      <c r="P19" s="42">
         <v>0</v>
       </c>
-      <c r="Q19" s="45">
+      <c r="Q19" s="43">
         <f t="shared" si="2"/>
         <v>1480000</v>
       </c>
@@ -4485,7 +4506,7 @@
       <c r="T19" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U19" s="65"/>
+      <c r="U19" s="56"/>
     </row>
     <row r="20" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
@@ -4527,13 +4548,13 @@
       <c r="N20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O20" s="45">
+      <c r="O20" s="43">
         <v>0</v>
       </c>
-      <c r="P20" s="45">
+      <c r="P20" s="43">
         <v>0</v>
       </c>
-      <c r="Q20" s="45">
+      <c r="Q20" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4547,7 +4568,7 @@
       <c r="T20" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U20" s="65"/>
+      <c r="U20" s="56"/>
     </row>
     <row r="21" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
@@ -4589,13 +4610,13 @@
       <c r="N21" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="O21" s="44">
+      <c r="O21" s="42">
         <v>3000000</v>
       </c>
-      <c r="P21" s="44">
+      <c r="P21" s="42">
         <v>270000</v>
       </c>
-      <c r="Q21" s="45">
+      <c r="Q21" s="43">
         <f t="shared" si="2"/>
         <v>3270000</v>
       </c>
@@ -4609,7 +4630,7 @@
       <c r="T21" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="U21" s="65"/>
+      <c r="U21" s="56"/>
     </row>
     <row r="22" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
@@ -4651,13 +4672,13 @@
       <c r="N22" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="O22" s="44">
+      <c r="O22" s="42">
         <v>2000000</v>
       </c>
-      <c r="P22" s="44">
+      <c r="P22" s="42">
         <v>380000</v>
       </c>
-      <c r="Q22" s="45">
+      <c r="Q22" s="43">
         <f t="shared" si="2"/>
         <v>2380000</v>
       </c>
@@ -4671,7 +4692,7 @@
       <c r="T22" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U22" s="65"/>
+      <c r="U22" s="56"/>
     </row>
     <row r="23" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
@@ -4716,10 +4737,10 @@
       <c r="O23" s="37">
         <v>0</v>
       </c>
-      <c r="P23" s="44">
+      <c r="P23" s="42">
         <v>0</v>
       </c>
-      <c r="Q23" s="45">
+      <c r="Q23" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4733,7 +4754,7 @@
       <c r="T23" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U23" s="65"/>
+      <c r="U23" s="56"/>
     </row>
     <row r="24" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
@@ -4775,13 +4796,13 @@
       <c r="N24" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O24" s="44">
+      <c r="O24" s="42">
         <v>0</v>
       </c>
-      <c r="P24" s="44">
+      <c r="P24" s="42">
         <v>0</v>
       </c>
-      <c r="Q24" s="45">
+      <c r="Q24" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4795,7 +4816,7 @@
       <c r="T24" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U24" s="65"/>
+      <c r="U24" s="56"/>
     </row>
     <row r="25" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
@@ -4837,13 +4858,13 @@
       <c r="N25" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O25" s="45">
+      <c r="O25" s="43">
         <v>144000</v>
       </c>
-      <c r="P25" s="45">
+      <c r="P25" s="43">
         <v>0</v>
       </c>
-      <c r="Q25" s="45">
+      <c r="Q25" s="43">
         <f t="shared" si="2"/>
         <v>144000</v>
       </c>
@@ -4857,7 +4878,7 @@
       <c r="T25" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U25" s="65"/>
+      <c r="U25" s="56"/>
     </row>
     <row r="26" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
@@ -4899,13 +4920,13 @@
       <c r="N26" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="O26" s="45">
+      <c r="O26" s="43">
         <v>1000000</v>
       </c>
-      <c r="P26" s="45">
+      <c r="P26" s="43">
         <v>0</v>
       </c>
-      <c r="Q26" s="45">
+      <c r="Q26" s="43">
         <f t="shared" si="2"/>
         <v>1000000</v>
       </c>
@@ -4919,7 +4940,7 @@
       <c r="T26" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U26" s="65"/>
+      <c r="U26" s="56"/>
     </row>
     <row r="27" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
@@ -4961,13 +4982,13 @@
       <c r="N27" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="O27" s="44">
+      <c r="O27" s="42">
         <v>847200</v>
       </c>
-      <c r="P27" s="44">
+      <c r="P27" s="42">
         <v>0</v>
       </c>
-      <c r="Q27" s="45">
+      <c r="Q27" s="43">
         <f t="shared" si="2"/>
         <v>847200</v>
       </c>
@@ -4981,7 +5002,7 @@
       <c r="T27" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U27" s="65"/>
+      <c r="U27" s="56"/>
     </row>
     <row r="28" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
@@ -5023,13 +5044,13 @@
       <c r="N28" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O28" s="44">
+      <c r="O28" s="42">
         <v>2500000</v>
       </c>
-      <c r="P28" s="44">
+      <c r="P28" s="42">
         <v>280000</v>
       </c>
-      <c r="Q28" s="45">
+      <c r="Q28" s="43">
         <f t="shared" si="2"/>
         <v>2780000</v>
       </c>
@@ -5043,7 +5064,7 @@
       <c r="T28" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U28" s="65"/>
+      <c r="U28" s="56"/>
     </row>
     <row r="29" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
@@ -5085,13 +5106,13 @@
       <c r="N29" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="O29" s="44">
+      <c r="O29" s="42">
         <v>32214683</v>
       </c>
-      <c r="P29" s="44">
+      <c r="P29" s="42">
         <v>6403996</v>
       </c>
-      <c r="Q29" s="45">
+      <c r="Q29" s="43">
         <f t="shared" si="2"/>
         <v>38618679</v>
       </c>
@@ -5105,7 +5126,7 @@
       <c r="T29" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U29" s="65"/>
+      <c r="U29" s="56"/>
     </row>
     <row r="30" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
@@ -5147,13 +5168,13 @@
       <c r="N30" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O30" s="45">
+      <c r="O30" s="43">
         <v>150000</v>
       </c>
-      <c r="P30" s="45">
+      <c r="P30" s="43">
         <v>40000</v>
       </c>
-      <c r="Q30" s="45">
+      <c r="Q30" s="43">
         <f t="shared" si="2"/>
         <v>190000</v>
       </c>
@@ -5167,7 +5188,7 @@
       <c r="T30" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U30" s="65"/>
+      <c r="U30" s="56"/>
     </row>
     <row r="31" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
@@ -5209,13 +5230,13 @@
       <c r="N31" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="O31" s="44">
+      <c r="O31" s="42">
         <v>0</v>
       </c>
-      <c r="P31" s="44">
+      <c r="P31" s="42">
         <v>40000</v>
       </c>
-      <c r="Q31" s="45">
+      <c r="Q31" s="43">
         <f t="shared" si="2"/>
         <v>40000</v>
       </c>
@@ -5229,7 +5250,7 @@
       <c r="T31" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U31" s="65"/>
+      <c r="U31" s="56"/>
     </row>
     <row r="32" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
@@ -5271,13 +5292,13 @@
       <c r="N32" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O32" s="44">
+      <c r="O32" s="42">
         <v>1000000</v>
       </c>
-      <c r="P32" s="44">
+      <c r="P32" s="42">
         <v>705164</v>
       </c>
-      <c r="Q32" s="45">
+      <c r="Q32" s="43">
         <f t="shared" si="2"/>
         <v>1705164</v>
       </c>
@@ -5291,7 +5312,7 @@
       <c r="T32" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U32" s="65"/>
+      <c r="U32" s="56"/>
     </row>
     <row r="33" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
@@ -5333,13 +5354,13 @@
       <c r="N33" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="O33" s="44">
+      <c r="O33" s="42">
         <v>0</v>
       </c>
-      <c r="P33" s="44">
+      <c r="P33" s="42">
         <v>170681</v>
       </c>
-      <c r="Q33" s="45">
+      <c r="Q33" s="43">
         <f t="shared" si="2"/>
         <v>170681</v>
       </c>
@@ -5353,7 +5374,7 @@
       <c r="T33" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U33" s="65"/>
+      <c r="U33" s="56"/>
     </row>
     <row r="34" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
@@ -5395,13 +5416,13 @@
       <c r="N34" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O34" s="44">
+      <c r="O34" s="42">
         <v>0</v>
       </c>
-      <c r="P34" s="44">
+      <c r="P34" s="42">
         <v>92730</v>
       </c>
-      <c r="Q34" s="45">
+      <c r="Q34" s="43">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
@@ -5415,7 +5436,7 @@
       <c r="T34" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U34" s="65"/>
+      <c r="U34" s="56"/>
     </row>
     <row r="35" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
@@ -5457,13 +5478,13 @@
       <c r="N35" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O35" s="44">
+      <c r="O35" s="42">
         <v>0</v>
       </c>
-      <c r="P35" s="44">
+      <c r="P35" s="42">
         <v>92730</v>
       </c>
-      <c r="Q35" s="45">
+      <c r="Q35" s="43">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
@@ -5477,7 +5498,7 @@
       <c r="T35" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U35" s="65"/>
+      <c r="U35" s="56"/>
     </row>
     <row r="36" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12" t="s">
@@ -5519,13 +5540,13 @@
       <c r="N36" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O36" s="44">
+      <c r="O36" s="42">
         <v>0</v>
       </c>
-      <c r="P36" s="44">
+      <c r="P36" s="42">
         <v>92730</v>
       </c>
-      <c r="Q36" s="45">
+      <c r="Q36" s="43">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
@@ -5539,7 +5560,7 @@
       <c r="T36" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U36" s="65"/>
+      <c r="U36" s="56"/>
     </row>
     <row r="37" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12" t="s">
@@ -5581,13 +5602,13 @@
       <c r="N37" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="O37" s="44">
+      <c r="O37" s="42">
         <v>0</v>
       </c>
-      <c r="P37" s="44">
+      <c r="P37" s="42">
         <v>92730</v>
       </c>
-      <c r="Q37" s="45">
+      <c r="Q37" s="43">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
@@ -5601,7 +5622,7 @@
       <c r="T37" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U37" s="65"/>
+      <c r="U37" s="56"/>
     </row>
     <row r="38" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
@@ -5643,13 +5664,13 @@
       <c r="N38" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O38" s="44">
+      <c r="O38" s="42">
         <v>2000500</v>
       </c>
-      <c r="P38" s="44">
+      <c r="P38" s="42">
         <v>667054</v>
       </c>
-      <c r="Q38" s="45">
+      <c r="Q38" s="43">
         <f t="shared" si="2"/>
         <v>2667554</v>
       </c>
@@ -5663,7 +5684,7 @@
       <c r="T38" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U38" s="65"/>
+      <c r="U38" s="56"/>
     </row>
     <row r="39" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
@@ -5705,13 +5726,13 @@
       <c r="N39" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O39" s="44">
+      <c r="O39" s="42">
         <v>0</v>
       </c>
-      <c r="P39" s="44">
+      <c r="P39" s="42">
         <v>189985</v>
       </c>
-      <c r="Q39" s="45">
+      <c r="Q39" s="43">
         <f t="shared" si="2"/>
         <v>189985</v>
       </c>
@@ -5725,7 +5746,7 @@
       <c r="T39" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U39" s="65"/>
+      <c r="U39" s="56"/>
     </row>
     <row r="40" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
@@ -5767,13 +5788,13 @@
       <c r="N40" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="O40" s="44">
+      <c r="O40" s="42">
         <v>0</v>
       </c>
-      <c r="P40" s="44">
+      <c r="P40" s="42">
         <v>92730</v>
       </c>
-      <c r="Q40" s="45">
+      <c r="Q40" s="43">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
@@ -5787,7 +5808,7 @@
       <c r="T40" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="U40" s="65"/>
+      <c r="U40" s="56"/>
     </row>
     <row r="41" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
@@ -5829,13 +5850,13 @@
       <c r="N41" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="O41" s="45">
+      <c r="O41" s="43">
         <v>0</v>
       </c>
-      <c r="P41" s="45">
+      <c r="P41" s="43">
         <v>0</v>
       </c>
-      <c r="Q41" s="45">
+      <c r="Q41" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5849,7 +5870,7 @@
       <c r="T41" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U41" s="65"/>
+      <c r="U41" s="56"/>
     </row>
     <row r="42" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
@@ -5891,13 +5912,13 @@
       <c r="N42" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="O42" s="44">
+      <c r="O42" s="42">
         <v>500000</v>
       </c>
-      <c r="P42" s="44">
+      <c r="P42" s="42">
         <v>500000</v>
       </c>
-      <c r="Q42" s="45">
+      <c r="Q42" s="43">
         <f t="shared" si="2"/>
         <v>1000000</v>
       </c>
@@ -5911,7 +5932,7 @@
       <c r="T42" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U42" s="65"/>
+      <c r="U42" s="56"/>
     </row>
     <row r="43" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
@@ -5953,13 +5974,13 @@
       <c r="N43" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O43" s="45">
+      <c r="O43" s="43">
         <v>150000</v>
       </c>
-      <c r="P43" s="45">
+      <c r="P43" s="43">
         <v>60000</v>
       </c>
-      <c r="Q43" s="45">
+      <c r="Q43" s="43">
         <f t="shared" si="2"/>
         <v>210000</v>
       </c>
@@ -5973,7 +5994,7 @@
       <c r="T43" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U43" s="65"/>
+      <c r="U43" s="56"/>
     </row>
     <row r="44" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
@@ -6015,13 +6036,13 @@
       <c r="N44" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O44" s="45">
+      <c r="O44" s="43">
         <v>150000</v>
       </c>
-      <c r="P44" s="45">
+      <c r="P44" s="43">
         <v>60000</v>
       </c>
-      <c r="Q44" s="45">
+      <c r="Q44" s="43">
         <f t="shared" si="2"/>
         <v>210000</v>
       </c>
@@ -6035,7 +6056,7 @@
       <c r="T44" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U44" s="65"/>
+      <c r="U44" s="56"/>
     </row>
     <row r="45" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
@@ -6077,13 +6098,13 @@
       <c r="N45" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="O45" s="45">
+      <c r="O45" s="43">
         <v>955437</v>
       </c>
-      <c r="P45" s="45">
+      <c r="P45" s="43">
         <v>0</v>
       </c>
-      <c r="Q45" s="45">
+      <c r="Q45" s="43">
         <f t="shared" si="2"/>
         <v>955437</v>
       </c>
@@ -6097,7 +6118,7 @@
       <c r="T45" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U45" s="65"/>
+      <c r="U45" s="56"/>
     </row>
     <row r="46" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="12" t="s">
@@ -6139,13 +6160,13 @@
       <c r="N46" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="O46" s="45">
+      <c r="O46" s="43">
         <v>500000</v>
       </c>
-      <c r="P46" s="45">
+      <c r="P46" s="43">
         <v>0</v>
       </c>
-      <c r="Q46" s="45">
+      <c r="Q46" s="43">
         <f t="shared" si="2"/>
         <v>500000</v>
       </c>
@@ -6159,7 +6180,7 @@
       <c r="T46" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U46" s="65"/>
+      <c r="U46" s="56"/>
     </row>
     <row r="47" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="12" t="s">
@@ -6201,13 +6222,13 @@
       <c r="N47" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="O47" s="44">
+      <c r="O47" s="42">
         <v>0</v>
       </c>
-      <c r="P47" s="44">
+      <c r="P47" s="42">
         <v>217691</v>
       </c>
-      <c r="Q47" s="45">
+      <c r="Q47" s="43">
         <f t="shared" si="2"/>
         <v>217691</v>
       </c>
@@ -6221,7 +6242,7 @@
       <c r="T47" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U47" s="65"/>
+      <c r="U47" s="56"/>
     </row>
     <row r="48" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="12" t="s">
@@ -6263,13 +6284,13 @@
       <c r="N48" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="O48" s="44">
+      <c r="O48" s="42">
         <v>2362401</v>
       </c>
-      <c r="P48" s="44">
+      <c r="P48" s="42">
         <v>300000</v>
       </c>
-      <c r="Q48" s="45">
+      <c r="Q48" s="43">
         <f t="shared" si="2"/>
         <v>2662401</v>
       </c>
@@ -6283,7 +6304,7 @@
       <c r="T48" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U48" s="65"/>
+      <c r="U48" s="56"/>
     </row>
     <row r="49" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="12" t="s">
@@ -6325,13 +6346,13 @@
       <c r="N49" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="O49" s="45">
+      <c r="O49" s="43">
         <v>0</v>
       </c>
-      <c r="P49" s="45">
+      <c r="P49" s="43">
         <v>0</v>
       </c>
-      <c r="Q49" s="45">
+      <c r="Q49" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6345,7 +6366,7 @@
       <c r="T49" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U49" s="65"/>
+      <c r="U49" s="56"/>
     </row>
     <row r="50" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12" t="s">
@@ -6387,13 +6408,13 @@
       <c r="N50" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="O50" s="44">
+      <c r="O50" s="42">
         <v>2000000</v>
       </c>
-      <c r="P50" s="44">
+      <c r="P50" s="42">
         <v>646323</v>
       </c>
-      <c r="Q50" s="45">
+      <c r="Q50" s="43">
         <f t="shared" si="2"/>
         <v>2646323</v>
       </c>
@@ -6407,7 +6428,7 @@
       <c r="T50" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U50" s="65"/>
+      <c r="U50" s="56"/>
     </row>
     <row r="51" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="12" t="s">
@@ -6449,13 +6470,13 @@
       <c r="N51" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O51" s="44">
+      <c r="O51" s="42">
         <v>0</v>
       </c>
-      <c r="P51" s="44">
+      <c r="P51" s="42">
         <v>0</v>
       </c>
-      <c r="Q51" s="45">
+      <c r="Q51" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6469,7 +6490,7 @@
       <c r="T51" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U51" s="65"/>
+      <c r="U51" s="56"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" s="12" t="s">
@@ -6511,13 +6532,13 @@
       <c r="N52" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O52" s="44">
+      <c r="O52" s="42">
         <v>500000</v>
       </c>
-      <c r="P52" s="44">
+      <c r="P52" s="42">
         <v>325000</v>
       </c>
-      <c r="Q52" s="45">
+      <c r="Q52" s="43">
         <f t="shared" si="2"/>
         <v>825000</v>
       </c>
@@ -6531,7 +6552,7 @@
       <c r="T52" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U52" s="65"/>
+      <c r="U52" s="56"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" s="12" t="s">
@@ -6573,13 +6594,13 @@
       <c r="N53" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="O53" s="44">
+      <c r="O53" s="42">
         <v>0</v>
       </c>
-      <c r="P53" s="44">
+      <c r="P53" s="42">
         <v>433989</v>
       </c>
-      <c r="Q53" s="45">
+      <c r="Q53" s="43">
         <f t="shared" si="2"/>
         <v>433989</v>
       </c>
@@ -6593,7 +6614,7 @@
       <c r="T53" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U53" s="65"/>
+      <c r="U53" s="56"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
@@ -6635,13 +6656,13 @@
       <c r="N54" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O54" s="45">
+      <c r="O54" s="43">
         <v>150000</v>
       </c>
-      <c r="P54" s="45">
+      <c r="P54" s="43">
         <v>40000</v>
       </c>
-      <c r="Q54" s="45">
+      <c r="Q54" s="43">
         <f t="shared" si="2"/>
         <v>190000</v>
       </c>
@@ -6655,7 +6676,7 @@
       <c r="T54" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U54" s="65"/>
+      <c r="U54" s="56"/>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
@@ -6697,13 +6718,13 @@
       <c r="N55" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O55" s="45">
+      <c r="O55" s="43">
         <v>1000000</v>
       </c>
-      <c r="P55" s="45">
+      <c r="P55" s="43">
         <v>231750</v>
       </c>
-      <c r="Q55" s="45">
+      <c r="Q55" s="43">
         <f t="shared" si="2"/>
         <v>1231750</v>
       </c>
@@ -6717,7 +6738,7 @@
       <c r="T55" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U55" s="65"/>
+      <c r="U55" s="56"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" s="12" t="s">
@@ -6759,13 +6780,13 @@
       <c r="N56" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="O56" s="44">
+      <c r="O56" s="42">
         <v>133779304</v>
       </c>
-      <c r="P56" s="44">
+      <c r="P56" s="42">
         <v>5620246</v>
       </c>
-      <c r="Q56" s="45">
+      <c r="Q56" s="43">
         <f t="shared" si="2"/>
         <v>139399550</v>
       </c>
@@ -6779,7 +6800,7 @@
       <c r="T56" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U56" s="65"/>
+      <c r="U56" s="56"/>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A57" s="12" t="s">
@@ -6821,13 +6842,13 @@
       <c r="N57" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="O57" s="44">
+      <c r="O57" s="42">
         <v>0</v>
       </c>
-      <c r="P57" s="44">
+      <c r="P57" s="42">
         <v>500000</v>
       </c>
-      <c r="Q57" s="45">
+      <c r="Q57" s="43">
         <f t="shared" si="2"/>
         <v>500000</v>
       </c>
@@ -6841,7 +6862,7 @@
       <c r="T57" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U57" s="65"/>
+      <c r="U57" s="56"/>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A58" s="12" t="s">
@@ -6883,13 +6904,13 @@
       <c r="N58" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="O58" s="44">
+      <c r="O58" s="42">
         <v>0</v>
       </c>
-      <c r="P58" s="44">
+      <c r="P58" s="42">
         <v>433989</v>
       </c>
-      <c r="Q58" s="45">
+      <c r="Q58" s="43">
         <f t="shared" si="2"/>
         <v>433989</v>
       </c>
@@ -6903,7 +6924,7 @@
       <c r="T58" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U58" s="65"/>
+      <c r="U58" s="56"/>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A59" s="12" t="s">
@@ -6945,13 +6966,13 @@
       <c r="N59" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O59" s="44">
+      <c r="O59" s="42">
         <v>500000</v>
       </c>
-      <c r="P59" s="44">
+      <c r="P59" s="42">
         <v>400000</v>
       </c>
-      <c r="Q59" s="45">
+      <c r="Q59" s="43">
         <f t="shared" si="2"/>
         <v>900000</v>
       </c>
@@ -6965,7 +6986,7 @@
       <c r="T59" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U59" s="65"/>
+      <c r="U59" s="56"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A60" s="12" t="s">
@@ -7007,13 +7028,13 @@
       <c r="N60" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="O60" s="44">
+      <c r="O60" s="42">
         <v>1109000</v>
       </c>
-      <c r="P60" s="44">
+      <c r="P60" s="42">
         <v>935000</v>
       </c>
-      <c r="Q60" s="45">
+      <c r="Q60" s="43">
         <f t="shared" si="2"/>
         <v>2044000</v>
       </c>
@@ -7027,7 +7048,7 @@
       <c r="T60" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U60" s="65"/>
+      <c r="U60" s="56"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A61" s="12" t="s">
@@ -7069,13 +7090,13 @@
       <c r="N61" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O61" s="44">
+      <c r="O61" s="42">
         <v>1670725</v>
       </c>
-      <c r="P61" s="44">
+      <c r="P61" s="42">
         <v>512000</v>
       </c>
-      <c r="Q61" s="45">
+      <c r="Q61" s="43">
         <f t="shared" si="2"/>
         <v>2182725</v>
       </c>
@@ -7089,7 +7110,7 @@
       <c r="T61" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U61" s="65"/>
+      <c r="U61" s="56"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A62" s="12" t="s">
@@ -7131,13 +7152,13 @@
       <c r="N62" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="O62" s="45">
+      <c r="O62" s="43">
         <v>200000</v>
       </c>
-      <c r="P62" s="45">
+      <c r="P62" s="43">
         <v>0</v>
       </c>
-      <c r="Q62" s="45">
+      <c r="Q62" s="43">
         <f t="shared" si="2"/>
         <v>200000</v>
       </c>
@@ -7151,7 +7172,7 @@
       <c r="T62" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U62" s="65"/>
+      <c r="U62" s="56"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A63" s="11" t="s">
@@ -7193,13 +7214,13 @@
       <c r="N63" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="O63" s="45">
+      <c r="O63" s="43">
         <v>200000</v>
       </c>
-      <c r="P63" s="45">
+      <c r="P63" s="43">
         <v>0</v>
       </c>
-      <c r="Q63" s="45">
+      <c r="Q63" s="43">
         <f t="shared" si="2"/>
         <v>200000</v>
       </c>
@@ -7213,7 +7234,7 @@
       <c r="T63" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U63" s="65"/>
+      <c r="U63" s="56"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A64" s="12" t="s">
@@ -7255,13 +7276,13 @@
       <c r="N64" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="O64" s="44">
+      <c r="O64" s="42">
         <v>0</v>
       </c>
-      <c r="P64" s="44">
+      <c r="P64" s="42">
         <v>170681</v>
       </c>
-      <c r="Q64" s="45">
+      <c r="Q64" s="43">
         <f t="shared" si="2"/>
         <v>170681</v>
       </c>
@@ -7275,7 +7296,7 @@
       <c r="T64" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U64" s="65"/>
+      <c r="U64" s="56"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A65" s="12" t="s">
@@ -7317,13 +7338,13 @@
       <c r="N65" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O65" s="44">
+      <c r="O65" s="42">
         <v>0</v>
       </c>
-      <c r="P65" s="44">
+      <c r="P65" s="42">
         <v>546923</v>
       </c>
-      <c r="Q65" s="45">
+      <c r="Q65" s="43">
         <f t="shared" si="2"/>
         <v>546923</v>
       </c>
@@ -7337,7 +7358,7 @@
       <c r="T65" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U65" s="65"/>
+      <c r="U65" s="56"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A66" s="12" t="s">
@@ -7379,13 +7400,13 @@
       <c r="N66" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O66" s="45">
+      <c r="O66" s="43">
         <v>0</v>
       </c>
-      <c r="P66" s="44">
+      <c r="P66" s="42">
         <v>92730</v>
       </c>
-      <c r="Q66" s="45">
+      <c r="Q66" s="43">
         <f t="shared" si="2"/>
         <v>92730</v>
       </c>
@@ -7399,7 +7420,7 @@
       <c r="T66" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U66" s="65"/>
+      <c r="U66" s="56"/>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A67" s="12" t="s">
@@ -7441,13 +7462,13 @@
       <c r="N67" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="O67" s="44">
+      <c r="O67" s="42">
         <v>855000</v>
       </c>
-      <c r="P67" s="44">
+      <c r="P67" s="42">
         <v>196700</v>
       </c>
-      <c r="Q67" s="45">
+      <c r="Q67" s="43">
         <f t="shared" si="2"/>
         <v>1051700</v>
       </c>
@@ -7461,7 +7482,7 @@
       <c r="T67" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U67" s="65"/>
+      <c r="U67" s="56"/>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
@@ -7503,13 +7524,13 @@
       <c r="N68" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O68" s="45">
+      <c r="O68" s="43">
         <v>150000</v>
       </c>
-      <c r="P68" s="45">
+      <c r="P68" s="43">
         <v>60000</v>
       </c>
-      <c r="Q68" s="45">
+      <c r="Q68" s="43">
         <f t="shared" si="2"/>
         <v>210000</v>
       </c>
@@ -7523,7 +7544,7 @@
       <c r="T68" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U68" s="65"/>
+      <c r="U68" s="56"/>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A69" s="12" t="s">
@@ -7565,13 +7586,13 @@
       <c r="N69" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O69" s="44">
+      <c r="O69" s="42">
         <v>1200000</v>
       </c>
-      <c r="P69" s="44">
+      <c r="P69" s="42">
         <v>525090</v>
       </c>
-      <c r="Q69" s="45">
+      <c r="Q69" s="43">
         <f t="shared" si="2"/>
         <v>1725090</v>
       </c>
@@ -7585,7 +7606,7 @@
       <c r="T69" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U69" s="65"/>
+      <c r="U69" s="56"/>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A70" s="22" t="s">
@@ -7627,13 +7648,13 @@
       <c r="N70" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O70" s="44">
+      <c r="O70" s="42">
         <v>3026000</v>
       </c>
-      <c r="P70" s="44">
+      <c r="P70" s="42">
         <v>250000</v>
       </c>
-      <c r="Q70" s="45">
+      <c r="Q70" s="43">
         <f t="shared" ref="Q70:Q75" si="5">P70+O70</f>
         <v>3276000</v>
       </c>
@@ -7647,7 +7668,7 @@
       <c r="T70" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U70" s="65"/>
+      <c r="U70" s="56"/>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
@@ -7689,13 +7710,13 @@
       <c r="N71" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="O71" s="45">
+      <c r="O71" s="43">
         <v>270000</v>
       </c>
-      <c r="P71" s="45">
+      <c r="P71" s="43">
         <v>111435</v>
       </c>
-      <c r="Q71" s="45">
+      <c r="Q71" s="43">
         <f t="shared" si="5"/>
         <v>381435</v>
       </c>
@@ -7709,7 +7730,7 @@
       <c r="T71" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U71" s="65"/>
+      <c r="U71" s="56"/>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
@@ -7751,13 +7772,13 @@
       <c r="N72" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O72" s="45">
+      <c r="O72" s="43">
         <v>150000</v>
       </c>
-      <c r="P72" s="45">
+      <c r="P72" s="43">
         <v>60000</v>
       </c>
-      <c r="Q72" s="45">
+      <c r="Q72" s="43">
         <f t="shared" si="5"/>
         <v>210000</v>
       </c>
@@ -7771,7 +7792,7 @@
       <c r="T72" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U72" s="65"/>
+      <c r="U72" s="56"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A73" s="12" t="s">
@@ -7813,13 +7834,13 @@
       <c r="N73" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="O73" s="44">
+      <c r="O73" s="42">
         <v>0</v>
       </c>
-      <c r="P73" s="44">
+      <c r="P73" s="42">
         <v>217691</v>
       </c>
-      <c r="Q73" s="45">
+      <c r="Q73" s="43">
         <f t="shared" si="5"/>
         <v>217691</v>
       </c>
@@ -7833,7 +7854,7 @@
       <c r="T73" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U73" s="65"/>
+      <c r="U73" s="56"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A74" s="12" t="s">
@@ -7875,13 +7896,13 @@
       <c r="N74" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O74" s="45">
+      <c r="O74" s="43">
         <v>1793983</v>
       </c>
-      <c r="P74" s="45">
+      <c r="P74" s="43">
         <v>200000</v>
       </c>
-      <c r="Q74" s="45">
+      <c r="Q74" s="43">
         <f t="shared" si="5"/>
         <v>1993983</v>
       </c>
@@ -7895,7 +7916,7 @@
       <c r="T74" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U74" s="65"/>
+      <c r="U74" s="56"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A75" s="12" t="s">
@@ -7937,13 +7958,13 @@
       <c r="N75" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O75" s="44">
+      <c r="O75" s="42">
         <v>0</v>
       </c>
-      <c r="P75" s="44">
+      <c r="P75" s="42">
         <v>540923</v>
       </c>
-      <c r="Q75" s="45">
+      <c r="Q75" s="43">
         <f t="shared" si="5"/>
         <v>540923</v>
       </c>
@@ -7957,7 +7978,7 @@
       <c r="T75" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U75" s="65"/>
+      <c r="U75" s="56"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A76" s="12" t="s">
@@ -7999,13 +8020,13 @@
       <c r="N76" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O76" s="44">
+      <c r="O76" s="42">
         <v>500000</v>
       </c>
-      <c r="P76" s="44">
+      <c r="P76" s="42">
         <v>819491</v>
       </c>
-      <c r="Q76" s="45">
+      <c r="Q76" s="43">
         <f>P76+O76</f>
         <v>1319491</v>
       </c>
@@ -8019,7 +8040,7 @@
       <c r="T76" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="U76" s="65"/>
+      <c r="U76" s="56"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A77" s="12" t="s">
@@ -8061,13 +8082,13 @@
       <c r="N77" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="O77" s="44">
+      <c r="O77" s="42">
         <v>1000000</v>
       </c>
-      <c r="P77" s="44">
+      <c r="P77" s="42">
         <v>300000</v>
       </c>
-      <c r="Q77" s="43">
+      <c r="Q77" s="41">
         <f t="shared" ref="Q77:Q97" si="7">P77+O77</f>
         <v>1300000</v>
       </c>
@@ -8081,7 +8102,7 @@
       <c r="T77" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="U77" s="65"/>
+      <c r="U77" s="56"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A78" s="12" t="s">
@@ -8123,13 +8144,13 @@
       <c r="N78" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O78" s="44">
+      <c r="O78" s="42">
         <v>500000</v>
       </c>
-      <c r="P78" s="44">
+      <c r="P78" s="42">
         <v>892535</v>
       </c>
-      <c r="Q78" s="43">
+      <c r="Q78" s="41">
         <f t="shared" si="7"/>
         <v>1392535</v>
       </c>
@@ -8143,7 +8164,7 @@
       <c r="T78" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="U78" s="65"/>
+      <c r="U78" s="56"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
@@ -8185,13 +8206,13 @@
       <c r="N79" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="O79" s="44">
+      <c r="O79" s="42">
         <v>150000</v>
       </c>
-      <c r="P79" s="44">
+      <c r="P79" s="42">
         <v>40000</v>
       </c>
-      <c r="Q79" s="43">
+      <c r="Q79" s="41">
         <f t="shared" si="7"/>
         <v>190000</v>
       </c>
@@ -8205,7 +8226,7 @@
       <c r="T79" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="U79" s="65"/>
+      <c r="U79" s="56"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A80" s="12" t="s">
@@ -8247,13 +8268,13 @@
       <c r="N80" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O80" s="44">
+      <c r="O80" s="42">
         <v>500000</v>
       </c>
-      <c r="P80" s="44">
+      <c r="P80" s="42">
         <v>391740</v>
       </c>
-      <c r="Q80" s="43">
+      <c r="Q80" s="41">
         <f t="shared" si="7"/>
         <v>891740</v>
       </c>
@@ -8267,7 +8288,7 @@
       <c r="T80" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="U80" s="65"/>
+      <c r="U80" s="56"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A81" s="12" t="s">
@@ -8309,13 +8330,13 @@
       <c r="N81" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O81" s="44">
+      <c r="O81" s="42">
         <v>788712</v>
       </c>
-      <c r="P81" s="44">
+      <c r="P81" s="42">
         <v>500000</v>
       </c>
-      <c r="Q81" s="43">
+      <c r="Q81" s="41">
         <f t="shared" si="7"/>
         <v>1288712</v>
       </c>
@@ -8329,7 +8350,7 @@
       <c r="T81" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="U81" s="65"/>
+      <c r="U81" s="56"/>
     </row>
     <row r="82" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="12" t="s">
@@ -8377,7 +8398,7 @@
       <c r="P82" s="31">
         <v>221635</v>
       </c>
-      <c r="Q82" s="43">
+      <c r="Q82" s="41">
         <f t="shared" si="7"/>
         <v>791635</v>
       </c>
@@ -8391,7 +8412,7 @@
       <c r="T82" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="U82" s="65"/>
+      <c r="U82" s="56"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A83" s="12" t="s">
@@ -8439,7 +8460,7 @@
       <c r="P83" s="15">
         <v>0</v>
       </c>
-      <c r="Q83" s="45">
+      <c r="Q83" s="43">
         <f t="shared" si="7"/>
         <v>200000</v>
       </c>
@@ -8453,7 +8474,7 @@
       <c r="T83" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="U83" s="65"/>
+      <c r="U83" s="56"/>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A84" s="12" t="s">
@@ -8498,10 +8519,10 @@
       <c r="O84" s="15">
         <v>200000</v>
       </c>
-      <c r="P84" s="44">
+      <c r="P84" s="42">
         <v>0</v>
       </c>
-      <c r="Q84" s="45">
+      <c r="Q84" s="43">
         <f t="shared" si="7"/>
         <v>200000</v>
       </c>
@@ -8515,7 +8536,7 @@
       <c r="T84" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="U84" s="65"/>
+      <c r="U84" s="56"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A85" s="12" t="s">
@@ -8557,13 +8578,13 @@
       <c r="N85" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O85" s="44">
+      <c r="O85" s="42">
         <v>0</v>
       </c>
-      <c r="P85" s="44">
+      <c r="P85" s="42">
         <v>0</v>
       </c>
-      <c r="Q85" s="45">
+      <c r="Q85" s="43">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -8577,7 +8598,7 @@
       <c r="T85" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="U85" s="65"/>
+      <c r="U85" s="56"/>
     </row>
     <row r="86" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="6" t="s">
@@ -8619,13 +8640,13 @@
       <c r="N86" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="O86" s="44">
+      <c r="O86" s="42">
         <v>360000</v>
       </c>
-      <c r="P86" s="44">
+      <c r="P86" s="42">
         <v>152495</v>
       </c>
-      <c r="Q86" s="43">
+      <c r="Q86" s="41">
         <f t="shared" si="7"/>
         <v>512495</v>
       </c>
@@ -8639,7 +8660,7 @@
       <c r="T86" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="U86" s="65"/>
+      <c r="U86" s="56"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A87" s="22" t="s">
@@ -8681,13 +8702,13 @@
       <c r="N87" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="O87" s="44">
+      <c r="O87" s="42">
         <v>0</v>
       </c>
-      <c r="P87" s="44">
+      <c r="P87" s="42">
         <v>0</v>
       </c>
-      <c r="Q87" s="45">
+      <c r="Q87" s="43">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -8701,7 +8722,7 @@
       <c r="T87" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="U87" s="65"/>
+      <c r="U87" s="56"/>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A88" s="12" t="s">
@@ -8743,13 +8764,13 @@
       <c r="N88" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="O88" s="44">
+      <c r="O88" s="42">
         <v>600000</v>
       </c>
-      <c r="P88" s="44">
+      <c r="P88" s="42">
         <v>400000</v>
       </c>
-      <c r="Q88" s="45">
+      <c r="Q88" s="43">
         <f t="shared" si="7"/>
         <v>1000000</v>
       </c>
@@ -8763,7 +8784,7 @@
       <c r="T88" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="U88" s="65"/>
+      <c r="U88" s="56"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A89" s="12" t="s">
@@ -8805,13 +8826,13 @@
       <c r="N89" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O89" s="44">
+      <c r="O89" s="42">
         <v>900000</v>
       </c>
-      <c r="P89" s="44">
+      <c r="P89" s="42">
         <v>461679</v>
       </c>
-      <c r="Q89" s="45">
+      <c r="Q89" s="43">
         <f t="shared" si="7"/>
         <v>1361679</v>
       </c>
@@ -8825,7 +8846,7 @@
       <c r="T89" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="U89" s="65"/>
+      <c r="U89" s="56"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A90" s="12" t="s">
@@ -8867,13 +8888,13 @@
       <c r="N90" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O90" s="44">
+      <c r="O90" s="42">
         <v>1000000</v>
       </c>
-      <c r="P90" s="44">
+      <c r="P90" s="42">
         <v>538647</v>
       </c>
-      <c r="Q90" s="45">
+      <c r="Q90" s="43">
         <f t="shared" si="7"/>
         <v>1538647</v>
       </c>
@@ -8887,7 +8908,7 @@
       <c r="T90" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="U90" s="65"/>
+      <c r="U90" s="56"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A91" s="12" t="s">
@@ -8929,13 +8950,13 @@
       <c r="N91" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O91" s="44">
+      <c r="O91" s="42">
         <v>5494650</v>
       </c>
-      <c r="P91" s="44">
+      <c r="P91" s="42">
         <v>1211081</v>
       </c>
-      <c r="Q91" s="45">
+      <c r="Q91" s="43">
         <f t="shared" si="7"/>
         <v>6705731</v>
       </c>
@@ -8949,7 +8970,7 @@
       <c r="T91" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="U91" s="65"/>
+      <c r="U91" s="56"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A92" s="12" t="s">
@@ -8991,13 +9012,13 @@
       <c r="N92" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O92" s="44">
+      <c r="O92" s="42">
         <v>1430307</v>
       </c>
-      <c r="P92" s="44">
+      <c r="P92" s="42">
         <v>600349</v>
       </c>
-      <c r="Q92" s="45">
+      <c r="Q92" s="43">
         <f t="shared" si="7"/>
         <v>2030656</v>
       </c>
@@ -9011,7 +9032,7 @@
       <c r="T92" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="U92" s="65"/>
+      <c r="U92" s="56"/>
     </row>
     <row r="93" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="29" t="s">
@@ -9053,13 +9074,13 @@
       <c r="N93" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="O93" s="44">
+      <c r="O93" s="42">
         <v>500000</v>
       </c>
-      <c r="P93" s="44">
+      <c r="P93" s="42">
         <v>590836</v>
       </c>
-      <c r="Q93" s="45">
+      <c r="Q93" s="43">
         <f t="shared" si="7"/>
         <v>1090836</v>
       </c>
@@ -9073,7 +9094,7 @@
       <c r="T93" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="U93" s="65"/>
+      <c r="U93" s="56"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A94" s="12" t="s">
@@ -9115,13 +9136,13 @@
       <c r="N94" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O94" s="44">
+      <c r="O94" s="42">
         <v>200000</v>
       </c>
-      <c r="P94" s="44">
+      <c r="P94" s="42">
         <v>0</v>
       </c>
-      <c r="Q94" s="45">
+      <c r="Q94" s="43">
         <f t="shared" si="7"/>
         <v>200000</v>
       </c>
@@ -9135,7 +9156,7 @@
       <c r="T94" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U94" s="65"/>
+      <c r="U94" s="56"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A95" s="12" t="s">
@@ -9177,13 +9198,13 @@
       <c r="N95" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="O95" s="44">
+      <c r="O95" s="42">
         <v>0</v>
       </c>
-      <c r="P95" s="44">
+      <c r="P95" s="42">
         <v>0</v>
       </c>
-      <c r="Q95" s="45">
+      <c r="Q95" s="43">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -9197,7 +9218,7 @@
       <c r="T95" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U95" s="65"/>
+      <c r="U95" s="56"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A96" s="8" t="s">
@@ -9239,13 +9260,13 @@
       <c r="N96" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="O96" s="45">
+      <c r="O96" s="43">
         <v>360000</v>
       </c>
-      <c r="P96" s="45">
+      <c r="P96" s="43">
         <v>92495</v>
       </c>
-      <c r="Q96" s="45">
+      <c r="Q96" s="43">
         <f t="shared" si="7"/>
         <v>452495</v>
       </c>
@@ -9259,7 +9280,7 @@
       <c r="T96" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U96" s="65"/>
+      <c r="U96" s="56"/>
     </row>
     <row r="97" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
@@ -9301,13 +9322,13 @@
       <c r="N97" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O97" s="44">
+      <c r="O97" s="42">
         <v>1000000</v>
       </c>
-      <c r="P97" s="44">
+      <c r="P97" s="42">
         <v>495000</v>
       </c>
-      <c r="Q97" s="45">
+      <c r="Q97" s="43">
         <f t="shared" si="7"/>
         <v>1495000</v>
       </c>
@@ -9321,7 +9342,7 @@
       <c r="T97" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U97" s="65"/>
+      <c r="U97" s="56"/>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98" s="12" t="s">
@@ -9363,13 +9384,13 @@
       <c r="N98" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O98" s="44">
+      <c r="O98" s="42">
         <v>2245845</v>
       </c>
-      <c r="P98" s="44">
+      <c r="P98" s="42">
         <v>474962</v>
       </c>
-      <c r="Q98" s="45">
+      <c r="Q98" s="43">
         <f>P98+O98</f>
         <v>2720807</v>
       </c>
@@ -9383,7 +9404,7 @@
       <c r="T98" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U98" s="65"/>
+      <c r="U98" s="56"/>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99" s="12" t="s">
@@ -9425,13 +9446,13 @@
       <c r="N99" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="O99" s="45">
+      <c r="O99" s="43">
         <v>0</v>
       </c>
-      <c r="P99" s="45">
+      <c r="P99" s="43">
         <v>725636</v>
       </c>
-      <c r="Q99" s="45">
+      <c r="Q99" s="43">
         <f>P99+O99</f>
         <v>725636</v>
       </c>
@@ -9445,7 +9466,7 @@
       <c r="T99" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U99" s="65"/>
+      <c r="U99" s="56"/>
     </row>
     <row r="100" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="29" t="s">
@@ -9487,13 +9508,13 @@
       <c r="N100" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O100" s="44">
+      <c r="O100" s="42">
         <v>1200000</v>
       </c>
-      <c r="P100" s="45">
+      <c r="P100" s="43">
         <v>515054</v>
       </c>
-      <c r="Q100" s="45">
+      <c r="Q100" s="43">
         <f>P100+O100</f>
         <v>1715054</v>
       </c>
@@ -9507,7 +9528,7 @@
       <c r="T100" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U100" s="65"/>
+      <c r="U100" s="56"/>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101" s="12" t="s">
@@ -9549,13 +9570,13 @@
       <c r="N101" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O101" s="44">
+      <c r="O101" s="42">
         <v>0</v>
       </c>
-      <c r="P101" s="44">
+      <c r="P101" s="42">
         <v>0</v>
       </c>
-      <c r="Q101" s="45">
+      <c r="Q101" s="43">
         <f>P101+O101</f>
         <v>0</v>
       </c>
@@ -9569,7 +9590,7 @@
       <c r="T101" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U101" s="65"/>
+      <c r="U101" s="56"/>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102" s="22" t="s">
@@ -9611,13 +9632,13 @@
       <c r="N102" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="O102" s="44">
+      <c r="O102" s="42">
         <v>0</v>
       </c>
-      <c r="P102" s="44">
+      <c r="P102" s="42">
         <v>0</v>
       </c>
-      <c r="Q102" s="45">
+      <c r="Q102" s="43">
         <f>P102+O102</f>
         <v>0</v>
       </c>
@@ -9631,7 +9652,7 @@
       <c r="T102" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U102" s="65"/>
+      <c r="U102" s="56"/>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A103" s="12" t="s">
@@ -9673,13 +9694,13 @@
       <c r="N103" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O103" s="44">
+      <c r="O103" s="42">
         <v>200000</v>
       </c>
-      <c r="P103" s="44">
+      <c r="P103" s="42">
         <v>0</v>
       </c>
-      <c r="Q103" s="45">
+      <c r="Q103" s="43">
         <f t="shared" ref="Q103:Q109" si="9">P103+O103</f>
         <v>200000</v>
       </c>
@@ -9693,7 +9714,7 @@
       <c r="T103" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U103" s="65"/>
+      <c r="U103" s="56"/>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104" s="12" t="s">
@@ -9735,13 +9756,13 @@
       <c r="N104" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O104" s="44">
+      <c r="O104" s="42">
         <v>2148649</v>
       </c>
-      <c r="P104" s="44">
+      <c r="P104" s="42">
         <v>0</v>
       </c>
-      <c r="Q104" s="45">
+      <c r="Q104" s="43">
         <f t="shared" si="9"/>
         <v>2148649</v>
       </c>
@@ -9755,7 +9776,7 @@
       <c r="T104" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U104" s="65"/>
+      <c r="U104" s="56"/>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
@@ -9803,7 +9824,7 @@
       <c r="P105" s="15">
         <v>0</v>
       </c>
-      <c r="Q105" s="45">
+      <c r="Q105" s="43">
         <f t="shared" si="9"/>
         <v>60000</v>
       </c>
@@ -9817,7 +9838,7 @@
       <c r="T105" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U105" s="65"/>
+      <c r="U105" s="56"/>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
@@ -9865,7 +9886,7 @@
       <c r="P106" s="15">
         <v>0</v>
       </c>
-      <c r="Q106" s="45">
+      <c r="Q106" s="43">
         <f t="shared" si="9"/>
         <v>60000</v>
       </c>
@@ -9879,7 +9900,7 @@
       <c r="T106" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U106" s="65"/>
+      <c r="U106" s="56"/>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
@@ -9927,7 +9948,7 @@
       <c r="P107" s="15">
         <v>40000</v>
       </c>
-      <c r="Q107" s="45">
+      <c r="Q107" s="43">
         <f t="shared" si="9"/>
         <v>190000</v>
       </c>
@@ -9941,7 +9962,7 @@
       <c r="T107" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U107" s="65"/>
+      <c r="U107" s="56"/>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
@@ -9989,7 +10010,7 @@
       <c r="P108" s="15">
         <v>231750</v>
       </c>
-      <c r="Q108" s="45">
+      <c r="Q108" s="43">
         <f t="shared" si="9"/>
         <v>1231750</v>
       </c>
@@ -10003,7 +10024,7 @@
       <c r="T108" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U108" s="65"/>
+      <c r="U108" s="56"/>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
@@ -10051,7 +10072,7 @@
       <c r="P109" s="15">
         <v>60000</v>
       </c>
-      <c r="Q109" s="45">
+      <c r="Q109" s="43">
         <f t="shared" si="9"/>
         <v>210000</v>
       </c>
@@ -10065,7 +10086,7 @@
       <c r="T109" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U109" s="65"/>
+      <c r="U109" s="56"/>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A110" s="12" t="s">
@@ -10107,13 +10128,13 @@
       <c r="N110" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O110" s="44">
+      <c r="O110" s="42">
         <v>835588</v>
       </c>
-      <c r="P110" s="44">
+      <c r="P110" s="42">
         <v>200000</v>
       </c>
-      <c r="Q110" s="45">
+      <c r="Q110" s="43">
         <f>P110+O110</f>
         <v>1035588</v>
       </c>
@@ -10127,7 +10148,7 @@
       <c r="T110" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U110" s="65"/>
+      <c r="U110" s="56"/>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A111" s="12" t="s">
@@ -10169,13 +10190,13 @@
       <c r="N111" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O111" s="44">
+      <c r="O111" s="42">
         <v>1500000</v>
       </c>
-      <c r="P111" s="44">
+      <c r="P111" s="42">
         <v>333527</v>
       </c>
-      <c r="Q111" s="45">
+      <c r="Q111" s="43">
         <f t="shared" ref="Q111:Q118" si="10">P111+O111</f>
         <v>1833527</v>
       </c>
@@ -10189,7 +10210,7 @@
       <c r="T111" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U111" s="65"/>
+      <c r="U111" s="56"/>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A112" s="11" t="s">
@@ -10231,13 +10252,13 @@
       <c r="N112" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="O112" s="45">
+      <c r="O112" s="43">
         <v>420853</v>
       </c>
-      <c r="P112" s="45">
+      <c r="P112" s="43">
         <v>467395</v>
       </c>
-      <c r="Q112" s="45">
+      <c r="Q112" s="43">
         <f t="shared" si="10"/>
         <v>888248</v>
       </c>
@@ -10251,7 +10272,7 @@
       <c r="T112" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="U112" s="65"/>
+      <c r="U112" s="56"/>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A113" s="12" t="s">
@@ -10293,13 +10314,13 @@
       <c r="N113" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O113" s="44">
+      <c r="O113" s="42">
         <v>500000</v>
       </c>
-      <c r="P113" s="44">
+      <c r="P113" s="42">
         <v>998817</v>
       </c>
-      <c r="Q113" s="45">
+      <c r="Q113" s="43">
         <f t="shared" si="10"/>
         <v>1498817</v>
       </c>
@@ -10313,7 +10334,7 @@
       <c r="T113" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="U113" s="65"/>
+      <c r="U113" s="56"/>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A114" s="12" t="s">
@@ -10355,13 +10376,13 @@
       <c r="N114" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O114" s="44">
+      <c r="O114" s="42">
         <v>700000</v>
       </c>
-      <c r="P114" s="44">
+      <c r="P114" s="42">
         <v>497454</v>
       </c>
-      <c r="Q114" s="45">
+      <c r="Q114" s="43">
         <f t="shared" si="10"/>
         <v>1197454</v>
       </c>
@@ -10375,7 +10396,7 @@
       <c r="T114" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="U114" s="65"/>
+      <c r="U114" s="56"/>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A115" s="12" t="s">
@@ -10417,13 +10438,13 @@
       <c r="N115" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O115" s="44">
+      <c r="O115" s="42">
         <v>638483</v>
       </c>
-      <c r="P115" s="44">
+      <c r="P115" s="42">
         <v>200000</v>
       </c>
-      <c r="Q115" s="45">
+      <c r="Q115" s="43">
         <f t="shared" si="10"/>
         <v>838483</v>
       </c>
@@ -10437,7 +10458,7 @@
       <c r="T115" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="U115" s="65"/>
+      <c r="U115" s="56"/>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A116" s="12" t="s">
@@ -10479,13 +10500,13 @@
       <c r="N116" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="O116" s="44">
+      <c r="O116" s="42">
         <v>2000500</v>
       </c>
-      <c r="P116" s="44">
+      <c r="P116" s="42">
         <v>557454</v>
       </c>
-      <c r="Q116" s="45">
+      <c r="Q116" s="43">
         <f t="shared" si="10"/>
         <v>2557954</v>
       </c>
@@ -10499,7 +10520,7 @@
       <c r="T116" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="U116" s="65"/>
+      <c r="U116" s="56"/>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
@@ -10541,13 +10562,13 @@
       <c r="N117" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O117" s="45">
+      <c r="O117" s="43">
         <v>150000</v>
       </c>
-      <c r="P117" s="45">
+      <c r="P117" s="43">
         <v>60000</v>
       </c>
-      <c r="Q117" s="45">
+      <c r="Q117" s="43">
         <f t="shared" si="10"/>
         <v>210000</v>
       </c>
@@ -10561,7 +10582,7 @@
       <c r="T117" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="U117" s="65"/>
+      <c r="U117" s="56"/>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
@@ -10603,13 +10624,13 @@
       <c r="N118" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O118" s="45">
+      <c r="O118" s="43">
         <v>1000000</v>
       </c>
-      <c r="P118" s="45">
+      <c r="P118" s="43">
         <v>231750</v>
       </c>
-      <c r="Q118" s="45">
+      <c r="Q118" s="43">
         <f t="shared" si="10"/>
         <v>1231750</v>
       </c>
@@ -10623,7 +10644,7 @@
       <c r="T118" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="U118" s="65"/>
+      <c r="U118" s="56"/>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A119" s="12" t="s">
@@ -10665,13 +10686,13 @@
       <c r="N119" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O119" s="45">
+      <c r="O119" s="43">
         <v>1474962</v>
       </c>
-      <c r="P119" s="44">
+      <c r="P119" s="42">
         <v>0</v>
       </c>
-      <c r="Q119" s="45">
+      <c r="Q119" s="43">
         <f>P119+O119</f>
         <v>1474962</v>
       </c>
@@ -10685,7 +10706,7 @@
       <c r="T119" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="U119" s="65"/>
+      <c r="U119" s="56"/>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A120" s="12" t="s">
@@ -10727,13 +10748,13 @@
       <c r="N120" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="O120" s="45">
+      <c r="O120" s="43">
         <v>2000000</v>
       </c>
-      <c r="P120" s="45">
+      <c r="P120" s="43">
         <v>0</v>
       </c>
-      <c r="Q120" s="45">
+      <c r="Q120" s="43">
         <f>P120+O120</f>
         <v>2000000</v>
       </c>
@@ -10747,7 +10768,7 @@
       <c r="T120" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="U120" s="65"/>
+      <c r="U120" s="56"/>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A121" s="12" t="s">
@@ -10789,13 +10810,13 @@
       <c r="N121" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="O121" s="45">
+      <c r="O121" s="43">
         <v>2000000</v>
       </c>
-      <c r="P121" s="45">
+      <c r="P121" s="43">
         <v>0</v>
       </c>
-      <c r="Q121" s="45">
+      <c r="Q121" s="43">
         <f>P121+O121</f>
         <v>2000000</v>
       </c>
@@ -10809,7 +10830,7 @@
       <c r="T121" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="U121" s="65"/>
+      <c r="U121" s="56"/>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A122" s="12" t="s">
@@ -10851,13 +10872,13 @@
       <c r="N122" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="O122" s="45">
+      <c r="O122" s="43">
         <v>2000000</v>
       </c>
-      <c r="P122" s="44">
+      <c r="P122" s="42">
         <v>300000</v>
       </c>
-      <c r="Q122" s="45">
+      <c r="Q122" s="43">
         <f>P122+O122</f>
         <v>2300000</v>
       </c>
@@ -10871,7 +10892,7 @@
       <c r="T122" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="U122" s="65"/>
+      <c r="U122" s="56"/>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A123" s="12" t="s">
@@ -10913,13 +10934,13 @@
       <c r="N123" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O123" s="44">
+      <c r="O123" s="42">
         <v>1000000</v>
       </c>
-      <c r="P123" s="44">
+      <c r="P123" s="42">
         <v>693500</v>
       </c>
-      <c r="Q123" s="45">
+      <c r="Q123" s="43">
         <f t="shared" ref="Q123:Q148" si="11">P123+O123</f>
         <v>1693500</v>
       </c>
@@ -10933,7 +10954,7 @@
       <c r="T123" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="U123" s="65"/>
+      <c r="U123" s="56"/>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A124" s="12" t="s">
@@ -10975,13 +10996,13 @@
       <c r="N124" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O124" s="45">
+      <c r="O124" s="43">
         <v>0</v>
       </c>
-      <c r="P124" s="45">
+      <c r="P124" s="43">
         <v>0</v>
       </c>
-      <c r="Q124" s="45">
+      <c r="Q124" s="43">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -10995,7 +11016,7 @@
       <c r="T124" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="U124" s="65"/>
+      <c r="U124" s="56"/>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A125" s="12" t="s">
@@ -11037,13 +11058,13 @@
       <c r="N125" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="O125" s="44">
+      <c r="O125" s="42">
         <v>150000</v>
       </c>
-      <c r="P125" s="44">
+      <c r="P125" s="42">
         <v>443127</v>
       </c>
-      <c r="Q125" s="45">
+      <c r="Q125" s="43">
         <f t="shared" si="11"/>
         <v>593127</v>
       </c>
@@ -11057,7 +11078,7 @@
       <c r="T125" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="U125" s="65"/>
+      <c r="U125" s="56"/>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A126" s="12" t="s">
@@ -11099,13 +11120,13 @@
       <c r="N126" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O126" s="44">
+      <c r="O126" s="42">
         <v>1987902</v>
       </c>
-      <c r="P126" s="44">
+      <c r="P126" s="42">
         <v>270000</v>
       </c>
-      <c r="Q126" s="45">
+      <c r="Q126" s="43">
         <f t="shared" si="11"/>
         <v>2257902</v>
       </c>
@@ -11119,7 +11140,7 @@
       <c r="T126" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="U126" s="65"/>
+      <c r="U126" s="56"/>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A127" s="12" t="s">
@@ -11165,13 +11186,13 @@
       <c r="N127" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O127" s="45">
+      <c r="O127" s="43">
         <v>1100000</v>
       </c>
-      <c r="P127" s="44">
+      <c r="P127" s="42">
         <v>474962</v>
       </c>
-      <c r="Q127" s="45">
+      <c r="Q127" s="43">
         <f t="shared" si="11"/>
         <v>1574962</v>
       </c>
@@ -11185,7 +11206,7 @@
       <c r="T127" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U127" s="65"/>
+      <c r="U127" s="56"/>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A128" s="12" t="s">
@@ -11231,13 +11252,13 @@
       <c r="N128" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O128" s="44">
+      <c r="O128" s="42">
         <v>1100000</v>
       </c>
-      <c r="P128" s="44">
+      <c r="P128" s="42">
         <v>474962</v>
       </c>
-      <c r="Q128" s="45">
+      <c r="Q128" s="43">
         <f t="shared" si="11"/>
         <v>1574962</v>
       </c>
@@ -11251,7 +11272,7 @@
       <c r="T128" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U128" s="65"/>
+      <c r="U128" s="56"/>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A129" s="12" t="s">
@@ -11297,13 +11318,13 @@
       <c r="N129" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O129" s="44">
+      <c r="O129" s="42">
         <v>0</v>
       </c>
-      <c r="P129" s="44">
+      <c r="P129" s="42">
         <v>0</v>
       </c>
-      <c r="Q129" s="45">
+      <c r="Q129" s="43">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -11317,7 +11338,7 @@
       <c r="T129" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U129" s="65"/>
+      <c r="U129" s="56"/>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
@@ -11363,13 +11384,13 @@
       <c r="N130" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="O130" s="44">
+      <c r="O130" s="42">
         <v>270000</v>
       </c>
-      <c r="P130" s="44">
+      <c r="P130" s="42">
         <v>71435</v>
       </c>
-      <c r="Q130" s="45">
+      <c r="Q130" s="43">
         <f t="shared" si="11"/>
         <v>341435</v>
       </c>
@@ -11383,7 +11404,7 @@
       <c r="T130" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U130" s="65"/>
+      <c r="U130" s="56"/>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A131" s="9" t="s">
@@ -11429,13 +11450,13 @@
       <c r="N131" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="O131" s="44">
+      <c r="O131" s="42">
         <v>360000</v>
       </c>
-      <c r="P131" s="44">
+      <c r="P131" s="42">
         <v>92495</v>
       </c>
-      <c r="Q131" s="45">
+      <c r="Q131" s="43">
         <f t="shared" si="11"/>
         <v>452495</v>
       </c>
@@ -11449,7 +11470,7 @@
       <c r="T131" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U131" s="65"/>
+      <c r="U131" s="56"/>
     </row>
     <row r="132" spans="1:21" s="26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A132" s="22" t="s">
@@ -11495,13 +11516,13 @@
       <c r="N132" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O132" s="44">
+      <c r="O132" s="42">
         <v>500000</v>
       </c>
-      <c r="P132" s="44">
+      <c r="P132" s="42">
         <v>1963000</v>
       </c>
-      <c r="Q132" s="45">
+      <c r="Q132" s="43">
         <f t="shared" si="11"/>
         <v>2463000</v>
       </c>
@@ -11515,7 +11536,7 @@
       <c r="T132" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U132" s="66"/>
+      <c r="U132" s="56"/>
     </row>
     <row r="133" spans="1:21" s="26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A133" s="12" t="s">
@@ -11561,13 +11582,13 @@
       <c r="N133" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O133" s="44">
+      <c r="O133" s="42">
         <v>500000</v>
       </c>
-      <c r="P133" s="44">
+      <c r="P133" s="42">
         <v>350000</v>
       </c>
-      <c r="Q133" s="45">
+      <c r="Q133" s="43">
         <f t="shared" si="11"/>
         <v>850000</v>
       </c>
@@ -11581,7 +11602,7 @@
       <c r="T133" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U133" s="66"/>
+      <c r="U133" s="56"/>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A134" s="12" t="s">
@@ -11627,13 +11648,13 @@
       <c r="N134" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="O134" s="44">
+      <c r="O134" s="42">
         <v>2000000</v>
       </c>
-      <c r="P134" s="44">
+      <c r="P134" s="42">
         <v>3000000</v>
       </c>
-      <c r="Q134" s="45">
+      <c r="Q134" s="43">
         <f t="shared" si="11"/>
         <v>5000000</v>
       </c>
@@ -11647,7 +11668,7 @@
       <c r="T134" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U134" s="65"/>
+      <c r="U134" s="56"/>
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A135" s="9" t="s">
@@ -11693,13 +11714,13 @@
       <c r="N135" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O135" s="45">
+      <c r="O135" s="43">
         <v>400000</v>
       </c>
-      <c r="P135" s="45">
+      <c r="P135" s="43">
         <v>0</v>
       </c>
-      <c r="Q135" s="45">
+      <c r="Q135" s="43">
         <f t="shared" si="11"/>
         <v>400000</v>
       </c>
@@ -11713,7 +11734,7 @@
       <c r="T135" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U135" s="65"/>
+      <c r="U135" s="56"/>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A136" s="9" t="s">
@@ -11759,13 +11780,13 @@
       <c r="N136" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O136" s="45">
+      <c r="O136" s="43">
         <v>150000</v>
       </c>
-      <c r="P136" s="45">
+      <c r="P136" s="43">
         <v>0</v>
       </c>
-      <c r="Q136" s="45">
+      <c r="Q136" s="43">
         <f t="shared" si="11"/>
         <v>150000</v>
       </c>
@@ -11779,7 +11800,7 @@
       <c r="T136" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U136" s="65"/>
+      <c r="U136" s="56"/>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A137" s="9" t="s">
@@ -11825,13 +11846,13 @@
       <c r="N137" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O137" s="45">
+      <c r="O137" s="43">
         <v>1000000</v>
       </c>
-      <c r="P137" s="45">
+      <c r="P137" s="43">
         <v>0</v>
       </c>
-      <c r="Q137" s="45">
+      <c r="Q137" s="43">
         <f t="shared" si="11"/>
         <v>1000000</v>
       </c>
@@ -11845,7 +11866,7 @@
       <c r="T137" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U137" s="65"/>
+      <c r="U137" s="56"/>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A138" s="9" t="s">
@@ -11891,13 +11912,13 @@
       <c r="N138" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O138" s="45">
+      <c r="O138" s="43">
         <v>1000000</v>
       </c>
-      <c r="P138" s="45">
+      <c r="P138" s="43">
         <v>0</v>
       </c>
-      <c r="Q138" s="45">
+      <c r="Q138" s="43">
         <f t="shared" si="11"/>
         <v>1000000</v>
       </c>
@@ -11911,7 +11932,7 @@
       <c r="T138" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U138" s="65"/>
+      <c r="U138" s="56"/>
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A139" s="9" t="s">
@@ -11957,13 +11978,13 @@
       <c r="N139" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O139" s="45">
+      <c r="O139" s="43">
         <v>108000</v>
       </c>
-      <c r="P139" s="45">
+      <c r="P139" s="43">
         <v>0</v>
       </c>
-      <c r="Q139" s="45">
+      <c r="Q139" s="43">
         <f t="shared" si="11"/>
         <v>108000</v>
       </c>
@@ -11977,7 +11998,7 @@
       <c r="T139" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U139" s="65"/>
+      <c r="U139" s="56"/>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
@@ -12023,13 +12044,13 @@
       <c r="N140" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="O140" s="45">
+      <c r="O140" s="43">
         <v>270000</v>
       </c>
-      <c r="P140" s="45">
+      <c r="P140" s="43">
         <v>71435</v>
       </c>
-      <c r="Q140" s="45">
+      <c r="Q140" s="43">
         <f t="shared" si="11"/>
         <v>341435</v>
       </c>
@@ -12043,7 +12064,7 @@
       <c r="T140" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U140" s="65"/>
+      <c r="U140" s="56"/>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
@@ -12089,13 +12110,13 @@
       <c r="N141" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O141" s="45">
+      <c r="O141" s="43">
         <v>3000000</v>
       </c>
-      <c r="P141" s="45">
+      <c r="P141" s="43">
         <v>139050</v>
       </c>
-      <c r="Q141" s="45">
+      <c r="Q141" s="43">
         <f t="shared" si="11"/>
         <v>3139050</v>
       </c>
@@ -12109,7 +12130,7 @@
       <c r="T141" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U141" s="65"/>
+      <c r="U141" s="56"/>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A142" s="12" t="s">
@@ -12155,13 +12176,13 @@
       <c r="N142" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O142" s="44">
+      <c r="O142" s="42">
         <v>350000</v>
       </c>
-      <c r="P142" s="44">
+      <c r="P142" s="42">
         <v>197989</v>
       </c>
-      <c r="Q142" s="45">
+      <c r="Q142" s="43">
         <f t="shared" si="11"/>
         <v>547989</v>
       </c>
@@ -12175,7 +12196,7 @@
       <c r="T142" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U142" s="65"/>
+      <c r="U142" s="56"/>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A143" s="12" t="s">
@@ -12221,13 +12242,13 @@
       <c r="N143" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="O143" s="45">
+      <c r="O143" s="43">
         <v>842820</v>
       </c>
-      <c r="P143" s="45">
+      <c r="P143" s="43">
         <v>0</v>
       </c>
-      <c r="Q143" s="45">
+      <c r="Q143" s="43">
         <f t="shared" si="11"/>
         <v>842820</v>
       </c>
@@ -12241,7 +12262,7 @@
       <c r="T143" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U143" s="65"/>
+      <c r="U143" s="56"/>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A144" s="12" t="s">
@@ -12287,13 +12308,13 @@
       <c r="N144" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="O144" s="44">
+      <c r="O144" s="42">
         <v>3986938</v>
       </c>
-      <c r="P144" s="44">
+      <c r="P144" s="42">
         <v>400908</v>
       </c>
-      <c r="Q144" s="45">
+      <c r="Q144" s="43">
         <f t="shared" si="11"/>
         <v>4387846</v>
       </c>
@@ -12307,7 +12328,7 @@
       <c r="T144" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U144" s="65"/>
+      <c r="U144" s="56"/>
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A145" s="12" t="s">
@@ -12353,13 +12374,13 @@
       <c r="N145" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="O145" s="44">
+      <c r="O145" s="42">
         <v>250000</v>
       </c>
-      <c r="P145" s="44">
+      <c r="P145" s="42">
         <v>370000</v>
       </c>
-      <c r="Q145" s="45">
+      <c r="Q145" s="43">
         <f t="shared" si="11"/>
         <v>620000</v>
       </c>
@@ -12373,7 +12394,7 @@
       <c r="T145" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U145" s="65"/>
+      <c r="U145" s="56"/>
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A146" s="12" t="s">
@@ -12419,13 +12440,13 @@
       <c r="N146" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O146" s="44">
+      <c r="O146" s="42">
         <v>1000000</v>
       </c>
-      <c r="P146" s="44">
+      <c r="P146" s="42">
         <v>965500</v>
       </c>
-      <c r="Q146" s="45">
+      <c r="Q146" s="43">
         <f t="shared" si="11"/>
         <v>1965500</v>
       </c>
@@ -12439,7 +12460,7 @@
       <c r="T146" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U146" s="65"/>
+      <c r="U146" s="56"/>
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A147" s="12" t="s">
@@ -12485,13 +12506,13 @@
       <c r="N147" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="O147" s="44">
+      <c r="O147" s="42">
         <v>2000000</v>
       </c>
-      <c r="P147" s="44">
+      <c r="P147" s="42">
         <v>300000</v>
       </c>
-      <c r="Q147" s="45">
+      <c r="Q147" s="43">
         <f t="shared" si="11"/>
         <v>2300000</v>
       </c>
@@ -12505,7 +12526,7 @@
       <c r="T147" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U147" s="65"/>
+      <c r="U147" s="56"/>
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A148" s="22" t="s">
@@ -12551,13 +12572,13 @@
       <c r="N148" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O148" s="44">
+      <c r="O148" s="42">
         <v>0</v>
       </c>
-      <c r="P148" s="44">
+      <c r="P148" s="42">
         <v>0</v>
       </c>
-      <c r="Q148" s="45">
+      <c r="Q148" s="43">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -12571,73 +12592,73 @@
       <c r="T148" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="U148" s="65"/>
+      <c r="U148" s="56"/>
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A149" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="B149" s="41" t="s">
+      <c r="B149" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C149" s="41">
+      <c r="C149" s="12">
         <v>57664431</v>
       </c>
-      <c r="D149" s="41" t="s">
+      <c r="D149" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="E149" s="41" t="s">
+      <c r="E149" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="F149" s="41" t="s">
+      <c r="F149" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G149" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H149" s="42">
+      <c r="G149" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H149" s="14">
         <v>46055</v>
       </c>
-      <c r="I149" s="42">
+      <c r="I149" s="14">
         <v>46083</v>
       </c>
       <c r="J149" s="24">
         <f t="shared" si="12"/>
         <v>21</v>
       </c>
-      <c r="K149" s="41" t="s">
+      <c r="K149" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L149" s="41" t="s">
+      <c r="L149" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M149" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N149" s="41" t="s">
+      <c r="M149" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N149" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O149" s="46">
+      <c r="O149" s="42">
         <v>2500000</v>
       </c>
-      <c r="P149" s="46">
+      <c r="P149" s="42">
         <v>2325347</v>
       </c>
-      <c r="Q149" s="44">
+      <c r="Q149" s="42">
         <f>P149+O149</f>
         <v>4825347</v>
       </c>
-      <c r="R149" s="42">
+      <c r="R149" s="14">
         <v>46084</v>
       </c>
       <c r="S149" s="24">
         <f t="shared" si="13"/>
         <v>22</v>
       </c>
-      <c r="T149" s="41" t="s">
+      <c r="T149" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="U149" s="48" t="s">
+      <c r="U149" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -12645,67 +12666,67 @@
       <c r="A150" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="B150" s="41" t="s">
+      <c r="B150" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C150" s="41">
+      <c r="C150" s="12">
         <v>57417024</v>
       </c>
-      <c r="D150" s="41" t="s">
+      <c r="D150" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E150" s="41">
+      <c r="E150" s="12">
         <v>2721710775</v>
       </c>
-      <c r="F150" s="41" t="s">
+      <c r="F150" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G150" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H150" s="42">
+      <c r="G150" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H150" s="14">
         <v>46050</v>
       </c>
-      <c r="I150" s="42">
+      <c r="I150" s="14">
         <v>46083</v>
       </c>
       <c r="J150" s="24">
         <f t="shared" si="12"/>
         <v>24</v>
       </c>
-      <c r="K150" s="41" t="s">
+      <c r="K150" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L150" s="41" t="s">
+      <c r="L150" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M150" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N150" s="41" t="s">
+      <c r="M150" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N150" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="O150" s="46">
+      <c r="O150" s="42">
         <v>150000</v>
       </c>
-      <c r="P150" s="46">
+      <c r="P150" s="42">
         <v>40000</v>
       </c>
-      <c r="Q150" s="44">
+      <c r="Q150" s="42">
         <f t="shared" ref="Q150:Q189" si="14">P150+O150</f>
         <v>190000</v>
       </c>
-      <c r="R150" s="42">
+      <c r="R150" s="14">
         <v>46084</v>
       </c>
       <c r="S150" s="24">
         <f t="shared" si="13"/>
         <v>25</v>
       </c>
-      <c r="T150" s="41" t="s">
+      <c r="T150" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="U150" s="48" t="s">
+      <c r="U150" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -12713,67 +12734,67 @@
       <c r="A151" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="B151" s="41" t="s">
+      <c r="B151" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C151" s="41">
+      <c r="C151" s="12">
         <v>57847231</v>
       </c>
-      <c r="D151" s="41" t="s">
+      <c r="D151" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="E151" s="41" t="s">
+      <c r="E151" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="F151" s="41" t="s">
+      <c r="F151" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G151" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H151" s="42">
+      <c r="G151" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H151" s="14">
         <v>46058</v>
       </c>
-      <c r="I151" s="42">
+      <c r="I151" s="14">
         <v>46078</v>
       </c>
       <c r="J151" s="24">
         <f t="shared" si="12"/>
         <v>15</v>
       </c>
-      <c r="K151" s="41" t="s">
+      <c r="K151" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L151" s="41" t="s">
+      <c r="L151" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M151" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N151" s="41" t="s">
+      <c r="M151" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N151" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="O151" s="46">
+      <c r="O151" s="42">
         <v>485500</v>
       </c>
-      <c r="P151" s="46">
+      <c r="P151" s="42">
         <v>251105</v>
       </c>
-      <c r="Q151" s="44">
+      <c r="Q151" s="42">
         <f t="shared" si="14"/>
         <v>736605</v>
       </c>
-      <c r="R151" s="42">
+      <c r="R151" s="14">
         <v>46085</v>
       </c>
       <c r="S151" s="24">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
-      <c r="T151" s="41" t="s">
+      <c r="T151" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="U151" s="48" t="s">
+      <c r="U151" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -12781,67 +12802,67 @@
       <c r="A152" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="B152" s="41" t="s">
+      <c r="B152" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C152" s="41">
+      <c r="C152" s="12">
         <v>24190516</v>
       </c>
-      <c r="D152" s="41" t="s">
+      <c r="D152" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="E152" s="41" t="s">
+      <c r="E152" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="F152" s="41" t="s">
+      <c r="F152" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G152" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H152" s="42">
+      <c r="G152" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H152" s="14">
         <v>45261</v>
       </c>
-      <c r="I152" s="42">
+      <c r="I152" s="14">
         <v>46079</v>
       </c>
       <c r="J152" s="24">
         <f t="shared" si="12"/>
         <v>585</v>
       </c>
-      <c r="K152" s="41" t="s">
+      <c r="K152" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="L152" s="41" t="s">
+      <c r="L152" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="M152" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N152" s="41" t="s">
+      <c r="M152" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N152" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="O152" s="46">
+      <c r="O152" s="42">
         <v>8018371</v>
       </c>
-      <c r="P152" s="46">
+      <c r="P152" s="42">
         <v>800000</v>
       </c>
-      <c r="Q152" s="44">
+      <c r="Q152" s="42">
         <f t="shared" si="14"/>
         <v>8818371</v>
       </c>
-      <c r="R152" s="42">
+      <c r="R152" s="14">
         <v>46085</v>
       </c>
       <c r="S152" s="24">
         <f t="shared" si="13"/>
         <v>589</v>
       </c>
-      <c r="T152" s="41" t="s">
+      <c r="T152" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="U152" s="48" t="s">
+      <c r="U152" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -12849,67 +12870,67 @@
       <c r="A153" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="B153" s="41" t="s">
+      <c r="B153" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="41">
+      <c r="C153" s="12">
         <v>58227435</v>
       </c>
-      <c r="D153" s="41" t="s">
+      <c r="D153" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E153" s="41" t="s">
+      <c r="E153" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="F153" s="41" t="s">
+      <c r="F153" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G153" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H153" s="42">
+      <c r="G153" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H153" s="14">
         <v>46069</v>
       </c>
-      <c r="I153" s="42">
+      <c r="I153" s="14">
         <v>46083</v>
       </c>
       <c r="J153" s="24">
         <f t="shared" si="12"/>
         <v>11</v>
       </c>
-      <c r="K153" s="41" t="s">
+      <c r="K153" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L153" s="41" t="s">
+      <c r="L153" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M153" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N153" s="41" t="s">
+      <c r="M153" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N153" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O153" s="46">
+      <c r="O153" s="42">
         <v>0</v>
       </c>
-      <c r="P153" s="46">
+      <c r="P153" s="42">
         <v>430500</v>
       </c>
-      <c r="Q153" s="44">
+      <c r="Q153" s="42">
         <f t="shared" si="14"/>
         <v>430500</v>
       </c>
-      <c r="R153" s="42">
+      <c r="R153" s="14">
         <v>46085</v>
       </c>
       <c r="S153" s="24">
         <f t="shared" si="13"/>
         <v>13</v>
       </c>
-      <c r="T153" s="41" t="s">
+      <c r="T153" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="U153" s="48" t="s">
+      <c r="U153" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -12917,67 +12938,67 @@
       <c r="A154" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B154" s="41" t="s">
+      <c r="B154" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C154" s="41">
+      <c r="C154" s="12">
         <v>54990268</v>
       </c>
-      <c r="D154" s="41" t="s">
+      <c r="D154" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="E154" s="41" t="s">
+      <c r="E154" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="F154" s="41" t="s">
+      <c r="F154" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G154" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H154" s="42">
+      <c r="G154" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H154" s="14">
         <v>46002</v>
       </c>
-      <c r="I154" s="42">
+      <c r="I154" s="14">
         <v>46084</v>
       </c>
       <c r="J154" s="24">
         <f t="shared" si="12"/>
         <v>59</v>
       </c>
-      <c r="K154" s="41" t="s">
+      <c r="K154" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L154" s="41" t="s">
+      <c r="L154" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="M154" s="41" t="s">
+      <c r="M154" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="N154" s="41" t="s">
+      <c r="N154" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O154" s="46">
+      <c r="O154" s="42">
         <v>0</v>
       </c>
-      <c r="P154" s="46">
+      <c r="P154" s="42">
         <v>0</v>
       </c>
-      <c r="Q154" s="44">
+      <c r="Q154" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="R154" s="42">
+      <c r="R154" s="14">
         <v>46085</v>
       </c>
       <c r="S154" s="24">
         <f t="shared" si="13"/>
         <v>60</v>
       </c>
-      <c r="T154" s="41" t="s">
+      <c r="T154" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="U154" s="48" t="s">
+      <c r="U154" s="11" t="s">
         <v>444</v>
       </c>
     </row>
@@ -12985,67 +13006,67 @@
       <c r="A155" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="B155" s="41" t="s">
+      <c r="B155" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C155" s="41">
+      <c r="C155" s="12">
         <v>57782724</v>
       </c>
-      <c r="D155" s="41" t="s">
+      <c r="D155" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E155" s="41">
+      <c r="E155" s="12">
         <v>2722229745</v>
       </c>
-      <c r="F155" s="41" t="s">
+      <c r="F155" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G155" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H155" s="42">
+      <c r="G155" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H155" s="14">
         <v>46057</v>
       </c>
-      <c r="I155" s="42">
+      <c r="I155" s="14">
         <v>46073</v>
       </c>
       <c r="J155" s="24">
         <f t="shared" si="12"/>
         <v>13</v>
       </c>
-      <c r="K155" s="41" t="s">
+      <c r="K155" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L155" s="41" t="s">
+      <c r="L155" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M155" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N155" s="41" t="s">
+      <c r="M155" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N155" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="O155" s="46">
+      <c r="O155" s="42">
         <v>150000</v>
       </c>
-      <c r="P155" s="46">
+      <c r="P155" s="42">
         <v>60000</v>
       </c>
-      <c r="Q155" s="44">
+      <c r="Q155" s="42">
         <f t="shared" si="14"/>
         <v>210000</v>
       </c>
-      <c r="R155" s="42">
+      <c r="R155" s="14">
         <v>46085</v>
       </c>
       <c r="S155" s="24">
         <f t="shared" si="13"/>
         <v>21</v>
       </c>
-      <c r="T155" s="41" t="s">
+      <c r="T155" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="U155" s="48" t="s">
+      <c r="U155" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -13053,203 +13074,203 @@
       <c r="A156" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="B156" s="41" t="s">
+      <c r="B156" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C156" s="41">
+      <c r="C156" s="12">
         <v>58585753</v>
       </c>
-      <c r="D156" s="41" t="s">
+      <c r="D156" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E156" s="41">
+      <c r="E156" s="12">
         <v>2722229950</v>
       </c>
-      <c r="F156" s="41" t="s">
+      <c r="F156" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G156" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H156" s="42">
+      <c r="G156" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H156" s="14">
         <v>46072</v>
       </c>
-      <c r="I156" s="42">
+      <c r="I156" s="14">
         <v>46084</v>
       </c>
       <c r="J156" s="24">
         <f t="shared" si="12"/>
         <v>9</v>
       </c>
-      <c r="K156" s="41" t="s">
+      <c r="K156" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L156" s="41" t="s">
+      <c r="L156" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M156" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N156" s="41" t="s">
+      <c r="M156" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N156" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="O156" s="46">
+      <c r="O156" s="42">
         <v>150000</v>
       </c>
-      <c r="P156" s="46">
+      <c r="P156" s="42">
         <v>60000</v>
       </c>
-      <c r="Q156" s="44">
+      <c r="Q156" s="42">
         <f t="shared" si="14"/>
         <v>210000</v>
       </c>
-      <c r="R156" s="42">
+      <c r="R156" s="14">
         <v>46085</v>
       </c>
       <c r="S156" s="24">
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
-      <c r="T156" s="41" t="s">
+      <c r="T156" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="U156" s="48" t="s">
+      <c r="U156" s="11" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A157" s="41" t="s">
+      <c r="A157" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B157" s="41" t="s">
+      <c r="B157" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C157" s="41">
+      <c r="C157" s="12">
         <v>55490966</v>
       </c>
-      <c r="D157" s="41" t="s">
+      <c r="D157" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E157" s="41" t="s">
+      <c r="E157" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="F157" s="41" t="s">
+      <c r="F157" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G157" s="41" t="s">
+      <c r="G157" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H157" s="42">
+      <c r="H157" s="14">
         <v>46010</v>
       </c>
-      <c r="I157" s="42">
+      <c r="I157" s="14">
         <v>46084</v>
       </c>
       <c r="J157" s="24">
         <f t="shared" si="12"/>
         <v>53</v>
       </c>
-      <c r="K157" s="47" t="s">
+      <c r="K157" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L157" s="48" t="s">
+      <c r="L157" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="M157" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="N157" s="41" t="s">
+      <c r="M157" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N157" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="O157" s="49">
+      <c r="O157" s="19">
         <v>0</v>
       </c>
-      <c r="P157" s="49">
+      <c r="P157" s="19">
         <v>0</v>
       </c>
-      <c r="Q157" s="44">
+      <c r="Q157" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="R157" s="50">
+      <c r="R157" s="13">
         <v>46086</v>
       </c>
       <c r="S157" s="24">
         <f t="shared" si="13"/>
         <v>55</v>
       </c>
-      <c r="T157" s="41" t="s">
+      <c r="T157" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="U157" s="48" t="s">
+      <c r="U157" s="11" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A158" s="41" t="s">
+      <c r="A158" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="B158" s="41" t="s">
+      <c r="B158" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C158" s="41">
+      <c r="C158" s="12">
         <v>58853643</v>
       </c>
-      <c r="D158" s="41" t="s">
+      <c r="D158" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="E158" s="41" t="s">
+      <c r="E158" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="F158" s="41" t="s">
+      <c r="F158" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G158" s="41" t="s">
+      <c r="G158" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H158" s="51">
+      <c r="H158" s="36">
         <v>46079</v>
       </c>
-      <c r="I158" s="51">
+      <c r="I158" s="36">
         <v>46085</v>
       </c>
       <c r="J158" s="24">
         <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="K158" s="47" t="s">
+      <c r="K158" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L158" s="48" t="s">
+      <c r="L158" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="M158" s="48" t="s">
+      <c r="M158" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="N158" s="41" t="s">
+      <c r="N158" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O158" s="49">
+      <c r="O158" s="19">
         <v>0</v>
       </c>
-      <c r="P158" s="49">
+      <c r="P158" s="19">
         <v>0</v>
       </c>
-      <c r="Q158" s="44">
+      <c r="Q158" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="R158" s="50">
+      <c r="R158" s="13">
         <v>46086</v>
       </c>
       <c r="S158" s="24">
         <f t="shared" si="13"/>
         <v>6</v>
       </c>
-      <c r="T158" s="41" t="s">
+      <c r="T158" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="U158" s="48" t="s">
+      <c r="U158" s="11" t="s">
         <v>444</v>
       </c>
     </row>
@@ -13260,13 +13281,13 @@
       <c r="B159" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C159" s="52">
+      <c r="C159" s="65">
         <v>54479742</v>
       </c>
       <c r="D159" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="E159" s="52" t="s">
+      <c r="E159" s="65" t="s">
         <v>366</v>
       </c>
       <c r="F159" s="11" t="s">
@@ -13275,23 +13296,23 @@
       <c r="G159" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H159" s="53">
+      <c r="H159" s="66">
         <v>45993</v>
       </c>
-      <c r="I159" s="53">
+      <c r="I159" s="66">
         <v>46084</v>
       </c>
       <c r="J159" s="24">
         <f t="shared" si="12"/>
         <v>66</v>
       </c>
-      <c r="K159" s="47" t="s">
+      <c r="K159" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L159" s="48" t="s">
+      <c r="L159" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="M159" s="48" t="s">
+      <c r="M159" s="11" t="s">
         <v>48</v>
       </c>
       <c r="N159" s="11" t="s">
@@ -13303,21 +13324,21 @@
       <c r="P159" s="5">
         <v>0</v>
       </c>
-      <c r="Q159" s="44">
+      <c r="Q159" s="42">
         <f t="shared" si="14"/>
         <v>6064001</v>
       </c>
-      <c r="R159" s="50">
+      <c r="R159" s="13">
         <v>46086</v>
       </c>
       <c r="S159" s="24">
         <f t="shared" si="13"/>
         <v>68</v>
       </c>
-      <c r="T159" s="41" t="s">
+      <c r="T159" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="U159" s="48" t="s">
+      <c r="U159" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -13325,67 +13346,67 @@
       <c r="A160" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="B160" s="41" t="s">
+      <c r="B160" s="12" t="s">
         <v>87</v>
       </c>
       <c r="C160" s="5">
         <v>58932414</v>
       </c>
-      <c r="D160" s="41" t="s">
+      <c r="D160" s="12" t="s">
         <v>368</v>
       </c>
       <c r="E160" s="5">
         <v>2722229955</v>
       </c>
-      <c r="F160" s="41" t="s">
+      <c r="F160" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G160" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H160" s="42">
+      <c r="G160" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H160" s="14">
         <v>46078</v>
       </c>
-      <c r="I160" s="42">
+      <c r="I160" s="14">
         <v>46086</v>
       </c>
       <c r="J160" s="24">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="K160" s="47" t="s">
+      <c r="K160" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L160" s="48" t="s">
+      <c r="L160" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="M160" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="N160" s="41" t="s">
+      <c r="M160" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N160" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="O160" s="49">
+      <c r="O160" s="19">
         <v>1000000</v>
       </c>
-      <c r="P160" s="49">
+      <c r="P160" s="19">
         <v>495000</v>
       </c>
-      <c r="Q160" s="44">
+      <c r="Q160" s="42">
         <f t="shared" si="14"/>
         <v>1495000</v>
       </c>
-      <c r="R160" s="50">
+      <c r="R160" s="13">
         <v>46086</v>
       </c>
       <c r="S160" s="24">
         <f t="shared" si="13"/>
         <v>7</v>
       </c>
-      <c r="T160" s="41" t="s">
+      <c r="T160" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="U160" s="48" t="s">
+      <c r="U160" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -13439,7 +13460,7 @@
       <c r="P161" s="19">
         <v>187644</v>
       </c>
-      <c r="Q161" s="44">
+      <c r="Q161" s="42">
         <f t="shared" si="14"/>
         <v>687644</v>
       </c>
@@ -13453,7 +13474,7 @@
       <c r="T161" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="U161" s="48" t="s">
+      <c r="U161" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -13507,7 +13528,7 @@
       <c r="P162" s="19">
         <v>667054</v>
       </c>
-      <c r="Q162" s="44">
+      <c r="Q162" s="42">
         <f t="shared" si="14"/>
         <v>3288468</v>
       </c>
@@ -13521,7 +13542,7 @@
       <c r="T162" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="U162" s="48" t="s">
+      <c r="U162" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -13575,7 +13596,7 @@
       <c r="P163" s="19">
         <v>380000</v>
       </c>
-      <c r="Q163" s="44">
+      <c r="Q163" s="42">
         <f t="shared" si="14"/>
         <v>2380000</v>
       </c>
@@ -13589,7 +13610,7 @@
       <c r="T163" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="U163" s="48" t="s">
+      <c r="U163" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -13643,7 +13664,7 @@
       <c r="P164" s="19">
         <v>1700000</v>
       </c>
-      <c r="Q164" s="44">
+      <c r="Q164" s="42">
         <f t="shared" si="14"/>
         <v>2700000</v>
       </c>
@@ -13657,7 +13678,7 @@
       <c r="T164" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U164" s="41" t="s">
+      <c r="U164" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -13711,7 +13732,7 @@
       <c r="P165" s="19">
         <v>1700000</v>
       </c>
-      <c r="Q165" s="44">
+      <c r="Q165" s="42">
         <f t="shared" si="14"/>
         <v>2700000</v>
       </c>
@@ -13725,7 +13746,7 @@
       <c r="T165" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U165" s="41" t="s">
+      <c r="U165" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -13779,7 +13800,7 @@
       <c r="P166" s="19">
         <v>1700000</v>
       </c>
-      <c r="Q166" s="44">
+      <c r="Q166" s="42">
         <f t="shared" si="14"/>
         <v>1950000</v>
       </c>
@@ -13793,7 +13814,7 @@
       <c r="T166" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U166" s="41" t="s">
+      <c r="U166" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -13847,7 +13868,7 @@
       <c r="P167" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q167" s="44">
+      <c r="Q167" s="42">
         <f t="shared" si="14"/>
         <v>1800000</v>
       </c>
@@ -13861,7 +13882,7 @@
       <c r="T167" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U167" s="41" t="s">
+      <c r="U167" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -13915,7 +13936,7 @@
       <c r="P168" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q168" s="44">
+      <c r="Q168" s="42">
         <f t="shared" si="14"/>
         <v>1800000</v>
       </c>
@@ -13929,7 +13950,7 @@
       <c r="T168" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U168" s="41" t="s">
+      <c r="U168" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -13983,7 +14004,7 @@
       <c r="P169" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q169" s="44">
+      <c r="Q169" s="42">
         <f t="shared" si="14"/>
         <v>1550000</v>
       </c>
@@ -13997,7 +14018,7 @@
       <c r="T169" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U169" s="41" t="s">
+      <c r="U169" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -14051,7 +14072,7 @@
       <c r="P170" s="12">
         <v>1300000</v>
       </c>
-      <c r="Q170" s="44">
+      <c r="Q170" s="42">
         <f t="shared" si="14"/>
         <v>1800000</v>
       </c>
@@ -14065,7 +14086,7 @@
       <c r="T170" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U170" s="41" t="s">
+      <c r="U170" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -14119,7 +14140,7 @@
       <c r="P171" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q171" s="44">
+      <c r="Q171" s="42">
         <f t="shared" si="14"/>
         <v>1800000</v>
       </c>
@@ -14133,7 +14154,7 @@
       <c r="T171" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U171" s="41" t="s">
+      <c r="U171" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -14144,7 +14165,7 @@
       <c r="B172" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C172" s="54">
+      <c r="C172" s="44">
         <v>55105863</v>
       </c>
       <c r="D172" s="12" t="s">
@@ -14187,7 +14208,7 @@
       <c r="P172" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q172" s="44">
+      <c r="Q172" s="42">
         <f t="shared" si="14"/>
         <v>2550000</v>
       </c>
@@ -14201,7 +14222,7 @@
       <c r="T172" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U172" s="41" t="s">
+      <c r="U172" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -14255,7 +14276,7 @@
       <c r="P173" s="19">
         <v>1700000</v>
       </c>
-      <c r="Q173" s="44">
+      <c r="Q173" s="42">
         <f t="shared" si="14"/>
         <v>2700000</v>
       </c>
@@ -14269,7 +14290,7 @@
       <c r="T173" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U173" s="41" t="s">
+      <c r="U173" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -14323,7 +14344,7 @@
       <c r="P174" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q174" s="44">
+      <c r="Q174" s="42">
         <f t="shared" si="14"/>
         <v>1550000</v>
       </c>
@@ -14337,7 +14358,7 @@
       <c r="T174" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U174" s="41" t="s">
+      <c r="U174" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -14391,7 +14412,7 @@
       <c r="P175" s="19">
         <v>1700000</v>
       </c>
-      <c r="Q175" s="44">
+      <c r="Q175" s="42">
         <f t="shared" si="14"/>
         <v>2200000</v>
       </c>
@@ -14405,7 +14426,7 @@
       <c r="T175" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U175" s="41" t="s">
+      <c r="U175" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -14459,7 +14480,7 @@
       <c r="P176" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q176" s="44">
+      <c r="Q176" s="42">
         <f t="shared" si="14"/>
         <v>2300000</v>
       </c>
@@ -14473,7 +14494,7 @@
       <c r="T176" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U176" s="41" t="s">
+      <c r="U176" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -14527,7 +14548,7 @@
       <c r="P177" s="19">
         <v>1700000</v>
       </c>
-      <c r="Q177" s="44">
+      <c r="Q177" s="42">
         <f t="shared" si="14"/>
         <v>2200000</v>
       </c>
@@ -14541,7 +14562,7 @@
       <c r="T177" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U177" s="41" t="s">
+      <c r="U177" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -14595,7 +14616,7 @@
       <c r="P178" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q178" s="44">
+      <c r="Q178" s="42">
         <f t="shared" si="14"/>
         <v>2800000</v>
       </c>
@@ -14609,7 +14630,7 @@
       <c r="T178" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U178" s="41" t="s">
+      <c r="U178" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -14663,7 +14684,7 @@
       <c r="P179" s="19">
         <v>1300000</v>
       </c>
-      <c r="Q179" s="44">
+      <c r="Q179" s="42">
         <f t="shared" si="14"/>
         <v>2550000</v>
       </c>
@@ -14677,7 +14698,7 @@
       <c r="T179" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U179" s="41" t="s">
+      <c r="U179" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -14731,7 +14752,7 @@
       <c r="P180" s="19">
         <v>2207940</v>
       </c>
-      <c r="Q180" s="44">
+      <c r="Q180" s="42">
         <f t="shared" si="14"/>
         <v>3596622</v>
       </c>
@@ -14745,7 +14766,7 @@
       <c r="T180" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U180" s="41" t="s">
+      <c r="U180" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -14799,7 +14820,7 @@
       <c r="P181" s="19">
         <v>0</v>
       </c>
-      <c r="Q181" s="44">
+      <c r="Q181" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -14813,7 +14834,7 @@
       <c r="T181" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U181" s="41" t="s">
+      <c r="U181" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -14867,7 +14888,7 @@
       <c r="P182" s="19">
         <v>590836</v>
       </c>
-      <c r="Q182" s="44">
+      <c r="Q182" s="42">
         <f t="shared" si="14"/>
         <v>1590836</v>
       </c>
@@ -14881,7 +14902,7 @@
       <c r="T182" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U182" s="41" t="s">
+      <c r="U182" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -14935,7 +14956,7 @@
       <c r="P183" s="19">
         <v>0</v>
       </c>
-      <c r="Q183" s="44">
+      <c r="Q183" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -14949,7 +14970,7 @@
       <c r="T183" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U183" s="41" t="s">
+      <c r="U183" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15003,7 +15024,7 @@
       <c r="P184" s="19">
         <v>0</v>
       </c>
-      <c r="Q184" s="44">
+      <c r="Q184" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -15017,7 +15038,7 @@
       <c r="T184" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U184" s="41" t="s">
+      <c r="U184" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15065,13 +15086,13 @@
       <c r="N185" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O185" s="56">
+      <c r="O185" s="46">
         <v>150000</v>
       </c>
-      <c r="P185" s="56">
+      <c r="P185" s="46">
         <v>60000</v>
       </c>
-      <c r="Q185" s="44">
+      <c r="Q185" s="42">
         <f t="shared" si="14"/>
         <v>210000</v>
       </c>
@@ -15085,7 +15106,7 @@
       <c r="T185" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U185" s="41" t="s">
+      <c r="U185" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15133,13 +15154,13 @@
       <c r="N186" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O186" s="56">
+      <c r="O186" s="46">
         <v>150000</v>
       </c>
-      <c r="P186" s="56">
+      <c r="P186" s="46">
         <v>60000</v>
       </c>
-      <c r="Q186" s="44">
+      <c r="Q186" s="42">
         <f t="shared" si="14"/>
         <v>210000</v>
       </c>
@@ -15153,7 +15174,7 @@
       <c r="T186" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U186" s="41" t="s">
+      <c r="U186" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15207,7 +15228,7 @@
       <c r="P187" s="19">
         <v>0</v>
       </c>
-      <c r="Q187" s="44">
+      <c r="Q187" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -15221,7 +15242,7 @@
       <c r="T187" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U187" s="41" t="s">
+      <c r="U187" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15275,7 +15296,7 @@
       <c r="P188" s="19">
         <v>0</v>
       </c>
-      <c r="Q188" s="44">
+      <c r="Q188" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -15289,7 +15310,7 @@
       <c r="T188" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U188" s="41" t="s">
+      <c r="U188" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15325,7 +15346,7 @@
         <f t="shared" si="12"/>
         <v>49</v>
       </c>
-      <c r="K189" s="55" t="s">
+      <c r="K189" s="45" t="s">
         <v>303</v>
       </c>
       <c r="L189" s="34" t="s">
@@ -15337,13 +15358,13 @@
       <c r="N189" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="O189" s="57">
+      <c r="O189" s="47">
         <v>0</v>
       </c>
-      <c r="P189" s="57">
+      <c r="P189" s="47">
         <v>0</v>
       </c>
-      <c r="Q189" s="44">
+      <c r="Q189" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -15357,7 +15378,7 @@
       <c r="T189" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U189" s="41" t="s">
+      <c r="U189" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15365,53 +15386,53 @@
       <c r="A190" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="B190" s="41" t="s">
+      <c r="B190" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C190" s="41">
+      <c r="C190" s="12">
         <v>50732535</v>
       </c>
-      <c r="D190" s="41" t="s">
+      <c r="D190" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E190" s="41" t="s">
+      <c r="E190" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="F190" s="41" t="s">
+      <c r="F190" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G190" s="41" t="s">
+      <c r="G190" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H190" s="42">
+      <c r="H190" s="14">
         <v>45919</v>
       </c>
-      <c r="I190" s="42">
+      <c r="I190" s="14">
         <v>46056</v>
       </c>
       <c r="J190" s="24">
         <f t="shared" si="12"/>
         <v>98</v>
       </c>
-      <c r="K190" s="41" t="s">
+      <c r="K190" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L190" s="41" t="s">
+      <c r="L190" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="M190" s="41" t="s">
+      <c r="M190" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="N190" s="41" t="s">
+      <c r="N190" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O190" s="41">
+      <c r="O190" s="12">
         <v>0</v>
       </c>
-      <c r="P190" s="41">
+      <c r="P190" s="12">
         <v>0</v>
       </c>
-      <c r="Q190" s="49">
+      <c r="Q190" s="19">
         <v>0</v>
       </c>
       <c r="R190" s="14">
@@ -15424,7 +15445,7 @@
       <c r="T190" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U190" s="41" t="s">
+      <c r="U190" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15432,53 +15453,53 @@
       <c r="A191" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="B191" s="41" t="s">
+      <c r="B191" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C191" s="41">
+      <c r="C191" s="12">
         <v>58205267</v>
       </c>
-      <c r="D191" s="41" t="s">
+      <c r="D191" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="E191" s="41" t="s">
+      <c r="E191" s="12" t="s">
         <v>434</v>
       </c>
-      <c r="F191" s="41" t="s">
+      <c r="F191" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G191" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H191" s="42">
+      <c r="G191" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H191" s="14">
         <v>46067</v>
       </c>
-      <c r="I191" s="42">
+      <c r="I191" s="14">
         <v>46087</v>
       </c>
       <c r="J191" s="24">
         <f t="shared" si="12"/>
         <v>15</v>
       </c>
-      <c r="K191" s="41" t="s">
+      <c r="K191" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L191" s="41" t="s">
+      <c r="L191" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M191" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N191" s="41" t="s">
+      <c r="M191" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N191" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O191" s="41">
+      <c r="O191" s="12">
         <v>0</v>
       </c>
-      <c r="P191" s="41">
+      <c r="P191" s="12">
         <v>430500</v>
       </c>
-      <c r="Q191" s="49">
+      <c r="Q191" s="19">
         <v>430500</v>
       </c>
       <c r="R191" s="14">
@@ -15491,7 +15512,7 @@
       <c r="T191" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U191" s="41" t="s">
+      <c r="U191" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15499,53 +15520,53 @@
       <c r="A192" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="B192" s="41" t="s">
+      <c r="B192" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C192" s="41">
+      <c r="C192" s="12">
         <v>58173859</v>
       </c>
-      <c r="D192" s="41" t="s">
+      <c r="D192" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="E192" s="41" t="s">
+      <c r="E192" s="12" t="s">
         <v>436</v>
       </c>
-      <c r="F192" s="41" t="s">
+      <c r="F192" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G192" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H192" s="42">
+      <c r="G192" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H192" s="14">
         <v>46066</v>
       </c>
-      <c r="I192" s="42">
+      <c r="I192" s="14">
         <v>46087</v>
       </c>
       <c r="J192" s="24">
         <f t="shared" si="12"/>
         <v>16</v>
       </c>
-      <c r="K192" s="41" t="s">
+      <c r="K192" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L192" s="41" t="s">
+      <c r="L192" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M192" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N192" s="41" t="s">
+      <c r="M192" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N192" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O192" s="41">
+      <c r="O192" s="12">
         <v>0</v>
       </c>
-      <c r="P192" s="41">
+      <c r="P192" s="12">
         <v>430500</v>
       </c>
-      <c r="Q192" s="49">
+      <c r="Q192" s="19">
         <v>430500</v>
       </c>
       <c r="R192" s="14">
@@ -15558,7 +15579,7 @@
       <c r="T192" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U192" s="41" t="s">
+      <c r="U192" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15566,53 +15587,53 @@
       <c r="A193" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="B193" s="41" t="s">
+      <c r="B193" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C193" s="41">
+      <c r="C193" s="12">
         <v>58650763</v>
       </c>
-      <c r="D193" s="41" t="s">
+      <c r="D193" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E193" s="41">
+      <c r="E193" s="12">
         <v>2722417296</v>
       </c>
-      <c r="F193" s="41" t="s">
+      <c r="F193" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G193" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H193" s="42">
+      <c r="G193" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H193" s="14">
         <v>46073</v>
       </c>
-      <c r="I193" s="42">
+      <c r="I193" s="14">
         <v>46092</v>
       </c>
       <c r="J193" s="24">
         <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="K193" s="41" t="s">
+      <c r="K193" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L193" s="41" t="s">
+      <c r="L193" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M193" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N193" s="41" t="s">
+      <c r="M193" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N193" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="O193" s="41">
+      <c r="O193" s="12">
         <v>150000</v>
       </c>
-      <c r="P193" s="41">
+      <c r="P193" s="12">
         <v>40000</v>
       </c>
-      <c r="Q193" s="49">
+      <c r="Q193" s="19">
         <v>190000</v>
       </c>
       <c r="R193" s="14">
@@ -15625,7 +15646,7 @@
       <c r="T193" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U193" s="41" t="s">
+      <c r="U193" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15633,53 +15654,53 @@
       <c r="A194" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="B194" s="41" t="s">
+      <c r="B194" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C194" s="41">
+      <c r="C194" s="12">
         <v>58276534</v>
       </c>
-      <c r="D194" s="41" t="s">
+      <c r="D194" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E194" s="41">
+      <c r="E194" s="12">
         <v>2723489370</v>
       </c>
-      <c r="F194" s="41" t="s">
+      <c r="F194" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G194" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H194" s="42">
+      <c r="G194" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H194" s="14">
         <v>46066</v>
       </c>
-      <c r="I194" s="42">
+      <c r="I194" s="14">
         <v>46092</v>
       </c>
       <c r="J194" s="24">
         <f t="shared" si="12"/>
         <v>19</v>
       </c>
-      <c r="K194" s="41" t="s">
+      <c r="K194" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L194" s="41" t="s">
+      <c r="L194" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M194" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N194" s="41" t="s">
+      <c r="M194" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N194" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="O194" s="41">
+      <c r="O194" s="12">
         <v>150000</v>
       </c>
-      <c r="P194" s="41">
+      <c r="P194" s="12">
         <v>40000</v>
       </c>
-      <c r="Q194" s="49">
+      <c r="Q194" s="19">
         <v>190000</v>
       </c>
       <c r="R194" s="14">
@@ -15692,7 +15713,7 @@
       <c r="T194" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U194" s="41" t="s">
+      <c r="U194" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15700,53 +15721,53 @@
       <c r="A195" s="12" t="s">
         <v>439</v>
       </c>
-      <c r="B195" s="41" t="s">
+      <c r="B195" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C195" s="41">
+      <c r="C195" s="12">
         <v>58853633</v>
       </c>
-      <c r="D195" s="41" t="s">
+      <c r="D195" s="12" t="s">
         <v>440</v>
       </c>
-      <c r="E195" s="41" t="s">
+      <c r="E195" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="F195" s="41" t="s">
+      <c r="F195" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G195" s="41" t="s">
+      <c r="G195" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H195" s="42">
+      <c r="H195" s="14">
         <v>46079</v>
       </c>
-      <c r="I195" s="42">
+      <c r="I195" s="14">
         <v>46092</v>
       </c>
       <c r="J195" s="24">
         <f t="shared" si="12"/>
         <v>10</v>
       </c>
-      <c r="K195" s="41" t="s">
+      <c r="K195" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L195" s="41" t="s">
+      <c r="L195" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M195" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N195" s="41" t="s">
+      <c r="M195" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N195" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="O195" s="41">
+      <c r="O195" s="12">
         <v>0</v>
       </c>
-      <c r="P195" s="41">
+      <c r="P195" s="12">
         <v>0</v>
       </c>
-      <c r="Q195" s="49">
+      <c r="Q195" s="19">
         <v>0</v>
       </c>
       <c r="R195" s="14">
@@ -15759,7 +15780,7 @@
       <c r="T195" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="U195" s="41" t="s">
+      <c r="U195" s="12" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15795,38 +15816,38 @@
         <f t="shared" si="12"/>
         <v>63</v>
       </c>
-      <c r="K196" s="41" t="s">
+      <c r="K196" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L196" s="41" t="s">
+      <c r="L196" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="M196" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N196" s="41" t="s">
+      <c r="M196" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N196" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O196" s="41">
+      <c r="O196" s="12">
         <v>2932569</v>
       </c>
-      <c r="P196" s="41">
+      <c r="P196" s="12">
         <v>709840</v>
       </c>
-      <c r="Q196" s="49">
+      <c r="Q196" s="19">
         <v>3642409</v>
       </c>
-      <c r="R196" s="42">
+      <c r="R196" s="14">
         <v>46093</v>
       </c>
       <c r="S196" s="24">
         <f t="shared" si="13"/>
         <v>73</v>
       </c>
-      <c r="T196" s="41" t="s">
+      <c r="T196" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="U196" s="48" t="s">
+      <c r="U196" s="11" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15862,38 +15883,38 @@
         <f t="shared" si="12"/>
         <v>19</v>
       </c>
-      <c r="K197" s="41" t="s">
+      <c r="K197" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L197" s="41" t="s">
+      <c r="L197" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M197" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N197" s="41" t="s">
+      <c r="M197" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N197" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O197" s="41">
+      <c r="O197" s="12">
         <v>0</v>
       </c>
-      <c r="P197" s="41">
+      <c r="P197" s="12">
         <v>430500</v>
       </c>
-      <c r="Q197" s="49">
+      <c r="Q197" s="19">
         <v>430500</v>
       </c>
-      <c r="R197" s="42">
+      <c r="R197" s="14">
         <v>46093</v>
       </c>
       <c r="S197" s="24">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
-      <c r="T197" s="41" t="s">
+      <c r="T197" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="U197" s="48" t="s">
+      <c r="U197" s="11" t="s">
         <v>444</v>
       </c>
     </row>
@@ -15929,38 +15950,38 @@
         <f t="shared" si="12"/>
         <v>42</v>
       </c>
-      <c r="K198" s="41" t="s">
+      <c r="K198" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L198" s="41" t="s">
+      <c r="L198" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M198" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N198" s="41" t="s">
+      <c r="M198" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N198" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="O198" s="41">
+      <c r="O198" s="12">
         <v>2000000</v>
       </c>
-      <c r="P198" s="41">
+      <c r="P198" s="12">
         <v>300000</v>
       </c>
-      <c r="Q198" s="49">
+      <c r="Q198" s="19">
         <v>2300000</v>
       </c>
-      <c r="R198" s="42">
+      <c r="R198" s="14">
         <v>46093</v>
       </c>
       <c r="S198" s="24">
         <f t="shared" si="13"/>
         <v>43</v>
       </c>
-      <c r="T198" s="41" t="s">
+      <c r="T198" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="U198" s="48" t="s">
+      <c r="U198" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -15996,38 +16017,38 @@
         <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="K199" s="41" t="s">
+      <c r="K199" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L199" s="41" t="s">
+      <c r="L199" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M199" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N199" s="41" t="s">
+      <c r="M199" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N199" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O199" s="41">
+      <c r="O199" s="12">
         <v>0</v>
       </c>
-      <c r="P199" s="41">
+      <c r="P199" s="12">
         <v>0</v>
       </c>
-      <c r="Q199" s="49">
+      <c r="Q199" s="19">
         <v>0</v>
       </c>
-      <c r="R199" s="42">
+      <c r="R199" s="14">
         <v>46093</v>
       </c>
       <c r="S199" s="24">
         <f t="shared" si="13"/>
         <v>96</v>
       </c>
-      <c r="T199" s="41" t="s">
+      <c r="T199" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="U199" s="48" t="s">
+      <c r="U199" s="11" t="s">
         <v>444</v>
       </c>
     </row>
@@ -16063,38 +16084,38 @@
         <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="K200" s="41" t="s">
+      <c r="K200" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L200" s="41" t="s">
+      <c r="L200" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M200" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N200" s="41" t="s">
+      <c r="M200" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N200" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O200" s="41">
+      <c r="O200" s="12">
         <v>0</v>
       </c>
-      <c r="P200" s="41">
+      <c r="P200" s="12">
         <v>0</v>
       </c>
-      <c r="Q200" s="49">
+      <c r="Q200" s="19">
         <v>0</v>
       </c>
-      <c r="R200" s="42">
+      <c r="R200" s="14">
         <v>46093</v>
       </c>
       <c r="S200" s="24">
         <f t="shared" si="13"/>
         <v>96</v>
       </c>
-      <c r="T200" s="41" t="s">
+      <c r="T200" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="U200" s="48" t="s">
+      <c r="U200" s="11" t="s">
         <v>444</v>
       </c>
     </row>
@@ -16130,35 +16151,35 @@
         <f t="shared" si="12"/>
         <v>40</v>
       </c>
-      <c r="K201" s="41" t="s">
+      <c r="K201" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L201" s="41" t="s">
+      <c r="L201" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M201" s="41" t="s">
+      <c r="M201" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="N201" s="41" t="s">
+      <c r="N201" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="O201" s="41">
+      <c r="O201" s="12">
         <v>2000000</v>
       </c>
-      <c r="P201" s="41">
+      <c r="P201" s="12">
         <v>0</v>
       </c>
-      <c r="Q201" s="49">
+      <c r="Q201" s="19">
         <v>2000000</v>
       </c>
-      <c r="R201" s="42">
+      <c r="R201" s="14">
         <v>46092</v>
       </c>
       <c r="S201" s="24">
         <f t="shared" si="13"/>
         <v>42</v>
       </c>
-      <c r="T201" s="41" t="s">
+      <c r="T201" s="12" t="s">
         <v>377</v>
       </c>
       <c r="U201" s="11" t="s">
@@ -16197,38 +16218,38 @@
         <f t="shared" si="12"/>
         <v>55</v>
       </c>
-      <c r="K202" s="41" t="s">
+      <c r="K202" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L202" s="41" t="s">
+      <c r="L202" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="M202" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N202" s="41" t="s">
+      <c r="M202" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N202" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O202" s="41">
+      <c r="O202" s="12">
         <v>0</v>
       </c>
-      <c r="P202" s="41">
+      <c r="P202" s="12">
         <v>0</v>
       </c>
-      <c r="Q202" s="49">
+      <c r="Q202" s="19">
         <v>0</v>
       </c>
-      <c r="R202" s="42">
+      <c r="R202" s="14">
         <v>46093</v>
       </c>
       <c r="S202" s="24">
         <f t="shared" si="13"/>
         <v>96</v>
       </c>
-      <c r="T202" s="41" t="s">
+      <c r="T202" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="U202" s="48" t="s">
+      <c r="U202" s="11" t="s">
         <v>444</v>
       </c>
     </row>
@@ -16264,38 +16285,38 @@
         <f t="shared" si="12"/>
         <v>22</v>
       </c>
-      <c r="K203" s="41" t="s">
+      <c r="K203" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L203" s="41" t="s">
+      <c r="L203" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M203" s="41" t="s">
+      <c r="M203" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="N203" s="41" t="s">
+      <c r="N203" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O203" s="41">
+      <c r="O203" s="12">
         <v>200000</v>
       </c>
-      <c r="P203" s="41">
+      <c r="P203" s="12">
         <v>0</v>
       </c>
-      <c r="Q203" s="49">
+      <c r="Q203" s="19">
         <v>200000</v>
       </c>
-      <c r="R203" s="42">
+      <c r="R203" s="14">
         <v>46094</v>
       </c>
       <c r="S203" s="24">
         <f t="shared" si="13"/>
         <v>23</v>
       </c>
-      <c r="T203" s="41" t="s">
+      <c r="T203" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="U203" s="48" t="s">
+      <c r="U203" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -16331,38 +16352,38 @@
         <f t="shared" si="12"/>
         <v>25</v>
       </c>
-      <c r="K204" s="41" t="s">
+      <c r="K204" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L204" s="41" t="s">
+      <c r="L204" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M204" s="41" t="s">
+      <c r="M204" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="N204" s="41" t="s">
+      <c r="N204" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="O204" s="41">
+      <c r="O204" s="12">
         <v>144000</v>
       </c>
-      <c r="P204" s="41">
+      <c r="P204" s="12">
         <v>0</v>
       </c>
-      <c r="Q204" s="49">
+      <c r="Q204" s="19">
         <v>144000</v>
       </c>
-      <c r="R204" s="42">
+      <c r="R204" s="14">
         <v>46094</v>
       </c>
       <c r="S204" s="24">
         <f t="shared" si="13"/>
         <v>25</v>
       </c>
-      <c r="T204" s="41" t="s">
+      <c r="T204" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="U204" s="48" t="s">
+      <c r="U204" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -16395,41 +16416,41 @@
         <v>46094</v>
       </c>
       <c r="J205" s="24">
-        <f t="shared" ref="J205:J243" si="15">+NETWORKDAYS(H205,I205)</f>
+        <f t="shared" ref="J205:J259" si="15">+NETWORKDAYS(H205,I205)</f>
         <v>18</v>
       </c>
-      <c r="K205" s="41" t="s">
+      <c r="K205" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L205" s="41" t="s">
+      <c r="L205" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="M205" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N205" s="41" t="s">
+      <c r="M205" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N205" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="O205" s="41">
+      <c r="O205" s="12">
         <v>360000</v>
       </c>
-      <c r="P205" s="41">
+      <c r="P205" s="12">
         <v>92495</v>
       </c>
-      <c r="Q205" s="49">
+      <c r="Q205" s="19">
         <v>452495</v>
       </c>
-      <c r="R205" s="42">
+      <c r="R205" s="14">
         <v>46094</v>
       </c>
       <c r="S205" s="24">
-        <f t="shared" ref="S205:S243" si="16">NETWORKDAYS(H205,R205)</f>
+        <f t="shared" ref="S205:S259" si="16">NETWORKDAYS(H205,R205)</f>
         <v>18</v>
       </c>
-      <c r="T205" s="41" t="s">
+      <c r="T205" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="U205" s="48" t="s">
+      <c r="U205" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -16477,13 +16498,13 @@
       <c r="N206" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="O206" s="56">
+      <c r="O206" s="46">
         <v>0</v>
       </c>
-      <c r="P206" s="56">
+      <c r="P206" s="46">
         <v>0</v>
       </c>
-      <c r="Q206" s="56">
+      <c r="Q206" s="46">
         <f t="shared" ref="Q206:Q212" si="17">P206+O206</f>
         <v>0</v>
       </c>
@@ -16545,13 +16566,13 @@
       <c r="N207" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O207" s="56">
+      <c r="O207" s="46">
         <v>0</v>
       </c>
-      <c r="P207" s="56">
+      <c r="P207" s="46">
         <v>0</v>
       </c>
-      <c r="Q207" s="56">
+      <c r="Q207" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
@@ -16613,13 +16634,13 @@
       <c r="N208" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O208" s="56">
+      <c r="O208" s="46">
         <v>0</v>
       </c>
-      <c r="P208" s="56">
+      <c r="P208" s="46">
         <v>0</v>
       </c>
-      <c r="Q208" s="56">
+      <c r="Q208" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
@@ -16681,13 +16702,13 @@
       <c r="N209" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O209" s="56">
+      <c r="O209" s="46">
         <v>577056</v>
       </c>
-      <c r="P209" s="56">
+      <c r="P209" s="46">
         <v>0</v>
       </c>
-      <c r="Q209" s="56">
+      <c r="Q209" s="46">
         <f t="shared" si="17"/>
         <v>577056</v>
       </c>
@@ -16755,7 +16776,7 @@
       <c r="P210" s="19">
         <v>462000</v>
       </c>
-      <c r="Q210" s="56">
+      <c r="Q210" s="46">
         <f t="shared" si="17"/>
         <v>2462000</v>
       </c>
@@ -16823,7 +16844,7 @@
       <c r="P211" s="19">
         <v>350000</v>
       </c>
-      <c r="Q211" s="56">
+      <c r="Q211" s="46">
         <f t="shared" si="17"/>
         <v>1000000</v>
       </c>
@@ -16885,13 +16906,13 @@
       <c r="N212" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O212" s="56">
+      <c r="O212" s="46">
         <v>150000</v>
       </c>
-      <c r="P212" s="56">
+      <c r="P212" s="46">
         <v>60000</v>
       </c>
-      <c r="Q212" s="56">
+      <c r="Q212" s="46">
         <f t="shared" si="17"/>
         <v>210000</v>
       </c>
@@ -16959,7 +16980,7 @@
       <c r="P213" s="19">
         <v>593997</v>
       </c>
-      <c r="Q213" s="56">
+      <c r="Q213" s="46">
         <f>P213+O213</f>
         <v>1093997</v>
       </c>
@@ -17027,7 +17048,7 @@
       <c r="P214" s="19">
         <v>1034117</v>
       </c>
-      <c r="Q214" s="56">
+      <c r="Q214" s="46">
         <f>P214+O214</f>
         <v>1434117</v>
       </c>
@@ -17095,7 +17116,7 @@
       <c r="P215" s="19">
         <v>462000</v>
       </c>
-      <c r="Q215" s="56">
+      <c r="Q215" s="46">
         <f>P215+O215</f>
         <v>2462000</v>
       </c>
@@ -17163,7 +17184,7 @@
       <c r="P216" s="19">
         <v>400000</v>
       </c>
-      <c r="Q216" s="56">
+      <c r="Q216" s="46">
         <f>P216+O216</f>
         <v>8433717</v>
       </c>
@@ -17231,7 +17252,7 @@
       <c r="P217" s="19">
         <v>700000</v>
       </c>
-      <c r="Q217" s="56">
+      <c r="Q217" s="46">
         <f>P217+O217</f>
         <v>2200000</v>
       </c>
@@ -17249,7 +17270,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="218" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A218" s="5" t="s">
         <v>483</v>
       </c>
@@ -17293,13 +17314,13 @@
       <c r="N218" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O218" s="56">
+      <c r="O218" s="46">
         <v>150000</v>
       </c>
-      <c r="P218" s="56">
+      <c r="P218" s="46">
         <v>40000</v>
       </c>
-      <c r="Q218" s="56">
+      <c r="Q218" s="46">
         <f t="shared" ref="Q218:Q224" si="18">P218+O218</f>
         <v>190000</v>
       </c>
@@ -17317,7 +17338,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="219" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A219" s="5" t="s">
         <v>484</v>
       </c>
@@ -17361,13 +17382,13 @@
       <c r="N219" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O219" s="56">
+      <c r="O219" s="46">
         <v>150000</v>
       </c>
-      <c r="P219" s="56">
+      <c r="P219" s="46">
         <v>40000</v>
       </c>
-      <c r="Q219" s="56">
+      <c r="Q219" s="46">
         <f t="shared" si="18"/>
         <v>190000</v>
       </c>
@@ -17385,7 +17406,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="220" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A220" s="5" t="s">
         <v>271</v>
       </c>
@@ -17429,13 +17450,13 @@
       <c r="N220" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O220" s="56">
+      <c r="O220" s="46">
         <v>150000</v>
       </c>
-      <c r="P220" s="56">
+      <c r="P220" s="46">
         <v>40000</v>
       </c>
-      <c r="Q220" s="56">
+      <c r="Q220" s="46">
         <f t="shared" si="18"/>
         <v>190000</v>
       </c>
@@ -17453,7 +17474,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="221" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A221" s="12" t="s">
         <v>485</v>
       </c>
@@ -17503,7 +17524,7 @@
       <c r="P221" s="19">
         <v>275790</v>
       </c>
-      <c r="Q221" s="56">
+      <c r="Q221" s="46">
         <f t="shared" si="18"/>
         <v>2675790</v>
       </c>
@@ -17521,7 +17542,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="222" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A222" s="12" t="s">
         <v>172</v>
       </c>
@@ -17571,7 +17592,7 @@
       <c r="P222" s="19">
         <v>115000</v>
       </c>
-      <c r="Q222" s="56">
+      <c r="Q222" s="46">
         <f t="shared" si="18"/>
         <v>658324</v>
       </c>
@@ -17589,7 +17610,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="223" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A223" s="12" t="s">
         <v>489</v>
       </c>
@@ -17639,7 +17660,7 @@
       <c r="P223" s="19">
         <v>569818</v>
       </c>
-      <c r="Q223" s="56">
+      <c r="Q223" s="46">
         <f t="shared" si="18"/>
         <v>1369818</v>
       </c>
@@ -17657,7 +17678,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="224" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A224" s="12" t="s">
         <v>492</v>
       </c>
@@ -17701,13 +17722,13 @@
       <c r="N224" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="O224" s="56">
+      <c r="O224" s="46">
         <v>0</v>
       </c>
-      <c r="P224" s="56">
+      <c r="P224" s="46">
         <v>0</v>
       </c>
-      <c r="Q224" s="56">
+      <c r="Q224" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
@@ -17725,7 +17746,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="225" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A225" s="5" t="s">
         <v>495</v>
       </c>
@@ -17769,13 +17790,13 @@
       <c r="N225" s="11" t="s">
         <v>498</v>
       </c>
-      <c r="O225" s="56">
+      <c r="O225" s="46">
         <v>600000</v>
       </c>
-      <c r="P225" s="56">
+      <c r="P225" s="46">
         <v>60000</v>
       </c>
-      <c r="Q225" s="56">
+      <c r="Q225" s="46">
         <f t="shared" ref="Q225:Q232" si="19">P225+O225</f>
         <v>660000</v>
       </c>
@@ -17793,7 +17814,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="226" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A226" s="5" t="s">
         <v>499</v>
       </c>
@@ -17837,13 +17858,13 @@
       <c r="N226" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="O226" s="56">
+      <c r="O226" s="46">
         <v>0</v>
       </c>
-      <c r="P226" s="56">
+      <c r="P226" s="46">
         <v>0</v>
       </c>
-      <c r="Q226" s="56">
+      <c r="Q226" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
@@ -17861,7 +17882,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="227" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A227" s="5" t="s">
         <v>502</v>
       </c>
@@ -17905,13 +17926,13 @@
       <c r="N227" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O227" s="69">
+      <c r="O227" s="59">
         <v>570000</v>
       </c>
-      <c r="P227" s="69">
+      <c r="P227" s="59">
         <v>141635</v>
       </c>
-      <c r="Q227" s="56">
+      <c r="Q227" s="46">
         <f t="shared" si="19"/>
         <v>711635</v>
       </c>
@@ -17929,7 +17950,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="228" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A228" s="5" t="s">
         <v>503</v>
       </c>
@@ -17973,13 +17994,13 @@
       <c r="N228" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O228" s="69">
+      <c r="O228" s="59">
         <v>1000000</v>
       </c>
-      <c r="P228" s="69">
+      <c r="P228" s="59">
         <v>231750</v>
       </c>
-      <c r="Q228" s="56">
+      <c r="Q228" s="46">
         <f t="shared" si="19"/>
         <v>1231750</v>
       </c>
@@ -17997,7 +18018,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="229" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A229" s="9" t="s">
         <v>505</v>
       </c>
@@ -18041,13 +18062,13 @@
       <c r="N229" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O229" s="70">
+      <c r="O229" s="60">
         <v>1000000</v>
       </c>
-      <c r="P229" s="70">
+      <c r="P229" s="60">
         <v>231750</v>
       </c>
-      <c r="Q229" s="56">
+      <c r="Q229" s="46">
         <f t="shared" si="19"/>
         <v>1231750</v>
       </c>
@@ -18065,7 +18086,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="230" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A230" s="9" t="s">
         <v>506</v>
       </c>
@@ -18109,13 +18130,13 @@
       <c r="N230" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O230" s="70">
+      <c r="O230" s="60">
         <v>150000</v>
       </c>
-      <c r="P230" s="70">
+      <c r="P230" s="60">
         <v>40000</v>
       </c>
-      <c r="Q230" s="56">
+      <c r="Q230" s="46">
         <f t="shared" si="19"/>
         <v>190000</v>
       </c>
@@ -18133,7 +18154,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="231" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A231" s="9" t="s">
         <v>507</v>
       </c>
@@ -18177,13 +18198,13 @@
       <c r="N231" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O231" s="70">
+      <c r="O231" s="60">
         <v>570000</v>
       </c>
-      <c r="P231" s="70">
+      <c r="P231" s="60">
         <v>221635</v>
       </c>
-      <c r="Q231" s="56">
+      <c r="Q231" s="46">
         <f t="shared" si="19"/>
         <v>791635</v>
       </c>
@@ -18201,7 +18222,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="232" spans="1:21" s="68" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:21" s="58" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A232" s="9" t="s">
         <v>508</v>
       </c>
@@ -18245,13 +18266,13 @@
       <c r="N232" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O232" s="70">
+      <c r="O232" s="60">
         <v>150000</v>
       </c>
-      <c r="P232" s="70">
+      <c r="P232" s="60">
         <v>60000</v>
       </c>
-      <c r="Q232" s="56">
+      <c r="Q232" s="46">
         <f t="shared" si="19"/>
         <v>210000</v>
       </c>
@@ -18291,10 +18312,10 @@
       <c r="G233" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="H233" s="71">
+      <c r="H233" s="61">
         <v>46098</v>
       </c>
-      <c r="I233" s="71">
+      <c r="I233" s="61">
         <v>46107</v>
       </c>
       <c r="J233" s="24">
@@ -18322,17 +18343,17 @@
       <c r="Q233" s="5">
         <v>0</v>
       </c>
-      <c r="R233" s="50">
+      <c r="R233" s="13">
         <v>46108</v>
       </c>
       <c r="S233" s="24">
         <f t="shared" si="16"/>
         <v>9</v>
       </c>
-      <c r="T233" s="48" t="s">
+      <c r="T233" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="U233" s="48" t="s">
+      <c r="U233" s="11" t="s">
         <v>443</v>
       </c>
     </row>
@@ -18358,10 +18379,10 @@
       <c r="G234" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H234" s="71">
+      <c r="H234" s="61">
         <v>46057</v>
       </c>
-      <c r="I234" s="71">
+      <c r="I234" s="61">
         <v>46107</v>
       </c>
       <c r="J234" s="24">
@@ -18389,853 +18410,1925 @@
       <c r="Q234" s="15">
         <v>3634117</v>
       </c>
-      <c r="R234" s="50">
+      <c r="R234" s="13">
         <v>46108</v>
       </c>
       <c r="S234" s="24">
         <f t="shared" si="16"/>
         <v>38</v>
       </c>
-      <c r="T234" s="48" t="s">
+      <c r="T234" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="U234" s="48" t="s">
+      <c r="U234" s="11" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A235" s="72" t="s">
+      <c r="A235" s="50" t="s">
         <v>516</v>
       </c>
-      <c r="B235" s="73" t="s">
+      <c r="B235" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="C235" s="72">
+      <c r="C235" s="50">
         <v>60423011</v>
       </c>
-      <c r="D235" s="73" t="s">
+      <c r="D235" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="E235" s="72" t="s">
+      <c r="E235" s="50" t="s">
         <v>517</v>
       </c>
-      <c r="F235" s="73" t="s">
+      <c r="F235" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="G235" s="73" t="s">
-        <v>23</v>
-      </c>
-      <c r="H235" s="74">
+      <c r="G235" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H235" s="67">
         <v>46105</v>
       </c>
-      <c r="I235" s="74">
+      <c r="I235" s="67">
         <v>46111</v>
       </c>
       <c r="J235" s="24">
         <f t="shared" si="15"/>
         <v>5</v>
       </c>
-      <c r="K235" s="75" t="s">
+      <c r="K235" s="45" t="s">
         <v>303</v>
       </c>
-      <c r="L235" s="73" t="s">
+      <c r="L235" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="M235" s="73" t="s">
+      <c r="M235" s="34" t="s">
         <v>358</v>
       </c>
-      <c r="N235" s="73" t="s">
+      <c r="N235" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="O235" s="76">
+      <c r="O235" s="47">
         <v>0</v>
       </c>
-      <c r="P235" s="76">
+      <c r="P235" s="47">
         <v>0</v>
       </c>
-      <c r="Q235" s="76">
+      <c r="Q235" s="47">
         <f t="shared" ref="Q235:Q243" si="20">P235+O235</f>
         <v>0</v>
       </c>
-      <c r="R235" s="77">
+      <c r="R235" s="35">
         <v>46111</v>
       </c>
       <c r="S235" s="24">
         <f t="shared" si="16"/>
         <v>5</v>
       </c>
-      <c r="T235" s="73" t="s">
+      <c r="T235" s="34" t="s">
         <v>518</v>
       </c>
-      <c r="U235" s="73" t="s">
+      <c r="U235" s="34" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A236" s="41" t="s">
+      <c r="A236" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="B236" s="48" t="s">
+      <c r="B236" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C236" s="41">
+      <c r="C236" s="12">
         <v>60422373</v>
       </c>
-      <c r="D236" s="48" t="s">
+      <c r="D236" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="E236" s="41" t="s">
+      <c r="E236" s="12" t="s">
         <v>519</v>
       </c>
-      <c r="F236" s="48" t="s">
+      <c r="F236" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G236" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="H236" s="42">
+      <c r="G236" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H236" s="14">
         <v>46105</v>
       </c>
-      <c r="I236" s="42">
+      <c r="I236" s="14">
         <v>46111</v>
       </c>
       <c r="J236" s="24">
         <f t="shared" si="15"/>
         <v>5</v>
       </c>
-      <c r="K236" s="47" t="s">
+      <c r="K236" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L236" s="48" t="s">
+      <c r="L236" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="M236" s="48" t="s">
+      <c r="M236" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="N236" s="48" t="s">
+      <c r="N236" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="O236" s="78">
+      <c r="O236" s="46">
         <v>0</v>
       </c>
-      <c r="P236" s="78">
+      <c r="P236" s="46">
         <v>0</v>
       </c>
-      <c r="Q236" s="78">
+      <c r="Q236" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="R236" s="50">
+      <c r="R236" s="13">
         <v>46111</v>
       </c>
       <c r="S236" s="24">
         <f t="shared" si="16"/>
         <v>5</v>
       </c>
-      <c r="T236" s="73" t="s">
+      <c r="T236" s="34" t="s">
         <v>518</v>
       </c>
-      <c r="U236" s="48" t="s">
+      <c r="U236" s="11" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A237" s="41" t="s">
+      <c r="A237" s="12" t="s">
         <v>520</v>
       </c>
-      <c r="B237" s="41" t="s">
+      <c r="B237" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C237" s="41">
+      <c r="C237" s="12">
         <v>58144220</v>
       </c>
-      <c r="D237" s="41" t="s">
+      <c r="D237" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E237" s="41" t="s">
+      <c r="E237" s="12" t="s">
         <v>521</v>
       </c>
-      <c r="F237" s="41" t="s">
+      <c r="F237" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G237" s="41" t="s">
+      <c r="G237" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H237" s="79">
+      <c r="H237" s="16">
         <v>46064</v>
       </c>
-      <c r="I237" s="42">
+      <c r="I237" s="14">
         <v>46111</v>
       </c>
       <c r="J237" s="24">
         <f t="shared" si="15"/>
         <v>34</v>
       </c>
-      <c r="K237" s="47" t="s">
+      <c r="K237" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L237" s="48" t="s">
+      <c r="L237" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="M237" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="N237" s="41" t="s">
+      <c r="M237" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N237" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O237" s="78">
+      <c r="O237" s="46">
         <v>0</v>
       </c>
-      <c r="P237" s="78">
+      <c r="P237" s="46">
         <v>0</v>
       </c>
-      <c r="Q237" s="78">
+      <c r="Q237" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="R237" s="50">
+      <c r="R237" s="13">
         <v>46111</v>
       </c>
       <c r="S237" s="24">
         <f t="shared" si="16"/>
         <v>34</v>
       </c>
-      <c r="T237" s="73" t="s">
+      <c r="T237" s="34" t="s">
         <v>518</v>
       </c>
-      <c r="U237" s="48" t="s">
+      <c r="U237" s="11" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A238" s="41" t="s">
+      <c r="A238" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="B238" s="41" t="s">
+      <c r="B238" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C238" s="41">
+      <c r="C238" s="12">
         <v>58808846</v>
       </c>
-      <c r="D238" s="41" t="s">
+      <c r="D238" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E238" s="41" t="s">
+      <c r="E238" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="F238" s="41" t="s">
+      <c r="F238" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G238" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H238" s="42">
+      <c r="G238" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H238" s="14">
         <v>46076</v>
       </c>
-      <c r="I238" s="42">
+      <c r="I238" s="14">
         <v>46108</v>
       </c>
       <c r="J238" s="24">
         <f t="shared" si="15"/>
         <v>25</v>
       </c>
-      <c r="K238" s="47" t="s">
+      <c r="K238" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L238" s="48" t="s">
+      <c r="L238" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="M238" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="N238" s="41" t="s">
+      <c r="M238" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N238" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O238" s="49">
+      <c r="O238" s="19">
         <v>2000000</v>
       </c>
-      <c r="P238" s="49">
+      <c r="P238" s="19">
         <v>462000</v>
       </c>
-      <c r="Q238" s="78">
+      <c r="Q238" s="46">
         <f t="shared" si="20"/>
         <v>2462000</v>
       </c>
-      <c r="R238" s="50">
+      <c r="R238" s="13">
         <v>46111</v>
       </c>
       <c r="S238" s="24">
         <f t="shared" si="16"/>
         <v>26</v>
       </c>
-      <c r="T238" s="73" t="s">
+      <c r="T238" s="34" t="s">
         <v>518</v>
       </c>
-      <c r="U238" s="48" t="s">
+      <c r="U238" s="11" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A239" s="41" t="s">
+      <c r="A239" s="12" t="s">
         <v>524</v>
       </c>
-      <c r="B239" s="48" t="s">
+      <c r="B239" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C239" s="41">
+      <c r="C239" s="12">
         <v>59821965</v>
       </c>
-      <c r="D239" s="48" t="s">
+      <c r="D239" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E239" s="41" t="s">
+      <c r="E239" s="12" t="s">
         <v>525</v>
       </c>
-      <c r="F239" s="41" t="s">
+      <c r="F239" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G239" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="H239" s="42">
+      <c r="G239" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H239" s="14">
         <v>46093</v>
       </c>
-      <c r="I239" s="42">
+      <c r="I239" s="14">
         <v>46111</v>
       </c>
       <c r="J239" s="24">
         <f t="shared" si="15"/>
         <v>13</v>
       </c>
-      <c r="K239" s="47" t="s">
+      <c r="K239" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L239" s="48" t="s">
+      <c r="L239" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="M239" s="48" t="s">
+      <c r="M239" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="N239" s="48" t="s">
+      <c r="N239" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="O239" s="78">
+      <c r="O239" s="46">
         <v>3000000</v>
       </c>
-      <c r="P239" s="78">
+      <c r="P239" s="46">
         <v>0</v>
       </c>
-      <c r="Q239" s="78">
+      <c r="Q239" s="46">
         <f>P239+O239</f>
         <v>3000000</v>
       </c>
-      <c r="R239" s="50">
+      <c r="R239" s="13">
         <v>46111</v>
       </c>
       <c r="S239" s="24">
         <f t="shared" si="16"/>
         <v>13</v>
       </c>
-      <c r="T239" s="73" t="s">
+      <c r="T239" s="34" t="s">
         <v>518</v>
       </c>
-      <c r="U239" s="48" t="s">
+      <c r="U239" s="11" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A240" s="41" t="s">
+      <c r="A240" s="12" t="s">
         <v>526</v>
       </c>
-      <c r="B240" s="41" t="s">
+      <c r="B240" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C240" s="41">
+      <c r="C240" s="12">
         <v>59894758</v>
       </c>
-      <c r="D240" s="41" t="s">
+      <c r="D240" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E240" s="41" t="s">
+      <c r="E240" s="12" t="s">
         <v>527</v>
       </c>
-      <c r="F240" s="41" t="s">
+      <c r="F240" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G240" s="41" t="s">
+      <c r="G240" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H240" s="42">
+      <c r="H240" s="14">
         <v>46094</v>
       </c>
-      <c r="I240" s="42">
+      <c r="I240" s="14">
         <v>46111</v>
       </c>
       <c r="J240" s="24">
         <f t="shared" si="15"/>
         <v>12</v>
       </c>
-      <c r="K240" s="47" t="s">
+      <c r="K240" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L240" s="48" t="s">
+      <c r="L240" s="11" t="s">
         <v>304</v>
       </c>
       <c r="M240" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N240" s="41" t="s">
+      <c r="N240" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="O240" s="49">
+      <c r="O240" s="19">
         <v>1000000</v>
       </c>
-      <c r="P240" s="49">
+      <c r="P240" s="19">
         <v>678945</v>
       </c>
-      <c r="Q240" s="78">
+      <c r="Q240" s="46">
         <f t="shared" si="20"/>
         <v>1678945</v>
       </c>
-      <c r="R240" s="50">
+      <c r="R240" s="13">
         <v>46111</v>
       </c>
       <c r="S240" s="24">
         <f t="shared" si="16"/>
         <v>12</v>
       </c>
-      <c r="T240" s="73" t="s">
+      <c r="T240" s="34" t="s">
         <v>518</v>
       </c>
-      <c r="U240" s="48" t="s">
+      <c r="U240" s="11" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="241" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A241" s="41" t="s">
+      <c r="A241" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="B241" s="41" t="s">
+      <c r="B241" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C241" s="41">
+      <c r="C241" s="12">
         <v>59278285</v>
       </c>
-      <c r="D241" s="41" t="s">
+      <c r="D241" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="E241" s="41" t="s">
+      <c r="E241" s="12" t="s">
         <v>530</v>
       </c>
-      <c r="F241" s="41" t="s">
+      <c r="F241" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G241" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H241" s="42">
+      <c r="G241" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H241" s="14">
         <v>46084</v>
       </c>
-      <c r="I241" s="42">
+      <c r="I241" s="14">
         <v>46105</v>
       </c>
       <c r="J241" s="24">
         <f t="shared" si="15"/>
         <v>16</v>
       </c>
-      <c r="K241" s="47" t="s">
+      <c r="K241" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L241" s="48" t="s">
+      <c r="L241" s="11" t="s">
         <v>304</v>
       </c>
       <c r="M241" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N241" s="41" t="s">
+      <c r="N241" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O241" s="49">
+      <c r="O241" s="19">
         <v>1050000</v>
       </c>
-      <c r="P241" s="49">
+      <c r="P241" s="19">
         <v>500000</v>
       </c>
-      <c r="Q241" s="78">
+      <c r="Q241" s="46">
         <f t="shared" si="20"/>
         <v>1550000</v>
       </c>
-      <c r="R241" s="50">
+      <c r="R241" s="13">
         <v>46112</v>
       </c>
       <c r="S241" s="24">
         <f t="shared" si="16"/>
         <v>21</v>
       </c>
-      <c r="T241" s="73" t="s">
+      <c r="T241" s="34" t="s">
         <v>518</v>
       </c>
-      <c r="U241" s="48" t="s">
+      <c r="U241" s="11" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A242" s="41" t="s">
+      <c r="A242" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="B242" s="41" t="s">
+      <c r="B242" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C242" s="41">
+      <c r="C242" s="12">
         <v>59278925</v>
       </c>
-      <c r="D242" s="41" t="s">
+      <c r="D242" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E242" s="41" t="s">
+      <c r="E242" s="12" t="s">
         <v>531</v>
       </c>
-      <c r="F242" s="41" t="s">
+      <c r="F242" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G242" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H242" s="42">
+      <c r="G242" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H242" s="14">
         <v>46084</v>
       </c>
-      <c r="I242" s="42">
+      <c r="I242" s="14">
         <v>46105</v>
       </c>
       <c r="J242" s="24">
         <f t="shared" si="15"/>
         <v>16</v>
       </c>
-      <c r="K242" s="47" t="s">
+      <c r="K242" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L242" s="48" t="s">
+      <c r="L242" s="11" t="s">
         <v>304</v>
       </c>
       <c r="M242" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N242" s="41" t="s">
+      <c r="N242" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O242" s="49">
+      <c r="O242" s="19">
         <v>1050000</v>
       </c>
-      <c r="P242" s="49">
+      <c r="P242" s="19">
         <v>500000</v>
       </c>
-      <c r="Q242" s="78">
+      <c r="Q242" s="46">
         <f t="shared" si="20"/>
         <v>1550000</v>
       </c>
-      <c r="R242" s="50">
+      <c r="R242" s="13">
         <v>46112</v>
       </c>
       <c r="S242" s="24">
         <f t="shared" si="16"/>
         <v>21</v>
       </c>
-      <c r="T242" s="73" t="s">
+      <c r="T242" s="34" t="s">
         <v>518</v>
       </c>
-      <c r="U242" s="48" t="s">
+      <c r="U242" s="11" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="243" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A243" s="41" t="s">
+      <c r="A243" s="12" t="s">
         <v>469</v>
       </c>
-      <c r="B243" s="41" t="s">
+      <c r="B243" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C243" s="80">
+      <c r="C243" s="5">
         <v>59300338</v>
       </c>
-      <c r="D243" s="41" t="s">
+      <c r="D243" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E243" s="41" t="s">
+      <c r="E243" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="F243" s="41" t="s">
+      <c r="F243" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G243" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H243" s="42">
+      <c r="G243" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H243" s="14">
         <v>46084</v>
       </c>
-      <c r="I243" s="42">
+      <c r="I243" s="14">
         <v>46112</v>
       </c>
       <c r="J243" s="24">
         <f t="shared" si="15"/>
         <v>21</v>
       </c>
-      <c r="K243" s="47" t="s">
+      <c r="K243" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="L243" s="48" t="s">
+      <c r="L243" s="11" t="s">
         <v>304</v>
       </c>
       <c r="M243" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N243" s="41" t="s">
+      <c r="N243" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O243" s="49">
+      <c r="O243" s="19">
         <v>2000000</v>
       </c>
-      <c r="P243" s="49">
+      <c r="P243" s="19">
         <v>462000</v>
       </c>
-      <c r="Q243" s="78">
+      <c r="Q243" s="46">
         <f t="shared" si="20"/>
         <v>2462000</v>
       </c>
-      <c r="R243" s="50">
+      <c r="R243" s="13">
         <v>46112</v>
       </c>
       <c r="S243" s="24">
         <f t="shared" si="16"/>
         <v>21</v>
       </c>
-      <c r="T243" s="73" t="s">
+      <c r="T243" s="34" t="s">
         <v>518</v>
       </c>
-      <c r="U243" s="48" t="s">
+      <c r="U243" s="11" t="s">
         <v>443</v>
       </c>
     </row>
+    <row r="244" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A244" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="B244" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C244" s="12">
+        <v>51053195</v>
+      </c>
+      <c r="D244" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E244" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="F244" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G244" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H244" s="14">
+        <v>45924</v>
+      </c>
+      <c r="I244" s="14">
+        <v>46112</v>
+      </c>
+      <c r="J244" s="24">
+        <f t="shared" si="15"/>
+        <v>135</v>
+      </c>
+      <c r="K244" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L244" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M244" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N244" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O244" s="12">
+        <v>200000</v>
+      </c>
+      <c r="P244" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q244" s="19">
+        <v>200000</v>
+      </c>
+      <c r="R244" s="14">
+        <v>46113</v>
+      </c>
+      <c r="S244" s="24">
+        <f t="shared" si="16"/>
+        <v>136</v>
+      </c>
+      <c r="T244" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="U244" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="245" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A245" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="B245" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C245" s="12">
+        <v>47878019</v>
+      </c>
+      <c r="D245" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="E245" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="F245" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G245" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H245" s="14">
+        <v>45861</v>
+      </c>
+      <c r="I245" s="14">
+        <v>46111</v>
+      </c>
+      <c r="J245" s="24">
+        <f t="shared" si="15"/>
+        <v>179</v>
+      </c>
+      <c r="K245" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L245" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M245" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N245" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="O245" s="12">
+        <v>1538480</v>
+      </c>
+      <c r="P245" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q245" s="19">
+        <v>1538480</v>
+      </c>
+      <c r="R245" s="14">
+        <v>46113</v>
+      </c>
+      <c r="S245" s="24">
+        <f t="shared" si="16"/>
+        <v>181</v>
+      </c>
+      <c r="T245" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="U245" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="246" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A246" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="B246" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C246" s="12">
+        <v>47653333</v>
+      </c>
+      <c r="D246" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E246" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="F246" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G246" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H246" s="14">
+        <v>45859</v>
+      </c>
+      <c r="I246" s="14">
+        <v>46112</v>
+      </c>
+      <c r="J246" s="24">
+        <f t="shared" si="15"/>
+        <v>182</v>
+      </c>
+      <c r="K246" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L246" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M246" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N246" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="O246" s="12">
+        <v>350000</v>
+      </c>
+      <c r="P246" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q246" s="19">
+        <v>350000</v>
+      </c>
+      <c r="R246" s="14">
+        <v>46113</v>
+      </c>
+      <c r="S246" s="24">
+        <f t="shared" si="16"/>
+        <v>183</v>
+      </c>
+      <c r="T246" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="U246" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="247" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A247" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="B247" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C247" s="12">
+        <v>58488142</v>
+      </c>
+      <c r="D247" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E247" s="12">
+        <v>2720211797</v>
+      </c>
+      <c r="F247" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G247" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H247" s="14">
+        <v>46070</v>
+      </c>
+      <c r="I247" s="14">
+        <v>46112</v>
+      </c>
+      <c r="J247" s="24">
+        <f t="shared" si="15"/>
+        <v>31</v>
+      </c>
+      <c r="K247" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L247" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M247" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N247" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="O247" s="12">
+        <v>108000</v>
+      </c>
+      <c r="P247" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q247" s="19">
+        <v>108000</v>
+      </c>
+      <c r="R247" s="14">
+        <v>46116</v>
+      </c>
+      <c r="S247" s="24">
+        <f t="shared" si="16"/>
+        <v>34</v>
+      </c>
+      <c r="T247" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U247" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="248" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A248" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="B248" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C248" s="12">
+        <v>58029496</v>
+      </c>
+      <c r="D248" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E248" s="12">
+        <v>2721358023</v>
+      </c>
+      <c r="F248" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G248" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H248" s="14">
+        <v>46062</v>
+      </c>
+      <c r="I248" s="14">
+        <v>46112</v>
+      </c>
+      <c r="J248" s="24">
+        <f t="shared" si="15"/>
+        <v>37</v>
+      </c>
+      <c r="K248" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L248" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M248" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N248" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="O248" s="12">
+        <v>60000</v>
+      </c>
+      <c r="P248" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q248" s="19">
+        <v>60000</v>
+      </c>
+      <c r="R248" s="14">
+        <v>46116</v>
+      </c>
+      <c r="S248" s="24">
+        <f t="shared" si="16"/>
+        <v>40</v>
+      </c>
+      <c r="T248" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U248" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="249" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A249" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="B249" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C249" s="12">
+        <v>52741559</v>
+      </c>
+      <c r="D249" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E249" s="12">
+        <v>2721300130</v>
+      </c>
+      <c r="F249" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G249" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H249" s="14">
+        <v>45959</v>
+      </c>
+      <c r="I249" s="14">
+        <v>46112</v>
+      </c>
+      <c r="J249" s="24">
+        <f t="shared" si="15"/>
+        <v>110</v>
+      </c>
+      <c r="K249" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L249" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M249" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N249" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="O249" s="12">
+        <v>400000</v>
+      </c>
+      <c r="P249" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q249" s="19">
+        <v>400000</v>
+      </c>
+      <c r="R249" s="14">
+        <v>46116</v>
+      </c>
+      <c r="S249" s="24">
+        <f t="shared" si="16"/>
+        <v>113</v>
+      </c>
+      <c r="T249" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U249" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="250" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A250" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="B250" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C250" s="12">
+        <v>58996002</v>
+      </c>
+      <c r="D250" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E250" s="12">
+        <v>2720306611</v>
+      </c>
+      <c r="F250" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G250" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H250" s="14">
+        <v>46079</v>
+      </c>
+      <c r="I250" s="14">
+        <v>46112</v>
+      </c>
+      <c r="J250" s="24">
+        <f t="shared" si="15"/>
+        <v>24</v>
+      </c>
+      <c r="K250" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L250" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M250" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N250" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="O250" s="12">
+        <v>60000</v>
+      </c>
+      <c r="P250" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q250" s="19">
+        <v>60000</v>
+      </c>
+      <c r="R250" s="14">
+        <v>46116</v>
+      </c>
+      <c r="S250" s="24">
+        <f t="shared" si="16"/>
+        <v>27</v>
+      </c>
+      <c r="T250" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U250" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="251" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A251" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="B251" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C251" s="12">
+        <v>47639322</v>
+      </c>
+      <c r="D251" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E251" s="12">
+        <v>2734711025</v>
+      </c>
+      <c r="F251" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G251" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H251" s="14">
+        <v>45856</v>
+      </c>
+      <c r="I251" s="14">
+        <v>46113</v>
+      </c>
+      <c r="J251" s="24">
+        <f t="shared" si="15"/>
+        <v>184</v>
+      </c>
+      <c r="K251" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L251" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M251" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N251" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="O251" s="12">
+        <v>108000</v>
+      </c>
+      <c r="P251" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q251" s="19">
+        <v>108000</v>
+      </c>
+      <c r="R251" s="14">
+        <v>46116</v>
+      </c>
+      <c r="S251" s="24">
+        <f t="shared" si="16"/>
+        <v>186</v>
+      </c>
+      <c r="T251" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U251" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="252" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A252" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="B252" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C252" s="12">
+        <v>60154802</v>
+      </c>
+      <c r="D252" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E252" s="12">
+        <v>2722520140</v>
+      </c>
+      <c r="F252" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G252" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H252" s="14">
+        <v>46100</v>
+      </c>
+      <c r="I252" s="14">
+        <v>46116</v>
+      </c>
+      <c r="J252" s="24">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="K252" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L252" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M252" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N252" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="O252" s="12">
+        <v>150000</v>
+      </c>
+      <c r="P252" s="12">
+        <v>40000</v>
+      </c>
+      <c r="Q252" s="19">
+        <v>190000</v>
+      </c>
+      <c r="R252" s="14">
+        <v>46119</v>
+      </c>
+      <c r="S252" s="24">
+        <f t="shared" si="16"/>
+        <v>14</v>
+      </c>
+      <c r="T252" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U252" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="253" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A253" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="B253" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C253" s="12">
+        <v>47658350</v>
+      </c>
+      <c r="D253" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E253" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="F253" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G253" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H253" s="14">
+        <v>45859</v>
+      </c>
+      <c r="I253" s="14">
+        <v>46115</v>
+      </c>
+      <c r="J253" s="24">
+        <f t="shared" si="15"/>
+        <v>185</v>
+      </c>
+      <c r="K253" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L253" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M253" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N253" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="O253" s="12">
+        <v>350000</v>
+      </c>
+      <c r="P253" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q253" s="19">
+        <v>350000</v>
+      </c>
+      <c r="R253" s="14">
+        <v>46119</v>
+      </c>
+      <c r="S253" s="24">
+        <f t="shared" si="16"/>
+        <v>187</v>
+      </c>
+      <c r="T253" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U253" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="254" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A254" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B254" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C254" s="12">
+        <v>48206525</v>
+      </c>
+      <c r="D254" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E254" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="F254" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G254" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H254" s="14">
+        <v>45869</v>
+      </c>
+      <c r="I254" s="14">
+        <v>46116</v>
+      </c>
+      <c r="J254" s="24">
+        <f t="shared" si="15"/>
+        <v>177</v>
+      </c>
+      <c r="K254" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L254" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M254" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N254" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="O254" s="12">
+        <v>200000</v>
+      </c>
+      <c r="P254" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q254" s="19">
+        <v>200000</v>
+      </c>
+      <c r="R254" s="14">
+        <v>46119</v>
+      </c>
+      <c r="S254" s="24">
+        <f t="shared" si="16"/>
+        <v>179</v>
+      </c>
+      <c r="T254" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U254" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="255" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A255" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B255" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C255" s="12">
+        <v>59308240</v>
+      </c>
+      <c r="D255" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E255" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="F255" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G255" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H255" s="14">
+        <v>46084</v>
+      </c>
+      <c r="I255" s="14">
+        <v>46113</v>
+      </c>
+      <c r="J255" s="24">
+        <f t="shared" si="15"/>
+        <v>22</v>
+      </c>
+      <c r="K255" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L255" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M255" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N255" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O255" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="P255" s="12">
+        <v>462000</v>
+      </c>
+      <c r="Q255" s="19">
+        <v>2462000</v>
+      </c>
+      <c r="R255" s="14">
+        <v>46119</v>
+      </c>
+      <c r="S255" s="24">
+        <f t="shared" si="16"/>
+        <v>26</v>
+      </c>
+      <c r="T255" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U255" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="256" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A256" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="B256" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C256" s="12">
+        <v>59301554</v>
+      </c>
+      <c r="D256" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="E256" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="F256" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G256" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H256" s="14">
+        <v>46084</v>
+      </c>
+      <c r="I256" s="14">
+        <v>46113</v>
+      </c>
+      <c r="J256" s="24">
+        <f t="shared" si="15"/>
+        <v>22</v>
+      </c>
+      <c r="K256" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L256" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M256" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N256" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O256" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="P256" s="12">
+        <v>462000</v>
+      </c>
+      <c r="Q256" s="19">
+        <v>2462000</v>
+      </c>
+      <c r="R256" s="14">
+        <v>46119</v>
+      </c>
+      <c r="S256" s="24">
+        <f t="shared" si="16"/>
+        <v>26</v>
+      </c>
+      <c r="T256" s="64" t="s">
+        <v>552</v>
+      </c>
+      <c r="U256" s="64" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="257" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A257" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="B257" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C257" s="12">
+        <v>59495495</v>
+      </c>
+      <c r="D257" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E257" s="12">
+        <v>2720219740</v>
+      </c>
+      <c r="F257" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G257" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H257" s="14">
+        <v>46087</v>
+      </c>
+      <c r="I257" s="14">
+        <v>46113</v>
+      </c>
+      <c r="J257" s="24">
+        <f t="shared" si="15"/>
+        <v>19</v>
+      </c>
+      <c r="K257" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L257" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M257" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N257" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="O257" s="12">
+        <v>150000</v>
+      </c>
+      <c r="P257" s="12">
+        <v>40000</v>
+      </c>
+      <c r="Q257" s="19">
+        <v>190000</v>
+      </c>
+      <c r="R257" s="14">
+        <v>46120</v>
+      </c>
+      <c r="S257" s="24">
+        <f t="shared" si="16"/>
+        <v>24</v>
+      </c>
+      <c r="T257" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U257" s="12" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="258" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A258" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="B258" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C258" s="12">
+        <v>60589306</v>
+      </c>
+      <c r="D258" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E258" s="12">
+        <v>2721351935</v>
+      </c>
+      <c r="F258" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G258" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H258" s="14">
+        <v>46108</v>
+      </c>
+      <c r="I258" s="14">
+        <v>46119</v>
+      </c>
+      <c r="J258" s="24">
+        <f t="shared" si="15"/>
+        <v>8</v>
+      </c>
+      <c r="K258" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L258" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M258" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N258" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="O258" s="12">
+        <v>150000</v>
+      </c>
+      <c r="P258" s="12">
+        <v>60000</v>
+      </c>
+      <c r="Q258" s="19">
+        <v>210000</v>
+      </c>
+      <c r="R258" s="14">
+        <v>46120</v>
+      </c>
+      <c r="S258" s="24">
+        <f t="shared" si="16"/>
+        <v>9</v>
+      </c>
+      <c r="T258" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U258" s="12" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="259" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A259" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="B259" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C259" s="12">
+        <v>48618333</v>
+      </c>
+      <c r="D259" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="E259" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="F259" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G259" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H259" s="14">
+        <v>46108</v>
+      </c>
+      <c r="I259" s="14">
+        <v>46119</v>
+      </c>
+      <c r="J259" s="24">
+        <f t="shared" si="15"/>
+        <v>8</v>
+      </c>
+      <c r="K259" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L259" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="M259" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N259" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="O259" s="12">
+        <v>800000</v>
+      </c>
+      <c r="P259" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q259" s="19">
+        <v>800000</v>
+      </c>
+      <c r="R259" s="14">
+        <v>46120</v>
+      </c>
+      <c r="S259" s="24">
+        <f t="shared" si="16"/>
+        <v>9</v>
+      </c>
+      <c r="T259" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U259" s="12" t="s">
+        <v>551</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U243" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U259" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="85" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="84"/>
     <cfRule type="duplicateValues" dxfId="83" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C205 C244:C1048576">
+    <cfRule type="duplicateValues" dxfId="79" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="103"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C212 C244:C1048576">
+    <cfRule type="duplicateValues" dxfId="77" priority="110"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C232 C244:C1048576">
+    <cfRule type="duplicateValues" dxfId="76" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="79" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="77" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="75" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="74" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="72" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="71" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="70" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="69" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="68" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="67" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="66" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="65" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="64" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="63" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="62" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="61" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="60" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="59" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="58" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="57" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
-    <cfRule type="duplicateValues" dxfId="56" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="55" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="54" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="52" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="51" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="50" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="49" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="48" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="46" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C114">
-    <cfRule type="duplicateValues" dxfId="45" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="44" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="43" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C157:C160">
-    <cfRule type="duplicateValues" dxfId="41" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C161:C163">
-    <cfRule type="duplicateValues" dxfId="40" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="39" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="37" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C168">
-    <cfRule type="duplicateValues" dxfId="35" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="34" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171">
-    <cfRule type="duplicateValues" dxfId="33" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173">
-    <cfRule type="duplicateValues" dxfId="32" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="30" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C175">
-    <cfRule type="duplicateValues" dxfId="29" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="28" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C178">
-    <cfRule type="duplicateValues" dxfId="27" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179">
-    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C206:C212">
-    <cfRule type="duplicateValues" dxfId="24" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
-    <cfRule type="duplicateValues" dxfId="23" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C208">
-    <cfRule type="duplicateValues" dxfId="21" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218:C223">
-    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C225:C232">
-    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C233:C243">
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="17" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="15" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="14" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="13" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="12" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="11" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="10" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="9" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="8" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172">
-    <cfRule type="duplicateValues" dxfId="7" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175">
-    <cfRule type="duplicateValues" dxfId="6" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E243">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C233:C243">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C205 C244:C1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="103"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C212 C244:C1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="110"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C232 C244:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="394" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{777F1244-B65D-4C91-BFFB-37E2249E79FA}"/>
+  <xr:revisionPtr revIDLastSave="410" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E66CBA1-EEF6-42B4-A78B-8573D1ABD908}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2658" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2717" uniqueCount="565">
   <si>
     <t>Client</t>
   </si>
@@ -1699,6 +1699,42 @@
   </si>
   <si>
     <t>S15</t>
+  </si>
+  <si>
+    <t>VIPNET</t>
+  </si>
+  <si>
+    <t>COC&gt;&gt;&gt;DABAKALA</t>
+  </si>
+  <si>
+    <t>SYTHD260018</t>
+  </si>
+  <si>
+    <t>MAGAL TELECOM AFRICA SARL</t>
+  </si>
+  <si>
+    <t>COCODY&gt;&gt;&gt;OUAGA</t>
+  </si>
+  <si>
+    <t>SYTHD250368</t>
+  </si>
+  <si>
+    <t>RIMCO</t>
+  </si>
+  <si>
+    <t>SYTHD260089</t>
+  </si>
+  <si>
+    <t>ODIENNE</t>
+  </si>
+  <si>
+    <t>VPNLL120010</t>
+  </si>
+  <si>
+    <t>DES SOCIETES D'ASSURANCE COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>Projet DMO</t>
   </si>
 </sst>
 </file>
@@ -1923,7 +1959,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2104,6 +2140,15 @@
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3307,7 +3352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U259"/>
+  <dimension ref="A1:U264"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="26" customWidth="1"/>
@@ -16416,7 +16461,7 @@
         <v>46094</v>
       </c>
       <c r="J205" s="24">
-        <f t="shared" ref="J205:J259" si="15">+NETWORKDAYS(H205,I205)</f>
+        <f t="shared" ref="J205:J264" si="15">+NETWORKDAYS(H205,I205)</f>
         <v>18</v>
       </c>
       <c r="K205" s="12" t="s">
@@ -16444,7 +16489,7 @@
         <v>46094</v>
       </c>
       <c r="S205" s="24">
-        <f t="shared" ref="S205:S259" si="16">NETWORKDAYS(H205,R205)</f>
+        <f t="shared" ref="S205:S264" si="16">NETWORKDAYS(H205,R205)</f>
         <v>18</v>
       </c>
       <c r="T205" s="12" t="s">
@@ -20105,6 +20150,341 @@
         <v>552</v>
       </c>
       <c r="U259" s="12" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="260" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A260" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="B260" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C260" s="68">
+        <v>48847621</v>
+      </c>
+      <c r="D260" s="68" t="s">
+        <v>554</v>
+      </c>
+      <c r="E260" s="68" t="s">
+        <v>555</v>
+      </c>
+      <c r="F260" s="68" t="s">
+        <v>196</v>
+      </c>
+      <c r="G260" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H260" s="69">
+        <v>45887</v>
+      </c>
+      <c r="I260" s="69">
+        <v>46099</v>
+      </c>
+      <c r="J260" s="24">
+        <f t="shared" si="15"/>
+        <v>153</v>
+      </c>
+      <c r="K260" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="L260" s="68" t="s">
+        <v>327</v>
+      </c>
+      <c r="M260" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="N260" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="O260" s="68">
+        <v>0</v>
+      </c>
+      <c r="P260" s="68">
+        <v>0</v>
+      </c>
+      <c r="Q260" s="70">
+        <v>0</v>
+      </c>
+      <c r="R260" s="69">
+        <v>46121</v>
+      </c>
+      <c r="S260" s="24">
+        <f t="shared" si="16"/>
+        <v>169</v>
+      </c>
+      <c r="T260" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U260" s="68" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="261" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A261" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="B261" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C261" s="68">
+        <v>54178346</v>
+      </c>
+      <c r="D261" s="68" t="s">
+        <v>557</v>
+      </c>
+      <c r="E261" s="68" t="s">
+        <v>558</v>
+      </c>
+      <c r="F261" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="G261" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H261" s="69">
+        <v>45994</v>
+      </c>
+      <c r="I261" s="69">
+        <v>46092</v>
+      </c>
+      <c r="J261" s="24">
+        <f t="shared" si="15"/>
+        <v>71</v>
+      </c>
+      <c r="K261" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="L261" s="68" t="s">
+        <v>327</v>
+      </c>
+      <c r="M261" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="N261" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="O261" s="68">
+        <v>0</v>
+      </c>
+      <c r="P261" s="68">
+        <v>0</v>
+      </c>
+      <c r="Q261" s="70">
+        <v>0</v>
+      </c>
+      <c r="R261" s="69">
+        <v>46121</v>
+      </c>
+      <c r="S261" s="24">
+        <f t="shared" si="16"/>
+        <v>92</v>
+      </c>
+      <c r="T261" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U261" s="68" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="262" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A262" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="B262" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C262" s="68">
+        <v>60358121</v>
+      </c>
+      <c r="D262" s="68" t="s">
+        <v>50</v>
+      </c>
+      <c r="E262" s="68" t="s">
+        <v>560</v>
+      </c>
+      <c r="F262" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="G262" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H262" s="69">
+        <v>46104</v>
+      </c>
+      <c r="I262" s="69">
+        <v>46121</v>
+      </c>
+      <c r="J262" s="24">
+        <f t="shared" si="15"/>
+        <v>14</v>
+      </c>
+      <c r="K262" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="L262" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="M262" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="N262" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="O262" s="68">
+        <v>500000</v>
+      </c>
+      <c r="P262" s="68">
+        <v>460000</v>
+      </c>
+      <c r="Q262" s="70">
+        <v>960000</v>
+      </c>
+      <c r="R262" s="69">
+        <v>46121</v>
+      </c>
+      <c r="S262" s="24">
+        <f t="shared" si="16"/>
+        <v>14</v>
+      </c>
+      <c r="T262" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U262" s="68" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="263" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A263" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B263" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C263" s="68">
+        <v>51016709</v>
+      </c>
+      <c r="D263" s="68" t="s">
+        <v>561</v>
+      </c>
+      <c r="E263" s="68" t="s">
+        <v>562</v>
+      </c>
+      <c r="F263" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="G263" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H263" s="69">
+        <v>45924</v>
+      </c>
+      <c r="I263" s="69">
+        <v>46121</v>
+      </c>
+      <c r="J263" s="24">
+        <f t="shared" si="15"/>
+        <v>142</v>
+      </c>
+      <c r="K263" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="L263" s="68" t="s">
+        <v>327</v>
+      </c>
+      <c r="M263" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="N263" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="O263" s="68">
+        <v>200000</v>
+      </c>
+      <c r="P263" s="68">
+        <v>0</v>
+      </c>
+      <c r="Q263" s="70">
+        <v>200000</v>
+      </c>
+      <c r="R263" s="69">
+        <v>46121</v>
+      </c>
+      <c r="S263" s="24">
+        <f t="shared" si="16"/>
+        <v>142</v>
+      </c>
+      <c r="T263" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U263" s="68" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="264" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A264" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="B264" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="C264" s="68">
+        <v>54962571</v>
+      </c>
+      <c r="D264" s="68" t="s">
+        <v>50</v>
+      </c>
+      <c r="E264" s="68">
+        <v>2721711850</v>
+      </c>
+      <c r="F264" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G264" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H264" s="69">
+        <v>46002</v>
+      </c>
+      <c r="I264" s="69">
+        <v>46121</v>
+      </c>
+      <c r="J264" s="24">
+        <f t="shared" si="15"/>
+        <v>86</v>
+      </c>
+      <c r="K264" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="L264" s="68" t="s">
+        <v>327</v>
+      </c>
+      <c r="M264" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="N264" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="O264" s="68">
+        <v>400000</v>
+      </c>
+      <c r="P264" s="68">
+        <v>0</v>
+      </c>
+      <c r="Q264" s="70">
+        <v>400000</v>
+      </c>
+      <c r="R264" s="69">
+        <v>46121</v>
+      </c>
+      <c r="S264" s="24">
+        <f t="shared" si="16"/>
+        <v>86</v>
+      </c>
+      <c r="T264" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U264" s="68" t="s">
         <v>551</v>
       </c>
     </row>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="410" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E66CBA1-EEF6-42B4-A78B-8573D1ABD908}"/>
+  <xr:revisionPtr revIDLastSave="427" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1493915E-6C28-441F-85B0-61B6D13B85BF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2717" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2834" uniqueCount="582">
   <si>
     <t>Client</t>
   </si>
@@ -1731,10 +1731,61 @@
     <t>VPNLL120010</t>
   </si>
   <si>
-    <t>DES SOCIETES D'ASSURANCE COTE D'IVOIRE</t>
-  </si>
-  <si>
     <t>Projet DMO</t>
+  </si>
+  <si>
+    <t>DES SOCIETES D'ASSURANCE CI</t>
+  </si>
+  <si>
+    <t>47871834 </t>
+  </si>
+  <si>
+    <t>SYTHD240171</t>
+  </si>
+  <si>
+    <t>HUAWEI TECHNOLOGIE SAU</t>
+  </si>
+  <si>
+    <t>SYTHD260058</t>
+  </si>
+  <si>
+    <t>SYTHD260091</t>
+  </si>
+  <si>
+    <t>NPW FRESH &amp;DRY CI</t>
+  </si>
+  <si>
+    <t>SYTHD260087</t>
+  </si>
+  <si>
+    <t>TAABO LAMPTO</t>
+  </si>
+  <si>
+    <t>BUVPN250213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUVPN260076 </t>
+  </si>
+  <si>
+    <t>MEDLOG COTE D'IVOIRE </t>
+  </si>
+  <si>
+    <t>ZENITH BANK COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>PLATEAU  AU  7 em</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESIDENCE DE LA REPUBLIQUE </t>
+  </si>
+  <si>
+    <t>PLATEAU  AU  8 em</t>
+  </si>
+  <si>
+    <t>DDPE</t>
+  </si>
+  <si>
+    <t>S16</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +2010,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2150,6 +2201,9 @@
     </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3352,7 +3406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U264"/>
+  <dimension ref="A1:U274"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="26" customWidth="1"/>
@@ -16461,7 +16515,7 @@
         <v>46094</v>
       </c>
       <c r="J205" s="24">
-        <f t="shared" ref="J205:J264" si="15">+NETWORKDAYS(H205,I205)</f>
+        <f t="shared" ref="J205:J268" si="15">+NETWORKDAYS(H205,I205)</f>
         <v>18</v>
       </c>
       <c r="K205" s="12" t="s">
@@ -16489,7 +16543,7 @@
         <v>46094</v>
       </c>
       <c r="S205" s="24">
-        <f t="shared" ref="S205:S264" si="16">NETWORKDAYS(H205,R205)</f>
+        <f t="shared" ref="S205:S268" si="16">NETWORKDAYS(H205,R205)</f>
         <v>18</v>
       </c>
       <c r="T205" s="12" t="s">
@@ -20217,7 +20271,7 @@
         <v>552</v>
       </c>
       <c r="U260" s="68" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="261" spans="1:21" x14ac:dyDescent="0.35">
@@ -20284,7 +20338,7 @@
         <v>552</v>
       </c>
       <c r="U261" s="68" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="262" spans="1:21" x14ac:dyDescent="0.35">
@@ -20423,7 +20477,7 @@
     </row>
     <row r="264" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A264" s="12" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B264" s="68" t="s">
         <v>31</v>
@@ -20485,6 +20539,676 @@
         <v>552</v>
       </c>
       <c r="U264" s="68" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="265" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A265" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="B265" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C265" s="68" t="s">
+        <v>565</v>
+      </c>
+      <c r="D265" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="E265" s="68" t="s">
+        <v>566</v>
+      </c>
+      <c r="F265" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="G265" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H265" s="69">
+        <v>45861</v>
+      </c>
+      <c r="I265" s="69">
+        <v>46115</v>
+      </c>
+      <c r="J265" s="24">
+        <f t="shared" si="15"/>
+        <v>183</v>
+      </c>
+      <c r="K265" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="L265" s="68" t="s">
+        <v>327</v>
+      </c>
+      <c r="M265" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="N265" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="O265" s="68">
+        <v>1300000</v>
+      </c>
+      <c r="P265" s="68">
+        <v>0</v>
+      </c>
+      <c r="Q265" s="70">
+        <v>1300000</v>
+      </c>
+      <c r="R265" s="69">
+        <v>46125</v>
+      </c>
+      <c r="S265" s="24">
+        <f t="shared" si="16"/>
+        <v>189</v>
+      </c>
+      <c r="T265" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="U265" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="266" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A266" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="B266" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C266" s="68">
+        <v>57899728</v>
+      </c>
+      <c r="D266" s="68" t="s">
+        <v>68</v>
+      </c>
+      <c r="E266" s="68" t="s">
+        <v>568</v>
+      </c>
+      <c r="F266" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="G266" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H266" s="69">
+        <v>46059</v>
+      </c>
+      <c r="I266" s="69">
+        <v>46113</v>
+      </c>
+      <c r="J266" s="24">
+        <f t="shared" si="15"/>
+        <v>39</v>
+      </c>
+      <c r="K266" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="L266" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="M266" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="N266" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="O266" s="68">
+        <v>1002937</v>
+      </c>
+      <c r="P266" s="68">
+        <v>3582860</v>
+      </c>
+      <c r="Q266" s="70">
+        <v>4585797</v>
+      </c>
+      <c r="R266" s="69">
+        <v>46125</v>
+      </c>
+      <c r="S266" s="24">
+        <f t="shared" si="16"/>
+        <v>47</v>
+      </c>
+      <c r="T266" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="U266" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="267" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A267" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="B267" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C267" s="68">
+        <v>60573620</v>
+      </c>
+      <c r="D267" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="E267" s="68" t="s">
+        <v>569</v>
+      </c>
+      <c r="F267" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="G267" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H267" s="69">
+        <v>46107</v>
+      </c>
+      <c r="I267" s="69">
+        <v>46119</v>
+      </c>
+      <c r="J267" s="24">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="K267" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="L267" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="M267" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="N267" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="O267" s="68">
+        <v>802977</v>
+      </c>
+      <c r="P267" s="68">
+        <v>0</v>
+      </c>
+      <c r="Q267" s="70">
+        <v>802977</v>
+      </c>
+      <c r="R267" s="69">
+        <v>46125</v>
+      </c>
+      <c r="S267" s="24">
+        <f t="shared" si="16"/>
+        <v>13</v>
+      </c>
+      <c r="T267" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="U267" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="268" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A268" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="B268" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C268" s="68">
+        <v>54973689</v>
+      </c>
+      <c r="D268" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="E268" s="68" t="s">
+        <v>571</v>
+      </c>
+      <c r="F268" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="G268" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H268" s="69">
+        <v>46007</v>
+      </c>
+      <c r="I268" s="69">
+        <v>46120</v>
+      </c>
+      <c r="J268" s="24">
+        <f t="shared" si="15"/>
+        <v>82</v>
+      </c>
+      <c r="K268" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="L268" s="68" t="s">
+        <v>327</v>
+      </c>
+      <c r="M268" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="N268" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="O268" s="68">
+        <v>0</v>
+      </c>
+      <c r="P268" s="68">
+        <v>664528</v>
+      </c>
+      <c r="Q268" s="70">
+        <v>664528</v>
+      </c>
+      <c r="R268" s="69">
+        <v>46125</v>
+      </c>
+      <c r="S268" s="24">
+        <f t="shared" si="16"/>
+        <v>85</v>
+      </c>
+      <c r="T268" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="U268" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="269" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A269" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B269" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C269" s="68">
+        <v>61220151</v>
+      </c>
+      <c r="D269" s="68" t="s">
+        <v>572</v>
+      </c>
+      <c r="E269" s="68" t="s">
+        <v>573</v>
+      </c>
+      <c r="F269" s="68" t="s">
+        <v>196</v>
+      </c>
+      <c r="G269" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H269" s="69">
+        <v>46121</v>
+      </c>
+      <c r="I269" s="69">
+        <v>46122</v>
+      </c>
+      <c r="J269" s="24">
+        <f t="shared" ref="J269:J274" si="21">+NETWORKDAYS(H269,I269)</f>
+        <v>2</v>
+      </c>
+      <c r="K269" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="L269" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="M269" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="N269" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="O269" s="68">
+        <v>0</v>
+      </c>
+      <c r="P269" s="68">
+        <v>1069231</v>
+      </c>
+      <c r="Q269" s="70">
+        <v>1069231</v>
+      </c>
+      <c r="R269" s="69">
+        <v>46126</v>
+      </c>
+      <c r="S269" s="24">
+        <f t="shared" ref="S269:S274" si="22">NETWORKDAYS(H269,R269)</f>
+        <v>4</v>
+      </c>
+      <c r="T269" s="71" t="s">
+        <v>581</v>
+      </c>
+      <c r="U269" s="71" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="270" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A270" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B270" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C270" s="68">
+        <v>52448985</v>
+      </c>
+      <c r="D270" s="68" t="s">
+        <v>365</v>
+      </c>
+      <c r="E270" s="68" t="s">
+        <v>574</v>
+      </c>
+      <c r="F270" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="G270" s="68" t="s">
+        <v>38</v>
+      </c>
+      <c r="H270" s="69">
+        <v>45952</v>
+      </c>
+      <c r="I270" s="69">
+        <v>46121</v>
+      </c>
+      <c r="J270" s="24">
+        <f t="shared" si="21"/>
+        <v>122</v>
+      </c>
+      <c r="K270" s="68" t="s">
+        <v>353</v>
+      </c>
+      <c r="L270" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="M270" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="N270" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="O270" s="68">
+        <v>0</v>
+      </c>
+      <c r="P270" s="68">
+        <v>170681</v>
+      </c>
+      <c r="Q270" s="70">
+        <v>170681</v>
+      </c>
+      <c r="R270" s="69">
+        <v>46126</v>
+      </c>
+      <c r="S270" s="24">
+        <f t="shared" si="22"/>
+        <v>125</v>
+      </c>
+      <c r="T270" s="71" t="s">
+        <v>581</v>
+      </c>
+      <c r="U270" s="71" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="271" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A271" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="B271" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="C271" s="68">
+        <v>49471604</v>
+      </c>
+      <c r="D271" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="E271" s="68">
+        <v>2721216390</v>
+      </c>
+      <c r="F271" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G271" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H271" s="69">
+        <v>45894</v>
+      </c>
+      <c r="I271" s="69">
+        <v>46122</v>
+      </c>
+      <c r="J271" s="24">
+        <f t="shared" si="21"/>
+        <v>165</v>
+      </c>
+      <c r="K271" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="L271" s="68" t="s">
+        <v>327</v>
+      </c>
+      <c r="M271" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="N271" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="O271" s="68">
+        <v>144000</v>
+      </c>
+      <c r="P271" s="68">
+        <v>0</v>
+      </c>
+      <c r="Q271" s="70">
+        <v>144000</v>
+      </c>
+      <c r="R271" s="69">
+        <v>46126</v>
+      </c>
+      <c r="S271" s="24">
+        <f t="shared" si="22"/>
+        <v>167</v>
+      </c>
+      <c r="T271" s="71" t="s">
+        <v>581</v>
+      </c>
+      <c r="U271" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="272" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A272" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="B272" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="C272" s="68">
+        <v>58642079</v>
+      </c>
+      <c r="D272" s="68" t="s">
+        <v>577</v>
+      </c>
+      <c r="E272" s="68">
+        <v>2720218600</v>
+      </c>
+      <c r="F272" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G272" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H272" s="69">
+        <v>46073</v>
+      </c>
+      <c r="I272" s="69">
+        <v>46125</v>
+      </c>
+      <c r="J272" s="24">
+        <f t="shared" si="21"/>
+        <v>37</v>
+      </c>
+      <c r="K272" s="68" t="s">
+        <v>353</v>
+      </c>
+      <c r="L272" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="M272" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="N272" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="O272" s="68">
+        <v>1000000</v>
+      </c>
+      <c r="P272" s="68">
+        <v>231750</v>
+      </c>
+      <c r="Q272" s="70">
+        <v>1231750</v>
+      </c>
+      <c r="R272" s="69">
+        <v>46126</v>
+      </c>
+      <c r="S272" s="24">
+        <f t="shared" si="22"/>
+        <v>38</v>
+      </c>
+      <c r="T272" s="71" t="s">
+        <v>581</v>
+      </c>
+      <c r="U272" s="71" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="273" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A273" s="12" t="s">
+        <v>578</v>
+      </c>
+      <c r="B273" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="C273" s="68">
+        <v>60612374</v>
+      </c>
+      <c r="D273" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="E273" s="68">
+        <v>2720238655</v>
+      </c>
+      <c r="F273" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G273" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H273" s="69">
+        <v>46108</v>
+      </c>
+      <c r="I273" s="69">
+        <v>46119</v>
+      </c>
+      <c r="J273" s="24">
+        <f t="shared" si="21"/>
+        <v>8</v>
+      </c>
+      <c r="K273" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="L273" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="M273" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="N273" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="O273" s="68">
+        <v>150000</v>
+      </c>
+      <c r="P273" s="68">
+        <v>40000</v>
+      </c>
+      <c r="Q273" s="70">
+        <v>190000</v>
+      </c>
+      <c r="R273" s="69">
+        <v>46126</v>
+      </c>
+      <c r="S273" s="24">
+        <f t="shared" si="22"/>
+        <v>13</v>
+      </c>
+      <c r="T273" s="71" t="s">
+        <v>581</v>
+      </c>
+      <c r="U273" s="71" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="274" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A274" s="12" t="s">
+        <v>578</v>
+      </c>
+      <c r="B274" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="C274" s="68">
+        <v>60611946</v>
+      </c>
+      <c r="D274" s="68" t="s">
+        <v>579</v>
+      </c>
+      <c r="E274" s="68">
+        <v>2720238660</v>
+      </c>
+      <c r="F274" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G274" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H274" s="69">
+        <v>46108</v>
+      </c>
+      <c r="I274" s="69">
+        <v>46120</v>
+      </c>
+      <c r="J274" s="24">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="K274" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="L274" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="M274" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="N274" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="O274" s="68">
+        <v>150000</v>
+      </c>
+      <c r="P274" s="68">
+        <v>40000</v>
+      </c>
+      <c r="Q274" s="70">
+        <v>190000</v>
+      </c>
+      <c r="R274" s="69">
+        <v>46126</v>
+      </c>
+      <c r="S274" s="24">
+        <f t="shared" si="22"/>
+        <v>13</v>
+      </c>
+      <c r="T274" s="71" t="s">
+        <v>581</v>
+      </c>
+      <c r="U274" s="71" t="s">
         <v>551</v>
       </c>
     </row>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="427" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1493915E-6C28-441F-85B0-61B6D13B85BF}"/>
+  <xr:revisionPtr revIDLastSave="442" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F63BE28-16F5-4DEF-B4FD-5385D23AEE1E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2834" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2987" uniqueCount="602">
   <si>
     <t>Client</t>
   </si>
@@ -1786,6 +1786,66 @@
   </si>
   <si>
     <t>S16</t>
+  </si>
+  <si>
+    <t>DGI</t>
+  </si>
+  <si>
+    <t>BUVPN260079</t>
+  </si>
+  <si>
+    <t>DALOA</t>
+  </si>
+  <si>
+    <t>BUVPN260068</t>
+  </si>
+  <si>
+    <t>KATIOLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUVPN260013 </t>
+  </si>
+  <si>
+    <t>BUVPN260067</t>
+  </si>
+  <si>
+    <t>SYTHD250350</t>
+  </si>
+  <si>
+    <t>SYTHD260092</t>
+  </si>
+  <si>
+    <t>SYTHD260066</t>
+  </si>
+  <si>
+    <t>PORT BOUET&gt;&gt;&gt;BKE</t>
+  </si>
+  <si>
+    <t>SYTHD250400</t>
+  </si>
+  <si>
+    <t>ABJ&gt;&gt;&gt;&gt;KONG</t>
+  </si>
+  <si>
+    <t>SYTHD250406</t>
+  </si>
+  <si>
+    <t>OPERATION DE TRANSIT ET DE LOGISTIQUE(OTL)</t>
+  </si>
+  <si>
+    <t>SYTHD260103</t>
+  </si>
+  <si>
+    <t>OQSF-CI / COCODY</t>
+  </si>
+  <si>
+    <t>ARABIAN CONSTRUCTION COMPANY</t>
+  </si>
+  <si>
+    <t>YESHI GROUPE COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>Projet OCI</t>
   </si>
 </sst>
 </file>
@@ -1799,7 +1859,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,##0\ _€"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1894,6 +1954,12 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2010,7 +2076,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2203,6 +2269,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3406,7 +3496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U274"/>
+  <dimension ref="A1:U287"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="26" customWidth="1"/>
@@ -20839,7 +20929,7 @@
         <v>46122</v>
       </c>
       <c r="J269" s="24">
-        <f t="shared" ref="J269:J274" si="21">+NETWORKDAYS(H269,I269)</f>
+        <f t="shared" ref="J269:J287" si="21">+NETWORKDAYS(H269,I269)</f>
         <v>2</v>
       </c>
       <c r="K269" s="68" t="s">
@@ -20867,7 +20957,7 @@
         <v>46126</v>
       </c>
       <c r="S269" s="24">
-        <f t="shared" ref="S269:S274" si="22">NETWORKDAYS(H269,R269)</f>
+        <f t="shared" ref="S269:S287" si="22">NETWORKDAYS(H269,R269)</f>
         <v>4</v>
       </c>
       <c r="T269" s="71" t="s">
@@ -21209,6 +21299,890 @@
         <v>581</v>
       </c>
       <c r="U274" s="71" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="275" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A275" s="12" t="s">
+        <v>582</v>
+      </c>
+      <c r="B275" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C275" s="68">
+        <v>60410207</v>
+      </c>
+      <c r="D275" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="E275" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="F275" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="G275" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H275" s="69">
+        <v>46105</v>
+      </c>
+      <c r="I275" s="69">
+        <v>46127</v>
+      </c>
+      <c r="J275" s="24">
+        <f t="shared" si="21"/>
+        <v>17</v>
+      </c>
+      <c r="K275" s="72" t="s">
+        <v>303</v>
+      </c>
+      <c r="L275" s="73" t="s">
+        <v>304</v>
+      </c>
+      <c r="M275" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="N275" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="O275" s="70">
+        <v>2987707</v>
+      </c>
+      <c r="P275" s="70">
+        <v>2031900</v>
+      </c>
+      <c r="Q275" s="46">
+        <f t="shared" ref="Q275:Q279" si="23">P275+O275</f>
+        <v>5019607</v>
+      </c>
+      <c r="R275" s="74">
+        <v>46128</v>
+      </c>
+      <c r="S275" s="24">
+        <f t="shared" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="T275" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="U275" s="68" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="276" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A276" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="B276" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C276" s="68">
+        <v>58889883</v>
+      </c>
+      <c r="D276" s="68" t="s">
+        <v>584</v>
+      </c>
+      <c r="E276" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="F276" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="G276" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="H276" s="69">
+        <v>46077</v>
+      </c>
+      <c r="I276" s="69">
+        <v>46127</v>
+      </c>
+      <c r="J276" s="24">
+        <f t="shared" si="21"/>
+        <v>37</v>
+      </c>
+      <c r="K276" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L276" s="71" t="s">
+        <v>304</v>
+      </c>
+      <c r="M276" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="N276" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="O276" s="70">
+        <v>0</v>
+      </c>
+      <c r="P276" s="70">
+        <v>0</v>
+      </c>
+      <c r="Q276" s="76">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="R276" s="77">
+        <v>46128</v>
+      </c>
+      <c r="S276" s="24">
+        <f t="shared" si="22"/>
+        <v>38</v>
+      </c>
+      <c r="T276" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="U276" s="68" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="277" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A277" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B277" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C277" s="68">
+        <v>56613961</v>
+      </c>
+      <c r="D277" s="68" t="s">
+        <v>586</v>
+      </c>
+      <c r="E277" s="68" t="s">
+        <v>587</v>
+      </c>
+      <c r="F277" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="G277" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H277" s="69">
+        <v>46035</v>
+      </c>
+      <c r="I277" s="69">
+        <v>46128</v>
+      </c>
+      <c r="J277" s="24">
+        <f t="shared" si="21"/>
+        <v>68</v>
+      </c>
+      <c r="K277" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L277" s="71" t="s">
+        <v>304</v>
+      </c>
+      <c r="M277" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="N277" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="O277" s="70">
+        <v>2000000</v>
+      </c>
+      <c r="P277" s="70">
+        <v>300000</v>
+      </c>
+      <c r="Q277" s="76">
+        <f t="shared" si="23"/>
+        <v>2300000</v>
+      </c>
+      <c r="R277" s="77">
+        <v>46128</v>
+      </c>
+      <c r="S277" s="24">
+        <f t="shared" si="22"/>
+        <v>68</v>
+      </c>
+      <c r="T277" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="U277" s="68" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="278" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A278" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="B278" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C278" s="68">
+        <v>58868860</v>
+      </c>
+      <c r="D278" s="68" t="s">
+        <v>138</v>
+      </c>
+      <c r="E278" s="68" t="s">
+        <v>588</v>
+      </c>
+      <c r="F278" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="G278" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="H278" s="69">
+        <v>46077</v>
+      </c>
+      <c r="I278" s="69">
+        <v>46128</v>
+      </c>
+      <c r="J278" s="24">
+        <f t="shared" si="21"/>
+        <v>38</v>
+      </c>
+      <c r="K278" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L278" s="71" t="s">
+        <v>304</v>
+      </c>
+      <c r="M278" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="N278" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="O278" s="70">
+        <v>0</v>
+      </c>
+      <c r="P278" s="70">
+        <v>0</v>
+      </c>
+      <c r="Q278" s="76">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="R278" s="77">
+        <v>46128</v>
+      </c>
+      <c r="S278" s="24">
+        <f t="shared" si="22"/>
+        <v>38</v>
+      </c>
+      <c r="T278" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="U278" s="68" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="279" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A279" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B279" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C279" s="68">
+        <v>52561795</v>
+      </c>
+      <c r="D279" s="68" t="s">
+        <v>365</v>
+      </c>
+      <c r="E279" s="68" t="s">
+        <v>589</v>
+      </c>
+      <c r="F279" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="G279" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="H279" s="69">
+        <v>45957</v>
+      </c>
+      <c r="I279" s="69">
+        <v>45985</v>
+      </c>
+      <c r="J279" s="24">
+        <f t="shared" si="21"/>
+        <v>21</v>
+      </c>
+      <c r="K279" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L279" s="71" t="s">
+        <v>304</v>
+      </c>
+      <c r="M279" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="N279" s="71" t="s">
+        <v>94</v>
+      </c>
+      <c r="O279" s="78">
+        <v>0</v>
+      </c>
+      <c r="P279" s="78">
+        <v>725636</v>
+      </c>
+      <c r="Q279" s="76">
+        <f t="shared" si="23"/>
+        <v>725636</v>
+      </c>
+      <c r="R279" s="77">
+        <v>46128</v>
+      </c>
+      <c r="S279" s="24">
+        <f t="shared" si="22"/>
+        <v>124</v>
+      </c>
+      <c r="T279" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="U279" s="68" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="280" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A280" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B280" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C280" s="68">
+        <v>52561777</v>
+      </c>
+      <c r="D280" s="68" t="s">
+        <v>365</v>
+      </c>
+      <c r="E280" s="68" t="s">
+        <v>590</v>
+      </c>
+      <c r="F280" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="G280" s="68" t="s">
+        <v>38</v>
+      </c>
+      <c r="H280" s="69">
+        <v>45957</v>
+      </c>
+      <c r="I280" s="69">
+        <v>46121</v>
+      </c>
+      <c r="J280" s="24">
+        <f t="shared" si="21"/>
+        <v>119</v>
+      </c>
+      <c r="K280" s="75" t="s">
+        <v>353</v>
+      </c>
+      <c r="L280" s="71" t="s">
+        <v>580</v>
+      </c>
+      <c r="M280" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="N280" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="O280" s="70">
+        <v>0</v>
+      </c>
+      <c r="P280" s="70">
+        <v>217691</v>
+      </c>
+      <c r="Q280" s="76">
+        <f>P280+O280</f>
+        <v>217691</v>
+      </c>
+      <c r="R280" s="77">
+        <v>46128</v>
+      </c>
+      <c r="S280" s="24">
+        <f t="shared" si="22"/>
+        <v>124</v>
+      </c>
+      <c r="T280" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="U280" s="68" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="281" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A281" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B281" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C281" s="68">
+        <v>54967903</v>
+      </c>
+      <c r="D281" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="E281" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="F281" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="G281" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H281" s="69">
+        <v>46002</v>
+      </c>
+      <c r="I281" s="69">
+        <v>46083</v>
+      </c>
+      <c r="J281" s="24">
+        <f t="shared" si="21"/>
+        <v>58</v>
+      </c>
+      <c r="K281" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L281" s="71" t="s">
+        <v>327</v>
+      </c>
+      <c r="M281" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="N281" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="O281" s="70">
+        <v>1000000</v>
+      </c>
+      <c r="P281" s="70">
+        <v>2200000</v>
+      </c>
+      <c r="Q281" s="76">
+        <f t="shared" ref="Q281:Q287" si="24">P281+O281</f>
+        <v>3200000</v>
+      </c>
+      <c r="R281" s="77">
+        <v>46129</v>
+      </c>
+      <c r="S281" s="24">
+        <f t="shared" si="22"/>
+        <v>92</v>
+      </c>
+      <c r="T281" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="U281" s="68" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="282" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A282" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B282" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C282" s="68">
+        <v>54970719</v>
+      </c>
+      <c r="D282" s="68" t="s">
+        <v>592</v>
+      </c>
+      <c r="E282" s="68" t="s">
+        <v>593</v>
+      </c>
+      <c r="F282" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="G282" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H282" s="69">
+        <v>46002</v>
+      </c>
+      <c r="I282" s="69">
+        <v>46027</v>
+      </c>
+      <c r="J282" s="24">
+        <f t="shared" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="K282" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L282" s="71" t="s">
+        <v>304</v>
+      </c>
+      <c r="M282" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="N282" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="O282" s="70">
+        <v>1000000</v>
+      </c>
+      <c r="P282" s="70">
+        <v>2200000</v>
+      </c>
+      <c r="Q282" s="76">
+        <f t="shared" si="24"/>
+        <v>3200000</v>
+      </c>
+      <c r="R282" s="77">
+        <v>46129</v>
+      </c>
+      <c r="S282" s="24">
+        <f t="shared" si="22"/>
+        <v>92</v>
+      </c>
+      <c r="T282" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="U282" s="68" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="283" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A283" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B283" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C283" s="68">
+        <v>55105103</v>
+      </c>
+      <c r="D283" s="68" t="s">
+        <v>594</v>
+      </c>
+      <c r="E283" s="68" t="s">
+        <v>595</v>
+      </c>
+      <c r="F283" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="G283" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H283" s="69">
+        <v>46004</v>
+      </c>
+      <c r="I283" s="69">
+        <v>46041</v>
+      </c>
+      <c r="J283" s="24">
+        <f t="shared" si="21"/>
+        <v>26</v>
+      </c>
+      <c r="K283" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L283" s="71" t="s">
+        <v>304</v>
+      </c>
+      <c r="M283" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="N283" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="O283" s="70">
+        <v>1500000</v>
+      </c>
+      <c r="P283" s="70">
+        <v>1700000</v>
+      </c>
+      <c r="Q283" s="76">
+        <f t="shared" si="24"/>
+        <v>3200000</v>
+      </c>
+      <c r="R283" s="77">
+        <v>46129</v>
+      </c>
+      <c r="S283" s="24">
+        <f t="shared" si="22"/>
+        <v>90</v>
+      </c>
+      <c r="T283" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="U283" s="68" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="284" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A284" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="B284" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C284" s="68">
+        <v>58151683</v>
+      </c>
+      <c r="D284" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="E284" s="68" t="s">
+        <v>597</v>
+      </c>
+      <c r="F284" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="G284" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H284" s="69">
+        <v>46064</v>
+      </c>
+      <c r="I284" s="69">
+        <v>46129</v>
+      </c>
+      <c r="J284" s="24">
+        <f t="shared" si="21"/>
+        <v>48</v>
+      </c>
+      <c r="K284" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L284" s="71" t="s">
+        <v>327</v>
+      </c>
+      <c r="M284" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="N284" s="68" t="s">
+        <v>29</v>
+      </c>
+      <c r="O284" s="70">
+        <v>1495565</v>
+      </c>
+      <c r="P284" s="70">
+        <v>837054</v>
+      </c>
+      <c r="Q284" s="76">
+        <f t="shared" si="24"/>
+        <v>2332619</v>
+      </c>
+      <c r="R284" s="77">
+        <v>46129</v>
+      </c>
+      <c r="S284" s="24">
+        <f t="shared" si="22"/>
+        <v>48</v>
+      </c>
+      <c r="T284" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="U284" s="68" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="285" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A285" s="12" t="s">
+        <v>598</v>
+      </c>
+      <c r="B285" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="C285" s="68">
+        <v>60868549</v>
+      </c>
+      <c r="D285" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="E285" s="68">
+        <v>2722520145</v>
+      </c>
+      <c r="F285" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G285" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H285" s="69">
+        <v>46113</v>
+      </c>
+      <c r="I285" s="69">
+        <v>46129</v>
+      </c>
+      <c r="J285" s="24">
+        <f t="shared" si="21"/>
+        <v>13</v>
+      </c>
+      <c r="K285" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L285" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M285" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N285" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O285" s="79">
+        <v>150000</v>
+      </c>
+      <c r="P285" s="79">
+        <v>40000</v>
+      </c>
+      <c r="Q285" s="46">
+        <f t="shared" si="24"/>
+        <v>190000</v>
+      </c>
+      <c r="R285" s="13">
+        <v>46129</v>
+      </c>
+      <c r="S285" s="24">
+        <f t="shared" si="22"/>
+        <v>13</v>
+      </c>
+      <c r="T285" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="U285" s="68" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="286" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A286" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="B286" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="C286" s="68">
+        <v>60395491</v>
+      </c>
+      <c r="D286" s="68" t="s">
+        <v>50</v>
+      </c>
+      <c r="E286" s="68">
+        <v>2721712025</v>
+      </c>
+      <c r="F286" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G286" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H286" s="69">
+        <v>46105</v>
+      </c>
+      <c r="I286" s="69">
+        <v>46129</v>
+      </c>
+      <c r="J286" s="24">
+        <f t="shared" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="K286" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L286" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M286" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N286" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O286" s="79">
+        <v>150000</v>
+      </c>
+      <c r="P286" s="79">
+        <v>40000</v>
+      </c>
+      <c r="Q286" s="46">
+        <f t="shared" si="24"/>
+        <v>190000</v>
+      </c>
+      <c r="R286" s="13">
+        <v>46129</v>
+      </c>
+      <c r="S286" s="24">
+        <f t="shared" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="T286" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="U286" s="68" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="287" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A287" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="B287" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="C287" s="68">
+        <v>60472385</v>
+      </c>
+      <c r="D287" s="68" t="s">
+        <v>50</v>
+      </c>
+      <c r="E287" s="68">
+        <v>2721250000</v>
+      </c>
+      <c r="F287" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G287" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="H287" s="69">
+        <v>46106</v>
+      </c>
+      <c r="I287" s="69">
+        <v>46122</v>
+      </c>
+      <c r="J287" s="24">
+        <f t="shared" si="21"/>
+        <v>13</v>
+      </c>
+      <c r="K287" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L287" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M287" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N287" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O287" s="79">
+        <v>150000</v>
+      </c>
+      <c r="P287" s="79">
+        <v>60000</v>
+      </c>
+      <c r="Q287" s="46">
+        <f t="shared" si="24"/>
+        <v>210000</v>
+      </c>
+      <c r="R287" s="13">
+        <v>46129</v>
+      </c>
+      <c r="S287" s="24">
+        <f t="shared" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="T287" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="U287" s="68" t="s">
         <v>551</v>
       </c>
     </row>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="442" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F63BE28-16F5-4DEF-B4FD-5385D23AEE1E}"/>
+  <xr:revisionPtr revIDLastSave="469" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04A9FC10-F90C-4614-803C-D886E2A1C84B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$295</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2987" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3082" uniqueCount="618">
   <si>
     <t>Client</t>
   </si>
@@ -1846,6 +1846,54 @@
   </si>
   <si>
     <t>Projet OCI</t>
+  </si>
+  <si>
+    <t>PROJET POLE AGRO INDUSTRIEL DANS LE NORD</t>
+  </si>
+  <si>
+    <t>SYTHD260095</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>SONATEL</t>
+  </si>
+  <si>
+    <t>SYTHD260049</t>
+  </si>
+  <si>
+    <t>PLATEAU&gt;&gt;&gt;&gt;DAKAR</t>
+  </si>
+  <si>
+    <t>SYTHD260072</t>
+  </si>
+  <si>
+    <t>SODEXAM STATION MÉTÉO</t>
+  </si>
+  <si>
+    <t>DIMBOKRO</t>
+  </si>
+  <si>
+    <t>SYTHD260106</t>
+  </si>
+  <si>
+    <t>SODEXAM  STATION METEOROLOGIQUE</t>
+  </si>
+  <si>
+    <t>ADIAKE</t>
+  </si>
+  <si>
+    <t>SYTHD260105</t>
+  </si>
+  <si>
+    <t>SYTHD260096</t>
+  </si>
+  <si>
+    <t>BUVPN200157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTITUT CARDIOLOGIE </t>
   </si>
 </sst>
 </file>
@@ -2301,7 +2349,877 @@
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="86">
+  <dxfs count="173">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3496,7 +4414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U287"/>
+  <dimension ref="A1:U295"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="26" customWidth="1"/>
@@ -20929,7 +21847,7 @@
         <v>46122</v>
       </c>
       <c r="J269" s="24">
-        <f t="shared" ref="J269:J287" si="21">+NETWORKDAYS(H269,I269)</f>
+        <f t="shared" ref="J269:J295" si="21">+NETWORKDAYS(H269,I269)</f>
         <v>2</v>
       </c>
       <c r="K269" s="68" t="s">
@@ -20957,7 +21875,7 @@
         <v>46126</v>
       </c>
       <c r="S269" s="24">
-        <f t="shared" ref="S269:S287" si="22">NETWORKDAYS(H269,R269)</f>
+        <f t="shared" ref="S269:S295" si="22">NETWORKDAYS(H269,R269)</f>
         <v>4</v>
       </c>
       <c r="T269" s="71" t="s">
@@ -22186,227 +23104,774 @@
         <v>551</v>
       </c>
     </row>
+    <row r="288" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A288" s="12" t="s">
+        <v>602</v>
+      </c>
+      <c r="B288" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C288" s="12">
+        <v>60416636</v>
+      </c>
+      <c r="D288" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="E288" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="F288" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G288" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H288" s="14">
+        <v>46105</v>
+      </c>
+      <c r="I288" s="14">
+        <v>46129</v>
+      </c>
+      <c r="J288" s="24">
+        <f t="shared" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="K288" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L288" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M288" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N288" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="O288" s="19">
+        <v>500000</v>
+      </c>
+      <c r="P288" s="19">
+        <v>356222</v>
+      </c>
+      <c r="Q288" s="46">
+        <f>P288+O288</f>
+        <v>856222</v>
+      </c>
+      <c r="R288" s="13">
+        <v>46132</v>
+      </c>
+      <c r="S288" s="24">
+        <f t="shared" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="T288" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="U288" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="289" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A289" s="12" t="s">
+        <v>605</v>
+      </c>
+      <c r="B289" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C289" s="12">
+        <v>57849095</v>
+      </c>
+      <c r="D289" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E289" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="F289" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G289" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H289" s="14">
+        <v>46062</v>
+      </c>
+      <c r="I289" s="14">
+        <v>46105</v>
+      </c>
+      <c r="J289" s="24">
+        <f t="shared" si="21"/>
+        <v>32</v>
+      </c>
+      <c r="K289" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L289" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M289" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N289" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="O289" s="46">
+        <v>0</v>
+      </c>
+      <c r="P289" s="46">
+        <v>0</v>
+      </c>
+      <c r="Q289" s="46">
+        <f>P289+O289</f>
+        <v>0</v>
+      </c>
+      <c r="R289" s="13">
+        <v>46132</v>
+      </c>
+      <c r="S289" s="24">
+        <f t="shared" si="22"/>
+        <v>51</v>
+      </c>
+      <c r="T289" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="U289" s="11" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="290" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A290" s="12" t="s">
+        <v>605</v>
+      </c>
+      <c r="B290" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C290" s="12">
+        <v>57692887</v>
+      </c>
+      <c r="D290" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="E290" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="F290" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G290" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H290" s="14">
+        <v>46057</v>
+      </c>
+      <c r="I290" s="14">
+        <v>46098</v>
+      </c>
+      <c r="J290" s="24">
+        <f t="shared" si="21"/>
+        <v>30</v>
+      </c>
+      <c r="K290" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L290" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M290" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N290" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="O290" s="46">
+        <v>0</v>
+      </c>
+      <c r="P290" s="46">
+        <v>0</v>
+      </c>
+      <c r="Q290" s="46">
+        <f>P290+O290</f>
+        <v>0</v>
+      </c>
+      <c r="R290" s="13">
+        <v>46132</v>
+      </c>
+      <c r="S290" s="24">
+        <f t="shared" si="22"/>
+        <v>54</v>
+      </c>
+      <c r="T290" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="U290" s="11" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="291" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A291" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="B291" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C291" s="12">
+        <v>61552809</v>
+      </c>
+      <c r="D291" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="E291" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="F291" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G291" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H291" s="14">
+        <v>46126</v>
+      </c>
+      <c r="I291" s="14">
+        <v>46132</v>
+      </c>
+      <c r="J291" s="24">
+        <f t="shared" si="21"/>
+        <v>5</v>
+      </c>
+      <c r="K291" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L291" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M291" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N291" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="O291" s="19">
+        <v>755590</v>
+      </c>
+      <c r="P291" s="19">
+        <v>474962</v>
+      </c>
+      <c r="Q291" s="46">
+        <f>P291+O291</f>
+        <v>1230552</v>
+      </c>
+      <c r="R291" s="13">
+        <v>46132</v>
+      </c>
+      <c r="S291" s="24">
+        <f t="shared" si="22"/>
+        <v>5</v>
+      </c>
+      <c r="T291" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="U291" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="292" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A292" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="B292" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C292" s="12">
+        <v>61506362</v>
+      </c>
+      <c r="D292" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="E292" s="12" t="s">
+        <v>614</v>
+      </c>
+      <c r="F292" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G292" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H292" s="14">
+        <v>46125</v>
+      </c>
+      <c r="I292" s="14">
+        <v>46129</v>
+      </c>
+      <c r="J292" s="24">
+        <f t="shared" si="21"/>
+        <v>5</v>
+      </c>
+      <c r="K292" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L292" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M292" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N292" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="O292" s="19">
+        <v>1218934</v>
+      </c>
+      <c r="P292" s="19">
+        <v>474962</v>
+      </c>
+      <c r="Q292" s="46">
+        <f>P292+O292</f>
+        <v>1693896</v>
+      </c>
+      <c r="R292" s="13">
+        <v>46133</v>
+      </c>
+      <c r="S292" s="24">
+        <f t="shared" si="22"/>
+        <v>7</v>
+      </c>
+      <c r="T292" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="U292" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="293" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A293" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B293" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C293" s="12">
+        <v>60399905</v>
+      </c>
+      <c r="D293" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="E293" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="F293" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G293" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H293" s="14">
+        <v>46105</v>
+      </c>
+      <c r="I293" s="14">
+        <v>46129</v>
+      </c>
+      <c r="J293" s="24">
+        <f t="shared" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="K293" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L293" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M293" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N293" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="O293" s="19">
+        <v>1000000</v>
+      </c>
+      <c r="P293" s="19">
+        <v>460000</v>
+      </c>
+      <c r="Q293" s="46">
+        <f>P293+O293</f>
+        <v>1460000</v>
+      </c>
+      <c r="R293" s="13">
+        <v>46133</v>
+      </c>
+      <c r="S293" s="24">
+        <f t="shared" si="22"/>
+        <v>21</v>
+      </c>
+      <c r="T293" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="U293" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="294" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A294" s="11" t="s">
+        <v>549</v>
+      </c>
+      <c r="B294" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C294" s="12">
+        <v>44431296</v>
+      </c>
+      <c r="D294" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="E294" s="12" t="s">
+        <v>616</v>
+      </c>
+      <c r="F294" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G294" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H294" s="14">
+        <v>45786</v>
+      </c>
+      <c r="I294" s="13">
+        <v>46133</v>
+      </c>
+      <c r="J294" s="24">
+        <f t="shared" si="21"/>
+        <v>248</v>
+      </c>
+      <c r="K294" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L294" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="M294" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N294" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="O294" s="46">
+        <v>700000</v>
+      </c>
+      <c r="P294" s="46">
+        <v>0</v>
+      </c>
+      <c r="Q294" s="46">
+        <f>P294+O294</f>
+        <v>700000</v>
+      </c>
+      <c r="R294" s="13">
+        <v>46133</v>
+      </c>
+      <c r="S294" s="24">
+        <f t="shared" si="22"/>
+        <v>248</v>
+      </c>
+      <c r="T294" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="U294" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="295" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A295" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="B295" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C295" s="5">
+        <v>60190035</v>
+      </c>
+      <c r="D295" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E295" s="5">
+        <v>2731640000</v>
+      </c>
+      <c r="F295" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G295" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H295" s="13">
+        <v>46100</v>
+      </c>
+      <c r="I295" s="13">
+        <v>46133</v>
+      </c>
+      <c r="J295" s="24">
+        <f t="shared" si="21"/>
+        <v>24</v>
+      </c>
+      <c r="K295" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="L295" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M295" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N295" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="O295" s="46">
+        <v>1000000</v>
+      </c>
+      <c r="P295" s="46">
+        <v>231750</v>
+      </c>
+      <c r="Q295" s="46">
+        <f>P295+O295</f>
+        <v>1231750</v>
+      </c>
+      <c r="R295" s="13">
+        <v>46134</v>
+      </c>
+      <c r="S295" s="24">
+        <f t="shared" si="22"/>
+        <v>25</v>
+      </c>
+      <c r="T295" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="U295" s="11" t="s">
+        <v>551</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U259" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U295" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="85" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C205 C244:C1048576">
-    <cfRule type="duplicateValues" dxfId="79" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="103"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C212 C244:C1048576">
-    <cfRule type="duplicateValues" dxfId="77" priority="110"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C232 C244:C1048576">
-    <cfRule type="duplicateValues" dxfId="76" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="75" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C58">
+    <cfRule type="duplicateValues" dxfId="78" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C70">
+    <cfRule type="duplicateValues" dxfId="76" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="duplicateValues" dxfId="75" priority="58"/>
     <cfRule type="duplicateValues" dxfId="74" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="73" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="71" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="70" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="58"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="68" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="67" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="66" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="65" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="64" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="63" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="62" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="61" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="60" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="59" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="58" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="57" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="56" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="55" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="54" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="53" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
-    <cfRule type="duplicateValues" dxfId="52" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="51" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="50" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="48" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="47" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="46" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="45" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="44" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="42" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C114">
-    <cfRule type="duplicateValues" dxfId="41" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="40" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C157:C160">
-    <cfRule type="duplicateValues" dxfId="37" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C161:C163">
-    <cfRule type="duplicateValues" dxfId="36" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="35" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="33" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C168">
-    <cfRule type="duplicateValues" dxfId="31" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="30" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171">
-    <cfRule type="duplicateValues" dxfId="29" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173">
-    <cfRule type="duplicateValues" dxfId="28" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="26" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C175">
-    <cfRule type="duplicateValues" dxfId="25" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="24" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C178">
-    <cfRule type="duplicateValues" dxfId="23" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179">
-    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C206:C212">
-    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
-    <cfRule type="duplicateValues" dxfId="19" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C208">
-    <cfRule type="duplicateValues" dxfId="17" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218:C223">
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C225:C232">
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C233:C243">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="12" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="10" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="9" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="8" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="7" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="6" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="5" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="4" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="3" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172">
-    <cfRule type="duplicateValues" dxfId="2" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175">
-    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E243">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C205 C244:C287 C296:C1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="117"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C212 C244:C287 C296:C1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="126"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C232 C244:C287 C296:C1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="131"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C294 C296:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="499" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BBB57C9-8C54-4137-B34A-1CF9AD56FF7C}"/>
+  <xr:revisionPtr revIDLastSave="528" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19EBB1A3-DBBF-494C-B3BA-61AFA3BDC228}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$327</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3175" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3460" uniqueCount="665">
   <si>
     <t>Client</t>
   </si>
@@ -1930,6 +1930,111 @@
   </si>
   <si>
     <t xml:space="preserve">T2 BACK UP CNPS </t>
+  </si>
+  <si>
+    <t>BUVPN260073</t>
+  </si>
+  <si>
+    <t>BUVPN260072</t>
+  </si>
+  <si>
+    <t>BUVPN260069</t>
+  </si>
+  <si>
+    <t>SYTHD260120</t>
+  </si>
+  <si>
+    <t>DEMANDE_LIGNE_SFA</t>
+  </si>
+  <si>
+    <t>BUVPN260087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORABANK </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CNPS </t>
+  </si>
+  <si>
+    <t>SYTHD260108</t>
+  </si>
+  <si>
+    <t>CRC CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYTHD260104 </t>
+  </si>
+  <si>
+    <t>SODEXAM  STATION MÉTÉO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  AFG BANK</t>
+  </si>
+  <si>
+    <t>SYTHD250359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUVPN260038 </t>
+  </si>
+  <si>
+    <t>BUVPN260041</t>
+  </si>
+  <si>
+    <t>BUVPN260042</t>
+  </si>
+  <si>
+    <t>BUVPN260081</t>
+  </si>
+  <si>
+    <t>BUVPN260074</t>
+  </si>
+  <si>
+    <t>BUVPN260039</t>
+  </si>
+  <si>
+    <t>SYTHD260094</t>
+  </si>
+  <si>
+    <t>ZENITH BANK CI</t>
+  </si>
+  <si>
+    <t>SYTHD260111</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ODIENNE</t>
+  </si>
+  <si>
+    <t>SYTHD260112</t>
+  </si>
+  <si>
+    <t>BUVPN190174</t>
+  </si>
+  <si>
+    <t>SYTHD260121</t>
+  </si>
+  <si>
+    <t>SYTHD260114</t>
+  </si>
+  <si>
+    <t>MANCALA</t>
+  </si>
+  <si>
+    <t>SYTHD260117</t>
+  </si>
+  <si>
+    <t>DEUX PLATEAUX</t>
+  </si>
+  <si>
+    <t>SGCI</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projet </t>
+  </si>
+  <si>
+    <t>Projet Interne</t>
   </si>
 </sst>
 </file>
@@ -2132,7 +2237,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2338,863 +2443,25 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="175">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="90">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4429,7 +3696,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U303"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:U327"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="20" customWidth="1"/>
@@ -4514,7 +3782,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="42" t="s">
         <v>154</v>
       </c>
@@ -4576,7 +3844,7 @@
       </c>
       <c r="U2" s="49"/>
     </row>
-    <row r="3" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>159</v>
       </c>
@@ -4638,7 +3906,7 @@
       </c>
       <c r="U3" s="49"/>
     </row>
-    <row r="4" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>154</v>
       </c>
@@ -4700,7 +3968,7 @@
       </c>
       <c r="U4" s="49"/>
     </row>
-    <row r="5" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>154</v>
       </c>
@@ -4762,7 +4030,7 @@
       </c>
       <c r="U5" s="49"/>
     </row>
-    <row r="6" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>164</v>
       </c>
@@ -4824,7 +4092,7 @@
       </c>
       <c r="U6" s="49"/>
     </row>
-    <row r="7" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>165</v>
       </c>
@@ -4886,7 +4154,7 @@
       </c>
       <c r="U7" s="49"/>
     </row>
-    <row r="8" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>166</v>
       </c>
@@ -4948,7 +4216,7 @@
       </c>
       <c r="U8" s="49"/>
     </row>
-    <row r="9" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>169</v>
       </c>
@@ -5010,7 +4278,7 @@
       </c>
       <c r="U9" s="49"/>
     </row>
-    <row r="10" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>172</v>
       </c>
@@ -5072,7 +4340,7 @@
       </c>
       <c r="U10" s="49"/>
     </row>
-    <row r="11" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>172</v>
       </c>
@@ -5134,7 +4402,7 @@
       </c>
       <c r="U11" s="49"/>
     </row>
-    <row r="12" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
         <v>177</v>
       </c>
@@ -5196,7 +4464,7 @@
       </c>
       <c r="U12" s="49"/>
     </row>
-    <row r="13" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
         <v>154</v>
       </c>
@@ -5258,7 +4526,7 @@
       </c>
       <c r="U13" s="49"/>
     </row>
-    <row r="14" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
         <v>154</v>
       </c>
@@ -5320,7 +4588,7 @@
       </c>
       <c r="U14" s="49"/>
     </row>
-    <row r="15" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>172</v>
       </c>
@@ -5382,7 +4650,7 @@
       </c>
       <c r="U15" s="49"/>
     </row>
-    <row r="16" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>154</v>
       </c>
@@ -5444,7 +4712,7 @@
       </c>
       <c r="U16" s="49"/>
     </row>
-    <row r="17" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>154</v>
       </c>
@@ -5506,7 +4774,7 @@
       </c>
       <c r="U17" s="49"/>
     </row>
-    <row r="18" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>186</v>
       </c>
@@ -5568,7 +4836,7 @@
       </c>
       <c r="U18" s="49"/>
     </row>
-    <row r="19" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>189</v>
       </c>
@@ -5630,7 +4898,7 @@
       </c>
       <c r="U19" s="49"/>
     </row>
-    <row r="20" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>189</v>
       </c>
@@ -5692,7 +4960,7 @@
       </c>
       <c r="U20" s="49"/>
     </row>
-    <row r="21" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>193</v>
       </c>
@@ -5754,7 +5022,7 @@
       </c>
       <c r="U21" s="49"/>
     </row>
-    <row r="22" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>43</v>
       </c>
@@ -5816,7 +5084,7 @@
       </c>
       <c r="U22" s="49"/>
     </row>
-    <row r="23" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>201</v>
       </c>
@@ -5878,7 +5146,7 @@
       </c>
       <c r="U23" s="49"/>
     </row>
-    <row r="24" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>204</v>
       </c>
@@ -5940,7 +5208,7 @@
       </c>
       <c r="U24" s="49"/>
     </row>
-    <row r="25" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>206</v>
       </c>
@@ -6002,7 +5270,7 @@
       </c>
       <c r="U25" s="49"/>
     </row>
-    <row r="26" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>207</v>
       </c>
@@ -6064,7 +5332,7 @@
       </c>
       <c r="U26" s="49"/>
     </row>
-    <row r="27" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
         <v>172</v>
       </c>
@@ -6126,7 +5394,7 @@
       </c>
       <c r="U27" s="49"/>
     </row>
-    <row r="28" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>210</v>
       </c>
@@ -6188,7 +5456,7 @@
       </c>
       <c r="U28" s="49"/>
     </row>
-    <row r="29" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
         <v>213</v>
       </c>
@@ -6250,7 +5518,7 @@
       </c>
       <c r="U29" s="49"/>
     </row>
-    <row r="30" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>217</v>
       </c>
@@ -6312,7 +5580,7 @@
       </c>
       <c r="U30" s="49"/>
     </row>
-    <row r="31" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>218</v>
       </c>
@@ -6374,7 +5642,7 @@
       </c>
       <c r="U31" s="49"/>
     </row>
-    <row r="32" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>81</v>
       </c>
@@ -6436,7 +5704,7 @@
       </c>
       <c r="U32" s="49"/>
     </row>
-    <row r="33" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>91</v>
       </c>
@@ -6498,7 +5766,7 @@
       </c>
       <c r="U33" s="49"/>
     </row>
-    <row r="34" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
         <v>91</v>
       </c>
@@ -6560,7 +5828,7 @@
       </c>
       <c r="U34" s="49"/>
     </row>
-    <row r="35" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>91</v>
       </c>
@@ -6622,7 +5890,7 @@
       </c>
       <c r="U35" s="49"/>
     </row>
-    <row r="36" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>91</v>
       </c>
@@ -6684,7 +5952,7 @@
       </c>
       <c r="U36" s="49"/>
     </row>
-    <row r="37" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>91</v>
       </c>
@@ -6746,7 +6014,7 @@
       </c>
       <c r="U37" s="49"/>
     </row>
-    <row r="38" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
         <v>226</v>
       </c>
@@ -6808,7 +6076,7 @@
       </c>
       <c r="U38" s="49"/>
     </row>
-    <row r="39" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>228</v>
       </c>
@@ -6870,7 +6138,7 @@
       </c>
       <c r="U39" s="49"/>
     </row>
-    <row r="40" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>91</v>
       </c>
@@ -6932,7 +6200,7 @@
       </c>
       <c r="U40" s="49"/>
     </row>
-    <row r="41" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>231</v>
       </c>
@@ -6994,7 +6262,7 @@
       </c>
       <c r="U41" s="49"/>
     </row>
-    <row r="42" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>234</v>
       </c>
@@ -7056,7 +6324,7 @@
       </c>
       <c r="U42" s="49"/>
     </row>
-    <row r="43" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>236</v>
       </c>
@@ -7118,7 +6386,7 @@
       </c>
       <c r="U43" s="49"/>
     </row>
-    <row r="44" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>237</v>
       </c>
@@ -7180,7 +6448,7 @@
       </c>
       <c r="U44" s="49"/>
     </row>
-    <row r="45" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>238</v>
       </c>
@@ -7242,7 +6510,7 @@
       </c>
       <c r="U45" s="49"/>
     </row>
-    <row r="46" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
         <v>240</v>
       </c>
@@ -7304,7 +6572,7 @@
       </c>
       <c r="U46" s="49"/>
     </row>
-    <row r="47" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>91</v>
       </c>
@@ -7366,7 +6634,7 @@
       </c>
       <c r="U47" s="49"/>
     </row>
-    <row r="48" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>243</v>
       </c>
@@ -7428,7 +6696,7 @@
       </c>
       <c r="U48" s="49"/>
     </row>
-    <row r="49" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>246</v>
       </c>
@@ -7490,7 +6758,7 @@
       </c>
       <c r="U49" s="49"/>
     </row>
-    <row r="50" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
         <v>248</v>
       </c>
@@ -7552,7 +6820,7 @@
       </c>
       <c r="U50" s="49"/>
     </row>
-    <row r="51" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
         <v>250</v>
       </c>
@@ -7614,7 +6882,7 @@
       </c>
       <c r="U51" s="49"/>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
         <v>250</v>
       </c>
@@ -7676,7 +6944,7 @@
       </c>
       <c r="U52" s="49"/>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>253</v>
       </c>
@@ -7738,7 +7006,7 @@
       </c>
       <c r="U53" s="49"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>256</v>
       </c>
@@ -7800,7 +7068,7 @@
       </c>
       <c r="U54" s="49"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>258</v>
       </c>
@@ -7862,7 +7130,7 @@
       </c>
       <c r="U55" s="49"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
         <v>259</v>
       </c>
@@ -7924,7 +7192,7 @@
       </c>
       <c r="U56" s="49"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="8" t="s">
         <v>259</v>
       </c>
@@ -7986,7 +7254,7 @@
       </c>
       <c r="U57" s="49"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="8" t="s">
         <v>253</v>
       </c>
@@ -8048,7 +7316,7 @@
       </c>
       <c r="U58" s="49"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="8" t="s">
         <v>265</v>
       </c>
@@ -8110,7 +7378,7 @@
       </c>
       <c r="U59" s="49"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="8" t="s">
         <v>267</v>
       </c>
@@ -8172,7 +7440,7 @@
       </c>
       <c r="U60" s="49"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="8" t="s">
         <v>271</v>
       </c>
@@ -8234,7 +7502,7 @@
       </c>
       <c r="U61" s="49"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="8" t="s">
         <v>43</v>
       </c>
@@ -8296,7 +7564,7 @@
       </c>
       <c r="U62" s="49"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
         <v>58</v>
       </c>
@@ -8358,7 +7626,7 @@
       </c>
       <c r="U63" s="49"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="8" t="s">
         <v>91</v>
       </c>
@@ -8420,7 +7688,7 @@
       </c>
       <c r="U64" s="49"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="8" t="s">
         <v>91</v>
       </c>
@@ -8482,7 +7750,7 @@
       </c>
       <c r="U65" s="49"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="8" t="s">
         <v>91</v>
       </c>
@@ -8544,7 +7812,7 @@
       </c>
       <c r="U66" s="49"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="8" t="s">
         <v>282</v>
       </c>
@@ -8606,7 +7874,7 @@
       </c>
       <c r="U67" s="49"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>285</v>
       </c>
@@ -8668,7 +7936,7 @@
       </c>
       <c r="U68" s="49"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="8" t="s">
         <v>286</v>
       </c>
@@ -8730,7 +7998,7 @@
       </c>
       <c r="U69" s="49"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="16" t="s">
         <v>288</v>
       </c>
@@ -8792,7 +8060,7 @@
       </c>
       <c r="U70" s="49"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>291</v>
       </c>
@@ -8854,7 +8122,7 @@
       </c>
       <c r="U71" s="49"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>292</v>
       </c>
@@ -8916,7 +8184,7 @@
       </c>
       <c r="U72" s="49"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="8" t="s">
         <v>91</v>
       </c>
@@ -8978,7 +8246,7 @@
       </c>
       <c r="U73" s="49"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="8" t="s">
         <v>294</v>
       </c>
@@ -9040,7 +8308,7 @@
       </c>
       <c r="U74" s="49"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="8" t="s">
         <v>91</v>
       </c>
@@ -9102,7 +8370,7 @@
       </c>
       <c r="U75" s="49"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="8" t="s">
         <v>299</v>
       </c>
@@ -9164,7 +8432,7 @@
       </c>
       <c r="U76" s="49"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="8" t="s">
         <v>18</v>
       </c>
@@ -9226,7 +8494,7 @@
       </c>
       <c r="U77" s="49"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="8" t="s">
         <v>27</v>
       </c>
@@ -9288,7 +8556,7 @@
       </c>
       <c r="U78" s="49"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>30</v>
       </c>
@@ -9350,7 +8618,7 @@
       </c>
       <c r="U79" s="49"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="8" t="s">
         <v>35</v>
       </c>
@@ -9412,7 +8680,7 @@
       </c>
       <c r="U80" s="49"/>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="8" t="s">
         <v>35</v>
       </c>
@@ -9474,7 +8742,7 @@
       </c>
       <c r="U81" s="49"/>
     </row>
-    <row r="82" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:21" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="8" t="s">
         <v>35</v>
       </c>
@@ -9536,7 +8804,7 @@
       </c>
       <c r="U82" s="49"/>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="8" t="s">
         <v>43</v>
       </c>
@@ -9598,7 +8866,7 @@
       </c>
       <c r="U83" s="49"/>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="8" t="s">
         <v>43</v>
       </c>
@@ -9660,7 +8928,7 @@
       </c>
       <c r="U84" s="49"/>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="8" t="s">
         <v>52</v>
       </c>
@@ -9722,7 +8990,7 @@
       </c>
       <c r="U85" s="49"/>
     </row>
-    <row r="86" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:21" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="2" t="s">
         <v>55</v>
       </c>
@@ -9784,7 +9052,7 @@
       </c>
       <c r="U86" s="49"/>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="16" t="s">
         <v>58</v>
       </c>
@@ -9846,7 +9114,7 @@
       </c>
       <c r="U87" s="49"/>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="8" t="s">
         <v>62</v>
       </c>
@@ -9908,7 +9176,7 @@
       </c>
       <c r="U88" s="49"/>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="8" t="s">
         <v>65</v>
       </c>
@@ -9970,7 +9238,7 @@
       </c>
       <c r="U89" s="49"/>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="8" t="s">
         <v>67</v>
       </c>
@@ -10032,7 +9300,7 @@
       </c>
       <c r="U90" s="49"/>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="8" t="s">
         <v>70</v>
       </c>
@@ -10094,7 +9362,7 @@
       </c>
       <c r="U91" s="49"/>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="8" t="s">
         <v>75</v>
       </c>
@@ -10156,7 +9424,7 @@
       </c>
       <c r="U92" s="49"/>
     </row>
-    <row r="93" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:21" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="23" t="s">
         <v>77</v>
       </c>
@@ -10218,7 +9486,7 @@
       </c>
       <c r="U93" s="49"/>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="8" t="s">
         <v>43</v>
       </c>
@@ -10280,7 +9548,7 @@
       </c>
       <c r="U94" s="49"/>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="8" t="s">
         <v>81</v>
       </c>
@@ -10342,7 +9610,7 @@
       </c>
       <c r="U95" s="49"/>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>85</v>
       </c>
@@ -10404,7 +9672,7 @@
       </c>
       <c r="U96" s="49"/>
     </row>
-    <row r="97" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:21" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="6" t="s">
         <v>86</v>
       </c>
@@ -10466,7 +9734,7 @@
       </c>
       <c r="U97" s="49"/>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="8" t="s">
         <v>88</v>
       </c>
@@ -10528,7 +9796,7 @@
       </c>
       <c r="U98" s="49"/>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="8" t="s">
         <v>91</v>
       </c>
@@ -10590,7 +9858,7 @@
       </c>
       <c r="U99" s="49"/>
     </row>
-    <row r="100" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:21" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="23" t="s">
         <v>95</v>
       </c>
@@ -10652,7 +9920,7 @@
       </c>
       <c r="U100" s="49"/>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="8" t="s">
         <v>58</v>
       </c>
@@ -10714,7 +9982,7 @@
       </c>
       <c r="U101" s="49"/>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="16" t="s">
         <v>58</v>
       </c>
@@ -10776,7 +10044,7 @@
       </c>
       <c r="U102" s="49"/>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="8" t="s">
         <v>43</v>
       </c>
@@ -10838,7 +10106,7 @@
       </c>
       <c r="U103" s="49"/>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="8" t="s">
         <v>103</v>
       </c>
@@ -10900,7 +10168,7 @@
       </c>
       <c r="U104" s="49"/>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>106</v>
       </c>
@@ -10962,7 +10230,7 @@
       </c>
       <c r="U105" s="49"/>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>81</v>
       </c>
@@ -11024,7 +10292,7 @@
       </c>
       <c r="U106" s="49"/>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>107</v>
       </c>
@@ -11086,7 +10354,7 @@
       </c>
       <c r="U107" s="49"/>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>108</v>
       </c>
@@ -11148,7 +10416,7 @@
       </c>
       <c r="U108" s="49"/>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>109</v>
       </c>
@@ -11210,7 +10478,7 @@
       </c>
       <c r="U109" s="49"/>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="8" t="s">
         <v>110</v>
       </c>
@@ -11272,7 +10540,7 @@
       </c>
       <c r="U110" s="49"/>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="8" t="s">
         <v>113</v>
       </c>
@@ -11334,7 +10602,7 @@
       </c>
       <c r="U111" s="49"/>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>116</v>
       </c>
@@ -11396,7 +10664,7 @@
       </c>
       <c r="U112" s="49"/>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="8" t="s">
         <v>120</v>
       </c>
@@ -11458,7 +10726,7 @@
       </c>
       <c r="U113" s="49"/>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="8" t="s">
         <v>123</v>
       </c>
@@ -11520,7 +10788,7 @@
       </c>
       <c r="U114" s="49"/>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="8" t="s">
         <v>110</v>
       </c>
@@ -11582,7 +10850,7 @@
       </c>
       <c r="U115" s="49"/>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="8" t="s">
         <v>127</v>
       </c>
@@ -11644,7 +10912,7 @@
       </c>
       <c r="U116" s="49"/>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>130</v>
       </c>
@@ -11706,7 +10974,7 @@
       </c>
       <c r="U117" s="49"/>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>131</v>
       </c>
@@ -11768,7 +11036,7 @@
       </c>
       <c r="U118" s="49"/>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="8" t="s">
         <v>132</v>
       </c>
@@ -11830,7 +11098,7 @@
       </c>
       <c r="U119" s="49"/>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="8" t="s">
         <v>134</v>
       </c>
@@ -11892,7 +11160,7 @@
       </c>
       <c r="U120" s="49"/>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="8" t="s">
         <v>134</v>
       </c>
@@ -11954,7 +11222,7 @@
       </c>
       <c r="U121" s="49"/>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="8" t="s">
         <v>140</v>
       </c>
@@ -12016,7 +11284,7 @@
       </c>
       <c r="U122" s="49"/>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="8" t="s">
         <v>143</v>
       </c>
@@ -12078,7 +11346,7 @@
       </c>
       <c r="U123" s="49"/>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="8" t="s">
         <v>145</v>
       </c>
@@ -12140,7 +11408,7 @@
       </c>
       <c r="U124" s="49"/>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="8" t="s">
         <v>149</v>
       </c>
@@ -12202,7 +11470,7 @@
       </c>
       <c r="U125" s="49"/>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="8" t="s">
         <v>143</v>
       </c>
@@ -12264,7 +11532,7 @@
       </c>
       <c r="U126" s="49"/>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="8" t="s">
         <v>301</v>
       </c>
@@ -12330,7 +11598,7 @@
       </c>
       <c r="U127" s="49"/>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="8" t="s">
         <v>305</v>
       </c>
@@ -12396,7 +11664,7 @@
       </c>
       <c r="U128" s="49"/>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="8" t="s">
         <v>145</v>
       </c>
@@ -12462,7 +11730,7 @@
       </c>
       <c r="U129" s="49"/>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>308</v>
       </c>
@@ -12528,7 +11796,7 @@
       </c>
       <c r="U130" s="49"/>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
         <v>309</v>
       </c>
@@ -12594,7 +11862,7 @@
       </c>
       <c r="U131" s="49"/>
     </row>
-    <row r="132" spans="1:21" s="20" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:21" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="16" t="s">
         <v>311</v>
       </c>
@@ -12660,7 +11928,7 @@
       </c>
       <c r="U132" s="49"/>
     </row>
-    <row r="133" spans="1:21" s="20" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:21" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="8" t="s">
         <v>311</v>
       </c>
@@ -12726,7 +11994,7 @@
       </c>
       <c r="U133" s="49"/>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="8" t="s">
         <v>317</v>
       </c>
@@ -12792,7 +12060,7 @@
       </c>
       <c r="U134" s="49"/>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
         <v>320</v>
       </c>
@@ -12858,7 +12126,7 @@
       </c>
       <c r="U135" s="49"/>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
         <v>321</v>
       </c>
@@ -12924,7 +12192,7 @@
       </c>
       <c r="U136" s="49"/>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
         <v>321</v>
       </c>
@@ -12990,7 +12258,7 @@
       </c>
       <c r="U137" s="49"/>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="5" t="s">
         <v>322</v>
       </c>
@@ -13056,7 +12324,7 @@
       </c>
       <c r="U138" s="49"/>
     </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
         <v>323</v>
       </c>
@@ -13122,7 +12390,7 @@
       </c>
       <c r="U139" s="49"/>
     </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>324</v>
       </c>
@@ -13188,7 +12456,7 @@
       </c>
       <c r="U140" s="49"/>
     </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>326</v>
       </c>
@@ -13254,7 +12522,7 @@
       </c>
       <c r="U141" s="49"/>
     </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="8" t="s">
         <v>328</v>
       </c>
@@ -13320,7 +12588,7 @@
       </c>
       <c r="U142" s="49"/>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="8" t="s">
         <v>331</v>
       </c>
@@ -13386,7 +12654,7 @@
       </c>
       <c r="U143" s="49"/>
     </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="8" t="s">
         <v>333</v>
       </c>
@@ -13452,7 +12720,7 @@
       </c>
       <c r="U144" s="49"/>
     </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="8" t="s">
         <v>335</v>
       </c>
@@ -13518,7 +12786,7 @@
       </c>
       <c r="U145" s="49"/>
     </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="8" t="s">
         <v>140</v>
       </c>
@@ -13584,7 +12852,7 @@
       </c>
       <c r="U146" s="49"/>
     </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="8" t="s">
         <v>140</v>
       </c>
@@ -13650,7 +12918,7 @@
       </c>
       <c r="U147" s="49"/>
     </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="16" t="s">
         <v>58</v>
       </c>
@@ -13716,7 +12984,7 @@
       </c>
       <c r="U148" s="49"/>
     </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="8" t="s">
         <v>344</v>
       </c>
@@ -13784,7 +13052,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="8" t="s">
         <v>348</v>
       </c>
@@ -13852,7 +13120,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="8" t="s">
         <v>324</v>
       </c>
@@ -13920,7 +13188,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="8" t="s">
         <v>350</v>
       </c>
@@ -13988,7 +13256,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="8" t="s">
         <v>354</v>
       </c>
@@ -14056,7 +13324,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="8" t="s">
         <v>145</v>
       </c>
@@ -14124,7 +13392,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="8" t="s">
         <v>359</v>
       </c>
@@ -14192,7 +13460,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="8" t="s">
         <v>360</v>
       </c>
@@ -14260,7 +13528,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="8" t="s">
         <v>43</v>
       </c>
@@ -14328,7 +13596,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="8" t="s">
         <v>362</v>
       </c>
@@ -14396,7 +13664,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>43</v>
       </c>
@@ -14464,7 +13732,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>367</v>
       </c>
@@ -14532,7 +13800,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="8" t="s">
         <v>369</v>
       </c>
@@ -14600,7 +13868,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="8" t="s">
         <v>371</v>
       </c>
@@ -14668,7 +13936,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="8" t="s">
         <v>43</v>
       </c>
@@ -14736,7 +14004,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="8" t="s">
         <v>374</v>
       </c>
@@ -14804,7 +14072,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="8" t="s">
         <v>374</v>
       </c>
@@ -14872,7 +14140,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="8" t="s">
         <v>374</v>
       </c>
@@ -14940,7 +14208,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="8" t="s">
         <v>374</v>
       </c>
@@ -15008,7 +14276,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="8" t="s">
         <v>374</v>
       </c>
@@ -15076,7 +14344,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="8" t="s">
         <v>374</v>
       </c>
@@ -15144,7 +14412,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="8" t="s">
         <v>374</v>
       </c>
@@ -15212,7 +14480,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="8" t="s">
         <v>374</v>
       </c>
@@ -15280,7 +14548,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="8" t="s">
         <v>374</v>
       </c>
@@ -15348,7 +14616,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="8" t="s">
         <v>374</v>
       </c>
@@ -15416,7 +14684,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="8" t="s">
         <v>374</v>
       </c>
@@ -15484,7 +14752,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="8" t="s">
         <v>374</v>
       </c>
@@ -15552,7 +14820,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="8" t="s">
         <v>374</v>
       </c>
@@ -15620,7 +14888,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="8" t="s">
         <v>374</v>
       </c>
@@ -15688,7 +14956,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="8" t="s">
         <v>374</v>
       </c>
@@ -15756,7 +15024,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="8" t="s">
         <v>374</v>
       </c>
@@ -15824,7 +15092,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="8" t="s">
         <v>408</v>
       </c>
@@ -15892,7 +15160,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="16" t="s">
         <v>411</v>
       </c>
@@ -15960,7 +15228,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="8" t="s">
         <v>414</v>
       </c>
@@ -16028,7 +15296,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="183" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="8" t="s">
         <v>416</v>
       </c>
@@ -16096,7 +15364,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="184" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="8" t="s">
         <v>416</v>
       </c>
@@ -16164,7 +15432,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="185" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>419</v>
       </c>
@@ -16232,7 +15500,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="186" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="5" t="s">
         <v>421</v>
       </c>
@@ -16300,7 +15568,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="187" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="8" t="s">
         <v>422</v>
       </c>
@@ -16368,7 +15636,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="188" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="8" t="s">
         <v>422</v>
       </c>
@@ -16436,7 +15704,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="189" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="8" t="s">
         <v>428</v>
       </c>
@@ -16504,7 +15772,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="8" t="s">
         <v>430</v>
       </c>
@@ -16571,7 +15839,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="191" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="8" t="s">
         <v>432</v>
       </c>
@@ -16638,7 +15906,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="8" t="s">
         <v>432</v>
       </c>
@@ -16705,7 +15973,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="193" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="8" t="s">
         <v>437</v>
       </c>
@@ -16772,7 +16040,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="194" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="8" t="s">
         <v>438</v>
       </c>
@@ -16839,7 +16107,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="195" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="8" t="s">
         <v>439</v>
       </c>
@@ -16906,7 +16174,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="196" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="8" t="s">
         <v>445</v>
       </c>
@@ -16973,7 +16241,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="197" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="8" t="s">
         <v>432</v>
       </c>
@@ -17040,7 +16308,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="198" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="8" t="s">
         <v>134</v>
       </c>
@@ -17107,7 +16375,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="199" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="8" t="s">
         <v>451</v>
       </c>
@@ -17174,7 +16442,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="200" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="8" t="s">
         <v>451</v>
       </c>
@@ -17241,7 +16509,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="201" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="8" t="s">
         <v>134</v>
       </c>
@@ -17308,7 +16576,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="202" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="8" t="s">
         <v>456</v>
       </c>
@@ -17375,7 +16643,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="203" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="8" t="s">
         <v>43</v>
       </c>
@@ -17442,7 +16710,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="204" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="8" t="s">
         <v>459</v>
       </c>
@@ -17509,7 +16777,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="205" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="8" t="s">
         <v>461</v>
       </c>
@@ -17576,7 +16844,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="206" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="8" t="s">
         <v>462</v>
       </c>
@@ -17644,7 +16912,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="207" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="8" t="s">
         <v>451</v>
       </c>
@@ -17712,7 +16980,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="208" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="8" t="s">
         <v>451</v>
       </c>
@@ -17780,7 +17048,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="209" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="7" t="s">
         <v>466</v>
       </c>
@@ -17848,7 +17116,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="210" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="8" t="s">
         <v>469</v>
       </c>
@@ -17916,7 +17184,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="211" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="8" t="s">
         <v>471</v>
       </c>
@@ -17984,7 +17252,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="212" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>473</v>
       </c>
@@ -18052,7 +17320,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="213" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="8" t="s">
         <v>120</v>
       </c>
@@ -18120,7 +17388,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="214" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="8" t="s">
         <v>476</v>
       </c>
@@ -18188,7 +17456,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="215" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="8" t="s">
         <v>469</v>
       </c>
@@ -18256,7 +17524,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="216" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="8" t="s">
         <v>58</v>
       </c>
@@ -18324,7 +17592,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="217" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="8" t="s">
         <v>481</v>
       </c>
@@ -18392,7 +17660,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="218" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>483</v>
       </c>
@@ -18460,7 +17728,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="219" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>484</v>
       </c>
@@ -18528,7 +17796,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="220" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>271</v>
       </c>
@@ -18596,7 +17864,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="221" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="8" t="s">
         <v>485</v>
       </c>
@@ -18664,7 +17932,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="222" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="8" t="s">
         <v>172</v>
       </c>
@@ -18732,7 +18000,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="223" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="8" t="s">
         <v>489</v>
       </c>
@@ -18800,7 +18068,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="224" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="8" t="s">
         <v>492</v>
       </c>
@@ -18868,7 +18136,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="225" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>495</v>
       </c>
@@ -18936,7 +18204,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="226" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>499</v>
       </c>
@@ -19004,7 +18272,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="227" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>502</v>
       </c>
@@ -19072,7 +18340,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="228" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>503</v>
       </c>
@@ -19140,7 +18408,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="229" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="5" t="s">
         <v>505</v>
       </c>
@@ -19208,7 +18476,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="230" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="5" t="s">
         <v>506</v>
       </c>
@@ -19276,7 +18544,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="231" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="5" t="s">
         <v>507</v>
       </c>
@@ -19344,7 +18612,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="232" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="5" t="s">
         <v>508</v>
       </c>
@@ -19412,7 +18680,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="233" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>509</v>
       </c>
@@ -19479,7 +18747,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="234" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>514</v>
       </c>
@@ -19546,7 +18814,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="235" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="44" t="s">
         <v>516</v>
       </c>
@@ -19614,7 +18882,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="236" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="8" t="s">
         <v>516</v>
       </c>
@@ -19682,7 +18950,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="237" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="8" t="s">
         <v>520</v>
       </c>
@@ -19750,7 +19018,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="238" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="8" t="s">
         <v>522</v>
       </c>
@@ -19818,7 +19086,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="239" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="8" t="s">
         <v>524</v>
       </c>
@@ -19886,7 +19154,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="240" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="8" t="s">
         <v>526</v>
       </c>
@@ -19954,7 +19222,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="241" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="8" t="s">
         <v>528</v>
       </c>
@@ -20022,7 +19290,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="242" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="8" t="s">
         <v>528</v>
       </c>
@@ -20090,7 +19358,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="243" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="8" t="s">
         <v>469</v>
       </c>
@@ -21862,7 +21130,7 @@
         <v>46122</v>
       </c>
       <c r="J269" s="18">
-        <f t="shared" ref="J269:J303" si="21">+NETWORKDAYS(H269,I269)</f>
+        <f t="shared" ref="J269:J327" si="21">+NETWORKDAYS(H269,I269)</f>
         <v>2</v>
       </c>
       <c r="K269" s="8" t="s">
@@ -21890,7 +21158,7 @@
         <v>46126</v>
       </c>
       <c r="S269" s="18">
-        <f t="shared" ref="S269:S303" si="22">NETWORKDAYS(H269,R269)</f>
+        <f t="shared" ref="S269:S327" si="22">NETWORKDAYS(H269,R269)</f>
         <v>4</v>
       </c>
       <c r="T269" s="7" t="s">
@@ -24207,8 +23475,1622 @@
         <v>625</v>
       </c>
     </row>
+    <row r="304" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A304" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="B304" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C304" s="75">
+        <v>61622459</v>
+      </c>
+      <c r="D304" s="75" t="s">
+        <v>660</v>
+      </c>
+      <c r="E304" s="75" t="s">
+        <v>659</v>
+      </c>
+      <c r="F304" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G304" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="H304" s="76">
+        <v>46127</v>
+      </c>
+      <c r="I304" s="76">
+        <v>46136</v>
+      </c>
+      <c r="J304" s="18">
+        <f t="shared" si="21"/>
+        <v>8</v>
+      </c>
+      <c r="K304" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L304" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M304" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N304" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="O304" s="75">
+        <v>0</v>
+      </c>
+      <c r="P304" s="75">
+        <v>0</v>
+      </c>
+      <c r="Q304" s="77">
+        <v>0</v>
+      </c>
+      <c r="R304" s="76">
+        <v>46139</v>
+      </c>
+      <c r="S304" s="18">
+        <f t="shared" si="22"/>
+        <v>9</v>
+      </c>
+      <c r="T304" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U304" s="78" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="305" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A305" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="B305" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C305" s="75">
+        <v>58274609</v>
+      </c>
+      <c r="D305" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="E305" s="75" t="s">
+        <v>657</v>
+      </c>
+      <c r="F305" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G305" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H305" s="76">
+        <v>46066</v>
+      </c>
+      <c r="I305" s="76">
+        <v>46136</v>
+      </c>
+      <c r="J305" s="18">
+        <f t="shared" si="21"/>
+        <v>51</v>
+      </c>
+      <c r="K305" s="75" t="s">
+        <v>353</v>
+      </c>
+      <c r="L305" s="75" t="s">
+        <v>580</v>
+      </c>
+      <c r="M305" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N305" s="75" t="s">
+        <v>61</v>
+      </c>
+      <c r="O305" s="75">
+        <v>522590</v>
+      </c>
+      <c r="P305" s="75">
+        <v>331989</v>
+      </c>
+      <c r="Q305" s="77">
+        <v>854579</v>
+      </c>
+      <c r="R305" s="76">
+        <v>46139</v>
+      </c>
+      <c r="S305" s="18">
+        <f t="shared" si="22"/>
+        <v>52</v>
+      </c>
+      <c r="T305" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U305" s="78" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="306" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A306" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="B306" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C306" s="75">
+        <v>61572859</v>
+      </c>
+      <c r="D306" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="E306" s="75" t="s">
+        <v>656</v>
+      </c>
+      <c r="F306" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="G306" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H306" s="76">
+        <v>46126</v>
+      </c>
+      <c r="I306" s="76">
+        <v>46139</v>
+      </c>
+      <c r="J306" s="18">
+        <f t="shared" si="21"/>
+        <v>10</v>
+      </c>
+      <c r="K306" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L306" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M306" s="75" t="s">
+        <v>157</v>
+      </c>
+      <c r="N306" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="O306" s="75">
+        <v>752977</v>
+      </c>
+      <c r="P306" s="75">
+        <v>0</v>
+      </c>
+      <c r="Q306" s="77">
+        <v>752977</v>
+      </c>
+      <c r="R306" s="76">
+        <v>46139</v>
+      </c>
+      <c r="S306" s="18">
+        <f t="shared" si="22"/>
+        <v>10</v>
+      </c>
+      <c r="T306" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U306" s="78" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="307" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A307" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B307" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C307" s="75">
+        <v>61376925</v>
+      </c>
+      <c r="D307" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="E307" s="75" t="s">
+        <v>655</v>
+      </c>
+      <c r="F307" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G307" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H307" s="76">
+        <v>46122</v>
+      </c>
+      <c r="I307" s="76">
+        <v>46139</v>
+      </c>
+      <c r="J307" s="18">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="K307" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L307" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M307" s="75" t="s">
+        <v>48</v>
+      </c>
+      <c r="N307" s="75" t="s">
+        <v>49</v>
+      </c>
+      <c r="O307" s="75">
+        <v>200000</v>
+      </c>
+      <c r="P307" s="75">
+        <v>0</v>
+      </c>
+      <c r="Q307" s="77">
+        <v>200000</v>
+      </c>
+      <c r="R307" s="76">
+        <v>46140</v>
+      </c>
+      <c r="S307" s="18">
+        <f t="shared" si="22"/>
+        <v>13</v>
+      </c>
+      <c r="T307" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U307" s="78" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="308" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A308" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="B308" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C308" s="75">
+        <v>61509436</v>
+      </c>
+      <c r="D308" s="75" t="s">
+        <v>276</v>
+      </c>
+      <c r="E308" s="75" t="s">
+        <v>654</v>
+      </c>
+      <c r="F308" s="75" t="s">
+        <v>196</v>
+      </c>
+      <c r="G308" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H308" s="76">
+        <v>46125</v>
+      </c>
+      <c r="I308" s="76">
+        <v>46140</v>
+      </c>
+      <c r="J308" s="18">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="K308" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L308" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M308" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N308" s="75" t="s">
+        <v>29</v>
+      </c>
+      <c r="O308" s="75">
+        <v>3850000</v>
+      </c>
+      <c r="P308" s="75">
+        <v>667054</v>
+      </c>
+      <c r="Q308" s="77">
+        <v>4517054</v>
+      </c>
+      <c r="R308" s="76">
+        <v>46140</v>
+      </c>
+      <c r="S308" s="18">
+        <f t="shared" si="22"/>
+        <v>12</v>
+      </c>
+      <c r="T308" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U308" s="78" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="309" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A309" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="B309" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C309" s="75">
+        <v>61510116</v>
+      </c>
+      <c r="D309" s="75" t="s">
+        <v>653</v>
+      </c>
+      <c r="E309" s="75" t="s">
+        <v>652</v>
+      </c>
+      <c r="F309" s="75" t="s">
+        <v>196</v>
+      </c>
+      <c r="G309" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H309" s="76">
+        <v>46125</v>
+      </c>
+      <c r="I309" s="76">
+        <v>46140</v>
+      </c>
+      <c r="J309" s="18">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="K309" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L309" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M309" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N309" s="75" t="s">
+        <v>29</v>
+      </c>
+      <c r="O309" s="75">
+        <v>3850000</v>
+      </c>
+      <c r="P309" s="75">
+        <v>667054</v>
+      </c>
+      <c r="Q309" s="77">
+        <v>4517054</v>
+      </c>
+      <c r="R309" s="76">
+        <v>46140</v>
+      </c>
+      <c r="S309" s="18">
+        <f t="shared" si="22"/>
+        <v>12</v>
+      </c>
+      <c r="T309" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U309" s="78" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="310" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A310" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="B310" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C310" s="75">
+        <v>58649837</v>
+      </c>
+      <c r="D310" s="75" t="s">
+        <v>36</v>
+      </c>
+      <c r="E310" s="75" t="s">
+        <v>650</v>
+      </c>
+      <c r="F310" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="G310" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="H310" s="76">
+        <v>46077</v>
+      </c>
+      <c r="I310" s="76">
+        <v>46140</v>
+      </c>
+      <c r="J310" s="18">
+        <f t="shared" si="21"/>
+        <v>46</v>
+      </c>
+      <c r="K310" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L310" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M310" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N310" s="75" t="s">
+        <v>73</v>
+      </c>
+      <c r="O310" s="75">
+        <v>2621414</v>
+      </c>
+      <c r="P310" s="75">
+        <v>1059070</v>
+      </c>
+      <c r="Q310" s="77">
+        <v>3680484</v>
+      </c>
+      <c r="R310" s="76">
+        <v>46140</v>
+      </c>
+      <c r="S310" s="18">
+        <f t="shared" si="22"/>
+        <v>46</v>
+      </c>
+      <c r="T310" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U310" s="78" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="311" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A311" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B311" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C311" s="75">
+        <v>58821553</v>
+      </c>
+      <c r="D311" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="E311" s="75" t="s">
+        <v>649</v>
+      </c>
+      <c r="F311" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G311" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="H311" s="76">
+        <v>46076</v>
+      </c>
+      <c r="I311" s="76">
+        <v>46139</v>
+      </c>
+      <c r="J311" s="18">
+        <f t="shared" si="21"/>
+        <v>46</v>
+      </c>
+      <c r="K311" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L311" s="75" t="s">
+        <v>310</v>
+      </c>
+      <c r="M311" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N311" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="O311" s="75">
+        <v>705000</v>
+      </c>
+      <c r="P311" s="75">
+        <v>115000</v>
+      </c>
+      <c r="Q311" s="77">
+        <v>820000</v>
+      </c>
+      <c r="R311" s="76">
+        <v>46141</v>
+      </c>
+      <c r="S311" s="18">
+        <f t="shared" si="22"/>
+        <v>48</v>
+      </c>
+      <c r="T311" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U311" s="78" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="312" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A312" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B312" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C312" s="75">
+        <v>60463210</v>
+      </c>
+      <c r="D312" s="75" t="s">
+        <v>325</v>
+      </c>
+      <c r="E312" s="75" t="s">
+        <v>648</v>
+      </c>
+      <c r="F312" s="75" t="s">
+        <v>512</v>
+      </c>
+      <c r="G312" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="H312" s="76">
+        <v>46106</v>
+      </c>
+      <c r="I312" s="76">
+        <v>46132</v>
+      </c>
+      <c r="J312" s="18">
+        <f t="shared" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="K312" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L312" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M312" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N312" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="O312" s="75">
+        <v>0</v>
+      </c>
+      <c r="P312" s="75">
+        <v>0</v>
+      </c>
+      <c r="Q312" s="77">
+        <v>0</v>
+      </c>
+      <c r="R312" s="76">
+        <v>46141</v>
+      </c>
+      <c r="S312" s="18">
+        <f t="shared" si="22"/>
+        <v>26</v>
+      </c>
+      <c r="T312" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U312" s="78" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="313" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A313" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B313" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C313" s="75">
+        <v>60458148</v>
+      </c>
+      <c r="D313" s="75" t="s">
+        <v>342</v>
+      </c>
+      <c r="E313" s="75" t="s">
+        <v>647</v>
+      </c>
+      <c r="F313" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="G313" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="H313" s="76">
+        <v>46112</v>
+      </c>
+      <c r="I313" s="76">
+        <v>46129</v>
+      </c>
+      <c r="J313" s="18">
+        <f t="shared" si="21"/>
+        <v>14</v>
+      </c>
+      <c r="K313" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L313" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M313" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N313" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="O313" s="75">
+        <v>580000</v>
+      </c>
+      <c r="P313" s="75">
+        <v>115000</v>
+      </c>
+      <c r="Q313" s="77">
+        <v>695000</v>
+      </c>
+      <c r="R313" s="76">
+        <v>46141</v>
+      </c>
+      <c r="S313" s="18">
+        <f t="shared" si="22"/>
+        <v>22</v>
+      </c>
+      <c r="T313" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U313" s="78" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="314" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A314" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B314" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C314" s="75">
+        <v>58821537</v>
+      </c>
+      <c r="D314" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="E314" s="75" t="s">
+        <v>646</v>
+      </c>
+      <c r="F314" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G314" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="H314" s="76">
+        <v>46076</v>
+      </c>
+      <c r="I314" s="76">
+        <v>46127</v>
+      </c>
+      <c r="J314" s="18">
+        <f t="shared" si="21"/>
+        <v>38</v>
+      </c>
+      <c r="K314" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L314" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M314" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N314" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="O314" s="75">
+        <v>0</v>
+      </c>
+      <c r="P314" s="75">
+        <v>30000</v>
+      </c>
+      <c r="Q314" s="77">
+        <v>30000</v>
+      </c>
+      <c r="R314" s="76">
+        <v>46141</v>
+      </c>
+      <c r="S314" s="18">
+        <f t="shared" si="22"/>
+        <v>48</v>
+      </c>
+      <c r="T314" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U314" s="78" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="315" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A315" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B315" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C315" s="75">
+        <v>58822576</v>
+      </c>
+      <c r="D315" s="75" t="s">
+        <v>289</v>
+      </c>
+      <c r="E315" s="75" t="s">
+        <v>645</v>
+      </c>
+      <c r="F315" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G315" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="H315" s="76">
+        <v>46076</v>
+      </c>
+      <c r="I315" s="76">
+        <v>46085</v>
+      </c>
+      <c r="J315" s="18">
+        <f t="shared" si="21"/>
+        <v>8</v>
+      </c>
+      <c r="K315" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L315" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M315" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N315" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="O315" s="75">
+        <v>1150000</v>
+      </c>
+      <c r="P315" s="75">
+        <v>115000</v>
+      </c>
+      <c r="Q315" s="77">
+        <v>1265000</v>
+      </c>
+      <c r="R315" s="76">
+        <v>46141</v>
+      </c>
+      <c r="S315" s="18">
+        <f t="shared" si="22"/>
+        <v>48</v>
+      </c>
+      <c r="T315" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U315" s="78" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="316" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A316" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B316" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C316" s="75">
+        <v>58822595</v>
+      </c>
+      <c r="D316" s="75" t="s">
+        <v>289</v>
+      </c>
+      <c r="E316" s="75" t="s">
+        <v>644</v>
+      </c>
+      <c r="F316" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="G316" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="H316" s="76">
+        <v>46076</v>
+      </c>
+      <c r="I316" s="76">
+        <v>46100</v>
+      </c>
+      <c r="J316" s="18">
+        <f t="shared" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="K316" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L316" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M316" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N316" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="O316" s="75">
+        <v>1150000</v>
+      </c>
+      <c r="P316" s="75">
+        <v>115000</v>
+      </c>
+      <c r="Q316" s="77">
+        <v>1265000</v>
+      </c>
+      <c r="R316" s="76">
+        <v>46141</v>
+      </c>
+      <c r="S316" s="18">
+        <f t="shared" si="22"/>
+        <v>48</v>
+      </c>
+      <c r="T316" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U316" s="78" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="317" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A317" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B317" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C317" s="75">
+        <v>61220566</v>
+      </c>
+      <c r="D317" s="75" t="s">
+        <v>572</v>
+      </c>
+      <c r="E317" s="75" t="s">
+        <v>643</v>
+      </c>
+      <c r="F317" s="75" t="s">
+        <v>196</v>
+      </c>
+      <c r="G317" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H317" s="76">
+        <v>46121</v>
+      </c>
+      <c r="I317" s="76">
+        <v>46122</v>
+      </c>
+      <c r="J317" s="18">
+        <f t="shared" si="21"/>
+        <v>2</v>
+      </c>
+      <c r="K317" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L317" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M317" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N317" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="O317" s="75">
+        <v>0</v>
+      </c>
+      <c r="P317" s="75">
+        <v>3780628</v>
+      </c>
+      <c r="Q317" s="77">
+        <v>3780628</v>
+      </c>
+      <c r="R317" s="76">
+        <v>46141</v>
+      </c>
+      <c r="S317" s="18">
+        <f t="shared" si="22"/>
+        <v>15</v>
+      </c>
+      <c r="T317" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U317" s="78" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="318" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A318" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="B318" s="75" t="s">
+        <v>87</v>
+      </c>
+      <c r="C318" s="75">
+        <v>61245220</v>
+      </c>
+      <c r="D318" s="75" t="s">
+        <v>36</v>
+      </c>
+      <c r="E318" s="75">
+        <v>2720254300</v>
+      </c>
+      <c r="F318" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G318" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="H318" s="76">
+        <v>46120</v>
+      </c>
+      <c r="I318" s="76">
+        <v>46138</v>
+      </c>
+      <c r="J318" s="18">
+        <f t="shared" si="21"/>
+        <v>13</v>
+      </c>
+      <c r="K318" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L318" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M318" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N318" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O318" s="75">
+        <v>0</v>
+      </c>
+      <c r="P318" s="75">
+        <v>0</v>
+      </c>
+      <c r="Q318" s="77">
+        <v>0</v>
+      </c>
+      <c r="R318" s="76">
+        <v>46141</v>
+      </c>
+      <c r="S318" s="18">
+        <f t="shared" si="22"/>
+        <v>16</v>
+      </c>
+      <c r="T318" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="U318" s="7" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="319" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A319" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="B319" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C319" s="75">
+        <v>61565561</v>
+      </c>
+      <c r="D319" s="75" t="s">
+        <v>138</v>
+      </c>
+      <c r="E319" s="75" t="s">
+        <v>640</v>
+      </c>
+      <c r="F319" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="G319" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H319" s="76">
+        <v>46126</v>
+      </c>
+      <c r="I319" s="76">
+        <v>46133</v>
+      </c>
+      <c r="J319" s="18">
+        <f t="shared" si="21"/>
+        <v>6</v>
+      </c>
+      <c r="K319" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L319" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M319" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N319" s="75" t="s">
+        <v>54</v>
+      </c>
+      <c r="O319" s="75">
+        <v>605000</v>
+      </c>
+      <c r="P319" s="75">
+        <v>474962</v>
+      </c>
+      <c r="Q319" s="77">
+        <v>1079962</v>
+      </c>
+      <c r="R319" s="76">
+        <v>46141</v>
+      </c>
+      <c r="S319" s="18">
+        <f t="shared" si="22"/>
+        <v>12</v>
+      </c>
+      <c r="T319" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U319" s="78" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="320" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A320" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="B320" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C320" s="75">
+        <v>61580430</v>
+      </c>
+      <c r="D320" s="75" t="s">
+        <v>36</v>
+      </c>
+      <c r="E320" s="75" t="s">
+        <v>638</v>
+      </c>
+      <c r="F320" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G320" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H320" s="76">
+        <v>46126</v>
+      </c>
+      <c r="I320" s="76">
+        <v>46133</v>
+      </c>
+      <c r="J320" s="18">
+        <f t="shared" si="21"/>
+        <v>6</v>
+      </c>
+      <c r="K320" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L320" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M320" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N320" s="75" t="s">
+        <v>119</v>
+      </c>
+      <c r="O320" s="75">
+        <v>2188000</v>
+      </c>
+      <c r="P320" s="75">
+        <v>750000</v>
+      </c>
+      <c r="Q320" s="77">
+        <v>2938000</v>
+      </c>
+      <c r="R320" s="76">
+        <v>46141</v>
+      </c>
+      <c r="S320" s="18">
+        <f t="shared" si="22"/>
+        <v>12</v>
+      </c>
+      <c r="T320" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U320" s="78" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="321" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A321" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="B321" s="75" t="s">
+        <v>87</v>
+      </c>
+      <c r="C321" s="75">
+        <v>61242255</v>
+      </c>
+      <c r="D321" s="75" t="s">
+        <v>36</v>
+      </c>
+      <c r="E321" s="75">
+        <v>2720334660</v>
+      </c>
+      <c r="F321" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G321" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="H321" s="76">
+        <v>46120</v>
+      </c>
+      <c r="I321" s="76">
+        <v>46139</v>
+      </c>
+      <c r="J321" s="18">
+        <f t="shared" si="21"/>
+        <v>14</v>
+      </c>
+      <c r="K321" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L321" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M321" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N321" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O321" s="75">
+        <v>0</v>
+      </c>
+      <c r="P321" s="75">
+        <v>0</v>
+      </c>
+      <c r="Q321" s="77">
+        <v>0</v>
+      </c>
+      <c r="R321" s="76">
+        <v>46141</v>
+      </c>
+      <c r="S321" s="18">
+        <f t="shared" si="22"/>
+        <v>16</v>
+      </c>
+      <c r="T321" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="U321" s="7" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="322" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A322" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="B322" s="75" t="s">
+        <v>87</v>
+      </c>
+      <c r="C322" s="75">
+        <v>59406937</v>
+      </c>
+      <c r="D322" s="75" t="s">
+        <v>36</v>
+      </c>
+      <c r="E322" s="75">
+        <v>2720255555</v>
+      </c>
+      <c r="F322" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G322" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="H322" s="76">
+        <v>46086</v>
+      </c>
+      <c r="I322" s="76">
+        <v>46139</v>
+      </c>
+      <c r="J322" s="18">
+        <f t="shared" si="21"/>
+        <v>38</v>
+      </c>
+      <c r="K322" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L322" s="75" t="s">
+        <v>327</v>
+      </c>
+      <c r="M322" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N322" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O322" s="75">
+        <v>0</v>
+      </c>
+      <c r="P322" s="75">
+        <v>0</v>
+      </c>
+      <c r="Q322" s="77">
+        <v>0</v>
+      </c>
+      <c r="R322" s="76">
+        <v>46141</v>
+      </c>
+      <c r="S322" s="18">
+        <f t="shared" si="22"/>
+        <v>40</v>
+      </c>
+      <c r="T322" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="U322" s="7" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="323" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A323" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B323" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C323" s="75">
+        <v>60461778</v>
+      </c>
+      <c r="D323" s="75" t="s">
+        <v>610</v>
+      </c>
+      <c r="E323" s="75" t="s">
+        <v>635</v>
+      </c>
+      <c r="F323" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="G323" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="H323" s="76">
+        <v>46106</v>
+      </c>
+      <c r="I323" s="76">
+        <v>46136</v>
+      </c>
+      <c r="J323" s="18">
+        <f t="shared" si="21"/>
+        <v>23</v>
+      </c>
+      <c r="K323" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L323" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M323" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N323" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="O323" s="75">
+        <v>780000</v>
+      </c>
+      <c r="P323" s="75">
+        <v>115000</v>
+      </c>
+      <c r="Q323" s="77">
+        <v>895000</v>
+      </c>
+      <c r="R323" s="76">
+        <v>46142</v>
+      </c>
+      <c r="S323" s="18">
+        <f t="shared" si="22"/>
+        <v>27</v>
+      </c>
+      <c r="T323" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U323" s="78" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="324" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A324" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="B324" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C324" s="75">
+        <v>62008380</v>
+      </c>
+      <c r="D324" s="75" t="s">
+        <v>202</v>
+      </c>
+      <c r="E324" s="75" t="s">
+        <v>633</v>
+      </c>
+      <c r="F324" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="G324" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H324" s="76">
+        <v>46133</v>
+      </c>
+      <c r="I324" s="76">
+        <v>46139</v>
+      </c>
+      <c r="J324" s="18">
+        <f t="shared" si="21"/>
+        <v>5</v>
+      </c>
+      <c r="K324" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L324" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M324" s="75" t="s">
+        <v>358</v>
+      </c>
+      <c r="N324" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="O324" s="75">
+        <v>0</v>
+      </c>
+      <c r="P324" s="75">
+        <v>0</v>
+      </c>
+      <c r="Q324" s="77">
+        <v>0</v>
+      </c>
+      <c r="R324" s="76">
+        <v>46142</v>
+      </c>
+      <c r="S324" s="18">
+        <f t="shared" si="22"/>
+        <v>8</v>
+      </c>
+      <c r="T324" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U324" s="78" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="325" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A325" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B325" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C325" s="75">
+        <v>58889872</v>
+      </c>
+      <c r="D325" s="75" t="s">
+        <v>584</v>
+      </c>
+      <c r="E325" s="75" t="s">
+        <v>632</v>
+      </c>
+      <c r="F325" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G325" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="H325" s="76">
+        <v>46077</v>
+      </c>
+      <c r="I325" s="76">
+        <v>46141</v>
+      </c>
+      <c r="J325" s="18">
+        <f t="shared" si="21"/>
+        <v>47</v>
+      </c>
+      <c r="K325" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L325" s="75" t="s">
+        <v>327</v>
+      </c>
+      <c r="M325" s="75" t="s">
+        <v>358</v>
+      </c>
+      <c r="N325" s="75" t="s">
+        <v>148</v>
+      </c>
+      <c r="O325" s="75">
+        <v>0</v>
+      </c>
+      <c r="P325" s="75">
+        <v>0</v>
+      </c>
+      <c r="Q325" s="77">
+        <v>0</v>
+      </c>
+      <c r="R325" s="76">
+        <v>46142</v>
+      </c>
+      <c r="S325" s="18">
+        <f t="shared" si="22"/>
+        <v>48</v>
+      </c>
+      <c r="T325" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U325" s="78" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="326" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A326" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B326" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C326" s="75">
+        <v>60458135</v>
+      </c>
+      <c r="D326" s="75" t="s">
+        <v>342</v>
+      </c>
+      <c r="E326" s="75" t="s">
+        <v>631</v>
+      </c>
+      <c r="F326" s="75" t="s">
+        <v>512</v>
+      </c>
+      <c r="G326" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="H326" s="76">
+        <v>46106</v>
+      </c>
+      <c r="I326" s="76">
+        <v>46141</v>
+      </c>
+      <c r="J326" s="18">
+        <f t="shared" si="21"/>
+        <v>26</v>
+      </c>
+      <c r="K326" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L326" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M326" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N326" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="O326" s="75">
+        <v>0</v>
+      </c>
+      <c r="P326" s="75">
+        <v>0</v>
+      </c>
+      <c r="Q326" s="77">
+        <v>0</v>
+      </c>
+      <c r="R326" s="76">
+        <v>46142</v>
+      </c>
+      <c r="S326" s="18">
+        <f t="shared" si="22"/>
+        <v>27</v>
+      </c>
+      <c r="T326" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U326" s="78" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="327" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A327" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B327" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C327" s="75">
+        <v>60461761</v>
+      </c>
+      <c r="D327" s="75" t="s">
+        <v>610</v>
+      </c>
+      <c r="E327" s="75" t="s">
+        <v>630</v>
+      </c>
+      <c r="F327" s="75" t="s">
+        <v>512</v>
+      </c>
+      <c r="G327" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="H327" s="76">
+        <v>46106</v>
+      </c>
+      <c r="I327" s="76">
+        <v>46141</v>
+      </c>
+      <c r="J327" s="18">
+        <f t="shared" si="21"/>
+        <v>26</v>
+      </c>
+      <c r="K327" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L327" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M327" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N327" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="O327" s="75">
+        <v>0</v>
+      </c>
+      <c r="P327" s="75">
+        <v>0</v>
+      </c>
+      <c r="Q327" s="77">
+        <v>0</v>
+      </c>
+      <c r="R327" s="76">
+        <v>46142</v>
+      </c>
+      <c r="S327" s="18">
+        <f t="shared" si="22"/>
+        <v>27</v>
+      </c>
+      <c r="T327" s="78" t="s">
+        <v>662</v>
+      </c>
+      <c r="U327" s="78" t="s">
+        <v>444</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U303" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U327" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="17">
+      <filters>
+        <dateGroupItem year="2026" month="4" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="C1">
     <cfRule type="duplicateValues" dxfId="87" priority="81"/>
     <cfRule type="duplicateValues" dxfId="86" priority="83"/>
@@ -24217,223 +25099,223 @@
     <cfRule type="duplicateValues" dxfId="83" priority="86"/>
     <cfRule type="duplicateValues" dxfId="82" priority="87"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C205 C244:C287 C304:C1048576">
+    <cfRule type="duplicateValues" dxfId="81" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="176"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C212 C244:C287 C304:C1048576">
+    <cfRule type="duplicateValues" dxfId="79" priority="185"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C232 C244:C287 C304:C1048576">
+    <cfRule type="duplicateValues" dxfId="78" priority="190"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C294 C304:C1048576">
+    <cfRule type="duplicateValues" dxfId="77" priority="195"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C295 C304:C1048576">
+    <cfRule type="duplicateValues" dxfId="76" priority="171"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="81" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="79" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="77" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="76" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="74" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="73" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="72" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="71" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="70" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="69" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="68" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="67" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="66" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="65" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="64" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="63" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="62" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="61" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="60" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="59" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
-    <cfRule type="duplicateValues" dxfId="58" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="57" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="56" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="54" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="53" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="52" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="51" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="50" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="48" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C114">
-    <cfRule type="duplicateValues" dxfId="47" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="46" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="45" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C157:C160">
-    <cfRule type="duplicateValues" dxfId="43" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C161:C163">
-    <cfRule type="duplicateValues" dxfId="42" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="41" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="39" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C168">
-    <cfRule type="duplicateValues" dxfId="37" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="36" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171">
-    <cfRule type="duplicateValues" dxfId="35" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173">
-    <cfRule type="duplicateValues" dxfId="34" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="32" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C175">
-    <cfRule type="duplicateValues" dxfId="31" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="30" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C178">
-    <cfRule type="duplicateValues" dxfId="29" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179">
-    <cfRule type="duplicateValues" dxfId="28" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C206:C212">
-    <cfRule type="duplicateValues" dxfId="26" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
-    <cfRule type="duplicateValues" dxfId="25" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C208">
-    <cfRule type="duplicateValues" dxfId="23" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218:C223">
-    <cfRule type="duplicateValues" dxfId="21" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C225:C232">
-    <cfRule type="duplicateValues" dxfId="20" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C233:C243">
-    <cfRule type="duplicateValues" dxfId="19" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="18" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="16" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="15" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="14" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="13" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="12" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="11" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="10" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="9" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172">
-    <cfRule type="duplicateValues" dxfId="8" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175">
-    <cfRule type="duplicateValues" dxfId="7" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E243">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C295 C304:C1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="171"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C205 C244:C287 C304:C1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="176"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C212 C244:C287 C304:C1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="185"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C232 C244:C287 C304:C1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="190"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C294 C304:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="528" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19EBB1A3-DBBF-494C-B3BA-61AFA3BDC228}"/>
+  <xr:revisionPtr revIDLastSave="546" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D14E4064-EEEE-41A3-83C4-CC0848260AE6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3460" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3484" uniqueCount="669">
   <si>
     <t>Client</t>
   </si>
@@ -2035,6 +2035,18 @@
   </si>
   <si>
     <t>Projet Interne</t>
+  </si>
+  <si>
+    <t>SYTHD260088</t>
+  </si>
+  <si>
+    <t>WINROCK</t>
+  </si>
+  <si>
+    <t>SYTHD260118</t>
+  </si>
+  <si>
+    <t>MAIRIE</t>
   </si>
 </sst>
 </file>
@@ -2461,27 +2473,7 @@
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="90">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="88">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3696,8 +3688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:U327"/>
+  <dimension ref="A1:U329"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="20" customWidth="1"/>
@@ -3782,7 +3773,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="42" t="s">
         <v>154</v>
       </c>
@@ -3844,7 +3835,7 @@
       </c>
       <c r="U2" s="49"/>
     </row>
-    <row r="3" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>159</v>
       </c>
@@ -3906,7 +3897,7 @@
       </c>
       <c r="U3" s="49"/>
     </row>
-    <row r="4" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>154</v>
       </c>
@@ -3968,7 +3959,7 @@
       </c>
       <c r="U4" s="49"/>
     </row>
-    <row r="5" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>154</v>
       </c>
@@ -4030,7 +4021,7 @@
       </c>
       <c r="U5" s="49"/>
     </row>
-    <row r="6" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>164</v>
       </c>
@@ -4092,7 +4083,7 @@
       </c>
       <c r="U6" s="49"/>
     </row>
-    <row r="7" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>165</v>
       </c>
@@ -4154,7 +4145,7 @@
       </c>
       <c r="U7" s="49"/>
     </row>
-    <row r="8" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>166</v>
       </c>
@@ -4216,7 +4207,7 @@
       </c>
       <c r="U8" s="49"/>
     </row>
-    <row r="9" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>169</v>
       </c>
@@ -4278,7 +4269,7 @@
       </c>
       <c r="U9" s="49"/>
     </row>
-    <row r="10" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>172</v>
       </c>
@@ -4340,7 +4331,7 @@
       </c>
       <c r="U10" s="49"/>
     </row>
-    <row r="11" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>172</v>
       </c>
@@ -4402,7 +4393,7 @@
       </c>
       <c r="U11" s="49"/>
     </row>
-    <row r="12" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
         <v>177</v>
       </c>
@@ -4464,7 +4455,7 @@
       </c>
       <c r="U12" s="49"/>
     </row>
-    <row r="13" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
         <v>154</v>
       </c>
@@ -4526,7 +4517,7 @@
       </c>
       <c r="U13" s="49"/>
     </row>
-    <row r="14" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
         <v>154</v>
       </c>
@@ -4588,7 +4579,7 @@
       </c>
       <c r="U14" s="49"/>
     </row>
-    <row r="15" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>172</v>
       </c>
@@ -4650,7 +4641,7 @@
       </c>
       <c r="U15" s="49"/>
     </row>
-    <row r="16" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>154</v>
       </c>
@@ -4712,7 +4703,7 @@
       </c>
       <c r="U16" s="49"/>
     </row>
-    <row r="17" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>154</v>
       </c>
@@ -4774,7 +4765,7 @@
       </c>
       <c r="U17" s="49"/>
     </row>
-    <row r="18" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>186</v>
       </c>
@@ -4836,7 +4827,7 @@
       </c>
       <c r="U18" s="49"/>
     </row>
-    <row r="19" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>189</v>
       </c>
@@ -4898,7 +4889,7 @@
       </c>
       <c r="U19" s="49"/>
     </row>
-    <row r="20" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>189</v>
       </c>
@@ -4960,7 +4951,7 @@
       </c>
       <c r="U20" s="49"/>
     </row>
-    <row r="21" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>193</v>
       </c>
@@ -5022,7 +5013,7 @@
       </c>
       <c r="U21" s="49"/>
     </row>
-    <row r="22" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>43</v>
       </c>
@@ -5084,7 +5075,7 @@
       </c>
       <c r="U22" s="49"/>
     </row>
-    <row r="23" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>201</v>
       </c>
@@ -5146,7 +5137,7 @@
       </c>
       <c r="U23" s="49"/>
     </row>
-    <row r="24" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>204</v>
       </c>
@@ -5208,7 +5199,7 @@
       </c>
       <c r="U24" s="49"/>
     </row>
-    <row r="25" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>206</v>
       </c>
@@ -5270,7 +5261,7 @@
       </c>
       <c r="U25" s="49"/>
     </row>
-    <row r="26" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>207</v>
       </c>
@@ -5332,7 +5323,7 @@
       </c>
       <c r="U26" s="49"/>
     </row>
-    <row r="27" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
         <v>172</v>
       </c>
@@ -5394,7 +5385,7 @@
       </c>
       <c r="U27" s="49"/>
     </row>
-    <row r="28" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>210</v>
       </c>
@@ -5456,7 +5447,7 @@
       </c>
       <c r="U28" s="49"/>
     </row>
-    <row r="29" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
         <v>213</v>
       </c>
@@ -5518,7 +5509,7 @@
       </c>
       <c r="U29" s="49"/>
     </row>
-    <row r="30" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>217</v>
       </c>
@@ -5580,7 +5571,7 @@
       </c>
       <c r="U30" s="49"/>
     </row>
-    <row r="31" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>218</v>
       </c>
@@ -5642,7 +5633,7 @@
       </c>
       <c r="U31" s="49"/>
     </row>
-    <row r="32" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>81</v>
       </c>
@@ -5704,7 +5695,7 @@
       </c>
       <c r="U32" s="49"/>
     </row>
-    <row r="33" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>91</v>
       </c>
@@ -5766,7 +5757,7 @@
       </c>
       <c r="U33" s="49"/>
     </row>
-    <row r="34" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
         <v>91</v>
       </c>
@@ -5828,7 +5819,7 @@
       </c>
       <c r="U34" s="49"/>
     </row>
-    <row r="35" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>91</v>
       </c>
@@ -5890,7 +5881,7 @@
       </c>
       <c r="U35" s="49"/>
     </row>
-    <row r="36" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>91</v>
       </c>
@@ -5952,7 +5943,7 @@
       </c>
       <c r="U36" s="49"/>
     </row>
-    <row r="37" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>91</v>
       </c>
@@ -6014,7 +6005,7 @@
       </c>
       <c r="U37" s="49"/>
     </row>
-    <row r="38" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
         <v>226</v>
       </c>
@@ -6076,7 +6067,7 @@
       </c>
       <c r="U38" s="49"/>
     </row>
-    <row r="39" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>228</v>
       </c>
@@ -6138,7 +6129,7 @@
       </c>
       <c r="U39" s="49"/>
     </row>
-    <row r="40" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>91</v>
       </c>
@@ -6200,7 +6191,7 @@
       </c>
       <c r="U40" s="49"/>
     </row>
-    <row r="41" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>231</v>
       </c>
@@ -6262,7 +6253,7 @@
       </c>
       <c r="U41" s="49"/>
     </row>
-    <row r="42" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>234</v>
       </c>
@@ -6324,7 +6315,7 @@
       </c>
       <c r="U42" s="49"/>
     </row>
-    <row r="43" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>236</v>
       </c>
@@ -6386,7 +6377,7 @@
       </c>
       <c r="U43" s="49"/>
     </row>
-    <row r="44" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>237</v>
       </c>
@@ -6448,7 +6439,7 @@
       </c>
       <c r="U44" s="49"/>
     </row>
-    <row r="45" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>238</v>
       </c>
@@ -6510,7 +6501,7 @@
       </c>
       <c r="U45" s="49"/>
     </row>
-    <row r="46" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
         <v>240</v>
       </c>
@@ -6572,7 +6563,7 @@
       </c>
       <c r="U46" s="49"/>
     </row>
-    <row r="47" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>91</v>
       </c>
@@ -6634,7 +6625,7 @@
       </c>
       <c r="U47" s="49"/>
     </row>
-    <row r="48" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>243</v>
       </c>
@@ -6696,7 +6687,7 @@
       </c>
       <c r="U48" s="49"/>
     </row>
-    <row r="49" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>246</v>
       </c>
@@ -6758,7 +6749,7 @@
       </c>
       <c r="U49" s="49"/>
     </row>
-    <row r="50" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
         <v>248</v>
       </c>
@@ -6820,7 +6811,7 @@
       </c>
       <c r="U50" s="49"/>
     </row>
-    <row r="51" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
         <v>250</v>
       </c>
@@ -6882,7 +6873,7 @@
       </c>
       <c r="U51" s="49"/>
     </row>
-    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
         <v>250</v>
       </c>
@@ -6944,7 +6935,7 @@
       </c>
       <c r="U52" s="49"/>
     </row>
-    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>253</v>
       </c>
@@ -7006,7 +6997,7 @@
       </c>
       <c r="U53" s="49"/>
     </row>
-    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>256</v>
       </c>
@@ -7068,7 +7059,7 @@
       </c>
       <c r="U54" s="49"/>
     </row>
-    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>258</v>
       </c>
@@ -7130,7 +7121,7 @@
       </c>
       <c r="U55" s="49"/>
     </row>
-    <row r="56" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
         <v>259</v>
       </c>
@@ -7192,7 +7183,7 @@
       </c>
       <c r="U56" s="49"/>
     </row>
-    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A57" s="8" t="s">
         <v>259</v>
       </c>
@@ -7254,7 +7245,7 @@
       </c>
       <c r="U57" s="49"/>
     </row>
-    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A58" s="8" t="s">
         <v>253</v>
       </c>
@@ -7316,7 +7307,7 @@
       </c>
       <c r="U58" s="49"/>
     </row>
-    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A59" s="8" t="s">
         <v>265</v>
       </c>
@@ -7378,7 +7369,7 @@
       </c>
       <c r="U59" s="49"/>
     </row>
-    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A60" s="8" t="s">
         <v>267</v>
       </c>
@@ -7440,7 +7431,7 @@
       </c>
       <c r="U60" s="49"/>
     </row>
-    <row r="61" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A61" s="8" t="s">
         <v>271</v>
       </c>
@@ -7502,7 +7493,7 @@
       </c>
       <c r="U61" s="49"/>
     </row>
-    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A62" s="8" t="s">
         <v>43</v>
       </c>
@@ -7564,7 +7555,7 @@
       </c>
       <c r="U62" s="49"/>
     </row>
-    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
         <v>58</v>
       </c>
@@ -7626,7 +7617,7 @@
       </c>
       <c r="U63" s="49"/>
     </row>
-    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A64" s="8" t="s">
         <v>91</v>
       </c>
@@ -7688,7 +7679,7 @@
       </c>
       <c r="U64" s="49"/>
     </row>
-    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A65" s="8" t="s">
         <v>91</v>
       </c>
@@ -7750,7 +7741,7 @@
       </c>
       <c r="U65" s="49"/>
     </row>
-    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A66" s="8" t="s">
         <v>91</v>
       </c>
@@ -7812,7 +7803,7 @@
       </c>
       <c r="U66" s="49"/>
     </row>
-    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A67" s="8" t="s">
         <v>282</v>
       </c>
@@ -7874,7 +7865,7 @@
       </c>
       <c r="U67" s="49"/>
     </row>
-    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>285</v>
       </c>
@@ -7936,7 +7927,7 @@
       </c>
       <c r="U68" s="49"/>
     </row>
-    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A69" s="8" t="s">
         <v>286</v>
       </c>
@@ -7998,7 +7989,7 @@
       </c>
       <c r="U69" s="49"/>
     </row>
-    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A70" s="16" t="s">
         <v>288</v>
       </c>
@@ -8060,7 +8051,7 @@
       </c>
       <c r="U70" s="49"/>
     </row>
-    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>291</v>
       </c>
@@ -8122,7 +8113,7 @@
       </c>
       <c r="U71" s="49"/>
     </row>
-    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>292</v>
       </c>
@@ -8184,7 +8175,7 @@
       </c>
       <c r="U72" s="49"/>
     </row>
-    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A73" s="8" t="s">
         <v>91</v>
       </c>
@@ -8246,7 +8237,7 @@
       </c>
       <c r="U73" s="49"/>
     </row>
-    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A74" s="8" t="s">
         <v>294</v>
       </c>
@@ -8308,7 +8299,7 @@
       </c>
       <c r="U74" s="49"/>
     </row>
-    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A75" s="8" t="s">
         <v>91</v>
       </c>
@@ -8370,7 +8361,7 @@
       </c>
       <c r="U75" s="49"/>
     </row>
-    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A76" s="8" t="s">
         <v>299</v>
       </c>
@@ -8432,7 +8423,7 @@
       </c>
       <c r="U76" s="49"/>
     </row>
-    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A77" s="8" t="s">
         <v>18</v>
       </c>
@@ -8494,7 +8485,7 @@
       </c>
       <c r="U77" s="49"/>
     </row>
-    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A78" s="8" t="s">
         <v>27</v>
       </c>
@@ -8556,7 +8547,7 @@
       </c>
       <c r="U78" s="49"/>
     </row>
-    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>30</v>
       </c>
@@ -8618,7 +8609,7 @@
       </c>
       <c r="U79" s="49"/>
     </row>
-    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A80" s="8" t="s">
         <v>35</v>
       </c>
@@ -8680,7 +8671,7 @@
       </c>
       <c r="U80" s="49"/>
     </row>
-    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A81" s="8" t="s">
         <v>35</v>
       </c>
@@ -8742,7 +8733,7 @@
       </c>
       <c r="U81" s="49"/>
     </row>
-    <row r="82" spans="1:21" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="8" t="s">
         <v>35</v>
       </c>
@@ -8804,7 +8795,7 @@
       </c>
       <c r="U82" s="49"/>
     </row>
-    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A83" s="8" t="s">
         <v>43</v>
       </c>
@@ -8866,7 +8857,7 @@
       </c>
       <c r="U83" s="49"/>
     </row>
-    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A84" s="8" t="s">
         <v>43</v>
       </c>
@@ -8928,7 +8919,7 @@
       </c>
       <c r="U84" s="49"/>
     </row>
-    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A85" s="8" t="s">
         <v>52</v>
       </c>
@@ -8990,7 +8981,7 @@
       </c>
       <c r="U85" s="49"/>
     </row>
-    <row r="86" spans="1:21" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="2" t="s">
         <v>55</v>
       </c>
@@ -9052,7 +9043,7 @@
       </c>
       <c r="U86" s="49"/>
     </row>
-    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A87" s="16" t="s">
         <v>58</v>
       </c>
@@ -9114,7 +9105,7 @@
       </c>
       <c r="U87" s="49"/>
     </row>
-    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A88" s="8" t="s">
         <v>62</v>
       </c>
@@ -9176,7 +9167,7 @@
       </c>
       <c r="U88" s="49"/>
     </row>
-    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A89" s="8" t="s">
         <v>65</v>
       </c>
@@ -9238,7 +9229,7 @@
       </c>
       <c r="U89" s="49"/>
     </row>
-    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A90" s="8" t="s">
         <v>67</v>
       </c>
@@ -9300,7 +9291,7 @@
       </c>
       <c r="U90" s="49"/>
     </row>
-    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A91" s="8" t="s">
         <v>70</v>
       </c>
@@ -9362,7 +9353,7 @@
       </c>
       <c r="U91" s="49"/>
     </row>
-    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A92" s="8" t="s">
         <v>75</v>
       </c>
@@ -9424,7 +9415,7 @@
       </c>
       <c r="U92" s="49"/>
     </row>
-    <row r="93" spans="1:21" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="23" t="s">
         <v>77</v>
       </c>
@@ -9486,7 +9477,7 @@
       </c>
       <c r="U93" s="49"/>
     </row>
-    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A94" s="8" t="s">
         <v>43</v>
       </c>
@@ -9548,7 +9539,7 @@
       </c>
       <c r="U94" s="49"/>
     </row>
-    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A95" s="8" t="s">
         <v>81</v>
       </c>
@@ -9610,7 +9601,7 @@
       </c>
       <c r="U95" s="49"/>
     </row>
-    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>85</v>
       </c>
@@ -9672,7 +9663,7 @@
       </c>
       <c r="U96" s="49"/>
     </row>
-    <row r="97" spans="1:21" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="6" t="s">
         <v>86</v>
       </c>
@@ -9734,7 +9725,7 @@
       </c>
       <c r="U97" s="49"/>
     </row>
-    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98" s="8" t="s">
         <v>88</v>
       </c>
@@ -9796,7 +9787,7 @@
       </c>
       <c r="U98" s="49"/>
     </row>
-    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99" s="8" t="s">
         <v>91</v>
       </c>
@@ -9858,7 +9849,7 @@
       </c>
       <c r="U99" s="49"/>
     </row>
-    <row r="100" spans="1:21" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="23" t="s">
         <v>95</v>
       </c>
@@ -9920,7 +9911,7 @@
       </c>
       <c r="U100" s="49"/>
     </row>
-    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101" s="8" t="s">
         <v>58</v>
       </c>
@@ -9982,7 +9973,7 @@
       </c>
       <c r="U101" s="49"/>
     </row>
-    <row r="102" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102" s="16" t="s">
         <v>58</v>
       </c>
@@ -10044,7 +10035,7 @@
       </c>
       <c r="U102" s="49"/>
     </row>
-    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A103" s="8" t="s">
         <v>43</v>
       </c>
@@ -10106,7 +10097,7 @@
       </c>
       <c r="U103" s="49"/>
     </row>
-    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104" s="8" t="s">
         <v>103</v>
       </c>
@@ -10168,7 +10159,7 @@
       </c>
       <c r="U104" s="49"/>
     </row>
-    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>106</v>
       </c>
@@ -10230,7 +10221,7 @@
       </c>
       <c r="U105" s="49"/>
     </row>
-    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>81</v>
       </c>
@@ -10292,7 +10283,7 @@
       </c>
       <c r="U106" s="49"/>
     </row>
-    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>107</v>
       </c>
@@ -10354,7 +10345,7 @@
       </c>
       <c r="U107" s="49"/>
     </row>
-    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>108</v>
       </c>
@@ -10416,7 +10407,7 @@
       </c>
       <c r="U108" s="49"/>
     </row>
-    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>109</v>
       </c>
@@ -10478,7 +10469,7 @@
       </c>
       <c r="U109" s="49"/>
     </row>
-    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A110" s="8" t="s">
         <v>110</v>
       </c>
@@ -10540,7 +10531,7 @@
       </c>
       <c r="U110" s="49"/>
     </row>
-    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A111" s="8" t="s">
         <v>113</v>
       </c>
@@ -10602,7 +10593,7 @@
       </c>
       <c r="U111" s="49"/>
     </row>
-    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>116</v>
       </c>
@@ -10664,7 +10655,7 @@
       </c>
       <c r="U112" s="49"/>
     </row>
-    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A113" s="8" t="s">
         <v>120</v>
       </c>
@@ -10726,7 +10717,7 @@
       </c>
       <c r="U113" s="49"/>
     </row>
-    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A114" s="8" t="s">
         <v>123</v>
       </c>
@@ -10788,7 +10779,7 @@
       </c>
       <c r="U114" s="49"/>
     </row>
-    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A115" s="8" t="s">
         <v>110</v>
       </c>
@@ -10850,7 +10841,7 @@
       </c>
       <c r="U115" s="49"/>
     </row>
-    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A116" s="8" t="s">
         <v>127</v>
       </c>
@@ -10912,7 +10903,7 @@
       </c>
       <c r="U116" s="49"/>
     </row>
-    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>130</v>
       </c>
@@ -10974,7 +10965,7 @@
       </c>
       <c r="U117" s="49"/>
     </row>
-    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>131</v>
       </c>
@@ -11036,7 +11027,7 @@
       </c>
       <c r="U118" s="49"/>
     </row>
-    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A119" s="8" t="s">
         <v>132</v>
       </c>
@@ -11098,7 +11089,7 @@
       </c>
       <c r="U119" s="49"/>
     </row>
-    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A120" s="8" t="s">
         <v>134</v>
       </c>
@@ -11160,7 +11151,7 @@
       </c>
       <c r="U120" s="49"/>
     </row>
-    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A121" s="8" t="s">
         <v>134</v>
       </c>
@@ -11222,7 +11213,7 @@
       </c>
       <c r="U121" s="49"/>
     </row>
-    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A122" s="8" t="s">
         <v>140</v>
       </c>
@@ -11284,7 +11275,7 @@
       </c>
       <c r="U122" s="49"/>
     </row>
-    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A123" s="8" t="s">
         <v>143</v>
       </c>
@@ -11346,7 +11337,7 @@
       </c>
       <c r="U123" s="49"/>
     </row>
-    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A124" s="8" t="s">
         <v>145</v>
       </c>
@@ -11408,7 +11399,7 @@
       </c>
       <c r="U124" s="49"/>
     </row>
-    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A125" s="8" t="s">
         <v>149</v>
       </c>
@@ -11470,7 +11461,7 @@
       </c>
       <c r="U125" s="49"/>
     </row>
-    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A126" s="8" t="s">
         <v>143</v>
       </c>
@@ -11532,7 +11523,7 @@
       </c>
       <c r="U126" s="49"/>
     </row>
-    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A127" s="8" t="s">
         <v>301</v>
       </c>
@@ -11598,7 +11589,7 @@
       </c>
       <c r="U127" s="49"/>
     </row>
-    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A128" s="8" t="s">
         <v>305</v>
       </c>
@@ -11664,7 +11655,7 @@
       </c>
       <c r="U128" s="49"/>
     </row>
-    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A129" s="8" t="s">
         <v>145</v>
       </c>
@@ -11730,7 +11721,7 @@
       </c>
       <c r="U129" s="49"/>
     </row>
-    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>308</v>
       </c>
@@ -11796,7 +11787,7 @@
       </c>
       <c r="U130" s="49"/>
     </row>
-    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
         <v>309</v>
       </c>
@@ -11862,7 +11853,7 @@
       </c>
       <c r="U131" s="49"/>
     </row>
-    <row r="132" spans="1:21" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:21" s="20" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A132" s="16" t="s">
         <v>311</v>
       </c>
@@ -11928,7 +11919,7 @@
       </c>
       <c r="U132" s="49"/>
     </row>
-    <row r="133" spans="1:21" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:21" s="20" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A133" s="8" t="s">
         <v>311</v>
       </c>
@@ -11994,7 +11985,7 @@
       </c>
       <c r="U133" s="49"/>
     </row>
-    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A134" s="8" t="s">
         <v>317</v>
       </c>
@@ -12060,7 +12051,7 @@
       </c>
       <c r="U134" s="49"/>
     </row>
-    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
         <v>320</v>
       </c>
@@ -12126,7 +12117,7 @@
       </c>
       <c r="U135" s="49"/>
     </row>
-    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
         <v>321</v>
       </c>
@@ -12192,7 +12183,7 @@
       </c>
       <c r="U136" s="49"/>
     </row>
-    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
         <v>321</v>
       </c>
@@ -12258,7 +12249,7 @@
       </c>
       <c r="U137" s="49"/>
     </row>
-    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A138" s="5" t="s">
         <v>322</v>
       </c>
@@ -12324,7 +12315,7 @@
       </c>
       <c r="U138" s="49"/>
     </row>
-    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
         <v>323</v>
       </c>
@@ -12390,7 +12381,7 @@
       </c>
       <c r="U139" s="49"/>
     </row>
-    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>324</v>
       </c>
@@ -12456,7 +12447,7 @@
       </c>
       <c r="U140" s="49"/>
     </row>
-    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>326</v>
       </c>
@@ -12522,7 +12513,7 @@
       </c>
       <c r="U141" s="49"/>
     </row>
-    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A142" s="8" t="s">
         <v>328</v>
       </c>
@@ -12588,7 +12579,7 @@
       </c>
       <c r="U142" s="49"/>
     </row>
-    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A143" s="8" t="s">
         <v>331</v>
       </c>
@@ -12654,7 +12645,7 @@
       </c>
       <c r="U143" s="49"/>
     </row>
-    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A144" s="8" t="s">
         <v>333</v>
       </c>
@@ -12720,7 +12711,7 @@
       </c>
       <c r="U144" s="49"/>
     </row>
-    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A145" s="8" t="s">
         <v>335</v>
       </c>
@@ -12786,7 +12777,7 @@
       </c>
       <c r="U145" s="49"/>
     </row>
-    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A146" s="8" t="s">
         <v>140</v>
       </c>
@@ -12852,7 +12843,7 @@
       </c>
       <c r="U146" s="49"/>
     </row>
-    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A147" s="8" t="s">
         <v>140</v>
       </c>
@@ -12918,7 +12909,7 @@
       </c>
       <c r="U147" s="49"/>
     </row>
-    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A148" s="16" t="s">
         <v>58</v>
       </c>
@@ -12984,7 +12975,7 @@
       </c>
       <c r="U148" s="49"/>
     </row>
-    <row r="149" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A149" s="8" t="s">
         <v>344</v>
       </c>
@@ -13052,7 +13043,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="150" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A150" s="8" t="s">
         <v>348</v>
       </c>
@@ -13120,7 +13111,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="151" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A151" s="8" t="s">
         <v>324</v>
       </c>
@@ -13188,7 +13179,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="152" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A152" s="8" t="s">
         <v>350</v>
       </c>
@@ -13256,7 +13247,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="153" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A153" s="8" t="s">
         <v>354</v>
       </c>
@@ -13324,7 +13315,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="154" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A154" s="8" t="s">
         <v>145</v>
       </c>
@@ -13392,7 +13383,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="155" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A155" s="8" t="s">
         <v>359</v>
       </c>
@@ -13460,7 +13451,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="156" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A156" s="8" t="s">
         <v>360</v>
       </c>
@@ -13528,7 +13519,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="157" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A157" s="8" t="s">
         <v>43</v>
       </c>
@@ -13596,7 +13587,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="158" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A158" s="8" t="s">
         <v>362</v>
       </c>
@@ -13664,7 +13655,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="159" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>43</v>
       </c>
@@ -13732,7 +13723,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="160" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>367</v>
       </c>
@@ -13800,7 +13791,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="161" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A161" s="8" t="s">
         <v>369</v>
       </c>
@@ -13868,7 +13859,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="162" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A162" s="8" t="s">
         <v>371</v>
       </c>
@@ -13936,7 +13927,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="163" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A163" s="8" t="s">
         <v>43</v>
       </c>
@@ -14004,7 +13995,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="164" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A164" s="8" t="s">
         <v>374</v>
       </c>
@@ -14072,7 +14063,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="165" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A165" s="8" t="s">
         <v>374</v>
       </c>
@@ -14140,7 +14131,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="166" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A166" s="8" t="s">
         <v>374</v>
       </c>
@@ -14208,7 +14199,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="167" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A167" s="8" t="s">
         <v>374</v>
       </c>
@@ -14276,7 +14267,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="168" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A168" s="8" t="s">
         <v>374</v>
       </c>
@@ -14344,7 +14335,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="169" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A169" s="8" t="s">
         <v>374</v>
       </c>
@@ -14412,7 +14403,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A170" s="8" t="s">
         <v>374</v>
       </c>
@@ -14480,7 +14471,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A171" s="8" t="s">
         <v>374</v>
       </c>
@@ -14548,7 +14539,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="172" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A172" s="8" t="s">
         <v>374</v>
       </c>
@@ -14616,7 +14607,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="173" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A173" s="8" t="s">
         <v>374</v>
       </c>
@@ -14684,7 +14675,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="174" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A174" s="8" t="s">
         <v>374</v>
       </c>
@@ -14752,7 +14743,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="175" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A175" s="8" t="s">
         <v>374</v>
       </c>
@@ -14820,7 +14811,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="176" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A176" s="8" t="s">
         <v>374</v>
       </c>
@@ -14888,7 +14879,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="177" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A177" s="8" t="s">
         <v>374</v>
       </c>
@@ -14956,7 +14947,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="178" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A178" s="8" t="s">
         <v>374</v>
       </c>
@@ -15024,7 +15015,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="179" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A179" s="8" t="s">
         <v>374</v>
       </c>
@@ -15092,7 +15083,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="180" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A180" s="8" t="s">
         <v>408</v>
       </c>
@@ -15160,7 +15151,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="181" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A181" s="16" t="s">
         <v>411</v>
       </c>
@@ -15228,7 +15219,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="182" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A182" s="8" t="s">
         <v>414</v>
       </c>
@@ -15296,7 +15287,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="183" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A183" s="8" t="s">
         <v>416</v>
       </c>
@@ -15364,7 +15355,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="184" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A184" s="8" t="s">
         <v>416</v>
       </c>
@@ -15432,7 +15423,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="185" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>419</v>
       </c>
@@ -15500,7 +15491,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="186" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A186" s="5" t="s">
         <v>421</v>
       </c>
@@ -15568,7 +15559,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="187" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A187" s="8" t="s">
         <v>422</v>
       </c>
@@ -15636,7 +15627,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="188" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A188" s="8" t="s">
         <v>422</v>
       </c>
@@ -15704,7 +15695,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="189" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A189" s="8" t="s">
         <v>428</v>
       </c>
@@ -15772,7 +15763,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="190" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A190" s="8" t="s">
         <v>430</v>
       </c>
@@ -15839,7 +15830,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="191" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A191" s="8" t="s">
         <v>432</v>
       </c>
@@ -15906,7 +15897,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="192" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A192" s="8" t="s">
         <v>432</v>
       </c>
@@ -15973,7 +15964,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="193" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A193" s="8" t="s">
         <v>437</v>
       </c>
@@ -16040,7 +16031,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="194" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A194" s="8" t="s">
         <v>438</v>
       </c>
@@ -16107,7 +16098,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="195" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A195" s="8" t="s">
         <v>439</v>
       </c>
@@ -16174,7 +16165,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="196" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A196" s="8" t="s">
         <v>445</v>
       </c>
@@ -16241,7 +16232,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="197" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A197" s="8" t="s">
         <v>432</v>
       </c>
@@ -16308,7 +16299,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="198" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A198" s="8" t="s">
         <v>134</v>
       </c>
@@ -16375,7 +16366,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="199" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A199" s="8" t="s">
         <v>451</v>
       </c>
@@ -16442,7 +16433,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="200" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A200" s="8" t="s">
         <v>451</v>
       </c>
@@ -16509,7 +16500,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="201" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A201" s="8" t="s">
         <v>134</v>
       </c>
@@ -16576,7 +16567,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="202" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A202" s="8" t="s">
         <v>456</v>
       </c>
@@ -16643,7 +16634,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="203" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A203" s="8" t="s">
         <v>43</v>
       </c>
@@ -16710,7 +16701,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="204" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A204" s="8" t="s">
         <v>459</v>
       </c>
@@ -16777,7 +16768,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="205" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A205" s="8" t="s">
         <v>461</v>
       </c>
@@ -16844,7 +16835,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="206" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A206" s="8" t="s">
         <v>462</v>
       </c>
@@ -16912,7 +16903,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="207" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A207" s="8" t="s">
         <v>451</v>
       </c>
@@ -16980,7 +16971,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="208" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A208" s="8" t="s">
         <v>451</v>
       </c>
@@ -17048,7 +17039,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="209" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A209" s="7" t="s">
         <v>466</v>
       </c>
@@ -17116,7 +17107,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="210" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A210" s="8" t="s">
         <v>469</v>
       </c>
@@ -17184,7 +17175,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="211" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A211" s="8" t="s">
         <v>471</v>
       </c>
@@ -17252,7 +17243,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="212" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>473</v>
       </c>
@@ -17320,7 +17311,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="213" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A213" s="8" t="s">
         <v>120</v>
       </c>
@@ -17388,7 +17379,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="214" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A214" s="8" t="s">
         <v>476</v>
       </c>
@@ -17456,7 +17447,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="215" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A215" s="8" t="s">
         <v>469</v>
       </c>
@@ -17524,7 +17515,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="216" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A216" s="8" t="s">
         <v>58</v>
       </c>
@@ -17592,7 +17583,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="217" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A217" s="8" t="s">
         <v>481</v>
       </c>
@@ -17660,7 +17651,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="218" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>483</v>
       </c>
@@ -17728,7 +17719,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="219" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>484</v>
       </c>
@@ -17796,7 +17787,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="220" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>271</v>
       </c>
@@ -17864,7 +17855,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="221" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A221" s="8" t="s">
         <v>485</v>
       </c>
@@ -17932,7 +17923,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="222" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A222" s="8" t="s">
         <v>172</v>
       </c>
@@ -18000,7 +17991,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="223" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A223" s="8" t="s">
         <v>489</v>
       </c>
@@ -18068,7 +18059,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="224" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A224" s="8" t="s">
         <v>492</v>
       </c>
@@ -18136,7 +18127,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="225" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>495</v>
       </c>
@@ -18204,7 +18195,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="226" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>499</v>
       </c>
@@ -18272,7 +18263,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="227" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>502</v>
       </c>
@@ -18340,7 +18331,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="228" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>503</v>
       </c>
@@ -18408,7 +18399,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="229" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A229" s="5" t="s">
         <v>505</v>
       </c>
@@ -18476,7 +18467,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="230" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A230" s="5" t="s">
         <v>506</v>
       </c>
@@ -18544,7 +18535,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="231" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A231" s="5" t="s">
         <v>507</v>
       </c>
@@ -18612,7 +18603,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="232" spans="1:21" s="51" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:21" s="51" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A232" s="5" t="s">
         <v>508</v>
       </c>
@@ -18680,7 +18671,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="233" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>509</v>
       </c>
@@ -18747,7 +18738,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="234" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>514</v>
       </c>
@@ -18814,7 +18805,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="235" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A235" s="44" t="s">
         <v>516</v>
       </c>
@@ -18882,7 +18873,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="236" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A236" s="8" t="s">
         <v>516</v>
       </c>
@@ -18950,7 +18941,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="237" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A237" s="8" t="s">
         <v>520</v>
       </c>
@@ -19018,7 +19009,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="238" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A238" s="8" t="s">
         <v>522</v>
       </c>
@@ -19086,7 +19077,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="239" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A239" s="8" t="s">
         <v>524</v>
       </c>
@@ -19154,7 +19145,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="240" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A240" s="8" t="s">
         <v>526</v>
       </c>
@@ -19222,7 +19213,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="241" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A241" s="8" t="s">
         <v>528</v>
       </c>
@@ -19290,7 +19281,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="242" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A242" s="8" t="s">
         <v>528</v>
       </c>
@@ -19358,7 +19349,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="243" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A243" s="8" t="s">
         <v>469</v>
       </c>
@@ -21130,7 +21121,7 @@
         <v>46122</v>
       </c>
       <c r="J269" s="18">
-        <f t="shared" ref="J269:J327" si="21">+NETWORKDAYS(H269,I269)</f>
+        <f t="shared" ref="J269:J329" si="21">+NETWORKDAYS(H269,I269)</f>
         <v>2</v>
       </c>
       <c r="K269" s="8" t="s">
@@ -21158,7 +21149,7 @@
         <v>46126</v>
       </c>
       <c r="S269" s="18">
-        <f t="shared" ref="S269:S327" si="22">NETWORKDAYS(H269,R269)</f>
+        <f t="shared" ref="S269:S329" si="22">NETWORKDAYS(H269,R269)</f>
         <v>4</v>
       </c>
       <c r="T269" s="7" t="s">
@@ -25083,25 +25074,153 @@
         <v>444</v>
       </c>
     </row>
+    <row r="328" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A328" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="B328" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C328" s="75">
+        <v>58649804</v>
+      </c>
+      <c r="D328" s="75" t="s">
+        <v>36</v>
+      </c>
+      <c r="E328" s="75" t="s">
+        <v>665</v>
+      </c>
+      <c r="F328" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G328" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="H328" s="76">
+        <v>46077</v>
+      </c>
+      <c r="I328" s="76">
+        <v>46141</v>
+      </c>
+      <c r="J328" s="18">
+        <f t="shared" si="21"/>
+        <v>47</v>
+      </c>
+      <c r="K328" s="75" t="s">
+        <v>353</v>
+      </c>
+      <c r="L328" s="75" t="s">
+        <v>668</v>
+      </c>
+      <c r="M328" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N328" s="75" t="s">
+        <v>73</v>
+      </c>
+      <c r="O328" s="75">
+        <v>500000</v>
+      </c>
+      <c r="P328" s="75">
+        <v>363324</v>
+      </c>
+      <c r="Q328" s="77">
+        <v>863324</v>
+      </c>
+      <c r="R328" s="76">
+        <v>46142</v>
+      </c>
+      <c r="S328" s="18">
+        <f t="shared" si="22"/>
+        <v>48</v>
+      </c>
+      <c r="T328" s="75" t="s">
+        <v>662</v>
+      </c>
+      <c r="U328" s="75" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="329" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A329" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="B329" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C329" s="75">
+        <v>61157877</v>
+      </c>
+      <c r="D329" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="E329" s="75" t="s">
+        <v>667</v>
+      </c>
+      <c r="F329" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G329" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H329" s="76">
+        <v>46119</v>
+      </c>
+      <c r="I329" s="76">
+        <v>46142</v>
+      </c>
+      <c r="J329" s="18">
+        <f t="shared" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="K329" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L329" s="75" t="s">
+        <v>310</v>
+      </c>
+      <c r="M329" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N329" s="75" t="s">
+        <v>29</v>
+      </c>
+      <c r="O329" s="75">
+        <v>500000</v>
+      </c>
+      <c r="P329" s="75">
+        <v>317989</v>
+      </c>
+      <c r="Q329" s="77">
+        <v>817989</v>
+      </c>
+      <c r="R329" s="76">
+        <v>46142</v>
+      </c>
+      <c r="S329" s="18">
+        <f t="shared" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="T329" s="75" t="s">
+        <v>662</v>
+      </c>
+      <c r="U329" s="75" t="s">
+        <v>551</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U327" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="17">
-      <filters>
-        <dateGroupItem year="2026" month="4" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:U327" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="87" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="85"/>
     <cfRule type="duplicateValues" dxfId="85" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C205 C244:C287 C304:C1048576">
-    <cfRule type="duplicateValues" dxfId="81" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C212 C244:C287 C304:C1048576">
     <cfRule type="duplicateValues" dxfId="79" priority="185"/>
@@ -25116,8 +25235,8 @@
     <cfRule type="duplicateValues" dxfId="76" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="75" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
     <cfRule type="duplicateValues" dxfId="73" priority="41"/>
@@ -25127,8 +25246,8 @@
     <cfRule type="duplicateValues" dxfId="71" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="70" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
     <cfRule type="duplicateValues" dxfId="68" priority="58"/>
@@ -25185,8 +25304,8 @@
     <cfRule type="duplicateValues" dxfId="51" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="50" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
     <cfRule type="duplicateValues" dxfId="48" priority="75"/>
@@ -25201,8 +25320,8 @@
     <cfRule type="duplicateValues" dxfId="45" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="44" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
     <cfRule type="duplicateValues" dxfId="42" priority="68"/>
@@ -25268,8 +25387,8 @@
     <cfRule type="duplicateValues" dxfId="18" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C208">
-    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218:C223">
     <cfRule type="duplicateValues" dxfId="15" priority="7"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="546" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D14E4064-EEEE-41A3-83C4-CC0848260AE6}"/>
+  <xr:revisionPtr revIDLastSave="564" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4F4BC86-029D-4C10-8E26-80863F14A635}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3484" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3612" uniqueCount="687">
   <si>
     <t>Client</t>
   </si>
@@ -2047,6 +2047,60 @@
   </si>
   <si>
     <t>MAIRIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CFAO MOBILITY COTE D'IVOIRE </t>
+  </si>
+  <si>
+    <t>SYTHD260085</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>PIL CI</t>
+  </si>
+  <si>
+    <t>SYTHD170017</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PLACE AFRICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RIVIERA</t>
+  </si>
+  <si>
+    <t>BOX AFRICA COCODY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHICKEN NATION </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASCOMA </t>
+  </si>
+  <si>
+    <t>SYTHD260107</t>
+  </si>
+  <si>
+    <t>BUVPN260075</t>
+  </si>
+  <si>
+    <t>CONNECTED NETWORKS SERVICES LTD</t>
+  </si>
+  <si>
+    <t>SYTHD260097</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MUGEFCI  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2720203600B </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BNI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2720303000B </t>
   </si>
 </sst>
 </file>
@@ -2060,7 +2114,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,##0\ _€"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2131,6 +2185,40 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0E0E0E"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -2249,7 +2337,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2465,6 +2553,45 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3688,7 +3815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U329"/>
+  <dimension ref="A1:W340"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="20" customWidth="1"/>
@@ -21121,7 +21248,7 @@
         <v>46122</v>
       </c>
       <c r="J269" s="18">
-        <f t="shared" ref="J269:J329" si="21">+NETWORKDAYS(H269,I269)</f>
+        <f t="shared" ref="J269:J332" si="21">+NETWORKDAYS(H269,I269)</f>
         <v>2</v>
       </c>
       <c r="K269" s="8" t="s">
@@ -21149,7 +21276,7 @@
         <v>46126</v>
       </c>
       <c r="S269" s="18">
-        <f t="shared" ref="S269:S329" si="22">NETWORKDAYS(H269,R269)</f>
+        <f t="shared" ref="S269:S332" si="22">NETWORKDAYS(H269,R269)</f>
         <v>4</v>
       </c>
       <c r="T269" s="7" t="s">
@@ -24605,7 +24732,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="321" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A321" s="8" t="s">
         <v>637</v>
       </c>
@@ -24672,7 +24799,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="322" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A322" s="8" t="s">
         <v>636</v>
       </c>
@@ -24739,7 +24866,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="323" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A323" s="8" t="s">
         <v>172</v>
       </c>
@@ -24806,7 +24933,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="324" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A324" s="8" t="s">
         <v>634</v>
       </c>
@@ -24873,7 +25000,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="325" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A325" s="8" t="s">
         <v>439</v>
       </c>
@@ -24940,7 +25067,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="326" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A326" s="8" t="s">
         <v>172</v>
       </c>
@@ -25007,7 +25134,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="327" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A327" s="8" t="s">
         <v>172</v>
       </c>
@@ -25074,7 +25201,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="328" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A328" s="8" t="s">
         <v>651</v>
       </c>
@@ -25141,7 +25268,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="329" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A329" s="8" t="s">
         <v>666</v>
       </c>
@@ -25208,35 +25335,794 @@
         <v>551</v>
       </c>
     </row>
+    <row r="330" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A330" s="75" t="s">
+        <v>669</v>
+      </c>
+      <c r="B330" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C330" s="75">
+        <v>59801109</v>
+      </c>
+      <c r="D330" s="75" t="s">
+        <v>460</v>
+      </c>
+      <c r="E330" s="75" t="s">
+        <v>670</v>
+      </c>
+      <c r="F330" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G330" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="H330" s="76">
+        <v>46128</v>
+      </c>
+      <c r="I330" s="76">
+        <v>46141</v>
+      </c>
+      <c r="J330" s="18">
+        <f t="shared" si="21"/>
+        <v>10</v>
+      </c>
+      <c r="K330" s="79" t="s">
+        <v>303</v>
+      </c>
+      <c r="L330" s="78" t="s">
+        <v>304</v>
+      </c>
+      <c r="M330" s="78" t="s">
+        <v>24</v>
+      </c>
+      <c r="N330" s="75" t="s">
+        <v>29</v>
+      </c>
+      <c r="O330" s="90">
+        <v>0</v>
+      </c>
+      <c r="P330" s="90">
+        <v>0</v>
+      </c>
+      <c r="Q330" s="40">
+        <f>P330+O330</f>
+        <v>0</v>
+      </c>
+      <c r="R330" s="80">
+        <v>46143</v>
+      </c>
+      <c r="S330" s="18">
+        <f t="shared" si="22"/>
+        <v>12</v>
+      </c>
+      <c r="T330" s="78" t="s">
+        <v>671</v>
+      </c>
+      <c r="U330" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="W330" s="50"/>
+    </row>
+    <row r="331" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A331" s="75" t="s">
+        <v>672</v>
+      </c>
+      <c r="B331" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C331" s="81">
+        <v>61532967</v>
+      </c>
+      <c r="D331" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="E331" s="75" t="s">
+        <v>673</v>
+      </c>
+      <c r="F331" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="G331" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H331" s="76">
+        <v>46126</v>
+      </c>
+      <c r="I331" s="82">
+        <v>46141</v>
+      </c>
+      <c r="J331" s="18">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="K331" s="79" t="s">
+        <v>303</v>
+      </c>
+      <c r="L331" s="78" t="s">
+        <v>304</v>
+      </c>
+      <c r="M331" s="80" t="s">
+        <v>48</v>
+      </c>
+      <c r="N331" s="75" t="s">
+        <v>61</v>
+      </c>
+      <c r="O331" s="77">
+        <v>423729</v>
+      </c>
+      <c r="P331" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q331" s="91">
+        <f>P331+O331</f>
+        <v>423729</v>
+      </c>
+      <c r="R331" s="80">
+        <v>46146</v>
+      </c>
+      <c r="S331" s="18">
+        <f t="shared" si="22"/>
+        <v>15</v>
+      </c>
+      <c r="T331" s="78" t="s">
+        <v>671</v>
+      </c>
+      <c r="U331" s="78" t="s">
+        <v>551</v>
+      </c>
+      <c r="W331" s="50"/>
+    </row>
+    <row r="332" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A332" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B332" s="75" t="s">
+        <v>31</v>
+      </c>
+      <c r="C332" s="1">
+        <v>61918089</v>
+      </c>
+      <c r="D332" s="75" t="s">
+        <v>675</v>
+      </c>
+      <c r="E332" s="1">
+        <v>2722229780</v>
+      </c>
+      <c r="F332" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G332" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H332" s="76">
+        <v>46132</v>
+      </c>
+      <c r="I332" s="76">
+        <v>46146</v>
+      </c>
+      <c r="J332" s="18">
+        <f t="shared" si="21"/>
+        <v>11</v>
+      </c>
+      <c r="K332" s="79" t="s">
+        <v>303</v>
+      </c>
+      <c r="L332" s="78" t="s">
+        <v>304</v>
+      </c>
+      <c r="M332" s="78" t="s">
+        <v>24</v>
+      </c>
+      <c r="N332" s="78" t="s">
+        <v>42</v>
+      </c>
+      <c r="O332" s="11">
+        <v>570000</v>
+      </c>
+      <c r="P332" s="1">
+        <v>221635</v>
+      </c>
+      <c r="Q332" s="91">
+        <f>P332+O332</f>
+        <v>791635</v>
+      </c>
+      <c r="R332" s="80">
+        <v>46146</v>
+      </c>
+      <c r="S332" s="18">
+        <f t="shared" si="22"/>
+        <v>11</v>
+      </c>
+      <c r="T332" s="78" t="s">
+        <v>671</v>
+      </c>
+      <c r="U332" s="78" t="s">
+        <v>551</v>
+      </c>
+      <c r="W332" s="50"/>
+    </row>
+    <row r="333" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A333" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B333" s="75" t="s">
+        <v>31</v>
+      </c>
+      <c r="C333" s="1">
+        <v>61915874</v>
+      </c>
+      <c r="D333" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="E333" s="1">
+        <v>2722229770</v>
+      </c>
+      <c r="F333" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G333" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H333" s="76">
+        <v>46132</v>
+      </c>
+      <c r="I333" s="76">
+        <v>46146</v>
+      </c>
+      <c r="J333" s="18">
+        <f t="shared" ref="J333:J340" si="28">+NETWORKDAYS(H333,I333)</f>
+        <v>11</v>
+      </c>
+      <c r="K333" s="79" t="s">
+        <v>303</v>
+      </c>
+      <c r="L333" s="78" t="s">
+        <v>304</v>
+      </c>
+      <c r="M333" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="N333" s="75" t="s">
+        <v>57</v>
+      </c>
+      <c r="O333" s="11">
+        <v>270000</v>
+      </c>
+      <c r="P333" s="1">
+        <v>111435</v>
+      </c>
+      <c r="Q333" s="91">
+        <f>P333+O333</f>
+        <v>381435</v>
+      </c>
+      <c r="R333" s="80">
+        <v>46146</v>
+      </c>
+      <c r="S333" s="18">
+        <f t="shared" ref="S333:S340" si="29">NETWORKDAYS(H333,R333)</f>
+        <v>11</v>
+      </c>
+      <c r="T333" s="78" t="s">
+        <v>671</v>
+      </c>
+      <c r="U333" s="78" t="s">
+        <v>551</v>
+      </c>
+      <c r="W333" s="50"/>
+    </row>
+    <row r="334" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A334" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B334" s="83" t="s">
+        <v>31</v>
+      </c>
+      <c r="C334" s="1">
+        <v>62248200</v>
+      </c>
+      <c r="D334" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="E334" s="1">
+        <v>2721712130</v>
+      </c>
+      <c r="F334" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G334" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H334" s="76">
+        <v>46137</v>
+      </c>
+      <c r="I334" s="76">
+        <v>46146</v>
+      </c>
+      <c r="J334" s="18">
+        <f t="shared" si="28"/>
+        <v>6</v>
+      </c>
+      <c r="K334" s="79" t="s">
+        <v>303</v>
+      </c>
+      <c r="L334" s="78" t="s">
+        <v>304</v>
+      </c>
+      <c r="M334" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="N334" s="75" t="s">
+        <v>57</v>
+      </c>
+      <c r="O334" s="11">
+        <v>270000</v>
+      </c>
+      <c r="P334" s="1">
+        <v>111435</v>
+      </c>
+      <c r="Q334" s="91">
+        <f>P334+O334</f>
+        <v>381435</v>
+      </c>
+      <c r="R334" s="80">
+        <v>46146</v>
+      </c>
+      <c r="S334" s="18">
+        <f t="shared" si="29"/>
+        <v>6</v>
+      </c>
+      <c r="T334" s="78" t="s">
+        <v>671</v>
+      </c>
+      <c r="U334" s="78" t="s">
+        <v>551</v>
+      </c>
+      <c r="W334" s="50"/>
+    </row>
+    <row r="335" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A335" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B335" s="83" t="s">
+        <v>31</v>
+      </c>
+      <c r="C335" s="1">
+        <v>61702223</v>
+      </c>
+      <c r="D335" s="75" t="s">
+        <v>490</v>
+      </c>
+      <c r="E335" s="1">
+        <v>2721387638</v>
+      </c>
+      <c r="F335" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G335" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H335" s="76">
+        <v>46128</v>
+      </c>
+      <c r="I335" s="84">
+        <v>46142</v>
+      </c>
+      <c r="J335" s="18">
+        <f t="shared" si="28"/>
+        <v>11</v>
+      </c>
+      <c r="K335" s="79" t="s">
+        <v>303</v>
+      </c>
+      <c r="L335" s="78" t="s">
+        <v>304</v>
+      </c>
+      <c r="M335" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="N335" s="75" t="s">
+        <v>34</v>
+      </c>
+      <c r="O335" s="11">
+        <v>150000</v>
+      </c>
+      <c r="P335" s="11">
+        <v>40000</v>
+      </c>
+      <c r="Q335" s="91">
+        <f>P335+O335</f>
+        <v>190000</v>
+      </c>
+      <c r="R335" s="80">
+        <v>46146</v>
+      </c>
+      <c r="S335" s="18">
+        <f t="shared" si="29"/>
+        <v>13</v>
+      </c>
+      <c r="T335" s="78" t="s">
+        <v>671</v>
+      </c>
+      <c r="U335" s="78" t="s">
+        <v>551</v>
+      </c>
+      <c r="W335" s="50"/>
+    </row>
+    <row r="336" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A336" s="85" t="s">
+        <v>609</v>
+      </c>
+      <c r="B336" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C336" s="75">
+        <v>61532855</v>
+      </c>
+      <c r="D336" s="75" t="s">
+        <v>340</v>
+      </c>
+      <c r="E336" s="75" t="s">
+        <v>679</v>
+      </c>
+      <c r="F336" s="75" t="s">
+        <v>196</v>
+      </c>
+      <c r="G336" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H336" s="76">
+        <v>46126</v>
+      </c>
+      <c r="I336" s="86">
+        <v>46146</v>
+      </c>
+      <c r="J336" s="18">
+        <f t="shared" si="28"/>
+        <v>15</v>
+      </c>
+      <c r="K336" s="79" t="s">
+        <v>303</v>
+      </c>
+      <c r="L336" s="78" t="s">
+        <v>304</v>
+      </c>
+      <c r="M336" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="N336" s="75" t="s">
+        <v>54</v>
+      </c>
+      <c r="O336" s="77">
+        <v>3850000</v>
+      </c>
+      <c r="P336" s="77">
+        <v>667054</v>
+      </c>
+      <c r="Q336" s="40">
+        <f>P336+O336</f>
+        <v>4517054</v>
+      </c>
+      <c r="R336" s="87">
+        <v>46147</v>
+      </c>
+      <c r="S336" s="18">
+        <f t="shared" si="29"/>
+        <v>16</v>
+      </c>
+      <c r="T336" s="78" t="s">
+        <v>671</v>
+      </c>
+      <c r="U336" s="78" t="s">
+        <v>551</v>
+      </c>
+      <c r="W336" s="50"/>
+    </row>
+    <row r="337" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A337" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="B337" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C337" s="75">
+        <v>59309764</v>
+      </c>
+      <c r="D337" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="E337" s="75" t="s">
+        <v>680</v>
+      </c>
+      <c r="F337" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G337" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H337" s="76">
+        <v>46084</v>
+      </c>
+      <c r="I337" s="76">
+        <v>46121</v>
+      </c>
+      <c r="J337" s="18">
+        <f t="shared" si="28"/>
+        <v>28</v>
+      </c>
+      <c r="K337" s="79" t="s">
+        <v>353</v>
+      </c>
+      <c r="L337" s="78" t="s">
+        <v>580</v>
+      </c>
+      <c r="M337" s="78" t="s">
+        <v>24</v>
+      </c>
+      <c r="N337" s="75" t="s">
+        <v>49</v>
+      </c>
+      <c r="O337" s="77">
+        <v>2000000</v>
+      </c>
+      <c r="P337" s="77">
+        <v>462000</v>
+      </c>
+      <c r="Q337" s="40">
+        <f>P337+O337</f>
+        <v>2462000</v>
+      </c>
+      <c r="R337" s="80">
+        <v>46148</v>
+      </c>
+      <c r="S337" s="18">
+        <f t="shared" si="29"/>
+        <v>47</v>
+      </c>
+      <c r="T337" s="78" t="s">
+        <v>671</v>
+      </c>
+      <c r="U337" s="78" t="s">
+        <v>551</v>
+      </c>
+      <c r="W337" s="50"/>
+    </row>
+    <row r="338" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A338" s="75" t="s">
+        <v>681</v>
+      </c>
+      <c r="B338" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C338" s="75">
+        <v>61317028</v>
+      </c>
+      <c r="D338" s="75" t="s">
+        <v>36</v>
+      </c>
+      <c r="E338" s="75" t="s">
+        <v>682</v>
+      </c>
+      <c r="F338" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G338" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H338" s="76">
+        <v>46132</v>
+      </c>
+      <c r="I338" s="76">
+        <v>46133</v>
+      </c>
+      <c r="J338" s="18">
+        <f t="shared" si="28"/>
+        <v>2</v>
+      </c>
+      <c r="K338" s="79" t="s">
+        <v>303</v>
+      </c>
+      <c r="L338" s="78" t="s">
+        <v>304</v>
+      </c>
+      <c r="M338" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="N338" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="O338" s="88">
+        <v>0</v>
+      </c>
+      <c r="P338" s="83">
+        <v>0</v>
+      </c>
+      <c r="Q338" s="40">
+        <f>P338+O338</f>
+        <v>0</v>
+      </c>
+      <c r="R338" s="80">
+        <v>46148</v>
+      </c>
+      <c r="S338" s="18">
+        <f t="shared" si="29"/>
+        <v>13</v>
+      </c>
+      <c r="T338" s="78" t="s">
+        <v>671</v>
+      </c>
+      <c r="U338" s="78" t="s">
+        <v>563</v>
+      </c>
+      <c r="W338" s="50"/>
+    </row>
+    <row r="339" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A339" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="B339" s="89" t="s">
+        <v>87</v>
+      </c>
+      <c r="C339" s="1">
+        <v>61239330</v>
+      </c>
+      <c r="D339" s="75" t="s">
+        <v>504</v>
+      </c>
+      <c r="E339" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="F339" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G339" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="H339" s="76">
+        <v>46120</v>
+      </c>
+      <c r="I339" s="76">
+        <v>46147</v>
+      </c>
+      <c r="J339" s="18">
+        <f t="shared" si="28"/>
+        <v>20</v>
+      </c>
+      <c r="K339" s="79" t="s">
+        <v>303</v>
+      </c>
+      <c r="L339" s="78" t="s">
+        <v>304</v>
+      </c>
+      <c r="M339" s="78" t="s">
+        <v>24</v>
+      </c>
+      <c r="N339" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O339" s="89">
+        <v>0</v>
+      </c>
+      <c r="P339" s="89">
+        <v>0</v>
+      </c>
+      <c r="Q339" s="40">
+        <f t="shared" ref="Q339:Q340" si="30">P339+O339</f>
+        <v>0</v>
+      </c>
+      <c r="R339" s="80">
+        <v>46148</v>
+      </c>
+      <c r="S339" s="18">
+        <f t="shared" si="29"/>
+        <v>21</v>
+      </c>
+      <c r="T339" s="78" t="s">
+        <v>671</v>
+      </c>
+      <c r="U339" s="75" t="s">
+        <v>625</v>
+      </c>
+      <c r="W339" s="50"/>
+    </row>
+    <row r="340" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A340" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B340" s="75" t="s">
+        <v>87</v>
+      </c>
+      <c r="C340" s="1">
+        <v>59409078</v>
+      </c>
+      <c r="D340" s="75" t="s">
+        <v>504</v>
+      </c>
+      <c r="E340" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="F340" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G340" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="H340" s="76">
+        <v>46086</v>
+      </c>
+      <c r="I340" s="76">
+        <v>46148</v>
+      </c>
+      <c r="J340" s="18">
+        <f t="shared" si="28"/>
+        <v>45</v>
+      </c>
+      <c r="K340" s="79" t="s">
+        <v>303</v>
+      </c>
+      <c r="L340" s="78" t="s">
+        <v>327</v>
+      </c>
+      <c r="M340" s="78" t="s">
+        <v>24</v>
+      </c>
+      <c r="N340" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="O340" s="89">
+        <v>0</v>
+      </c>
+      <c r="P340" s="89">
+        <v>0</v>
+      </c>
+      <c r="Q340" s="40">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="R340" s="80">
+        <v>46148</v>
+      </c>
+      <c r="S340" s="18">
+        <f t="shared" si="29"/>
+        <v>45</v>
+      </c>
+      <c r="T340" s="78" t="s">
+        <v>671</v>
+      </c>
+      <c r="U340" s="75" t="s">
+        <v>625</v>
+      </c>
+      <c r="W340" s="50"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U327" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="87" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="83"/>
     <cfRule type="duplicateValues" dxfId="85" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="87"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C205 C244:C287 C304:C1048576">
-    <cfRule type="duplicateValues" dxfId="81" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="175"/>
+  <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C341:C1048576">
+    <cfRule type="duplicateValues" dxfId="81" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="176"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C212 C244:C287 C304:C1048576">
+  <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C341:C1048576">
     <cfRule type="duplicateValues" dxfId="79" priority="185"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C232 C244:C287 C304:C1048576">
+  <conditionalFormatting sqref="C1:C232 C244:C287 C304:C329 C341:C1048576">
     <cfRule type="duplicateValues" dxfId="78" priority="190"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C294 C304:C1048576">
+  <conditionalFormatting sqref="C1:C294 C304:C329 C341:C1048576">
     <cfRule type="duplicateValues" dxfId="77" priority="195"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C295 C304:C1048576">
+  <conditionalFormatting sqref="C1:C295 C304:C329 C341:C1048576">
     <cfRule type="duplicateValues" dxfId="76" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="75" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
     <cfRule type="duplicateValues" dxfId="73" priority="41"/>
@@ -25246,8 +26132,8 @@
     <cfRule type="duplicateValues" dxfId="71" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="70" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
     <cfRule type="duplicateValues" dxfId="68" priority="58"/>
@@ -25304,8 +26190,8 @@
     <cfRule type="duplicateValues" dxfId="51" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="50" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
     <cfRule type="duplicateValues" dxfId="48" priority="75"/>
@@ -25320,8 +26206,8 @@
     <cfRule type="duplicateValues" dxfId="45" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="44" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
     <cfRule type="duplicateValues" dxfId="42" priority="68"/>
@@ -25387,8 +26273,8 @@
     <cfRule type="duplicateValues" dxfId="18" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C208">
-    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218:C223">
     <cfRule type="duplicateValues" dxfId="15" priority="7"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="598" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4FDAB90-F513-48A4-8D17-0AF439E3DB8C}"/>
+  <xr:revisionPtr revIDLastSave="617" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{195356D2-B34C-48D5-A594-EEF1D313F586}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$347</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$355</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3707" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3788" uniqueCount="711">
   <si>
     <t>Client</t>
   </si>
@@ -2140,6 +2140,39 @@
   </si>
   <si>
     <t>SYTHD260109</t>
+  </si>
+  <si>
+    <t>AIR LIQUIDE COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>SYTHD140099</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>GOS</t>
+  </si>
+  <si>
+    <t>GD-BASSAM VITIB</t>
+  </si>
+  <si>
+    <t>SYTHD190044</t>
+  </si>
+  <si>
+    <t>155M</t>
+  </si>
+  <si>
+    <t>ANSSI</t>
+  </si>
+  <si>
+    <t>SYTHD260125</t>
+  </si>
+  <si>
+    <t>BUVPN260033</t>
+  </si>
+  <si>
+    <t>BNI GESTION</t>
   </si>
 </sst>
 </file>
@@ -2153,7 +2186,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,##0\ _€"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2230,6 +2263,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0E0E0E"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2292,7 +2331,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2435,6 +2474,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3668,7 +3710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W348"/>
+  <dimension ref="A1:W355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="18" customWidth="1"/>
@@ -25424,7 +25466,7 @@
         <v>46146</v>
       </c>
       <c r="J333" s="16">
-        <f t="shared" ref="J333:J348" si="29">+NETWORKDAYS(H333,I333)</f>
+        <f t="shared" ref="J333:J355" si="29">+NETWORKDAYS(H333,I333)</f>
         <v>11</v>
       </c>
       <c r="K333" s="17" t="s">
@@ -25453,7 +25495,7 @@
         <v>46146</v>
       </c>
       <c r="S333" s="16">
-        <f t="shared" ref="S333:S348" si="30">NETWORKDAYS(H333,R333)</f>
+        <f t="shared" ref="S333:S355" si="30">NETWORKDAYS(H333,R333)</f>
         <v>11</v>
       </c>
       <c r="T333" s="5" t="s">
@@ -26491,8 +26533,484 @@
         <v>664</v>
       </c>
     </row>
+    <row r="349" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A349" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="B349" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C349" s="6">
+        <v>61363241</v>
+      </c>
+      <c r="D349" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E349" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="F349" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G349" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H349" s="8">
+        <v>46122</v>
+      </c>
+      <c r="I349" s="8">
+        <v>46153</v>
+      </c>
+      <c r="J349" s="16">
+        <f t="shared" si="29"/>
+        <v>22</v>
+      </c>
+      <c r="K349" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L349" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M349" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N349" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="O349" s="41">
+        <v>0</v>
+      </c>
+      <c r="P349" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q349" s="33">
+        <f>P349+O349</f>
+        <v>0</v>
+      </c>
+      <c r="R349" s="7">
+        <v>46153</v>
+      </c>
+      <c r="S349" s="16">
+        <f t="shared" si="30"/>
+        <v>22</v>
+      </c>
+      <c r="T349" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="U349" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="350" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A350" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C350" s="54">
+        <v>62840921</v>
+      </c>
+      <c r="D350" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="E350" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="F350" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G350" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H350" s="8">
+        <v>46148</v>
+      </c>
+      <c r="I350" s="8">
+        <v>46150</v>
+      </c>
+      <c r="J350" s="16">
+        <f t="shared" si="29"/>
+        <v>3</v>
+      </c>
+      <c r="K350" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L350" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M350" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N350" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="O350" s="41">
+        <v>0</v>
+      </c>
+      <c r="P350" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q350" s="33">
+        <f>P350+O350</f>
+        <v>0</v>
+      </c>
+      <c r="R350" s="7">
+        <v>46153</v>
+      </c>
+      <c r="S350" s="16">
+        <f t="shared" si="30"/>
+        <v>4</v>
+      </c>
+      <c r="T350" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="U350" s="5" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="351" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A351" s="14" t="s">
+        <v>707</v>
+      </c>
+      <c r="B351" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C351" s="6">
+        <v>62742919</v>
+      </c>
+      <c r="D351" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E351" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="F351" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G351" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H351" s="8">
+        <v>46147</v>
+      </c>
+      <c r="I351" s="8">
+        <v>46153</v>
+      </c>
+      <c r="J351" s="16">
+        <f t="shared" si="29"/>
+        <v>5</v>
+      </c>
+      <c r="K351" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L351" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M351" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N351" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O351" s="12">
+        <v>0</v>
+      </c>
+      <c r="P351" s="12">
+        <v>670000</v>
+      </c>
+      <c r="Q351" s="33">
+        <f>P351+O351</f>
+        <v>670000</v>
+      </c>
+      <c r="R351" s="7">
+        <v>46153</v>
+      </c>
+      <c r="S351" s="16">
+        <f t="shared" si="30"/>
+        <v>5</v>
+      </c>
+      <c r="T351" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="U351" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="352" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A352" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B352" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C352" s="6">
+        <v>57651441</v>
+      </c>
+      <c r="D352" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E352" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="F352" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G352" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H352" s="8">
+        <v>46055</v>
+      </c>
+      <c r="I352" s="8">
+        <v>46154</v>
+      </c>
+      <c r="J352" s="16">
+        <f t="shared" si="29"/>
+        <v>72</v>
+      </c>
+      <c r="K352" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L352" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="M352" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N352" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="O352" s="12">
+        <v>1635147</v>
+      </c>
+      <c r="P352" s="12">
+        <v>270000</v>
+      </c>
+      <c r="Q352" s="33">
+        <f>P352+O352</f>
+        <v>1905147</v>
+      </c>
+      <c r="R352" s="43">
+        <v>46154</v>
+      </c>
+      <c r="S352" s="16">
+        <f t="shared" si="30"/>
+        <v>72</v>
+      </c>
+      <c r="T352" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="U352" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="353" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A353" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C353" s="1">
+        <v>62415793</v>
+      </c>
+      <c r="D353" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E353" s="1">
+        <v>2720310777</v>
+      </c>
+      <c r="F353" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G353" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H353" s="7">
+        <v>46140</v>
+      </c>
+      <c r="I353" s="7">
+        <v>46147</v>
+      </c>
+      <c r="J353" s="16">
+        <f t="shared" si="29"/>
+        <v>6</v>
+      </c>
+      <c r="K353" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L353" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M353" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N353" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="O353" s="1">
+        <v>228000</v>
+      </c>
+      <c r="P353" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q353" s="33">
+        <f>P353+O353</f>
+        <v>228000</v>
+      </c>
+      <c r="R353" s="43">
+        <v>46154</v>
+      </c>
+      <c r="S353" s="16">
+        <f t="shared" si="30"/>
+        <v>11</v>
+      </c>
+      <c r="T353" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="U353" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="354" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A354" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B354" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C354" s="1">
+        <v>62416938</v>
+      </c>
+      <c r="D354" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E354" s="1">
+        <v>2720208110</v>
+      </c>
+      <c r="F354" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G354" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H354" s="8">
+        <v>46140</v>
+      </c>
+      <c r="I354" s="7">
+        <v>46147</v>
+      </c>
+      <c r="J354" s="16">
+        <f t="shared" si="29"/>
+        <v>6</v>
+      </c>
+      <c r="K354" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L354" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M354" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N354" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O354" s="33">
+        <v>60000</v>
+      </c>
+      <c r="P354" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q354" s="33">
+        <f>P354+O354</f>
+        <v>60000</v>
+      </c>
+      <c r="R354" s="43">
+        <v>46154</v>
+      </c>
+      <c r="S354" s="16">
+        <f t="shared" si="30"/>
+        <v>11</v>
+      </c>
+      <c r="T354" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="U354" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="355" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A355" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B355" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C355" s="1">
+        <v>62417396</v>
+      </c>
+      <c r="D355" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E355" s="1">
+        <v>2720312270</v>
+      </c>
+      <c r="F355" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G355" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H355" s="8">
+        <v>46140</v>
+      </c>
+      <c r="I355" s="7">
+        <v>46147</v>
+      </c>
+      <c r="J355" s="16">
+        <f t="shared" si="29"/>
+        <v>6</v>
+      </c>
+      <c r="K355" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L355" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M355" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N355" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="O355" s="12">
+        <v>108000</v>
+      </c>
+      <c r="P355" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q355" s="33">
+        <f>P355+O355</f>
+        <v>108000</v>
+      </c>
+      <c r="R355" s="43">
+        <v>46154</v>
+      </c>
+      <c r="S355" s="16">
+        <f t="shared" si="30"/>
+        <v>11</v>
+      </c>
+      <c r="T355" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="U355" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U347" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U355" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
     <cfRule type="duplicateValues" dxfId="88" priority="82"/>
     <cfRule type="duplicateValues" dxfId="87" priority="84"/>
@@ -26501,20 +27019,20 @@
     <cfRule type="duplicateValues" dxfId="84" priority="87"/>
     <cfRule type="duplicateValues" dxfId="83" priority="88"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C349:C1048576">
+  <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C356:C1048576">
     <cfRule type="duplicateValues" dxfId="82" priority="176"/>
     <cfRule type="duplicateValues" dxfId="81" priority="177"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C349:C1048576">
+  <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C356:C1048576">
     <cfRule type="duplicateValues" dxfId="80" priority="186"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C232 C244:C287 C304:C329 C349:C1048576">
+  <conditionalFormatting sqref="C1:C232 C244:C287 C304:C329 C356:C1048576">
     <cfRule type="duplicateValues" dxfId="79" priority="191"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C294 C304:C329 C349:C1048576">
+  <conditionalFormatting sqref="C1:C294 C304:C329 C356:C1048576">
     <cfRule type="duplicateValues" dxfId="78" priority="196"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C295 C304:C329 C349:C1048576">
+  <conditionalFormatting sqref="C1:C295 C304:C329 C356:C1048576">
     <cfRule type="duplicateValues" dxfId="77" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="617" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{195356D2-B34C-48D5-A594-EEF1D313F586}"/>
+  <xr:revisionPtr revIDLastSave="639" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7F043AF-9B66-48FA-8CEC-C3D8AFB2C0EA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3788" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3812" uniqueCount="714">
   <si>
     <t>Client</t>
   </si>
@@ -2173,6 +2173,15 @@
   </si>
   <si>
     <t>BNI GESTION</t>
+  </si>
+  <si>
+    <t>SOFITEL ABIDJAN HOTEL IVOIRE</t>
+  </si>
+  <si>
+    <t>SYTHD260138</t>
+  </si>
+  <si>
+    <t>SYTHD260124</t>
   </si>
 </sst>
 </file>
@@ -2331,7 +2340,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2478,6 +2487,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3710,7 +3725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W355"/>
+  <dimension ref="A1:W357"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="18" customWidth="1"/>
@@ -25466,7 +25481,7 @@
         <v>46146</v>
       </c>
       <c r="J333" s="16">
-        <f t="shared" ref="J333:J355" si="29">+NETWORKDAYS(H333,I333)</f>
+        <f t="shared" ref="J333:J357" si="29">+NETWORKDAYS(H333,I333)</f>
         <v>11</v>
       </c>
       <c r="K333" s="17" t="s">
@@ -25495,7 +25510,7 @@
         <v>46146</v>
       </c>
       <c r="S333" s="16">
-        <f t="shared" ref="S333:S355" si="30">NETWORKDAYS(H333,R333)</f>
+        <f t="shared" ref="S333:S357" si="30">NETWORKDAYS(H333,R333)</f>
         <v>11</v>
       </c>
       <c r="T333" s="5" t="s">
@@ -26244,7 +26259,7 @@
         <v>0</v>
       </c>
       <c r="Q344" s="33">
-        <f>P344+O344</f>
+        <f t="shared" ref="Q344:Q355" si="33">P344+O344</f>
         <v>0</v>
       </c>
       <c r="R344" s="7">
@@ -26312,7 +26327,7 @@
         <v>552000</v>
       </c>
       <c r="Q345" s="33">
-        <f>P345+O345</f>
+        <f t="shared" si="33"/>
         <v>1252000</v>
       </c>
       <c r="R345" s="7">
@@ -26380,7 +26395,7 @@
         <v>474962</v>
       </c>
       <c r="Q346" s="33">
-        <f>P346+O346</f>
+        <f t="shared" si="33"/>
         <v>4324962</v>
       </c>
       <c r="R346" s="7">
@@ -26448,7 +26463,7 @@
         <v>60000</v>
       </c>
       <c r="Q347" s="33">
-        <f>P347+O347</f>
+        <f t="shared" si="33"/>
         <v>210000</v>
       </c>
       <c r="R347" s="7">
@@ -26516,7 +26531,7 @@
         <v>0</v>
       </c>
       <c r="Q348" s="33">
-        <f>P348+O348</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="R348" s="7">
@@ -26584,7 +26599,7 @@
         <v>0</v>
       </c>
       <c r="Q349" s="33">
-        <f>P349+O349</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="R349" s="7">
@@ -26652,7 +26667,7 @@
         <v>0</v>
       </c>
       <c r="Q350" s="33">
-        <f>P350+O350</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="R350" s="7">
@@ -26720,7 +26735,7 @@
         <v>670000</v>
       </c>
       <c r="Q351" s="33">
-        <f>P351+O351</f>
+        <f t="shared" si="33"/>
         <v>670000</v>
       </c>
       <c r="R351" s="7">
@@ -26788,7 +26803,7 @@
         <v>270000</v>
       </c>
       <c r="Q352" s="33">
-        <f>P352+O352</f>
+        <f t="shared" si="33"/>
         <v>1905147</v>
       </c>
       <c r="R352" s="43">
@@ -26856,7 +26871,7 @@
         <v>0</v>
       </c>
       <c r="Q353" s="33">
-        <f>P353+O353</f>
+        <f t="shared" si="33"/>
         <v>228000</v>
       </c>
       <c r="R353" s="43">
@@ -26924,7 +26939,7 @@
         <v>0</v>
       </c>
       <c r="Q354" s="33">
-        <f>P354+O354</f>
+        <f t="shared" si="33"/>
         <v>60000</v>
       </c>
       <c r="R354" s="43">
@@ -26992,7 +27007,7 @@
         <v>0</v>
       </c>
       <c r="Q355" s="33">
-        <f>P355+O355</f>
+        <f t="shared" si="33"/>
         <v>108000</v>
       </c>
       <c r="R355" s="43">
@@ -27009,19 +27024,153 @@
         <v>551</v>
       </c>
     </row>
+    <row r="356" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A356" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="B356" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C356" s="55">
+        <v>62852675</v>
+      </c>
+      <c r="D356" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E356" s="55" t="s">
+        <v>712</v>
+      </c>
+      <c r="F356" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="G356" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H356" s="56">
+        <v>46148</v>
+      </c>
+      <c r="I356" s="56">
+        <v>46153</v>
+      </c>
+      <c r="J356" s="16">
+        <f t="shared" si="29"/>
+        <v>4</v>
+      </c>
+      <c r="K356" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L356" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M356" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N356" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O356" s="6">
+        <v>1416000</v>
+      </c>
+      <c r="P356" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q356" s="12">
+        <v>1416000</v>
+      </c>
+      <c r="R356" s="8">
+        <v>46155</v>
+      </c>
+      <c r="S356" s="16">
+        <f t="shared" si="30"/>
+        <v>6</v>
+      </c>
+      <c r="T356" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="U356" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="357" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A357" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="B357" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C357" s="55">
+        <v>62746621</v>
+      </c>
+      <c r="D357" s="55" t="s">
+        <v>446</v>
+      </c>
+      <c r="E357" s="55" t="s">
+        <v>713</v>
+      </c>
+      <c r="F357" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="G357" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H357" s="56">
+        <v>46147</v>
+      </c>
+      <c r="I357" s="56">
+        <v>46154</v>
+      </c>
+      <c r="J357" s="16">
+        <f t="shared" si="29"/>
+        <v>6</v>
+      </c>
+      <c r="K357" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L357" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M357" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N357" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O357" s="6">
+        <v>0</v>
+      </c>
+      <c r="P357" s="6">
+        <v>670000</v>
+      </c>
+      <c r="Q357" s="12">
+        <v>670000</v>
+      </c>
+      <c r="R357" s="8">
+        <v>46155</v>
+      </c>
+      <c r="S357" s="16">
+        <f t="shared" si="30"/>
+        <v>7</v>
+      </c>
+      <c r="T357" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="U357" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U355" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="88" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="85"/>
     <cfRule type="duplicateValues" dxfId="87" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C356:C1048576">
-    <cfRule type="duplicateValues" dxfId="82" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C356:C1048576">
     <cfRule type="duplicateValues" dxfId="80" priority="186"/>
@@ -27047,8 +27196,8 @@
     <cfRule type="duplicateValues" dxfId="72" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="71" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
     <cfRule type="duplicateValues" dxfId="69" priority="59"/>
@@ -27105,8 +27254,8 @@
     <cfRule type="duplicateValues" dxfId="52" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="51" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
     <cfRule type="duplicateValues" dxfId="49" priority="76"/>
@@ -27188,8 +27337,8 @@
     <cfRule type="duplicateValues" dxfId="19" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C208">
-    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218:C223">
     <cfRule type="duplicateValues" dxfId="16" priority="8"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="639" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7F043AF-9B66-48FA-8CEC-C3D8AFB2C0EA}"/>
+  <xr:revisionPtr revIDLastSave="660" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B3B55B1-8289-417E-8018-68C30626AF01}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3812" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3858" uniqueCount="721">
   <si>
     <t>Client</t>
   </si>
@@ -2182,6 +2182,27 @@
   </si>
   <si>
     <t>SYTHD260124</t>
+  </si>
+  <si>
+    <t>OFI OLAM IVOIRE</t>
+  </si>
+  <si>
+    <t>SYTHD260101</t>
+  </si>
+  <si>
+    <t>SYTHD260123</t>
+  </si>
+  <si>
+    <t>MINISTERE DES FINANES ( DGTCP  )</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>ASCOMA</t>
+  </si>
+  <si>
+    <t>SAN-PEDRO</t>
   </si>
 </sst>
 </file>
@@ -2311,7 +2332,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2334,13 +2355,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2493,6 +2527,12 @@
     </xf>
     <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3725,7 +3765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W357"/>
+  <dimension ref="A1:W361"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="18" customWidth="1"/>
@@ -25481,7 +25521,7 @@
         <v>46146</v>
       </c>
       <c r="J333" s="16">
-        <f t="shared" ref="J333:J357" si="29">+NETWORKDAYS(H333,I333)</f>
+        <f t="shared" ref="J333:J361" si="29">+NETWORKDAYS(H333,I333)</f>
         <v>11</v>
       </c>
       <c r="K333" s="17" t="s">
@@ -25510,7 +25550,7 @@
         <v>46146</v>
       </c>
       <c r="S333" s="16">
-        <f t="shared" ref="S333:S357" si="30">NETWORKDAYS(H333,R333)</f>
+        <f t="shared" ref="S333:S361" si="30">NETWORKDAYS(H333,R333)</f>
         <v>11</v>
       </c>
       <c r="T333" s="5" t="s">
@@ -27158,30 +27198,302 @@
         <v>551</v>
       </c>
     </row>
+    <row r="358" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A358" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="B358" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C358" s="6">
+        <v>60026486</v>
+      </c>
+      <c r="D358" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E358" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="F358" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G358" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H358" s="10">
+        <v>46098</v>
+      </c>
+      <c r="I358" s="8">
+        <v>46140</v>
+      </c>
+      <c r="J358" s="16">
+        <f t="shared" si="29"/>
+        <v>31</v>
+      </c>
+      <c r="K358" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L358" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M358" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N358" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="O358" s="12">
+        <v>0</v>
+      </c>
+      <c r="P358" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q358" s="33">
+        <f>P358+O358</f>
+        <v>0</v>
+      </c>
+      <c r="R358" s="7">
+        <v>46158</v>
+      </c>
+      <c r="S358" s="16">
+        <f t="shared" si="30"/>
+        <v>44</v>
+      </c>
+      <c r="T358" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="U358" s="6" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="359" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A359" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B359" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C359" s="6">
+        <v>57706849</v>
+      </c>
+      <c r="D359" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E359" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="F359" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G359" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H359" s="8">
+        <v>46056</v>
+      </c>
+      <c r="I359" s="8">
+        <v>46155</v>
+      </c>
+      <c r="J359" s="16">
+        <f t="shared" si="29"/>
+        <v>72</v>
+      </c>
+      <c r="K359" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="L359" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="M359" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N359" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O359" s="33">
+        <v>0</v>
+      </c>
+      <c r="P359" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q359" s="33">
+        <f>P359+O359</f>
+        <v>0</v>
+      </c>
+      <c r="R359" s="7">
+        <v>46158</v>
+      </c>
+      <c r="S359" s="16">
+        <f t="shared" si="30"/>
+        <v>74</v>
+      </c>
+      <c r="T359" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="U359" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="360" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A360" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="B360" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C360" s="1">
+        <v>62546484</v>
+      </c>
+      <c r="D360" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E360" s="6">
+        <v>2722224600</v>
+      </c>
+      <c r="F360" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G360" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H360" s="7">
+        <v>46142</v>
+      </c>
+      <c r="I360" s="7">
+        <v>46154</v>
+      </c>
+      <c r="J360" s="16">
+        <f t="shared" si="29"/>
+        <v>9</v>
+      </c>
+      <c r="K360" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L360" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M360" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N360" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="O360" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="P360" s="1">
+        <v>231750</v>
+      </c>
+      <c r="Q360" s="57">
+        <f t="shared" ref="Q360:Q361" si="34">P360+O360</f>
+        <v>1231750</v>
+      </c>
+      <c r="R360" s="7">
+        <v>46160</v>
+      </c>
+      <c r="S360" s="16">
+        <f t="shared" si="30"/>
+        <v>13</v>
+      </c>
+      <c r="T360" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="U360" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="361" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A361" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B361" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C361" s="1">
+        <v>61702838</v>
+      </c>
+      <c r="D361" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="E361" s="6">
+        <v>2734710371</v>
+      </c>
+      <c r="F361" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G361" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H361" s="7">
+        <v>46128</v>
+      </c>
+      <c r="I361" s="7">
+        <v>46154</v>
+      </c>
+      <c r="J361" s="16">
+        <f t="shared" si="29"/>
+        <v>19</v>
+      </c>
+      <c r="K361" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L361" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M361" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N361" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="O361" s="9">
+        <v>150000</v>
+      </c>
+      <c r="P361" s="9">
+        <v>40000</v>
+      </c>
+      <c r="Q361" s="58">
+        <f t="shared" si="34"/>
+        <v>190000</v>
+      </c>
+      <c r="R361" s="7">
+        <v>46160</v>
+      </c>
+      <c r="S361" s="16">
+        <f t="shared" si="30"/>
+        <v>23</v>
+      </c>
+      <c r="T361" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="U361" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U355" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="88" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="82"/>
     <cfRule type="duplicateValues" dxfId="87" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="88"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C356:C1048576">
-    <cfRule type="duplicateValues" dxfId="82" priority="177"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="176"/>
+  <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C356:C357 C362:C1048576">
+    <cfRule type="duplicateValues" dxfId="82" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="177"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C356:C1048576">
+  <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C356:C357 C362:C1048576">
     <cfRule type="duplicateValues" dxfId="80" priority="186"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C232 C244:C287 C304:C329 C356:C1048576">
+  <conditionalFormatting sqref="C1:C232 C244:C287 C304:C329 C356:C357 C362:C1048576">
     <cfRule type="duplicateValues" dxfId="79" priority="191"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C294 C304:C329 C356:C1048576">
+  <conditionalFormatting sqref="C1:C294 C304:C329 C356:C357 C362:C1048576">
     <cfRule type="duplicateValues" dxfId="78" priority="196"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C295 C304:C329 C356:C1048576">
+  <conditionalFormatting sqref="C1:C295 C304:C329 C356:C357 C362:C1048576">
     <cfRule type="duplicateValues" dxfId="77" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
@@ -27196,8 +27508,8 @@
     <cfRule type="duplicateValues" dxfId="72" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="71" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
     <cfRule type="duplicateValues" dxfId="69" priority="59"/>
@@ -27254,8 +27566,8 @@
     <cfRule type="duplicateValues" dxfId="52" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="51" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
     <cfRule type="duplicateValues" dxfId="49" priority="76"/>
@@ -27337,8 +27649,8 @@
     <cfRule type="duplicateValues" dxfId="19" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C208">
-    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218:C223">
     <cfRule type="duplicateValues" dxfId="16" priority="8"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="660" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B3B55B1-8289-417E-8018-68C30626AF01}"/>
+  <xr:revisionPtr revIDLastSave="672" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B737E153-F40B-4D5F-8620-8D6F09ED6CE5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3858" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3870" uniqueCount="723">
   <si>
     <t>Client</t>
   </si>
@@ -2203,6 +2203,12 @@
   </si>
   <si>
     <t>SAN-PEDRO</t>
+  </si>
+  <si>
+    <t>XPERIENCE GLOBAL SERVICES</t>
+  </si>
+  <si>
+    <t>SYTHD260128</t>
   </si>
 </sst>
 </file>
@@ -2374,7 +2380,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2532,6 +2538,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3765,7 +3780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W361"/>
+  <dimension ref="A1:W362"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="18" customWidth="1"/>
@@ -25521,7 +25536,7 @@
         <v>46146</v>
       </c>
       <c r="J333" s="16">
-        <f t="shared" ref="J333:J361" si="29">+NETWORKDAYS(H333,I333)</f>
+        <f t="shared" ref="J333:J362" si="29">+NETWORKDAYS(H333,I333)</f>
         <v>11</v>
       </c>
       <c r="K333" s="17" t="s">
@@ -25550,7 +25565,7 @@
         <v>46146</v>
       </c>
       <c r="S333" s="16">
-        <f t="shared" ref="S333:S361" si="30">NETWORKDAYS(H333,R333)</f>
+        <f t="shared" ref="S333:S362" si="30">NETWORKDAYS(H333,R333)</f>
         <v>11</v>
       </c>
       <c r="T333" s="5" t="s">
@@ -27467,6 +27482,74 @@
         <v>718</v>
       </c>
       <c r="U361" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="362" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A362" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="B362" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C362" s="6">
+        <v>62241651</v>
+      </c>
+      <c r="D362" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E362" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="F362" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G362" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H362" s="8">
+        <v>46137</v>
+      </c>
+      <c r="I362" s="8">
+        <v>46157</v>
+      </c>
+      <c r="J362" s="16">
+        <f t="shared" si="29"/>
+        <v>15</v>
+      </c>
+      <c r="K362" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L362" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M362" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="N362" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="O362" s="60">
+        <v>500000</v>
+      </c>
+      <c r="P362" s="60">
+        <v>943235</v>
+      </c>
+      <c r="Q362" s="58">
+        <f>P362+O362</f>
+        <v>1443235</v>
+      </c>
+      <c r="R362" s="61">
+        <v>46160</v>
+      </c>
+      <c r="S362" s="16">
+        <f t="shared" si="30"/>
+        <v>16</v>
+      </c>
+      <c r="T362" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="U362" s="5" t="s">
         <v>551</v>
       </c>
     </row>
@@ -27480,20 +27563,20 @@
     <cfRule type="duplicateValues" dxfId="84" priority="87"/>
     <cfRule type="duplicateValues" dxfId="83" priority="88"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C356:C357 C362:C1048576">
+  <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C356:C357 C363:C1048576">
     <cfRule type="duplicateValues" dxfId="82" priority="176"/>
     <cfRule type="duplicateValues" dxfId="81" priority="177"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C356:C357 C362:C1048576">
+  <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C356:C357 C363:C1048576">
     <cfRule type="duplicateValues" dxfId="80" priority="186"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C232 C244:C287 C304:C329 C356:C357 C362:C1048576">
+  <conditionalFormatting sqref="C1:C232 C244:C287 C304:C329 C356:C357 C363:C1048576">
     <cfRule type="duplicateValues" dxfId="79" priority="191"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C294 C304:C329 C356:C357 C362:C1048576">
+  <conditionalFormatting sqref="C1:C294 C304:C329 C356:C357 C363:C1048576">
     <cfRule type="duplicateValues" dxfId="78" priority="196"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C295 C304:C329 C356:C357 C362:C1048576">
+  <conditionalFormatting sqref="C1:C295 C304:C329 C356:C357 C363:C1048576">
     <cfRule type="duplicateValues" dxfId="77" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="672" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B737E153-F40B-4D5F-8620-8D6F09ED6CE5}"/>
+  <xr:revisionPtr revIDLastSave="692" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC0F245B-D58E-4D45-9423-6A8DA5AA033B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$355</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$370</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3870" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3963" uniqueCount="736">
   <si>
     <t>Client</t>
   </si>
@@ -2209,6 +2209,45 @@
   </si>
   <si>
     <t>SYTHD260128</t>
+  </si>
+  <si>
+    <t>SIB</t>
+  </si>
+  <si>
+    <t>COCODY RIVIERA 2</t>
+  </si>
+  <si>
+    <t>BUVPN260091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASCOMA SUR LE SITE DE </t>
+  </si>
+  <si>
+    <t>IVOIRE TECHNO COM COCODY</t>
+  </si>
+  <si>
+    <t>SUD COMOE CAOUTCHOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ABOISSO</t>
+  </si>
+  <si>
+    <t>TREICHVILLE ZONE 3</t>
+  </si>
+  <si>
+    <t>SYTHD260137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYTHD260130 </t>
+  </si>
+  <si>
+    <t>ARTCI</t>
+  </si>
+  <si>
+    <t>SYTHD260141</t>
+  </si>
+  <si>
+    <t>SYTHD260142</t>
   </si>
 </sst>
 </file>
@@ -3780,7 +3819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W362"/>
+  <dimension ref="A1:W370"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="18" customWidth="1"/>
@@ -25536,7 +25575,7 @@
         <v>46146</v>
       </c>
       <c r="J333" s="16">
-        <f t="shared" ref="J333:J362" si="29">+NETWORKDAYS(H333,I333)</f>
+        <f t="shared" ref="J333:J370" si="29">+NETWORKDAYS(H333,I333)</f>
         <v>11</v>
       </c>
       <c r="K333" s="17" t="s">
@@ -25565,7 +25604,7 @@
         <v>46146</v>
       </c>
       <c r="S333" s="16">
-        <f t="shared" ref="S333:S362" si="30">NETWORKDAYS(H333,R333)</f>
+        <f t="shared" ref="S333:S370" si="30">NETWORKDAYS(H333,R333)</f>
         <v>11</v>
       </c>
       <c r="T333" s="5" t="s">
@@ -27553,19 +27592,555 @@
         <v>551</v>
       </c>
     </row>
+    <row r="363" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A363" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="B363" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="C363" s="55">
+        <v>62544794</v>
+      </c>
+      <c r="D363" s="55" t="s">
+        <v>724</v>
+      </c>
+      <c r="E363" s="55" t="s">
+        <v>725</v>
+      </c>
+      <c r="F363" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="G363" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H363" s="56">
+        <v>46142</v>
+      </c>
+      <c r="I363" s="56">
+        <v>46160</v>
+      </c>
+      <c r="J363" s="16">
+        <f t="shared" si="29"/>
+        <v>13</v>
+      </c>
+      <c r="K363" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="L363" s="55" t="s">
+        <v>304</v>
+      </c>
+      <c r="M363" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="N363" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="O363" s="55">
+        <v>500000</v>
+      </c>
+      <c r="P363" s="55">
+        <v>250000</v>
+      </c>
+      <c r="Q363" s="60">
+        <v>750000</v>
+      </c>
+      <c r="R363" s="56">
+        <v>46160</v>
+      </c>
+      <c r="S363" s="16">
+        <f t="shared" si="30"/>
+        <v>13</v>
+      </c>
+      <c r="T363" s="55" t="s">
+        <v>718</v>
+      </c>
+      <c r="U363" s="55" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="364" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A364" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="B364" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C364" s="55">
+        <v>61700587</v>
+      </c>
+      <c r="D364" s="55" t="s">
+        <v>529</v>
+      </c>
+      <c r="E364" s="55">
+        <v>2722419000</v>
+      </c>
+      <c r="F364" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="G364" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H364" s="56">
+        <v>46128</v>
+      </c>
+      <c r="I364" s="56">
+        <v>46160</v>
+      </c>
+      <c r="J364" s="16">
+        <f t="shared" si="29"/>
+        <v>23</v>
+      </c>
+      <c r="K364" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="L364" s="55" t="s">
+        <v>304</v>
+      </c>
+      <c r="M364" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="N364" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="O364" s="55">
+        <v>150000</v>
+      </c>
+      <c r="P364" s="55">
+        <v>40000</v>
+      </c>
+      <c r="Q364" s="60">
+        <v>190000</v>
+      </c>
+      <c r="R364" s="56">
+        <v>46160</v>
+      </c>
+      <c r="S364" s="16">
+        <f t="shared" si="30"/>
+        <v>23</v>
+      </c>
+      <c r="T364" s="55" t="s">
+        <v>718</v>
+      </c>
+      <c r="U364" s="55" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="365" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A365" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="B365" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C365" s="55">
+        <v>62249046</v>
+      </c>
+      <c r="D365" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E365" s="55">
+        <v>2722560065</v>
+      </c>
+      <c r="F365" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="G365" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H365" s="56">
+        <v>46137</v>
+      </c>
+      <c r="I365" s="56">
+        <v>46160</v>
+      </c>
+      <c r="J365" s="16">
+        <f t="shared" si="29"/>
+        <v>16</v>
+      </c>
+      <c r="K365" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="L365" s="55" t="s">
+        <v>304</v>
+      </c>
+      <c r="M365" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="N365" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="O365" s="55">
+        <v>150000</v>
+      </c>
+      <c r="P365" s="55">
+        <v>40000</v>
+      </c>
+      <c r="Q365" s="60">
+        <v>190000</v>
+      </c>
+      <c r="R365" s="56">
+        <v>46160</v>
+      </c>
+      <c r="S365" s="16">
+        <f t="shared" si="30"/>
+        <v>16</v>
+      </c>
+      <c r="T365" s="55" t="s">
+        <v>718</v>
+      </c>
+      <c r="U365" s="55" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="366" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A366" s="6" t="s">
+        <v>728</v>
+      </c>
+      <c r="B366" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C366" s="55">
+        <v>59480507</v>
+      </c>
+      <c r="D366" s="55" t="s">
+        <v>729</v>
+      </c>
+      <c r="E366" s="55">
+        <v>2721712020</v>
+      </c>
+      <c r="F366" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="G366" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H366" s="56">
+        <v>46087</v>
+      </c>
+      <c r="I366" s="56">
+        <v>46160</v>
+      </c>
+      <c r="J366" s="16">
+        <f t="shared" si="29"/>
+        <v>52</v>
+      </c>
+      <c r="K366" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="L366" s="55" t="s">
+        <v>327</v>
+      </c>
+      <c r="M366" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="N366" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="O366" s="55">
+        <v>150000</v>
+      </c>
+      <c r="P366" s="55">
+        <v>40000</v>
+      </c>
+      <c r="Q366" s="60">
+        <v>190000</v>
+      </c>
+      <c r="R366" s="56">
+        <v>46160</v>
+      </c>
+      <c r="S366" s="16">
+        <f t="shared" si="30"/>
+        <v>52</v>
+      </c>
+      <c r="T366" s="55" t="s">
+        <v>718</v>
+      </c>
+      <c r="U366" s="55" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="367" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A367" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="B367" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C367" s="55">
+        <v>60356605</v>
+      </c>
+      <c r="D367" s="55" t="s">
+        <v>730</v>
+      </c>
+      <c r="E367" s="55" t="s">
+        <v>731</v>
+      </c>
+      <c r="F367" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="G367" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H367" s="56">
+        <v>46104</v>
+      </c>
+      <c r="I367" s="56">
+        <v>46160</v>
+      </c>
+      <c r="J367" s="16">
+        <f t="shared" si="29"/>
+        <v>41</v>
+      </c>
+      <c r="K367" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="L367" s="55" t="s">
+        <v>327</v>
+      </c>
+      <c r="M367" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="N367" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="O367" s="55">
+        <v>1000000</v>
+      </c>
+      <c r="P367" s="55">
+        <v>460000</v>
+      </c>
+      <c r="Q367" s="60">
+        <v>1460000</v>
+      </c>
+      <c r="R367" s="56">
+        <v>46161</v>
+      </c>
+      <c r="S367" s="16">
+        <f t="shared" si="30"/>
+        <v>42</v>
+      </c>
+      <c r="T367" s="55" t="s">
+        <v>718</v>
+      </c>
+      <c r="U367" s="55" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="368" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A368" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="B368" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="C368" s="55">
+        <v>62748443</v>
+      </c>
+      <c r="D368" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E368" s="55" t="s">
+        <v>732</v>
+      </c>
+      <c r="F368" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="G368" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H368" s="56">
+        <v>46147</v>
+      </c>
+      <c r="I368" s="56">
+        <v>46160</v>
+      </c>
+      <c r="J368" s="16">
+        <f t="shared" si="29"/>
+        <v>10</v>
+      </c>
+      <c r="K368" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="L368" s="55" t="s">
+        <v>304</v>
+      </c>
+      <c r="M368" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="N368" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="O368" s="55">
+        <v>0</v>
+      </c>
+      <c r="P368" s="55">
+        <v>500000</v>
+      </c>
+      <c r="Q368" s="60">
+        <v>500000</v>
+      </c>
+      <c r="R368" s="56">
+        <v>46161</v>
+      </c>
+      <c r="S368" s="16">
+        <f t="shared" si="30"/>
+        <v>11</v>
+      </c>
+      <c r="T368" s="55" t="s">
+        <v>718</v>
+      </c>
+      <c r="U368" s="55" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="369" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A369" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="B369" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C369" s="55">
+        <v>63302106</v>
+      </c>
+      <c r="D369" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="E369" s="55" t="s">
+        <v>734</v>
+      </c>
+      <c r="F369" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="G369" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H369" s="56">
+        <v>46157</v>
+      </c>
+      <c r="I369" s="56">
+        <v>46161</v>
+      </c>
+      <c r="J369" s="16">
+        <f t="shared" si="29"/>
+        <v>3</v>
+      </c>
+      <c r="K369" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="L369" s="55" t="s">
+        <v>304</v>
+      </c>
+      <c r="M369" s="55" t="s">
+        <v>157</v>
+      </c>
+      <c r="N369" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="O369" s="55">
+        <v>946305</v>
+      </c>
+      <c r="P369" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q369" s="60">
+        <v>946305</v>
+      </c>
+      <c r="R369" s="56">
+        <v>46162</v>
+      </c>
+      <c r="S369" s="16">
+        <f t="shared" si="30"/>
+        <v>4</v>
+      </c>
+      <c r="T369" s="55" t="s">
+        <v>718</v>
+      </c>
+      <c r="U369" s="55" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="370" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A370" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="B370" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C370" s="55">
+        <v>63303380</v>
+      </c>
+      <c r="D370" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="E370" s="55" t="s">
+        <v>735</v>
+      </c>
+      <c r="F370" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="G370" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H370" s="56">
+        <v>46157</v>
+      </c>
+      <c r="I370" s="56">
+        <v>46161</v>
+      </c>
+      <c r="J370" s="16">
+        <f t="shared" si="29"/>
+        <v>3</v>
+      </c>
+      <c r="K370" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="L370" s="55" t="s">
+        <v>304</v>
+      </c>
+      <c r="M370" s="55" t="s">
+        <v>157</v>
+      </c>
+      <c r="N370" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="O370" s="55">
+        <v>4053290</v>
+      </c>
+      <c r="P370" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q370" s="60">
+        <v>4053290</v>
+      </c>
+      <c r="R370" s="56">
+        <v>46162</v>
+      </c>
+      <c r="S370" s="16">
+        <f t="shared" si="30"/>
+        <v>4</v>
+      </c>
+      <c r="T370" s="55" t="s">
+        <v>718</v>
+      </c>
+      <c r="U370" s="55" t="s">
+        <v>551</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U355" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U370" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="88" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="85"/>
     <cfRule type="duplicateValues" dxfId="87" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C356:C357 C363:C1048576">
-    <cfRule type="duplicateValues" dxfId="82" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C356:C357 C363:C1048576">
     <cfRule type="duplicateValues" dxfId="80" priority="186"/>
@@ -27591,8 +28166,8 @@
     <cfRule type="duplicateValues" dxfId="72" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="71" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
     <cfRule type="duplicateValues" dxfId="69" priority="59"/>
@@ -27649,8 +28224,8 @@
     <cfRule type="duplicateValues" dxfId="52" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="51" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
     <cfRule type="duplicateValues" dxfId="49" priority="76"/>
@@ -27732,8 +28307,8 @@
     <cfRule type="duplicateValues" dxfId="19" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C208">
-    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218:C223">
     <cfRule type="duplicateValues" dxfId="16" priority="8"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="692" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC0F245B-D58E-4D45-9423-6A8DA5AA033B}"/>
+  <xr:revisionPtr revIDLastSave="754" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D75B285E-1600-4B0B-8575-D44C5BD0CFD1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$370</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$384</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3963" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4130" uniqueCount="764">
   <si>
     <t>Client</t>
   </si>
@@ -2248,6 +2248,90 @@
   </si>
   <si>
     <t>SYTHD260142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNPS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLATEAU SIEGE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2720334660B </t>
+  </si>
+  <si>
+    <t>T0 AROLI GROUPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COCODY </t>
+  </si>
+  <si>
+    <t>NESKAO</t>
+  </si>
+  <si>
+    <t>SYTHD260129</t>
+  </si>
+  <si>
+    <t>GIABA</t>
+  </si>
+  <si>
+    <t>62968196 </t>
+  </si>
+  <si>
+    <t>SYTHD260143</t>
+  </si>
+  <si>
+    <t>GNX</t>
+  </si>
+  <si>
+    <t>SYTHD260139</t>
+  </si>
+  <si>
+    <t>DEMANDE_LIGNE_JCI DU 20 MAI 2026 AU 23 MAI 2026</t>
+  </si>
+  <si>
+    <t>SYTHD260145</t>
+  </si>
+  <si>
+    <t>AGENCE EMPLOI JEUNE</t>
+  </si>
+  <si>
+    <t>SYTHD260144</t>
+  </si>
+  <si>
+    <t>EGLISE VASE D'HONNEUR</t>
+  </si>
+  <si>
+    <t>SYTHD260147</t>
+  </si>
+  <si>
+    <t>SYTHD260146</t>
+  </si>
+  <si>
+    <t>ALIWAX   COCODY</t>
+  </si>
+  <si>
+    <t>AGEROUTE C2D</t>
+  </si>
+  <si>
+    <t>COCODY PALMERAIE</t>
+  </si>
+  <si>
+    <t>BUVPN260092</t>
+  </si>
+  <si>
+    <t>VITIB</t>
+  </si>
+  <si>
+    <t>VPNLL120246</t>
+  </si>
+  <si>
+    <t>BUVPN260070</t>
+  </si>
+  <si>
+    <t>LAGUNE ENERGIES</t>
+  </si>
+  <si>
+    <t>SYTHD260116</t>
   </si>
 </sst>
 </file>
@@ -2594,7 +2678,967 @@
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="89">
+  <dxfs count="185">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3819,7 +4863,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W370"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:W384"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="18" customWidth="1"/>
@@ -3904,7 +4949,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="51" t="s">
         <v>154</v>
       </c>
@@ -3966,7 +5011,7 @@
       </c>
       <c r="U2" s="34"/>
     </row>
-    <row r="3" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>159</v>
       </c>
@@ -4028,7 +5073,7 @@
       </c>
       <c r="U3" s="34"/>
     </row>
-    <row r="4" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
         <v>154</v>
       </c>
@@ -4090,7 +5135,7 @@
       </c>
       <c r="U4" s="34"/>
     </row>
-    <row r="5" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>154</v>
       </c>
@@ -4152,7 +5197,7 @@
       </c>
       <c r="U5" s="34"/>
     </row>
-    <row r="6" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>164</v>
       </c>
@@ -4214,7 +5259,7 @@
       </c>
       <c r="U6" s="34"/>
     </row>
-    <row r="7" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>165</v>
       </c>
@@ -4276,7 +5321,7 @@
       </c>
       <c r="U7" s="34"/>
     </row>
-    <row r="8" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>166</v>
       </c>
@@ -4338,7 +5383,7 @@
       </c>
       <c r="U8" s="34"/>
     </row>
-    <row r="9" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>169</v>
       </c>
@@ -4400,7 +5445,7 @@
       </c>
       <c r="U9" s="34"/>
     </row>
-    <row r="10" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>172</v>
       </c>
@@ -4462,7 +5507,7 @@
       </c>
       <c r="U10" s="34"/>
     </row>
-    <row r="11" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>172</v>
       </c>
@@ -4524,7 +5569,7 @@
       </c>
       <c r="U11" s="34"/>
     </row>
-    <row r="12" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
         <v>177</v>
       </c>
@@ -4586,7 +5631,7 @@
       </c>
       <c r="U12" s="34"/>
     </row>
-    <row r="13" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>154</v>
       </c>
@@ -4648,7 +5693,7 @@
       </c>
       <c r="U13" s="34"/>
     </row>
-    <row r="14" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
         <v>154</v>
       </c>
@@ -4710,7 +5755,7 @@
       </c>
       <c r="U14" s="34"/>
     </row>
-    <row r="15" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>172</v>
       </c>
@@ -4772,7 +5817,7 @@
       </c>
       <c r="U15" s="34"/>
     </row>
-    <row r="16" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>154</v>
       </c>
@@ -4834,7 +5879,7 @@
       </c>
       <c r="U16" s="34"/>
     </row>
-    <row r="17" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>154</v>
       </c>
@@ -4896,7 +5941,7 @@
       </c>
       <c r="U17" s="34"/>
     </row>
-    <row r="18" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>186</v>
       </c>
@@ -4958,7 +6003,7 @@
       </c>
       <c r="U18" s="34"/>
     </row>
-    <row r="19" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>189</v>
       </c>
@@ -5020,7 +6065,7 @@
       </c>
       <c r="U19" s="34"/>
     </row>
-    <row r="20" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>189</v>
       </c>
@@ -5082,7 +6127,7 @@
       </c>
       <c r="U20" s="34"/>
     </row>
-    <row r="21" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>193</v>
       </c>
@@ -5144,7 +6189,7 @@
       </c>
       <c r="U21" s="34"/>
     </row>
-    <row r="22" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>43</v>
       </c>
@@ -5206,7 +6251,7 @@
       </c>
       <c r="U22" s="34"/>
     </row>
-    <row r="23" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>201</v>
       </c>
@@ -5268,7 +6313,7 @@
       </c>
       <c r="U23" s="34"/>
     </row>
-    <row r="24" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>204</v>
       </c>
@@ -5330,7 +6375,7 @@
       </c>
       <c r="U24" s="34"/>
     </row>
-    <row r="25" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>206</v>
       </c>
@@ -5392,7 +6437,7 @@
       </c>
       <c r="U25" s="34"/>
     </row>
-    <row r="26" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>207</v>
       </c>
@@ -5454,7 +6499,7 @@
       </c>
       <c r="U26" s="34"/>
     </row>
-    <row r="27" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>172</v>
       </c>
@@ -5516,7 +6561,7 @@
       </c>
       <c r="U27" s="34"/>
     </row>
-    <row r="28" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>210</v>
       </c>
@@ -5578,7 +6623,7 @@
       </c>
       <c r="U28" s="34"/>
     </row>
-    <row r="29" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>213</v>
       </c>
@@ -5640,7 +6685,7 @@
       </c>
       <c r="U29" s="34"/>
     </row>
-    <row r="30" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>217</v>
       </c>
@@ -5702,7 +6747,7 @@
       </c>
       <c r="U30" s="34"/>
     </row>
-    <row r="31" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>218</v>
       </c>
@@ -5764,7 +6809,7 @@
       </c>
       <c r="U31" s="34"/>
     </row>
-    <row r="32" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>81</v>
       </c>
@@ -5826,7 +6871,7 @@
       </c>
       <c r="U32" s="34"/>
     </row>
-    <row r="33" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>91</v>
       </c>
@@ -5888,7 +6933,7 @@
       </c>
       <c r="U33" s="34"/>
     </row>
-    <row r="34" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>91</v>
       </c>
@@ -5950,7 +6995,7 @@
       </c>
       <c r="U34" s="34"/>
     </row>
-    <row r="35" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>91</v>
       </c>
@@ -6012,7 +7057,7 @@
       </c>
       <c r="U35" s="34"/>
     </row>
-    <row r="36" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>91</v>
       </c>
@@ -6074,7 +7119,7 @@
       </c>
       <c r="U36" s="34"/>
     </row>
-    <row r="37" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>91</v>
       </c>
@@ -6136,7 +7181,7 @@
       </c>
       <c r="U37" s="34"/>
     </row>
-    <row r="38" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>226</v>
       </c>
@@ -6198,7 +7243,7 @@
       </c>
       <c r="U38" s="34"/>
     </row>
-    <row r="39" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
         <v>228</v>
       </c>
@@ -6260,7 +7305,7 @@
       </c>
       <c r="U39" s="34"/>
     </row>
-    <row r="40" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>91</v>
       </c>
@@ -6322,7 +7367,7 @@
       </c>
       <c r="U40" s="34"/>
     </row>
-    <row r="41" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>231</v>
       </c>
@@ -6384,7 +7429,7 @@
       </c>
       <c r="U41" s="34"/>
     </row>
-    <row r="42" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>234</v>
       </c>
@@ -6446,7 +7491,7 @@
       </c>
       <c r="U42" s="34"/>
     </row>
-    <row r="43" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>236</v>
       </c>
@@ -6508,7 +7553,7 @@
       </c>
       <c r="U43" s="34"/>
     </row>
-    <row r="44" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>237</v>
       </c>
@@ -6570,7 +7615,7 @@
       </c>
       <c r="U44" s="34"/>
     </row>
-    <row r="45" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>238</v>
       </c>
@@ -6632,7 +7677,7 @@
       </c>
       <c r="U45" s="34"/>
     </row>
-    <row r="46" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>240</v>
       </c>
@@ -6694,7 +7739,7 @@
       </c>
       <c r="U46" s="34"/>
     </row>
-    <row r="47" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
         <v>91</v>
       </c>
@@ -6756,7 +7801,7 @@
       </c>
       <c r="U47" s="34"/>
     </row>
-    <row r="48" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>243</v>
       </c>
@@ -6818,7 +7863,7 @@
       </c>
       <c r="U48" s="34"/>
     </row>
-    <row r="49" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
         <v>246</v>
       </c>
@@ -6880,7 +7925,7 @@
       </c>
       <c r="U49" s="34"/>
     </row>
-    <row r="50" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>248</v>
       </c>
@@ -6942,7 +7987,7 @@
       </c>
       <c r="U50" s="34"/>
     </row>
-    <row r="51" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
         <v>250</v>
       </c>
@@ -7004,7 +8049,7 @@
       </c>
       <c r="U51" s="34"/>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>250</v>
       </c>
@@ -7066,7 +8111,7 @@
       </c>
       <c r="U52" s="34"/>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
         <v>253</v>
       </c>
@@ -7128,7 +8173,7 @@
       </c>
       <c r="U53" s="34"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>256</v>
       </c>
@@ -7190,7 +8235,7 @@
       </c>
       <c r="U54" s="34"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>258</v>
       </c>
@@ -7252,7 +8297,7 @@
       </c>
       <c r="U55" s="34"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>259</v>
       </c>
@@ -7314,7 +8359,7 @@
       </c>
       <c r="U56" s="34"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>259</v>
       </c>
@@ -7376,7 +8421,7 @@
       </c>
       <c r="U57" s="34"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
         <v>253</v>
       </c>
@@ -7438,7 +8483,7 @@
       </c>
       <c r="U58" s="34"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
         <v>265</v>
       </c>
@@ -7500,7 +8545,7 @@
       </c>
       <c r="U59" s="34"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>267</v>
       </c>
@@ -7562,7 +8607,7 @@
       </c>
       <c r="U60" s="34"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>271</v>
       </c>
@@ -7624,7 +8669,7 @@
       </c>
       <c r="U61" s="34"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
         <v>43</v>
       </c>
@@ -7686,7 +8731,7 @@
       </c>
       <c r="U62" s="34"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
         <v>58</v>
       </c>
@@ -7748,7 +8793,7 @@
       </c>
       <c r="U63" s="34"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>91</v>
       </c>
@@ -7810,7 +8855,7 @@
       </c>
       <c r="U64" s="34"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>91</v>
       </c>
@@ -7872,7 +8917,7 @@
       </c>
       <c r="U65" s="34"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>91</v>
       </c>
@@ -7934,7 +8979,7 @@
       </c>
       <c r="U66" s="34"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>282</v>
       </c>
@@ -7996,7 +9041,7 @@
       </c>
       <c r="U67" s="34"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>285</v>
       </c>
@@ -8058,7 +9103,7 @@
       </c>
       <c r="U68" s="34"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
         <v>286</v>
       </c>
@@ -8120,7 +9165,7 @@
       </c>
       <c r="U69" s="34"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="14" t="s">
         <v>288</v>
       </c>
@@ -8182,7 +9227,7 @@
       </c>
       <c r="U70" s="34"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>291</v>
       </c>
@@ -8244,7 +9289,7 @@
       </c>
       <c r="U71" s="34"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>292</v>
       </c>
@@ -8306,7 +9351,7 @@
       </c>
       <c r="U72" s="34"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="6" t="s">
         <v>91</v>
       </c>
@@ -8368,7 +9413,7 @@
       </c>
       <c r="U73" s="34"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
         <v>294</v>
       </c>
@@ -8430,7 +9475,7 @@
       </c>
       <c r="U74" s="34"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
         <v>91</v>
       </c>
@@ -8492,7 +9537,7 @@
       </c>
       <c r="U75" s="34"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="6" t="s">
         <v>299</v>
       </c>
@@ -8554,7 +9599,7 @@
       </c>
       <c r="U76" s="34"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="6" t="s">
         <v>18</v>
       </c>
@@ -8616,7 +9661,7 @@
       </c>
       <c r="U77" s="34"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>27</v>
       </c>
@@ -8678,7 +9723,7 @@
       </c>
       <c r="U78" s="34"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>30</v>
       </c>
@@ -8740,7 +9785,7 @@
       </c>
       <c r="U79" s="34"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
         <v>35</v>
       </c>
@@ -8802,7 +9847,7 @@
       </c>
       <c r="U80" s="34"/>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="6" t="s">
         <v>35</v>
       </c>
@@ -8864,7 +9909,7 @@
       </c>
       <c r="U81" s="34"/>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
         <v>35</v>
       </c>
@@ -8926,7 +9971,7 @@
       </c>
       <c r="U82" s="34"/>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="6" t="s">
         <v>43</v>
       </c>
@@ -8988,7 +10033,7 @@
       </c>
       <c r="U83" s="34"/>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="6" t="s">
         <v>43</v>
       </c>
@@ -9050,7 +10095,7 @@
       </c>
       <c r="U84" s="34"/>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
         <v>52</v>
       </c>
@@ -9112,7 +10157,7 @@
       </c>
       <c r="U85" s="34"/>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>55</v>
       </c>
@@ -9174,7 +10219,7 @@
       </c>
       <c r="U86" s="34"/>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="14" t="s">
         <v>58</v>
       </c>
@@ -9236,7 +10281,7 @@
       </c>
       <c r="U87" s="34"/>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
         <v>62</v>
       </c>
@@ -9298,7 +10343,7 @@
       </c>
       <c r="U88" s="34"/>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="6" t="s">
         <v>65</v>
       </c>
@@ -9360,7 +10405,7 @@
       </c>
       <c r="U89" s="34"/>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
         <v>67</v>
       </c>
@@ -9422,7 +10467,7 @@
       </c>
       <c r="U90" s="34"/>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="6" t="s">
         <v>70</v>
       </c>
@@ -9484,7 +10529,7 @@
       </c>
       <c r="U91" s="34"/>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="6" t="s">
         <v>75</v>
       </c>
@@ -9546,7 +10591,7 @@
       </c>
       <c r="U92" s="34"/>
     </row>
-    <row r="93" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:21" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="21" t="s">
         <v>77</v>
       </c>
@@ -9608,7 +10653,7 @@
       </c>
       <c r="U93" s="34"/>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="6" t="s">
         <v>43</v>
       </c>
@@ -9670,7 +10715,7 @@
       </c>
       <c r="U94" s="34"/>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="6" t="s">
         <v>81</v>
       </c>
@@ -9732,7 +10777,7 @@
       </c>
       <c r="U95" s="34"/>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>85</v>
       </c>
@@ -9794,7 +10839,7 @@
       </c>
       <c r="U96" s="34"/>
     </row>
-    <row r="97" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:21" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>86</v>
       </c>
@@ -9856,7 +10901,7 @@
       </c>
       <c r="U97" s="34"/>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="6" t="s">
         <v>88</v>
       </c>
@@ -9918,7 +10963,7 @@
       </c>
       <c r="U98" s="34"/>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="6" t="s">
         <v>91</v>
       </c>
@@ -9980,7 +11025,7 @@
       </c>
       <c r="U99" s="34"/>
     </row>
-    <row r="100" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:21" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="21" t="s">
         <v>95</v>
       </c>
@@ -10042,7 +11087,7 @@
       </c>
       <c r="U100" s="34"/>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="6" t="s">
         <v>58</v>
       </c>
@@ -10104,7 +11149,7 @@
       </c>
       <c r="U101" s="34"/>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="14" t="s">
         <v>58</v>
       </c>
@@ -10166,7 +11211,7 @@
       </c>
       <c r="U102" s="34"/>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="6" t="s">
         <v>43</v>
       </c>
@@ -10228,7 +11273,7 @@
       </c>
       <c r="U103" s="34"/>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="6" t="s">
         <v>103</v>
       </c>
@@ -10290,7 +11335,7 @@
       </c>
       <c r="U104" s="34"/>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>106</v>
       </c>
@@ -10352,7 +11397,7 @@
       </c>
       <c r="U105" s="34"/>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>81</v>
       </c>
@@ -10414,7 +11459,7 @@
       </c>
       <c r="U106" s="34"/>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>107</v>
       </c>
@@ -10476,7 +11521,7 @@
       </c>
       <c r="U107" s="34"/>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>108</v>
       </c>
@@ -10538,7 +11583,7 @@
       </c>
       <c r="U108" s="34"/>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>109</v>
       </c>
@@ -10600,7 +11645,7 @@
       </c>
       <c r="U109" s="34"/>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="6" t="s">
         <v>110</v>
       </c>
@@ -10662,7 +11707,7 @@
       </c>
       <c r="U110" s="34"/>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="6" t="s">
         <v>113</v>
       </c>
@@ -10724,7 +11769,7 @@
       </c>
       <c r="U111" s="34"/>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
         <v>116</v>
       </c>
@@ -10786,7 +11831,7 @@
       </c>
       <c r="U112" s="34"/>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="6" t="s">
         <v>120</v>
       </c>
@@ -10848,7 +11893,7 @@
       </c>
       <c r="U113" s="34"/>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="6" t="s">
         <v>123</v>
       </c>
@@ -10910,7 +11955,7 @@
       </c>
       <c r="U114" s="34"/>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="6" t="s">
         <v>110</v>
       </c>
@@ -10972,7 +12017,7 @@
       </c>
       <c r="U115" s="34"/>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="6" t="s">
         <v>127</v>
       </c>
@@ -11034,7 +12079,7 @@
       </c>
       <c r="U116" s="34"/>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>130</v>
       </c>
@@ -11096,7 +12141,7 @@
       </c>
       <c r="U117" s="34"/>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>131</v>
       </c>
@@ -11158,7 +12203,7 @@
       </c>
       <c r="U118" s="34"/>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="6" t="s">
         <v>132</v>
       </c>
@@ -11220,7 +12265,7 @@
       </c>
       <c r="U119" s="34"/>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="6" t="s">
         <v>134</v>
       </c>
@@ -11282,7 +12327,7 @@
       </c>
       <c r="U120" s="34"/>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="6" t="s">
         <v>134</v>
       </c>
@@ -11344,7 +12389,7 @@
       </c>
       <c r="U121" s="34"/>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="6" t="s">
         <v>140</v>
       </c>
@@ -11406,7 +12451,7 @@
       </c>
       <c r="U122" s="34"/>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="6" t="s">
         <v>143</v>
       </c>
@@ -11468,7 +12513,7 @@
       </c>
       <c r="U123" s="34"/>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="6" t="s">
         <v>145</v>
       </c>
@@ -11530,7 +12575,7 @@
       </c>
       <c r="U124" s="34"/>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="6" t="s">
         <v>149</v>
       </c>
@@ -11592,7 +12637,7 @@
       </c>
       <c r="U125" s="34"/>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="6" t="s">
         <v>143</v>
       </c>
@@ -11654,7 +12699,7 @@
       </c>
       <c r="U126" s="34"/>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="6" t="s">
         <v>301</v>
       </c>
@@ -11720,7 +12765,7 @@
       </c>
       <c r="U127" s="34"/>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="6" t="s">
         <v>305</v>
       </c>
@@ -11786,7 +12831,7 @@
       </c>
       <c r="U128" s="34"/>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="6" t="s">
         <v>145</v>
       </c>
@@ -11852,7 +12897,7 @@
       </c>
       <c r="U129" s="34"/>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>308</v>
       </c>
@@ -11918,7 +12963,7 @@
       </c>
       <c r="U130" s="34"/>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>309</v>
       </c>
@@ -11984,7 +13029,7 @@
       </c>
       <c r="U131" s="34"/>
     </row>
-    <row r="132" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:21" s="18" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="14" t="s">
         <v>311</v>
       </c>
@@ -12050,7 +13095,7 @@
       </c>
       <c r="U132" s="34"/>
     </row>
-    <row r="133" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:21" s="18" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="6" t="s">
         <v>311</v>
       </c>
@@ -12116,7 +13161,7 @@
       </c>
       <c r="U133" s="34"/>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="6" t="s">
         <v>317</v>
       </c>
@@ -12182,7 +13227,7 @@
       </c>
       <c r="U134" s="34"/>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>320</v>
       </c>
@@ -12248,7 +13293,7 @@
       </c>
       <c r="U135" s="34"/>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
         <v>321</v>
       </c>
@@ -12314,7 +13359,7 @@
       </c>
       <c r="U136" s="34"/>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>321</v>
       </c>
@@ -12380,7 +13425,7 @@
       </c>
       <c r="U137" s="34"/>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
         <v>322</v>
       </c>
@@ -12446,7 +13491,7 @@
       </c>
       <c r="U138" s="34"/>
     </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>323</v>
       </c>
@@ -12512,7 +13557,7 @@
       </c>
       <c r="U139" s="34"/>
     </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>324</v>
       </c>
@@ -12578,7 +13623,7 @@
       </c>
       <c r="U140" s="34"/>
     </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>326</v>
       </c>
@@ -12644,7 +13689,7 @@
       </c>
       <c r="U141" s="34"/>
     </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="6" t="s">
         <v>328</v>
       </c>
@@ -12710,7 +13755,7 @@
       </c>
       <c r="U142" s="34"/>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="6" t="s">
         <v>331</v>
       </c>
@@ -12776,7 +13821,7 @@
       </c>
       <c r="U143" s="34"/>
     </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="6" t="s">
         <v>333</v>
       </c>
@@ -12842,7 +13887,7 @@
       </c>
       <c r="U144" s="34"/>
     </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="6" t="s">
         <v>335</v>
       </c>
@@ -12908,7 +13953,7 @@
       </c>
       <c r="U145" s="34"/>
     </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="6" t="s">
         <v>140</v>
       </c>
@@ -12974,7 +14019,7 @@
       </c>
       <c r="U146" s="34"/>
     </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="6" t="s">
         <v>140</v>
       </c>
@@ -13040,7 +14085,7 @@
       </c>
       <c r="U147" s="34"/>
     </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="14" t="s">
         <v>58</v>
       </c>
@@ -13106,7 +14151,7 @@
       </c>
       <c r="U148" s="34"/>
     </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="6" t="s">
         <v>344</v>
       </c>
@@ -13174,7 +14219,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="6" t="s">
         <v>348</v>
       </c>
@@ -13242,7 +14287,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="6" t="s">
         <v>324</v>
       </c>
@@ -13310,7 +14355,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="6" t="s">
         <v>350</v>
       </c>
@@ -13378,7 +14423,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="6" t="s">
         <v>354</v>
       </c>
@@ -13446,7 +14491,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="6" t="s">
         <v>145</v>
       </c>
@@ -13514,7 +14559,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="6" t="s">
         <v>359</v>
       </c>
@@ -13582,7 +14627,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="6" t="s">
         <v>360</v>
       </c>
@@ -13650,7 +14695,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="6" t="s">
         <v>43</v>
       </c>
@@ -13718,7 +14763,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="6" t="s">
         <v>362</v>
       </c>
@@ -13786,7 +14831,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>43</v>
       </c>
@@ -13854,7 +14899,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>367</v>
       </c>
@@ -13922,7 +14967,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="6" t="s">
         <v>369</v>
       </c>
@@ -13990,7 +15035,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="6" t="s">
         <v>371</v>
       </c>
@@ -14058,7 +15103,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="6" t="s">
         <v>43</v>
       </c>
@@ -14126,7 +15171,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="6" t="s">
         <v>374</v>
       </c>
@@ -14194,7 +15239,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="6" t="s">
         <v>374</v>
       </c>
@@ -14262,7 +15307,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="6" t="s">
         <v>374</v>
       </c>
@@ -14330,7 +15375,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="6" t="s">
         <v>374</v>
       </c>
@@ -14398,7 +15443,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="6" t="s">
         <v>374</v>
       </c>
@@ -14466,7 +15511,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="6" t="s">
         <v>374</v>
       </c>
@@ -14534,7 +15579,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="6" t="s">
         <v>374</v>
       </c>
@@ -14602,7 +15647,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="6" t="s">
         <v>374</v>
       </c>
@@ -14670,7 +15715,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="6" t="s">
         <v>374</v>
       </c>
@@ -14738,7 +15783,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="6" t="s">
         <v>374</v>
       </c>
@@ -14806,7 +15851,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="6" t="s">
         <v>374</v>
       </c>
@@ -14874,7 +15919,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="6" t="s">
         <v>374</v>
       </c>
@@ -14942,7 +15987,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="6" t="s">
         <v>374</v>
       </c>
@@ -15010,7 +16055,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="6" t="s">
         <v>374</v>
       </c>
@@ -15078,7 +16123,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="6" t="s">
         <v>374</v>
       </c>
@@ -15146,7 +16191,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="6" t="s">
         <v>374</v>
       </c>
@@ -15214,7 +16259,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="6" t="s">
         <v>408</v>
       </c>
@@ -15282,7 +16327,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="14" t="s">
         <v>411</v>
       </c>
@@ -15350,7 +16395,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="6" t="s">
         <v>414</v>
       </c>
@@ -15418,7 +16463,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="183" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="6" t="s">
         <v>416</v>
       </c>
@@ -15486,7 +16531,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="184" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="6" t="s">
         <v>416</v>
       </c>
@@ -15554,7 +16599,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="185" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>419</v>
       </c>
@@ -15622,7 +16667,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="186" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="3" t="s">
         <v>421</v>
       </c>
@@ -15690,7 +16735,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="187" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="6" t="s">
         <v>422</v>
       </c>
@@ -15758,7 +16803,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="188" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="6" t="s">
         <v>422</v>
       </c>
@@ -15826,7 +16871,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="189" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="6" t="s">
         <v>428</v>
       </c>
@@ -15894,7 +16939,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="6" t="s">
         <v>430</v>
       </c>
@@ -15961,7 +17006,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="191" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="6" t="s">
         <v>432</v>
       </c>
@@ -16028,7 +17073,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="6" t="s">
         <v>432</v>
       </c>
@@ -16095,7 +17140,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="193" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="6" t="s">
         <v>437</v>
       </c>
@@ -16162,7 +17207,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="194" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="6" t="s">
         <v>438</v>
       </c>
@@ -16229,7 +17274,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="195" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="6" t="s">
         <v>439</v>
       </c>
@@ -16296,7 +17341,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="196" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="6" t="s">
         <v>445</v>
       </c>
@@ -16363,7 +17408,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="197" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="6" t="s">
         <v>432</v>
       </c>
@@ -16430,7 +17475,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="198" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="6" t="s">
         <v>134</v>
       </c>
@@ -16497,7 +17542,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="199" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="6" t="s">
         <v>451</v>
       </c>
@@ -16564,7 +17609,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="200" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="6" t="s">
         <v>451</v>
       </c>
@@ -16631,7 +17676,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="201" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="6" t="s">
         <v>134</v>
       </c>
@@ -16698,7 +17743,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="202" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="6" t="s">
         <v>456</v>
       </c>
@@ -16765,7 +17810,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="203" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="6" t="s">
         <v>43</v>
       </c>
@@ -16832,7 +17877,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="204" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="6" t="s">
         <v>459</v>
       </c>
@@ -16899,7 +17944,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="205" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="6" t="s">
         <v>461</v>
       </c>
@@ -16966,7 +18011,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="206" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="6" t="s">
         <v>462</v>
       </c>
@@ -17034,7 +18079,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="207" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="6" t="s">
         <v>451</v>
       </c>
@@ -17102,7 +18147,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="208" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="6" t="s">
         <v>451</v>
       </c>
@@ -17170,7 +18215,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="209" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="5" t="s">
         <v>466</v>
       </c>
@@ -17238,7 +18283,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="210" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="6" t="s">
         <v>469</v>
       </c>
@@ -17306,7 +18351,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="211" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="6" t="s">
         <v>471</v>
       </c>
@@ -17374,7 +18419,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="212" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>473</v>
       </c>
@@ -17442,7 +18487,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="213" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="6" t="s">
         <v>120</v>
       </c>
@@ -17510,7 +18555,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="214" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="6" t="s">
         <v>476</v>
       </c>
@@ -17578,7 +18623,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="215" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="6" t="s">
         <v>469</v>
       </c>
@@ -17646,7 +18691,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="216" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="6" t="s">
         <v>58</v>
       </c>
@@ -17714,7 +18759,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="217" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="6" t="s">
         <v>481</v>
       </c>
@@ -17782,7 +18827,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="218" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>483</v>
       </c>
@@ -17850,7 +18895,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="219" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>484</v>
       </c>
@@ -17918,7 +18963,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="220" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>271</v>
       </c>
@@ -17986,7 +19031,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="221" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6" t="s">
         <v>485</v>
       </c>
@@ -18054,7 +19099,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="222" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6" t="s">
         <v>172</v>
       </c>
@@ -18122,7 +19167,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="223" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
         <v>489</v>
       </c>
@@ -18190,7 +19235,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="224" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
         <v>492</v>
       </c>
@@ -18258,7 +19303,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="225" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>495</v>
       </c>
@@ -18326,7 +19371,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="226" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>499</v>
       </c>
@@ -18394,7 +19439,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="227" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>502</v>
       </c>
@@ -18462,7 +19507,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="228" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>503</v>
       </c>
@@ -18530,7 +19575,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="229" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>505</v>
       </c>
@@ -18598,7 +19643,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="230" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>506</v>
       </c>
@@ -18666,7 +19711,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="231" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>507</v>
       </c>
@@ -18734,7 +19779,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="232" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>508</v>
       </c>
@@ -18802,7 +19847,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="233" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>509</v>
       </c>
@@ -18869,7 +19914,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="234" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>514</v>
       </c>
@@ -18936,7 +19981,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="235" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="6" t="s">
         <v>516</v>
       </c>
@@ -19004,7 +20049,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="236" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="6" t="s">
         <v>516</v>
       </c>
@@ -19072,7 +20117,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="237" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="6" t="s">
         <v>520</v>
       </c>
@@ -19140,7 +20185,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="238" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="6" t="s">
         <v>522</v>
       </c>
@@ -19208,7 +20253,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="239" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="6" t="s">
         <v>524</v>
       </c>
@@ -19276,7 +20321,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="240" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="6" t="s">
         <v>526</v>
       </c>
@@ -19344,7 +20389,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="241" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="6" t="s">
         <v>528</v>
       </c>
@@ -19412,7 +20457,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="242" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="6" t="s">
         <v>528</v>
       </c>
@@ -19480,7 +20525,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="243" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="6" t="s">
         <v>469</v>
       </c>
@@ -19548,7 +20593,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="244" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="6" t="s">
         <v>533</v>
       </c>
@@ -19615,7 +20660,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="245" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="6" t="s">
         <v>535</v>
       </c>
@@ -19682,7 +20727,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="246" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="6" t="s">
         <v>535</v>
       </c>
@@ -19749,7 +20794,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="247" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="6" t="s">
         <v>538</v>
       </c>
@@ -19816,7 +20861,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="248" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="6" t="s">
         <v>459</v>
       </c>
@@ -19883,7 +20928,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="249" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="6" t="s">
         <v>535</v>
       </c>
@@ -19950,7 +20995,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="250" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="6" t="s">
         <v>539</v>
       </c>
@@ -20017,7 +21062,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="251" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="6" t="s">
         <v>535</v>
       </c>
@@ -20084,7 +21129,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="252" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="6" t="s">
         <v>540</v>
       </c>
@@ -20151,7 +21196,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="253" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="6" t="s">
         <v>541</v>
       </c>
@@ -20218,7 +21263,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="254" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="6" t="s">
         <v>43</v>
       </c>
@@ -20285,7 +21330,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="255" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="6" t="s">
         <v>43</v>
       </c>
@@ -20352,7 +21397,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="256" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="6" t="s">
         <v>469</v>
       </c>
@@ -20419,7 +21464,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="257" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="6" t="s">
         <v>547</v>
       </c>
@@ -20486,7 +21531,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="258" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="6" t="s">
         <v>548</v>
       </c>
@@ -20553,7 +21598,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="259" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="6" t="s">
         <v>549</v>
       </c>
@@ -20620,7 +21665,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="260" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="6" t="s">
         <v>553</v>
       </c>
@@ -20687,7 +21732,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="261" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="6" t="s">
         <v>556</v>
       </c>
@@ -20754,7 +21799,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="262" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="6" t="s">
         <v>559</v>
       </c>
@@ -20821,7 +21866,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="263" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="6" t="s">
         <v>43</v>
       </c>
@@ -20888,7 +21933,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="264" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="6" t="s">
         <v>564</v>
       </c>
@@ -20955,7 +22000,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="265" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="6" t="s">
         <v>541</v>
       </c>
@@ -21022,7 +22067,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="266" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="6" t="s">
         <v>567</v>
       </c>
@@ -21089,7 +22134,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="267" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="6" t="s">
         <v>466</v>
       </c>
@@ -21156,7 +22201,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="268" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="6" t="s">
         <v>570</v>
       </c>
@@ -21223,7 +22268,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="269" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="6" t="s">
         <v>91</v>
       </c>
@@ -21290,7 +22335,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="270" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="6" t="s">
         <v>91</v>
       </c>
@@ -21357,7 +22402,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="271" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="6" t="s">
         <v>575</v>
       </c>
@@ -21424,7 +22469,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="272" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="6" t="s">
         <v>576</v>
       </c>
@@ -21491,7 +22536,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="273" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="6" t="s">
         <v>578</v>
       </c>
@@ -21558,7 +22603,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="274" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="6" t="s">
         <v>578</v>
       </c>
@@ -21625,7 +22670,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="275" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="6" t="s">
         <v>582</v>
       </c>
@@ -21693,7 +22738,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="276" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="6" t="s">
         <v>439</v>
       </c>
@@ -21761,7 +22806,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="277" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="6" t="s">
         <v>140</v>
       </c>
@@ -21829,7 +22874,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="278" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="6" t="s">
         <v>439</v>
       </c>
@@ -21897,7 +22942,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="279" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="6" t="s">
         <v>91</v>
       </c>
@@ -21965,7 +23010,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="280" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="6" t="s">
         <v>91</v>
       </c>
@@ -22033,7 +23078,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="281" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="6" t="s">
         <v>374</v>
       </c>
@@ -22101,7 +23146,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="282" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="6" t="s">
         <v>374</v>
       </c>
@@ -22169,7 +23214,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="283" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="6" t="s">
         <v>374</v>
       </c>
@@ -22237,7 +23282,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="284" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="6" t="s">
         <v>596</v>
       </c>
@@ -22305,7 +23350,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="285" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="6" t="s">
         <v>598</v>
       </c>
@@ -22373,7 +23418,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="286" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="6" t="s">
         <v>599</v>
       </c>
@@ -22441,7 +23486,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="287" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="6" t="s">
         <v>600</v>
       </c>
@@ -22509,7 +23554,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="288" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="6" t="s">
         <v>602</v>
       </c>
@@ -22577,7 +23622,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="289" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="6" t="s">
         <v>605</v>
       </c>
@@ -22645,7 +23690,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="290" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="6" t="s">
         <v>605</v>
       </c>
@@ -22713,7 +23758,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="291" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="14" t="s">
         <v>609</v>
       </c>
@@ -22781,7 +23826,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="292" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="6" t="s">
         <v>612</v>
       </c>
@@ -22849,7 +23894,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="293" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="6" t="s">
         <v>354</v>
       </c>
@@ -22917,7 +23962,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="294" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="5" t="s">
         <v>549</v>
       </c>
@@ -22985,7 +24030,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="295" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="1" t="s">
         <v>617</v>
       </c>
@@ -23053,7 +24098,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="296" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="6" t="s">
         <v>612</v>
       </c>
@@ -23121,7 +24166,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="297" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="6" t="s">
         <v>143</v>
       </c>
@@ -23189,7 +24234,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="298" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="6" t="s">
         <v>140</v>
       </c>
@@ -23257,7 +24302,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="299" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="14" t="s">
         <v>622</v>
       </c>
@@ -23325,7 +24370,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="300" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="6" t="s">
         <v>140</v>
       </c>
@@ -23393,7 +24438,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="301" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="3" t="s">
         <v>626</v>
       </c>
@@ -23461,7 +24506,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="302" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>628</v>
       </c>
@@ -23529,7 +24574,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="303" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>629</v>
       </c>
@@ -23597,7 +24642,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="304" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="6" t="s">
         <v>661</v>
       </c>
@@ -23664,7 +24709,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="305" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="6" t="s">
         <v>658</v>
       </c>
@@ -23731,7 +24776,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="306" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" s="6" t="s">
         <v>466</v>
       </c>
@@ -23798,7 +24843,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="307" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" s="6" t="s">
         <v>43</v>
       </c>
@@ -23865,7 +24910,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="308" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="6" t="s">
         <v>641</v>
       </c>
@@ -23932,7 +24977,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="309" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="6" t="s">
         <v>641</v>
       </c>
@@ -23999,7 +25044,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="310" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" s="6" t="s">
         <v>651</v>
       </c>
@@ -24066,7 +25111,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="311" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="6" t="s">
         <v>172</v>
       </c>
@@ -24133,7 +25178,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="312" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" s="6" t="s">
         <v>172</v>
       </c>
@@ -24200,7 +25245,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="313" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" s="6" t="s">
         <v>172</v>
       </c>
@@ -24267,7 +25312,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="314" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="6" t="s">
         <v>172</v>
       </c>
@@ -24334,7 +25379,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="315" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="6" t="s">
         <v>172</v>
       </c>
@@ -24401,7 +25446,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="316" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" s="6" t="s">
         <v>172</v>
       </c>
@@ -24468,7 +25513,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="317" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" s="6" t="s">
         <v>91</v>
       </c>
@@ -24535,7 +25580,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="318" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" s="6" t="s">
         <v>642</v>
       </c>
@@ -24602,7 +25647,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="319" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="6" t="s">
         <v>641</v>
       </c>
@@ -24669,7 +25714,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="320" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" s="6" t="s">
         <v>639</v>
       </c>
@@ -24736,7 +25781,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="321" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="6" t="s">
         <v>637</v>
       </c>
@@ -24803,7 +25848,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="322" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" s="6" t="s">
         <v>636</v>
       </c>
@@ -24870,7 +25915,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="323" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="6" t="s">
         <v>172</v>
       </c>
@@ -24937,7 +25982,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="324" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="6" t="s">
         <v>634</v>
       </c>
@@ -25004,7 +26049,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="325" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="6" t="s">
         <v>439</v>
       </c>
@@ -25071,7 +26116,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="326" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="6" t="s">
         <v>172</v>
       </c>
@@ -25138,7 +26183,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="327" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="6" t="s">
         <v>172</v>
       </c>
@@ -25205,7 +26250,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="328" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" s="6" t="s">
         <v>651</v>
       </c>
@@ -25272,7 +26317,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="329" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" s="6" t="s">
         <v>666</v>
       </c>
@@ -25575,7 +26620,7 @@
         <v>46146</v>
       </c>
       <c r="J333" s="16">
-        <f t="shared" ref="J333:J370" si="29">+NETWORKDAYS(H333,I333)</f>
+        <f t="shared" ref="J333:J384" si="29">+NETWORKDAYS(H333,I333)</f>
         <v>11</v>
       </c>
       <c r="K333" s="17" t="s">
@@ -25604,7 +26649,7 @@
         <v>46146</v>
       </c>
       <c r="S333" s="16">
-        <f t="shared" ref="S333:S370" si="30">NETWORKDAYS(H333,R333)</f>
+        <f t="shared" ref="S333:S384" si="30">NETWORKDAYS(H333,R333)</f>
         <v>11</v>
       </c>
       <c r="T333" s="5" t="s">
@@ -28128,236 +29173,1193 @@
         <v>551</v>
       </c>
     </row>
+    <row r="371" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A371" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B371" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C371" s="1">
+        <v>61240462</v>
+      </c>
+      <c r="D371" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="E371" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="F371" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G371" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H371" s="8">
+        <v>46120</v>
+      </c>
+      <c r="I371" s="7">
+        <v>46162</v>
+      </c>
+      <c r="J371" s="16">
+        <f t="shared" si="29"/>
+        <v>31</v>
+      </c>
+      <c r="K371" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L371" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="M371" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N371" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O371" s="6">
+        <v>0</v>
+      </c>
+      <c r="P371" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q371" s="12">
+        <v>0</v>
+      </c>
+      <c r="R371" s="8">
+        <v>46162</v>
+      </c>
+      <c r="S371" s="16">
+        <f t="shared" si="30"/>
+        <v>31</v>
+      </c>
+      <c r="T371" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="U371" s="6" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="372" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A372" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B372" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C372" s="1">
+        <v>62715782</v>
+      </c>
+      <c r="D372" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="E372" s="1">
+        <v>2722520200</v>
+      </c>
+      <c r="F372" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G372" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H372" s="8">
+        <v>46146</v>
+      </c>
+      <c r="I372" s="7">
+        <v>46162</v>
+      </c>
+      <c r="J372" s="16">
+        <f t="shared" si="29"/>
+        <v>13</v>
+      </c>
+      <c r="K372" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L372" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M372" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N372" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O372" s="6">
+        <v>150000</v>
+      </c>
+      <c r="P372" s="6">
+        <v>40000</v>
+      </c>
+      <c r="Q372" s="12">
+        <v>190000</v>
+      </c>
+      <c r="R372" s="8">
+        <v>46162</v>
+      </c>
+      <c r="S372" s="16">
+        <f t="shared" si="30"/>
+        <v>13</v>
+      </c>
+      <c r="T372" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="U372" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="373" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A373" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="B373" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C373" s="1">
+        <v>62243628</v>
+      </c>
+      <c r="D373" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E373" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="F373" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G373" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H373" s="8">
+        <v>46137</v>
+      </c>
+      <c r="I373" s="8">
+        <v>46163</v>
+      </c>
+      <c r="J373" s="16">
+        <f t="shared" si="29"/>
+        <v>19</v>
+      </c>
+      <c r="K373" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L373" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M373" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N373" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="O373" s="6">
+        <v>500000</v>
+      </c>
+      <c r="P373" s="6">
+        <v>850000</v>
+      </c>
+      <c r="Q373" s="12">
+        <v>1350000</v>
+      </c>
+      <c r="R373" s="8">
+        <v>46163</v>
+      </c>
+      <c r="S373" s="16">
+        <f t="shared" si="30"/>
+        <v>19</v>
+      </c>
+      <c r="T373" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="U373" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="374" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A374" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="B374" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C374" s="19" t="s">
+        <v>744</v>
+      </c>
+      <c r="D374" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E374" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="F374" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G374" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H374" s="8">
+        <v>46150</v>
+      </c>
+      <c r="I374" s="7">
+        <v>46160</v>
+      </c>
+      <c r="J374" s="16">
+        <f t="shared" si="29"/>
+        <v>7</v>
+      </c>
+      <c r="K374" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L374" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M374" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N374" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="O374" s="6">
+        <v>2881416</v>
+      </c>
+      <c r="P374" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q374" s="12">
+        <v>2881416</v>
+      </c>
+      <c r="R374" s="8">
+        <v>46163</v>
+      </c>
+      <c r="S374" s="16">
+        <f t="shared" si="30"/>
+        <v>10</v>
+      </c>
+      <c r="T374" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="U374" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="375" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A375" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="B375" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C375" s="6">
+        <v>59684312</v>
+      </c>
+      <c r="D375" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E375" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="F375" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G375" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H375" s="8">
+        <v>46098</v>
+      </c>
+      <c r="I375" s="8">
+        <v>46162</v>
+      </c>
+      <c r="J375" s="16">
+        <f t="shared" si="29"/>
+        <v>47</v>
+      </c>
+      <c r="K375" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L375" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M375" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N375" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O375" s="6">
+        <v>0</v>
+      </c>
+      <c r="P375" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q375" s="12">
+        <v>0</v>
+      </c>
+      <c r="R375" s="8">
+        <v>46163</v>
+      </c>
+      <c r="S375" s="16">
+        <f t="shared" si="30"/>
+        <v>48</v>
+      </c>
+      <c r="T375" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="U375" s="6" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="376" spans="1:21" ht="24.5" x14ac:dyDescent="0.35">
+      <c r="A376" s="21" t="s">
+        <v>748</v>
+      </c>
+      <c r="B376" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C376" s="6">
+        <v>62014200</v>
+      </c>
+      <c r="D376" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E376" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="F376" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G376" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H376" s="8">
+        <v>46133</v>
+      </c>
+      <c r="I376" s="8">
+        <v>46162</v>
+      </c>
+      <c r="J376" s="16">
+        <f t="shared" si="29"/>
+        <v>22</v>
+      </c>
+      <c r="K376" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L376" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M376" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N376" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O376" s="6">
+        <v>0</v>
+      </c>
+      <c r="P376" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q376" s="12">
+        <v>0</v>
+      </c>
+      <c r="R376" s="8">
+        <v>46163</v>
+      </c>
+      <c r="S376" s="16">
+        <f t="shared" si="30"/>
+        <v>23</v>
+      </c>
+      <c r="T376" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="U376" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="377" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A377" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="B377" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C377" s="6">
+        <v>63143165</v>
+      </c>
+      <c r="D377" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E377" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="F377" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G377" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H377" s="10">
+        <v>46154</v>
+      </c>
+      <c r="I377" s="8">
+        <v>46161</v>
+      </c>
+      <c r="J377" s="16">
+        <f t="shared" si="29"/>
+        <v>6</v>
+      </c>
+      <c r="K377" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L377" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M377" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N377" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="O377" s="6">
+        <v>7837678</v>
+      </c>
+      <c r="P377" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q377" s="12">
+        <v>7837678</v>
+      </c>
+      <c r="R377" s="8">
+        <v>46163</v>
+      </c>
+      <c r="S377" s="16">
+        <f t="shared" si="30"/>
+        <v>8</v>
+      </c>
+      <c r="T377" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="U377" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="378" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A378" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="B378" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C378" s="6">
+        <v>63518049</v>
+      </c>
+      <c r="D378" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E378" s="6" t="s">
+        <v>753</v>
+      </c>
+      <c r="F378" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G378" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H378" s="8">
+        <v>46161</v>
+      </c>
+      <c r="I378" s="8">
+        <v>46163</v>
+      </c>
+      <c r="J378" s="16">
+        <f t="shared" si="29"/>
+        <v>3</v>
+      </c>
+      <c r="K378" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L378" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M378" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N378" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O378" s="6">
+        <v>1100000</v>
+      </c>
+      <c r="P378" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q378" s="12">
+        <v>1100000</v>
+      </c>
+      <c r="R378" s="8">
+        <v>46163</v>
+      </c>
+      <c r="S378" s="16">
+        <f t="shared" si="30"/>
+        <v>3</v>
+      </c>
+      <c r="T378" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="U378" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="379" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A379" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="B379" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C379" s="6">
+        <v>63518010</v>
+      </c>
+      <c r="D379" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E379" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="F379" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G379" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H379" s="8">
+        <v>46161</v>
+      </c>
+      <c r="I379" s="8">
+        <v>46163</v>
+      </c>
+      <c r="J379" s="16">
+        <f t="shared" si="29"/>
+        <v>3</v>
+      </c>
+      <c r="K379" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L379" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M379" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N379" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O379" s="6">
+        <v>1100000</v>
+      </c>
+      <c r="P379" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q379" s="12">
+        <v>1100000</v>
+      </c>
+      <c r="R379" s="8">
+        <v>46163</v>
+      </c>
+      <c r="S379" s="16">
+        <f t="shared" si="30"/>
+        <v>3</v>
+      </c>
+      <c r="T379" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="U379" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="380" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A380" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B380" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C380" s="1">
+        <v>60874276</v>
+      </c>
+      <c r="D380" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E380" s="1">
+        <v>2722229530</v>
+      </c>
+      <c r="F380" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G380" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H380" s="7">
+        <v>46113</v>
+      </c>
+      <c r="I380" s="8">
+        <v>46163</v>
+      </c>
+      <c r="J380" s="16">
+        <f t="shared" si="29"/>
+        <v>37</v>
+      </c>
+      <c r="K380" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L380" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M380" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N380" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O380" s="6">
+        <v>60000</v>
+      </c>
+      <c r="P380" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q380" s="12">
+        <v>60000</v>
+      </c>
+      <c r="R380" s="8">
+        <v>46163</v>
+      </c>
+      <c r="S380" s="16">
+        <f t="shared" si="30"/>
+        <v>37</v>
+      </c>
+      <c r="T380" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="U380" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="381" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A381" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="B381" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C381" s="6">
+        <v>62170297</v>
+      </c>
+      <c r="D381" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="E381" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="F381" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G381" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H381" s="8">
+        <v>46136</v>
+      </c>
+      <c r="I381" s="8">
+        <v>46163</v>
+      </c>
+      <c r="J381" s="16">
+        <f t="shared" si="29"/>
+        <v>20</v>
+      </c>
+      <c r="K381" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L381" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M381" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N381" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O381" s="6">
+        <v>1500000</v>
+      </c>
+      <c r="P381" s="6">
+        <v>456057</v>
+      </c>
+      <c r="Q381" s="12">
+        <v>1956057</v>
+      </c>
+      <c r="R381" s="8">
+        <v>46164</v>
+      </c>
+      <c r="S381" s="16">
+        <f t="shared" si="30"/>
+        <v>21</v>
+      </c>
+      <c r="T381" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="U381" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="382" spans="1:21" ht="24" x14ac:dyDescent="0.35">
+      <c r="A382" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="B382" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C382" s="6">
+        <v>58896886</v>
+      </c>
+      <c r="D382" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="E382" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="F382" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G382" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H382" s="8">
+        <v>46079</v>
+      </c>
+      <c r="I382" s="8">
+        <v>46163</v>
+      </c>
+      <c r="J382" s="16">
+        <f t="shared" si="29"/>
+        <v>61</v>
+      </c>
+      <c r="K382" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L382" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M382" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N382" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O382" s="6">
+        <v>2000000</v>
+      </c>
+      <c r="P382" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q382" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="R382" s="8">
+        <v>46164</v>
+      </c>
+      <c r="S382" s="16">
+        <f t="shared" si="30"/>
+        <v>62</v>
+      </c>
+      <c r="T382" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="U382" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="383" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A383" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B383" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C383" s="6">
+        <v>58797846</v>
+      </c>
+      <c r="D383" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E383" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="F383" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G383" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H383" s="8">
+        <v>46076</v>
+      </c>
+      <c r="I383" s="8">
+        <v>46164</v>
+      </c>
+      <c r="J383" s="16">
+        <f t="shared" si="29"/>
+        <v>65</v>
+      </c>
+      <c r="K383" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L383" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="M383" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N383" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="O383" s="6">
+        <v>2000000</v>
+      </c>
+      <c r="P383" s="6">
+        <v>462000</v>
+      </c>
+      <c r="Q383" s="12">
+        <v>2462000</v>
+      </c>
+      <c r="R383" s="8">
+        <v>46164</v>
+      </c>
+      <c r="S383" s="16">
+        <f t="shared" si="30"/>
+        <v>65</v>
+      </c>
+      <c r="T383" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="U383" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="384" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A384" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="B384" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C384" s="6">
+        <v>61828334</v>
+      </c>
+      <c r="D384" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E384" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="F384" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G384" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H384" s="8">
+        <v>46130</v>
+      </c>
+      <c r="I384" s="8">
+        <v>46162</v>
+      </c>
+      <c r="J384" s="16">
+        <f t="shared" si="29"/>
+        <v>23</v>
+      </c>
+      <c r="K384" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L384" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="M384" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N384" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="O384" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="P384" s="12">
+        <v>678945</v>
+      </c>
+      <c r="Q384" s="33">
+        <f>P384+O384</f>
+        <v>1678945</v>
+      </c>
+      <c r="R384" s="7">
+        <v>46164</v>
+      </c>
+      <c r="S384" s="16">
+        <f t="shared" si="30"/>
+        <v>25</v>
+      </c>
+      <c r="T384" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="U384" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U370" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U384" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="17">
+      <filters>
+        <dateGroupItem year="2026" month="5" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="88" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="92"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C356:C357 C363:C1048576">
-    <cfRule type="duplicateValues" dxfId="82" priority="177"/>
+  <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C356:C357 C363:C370 C385:C1048576">
+    <cfRule type="duplicateValues" dxfId="86" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="181"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C356:C357 C363:C370 C385:C1048576">
+    <cfRule type="duplicateValues" dxfId="84" priority="190"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C232 C244:C287 C304:C329 C356:C357 C363:C370 C385:C1048576">
+    <cfRule type="duplicateValues" dxfId="83" priority="195"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C294 C304:C329 C356:C357 C363:C370 C385:C1048576">
+    <cfRule type="duplicateValues" dxfId="82" priority="200"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C295 C304:C329 C356:C357 C363:C370 C385:C1048576">
     <cfRule type="duplicateValues" dxfId="81" priority="176"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C356:C357 C363:C1048576">
-    <cfRule type="duplicateValues" dxfId="80" priority="186"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C232 C244:C287 C304:C329 C356:C357 C363:C1048576">
-    <cfRule type="duplicateValues" dxfId="79" priority="191"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C294 C304:C329 C356:C357 C363:C1048576">
-    <cfRule type="duplicateValues" dxfId="78" priority="196"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C295 C304:C329 C356:C357 C363:C1048576">
-    <cfRule type="duplicateValues" dxfId="77" priority="172"/>
+  <conditionalFormatting sqref="C1:C370 C385:C1048576">
+    <cfRule type="duplicateValues" dxfId="80" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="76" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="74" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="72" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="71" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="69" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="68" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="67" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="66" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="65" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="64" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
+    <cfRule type="duplicateValues" dxfId="66" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C33:C37">
+    <cfRule type="duplicateValues" dxfId="65" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C39">
+    <cfRule type="duplicateValues" dxfId="64" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40">
     <cfRule type="duplicateValues" dxfId="63" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="62" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="61" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="60" priority="49"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="59" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="58" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="57" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="56" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="55" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="54" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
-    <cfRule type="duplicateValues" dxfId="53" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="52" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="51" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C92">
+    <cfRule type="duplicateValues" dxfId="52" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C93">
+    <cfRule type="duplicateValues" dxfId="51" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C98">
     <cfRule type="duplicateValues" dxfId="50" priority="77"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C92">
+  <conditionalFormatting sqref="C101">
     <cfRule type="duplicateValues" dxfId="49" priority="76"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="48" priority="75"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="47" priority="73"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="46" priority="72"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="45" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="43" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C114">
-    <cfRule type="duplicateValues" dxfId="42" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="41" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="40" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C157:C160">
-    <cfRule type="duplicateValues" dxfId="38" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C161:C163">
-    <cfRule type="duplicateValues" dxfId="37" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="36" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C167">
+    <cfRule type="duplicateValues" dxfId="37" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C168">
     <cfRule type="duplicateValues" dxfId="35" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
+  <conditionalFormatting sqref="C170">
+    <cfRule type="duplicateValues" dxfId="34" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C171">
     <cfRule type="duplicateValues" dxfId="33" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C168">
-    <cfRule type="duplicateValues" dxfId="32" priority="29"/>
+  <conditionalFormatting sqref="C173">
+    <cfRule type="duplicateValues" dxfId="32" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="31" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C171">
+  <conditionalFormatting sqref="C174">
     <cfRule type="duplicateValues" dxfId="30" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C173">
-    <cfRule type="duplicateValues" dxfId="29" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C175">
-    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="25" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C178">
-    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179">
-    <cfRule type="duplicateValues" dxfId="23" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C206:C212">
-    <cfRule type="duplicateValues" dxfId="21" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
-    <cfRule type="duplicateValues" dxfId="20" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C208">
+    <cfRule type="duplicateValues" dxfId="21" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C218:C223">
     <cfRule type="duplicateValues" dxfId="19" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C208">
-    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C218:C223">
-    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C225:C232">
-    <cfRule type="duplicateValues" dxfId="15" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C233:C243">
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C341:C347">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="12" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="10" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="9" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="8" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="7" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="6" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="5" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="4" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="3" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172">
-    <cfRule type="duplicateValues" dxfId="2" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175">
-    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E243">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C371:C381">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C384">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="754" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D75B285E-1600-4B0B-8575-D44C5BD0CFD1}"/>
+  <xr:revisionPtr revIDLastSave="811" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A756E5D-AE0A-41C6-91C5-9ABA3CB29A99}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$384</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$390</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4130" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4202" uniqueCount="775">
   <si>
     <t>Client</t>
   </si>
@@ -2332,6 +2332,39 @@
   </si>
   <si>
     <t>SYTHD260116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYTHD260093 </t>
+  </si>
+  <si>
+    <t>MANKONO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUVPN260014 </t>
+  </si>
+  <si>
+    <t>TOUMODI</t>
+  </si>
+  <si>
+    <t>BUVPN260027</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>SYTHD260133</t>
+  </si>
+  <si>
+    <t>GOULIA</t>
+  </si>
+  <si>
+    <t>BUVPN260089</t>
+  </si>
+  <si>
+    <t>BRIDGE MICROFINANCE</t>
+  </si>
+  <si>
+    <t>SYTHD260140</t>
   </si>
 </sst>
 </file>
@@ -2678,927 +2711,7 @@
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="185">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="93">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4864,7 +3977,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:W384"/>
+  <dimension ref="A1:W390"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="18" customWidth="1"/>
@@ -26620,7 +25733,7 @@
         <v>46146</v>
       </c>
       <c r="J333" s="16">
-        <f t="shared" ref="J333:J384" si="29">+NETWORKDAYS(H333,I333)</f>
+        <f t="shared" ref="J333:J390" si="29">+NETWORKDAYS(H333,I333)</f>
         <v>11</v>
       </c>
       <c r="K333" s="17" t="s">
@@ -26649,7 +25762,7 @@
         <v>46146</v>
       </c>
       <c r="S333" s="16">
-        <f t="shared" ref="S333:S384" si="30">NETWORKDAYS(H333,R333)</f>
+        <f t="shared" ref="S333:S390" si="30">NETWORKDAYS(H333,R333)</f>
         <v>11</v>
       </c>
       <c r="T333" s="5" t="s">
@@ -30112,8 +29225,410 @@
         <v>551</v>
       </c>
     </row>
+    <row r="385" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A385" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B385" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C385" s="55">
+        <v>58963646</v>
+      </c>
+      <c r="D385" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="E385" s="55" t="s">
+        <v>764</v>
+      </c>
+      <c r="F385" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="G385" s="55" t="s">
+        <v>41</v>
+      </c>
+      <c r="H385" s="56">
+        <v>46078</v>
+      </c>
+      <c r="I385" s="56">
+        <v>46163</v>
+      </c>
+      <c r="J385" s="16">
+        <f t="shared" si="29"/>
+        <v>62</v>
+      </c>
+      <c r="K385" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L385" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="M385" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N385" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="O385" s="6">
+        <v>0</v>
+      </c>
+      <c r="P385" s="6">
+        <v>899000</v>
+      </c>
+      <c r="Q385" s="12">
+        <v>899000</v>
+      </c>
+      <c r="R385" s="8">
+        <v>46164</v>
+      </c>
+      <c r="S385" s="16">
+        <f t="shared" si="30"/>
+        <v>63</v>
+      </c>
+      <c r="T385" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="U385" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="386" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A386" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B386" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="C386" s="55">
+        <v>56611212</v>
+      </c>
+      <c r="D386" s="55" t="s">
+        <v>765</v>
+      </c>
+      <c r="E386" s="55" t="s">
+        <v>766</v>
+      </c>
+      <c r="F386" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="G386" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H386" s="56">
+        <v>46035</v>
+      </c>
+      <c r="I386" s="56">
+        <v>46136</v>
+      </c>
+      <c r="J386" s="16">
+        <f t="shared" si="29"/>
+        <v>74</v>
+      </c>
+      <c r="K386" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L386" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="M386" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N386" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="O386" s="6">
+        <v>2000000</v>
+      </c>
+      <c r="P386" s="6">
+        <v>300000</v>
+      </c>
+      <c r="Q386" s="12">
+        <v>2300000</v>
+      </c>
+      <c r="R386" s="8">
+        <v>46168</v>
+      </c>
+      <c r="S386" s="16">
+        <f t="shared" si="30"/>
+        <v>96</v>
+      </c>
+      <c r="T386" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="U386" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="387" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A387" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B387" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="C387" s="55">
+        <v>56607988</v>
+      </c>
+      <c r="D387" s="55" t="s">
+        <v>767</v>
+      </c>
+      <c r="E387" s="55" t="s">
+        <v>768</v>
+      </c>
+      <c r="F387" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="G387" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H387" s="56">
+        <v>46035</v>
+      </c>
+      <c r="I387" s="56">
+        <v>46141</v>
+      </c>
+      <c r="J387" s="16">
+        <f t="shared" si="29"/>
+        <v>77</v>
+      </c>
+      <c r="K387" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L387" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="M387" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N387" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="O387" s="6">
+        <v>2000000</v>
+      </c>
+      <c r="P387" s="6">
+        <v>300000</v>
+      </c>
+      <c r="Q387" s="12">
+        <v>2300000</v>
+      </c>
+      <c r="R387" s="8">
+        <v>46168</v>
+      </c>
+      <c r="S387" s="16">
+        <f t="shared" si="30"/>
+        <v>96</v>
+      </c>
+      <c r="T387" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="U387" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="388" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A388" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B388" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C388" s="6">
+        <v>58963630</v>
+      </c>
+      <c r="D388" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E388" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="F388" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G388" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H388" s="8">
+        <v>46078</v>
+      </c>
+      <c r="I388" s="8">
+        <v>46168</v>
+      </c>
+      <c r="J388" s="16">
+        <f t="shared" si="29"/>
+        <v>65</v>
+      </c>
+      <c r="K388" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L388" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="M388" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N388" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="O388" s="6">
+        <v>0</v>
+      </c>
+      <c r="P388" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q388" s="12">
+        <v>0</v>
+      </c>
+      <c r="R388" s="8">
+        <v>46168</v>
+      </c>
+      <c r="S388" s="16">
+        <f t="shared" si="30"/>
+        <v>65</v>
+      </c>
+      <c r="T388" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="U388" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="389" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A389" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B389" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="C389" s="55">
+        <v>56601982</v>
+      </c>
+      <c r="D389" s="55" t="s">
+        <v>771</v>
+      </c>
+      <c r="E389" s="55" t="s">
+        <v>772</v>
+      </c>
+      <c r="F389" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="G389" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H389" s="56">
+        <v>46035</v>
+      </c>
+      <c r="I389" s="56">
+        <v>46162</v>
+      </c>
+      <c r="J389" s="16">
+        <f t="shared" si="29"/>
+        <v>92</v>
+      </c>
+      <c r="K389" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="L389" s="55" t="s">
+        <v>327</v>
+      </c>
+      <c r="M389" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="N389" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="O389" s="55">
+        <v>8033717</v>
+      </c>
+      <c r="P389" s="55">
+        <v>400000</v>
+      </c>
+      <c r="Q389" s="60">
+        <v>8433717</v>
+      </c>
+      <c r="R389" s="56">
+        <v>46168</v>
+      </c>
+      <c r="S389" s="16">
+        <f t="shared" si="30"/>
+        <v>96</v>
+      </c>
+      <c r="T389" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="U389" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="390" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A390" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="B390" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C390" s="55">
+        <v>62937923</v>
+      </c>
+      <c r="D390" s="55" t="s">
+        <v>529</v>
+      </c>
+      <c r="E390" s="55" t="s">
+        <v>774</v>
+      </c>
+      <c r="F390" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="G390" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H390" s="56">
+        <v>46150</v>
+      </c>
+      <c r="I390" s="56">
+        <v>46164</v>
+      </c>
+      <c r="J390" s="16">
+        <f t="shared" si="29"/>
+        <v>11</v>
+      </c>
+      <c r="K390" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="L390" s="55" t="s">
+        <v>304</v>
+      </c>
+      <c r="M390" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="N390" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="O390" s="55">
+        <v>250000</v>
+      </c>
+      <c r="P390" s="55">
+        <v>370000</v>
+      </c>
+      <c r="Q390" s="60">
+        <v>620000</v>
+      </c>
+      <c r="R390" s="56">
+        <v>46168</v>
+      </c>
+      <c r="S390" s="16">
+        <f t="shared" si="30"/>
+        <v>13</v>
+      </c>
+      <c r="T390" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="U390" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U384" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:U390" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="17">
       <filters>
         <dateGroupItem year="2026" month="5" dateTimeGrouping="month"/>
@@ -30147,219 +29662,219 @@
   <conditionalFormatting sqref="C1:C370 C385:C1048576">
     <cfRule type="duplicateValues" dxfId="80" priority="4"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="79" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="79" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
-    <cfRule type="duplicateValues" dxfId="77" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="75" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="74" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="72" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="71" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="70" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="duplicateValues" dxfId="69" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="68" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C31">
-    <cfRule type="duplicateValues" dxfId="67" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="66" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="duplicateValues" dxfId="65" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39">
-    <cfRule type="duplicateValues" dxfId="64" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="duplicateValues" dxfId="63" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="duplicateValues" dxfId="62" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C66">
-    <cfRule type="duplicateValues" dxfId="61" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="60" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="59" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="58" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C109 C1">
-    <cfRule type="duplicateValues" dxfId="57" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
-    <cfRule type="duplicateValues" dxfId="56" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C80:C81">
-    <cfRule type="duplicateValues" dxfId="55" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="54" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="52" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="51" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="50" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="49" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="48" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
-    <cfRule type="duplicateValues" dxfId="46" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C114">
-    <cfRule type="duplicateValues" dxfId="45" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115">
-    <cfRule type="duplicateValues" dxfId="44" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="43" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C157:C160">
-    <cfRule type="duplicateValues" dxfId="41" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C161:C163">
-    <cfRule type="duplicateValues" dxfId="40" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="39" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="37" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C168">
-    <cfRule type="duplicateValues" dxfId="35" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="34" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171">
-    <cfRule type="duplicateValues" dxfId="33" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173">
-    <cfRule type="duplicateValues" dxfId="32" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="30" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C175">
-    <cfRule type="duplicateValues" dxfId="29" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="28" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C178">
-    <cfRule type="duplicateValues" dxfId="27" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179">
-    <cfRule type="duplicateValues" dxfId="26" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C206:C212">
-    <cfRule type="duplicateValues" dxfId="24" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
-    <cfRule type="duplicateValues" dxfId="23" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C208">
-    <cfRule type="duplicateValues" dxfId="21" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218:C223">
-    <cfRule type="duplicateValues" dxfId="19" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C225:C232">
-    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C233:C243">
-    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C341:C347">
-    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C371:C381">
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C384">
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="15" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E15 E17:E31">
-    <cfRule type="duplicateValues" dxfId="13" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="12" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E31">
-    <cfRule type="duplicateValues" dxfId="11" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="10" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="duplicateValues" dxfId="9" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="8" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="duplicateValues" dxfId="7" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E77:E97 E1">
-    <cfRule type="duplicateValues" dxfId="6" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172">
-    <cfRule type="duplicateValues" dxfId="5" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175">
-    <cfRule type="duplicateValues" dxfId="4" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E243">
-    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C371:C381">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C384">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="811" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A756E5D-AE0A-41C6-91C5-9ABA3CB29A99}"/>
+  <xr:revisionPtr revIDLastSave="834" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDF0F2A0-FD9A-4F6F-9A90-8F8F2616E3D8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$390</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$395</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4202" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4260" uniqueCount="782">
   <si>
     <t>Client</t>
   </si>
@@ -2365,6 +2365,27 @@
   </si>
   <si>
     <t>SYTHD260140</t>
+  </si>
+  <si>
+    <t>STE SICPA CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MANTRA IVOIRE SA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYTHD260131 </t>
+  </si>
+  <si>
+    <t>INTELCIA COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>SYTHD170169</t>
+  </si>
+  <si>
+    <t>SYTHD170178</t>
+  </si>
+  <si>
+    <t>MINISTERE ECONOMIE ET FINANCES/ OQSF- CI</t>
   </si>
 </sst>
 </file>
@@ -3977,7 +3998,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:W390"/>
+  <dimension ref="A1:W395"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="18" customWidth="1"/>
@@ -25733,7 +25754,7 @@
         <v>46146</v>
       </c>
       <c r="J333" s="16">
-        <f t="shared" ref="J333:J390" si="29">+NETWORKDAYS(H333,I333)</f>
+        <f t="shared" ref="J333:J395" si="29">+NETWORKDAYS(H333,I333)</f>
         <v>11</v>
       </c>
       <c r="K333" s="17" t="s">
@@ -25762,7 +25783,7 @@
         <v>46146</v>
       </c>
       <c r="S333" s="16">
-        <f t="shared" ref="S333:S390" si="30">NETWORKDAYS(H333,R333)</f>
+        <f t="shared" ref="S333:S395" si="30">NETWORKDAYS(H333,R333)</f>
         <v>11</v>
       </c>
       <c r="T333" s="5" t="s">
@@ -29627,8 +29648,343 @@
         <v>551</v>
       </c>
     </row>
+    <row r="391" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A391" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="B391" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C391" s="6">
+        <v>61710072</v>
+      </c>
+      <c r="D391" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E391" s="6">
+        <v>2721711717</v>
+      </c>
+      <c r="F391" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G391" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H391" s="8">
+        <v>46128</v>
+      </c>
+      <c r="I391" s="8">
+        <v>46168</v>
+      </c>
+      <c r="J391" s="16">
+        <f t="shared" si="29"/>
+        <v>29</v>
+      </c>
+      <c r="K391" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L391" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M391" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N391" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O391" s="6">
+        <v>150000</v>
+      </c>
+      <c r="P391" s="6">
+        <v>40000</v>
+      </c>
+      <c r="Q391" s="12">
+        <v>190000</v>
+      </c>
+      <c r="R391" s="8">
+        <v>46168</v>
+      </c>
+      <c r="S391" s="16">
+        <f t="shared" si="30"/>
+        <v>29</v>
+      </c>
+      <c r="T391" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="U391" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="392" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A392" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="B392" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C392" s="6">
+        <v>59541145</v>
+      </c>
+      <c r="D392" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E392" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="F392" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G392" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H392" s="8">
+        <v>46088</v>
+      </c>
+      <c r="I392" s="8">
+        <v>46162</v>
+      </c>
+      <c r="J392" s="16">
+        <f t="shared" si="29"/>
+        <v>53</v>
+      </c>
+      <c r="K392" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L392" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="M392" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N392" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="O392" s="6">
+        <v>0</v>
+      </c>
+      <c r="P392" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q392" s="12">
+        <v>0</v>
+      </c>
+      <c r="R392" s="8">
+        <v>46170</v>
+      </c>
+      <c r="S392" s="16">
+        <f t="shared" si="30"/>
+        <v>59</v>
+      </c>
+      <c r="T392" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="U392" s="6" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="393" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A393" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="B393" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C393" s="6">
+        <v>62348127</v>
+      </c>
+      <c r="D393" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E393" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="F393" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G393" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H393" s="8">
+        <v>46139</v>
+      </c>
+      <c r="I393" s="8">
+        <v>46170</v>
+      </c>
+      <c r="J393" s="16">
+        <f t="shared" si="29"/>
+        <v>24</v>
+      </c>
+      <c r="K393" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L393" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M393" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N393" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="O393" s="6">
+        <v>0</v>
+      </c>
+      <c r="P393" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q393" s="12">
+        <v>0</v>
+      </c>
+      <c r="R393" s="8">
+        <v>46170</v>
+      </c>
+      <c r="S393" s="16">
+        <f t="shared" si="30"/>
+        <v>24</v>
+      </c>
+      <c r="T393" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="U393" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="394" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A394" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="B394" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C394" s="6">
+        <v>62346912</v>
+      </c>
+      <c r="D394" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E394" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="F394" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G394" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H394" s="8">
+        <v>46139</v>
+      </c>
+      <c r="I394" s="8">
+        <v>46170</v>
+      </c>
+      <c r="J394" s="16">
+        <f t="shared" si="29"/>
+        <v>24</v>
+      </c>
+      <c r="K394" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L394" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M394" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N394" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="O394" s="6">
+        <v>1500000</v>
+      </c>
+      <c r="P394" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q394" s="12">
+        <v>1500000</v>
+      </c>
+      <c r="R394" s="8">
+        <v>46170</v>
+      </c>
+      <c r="S394" s="16">
+        <f t="shared" si="30"/>
+        <v>24</v>
+      </c>
+      <c r="T394" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="U394" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="395" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A395" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="B395" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C395" s="6">
+        <v>62880812</v>
+      </c>
+      <c r="D395" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E395" s="6">
+        <v>2722560070</v>
+      </c>
+      <c r="F395" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G395" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H395" s="8">
+        <v>46149</v>
+      </c>
+      <c r="I395" s="8">
+        <v>46170</v>
+      </c>
+      <c r="J395" s="16">
+        <f t="shared" si="29"/>
+        <v>16</v>
+      </c>
+      <c r="K395" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L395" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M395" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N395" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O395" s="6">
+        <v>150000</v>
+      </c>
+      <c r="P395" s="6">
+        <v>40000</v>
+      </c>
+      <c r="Q395" s="12">
+        <v>190000</v>
+      </c>
+      <c r="R395" s="8">
+        <v>46170</v>
+      </c>
+      <c r="S395" s="16">
+        <f t="shared" si="30"/>
+        <v>16</v>
+      </c>
+      <c r="T395" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="U395" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U390" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:U395" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="17">
       <filters>
         <dateGroupItem year="2026" month="5" dateTimeGrouping="month"/>
@@ -29637,15 +29993,15 @@
   </autoFilter>
   <conditionalFormatting sqref="C1">
     <cfRule type="duplicateValues" dxfId="92" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="92"/>
     <cfRule type="duplicateValues" dxfId="89" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C356:C357 C363:C370 C385:C1048576">
-    <cfRule type="duplicateValues" dxfId="86" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C356:C357 C363:C370 C385:C1048576">
     <cfRule type="duplicateValues" dxfId="84" priority="190"/>
@@ -29666,8 +30022,8 @@
     <cfRule type="duplicateValues" dxfId="79" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="78" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
     <cfRule type="duplicateValues" dxfId="76" priority="46"/>
@@ -29735,8 +30091,8 @@
     <cfRule type="duplicateValues" dxfId="54" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="53" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
     <cfRule type="duplicateValues" dxfId="51" priority="80"/>
@@ -29751,8 +30107,8 @@
     <cfRule type="duplicateValues" dxfId="48" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="47" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
     <cfRule type="duplicateValues" dxfId="45" priority="73"/>
@@ -29764,8 +30120,8 @@
     <cfRule type="duplicateValues" dxfId="43" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="42" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C157:C160">
     <cfRule type="duplicateValues" dxfId="40" priority="100"/>
@@ -29807,15 +30163,15 @@
     <cfRule type="duplicateValues" dxfId="26" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179">
-    <cfRule type="duplicateValues" dxfId="25" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C206:C212">
     <cfRule type="duplicateValues" dxfId="23" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
-    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C208">
     <cfRule type="duplicateValues" dxfId="20" priority="17"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="834" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDF0F2A0-FD9A-4F6F-9A90-8F8F2616E3D8}"/>
+  <xr:revisionPtr revIDLastSave="856" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52142486-C238-4408-B765-B99D48F43AFA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4260" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4272" uniqueCount="784">
   <si>
     <t>Client</t>
   </si>
@@ -2385,7 +2385,13 @@
     <t>SYTHD170178</t>
   </si>
   <si>
-    <t>MINISTERE ECONOMIE ET FINANCES/ OQSF- CI</t>
+    <t>MINISTERE ECONOMIE ET FINANCES/OQSF-CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TREICHVILLE CNTCI </t>
+  </si>
+  <si>
+    <t>BUVPN260096</t>
   </si>
 </sst>
 </file>
@@ -3998,7 +4004,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:W395"/>
+  <dimension ref="A1:W396"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="18" customWidth="1"/>
@@ -25754,7 +25760,7 @@
         <v>46146</v>
       </c>
       <c r="J333" s="16">
-        <f t="shared" ref="J333:J395" si="29">+NETWORKDAYS(H333,I333)</f>
+        <f t="shared" ref="J333:J396" si="29">+NETWORKDAYS(H333,I333)</f>
         <v>11</v>
       </c>
       <c r="K333" s="17" t="s">
@@ -25783,7 +25789,7 @@
         <v>46146</v>
       </c>
       <c r="S333" s="16">
-        <f t="shared" ref="S333:S395" si="30">NETWORKDAYS(H333,R333)</f>
+        <f t="shared" ref="S333:S396" si="30">NETWORKDAYS(H333,R333)</f>
         <v>11</v>
       </c>
       <c r="T333" s="5" t="s">
@@ -29980,6 +29986,73 @@
         <v>769</v>
       </c>
       <c r="U395" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="396" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A396" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B396" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="C396" s="55">
+        <v>63178332</v>
+      </c>
+      <c r="D396" s="55" t="s">
+        <v>782</v>
+      </c>
+      <c r="E396" s="55" t="s">
+        <v>783</v>
+      </c>
+      <c r="F396" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="G396" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="H396" s="56">
+        <v>46154</v>
+      </c>
+      <c r="I396" s="56">
+        <v>46171</v>
+      </c>
+      <c r="J396" s="16">
+        <f t="shared" si="29"/>
+        <v>14</v>
+      </c>
+      <c r="K396" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="L396" s="55" t="s">
+        <v>304</v>
+      </c>
+      <c r="M396" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="N396" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="O396" s="55">
+        <v>2000000</v>
+      </c>
+      <c r="P396" s="55">
+        <v>462000</v>
+      </c>
+      <c r="Q396" s="60">
+        <v>2462000</v>
+      </c>
+      <c r="R396" s="56">
+        <v>46171</v>
+      </c>
+      <c r="S396" s="16">
+        <f t="shared" si="30"/>
+        <v>14</v>
+      </c>
+      <c r="T396" s="55" t="s">
+        <v>769</v>
+      </c>
+      <c r="U396" s="55" t="s">
         <v>551</v>
       </c>
     </row>
@@ -29993,15 +30066,15 @@
   </autoFilter>
   <conditionalFormatting sqref="C1">
     <cfRule type="duplicateValues" dxfId="92" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="89"/>
     <cfRule type="duplicateValues" dxfId="89" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C356:C357 C363:C370 C385:C1048576">
-    <cfRule type="duplicateValues" dxfId="86" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C356:C357 C363:C370 C385:C1048576">
     <cfRule type="duplicateValues" dxfId="84" priority="190"/>
@@ -30022,8 +30095,8 @@
     <cfRule type="duplicateValues" dxfId="79" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="78" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
     <cfRule type="duplicateValues" dxfId="76" priority="46"/>
@@ -30091,8 +30164,8 @@
     <cfRule type="duplicateValues" dxfId="54" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="53" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
     <cfRule type="duplicateValues" dxfId="51" priority="80"/>
@@ -30107,8 +30180,8 @@
     <cfRule type="duplicateValues" dxfId="48" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="47" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103:C109">
     <cfRule type="duplicateValues" dxfId="45" priority="73"/>
@@ -30120,8 +30193,8 @@
     <cfRule type="duplicateValues" dxfId="43" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C145">
-    <cfRule type="duplicateValues" dxfId="42" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C157:C160">
     <cfRule type="duplicateValues" dxfId="40" priority="100"/>
@@ -30163,15 +30236,15 @@
     <cfRule type="duplicateValues" dxfId="26" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179">
-    <cfRule type="duplicateValues" dxfId="25" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C206:C212">
     <cfRule type="duplicateValues" dxfId="23" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
-    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C208">
     <cfRule type="duplicateValues" dxfId="20" priority="17"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="856" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52142486-C238-4408-B765-B99D48F43AFA}"/>
+  <xr:revisionPtr revIDLastSave="875" documentId="8_{96B9E37B-5941-46BA-AA97-B18EA540EAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8C548F7-52BD-4A30-AF98-88042DEBE348}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$395</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$402</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4272" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4342" uniqueCount="793">
   <si>
     <t>Client</t>
   </si>
@@ -2392,6 +2392,33 @@
   </si>
   <si>
     <t>BUVPN260096</t>
+  </si>
+  <si>
+    <t>BICICI</t>
+  </si>
+  <si>
+    <t>SYTHD260127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYTHD260126 </t>
+  </si>
+  <si>
+    <t>CFAO RETAIL</t>
+  </si>
+  <si>
+    <t>SYTHD220159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMMOBILIARE </t>
+  </si>
+  <si>
+    <t>COCODY ABATTA</t>
+  </si>
+  <si>
+    <t>ABIDJAN CINÉ SCRATC 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYTHD250140 </t>
   </si>
 </sst>
 </file>
@@ -2563,7 +2590,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2732,13 +2759,974 @@
     <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
     <cellStyle name="Monétaire [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="93">
+  <dxfs count="187">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4003,8 +4991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:W396"/>
+  <dimension ref="A1:W402"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.90625" style="18" customWidth="1"/>
@@ -4089,7 +5076,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="51" t="s">
         <v>154</v>
       </c>
@@ -4151,7 +5138,7 @@
       </c>
       <c r="U2" s="34"/>
     </row>
-    <row r="3" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>159</v>
       </c>
@@ -4213,7 +5200,7 @@
       </c>
       <c r="U3" s="34"/>
     </row>
-    <row r="4" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
         <v>154</v>
       </c>
@@ -4275,7 +5262,7 @@
       </c>
       <c r="U4" s="34"/>
     </row>
-    <row r="5" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>154</v>
       </c>
@@ -4337,7 +5324,7 @@
       </c>
       <c r="U5" s="34"/>
     </row>
-    <row r="6" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>164</v>
       </c>
@@ -4399,7 +5386,7 @@
       </c>
       <c r="U6" s="34"/>
     </row>
-    <row r="7" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>165</v>
       </c>
@@ -4461,7 +5448,7 @@
       </c>
       <c r="U7" s="34"/>
     </row>
-    <row r="8" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>166</v>
       </c>
@@ -4523,7 +5510,7 @@
       </c>
       <c r="U8" s="34"/>
     </row>
-    <row r="9" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>169</v>
       </c>
@@ -4585,7 +5572,7 @@
       </c>
       <c r="U9" s="34"/>
     </row>
-    <row r="10" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>172</v>
       </c>
@@ -4647,7 +5634,7 @@
       </c>
       <c r="U10" s="34"/>
     </row>
-    <row r="11" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>172</v>
       </c>
@@ -4709,7 +5696,7 @@
       </c>
       <c r="U11" s="34"/>
     </row>
-    <row r="12" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
         <v>177</v>
       </c>
@@ -4771,7 +5758,7 @@
       </c>
       <c r="U12" s="34"/>
     </row>
-    <row r="13" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>154</v>
       </c>
@@ -4833,7 +5820,7 @@
       </c>
       <c r="U13" s="34"/>
     </row>
-    <row r="14" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
         <v>154</v>
       </c>
@@ -4895,7 +5882,7 @@
       </c>
       <c r="U14" s="34"/>
     </row>
-    <row r="15" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>172</v>
       </c>
@@ -4957,7 +5944,7 @@
       </c>
       <c r="U15" s="34"/>
     </row>
-    <row r="16" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>154</v>
       </c>
@@ -5019,7 +6006,7 @@
       </c>
       <c r="U16" s="34"/>
     </row>
-    <row r="17" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>154</v>
       </c>
@@ -5081,7 +6068,7 @@
       </c>
       <c r="U17" s="34"/>
     </row>
-    <row r="18" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>186</v>
       </c>
@@ -5143,7 +6130,7 @@
       </c>
       <c r="U18" s="34"/>
     </row>
-    <row r="19" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>189</v>
       </c>
@@ -5205,7 +6192,7 @@
       </c>
       <c r="U19" s="34"/>
     </row>
-    <row r="20" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>189</v>
       </c>
@@ -5267,7 +6254,7 @@
       </c>
       <c r="U20" s="34"/>
     </row>
-    <row r="21" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>193</v>
       </c>
@@ -5329,7 +6316,7 @@
       </c>
       <c r="U21" s="34"/>
     </row>
-    <row r="22" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>43</v>
       </c>
@@ -5391,7 +6378,7 @@
       </c>
       <c r="U22" s="34"/>
     </row>
-    <row r="23" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>201</v>
       </c>
@@ -5453,7 +6440,7 @@
       </c>
       <c r="U23" s="34"/>
     </row>
-    <row r="24" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>204</v>
       </c>
@@ -5515,7 +6502,7 @@
       </c>
       <c r="U24" s="34"/>
     </row>
-    <row r="25" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>206</v>
       </c>
@@ -5577,7 +6564,7 @@
       </c>
       <c r="U25" s="34"/>
     </row>
-    <row r="26" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>207</v>
       </c>
@@ -5639,7 +6626,7 @@
       </c>
       <c r="U26" s="34"/>
     </row>
-    <row r="27" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>172</v>
       </c>
@@ -5701,7 +6688,7 @@
       </c>
       <c r="U27" s="34"/>
     </row>
-    <row r="28" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>210</v>
       </c>
@@ -5763,7 +6750,7 @@
       </c>
       <c r="U28" s="34"/>
     </row>
-    <row r="29" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>213</v>
       </c>
@@ -5825,7 +6812,7 @@
       </c>
       <c r="U29" s="34"/>
     </row>
-    <row r="30" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>217</v>
       </c>
@@ -5887,7 +6874,7 @@
       </c>
       <c r="U30" s="34"/>
     </row>
-    <row r="31" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>218</v>
       </c>
@@ -5949,7 +6936,7 @@
       </c>
       <c r="U31" s="34"/>
     </row>
-    <row r="32" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>81</v>
       </c>
@@ -6011,7 +6998,7 @@
       </c>
       <c r="U32" s="34"/>
     </row>
-    <row r="33" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>91</v>
       </c>
@@ -6073,7 +7060,7 @@
       </c>
       <c r="U33" s="34"/>
     </row>
-    <row r="34" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>91</v>
       </c>
@@ -6135,7 +7122,7 @@
       </c>
       <c r="U34" s="34"/>
     </row>
-    <row r="35" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>91</v>
       </c>
@@ -6197,7 +7184,7 @@
       </c>
       <c r="U35" s="34"/>
     </row>
-    <row r="36" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>91</v>
       </c>
@@ -6259,7 +7246,7 @@
       </c>
       <c r="U36" s="34"/>
     </row>
-    <row r="37" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>91</v>
       </c>
@@ -6321,7 +7308,7 @@
       </c>
       <c r="U37" s="34"/>
     </row>
-    <row r="38" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>226</v>
       </c>
@@ -6383,7 +7370,7 @@
       </c>
       <c r="U38" s="34"/>
     </row>
-    <row r="39" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
         <v>228</v>
       </c>
@@ -6445,7 +7432,7 @@
       </c>
       <c r="U39" s="34"/>
     </row>
-    <row r="40" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>91</v>
       </c>
@@ -6507,7 +7494,7 @@
       </c>
       <c r="U40" s="34"/>
     </row>
-    <row r="41" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>231</v>
       </c>
@@ -6569,7 +7556,7 @@
       </c>
       <c r="U41" s="34"/>
     </row>
-    <row r="42" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>234</v>
       </c>
@@ -6631,7 +7618,7 @@
       </c>
       <c r="U42" s="34"/>
     </row>
-    <row r="43" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>236</v>
       </c>
@@ -6693,7 +7680,7 @@
       </c>
       <c r="U43" s="34"/>
     </row>
-    <row r="44" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>237</v>
       </c>
@@ -6755,7 +7742,7 @@
       </c>
       <c r="U44" s="34"/>
     </row>
-    <row r="45" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>238</v>
       </c>
@@ -6817,7 +7804,7 @@
       </c>
       <c r="U45" s="34"/>
     </row>
-    <row r="46" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>240</v>
       </c>
@@ -6879,7 +7866,7 @@
       </c>
       <c r="U46" s="34"/>
     </row>
-    <row r="47" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
         <v>91</v>
       </c>
@@ -6941,7 +7928,7 @@
       </c>
       <c r="U47" s="34"/>
     </row>
-    <row r="48" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>243</v>
       </c>
@@ -7003,7 +7990,7 @@
       </c>
       <c r="U48" s="34"/>
     </row>
-    <row r="49" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
         <v>246</v>
       </c>
@@ -7065,7 +8052,7 @@
       </c>
       <c r="U49" s="34"/>
     </row>
-    <row r="50" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>248</v>
       </c>
@@ -7127,7 +8114,7 @@
       </c>
       <c r="U50" s="34"/>
     </row>
-    <row r="51" spans="1:21" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:21" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
         <v>250</v>
       </c>
@@ -7189,7 +8176,7 @@
       </c>
       <c r="U51" s="34"/>
     </row>
-    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>250</v>
       </c>
@@ -7251,7 +8238,7 @@
       </c>
       <c r="U52" s="34"/>
     </row>
-    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
         <v>253</v>
       </c>
@@ -7313,7 +8300,7 @@
       </c>
       <c r="U53" s="34"/>
     </row>
-    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>256</v>
       </c>
@@ -7375,7 +8362,7 @@
       </c>
       <c r="U54" s="34"/>
     </row>
-    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>258</v>
       </c>
@@ -7437,7 +8424,7 @@
       </c>
       <c r="U55" s="34"/>
     </row>
-    <row r="56" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>259</v>
       </c>
@@ -7499,7 +8486,7 @@
       </c>
       <c r="U56" s="34"/>
     </row>
-    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>259</v>
       </c>
@@ -7561,7 +8548,7 @@
       </c>
       <c r="U57" s="34"/>
     </row>
-    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
         <v>253</v>
       </c>
@@ -7623,7 +8610,7 @@
       </c>
       <c r="U58" s="34"/>
     </row>
-    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
         <v>265</v>
       </c>
@@ -7685,7 +8672,7 @@
       </c>
       <c r="U59" s="34"/>
     </row>
-    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>267</v>
       </c>
@@ -7747,7 +8734,7 @@
       </c>
       <c r="U60" s="34"/>
     </row>
-    <row r="61" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>271</v>
       </c>
@@ -7809,7 +8796,7 @@
       </c>
       <c r="U61" s="34"/>
     </row>
-    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
         <v>43</v>
       </c>
@@ -7871,7 +8858,7 @@
       </c>
       <c r="U62" s="34"/>
     </row>
-    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
         <v>58</v>
       </c>
@@ -7933,7 +8920,7 @@
       </c>
       <c r="U63" s="34"/>
     </row>
-    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>91</v>
       </c>
@@ -7995,7 +8982,7 @@
       </c>
       <c r="U64" s="34"/>
     </row>
-    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>91</v>
       </c>
@@ -8057,7 +9044,7 @@
       </c>
       <c r="U65" s="34"/>
     </row>
-    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>91</v>
       </c>
@@ -8119,7 +9106,7 @@
       </c>
       <c r="U66" s="34"/>
     </row>
-    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>282</v>
       </c>
@@ -8181,7 +9168,7 @@
       </c>
       <c r="U67" s="34"/>
     </row>
-    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>285</v>
       </c>
@@ -8243,7 +9230,7 @@
       </c>
       <c r="U68" s="34"/>
     </row>
-    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
         <v>286</v>
       </c>
@@ -8305,7 +9292,7 @@
       </c>
       <c r="U69" s="34"/>
     </row>
-    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A70" s="14" t="s">
         <v>288</v>
       </c>
@@ -8367,7 +9354,7 @@
       </c>
       <c r="U70" s="34"/>
     </row>
-    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>291</v>
       </c>
@@ -8429,7 +9416,7 @@
       </c>
       <c r="U71" s="34"/>
     </row>
-    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>292</v>
       </c>
@@ -8491,7 +9478,7 @@
       </c>
       <c r="U72" s="34"/>
     </row>
-    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A73" s="6" t="s">
         <v>91</v>
       </c>
@@ -8553,7 +9540,7 @@
       </c>
       <c r="U73" s="34"/>
     </row>
-    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
         <v>294</v>
       </c>
@@ -8615,7 +9602,7 @@
       </c>
       <c r="U74" s="34"/>
     </row>
-    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
         <v>91</v>
       </c>
@@ -8677,7 +9664,7 @@
       </c>
       <c r="U75" s="34"/>
     </row>
-    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A76" s="6" t="s">
         <v>299</v>
       </c>
@@ -8739,7 +9726,7 @@
       </c>
       <c r="U76" s="34"/>
     </row>
-    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A77" s="6" t="s">
         <v>18</v>
       </c>
@@ -8801,7 +9788,7 @@
       </c>
       <c r="U77" s="34"/>
     </row>
-    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>27</v>
       </c>
@@ -8863,7 +9850,7 @@
       </c>
       <c r="U78" s="34"/>
     </row>
-    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>30</v>
       </c>
@@ -8925,7 +9912,7 @@
       </c>
       <c r="U79" s="34"/>
     </row>
-    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
         <v>35</v>
       </c>
@@ -8987,7 +9974,7 @@
       </c>
       <c r="U80" s="34"/>
     </row>
-    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A81" s="6" t="s">
         <v>35</v>
       </c>
@@ -9049,7 +10036,7 @@
       </c>
       <c r="U81" s="34"/>
     </row>
-    <row r="82" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
         <v>35</v>
       </c>
@@ -9111,7 +10098,7 @@
       </c>
       <c r="U82" s="34"/>
     </row>
-    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A83" s="6" t="s">
         <v>43</v>
       </c>
@@ -9173,7 +10160,7 @@
       </c>
       <c r="U83" s="34"/>
     </row>
-    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A84" s="6" t="s">
         <v>43</v>
       </c>
@@ -9235,7 +10222,7 @@
       </c>
       <c r="U84" s="34"/>
     </row>
-    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
         <v>52</v>
       </c>
@@ -9297,7 +10284,7 @@
       </c>
       <c r="U85" s="34"/>
     </row>
-    <row r="86" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>55</v>
       </c>
@@ -9359,7 +10346,7 @@
       </c>
       <c r="U86" s="34"/>
     </row>
-    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A87" s="14" t="s">
         <v>58</v>
       </c>
@@ -9421,7 +10408,7 @@
       </c>
       <c r="U87" s="34"/>
     </row>
-    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
         <v>62</v>
       </c>
@@ -9483,7 +10470,7 @@
       </c>
       <c r="U88" s="34"/>
     </row>
-    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A89" s="6" t="s">
         <v>65</v>
       </c>
@@ -9545,7 +10532,7 @@
       </c>
       <c r="U89" s="34"/>
     </row>
-    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
         <v>67</v>
       </c>
@@ -9607,7 +10594,7 @@
       </c>
       <c r="U90" s="34"/>
     </row>
-    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A91" s="6" t="s">
         <v>70</v>
       </c>
@@ -9669,7 +10656,7 @@
       </c>
       <c r="U91" s="34"/>
     </row>
-    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A92" s="6" t="s">
         <v>75</v>
       </c>
@@ -9731,7 +10718,7 @@
       </c>
       <c r="U92" s="34"/>
     </row>
-    <row r="93" spans="1:21" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="21" t="s">
         <v>77</v>
       </c>
@@ -9793,7 +10780,7 @@
       </c>
       <c r="U93" s="34"/>
     </row>
-    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A94" s="6" t="s">
         <v>43</v>
       </c>
@@ -9855,7 +10842,7 @@
       </c>
       <c r="U94" s="34"/>
     </row>
-    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A95" s="6" t="s">
         <v>81</v>
       </c>
@@ -9917,7 +10904,7 @@
       </c>
       <c r="U95" s="34"/>
     </row>
-    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>85</v>
       </c>
@@ -9979,7 +10966,7 @@
       </c>
       <c r="U96" s="34"/>
     </row>
-    <row r="97" spans="1:21" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>86</v>
       </c>
@@ -10041,7 +11028,7 @@
       </c>
       <c r="U97" s="34"/>
     </row>
-    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98" s="6" t="s">
         <v>88</v>
       </c>
@@ -10103,7 +11090,7 @@
       </c>
       <c r="U98" s="34"/>
     </row>
-    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99" s="6" t="s">
         <v>91</v>
       </c>
@@ -10165,7 +11152,7 @@
       </c>
       <c r="U99" s="34"/>
     </row>
-    <row r="100" spans="1:21" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="21" t="s">
         <v>95</v>
       </c>
@@ -10227,7 +11214,7 @@
       </c>
       <c r="U100" s="34"/>
     </row>
-    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101" s="6" t="s">
         <v>58</v>
       </c>
@@ -10289,7 +11276,7 @@
       </c>
       <c r="U101" s="34"/>
     </row>
-    <row r="102" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102" s="14" t="s">
         <v>58</v>
       </c>
@@ -10351,7 +11338,7 @@
       </c>
       <c r="U102" s="34"/>
     </row>
-    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A103" s="6" t="s">
         <v>43</v>
       </c>
@@ -10413,7 +11400,7 @@
       </c>
       <c r="U103" s="34"/>
     </row>
-    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104" s="6" t="s">
         <v>103</v>
       </c>
@@ -10475,7 +11462,7 @@
       </c>
       <c r="U104" s="34"/>
     </row>
-    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>106</v>
       </c>
@@ -10537,7 +11524,7 @@
       </c>
       <c r="U105" s="34"/>
     </row>
-    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>81</v>
       </c>
@@ -10599,7 +11586,7 @@
       </c>
       <c r="U106" s="34"/>
     </row>
-    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>107</v>
       </c>
@@ -10661,7 +11648,7 @@
       </c>
       <c r="U107" s="34"/>
     </row>
-    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>108</v>
       </c>
@@ -10723,7 +11710,7 @@
       </c>
       <c r="U108" s="34"/>
     </row>
-    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>109</v>
       </c>
@@ -10785,7 +11772,7 @@
       </c>
       <c r="U109" s="34"/>
     </row>
-    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A110" s="6" t="s">
         <v>110</v>
       </c>
@@ -10847,7 +11834,7 @@
       </c>
       <c r="U110" s="34"/>
     </row>
-    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A111" s="6" t="s">
         <v>113</v>
       </c>
@@ -10909,7 +11896,7 @@
       </c>
       <c r="U111" s="34"/>
     </row>
-    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
         <v>116</v>
       </c>
@@ -10971,7 +11958,7 @@
       </c>
       <c r="U112" s="34"/>
     </row>
-    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A113" s="6" t="s">
         <v>120</v>
       </c>
@@ -11033,7 +12020,7 @@
       </c>
       <c r="U113" s="34"/>
     </row>
-    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A114" s="6" t="s">
         <v>123</v>
       </c>
@@ -11095,7 +12082,7 @@
       </c>
       <c r="U114" s="34"/>
     </row>
-    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A115" s="6" t="s">
         <v>110</v>
       </c>
@@ -11157,7 +12144,7 @@
       </c>
       <c r="U115" s="34"/>
     </row>
-    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A116" s="6" t="s">
         <v>127</v>
       </c>
@@ -11219,7 +12206,7 @@
       </c>
       <c r="U116" s="34"/>
     </row>
-    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>130</v>
       </c>
@@ -11281,7 +12268,7 @@
       </c>
       <c r="U117" s="34"/>
     </row>
-    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>131</v>
       </c>
@@ -11343,7 +12330,7 @@
       </c>
       <c r="U118" s="34"/>
     </row>
-    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A119" s="6" t="s">
         <v>132</v>
       </c>
@@ -11405,7 +12392,7 @@
       </c>
       <c r="U119" s="34"/>
     </row>
-    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A120" s="6" t="s">
         <v>134</v>
       </c>
@@ -11467,7 +12454,7 @@
       </c>
       <c r="U120" s="34"/>
     </row>
-    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A121" s="6" t="s">
         <v>134</v>
       </c>
@@ -11529,7 +12516,7 @@
       </c>
       <c r="U121" s="34"/>
     </row>
-    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A122" s="6" t="s">
         <v>140</v>
       </c>
@@ -11591,7 +12578,7 @@
       </c>
       <c r="U122" s="34"/>
     </row>
-    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A123" s="6" t="s">
         <v>143</v>
       </c>
@@ -11653,7 +12640,7 @@
       </c>
       <c r="U123" s="34"/>
     </row>
-    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A124" s="6" t="s">
         <v>145</v>
       </c>
@@ -11715,7 +12702,7 @@
       </c>
       <c r="U124" s="34"/>
     </row>
-    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A125" s="6" t="s">
         <v>149</v>
       </c>
@@ -11777,7 +12764,7 @@
       </c>
       <c r="U125" s="34"/>
     </row>
-    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A126" s="6" t="s">
         <v>143</v>
       </c>
@@ -11839,7 +12826,7 @@
       </c>
       <c r="U126" s="34"/>
     </row>
-    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A127" s="6" t="s">
         <v>301</v>
       </c>
@@ -11905,7 +12892,7 @@
       </c>
       <c r="U127" s="34"/>
     </row>
-    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A128" s="6" t="s">
         <v>305</v>
       </c>
@@ -11971,7 +12958,7 @@
       </c>
       <c r="U128" s="34"/>
     </row>
-    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A129" s="6" t="s">
         <v>145</v>
       </c>
@@ -12037,7 +13024,7 @@
       </c>
       <c r="U129" s="34"/>
     </row>
-    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>308</v>
       </c>
@@ -12103,7 +13090,7 @@
       </c>
       <c r="U130" s="34"/>
     </row>
-    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>309</v>
       </c>
@@ -12169,7 +13156,7 @@
       </c>
       <c r="U131" s="34"/>
     </row>
-    <row r="132" spans="1:21" s="18" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A132" s="14" t="s">
         <v>311</v>
       </c>
@@ -12235,7 +13222,7 @@
       </c>
       <c r="U132" s="34"/>
     </row>
-    <row r="133" spans="1:21" s="18" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A133" s="6" t="s">
         <v>311</v>
       </c>
@@ -12301,7 +13288,7 @@
       </c>
       <c r="U133" s="34"/>
     </row>
-    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A134" s="6" t="s">
         <v>317</v>
       </c>
@@ -12367,7 +13354,7 @@
       </c>
       <c r="U134" s="34"/>
     </row>
-    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>320</v>
       </c>
@@ -12433,7 +13420,7 @@
       </c>
       <c r="U135" s="34"/>
     </row>
-    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
         <v>321</v>
       </c>
@@ -12499,7 +13486,7 @@
       </c>
       <c r="U136" s="34"/>
     </row>
-    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>321</v>
       </c>
@@ -12565,7 +13552,7 @@
       </c>
       <c r="U137" s="34"/>
     </row>
-    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
         <v>322</v>
       </c>
@@ -12631,7 +13618,7 @@
       </c>
       <c r="U138" s="34"/>
     </row>
-    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>323</v>
       </c>
@@ -12697,7 +13684,7 @@
       </c>
       <c r="U139" s="34"/>
     </row>
-    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>324</v>
       </c>
@@ -12763,7 +13750,7 @@
       </c>
       <c r="U140" s="34"/>
     </row>
-    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>326</v>
       </c>
@@ -12829,7 +13816,7 @@
       </c>
       <c r="U141" s="34"/>
     </row>
-    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A142" s="6" t="s">
         <v>328</v>
       </c>
@@ -12895,7 +13882,7 @@
       </c>
       <c r="U142" s="34"/>
     </row>
-    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A143" s="6" t="s">
         <v>331</v>
       </c>
@@ -12961,7 +13948,7 @@
       </c>
       <c r="U143" s="34"/>
     </row>
-    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A144" s="6" t="s">
         <v>333</v>
       </c>
@@ -13027,7 +14014,7 @@
       </c>
       <c r="U144" s="34"/>
     </row>
-    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A145" s="6" t="s">
         <v>335</v>
       </c>
@@ -13093,7 +14080,7 @@
       </c>
       <c r="U145" s="34"/>
     </row>
-    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A146" s="6" t="s">
         <v>140</v>
       </c>
@@ -13159,7 +14146,7 @@
       </c>
       <c r="U146" s="34"/>
     </row>
-    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A147" s="6" t="s">
         <v>140</v>
       </c>
@@ -13225,7 +14212,7 @@
       </c>
       <c r="U147" s="34"/>
     </row>
-    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A148" s="14" t="s">
         <v>58</v>
       </c>
@@ -13291,7 +14278,7 @@
       </c>
       <c r="U148" s="34"/>
     </row>
-    <row r="149" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A149" s="6" t="s">
         <v>344</v>
       </c>
@@ -13359,7 +14346,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="150" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A150" s="6" t="s">
         <v>348</v>
       </c>
@@ -13427,7 +14414,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="151" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A151" s="6" t="s">
         <v>324</v>
       </c>
@@ -13495,7 +14482,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="152" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A152" s="6" t="s">
         <v>350</v>
       </c>
@@ -13563,7 +14550,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="153" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A153" s="6" t="s">
         <v>354</v>
       </c>
@@ -13631,7 +14618,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="154" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A154" s="6" t="s">
         <v>145</v>
       </c>
@@ -13699,7 +14686,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="155" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A155" s="6" t="s">
         <v>359</v>
       </c>
@@ -13767,7 +14754,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="156" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A156" s="6" t="s">
         <v>360</v>
       </c>
@@ -13835,7 +14822,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="157" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A157" s="6" t="s">
         <v>43</v>
       </c>
@@ -13903,7 +14890,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="158" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A158" s="6" t="s">
         <v>362</v>
       </c>
@@ -13971,7 +14958,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="159" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>43</v>
       </c>
@@ -14039,7 +15026,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="160" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>367</v>
       </c>
@@ -14107,7 +15094,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="161" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A161" s="6" t="s">
         <v>369</v>
       </c>
@@ -14175,7 +15162,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="162" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A162" s="6" t="s">
         <v>371</v>
       </c>
@@ -14243,7 +15230,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="163" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A163" s="6" t="s">
         <v>43</v>
       </c>
@@ -14311,7 +15298,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="164" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A164" s="6" t="s">
         <v>374</v>
       </c>
@@ -14379,7 +15366,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="165" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A165" s="6" t="s">
         <v>374</v>
       </c>
@@ -14447,7 +15434,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="166" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A166" s="6" t="s">
         <v>374</v>
       </c>
@@ -14515,7 +15502,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="167" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A167" s="6" t="s">
         <v>374</v>
       </c>
@@ -14583,7 +15570,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="168" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A168" s="6" t="s">
         <v>374</v>
       </c>
@@ -14651,7 +15638,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="169" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A169" s="6" t="s">
         <v>374</v>
       </c>
@@ -14719,7 +15706,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A170" s="6" t="s">
         <v>374</v>
       </c>
@@ -14787,7 +15774,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A171" s="6" t="s">
         <v>374</v>
       </c>
@@ -14855,7 +15842,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="172" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A172" s="6" t="s">
         <v>374</v>
       </c>
@@ -14923,7 +15910,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="173" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A173" s="6" t="s">
         <v>374</v>
       </c>
@@ -14991,7 +15978,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="174" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A174" s="6" t="s">
         <v>374</v>
       </c>
@@ -15059,7 +16046,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="175" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A175" s="6" t="s">
         <v>374</v>
       </c>
@@ -15127,7 +16114,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="176" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A176" s="6" t="s">
         <v>374</v>
       </c>
@@ -15195,7 +16182,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="177" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A177" s="6" t="s">
         <v>374</v>
       </c>
@@ -15263,7 +16250,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="178" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A178" s="6" t="s">
         <v>374</v>
       </c>
@@ -15331,7 +16318,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="179" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A179" s="6" t="s">
         <v>374</v>
       </c>
@@ -15399,7 +16386,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="180" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A180" s="6" t="s">
         <v>408</v>
       </c>
@@ -15467,7 +16454,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="181" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A181" s="14" t="s">
         <v>411</v>
       </c>
@@ -15535,7 +16522,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="182" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A182" s="6" t="s">
         <v>414</v>
       </c>
@@ -15603,7 +16590,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="183" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A183" s="6" t="s">
         <v>416</v>
       </c>
@@ -15671,7 +16658,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="184" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A184" s="6" t="s">
         <v>416</v>
       </c>
@@ -15739,7 +16726,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="185" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>419</v>
       </c>
@@ -15807,7 +16794,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="186" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A186" s="3" t="s">
         <v>421</v>
       </c>
@@ -15875,7 +16862,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="187" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A187" s="6" t="s">
         <v>422</v>
       </c>
@@ -15943,7 +16930,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="188" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A188" s="6" t="s">
         <v>422</v>
       </c>
@@ -16011,7 +16998,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="189" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A189" s="6" t="s">
         <v>428</v>
       </c>
@@ -16079,7 +17066,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="190" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A190" s="6" t="s">
         <v>430</v>
       </c>
@@ -16146,7 +17133,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="191" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A191" s="6" t="s">
         <v>432</v>
       </c>
@@ -16213,7 +17200,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="192" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A192" s="6" t="s">
         <v>432</v>
       </c>
@@ -16280,7 +17267,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="193" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A193" s="6" t="s">
         <v>437</v>
       </c>
@@ -16347,7 +17334,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="194" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A194" s="6" t="s">
         <v>438</v>
       </c>
@@ -16414,7 +17401,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="195" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A195" s="6" t="s">
         <v>439</v>
       </c>
@@ -16481,7 +17468,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="196" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A196" s="6" t="s">
         <v>445</v>
       </c>
@@ -16548,7 +17535,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="197" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A197" s="6" t="s">
         <v>432</v>
       </c>
@@ -16615,7 +17602,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="198" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A198" s="6" t="s">
         <v>134</v>
       </c>
@@ -16682,7 +17669,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="199" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A199" s="6" t="s">
         <v>451</v>
       </c>
@@ -16749,7 +17736,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="200" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A200" s="6" t="s">
         <v>451</v>
       </c>
@@ -16816,7 +17803,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="201" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A201" s="6" t="s">
         <v>134</v>
       </c>
@@ -16883,7 +17870,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="202" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A202" s="6" t="s">
         <v>456</v>
       </c>
@@ -16950,7 +17937,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="203" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A203" s="6" t="s">
         <v>43</v>
       </c>
@@ -17017,7 +18004,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="204" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A204" s="6" t="s">
         <v>459</v>
       </c>
@@ -17084,7 +18071,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="205" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A205" s="6" t="s">
         <v>461</v>
       </c>
@@ -17151,7 +18138,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="206" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A206" s="6" t="s">
         <v>462</v>
       </c>
@@ -17219,7 +18206,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="207" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A207" s="6" t="s">
         <v>451</v>
       </c>
@@ -17287,7 +18274,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="208" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A208" s="6" t="s">
         <v>451</v>
       </c>
@@ -17355,7 +18342,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="209" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A209" s="5" t="s">
         <v>466</v>
       </c>
@@ -17423,7 +18410,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="210" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A210" s="6" t="s">
         <v>469</v>
       </c>
@@ -17491,7 +18478,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="211" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A211" s="6" t="s">
         <v>471</v>
       </c>
@@ -17559,7 +18546,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="212" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>473</v>
       </c>
@@ -17627,7 +18614,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="213" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A213" s="6" t="s">
         <v>120</v>
       </c>
@@ -17695,7 +18682,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="214" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A214" s="6" t="s">
         <v>476</v>
       </c>
@@ -17763,7 +18750,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="215" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A215" s="6" t="s">
         <v>469</v>
       </c>
@@ -17831,7 +18818,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="216" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A216" s="6" t="s">
         <v>58</v>
       </c>
@@ -17899,7 +18886,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="217" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A217" s="6" t="s">
         <v>481</v>
       </c>
@@ -17967,7 +18954,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="218" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>483</v>
       </c>
@@ -18035,7 +19022,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="219" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>484</v>
       </c>
@@ -18103,7 +19090,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="220" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>271</v>
       </c>
@@ -18171,7 +19158,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="221" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A221" s="6" t="s">
         <v>485</v>
       </c>
@@ -18239,7 +19226,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="222" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A222" s="6" t="s">
         <v>172</v>
       </c>
@@ -18307,7 +19294,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="223" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
         <v>489</v>
       </c>
@@ -18375,7 +19362,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="224" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
         <v>492</v>
       </c>
@@ -18443,7 +19430,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="225" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>495</v>
       </c>
@@ -18511,7 +19498,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="226" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>499</v>
       </c>
@@ -18579,7 +19566,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="227" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>502</v>
       </c>
@@ -18647,7 +19634,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="228" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>503</v>
       </c>
@@ -18715,7 +19702,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="229" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>505</v>
       </c>
@@ -18783,7 +19770,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="230" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>506</v>
       </c>
@@ -18851,7 +19838,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="231" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>507</v>
       </c>
@@ -18919,7 +19906,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="232" spans="1:21" s="36" customFormat="1" ht="12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:21" s="36" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>508</v>
       </c>
@@ -18987,7 +19974,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="233" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>509</v>
       </c>
@@ -19054,7 +20041,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="234" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>514</v>
       </c>
@@ -19121,7 +20108,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="235" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A235" s="6" t="s">
         <v>516</v>
       </c>
@@ -19189,7 +20176,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="236" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A236" s="6" t="s">
         <v>516</v>
       </c>
@@ -19257,7 +20244,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="237" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A237" s="6" t="s">
         <v>520</v>
       </c>
@@ -19325,7 +20312,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="238" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A238" s="6" t="s">
         <v>522</v>
       </c>
@@ -19393,7 +20380,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="239" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A239" s="6" t="s">
         <v>524</v>
       </c>
@@ -19461,7 +20448,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="240" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A240" s="6" t="s">
         <v>526</v>
       </c>
@@ -19529,7 +20516,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="241" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A241" s="6" t="s">
         <v>528</v>
       </c>
@@ -19597,7 +20584,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="242" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A242" s="6" t="s">
         <v>528</v>
       </c>
@@ -19665,7 +20652,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="243" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A243" s="6" t="s">
         <v>469</v>
       </c>
@@ -19733,7 +20720,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="244" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A244" s="6" t="s">
         <v>533</v>
       </c>
@@ -19800,7 +20787,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="245" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A245" s="6" t="s">
         <v>535</v>
       </c>
@@ -19867,7 +20854,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="246" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A246" s="6" t="s">
         <v>535</v>
       </c>
@@ -19934,7 +20921,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="247" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A247" s="6" t="s">
         <v>538</v>
       </c>
@@ -20001,7 +20988,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="248" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A248" s="6" t="s">
         <v>459</v>
       </c>
@@ -20068,7 +21055,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="249" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A249" s="6" t="s">
         <v>535</v>
       </c>
@@ -20135,7 +21122,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="250" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A250" s="6" t="s">
         <v>539</v>
       </c>
@@ -20202,7 +21189,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="251" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A251" s="6" t="s">
         <v>535</v>
       </c>
@@ -20269,7 +21256,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="252" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A252" s="6" t="s">
         <v>540</v>
       </c>
@@ -20336,7 +21323,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="253" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A253" s="6" t="s">
         <v>541</v>
       </c>
@@ -20403,7 +21390,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="254" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A254" s="6" t="s">
         <v>43</v>
       </c>
@@ -20470,7 +21457,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="255" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A255" s="6" t="s">
         <v>43</v>
       </c>
@@ -20537,7 +21524,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="256" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A256" s="6" t="s">
         <v>469</v>
       </c>
@@ -20604,7 +21591,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="257" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A257" s="6" t="s">
         <v>547</v>
       </c>
@@ -20671,7 +21658,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="258" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A258" s="6" t="s">
         <v>548</v>
       </c>
@@ -20738,7 +21725,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="259" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A259" s="6" t="s">
         <v>549</v>
       </c>
@@ -20805,7 +21792,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="260" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A260" s="6" t="s">
         <v>553</v>
       </c>
@@ -20872,7 +21859,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="261" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A261" s="6" t="s">
         <v>556</v>
       </c>
@@ -20939,7 +21926,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="262" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A262" s="6" t="s">
         <v>559</v>
       </c>
@@ -21006,7 +21993,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="263" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A263" s="6" t="s">
         <v>43</v>
       </c>
@@ -21073,7 +22060,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="264" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A264" s="6" t="s">
         <v>564</v>
       </c>
@@ -21140,7 +22127,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="265" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A265" s="6" t="s">
         <v>541</v>
       </c>
@@ -21207,7 +22194,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="266" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A266" s="6" t="s">
         <v>567</v>
       </c>
@@ -21274,7 +22261,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="267" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A267" s="6" t="s">
         <v>466</v>
       </c>
@@ -21341,7 +22328,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="268" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A268" s="6" t="s">
         <v>570</v>
       </c>
@@ -21408,7 +22395,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="269" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A269" s="6" t="s">
         <v>91</v>
       </c>
@@ -21475,7 +22462,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="270" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A270" s="6" t="s">
         <v>91</v>
       </c>
@@ -21542,7 +22529,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="271" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A271" s="6" t="s">
         <v>575</v>
       </c>
@@ -21609,7 +22596,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="272" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A272" s="6" t="s">
         <v>576</v>
       </c>
@@ -21676,7 +22663,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="273" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A273" s="6" t="s">
         <v>578</v>
       </c>
@@ -21743,7 +22730,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="274" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A274" s="6" t="s">
         <v>578</v>
       </c>
@@ -21810,7 +22797,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="275" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A275" s="6" t="s">
         <v>582</v>
       </c>
@@ -21878,7 +22865,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="276" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A276" s="6" t="s">
         <v>439</v>
       </c>
@@ -21946,7 +22933,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="277" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A277" s="6" t="s">
         <v>140</v>
       </c>
@@ -22014,7 +23001,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="278" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A278" s="6" t="s">
         <v>439</v>
       </c>
@@ -22082,7 +23069,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="279" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A279" s="6" t="s">
         <v>91</v>
       </c>
@@ -22150,7 +23137,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="280" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A280" s="6" t="s">
         <v>91</v>
       </c>
@@ -22218,7 +23205,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="281" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A281" s="6" t="s">
         <v>374</v>
       </c>
@@ -22286,7 +23273,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="282" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A282" s="6" t="s">
         <v>374</v>
       </c>
@@ -22354,7 +23341,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="283" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A283" s="6" t="s">
         <v>374</v>
       </c>
@@ -22422,7 +23409,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="284" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A284" s="6" t="s">
         <v>596</v>
       </c>
@@ -22490,7 +23477,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="285" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A285" s="6" t="s">
         <v>598</v>
       </c>
@@ -22558,7 +23545,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="286" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A286" s="6" t="s">
         <v>599</v>
       </c>
@@ -22626,7 +23613,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="287" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A287" s="6" t="s">
         <v>600</v>
       </c>
@@ -22694,7 +23681,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="288" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A288" s="6" t="s">
         <v>602</v>
       </c>
@@ -22762,7 +23749,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="289" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A289" s="6" t="s">
         <v>605</v>
       </c>
@@ -22830,7 +23817,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="290" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A290" s="6" t="s">
         <v>605</v>
       </c>
@@ -22898,7 +23885,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="291" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A291" s="14" t="s">
         <v>609</v>
       </c>
@@ -22966,7 +23953,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="292" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A292" s="6" t="s">
         <v>612</v>
       </c>
@@ -23034,7 +24021,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="293" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A293" s="6" t="s">
         <v>354</v>
       </c>
@@ -23102,7 +24089,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="294" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A294" s="5" t="s">
         <v>549</v>
       </c>
@@ -23170,7 +24157,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="295" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A295" s="1" t="s">
         <v>617</v>
       </c>
@@ -23238,7 +24225,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="296" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A296" s="6" t="s">
         <v>612</v>
       </c>
@@ -23306,7 +24293,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="297" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A297" s="6" t="s">
         <v>143</v>
       </c>
@@ -23374,7 +24361,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="298" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A298" s="6" t="s">
         <v>140</v>
       </c>
@@ -23442,7 +24429,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="299" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A299" s="14" t="s">
         <v>622</v>
       </c>
@@ -23510,7 +24497,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="300" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A300" s="6" t="s">
         <v>140</v>
       </c>
@@ -23578,7 +24565,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="301" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A301" s="3" t="s">
         <v>626</v>
       </c>
@@ -23646,7 +24633,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="302" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>628</v>
       </c>
@@ -23714,7 +24701,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="303" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>629</v>
       </c>
@@ -23782,7 +24769,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="304" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A304" s="6" t="s">
         <v>661</v>
       </c>
@@ -23849,7 +24836,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="305" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A305" s="6" t="s">
         <v>658</v>
       </c>
@@ -23916,7 +24903,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="306" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A306" s="6" t="s">
         <v>466</v>
       </c>
@@ -23983,7 +24970,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="307" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A307" s="6" t="s">
         <v>43</v>
       </c>
@@ -24050,7 +25037,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="308" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A308" s="6" t="s">
         <v>641</v>
       </c>
@@ -24117,7 +25104,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="309" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A309" s="6" t="s">
         <v>641</v>
       </c>
@@ -24184,7 +25171,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="310" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A310" s="6" t="s">
         <v>651</v>
       </c>
@@ -24251,7 +25238,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="311" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A311" s="6" t="s">
         <v>172</v>
       </c>
@@ -24318,7 +25305,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="312" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A312" s="6" t="s">
         <v>172</v>
       </c>
@@ -24385,7 +25372,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="313" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A313" s="6" t="s">
         <v>172</v>
       </c>
@@ -24452,7 +25439,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="314" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A314" s="6" t="s">
         <v>172</v>
       </c>
@@ -24519,7 +25506,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="315" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A315" s="6" t="s">
         <v>172</v>
       </c>
@@ -24586,7 +25573,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="316" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A316" s="6" t="s">
         <v>172</v>
       </c>
@@ -24653,7 +25640,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="317" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A317" s="6" t="s">
         <v>91</v>
       </c>
@@ -24720,7 +25707,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="318" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A318" s="6" t="s">
         <v>642</v>
       </c>
@@ -24787,7 +25774,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="319" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A319" s="6" t="s">
         <v>641</v>
       </c>
@@ -24854,7 +25841,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="320" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A320" s="6" t="s">
         <v>639</v>
       </c>
@@ -24921,7 +25908,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="321" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A321" s="6" t="s">
         <v>637</v>
       </c>
@@ -24988,7 +25975,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="322" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A322" s="6" t="s">
         <v>636</v>
       </c>
@@ -25055,7 +26042,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="323" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A323" s="6" t="s">
         <v>172</v>
       </c>
@@ -25122,7 +26109,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="324" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A324" s="6" t="s">
         <v>634</v>
       </c>
@@ -25189,7 +26176,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="325" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A325" s="6" t="s">
         <v>439</v>
       </c>
@@ -25256,7 +26243,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="326" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A326" s="6" t="s">
         <v>172</v>
       </c>
@@ -25323,7 +26310,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="327" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A327" s="6" t="s">
         <v>172</v>
       </c>
@@ -25390,7 +26377,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="328" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A328" s="6" t="s">
         <v>651</v>
       </c>
@@ -25457,7 +26444,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="329" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A329" s="6" t="s">
         <v>666</v>
       </c>
@@ -25760,7 +26747,7 @@
         <v>46146</v>
       </c>
       <c r="J333" s="16">
-        <f t="shared" ref="J333:J396" si="29">+NETWORKDAYS(H333,I333)</f>
+        <f t="shared" ref="J333:J397" si="29">+NETWORKDAYS(H333,I333)</f>
         <v>11</v>
       </c>
       <c r="K333" s="17" t="s">
@@ -25789,7 +26776,7 @@
         <v>46146</v>
       </c>
       <c r="S333" s="16">
-        <f t="shared" ref="S333:S396" si="30">NETWORKDAYS(H333,R333)</f>
+        <f t="shared" ref="S333:S397" si="30">NETWORKDAYS(H333,R333)</f>
         <v>11</v>
       </c>
       <c r="T333" s="5" t="s">
@@ -30056,254 +31043,659 @@
         <v>551</v>
       </c>
     </row>
+    <row r="397" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A397" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="B397" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C397" s="6">
+        <v>62880594</v>
+      </c>
+      <c r="D397" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E397" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="F397" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G397" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H397" s="8">
+        <v>46149</v>
+      </c>
+      <c r="I397" s="8">
+        <v>46150</v>
+      </c>
+      <c r="J397" s="16">
+        <f t="shared" si="29"/>
+        <v>2</v>
+      </c>
+      <c r="K397" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L397" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M397" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N397" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="O397" s="33">
+        <v>0</v>
+      </c>
+      <c r="P397" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q397" s="33">
+        <f>P397+O397</f>
+        <v>0</v>
+      </c>
+      <c r="R397" s="7">
+        <v>46171</v>
+      </c>
+      <c r="S397" s="16">
+        <f t="shared" si="30"/>
+        <v>17</v>
+      </c>
+      <c r="T397" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="U397" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="398" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A398" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="B398" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C398" s="6">
+        <v>62880628</v>
+      </c>
+      <c r="D398" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E398" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="F398" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G398" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H398" s="8">
+        <v>46149</v>
+      </c>
+      <c r="I398" s="8">
+        <v>46150</v>
+      </c>
+      <c r="J398" s="16">
+        <f t="shared" ref="J398:J402" si="35">+NETWORKDAYS(H398,I398)</f>
+        <v>2</v>
+      </c>
+      <c r="K398" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L398" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M398" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N398" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="O398" s="33">
+        <v>0</v>
+      </c>
+      <c r="P398" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q398" s="33">
+        <f>P398+O398</f>
+        <v>0</v>
+      </c>
+      <c r="R398" s="7">
+        <v>46171</v>
+      </c>
+      <c r="S398" s="16">
+        <f t="shared" ref="S398:S402" si="36">NETWORKDAYS(H398,R398)</f>
+        <v>17</v>
+      </c>
+      <c r="T398" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="U398" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="399" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A399" s="62" t="s">
+        <v>787</v>
+      </c>
+      <c r="B399" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="C399" s="64">
+        <v>64009558</v>
+      </c>
+      <c r="D399" s="63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E399" s="62" t="s">
+        <v>788</v>
+      </c>
+      <c r="F399" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="G399" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="H399" s="65">
+        <v>46171</v>
+      </c>
+      <c r="I399" s="65">
+        <v>46171</v>
+      </c>
+      <c r="J399" s="16">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="K399" s="66" t="s">
+        <v>303</v>
+      </c>
+      <c r="L399" s="63" t="s">
+        <v>304</v>
+      </c>
+      <c r="M399" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="N399" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="O399" s="67">
+        <v>0</v>
+      </c>
+      <c r="P399" s="67">
+        <v>0</v>
+      </c>
+      <c r="Q399" s="67">
+        <f>P399+O399</f>
+        <v>0</v>
+      </c>
+      <c r="R399" s="68">
+        <v>46171</v>
+      </c>
+      <c r="S399" s="16">
+        <f t="shared" si="36"/>
+        <v>1</v>
+      </c>
+      <c r="T399" s="63" t="s">
+        <v>769</v>
+      </c>
+      <c r="U399" s="63" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="400" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A400" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="B400" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C400" s="3">
+        <v>62682536</v>
+      </c>
+      <c r="D400" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="E400" s="3">
+        <v>2722560160</v>
+      </c>
+      <c r="F400" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G400" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H400" s="10">
+        <v>46146</v>
+      </c>
+      <c r="I400" s="8">
+        <v>46170</v>
+      </c>
+      <c r="J400" s="16">
+        <f t="shared" si="35"/>
+        <v>19</v>
+      </c>
+      <c r="K400" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L400" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="M400" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N400" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="O400" s="33">
+        <v>150000</v>
+      </c>
+      <c r="P400" s="33">
+        <v>60000</v>
+      </c>
+      <c r="Q400" s="33">
+        <f>P400+O400</f>
+        <v>210000</v>
+      </c>
+      <c r="R400" s="7">
+        <v>46171</v>
+      </c>
+      <c r="S400" s="16">
+        <f t="shared" si="36"/>
+        <v>20</v>
+      </c>
+      <c r="T400" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="U400" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="401" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A401" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="B401" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C401" s="3">
+        <v>62348771</v>
+      </c>
+      <c r="D401" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E401" s="3">
+        <v>2722496350</v>
+      </c>
+      <c r="F401" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G401" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H401" s="8">
+        <v>46139</v>
+      </c>
+      <c r="I401" s="8">
+        <v>46170</v>
+      </c>
+      <c r="J401" s="16">
+        <f t="shared" si="35"/>
+        <v>24</v>
+      </c>
+      <c r="K401" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L401" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M401" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N401" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="O401" s="33">
+        <v>400000</v>
+      </c>
+      <c r="P401" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q401" s="33">
+        <f>P401+O401</f>
+        <v>400000</v>
+      </c>
+      <c r="R401" s="7">
+        <v>46171</v>
+      </c>
+      <c r="S401" s="16">
+        <f t="shared" si="36"/>
+        <v>25</v>
+      </c>
+      <c r="T401" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="U401" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="402" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A402" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="B402" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C402" s="6">
+        <v>63330974</v>
+      </c>
+      <c r="D402" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E402" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="F402" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G402" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H402" s="8">
+        <v>46157</v>
+      </c>
+      <c r="I402" s="8">
+        <v>46172</v>
+      </c>
+      <c r="J402" s="16">
+        <f t="shared" si="35"/>
+        <v>11</v>
+      </c>
+      <c r="K402" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L402" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="M402" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="N402" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="O402" s="33">
+        <v>0</v>
+      </c>
+      <c r="P402" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q402" s="33">
+        <f>P402+O402</f>
+        <v>0</v>
+      </c>
+      <c r="R402" s="7">
+        <v>46171</v>
+      </c>
+      <c r="S402" s="16">
+        <f t="shared" si="36"/>
+        <v>11</v>
+      </c>
+      <c r="T402" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="U402" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U395" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="17">
-      <filters>
-        <dateGroupItem year="2026" month="5" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:U402" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="92" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="89"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C356:C357 C363:C370 C385:C1048576">
-    <cfRule type="duplicateValues" dxfId="86" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="181"/>
+  <conditionalFormatting sqref="C1:C205 C244:C287 C304:C329 C356:C357 C363:C370 C385:C396 C403:C1048576">
+    <cfRule type="duplicateValues" dxfId="180" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="181"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C356:C357 C363:C370 C385:C1048576">
-    <cfRule type="duplicateValues" dxfId="84" priority="190"/>
+  <conditionalFormatting sqref="C1:C212 C244:C287 C304:C329 C356:C357 C363:C370 C385:C396 C403:C1048576">
+    <cfRule type="duplicateValues" dxfId="178" priority="191"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C232 C244:C287 C304:C329 C356:C357 C363:C370 C385:C1048576">
-    <cfRule type="duplicateValues" dxfId="83" priority="195"/>
+  <conditionalFormatting sqref="C1:C232 C244:C287 C304:C329 C356:C357 C363:C370 C385:C396 C403:C1048576">
+    <cfRule type="duplicateValues" dxfId="177" priority="196"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C294 C304:C329 C356:C357 C363:C370 C385:C1048576">
-    <cfRule type="duplicateValues" dxfId="82" priority="200"/>
+  <conditionalFormatting sqref="C1:C294 C304:C329 C356:C357 C363:C370 C385:C396 C403:C1048576">
+    <cfRule type="duplicateValues" dxfId="176" priority="201"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C295 C304:C329 C356:C357 C363:C370 C385:C1048576">
-    <cfRule type="duplicateValues" dxfId="81" priority="176"/>
+  <conditionalFormatting sqref="C1:C295 C304:C329 C356:C357 C363:C370 C385:C396 C403:C1048576">
+    <cfRule type="duplicateValues" dxfId="175" priority="177"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C370 C385:C1048576">
-    <cfRule type="duplicateValues" dxfId="80" priority="4"/>
+  <conditionalFormatting sqref="C1:C370 C385:C396 C403:C1048576">
+    <cfRule type="duplicateValues" dxfId="174" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C396 C403:C1048576">
+    <cfRule type="duplicateValues" dxfId="173" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C15 C17:C31">
+    <cfRule type="duplicateValues" dxfId="172" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C58">
+    <cfRule type="duplicateValues" dxfId="170" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C70">
+    <cfRule type="duplicateValues" dxfId="168" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="duplicateValues" dxfId="167" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="duplicateValues" dxfId="165" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="duplicateValues" dxfId="164" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12">
+    <cfRule type="duplicateValues" dxfId="163" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15">
+    <cfRule type="duplicateValues" dxfId="162" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16">
+    <cfRule type="duplicateValues" dxfId="161" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:C31">
+    <cfRule type="duplicateValues" dxfId="160" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32">
+    <cfRule type="duplicateValues" dxfId="159" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C33:C37">
+    <cfRule type="duplicateValues" dxfId="158" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C39">
+    <cfRule type="duplicateValues" dxfId="157" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40">
+    <cfRule type="duplicateValues" dxfId="156" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C47">
+    <cfRule type="duplicateValues" dxfId="155" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C59:C66">
+    <cfRule type="duplicateValues" dxfId="154" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C73">
+    <cfRule type="duplicateValues" dxfId="153" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C75">
+    <cfRule type="duplicateValues" dxfId="152" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C77">
+    <cfRule type="duplicateValues" dxfId="151" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C77:C109 C1">
+    <cfRule type="duplicateValues" dxfId="150" priority="95"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C78">
+    <cfRule type="duplicateValues" dxfId="149" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C80:C81">
+    <cfRule type="duplicateValues" dxfId="148" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C85">
+    <cfRule type="duplicateValues" dxfId="147" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C92">
+    <cfRule type="duplicateValues" dxfId="145" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C93">
+    <cfRule type="duplicateValues" dxfId="144" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C98">
+    <cfRule type="duplicateValues" dxfId="143" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C101">
+    <cfRule type="duplicateValues" dxfId="142" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C102">
+    <cfRule type="duplicateValues" dxfId="141" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C103:C109">
+    <cfRule type="duplicateValues" dxfId="139" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C114">
+    <cfRule type="duplicateValues" dxfId="138" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C115">
+    <cfRule type="duplicateValues" dxfId="137" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C145">
+    <cfRule type="duplicateValues" dxfId="136" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C157:C160">
+    <cfRule type="duplicateValues" dxfId="134" priority="101"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C161:C163">
+    <cfRule type="duplicateValues" dxfId="133" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C166">
+    <cfRule type="duplicateValues" dxfId="132" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C167">
+    <cfRule type="duplicateValues" dxfId="130" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C168">
+    <cfRule type="duplicateValues" dxfId="128" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C170">
+    <cfRule type="duplicateValues" dxfId="127" priority="33"/>
+  </conditionalFormatting>
+  <